--- a/docs/Bugs.xlsx
+++ b/docs/Bugs.xlsx
@@ -8,13 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Msi\projects\SDLC-App\AI-First-SDLC-App\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{98A39E8F-279E-4CEE-AD96-32237FF0191F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91E28B2A-9AB7-418D-9539-899C5EA95623}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{F2A77115-FBCF-40F3-AB9C-91EDA042E1D8}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$E$1:$E$4</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -25,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="44">
   <si>
     <t>S.No</t>
   </si>
@@ -42,9 +45,6 @@
     <t>Reference</t>
   </si>
   <si>
-    <t xml:space="preserve">Showing 'Welcome back to Acme Corp.' </t>
-  </si>
-  <si>
     <t>Description</t>
   </si>
   <si>
@@ -52,6 +52,129 @@
   </si>
   <si>
     <t>Fix Implemented</t>
+  </si>
+  <si>
+    <t>Login</t>
+  </si>
+  <si>
+    <t>Hardcoded 'Welcome back to Acme Corp.' in Login Page</t>
+  </si>
+  <si>
+    <t>Type</t>
+  </si>
+  <si>
+    <t>Bug</t>
+  </si>
+  <si>
+    <t>Show place holders in all the Forms</t>
+  </si>
+  <si>
+    <t>Enhancement</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> email field: showing an email' sarah@acme.com' by default</t>
+  </si>
+  <si>
+    <t>In the login page, an email is shown by default. User has to remove it and provide the email</t>
+  </si>
+  <si>
+    <t>Showing default values in Signup form</t>
+  </si>
+  <si>
+    <t>In the Signup page,  default values are shown. User has to remove it and provide the details</t>
+  </si>
+  <si>
+    <t>Showing 'payment Gateway v2' in navigation bar by default after first login</t>
+  </si>
+  <si>
+    <t>Priority</t>
+  </si>
+  <si>
+    <t>P1</t>
+  </si>
+  <si>
+    <t>P2</t>
+  </si>
+  <si>
+    <t>P3</t>
+  </si>
+  <si>
+    <t>Showing tick mark for Create project in get started page wirhout created in project after first login</t>
+  </si>
+  <si>
+    <t>Showing a default project name 'payment Gateway v2' in create project page</t>
+  </si>
+  <si>
+    <t>Signup</t>
+  </si>
+  <si>
+    <t>Initial project setup</t>
+  </si>
+  <si>
+    <t>Remove the text 'Greenfield starts from a blank profile. Brownfield opens onboarding to assess what already exists.' in create project page and instead show a tool tip for track</t>
+  </si>
+  <si>
+    <t>project profile</t>
+  </si>
+  <si>
+    <t>Frontend: TypeScript 5.x (Strict Mode enabled)
+Frontend Framework: Next.js 14 (App Router; SSR for doctor discovery &amp; SEO, CSR for appointment flow and dashboards)
+Backend: Python 3.12
+Backend Framework: Django 5.x + Django REST Framework (DRF) 3.15
+UI Library: Tailwind CSS 3.x (Utility-first; desktop-first breakpoints)
+Database: PostgreSQL 16 (Primary database with UUID primary keys)
+State Management: TBD (To be determined by the Architecture Agent)
+Cache: Redis 7.x (Sessions, slot availability cache with 5-minute TTL, rate limiting)
+PDF Generation: TBD (To be determined by the Architecture Agent)
+Email Service: SendGrid (Latest version; appointment confirmations, prescription delivery, reminders)
+Cloud Provider: AWS
+Object Storage: AWS S3 (Health record uploads and generated prescription PDFs)
+Content Delivery Network (CDN): AWS CloudFront (Static assets and S3-served documents)
+Compute Platform: AWS ECS (Fargate) (Containerized deployment with separate frontend and backend services)</t>
+  </si>
+  <si>
+    <t>Tech stack text field/box should be large to fit in user input. The input present in the reference column is not fitting in the current text box</t>
+  </si>
+  <si>
+    <t>Showing '✓ Saved · v1' in project profile page(top) after adiing the project details in 'create project' page. Also showing 'Saving will create v2' at the bottom of the form after entering the details</t>
+  </si>
+  <si>
+    <t>In the Get started page, Create your first project-&gt;Connect your machine-&gt;Invite your team-&gt;Connect integrations are present like steps. But in the flow, after creating the project, it navigates to project profile. After saving details in project profile, the data gets saved. How will user completes the next steps?</t>
+  </si>
+  <si>
+    <t>Design Issue</t>
+  </si>
+  <si>
+    <t>Why is the API
+'http://localhost:8000/api/runners/' being called continuosly in all the UI screens?</t>
+  </si>
+  <si>
+    <t>Clarification</t>
+  </si>
+  <si>
+    <t>Copy option is not visible for Token generation in Connect your machine page. Also, the copy option is not working in that page</t>
+  </si>
+  <si>
+    <t>Connect machine</t>
+  </si>
+  <si>
+    <t>Hardcoded 'https://app.acme.com' in run the commands for connect machine</t>
+  </si>
+  <si>
+    <t>Showing two loaders with the text '
+Waiting for first check-in — run the command above…' after generating token on connect machine page</t>
+  </si>
+  <si>
+    <t>Fixed</t>
+  </si>
+  <si>
+    <t>When clicked on create wok item, a form opened. The design is not good. Some grey backgroud is shown and the form is on th eright side. Attached image in Refecrence.Need to redesign it</t>
+  </si>
+  <si>
+    <t>Work Item</t>
+  </si>
+  <si>
+    <t>Title is mandatory in the create work Item not optional</t>
   </si>
 </sst>
 </file>
@@ -75,12 +198,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -95,9 +224,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -113,6 +248,160 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>127000</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>25400</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>3530600</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>2303105</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Picture 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{97D575C0-8328-1E40-2F3B-9E4F264013B2}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7607300" y="577850"/>
+          <a:ext cx="3403600" cy="2277705"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>1</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>35046</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>3417795</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>1543921</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="Picture 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{397F8390-89EE-E402-53AC-D9D811EA5729}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7489266" y="3639605"/>
+          <a:ext cx="3417794" cy="1508875"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>1</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>3587193</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>1147740</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="8" name="Picture 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BDE242B9-D13B-31AB-8F09-86E97908444C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7486316" y="19551317"/>
+          <a:ext cx="3587193" cy="1147456"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -412,48 +701,297 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1558133E-8F2D-496A-BE74-D0F55F6404BE}">
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:J18"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="25.90625" customWidth="1"/>
-    <col min="3" max="3" width="30.453125" customWidth="1"/>
-    <col min="4" max="4" width="25.453125" customWidth="1"/>
-    <col min="5" max="7" width="28" customWidth="1"/>
-    <col min="8" max="8" width="40.36328125" customWidth="1"/>
+    <col min="2" max="2" width="25.90625" style="3" customWidth="1"/>
+    <col min="3" max="3" width="40" style="3" customWidth="1"/>
+    <col min="4" max="4" width="16.08984375" customWidth="1"/>
+    <col min="5" max="5" width="16.36328125" customWidth="1"/>
+    <col min="6" max="6" width="52.81640625" customWidth="1"/>
+    <col min="7" max="7" width="11.6328125" customWidth="1"/>
+    <col min="8" max="9" width="28" customWidth="1"/>
+    <col min="10" max="10" width="40.36328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>6</v>
+      <c r="C1" s="2" t="s">
+        <v>5</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="J1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="29" x14ac:dyDescent="0.35">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" t="s">
         <v>8</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="E2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="182.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="29" x14ac:dyDescent="0.35">
+      <c r="A4">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="B2" t="s">
-        <v>5</v>
+      <c r="B4" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="29" x14ac:dyDescent="0.35">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D5" t="s">
+        <v>25</v>
+      </c>
+      <c r="E5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="123.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B6" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D6" t="s">
+        <v>26</v>
+      </c>
+      <c r="E6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G6" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+      <c r="B7" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D7" t="s">
+        <v>26</v>
+      </c>
+      <c r="E7" t="s">
+        <v>11</v>
+      </c>
+      <c r="G7" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="B8" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D8" t="s">
+        <v>26</v>
+      </c>
+      <c r="E8" t="s">
+        <v>11</v>
+      </c>
+      <c r="G8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="101.5" x14ac:dyDescent="0.35">
+      <c r="B9" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D9" t="s">
+        <v>26</v>
+      </c>
+      <c r="E9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G9" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="101.5" x14ac:dyDescent="0.35">
+      <c r="B10" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D10" t="s">
+        <v>28</v>
+      </c>
+      <c r="E10" t="s">
+        <v>11</v>
+      </c>
+      <c r="G10" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="362.5" x14ac:dyDescent="0.35">
+      <c r="B11" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D11" t="s">
+        <v>28</v>
+      </c>
+      <c r="E11" t="s">
+        <v>11</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" ht="174" x14ac:dyDescent="0.35">
+      <c r="B12" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D12" t="s">
+        <v>26</v>
+      </c>
+      <c r="E12" t="s">
+        <v>33</v>
+      </c>
+      <c r="G12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="B13" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="E13" t="s">
+        <v>35</v>
+      </c>
+      <c r="G13" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="B14" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="D14" t="s">
+        <v>37</v>
+      </c>
+      <c r="E14" t="s">
+        <v>11</v>
+      </c>
+      <c r="G14" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+      <c r="B15" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="D15" t="s">
+        <v>37</v>
+      </c>
+      <c r="E15" t="s">
+        <v>11</v>
+      </c>
+      <c r="G15" t="s">
+        <v>20</v>
+      </c>
+      <c r="J15" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" ht="87" x14ac:dyDescent="0.35">
+      <c r="B16" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="D16" t="s">
+        <v>37</v>
+      </c>
+      <c r="E16" t="s">
+        <v>11</v>
+      </c>
+      <c r="G16" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="17" spans="2:5" ht="116" x14ac:dyDescent="0.35">
+      <c r="B17" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="D17" t="s">
+        <v>42</v>
+      </c>
+      <c r="E17" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="18" spans="2:5" ht="29" x14ac:dyDescent="0.35">
+      <c r="B18" s="3" t="s">
+        <v>43</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/docs/Bugs.xlsx
+++ b/docs/Bugs.xlsx
@@ -705,7 +705,22 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>The login page's email box was pre-filled with a sample address, sarah@acme.com, so a returning user had to clear it before typing their own email.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Made the email box start empty with an example hint ('you@company.com'), matching the signup form. Re-prioritised from P2 to P1 on team request so it ships with the sibling Login fix (row for 'Welcome back to Acme Corp.'). (Login.tsx line 19 and the email input.)</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
     </row>

--- a/docs/Bugs.xlsx
+++ b/docs/Bugs.xlsx
@@ -1413,10 +1413,20 @@
       <c r="G17" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="H17" s="2"/>
-      <c r="I17" s="2"/>
-      <c r="J17" s="2" t="s">
-        <v>64</v>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The shared Drawer and Modal building blocks were originally written as flat 'gallery' swatches for the design catalogue - their styling sat inside the page instead of floating above it, which is why opening the Create work item / Invite / Integrations form showed a grey block wedged into the page with the form squashed to the right, and the X and clicking outside did nothing.</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rebuilt Drawer and Modal as real overlays: a proper dimmed backdrop over the whole page with the form panel above it, and the X, a click on the dimmed area, and the Esc key all close it. Fixed once at the shared-component level so all three screens (Create work item, Invite user, Integrations connect forms) are corrected together. The Integrations connect screen, which is a full page rather than a pop-over, now shows a clean centred card instead of the grey right-floated block. frontend/src/components/ui/index.tsx (Drawer, Modal) + styles/components.css (.scrim-overlay). All 190 frontend tests pass.</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fixed</t>
+        </is>
       </c>
     </row>
     <row r="18" spans="1:10" ht="29" customHeight="1" x14ac:dyDescent="0.35">
@@ -1436,10 +1446,20 @@
       <c r="G18" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="H18" s="2"/>
-      <c r="I18" s="2"/>
-      <c r="J18" s="2" t="s">
-        <v>64</v>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The Create work item form marked Title as optional; the reporter wants it required. Separately, the Type field had no explanation of what Epic/Story/Task/Defect mean.</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Title is now required: the field is marked with * and the Create button stays disabled until a title is entered. Added a tooltip/hint on the Type field explaining each type (Epic/Story = plan tier, Task = build tier, Defect = remediation) - this also closes the type-tooltip enhancement noted under the Work Item lifecycle row. frontend/src/features/lifecycle/WorkItemsBoard.tsx.</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fixed</t>
+        </is>
       </c>
     </row>
     <row r="19" spans="1:10" ht="188.5" x14ac:dyDescent="0.35">
@@ -1499,8 +1519,20 @@
       <c r="G21" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="J21" s="2" t="s">
-        <v>64</v>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The invite form hard-coded only four roles and showed them as raw keys like 'product_owner' (with the underscore), and once you added a role row with 'grant another role' there was no way to remove it.</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The role dropdown now lists the full set of ten roles from one shared source, every role shows a human-readable label (Product Owner, Security Engineer, ...) with no underscores, and each granted-role row has an X to remove it (shown whenever there's more than one). The same labels are used wherever a user's roles are listed. New shared list frontend/src/features/identity/roles.ts; UsersInvites.tsx; tests in roles.test.ts.</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fixed</t>
+        </is>
       </c>
     </row>
     <row r="22" spans="1:10" ht="409.5" x14ac:dyDescent="0.35">
@@ -1519,8 +1551,20 @@
       <c r="G22" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="J22" s="2" t="s">
-        <v>64</v>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Several issues on the work-item lifecycle screen. (i) The rail listed brownfield/onboarding phases (context bridge, context extraction, on-boarding) that don't belong on a normal work item, and phase names showed with underscores/number prefixes. (ii) A Story (or any non-Epic) still showed 'Epic' because the screen hard-coded that word. (iv) The run console showed nothing because run events are stored with an 'action' + 'payload' but the console reads 'kind' and 'message', which weren't being sent - so every line rendered blank. (v) Re-running a failed phase sent the run's internal id (a UUID) where the system expects the short phase key, producing 'no AgentSpec registered for key &lt;uuid&gt;', and a failed run gave no reason.</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(i) Phase names are now human-readable everywhere (Task Breakdown, Architecture, ...) and the brownfield/onboarding phases are hidden from a work item's rail - a display-only filter, no change to orchestration (as agreed with the team). (ii) The type badge and headings now show the work item's real type. (iv) Run events now carry a colour ('kind') and a readable 'message' from the action + payload, so the console shows progress - verified live on a real run, e.g. 'Phase dispatched - ideation' and 'Run failed - Command failed with exit code 1'. (v) Re-run now sends the phase key, not the UUID; verified live with the exact id from the report (d32f5ced-...): the UUID reproduces the error, the key '01_ideation' starts a run cleanly. A failed run now shows the actual reason. (iii, type tooltip, was an enhancement and is also done - see the 'Title is mandatory' row.) Files: frontend lifecycle/phases.ts, WorkItemEpic/Task/Defect.tsx, PhasesAndRuns.tsx, RunConsole.tsx, observability/OfflineTakeover.tsx, RunTranscriptScreen.tsx; backend api/serializers.py (RunSerializer agent_key/agent_phase, EventSerializer kind/message).</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fixed</t>
+        </is>
       </c>
     </row>
     <row r="23" spans="1:10" ht="409.5" x14ac:dyDescent="0.35">
@@ -1539,8 +1583,20 @@
       <c r="G23" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="J23" s="2" t="s">
-        <v>64</v>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Artifacts generated by a phase are registered as internal drafts with the draft text stored inline in the artifact's external_ref.body field and an empty s3_key (the agent hadn't staged a snapshot to object storage). The Preview endpoint only knew how to fetch a body from s3_key, so for these drafts it found nothing and returned 'artifact has no body to preview' even though the text was sitting right there in external_ref.body.</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Taught the preview read-through to also read an internal draft's body from external_ref.body when there is no s3_key yet, choosing the content type from the draft's 'format'. Nothing is copied or stored anywhere new - it's read where it already lives, so tenant isolation and 'platform owns state, not content' are untouched. Verified LIVE on the exact artifact from the report (08efb4c5-...-a232e): it previously 404'd and now returns its 5,834-character markdown body. On MinIO: the local object store container is up and healthy, and artifacts that DO have an s3_key still preview from S3 as before - both paths work. backend/integrations/preview.py (_read_internal); regression test test_preview_internal_artifact_reads_inline_external_ref_body.</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fixed</t>
+        </is>
       </c>
     </row>
     <row r="24" spans="1:10" ht="58" x14ac:dyDescent="0.35">
@@ -1579,8 +1635,20 @@
       <c r="G25" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="J25" s="2" t="s">
-        <v>64</v>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">When a clarification question offered an 'Other (please specify)' choice, picking it gave the user nowhere to type the specifics, and the literal option text would have been sent as the answer.</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Selecting an 'Other / please specify' style option now reveals a text box, and what the user types is submitted as the answer (an empty box counts as unanswered so a required question still blocks). frontend/src/features/lifecycle/Clarifications.tsx.</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fixed</t>
+        </is>
       </c>
     </row>
     <row r="26" spans="1:10" ht="145" x14ac:dyDescent="0.35">
@@ -1599,8 +1667,20 @@
       <c r="G26" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="J26" s="2" t="s">
-        <v>64</v>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">When registering generated artifacts the agent raised a clarification asking the user for the project id, which the user can't know. The registration tool required project_id (and run_id) as inputs, so if the agent didn't have them it asked.</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The platform now binds the project id and run id from the run the phase is executing under (the same way the tenant is already bound), so artifact registration fills them in automatically and never asks the user. Done on both the live companion path and the server-side path. runner/companion/state_mcp.py + runner.py (RUNNER_PROJECT_ID), mcp_platform_state/server.py + backend/orchestration/activities.py (PLATFORM_PROJECT_ID/RUN_ID).</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fixed</t>
+        </is>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.35">

--- a/docs/Bugs.xlsx
+++ b/docs/Bugs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Msi\projects\SDLC-App\AI-First-SDLC-App\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEC72D5E-88D7-4CFC-94FB-0695301C0DE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37F27ECA-6C01-47A3-B7E3-88ECE724B660}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="98">
   <si>
     <t>S.No</t>
   </si>
@@ -298,6 +298,92 @@
   </si>
   <si>
     <t>Clarifications</t>
+  </si>
+  <si>
+    <t>The shared Drawer and Modal building blocks were originally written as flat 'gallery' swatches for the design catalogue - their styling sat inside the page instead of floating above it, which is why opening the Create work item / Invite / Integrations form showed a grey block wedged into the page with the form squashed to the right, and the X and clicking outside did nothing.</t>
+  </si>
+  <si>
+    <t>Rebuilt Drawer and Modal as real overlays: a proper dimmed backdrop over the whole page with the form panel above it, and the X, a click on the dimmed area, and the Esc key all close it. Fixed once at the shared-component level so all three screens (Create work item, Invite user, Integrations connect forms) are corrected together. The Integrations connect screen, which is a full page rather than a pop-over, now shows a clean centred card instead of the grey right-floated block. frontend/src/components/ui/index.tsx (Drawer, Modal) + styles/components.css (.scrim-overlay). All 190 frontend tests pass.</t>
+  </si>
+  <si>
+    <t>The Create work item form marked Title as optional; the reporter wants it required. Separately, the Type field had no explanation of what Epic/Story/Task/Defect mean.</t>
+  </si>
+  <si>
+    <t>Title is now required: the field is marked with * and the Create button stays disabled until a title is entered. Added a tooltip/hint on the Type field explaining each type (Epic/Story = plan tier, Task = build tier, Defect = remediation) - this also closes the type-tooltip enhancement noted under the Work Item lifecycle row. frontend/src/features/lifecycle/WorkItemsBoard.tsx.</t>
+  </si>
+  <si>
+    <t>The invite form hard-coded only four roles and showed them as raw keys like 'product_owner' (with the underscore), and once you added a role row with 'grant another role' there was no way to remove it.</t>
+  </si>
+  <si>
+    <t>The role dropdown now lists the full set of ten roles from one shared source, every role shows a human-readable label (Product Owner, Security Engineer, ...) with no underscores, and each granted-role row has an X to remove it (shown whenever there's more than one). The same labels are used wherever a user's roles are listed. New shared list frontend/src/features/identity/roles.ts; UsersInvites.tsx; tests in roles.test.ts.</t>
+  </si>
+  <si>
+    <t>Several issues on the work-item lifecycle screen. (i) The rail listed brownfield/onboarding phases (context bridge, context extraction, on-boarding) that don't belong on a normal work item, and phase names showed with underscores/number prefixes. (ii) A Story (or any non-Epic) still showed 'Epic' because the screen hard-coded that word. (iv) The run console showed nothing because run events are stored with an 'action' + 'payload' but the console reads 'kind' and 'message', which weren't being sent - so every line rendered blank. (v) Re-running a failed phase sent the run's internal id (a UUID) where the system expects the short phase key, producing 'no AgentSpec registered for key &lt;uuid&gt;', and a failed run gave no reason.</t>
+  </si>
+  <si>
+    <t>(i) Phase names are now human-readable everywhere (Task Breakdown, Architecture, ...) and the brownfield/onboarding phases are hidden from a work item's rail - a display-only filter, no change to orchestration (as agreed with the team). (ii) The type badge and headings now show the work item's real type. (iv) Run events now carry a colour ('kind') and a readable 'message' from the action + payload, so the console shows progress - verified live on a real run, e.g. 'Phase dispatched - ideation' and 'Run failed - Command failed with exit code 1'. (v) Re-run now sends the phase key, not the UUID; verified live with the exact id from the report (d32f5ced-...): the UUID reproduces the error, the key '01_ideation' starts a run cleanly. A failed run now shows the actual reason. (iii, type tooltip, was an enhancement and is also done - see the 'Title is mandatory' row.) Files: frontend lifecycle/phases.ts, WorkItemEpic/Task/Defect.tsx, PhasesAndRuns.tsx, RunConsole.tsx, observability/OfflineTakeover.tsx, RunTranscriptScreen.tsx; backend api/serializers.py (RunSerializer agent_key/agent_phase, EventSerializer kind/message).</t>
+  </si>
+  <si>
+    <t>Artifacts generated by a phase are registered as internal drafts with the draft text stored inline in the artifact's external_ref.body field and an empty s3_key (the agent hadn't staged a snapshot to object storage). The Preview endpoint only knew how to fetch a body from s3_key, so for these drafts it found nothing and returned 'artifact has no body to preview' even though the text was sitting right there in external_ref.body.</t>
+  </si>
+  <si>
+    <t>Taught the preview read-through to also read an internal draft's body from external_ref.body when there is no s3_key yet, choosing the content type from the draft's 'format'. Nothing is copied or stored anywhere new - it's read where it already lives, so tenant isolation and 'platform owns state, not content' are untouched. Verified LIVE on the exact artifact from the report (08efb4c5-...-a232e): it previously 404'd and now returns its 5,834-character markdown body. On MinIO: the local object store container is up and healthy, and artifacts that DO have an s3_key still preview from S3 as before - both paths work. backend/integrations/preview.py (_read_internal); regression test test_preview_internal_artifact_reads_inline_external_ref_body.</t>
+  </si>
+  <si>
+    <t>When a clarification question offered an 'Other (please specify)' choice, picking it gave the user nowhere to type the specifics, and the literal option text would have been sent as the answer.</t>
+  </si>
+  <si>
+    <t>Selecting an 'Other / please specify' style option now reveals a text box, and what the user types is submitted as the answer (an empty box counts as unanswered so a required question still blocks). frontend/src/features/lifecycle/Clarifications.tsx.</t>
+  </si>
+  <si>
+    <t>When registering generated artifacts the agent raised a clarification asking the user for the project id, which the user can't know. The registration tool required project_id (and run_id) as inputs, so if the agent didn't have them it asked.</t>
+  </si>
+  <si>
+    <t>The platform now binds the project id and run id from the run the phase is executing under (the same way the tenant is already bound), so artifact registration fills them in automatically and never asks the user. Done on both the live companion path and the server-side path. runner/companion/state_mcp.py + runner.py (RUNNER_PROJECT_ID), mcp_platform_state/server.py + backend/orchestration/activities.py (PLATFORM_PROJECT_ID/RUN_ID).</t>
+  </si>
+  <si>
+    <t>Work Items
+1. In work items board all the trigger phases are not present in a perfect SDLC order - only 4 trigger phases are shown - Need to fix it
+2. In work item cards, when a phase is in waiting for gate approval, phase clarification - the card design is disturbed and not looking good appealing the user. Any unse of underscore names should also be humanised and readable.</t>
+  </si>
+  <si>
+    <t>Work item</t>
+  </si>
+  <si>
+    <t>Workspace Dashboard
+1. In the "Needs me" section all the info regarding - pending gates, clarifications and running work items etc should be human readable (currently underscores are been used) - need to fix. 
+Reference: Refer to the designs screen S31 in docs/designs
+2. Some values are hardcoded in the work space dashboard Navigation bar and side bar - namely: Notification icon showing 4 by default, clarifications showing 3 by default and gates showing one by default. Need to fix them.</t>
+  </si>
+  <si>
+    <t>Work Space Dashboard</t>
+  </si>
+  <si>
+    <t>Universal SDLC Application Flow Fixes needed - V1:
+1. In the SDLC app user flow: Wherever there is a usage of underscores for the names representation, thise should be human readable.
+2. In the application flow wherever you find a hardcoded value that should have been dynamic - you have to make them dynamic.</t>
+  </si>
+  <si>
+    <t>Universal</t>
+  </si>
+  <si>
+    <t>Work Space Admin</t>
+  </si>
+  <si>
+    <t>Workspace Admin Page
+1. Currently the users who are registered and invited are not been shown, but when clicked on the invite button it is showing in the background. Need to propely fix this
+2. The hardcoded "Acme Corp workspace" is shown but it should be dynamic as per registered work space.</t>
+  </si>
+  <si>
+    <t>After initial sign in, the get started page is shown for the user to set up his complete the 4 step process: During that process if the user clicks on "connect machine", "invite users" and "integrations" it takes the respective page and the user will see a button or link as "Back to get started" as option, once user does the 4 step process and then goes to any one of the above screens, it shows the same "back to get started" option even though the user has completed the on-borading process.</t>
+  </si>
+  <si>
+    <t>General issue</t>
+  </si>
+  <si>
+    <t>Artifacts &amp; Traceability
+1. The generated phase artifacts are Markdown files and the application is showing the preview as markdown text not a rendered markdwon file. In some cases when a architecure diagram present then it wont be human understandable Need to fix the rendering
+2. When artifacts are generated for a work item, if the same work item phase is run again: The artifacts are duplicated with same v1 as version instead of v2 and when clicked on preview it showing versions a v1 for both not v1 and v2 etc.</t>
   </si>
 </sst>
 </file>
@@ -674,6 +760,306 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>3673039</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>1796213</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="Picture 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3B2D494A-C781-F33D-1FB1-5E4C871A6036}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7470588" y="44138725"/>
+          <a:ext cx="3673039" cy="1796213"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>1</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>4026</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>1739347</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="11" name="Picture 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4B6CCA93-20F1-AEC4-0D2F-70053E9D32B3}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7468153" y="47252283"/>
+          <a:ext cx="3689786" cy="1739347"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>1</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>3672703</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>1762444</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="13" name="Picture 12">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A4F375C2-42D0-71E6-F0E4-A815E3E01DE3}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7482704" y="49581486"/>
+          <a:ext cx="3672702" cy="1762444"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>1</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>3228411</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>1531714</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="15" name="Picture 14">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{02467A17-CCE0-9D56-7860-DFFEF836ADFA}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId10" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7483506" y="56253879"/>
+          <a:ext cx="3228410" cy="1531783"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>1120588</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>1743138</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>3623235</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>3505976</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="17" name="Picture 16">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{586E977A-EC3E-F17A-8EDB-DCE42404AFEA}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId11" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7445686" y="58021569"/>
+          <a:ext cx="3648137" cy="1762838"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>1127125</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>1857375</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>3654393</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>3635375</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="19" name="Picture 18">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B15BF7FE-AFEA-0C56-4784-5716E21958AE}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId12" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7461250" y="49101375"/>
+          <a:ext cx="3670268" cy="1778000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -1413,20 +1799,14 @@
       <c r="G17" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The shared Drawer and Modal building blocks were originally written as flat 'gallery' swatches for the design catalogue - their styling sat inside the page instead of floating above it, which is why opening the Create work item / Invite / Integrations form showed a grey block wedged into the page with the form squashed to the right, and the X and clicking outside did nothing.</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Rebuilt Drawer and Modal as real overlays: a proper dimmed backdrop over the whole page with the form panel above it, and the X, a click on the dimmed area, and the Esc key all close it. Fixed once at the shared-component level so all three screens (Create work item, Invite user, Integrations connect forms) are corrected together. The Integrations connect screen, which is a full page rather than a pop-over, now shows a clean centred card instead of the grey right-floated block. frontend/src/components/ui/index.tsx (Drawer, Modal) + styles/components.css (.scrim-overlay). All 190 frontend tests pass.</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Fixed</t>
-        </is>
+      <c r="H17" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="I17" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="J17" s="2" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="18" spans="1:10" ht="29" customHeight="1" x14ac:dyDescent="0.35">
@@ -1446,20 +1826,14 @@
       <c r="G18" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The Create work item form marked Title as optional; the reporter wants it required. Separately, the Type field had no explanation of what Epic/Story/Task/Defect mean.</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Title is now required: the field is marked with * and the Create button stays disabled until a title is entered. Added a tooltip/hint on the Type field explaining each type (Epic/Story = plan tier, Task = build tier, Defect = remediation) - this also closes the type-tooltip enhancement noted under the Work Item lifecycle row. frontend/src/features/lifecycle/WorkItemsBoard.tsx.</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Fixed</t>
-        </is>
+      <c r="H18" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="I18" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="J18" s="2" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="19" spans="1:10" ht="188.5" x14ac:dyDescent="0.35">
@@ -1519,20 +1893,14 @@
       <c r="G21" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The invite form hard-coded only four roles and showed them as raw keys like 'product_owner' (with the underscore), and once you added a role row with 'grant another role' there was no way to remove it.</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The role dropdown now lists the full set of ten roles from one shared source, every role shows a human-readable label (Product Owner, Security Engineer, ...) with no underscores, and each granted-role row has an X to remove it (shown whenever there's more than one). The same labels are used wherever a user's roles are listed. New shared list frontend/src/features/identity/roles.ts; UsersInvites.tsx; tests in roles.test.ts.</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Fixed</t>
-        </is>
+      <c r="H21" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="I21" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="J21" s="2" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="22" spans="1:10" ht="409.5" x14ac:dyDescent="0.35">
@@ -1551,20 +1919,14 @@
       <c r="G22" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Several issues on the work-item lifecycle screen. (i) The rail listed brownfield/onboarding phases (context bridge, context extraction, on-boarding) that don't belong on a normal work item, and phase names showed with underscores/number prefixes. (ii) A Story (or any non-Epic) still showed 'Epic' because the screen hard-coded that word. (iv) The run console showed nothing because run events are stored with an 'action' + 'payload' but the console reads 'kind' and 'message', which weren't being sent - so every line rendered blank. (v) Re-running a failed phase sent the run's internal id (a UUID) where the system expects the short phase key, producing 'no AgentSpec registered for key &lt;uuid&gt;', and a failed run gave no reason.</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(i) Phase names are now human-readable everywhere (Task Breakdown, Architecture, ...) and the brownfield/onboarding phases are hidden from a work item's rail - a display-only filter, no change to orchestration (as agreed with the team). (ii) The type badge and headings now show the work item's real type. (iv) Run events now carry a colour ('kind') and a readable 'message' from the action + payload, so the console shows progress - verified live on a real run, e.g. 'Phase dispatched - ideation' and 'Run failed - Command failed with exit code 1'. (v) Re-run now sends the phase key, not the UUID; verified live with the exact id from the report (d32f5ced-...): the UUID reproduces the error, the key '01_ideation' starts a run cleanly. A failed run now shows the actual reason. (iii, type tooltip, was an enhancement and is also done - see the 'Title is mandatory' row.) Files: frontend lifecycle/phases.ts, WorkItemEpic/Task/Defect.tsx, PhasesAndRuns.tsx, RunConsole.tsx, observability/OfflineTakeover.tsx, RunTranscriptScreen.tsx; backend api/serializers.py (RunSerializer agent_key/agent_phase, EventSerializer kind/message).</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Fixed</t>
-        </is>
+      <c r="H22" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="I22" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="J22" s="2" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="23" spans="1:10" ht="409.5" x14ac:dyDescent="0.35">
@@ -1583,20 +1945,14 @@
       <c r="G23" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Artifacts generated by a phase are registered as internal drafts with the draft text stored inline in the artifact's external_ref.body field and an empty s3_key (the agent hadn't staged a snapshot to object storage). The Preview endpoint only knew how to fetch a body from s3_key, so for these drafts it found nothing and returned 'artifact has no body to preview' even though the text was sitting right there in external_ref.body.</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Taught the preview read-through to also read an internal draft's body from external_ref.body when there is no s3_key yet, choosing the content type from the draft's 'format'. Nothing is copied or stored anywhere new - it's read where it already lives, so tenant isolation and 'platform owns state, not content' are untouched. Verified LIVE on the exact artifact from the report (08efb4c5-...-a232e): it previously 404'd and now returns its 5,834-character markdown body. On MinIO: the local object store container is up and healthy, and artifacts that DO have an s3_key still preview from S3 as before - both paths work. backend/integrations/preview.py (_read_internal); regression test test_preview_internal_artifact_reads_inline_external_ref_body.</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Fixed</t>
-        </is>
+      <c r="H23" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="I23" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="J23" s="2" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="24" spans="1:10" ht="58" x14ac:dyDescent="0.35">
@@ -1635,23 +1991,17 @@
       <c r="G25" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">When a clarification question offered an 'Other (please specify)' choice, picking it gave the user nowhere to type the specifics, and the literal option text would have been sent as the answer.</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Selecting an 'Other / please specify' style option now reveals a text box, and what the user types is submitted as the answer (an empty box counts as unanswered so a required question still blocks). frontend/src/features/lifecycle/Clarifications.tsx.</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Fixed</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" spans="1:10" ht="145" x14ac:dyDescent="0.35">
+      <c r="H25" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="I25" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="J25" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" ht="275.5" x14ac:dyDescent="0.35">
       <c r="A26" s="2">
         <v>25</v>
       </c>
@@ -1667,50 +2017,134 @@
       <c r="G26" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">When registering generated artifacts the agent raised a clarification asking the user for the project id, which the user can't know. The registration tool required project_id (and run_id) as inputs, so if the agent didn't have them it asked.</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The platform now binds the project id and run id from the run the phase is executing under (the same way the tenant is already bound), so artifact registration fills them in automatically and never asks the user. Done on both the live companion path and the server-side path. runner/companion/state_mcp.py + runner.py (RUNNER_PROJECT_ID), mcp_platform_state/server.py + backend/orchestration/activities.py (PLATFORM_PROJECT_ID/RUN_ID).</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Fixed</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="H26" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="I26" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="J26" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" ht="246.5" x14ac:dyDescent="0.35">
       <c r="A27" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="B27" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="J27" s="2" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" ht="333.5" x14ac:dyDescent="0.35">
       <c r="A28" s="2">
         <v>27</v>
       </c>
-    </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="B28" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="J28" s="2" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" ht="319" x14ac:dyDescent="0.35">
       <c r="A29" s="2">
         <v>28</v>
       </c>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="B29" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="J29" s="2" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" ht="203" x14ac:dyDescent="0.35">
       <c r="A30" s="2">
         <v>29</v>
       </c>
-    </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="B30" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J30" s="2" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" ht="325" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="2">
         <v>30</v>
       </c>
-    </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="B31" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G31" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J31" s="2" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" ht="261" x14ac:dyDescent="0.35">
       <c r="A32" s="2">
         <v>31</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G32" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="J32" s="2" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.35">

--- a/docs/Bugs.xlsx
+++ b/docs/Bugs.xlsx
@@ -8,19 +8,22 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Msi\projects\SDLC-App\AI-First-SDLC-App\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37F27ECA-6C01-47A3-B7E3-88ECE724B660}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08916249-B9BA-4992-97A5-5949A1C6C751}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$J$216</definedName>
+  </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="100">
   <si>
     <t>S.No</t>
   </si>
@@ -378,12 +381,18 @@
     <t>After initial sign in, the get started page is shown for the user to set up his complete the 4 step process: During that process if the user clicks on "connect machine", "invite users" and "integrations" it takes the respective page and the user will see a button or link as "Back to get started" as option, once user does the 4 step process and then goes to any one of the above screens, it shows the same "back to get started" option even though the user has completed the on-borading process.</t>
   </si>
   <si>
-    <t>General issue</t>
-  </si>
-  <si>
     <t>Artifacts &amp; Traceability
 1. The generated phase artifacts are Markdown files and the application is showing the preview as markdown text not a rendered markdwon file. In some cases when a architecure diagram present then it wont be human understandable Need to fix the rendering
 2. When artifacts are generated for a work item, if the same work item phase is run again: The artifacts are duplicated with same v1 as version instead of v2 and when clicked on preview it showing versions a v1 for both not v1 and v2 etc.</t>
+  </si>
+  <si>
+    <t>Common issue</t>
+  </si>
+  <si>
+    <t>In phases &amp; Runs, when the companion is not connected the developed design isn't same the UI wireframe. Also, the phases should be human readable. It should  have underscores like 'ux_design' etc</t>
+  </si>
+  <si>
+    <t>Phases &amp; Runs</t>
   </si>
 </sst>
 </file>
@@ -479,7 +488,7 @@
       <xdr:col>5</xdr:col>
       <xdr:colOff>3530600</xdr:colOff>
       <xdr:row>3</xdr:row>
-      <xdr:rowOff>1230</xdr:rowOff>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1060,6 +1069,56 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>1</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>2609453</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>1415835</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="23" name="Picture 22">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AAE6813F-E458-C1C8-389C-AE98CEDCE310}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId13" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7471172" y="65553829"/>
+          <a:ext cx="2609453" cy="1415834"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -2043,8 +2102,20 @@
       <c r="G27" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="J27" s="2" t="s">
-        <v>64</v>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Two problems on the Work Items board. (1) The board only ever showed four phase columns (Ideation, Requirements, Architecture, UX Design) and in the wrong order - PRD was missing - because the columns were a hardcoded list of four rather than the real lifecycle. (2) When a card was waiting for a gate or a clarification, a long status label overflowed and broke the card layout, and gate labels showed a raw phase name with underscores (e.g. '04_architecture gate').</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(1) The board now builds its columns from the real phase catalog, so every lifecycle phase from Ideation through Deployment shows in correct SDLC order; the board already scrolls sideways so the extra columns just work, and each column title is human-readable. (2) The card header now wraps so a long 'needs' label no longer breaks the layout, and gate labels are humanised (e.g. 'Architecture gate' instead of '04_architecture gate'). Verified: the frontend compiles clean and all 204 UI tests pass, including new tests for the phase-column list and the label humaniser. Files: frontend WorkItemsBoard.tsx, lifecycle/phases.ts (lifecyclePhaseColumns / humanizeLabel), styles/components.css.</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fixed</t>
+        </is>
       </c>
     </row>
     <row r="28" spans="1:10" ht="333.5" x14ac:dyDescent="0.35">
@@ -2052,7 +2123,7 @@
         <v>27</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D28" s="2" t="s">
         <v>68</v>
@@ -2063,8 +2134,20 @@
       <c r="G28" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="J28" s="2" t="s">
-        <v>64</v>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(1) Generated artifacts are Markdown, but the preview showed the raw Markdown source in a plain text box, and any embedded diagram was unreadable - the preview only knew how to render HTML. (2) Re-running the same work-item phase created a second artifact still labelled v1 instead of v2, and the preview's version history showed v1 for both, because artifact registration always stamped version 1 and never looked at the previous versions.</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(1) The preview now renders Markdown properly (headings, lists, tables, code) with a real Markdown renderer, and ```mermaid diagram blocks are drawn as actual diagrams instead of shown as text. (2) A newly registered artifact now takes the next version number after the highest existing one for the same project+phase+type, so re-running a phase yields v2, v3, ... Only the version number changes - artifacts stay pointers, not content, and tenant isolation is untouched. Verified LIVE against the running backend: registering the same phase twice returned v1 then v2, the preview reported content type 'text/markdown' with a mermaid diagram in the body, and the version history listed [2, 1]; the single-instance API-contract artifact is unaffected (its tests still pass). Files: frontend components/ui/Markdown.tsx + observability/ArtifactPreviewScreen.tsx; backend mcp_platform_state/tools.py (register_artifact). New dependencies: react-markdown, remark-gfm, mermaid.</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fixed</t>
+        </is>
       </c>
     </row>
     <row r="29" spans="1:10" ht="319" x14ac:dyDescent="0.35">
@@ -2083,8 +2166,20 @@
       <c r="G29" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="J29" s="2" t="s">
-        <v>64</v>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(1) In the 'Needs me' section of the Workspace Dashboard, phase and role names were shown raw with underscores (e.g. '04_architecture', 'product_owner'). (2) The sidebar and top bar showed hardcoded counts that never changed - Gates always '3', Clarifications always '1', and the notification bell always '4' - regardless of what actually needed the user.</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(1) The Needs-me tiles and list now show human-readable phase and role names (e.g. 'Architecture', 'Product Owner') via the shared label helpers. (2) The sidebar Gates and Clarifications counts and the notification bell are now driven by the real needs-me totals (bell = gates + clarifications) and hide when nothing is pending, instead of the old fixed 3/1/4. Verified: frontend compiles clean and all 204 UI tests pass. Files: frontend observability/Dashboard.tsx, components/AppShell.tsx (live counts from the existing dashboard rollup).</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fixed</t>
+        </is>
       </c>
     </row>
     <row r="30" spans="1:10" ht="203" x14ac:dyDescent="0.35">
@@ -2135,7 +2230,7 @@
         <v>95</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>12</v>
@@ -2147,82 +2242,94 @@
         <v>64</v>
       </c>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:7" ht="116" x14ac:dyDescent="0.35">
       <c r="A33" s="2">
         <v>32</v>
       </c>
-    </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="B33" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G33" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A34" s="2">
         <v>33</v>
       </c>
     </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A35" s="2">
         <v>34</v>
       </c>
     </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A36" s="2">
         <v>35</v>
       </c>
     </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A37" s="2">
         <v>36</v>
       </c>
     </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A38" s="2">
         <v>37</v>
       </c>
     </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A39" s="2">
         <v>38</v>
       </c>
     </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A40" s="2">
         <v>39</v>
       </c>
     </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A41" s="2">
         <v>40</v>
       </c>
     </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A42" s="2">
         <v>41</v>
       </c>
     </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A43" s="2">
         <v>42</v>
       </c>
     </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A44" s="2">
         <v>43</v>
       </c>
     </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A45" s="2">
         <v>44</v>
       </c>
     </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A46" s="2">
         <v>45</v>
       </c>
     </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A47" s="2">
         <v>46</v>
       </c>
     </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A48" s="2">
         <v>47</v>
       </c>
@@ -3068,6 +3175,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:J216" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/docs/Bugs.xlsx
+++ b/docs/Bugs.xlsx
@@ -1539,6 +1539,21 @@
       <c r="H4" s="2"/>
       <c r="I4" s="2"/>
       <c r="J4" s="2"/>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Enhancement: several form fields had no placeholder text to hint the expected input.</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Added placeholders to the remaining form fields (Login password, Accept-Invite name/password, the Invite teammate name field); the signup, create-project and create-work-item forms already had them. frontend features/identity/Login.tsx, AcceptInvite.tsx, UsersInvites.tsx.</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fixed</t>
+        </is>
+      </c>
     </row>
     <row r="5" spans="1:10" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="2">
@@ -1617,6 +1632,21 @@
       <c r="H7" s="2"/>
       <c r="I7" s="2"/>
       <c r="J7" s="2"/>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">After first login, the get-started panel on the Workspace Dashboard showed a green tick on 'Create your first project' even though no project had been created. Confirmed against the backend: signup creates the workspace and the admin user but no project, so the tick was simply hardcoded as done in that panel.</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The 'Create your first project' step is now shown as the active, not-yet-done step (numbered 1) with a 'Create a project' action, and 'Connect your machine' follows as the next step. frontend features/observability/Dashboard.tsx. (The separate Setup checklist screen was already correct - it computes each step from real data.)</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fixed</t>
+        </is>
+      </c>
     </row>
     <row r="8" spans="1:10" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="2">
@@ -1662,10 +1692,20 @@
       <c r="G9" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="H9" s="2"/>
-      <c r="I9" s="2"/>
-      <c r="J9" s="2" t="s">
-        <v>64</v>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Enhancement: the create-project page showed a long 'Greenfield starts from a blank profile. Brownfield opens onboarding…' sentence under the track selector; the request was to move it into a tooltip instead.</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Removed the sentence and surfaced the same explanation as a hover tooltip on the Track selector (an info marker next to the label, plus tooltips on the Greenfield/Brownfield buttons). frontend features/setup/CreateProject.tsx + styles/components.css (.field__tip).</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fixed</t>
+        </is>
       </c>
     </row>
     <row r="10" spans="1:10" ht="101.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -1835,10 +1875,20 @@
       <c r="G16" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="H16" s="2"/>
-      <c r="I16" s="2"/>
-      <c r="J16" s="2" t="s">
-        <v>64</v>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">On the Connect Machine page, after generating a token, two spinning loaders appeared next to 'Waiting for first check-in…'. The waiting status component already draws its own spinner, and the page was also passing a second spinner into it.</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Removed the extra spinner; the waiting status now shows a single loader. frontend features/identity/ConnectMachine.tsx.</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fixed</t>
+        </is>
       </c>
     </row>
     <row r="17" spans="1:10" ht="116" customHeight="1" x14ac:dyDescent="0.35">
@@ -1932,8 +1982,20 @@
       <c r="G20" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="J20" s="2" t="s">
-        <v>64</v>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">On the Users &amp; Invitations (Workspace Admin) page the subtitle hardcoded 'Acme Corp' as the workspace name instead of the real registered workspace.</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The subtitle now shows the actual workspace name from the signed-in session (e.g. 'Everyone in the Edven workspace…'). Same fix also covers the Workspace Admin row's hardcoded-name point. frontend features/identity/UsersInvites.tsx.</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fixed</t>
+        </is>
       </c>
     </row>
     <row r="21" spans="1:10" ht="188.5" x14ac:dyDescent="0.35">
@@ -2030,8 +2092,20 @@
       <c r="G24" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="J24" s="2" t="s">
-        <v>64</v>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">On the Artifacts &amp; Traceability page the search box and the Phase/Type/Status filters did nothing, and the filter dropdowns had no options to pick from.</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The search box and all three filters now work: search matches on artifact type/phase, and the Phase/Type/Status dropdowns are populated from the artifacts actually present (labels humanised). Filtering is combinable, and a 'No artifacts match these filters' message shows when a combination excludes everything. frontend features/observability/ArtifactsRegistry.tsx.</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fixed</t>
+        </is>
       </c>
     </row>
     <row r="25" spans="1:10" ht="145" x14ac:dyDescent="0.35">
@@ -2198,8 +2272,20 @@
       <c r="G30" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="J30" s="2" t="s">
-        <v>64</v>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Universal: (1) underscore-style names (phases, roles, statuses) should be human-readable everywhere; (2) values that were hardcoded but should be dynamic should be made dynamic.</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bounded sweep across the main in-app screens (brownfield/code-intel screens deferred to their own session, as agreed). (1) Humanised remaining raw phase/role renders on the Gate-role coverage list, Clarifications, Phases &amp; Runs gate tooltip, Work Item Epic/Task clarification rows, Traceability nodes, and the Run transcript title. (2) Made the sidebar/top-bar Companion status pill reflect the real runner status instead of a fixed 'Ready'; the workspace name, nav Gates/Clarifications counts and notification bell were made dynamic in the P1 work and the rows above. Much of this row overlaps the Work Items / Dashboard / Artifacts / Users rows and is cross-referenced there. frontend RolesMatrix.tsx, Clarifications.tsx, PhasesAndRuns.tsx, WorkItemEpic.tsx, WorkItemTask.tsx, TraceabilityView.tsx, RunTranscriptScreen.tsx, AppShell.tsx.</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fixed</t>
+        </is>
       </c>
     </row>
     <row r="31" spans="1:10" ht="325" customHeight="1" x14ac:dyDescent="0.35">
@@ -2218,8 +2304,20 @@
       <c r="G31" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="J31" s="2" t="s">
-        <v>64</v>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Workspace Admin page. (1) Registered and invited users weren't listed - the page showed an 'It's just you so far' empty state, and the users only appeared 'in the background' once the Invite drawer was opened. The empty state was being shown whenever there was at most one user and no still-pending invite, which hid the admin's own row (and any revoked/older invites). (2) The workspace name was hardcoded 'Acme Corp'.</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(1) The table now shows whenever there's anyone to list (the signed-in admin always is a row); the empty state only appears when the list is genuinely empty. Verified against the live data (workspace 'Edven': the admin user plus a revoked invite) - the admin now shows in the table instead of being hidden. (2) The workspace name is now dynamic (same fix as the Users &amp; Invitations row). frontend features/identity/UsersInvites.tsx.</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fixed</t>
+        </is>
       </c>
     </row>
     <row r="32" spans="1:10" ht="261" x14ac:dyDescent="0.35">
@@ -2257,6 +2355,21 @@
       </c>
       <c r="G33" s="2" t="s">
         <v>23</v>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">On Phases &amp; Runs, when the companion isn't connected the screen didn't match the wireframe: the Runs panel still showed hardcoded sample/demo runs instead of an empty state, and the disabled phase list didn't match. (Phase names also needed to be human-readable.)</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">When the companion is offline (or there are simply no runs yet) the Runs panel now shows the 'No runs yet' empty state instead of demo rows, matching the S-18 wireframe, and the disabled phase buttons were aligned to the wireframe (Architecture, UX Design, Task Breakdown). Phase names on this screen go through the shared humaniser. Verified live against the running stack. frontend features/lifecycle/PhasesAndRuns.tsx.</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fixed</t>
+        </is>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.35">

--- a/docs/Bugs.xlsx
+++ b/docs/Bugs.xlsx
@@ -1725,10 +1725,20 @@
       <c r="G10" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="H10" s="2"/>
-      <c r="I10" s="2"/>
-      <c r="J10" s="2" t="s">
-        <v>64</v>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">After creating a project the profile page showed '✓ Saved · v1' at the top and 'Saving will create v2' at the bottom, even though the profile had never been saved. Confirmed against the backend: a project with no profile yet returns a 404 (no version), and the page was defaulting that missing version to 1 - so it invented 'v1' as already saved, and the next-save hint then said v2.</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A project with no saved profile is now treated as not-saved (version 0): the top badge shows 'Draft · not saved yet' until the first save, and the save hint correctly reads 'Saving will create v1'. Once saved it shows '✓ Saved · v1', then v2 on the next edit, as expected. frontend features/setup/ProjectProfileEditor.tsx.</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fixed</t>
+        </is>
       </c>
     </row>
     <row r="11" spans="1:10" ht="362.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -1802,10 +1812,20 @@
       <c r="G13" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="H13" s="2"/>
-      <c r="I13" s="2"/>
-      <c r="J13" s="2" t="s">
-        <v>64</v>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Clarification: the API GET /api/runners/ is called on a repeating timer on every screen. This is the companion-liveness poll - the app checks whether your machine is still connected. It runs on every screen because the companion status pill lives in the app shell (which is always on screen); it became global as part of the P2 companion-pill fix. React Query de-duplicates all callers under one 'runners' key, so it's a single request per tick, not one per component.</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Answered, and the background churn was reduced: the poll interval is now configurable, and the always-on app shell polls gently (every ~15s) while the Connect Machine and Phases &amp; Runs screens keep the fast ~4s cadence where live connection status actually matters - about a 4x reduction in background calls on ordinary screens. frontend features/identity/hooks.ts (useRunners interval) + components/AppShell.tsx.</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fixed</t>
+        </is>
       </c>
     </row>
     <row r="14" spans="1:10" ht="72.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -1825,10 +1845,20 @@
       <c r="G14" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="H14" s="2"/>
-      <c r="I14" s="2"/>
-      <c r="J14" s="2" t="s">
-        <v>64</v>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">On the Connect Machine page the Copy button next to the generated token did nothing when clicked, and on the token card it was barely visible. The button had no click handler at all, and its styling (white text on a translucent background, designed for the dark command block) was almost invisible on the light token card.</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The Copy buttons on both the token and the command blocks now actually copy to the clipboard (with a fallback for older browsers) and briefly show '✓ Copied!' as confirmation; the button on the light token card was given proper contrast so it's clearly visible. frontend components/ui/index.tsx (new shared CopyButton, used by TokenReveal + CmdBlock) + styles/components.css.</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fixed</t>
+        </is>
       </c>
     </row>
     <row r="15" spans="1:10" ht="58" customHeight="1" x14ac:dyDescent="0.35">
@@ -1962,8 +1992,20 @@
       <c r="G19" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="J19" s="2" t="s">
-        <v>64</v>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Navigation bar and sidebar showed hardcoded values: the notification bell always showed 4, the companion pill was always green 'Ready' even when not connected, and the sidebar Gates/Clarifications tabs showed fixed default counts.</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Already resolved as part of the earlier P1/P2 fixes and re-verified here: the sidebar Gates and Clarifications counts and the notification bell are now driven by the real needs-me totals and hide when there's nothing pending; the companion pill (both sidebar and top bar) now shows Ready/Offline from the actual companion status. frontend components/AppShell.tsx.</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fixed</t>
+        </is>
       </c>
     </row>
     <row r="20" spans="1:10" ht="116" x14ac:dyDescent="0.35">
@@ -2336,8 +2378,20 @@
       <c r="G32" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="J32" s="2" t="s">
-        <v>64</v>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The '← Back to Get started' link kept showing on the Connect Machine / Invite / Integrations screens even after the user had finished setting up. It only hid once the user had a project, a connected machine, AND a second teammate who had accepted an invite - so a solo developer (who never needs to invite anyone) saw the link forever.</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Per team decision, the link now hides once the user has a project and a connected machine (inviting a team stays optional), so it no longer nags after setup. frontend features/identity/SetupReturnLink.tsx.</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fixed</t>
+        </is>
       </c>
     </row>
     <row r="33" spans="1:7" ht="116" x14ac:dyDescent="0.35">

--- a/docs/Bugs.xlsx
+++ b/docs/Bugs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Msi\projects\SDLC-App\AI-First-SDLC-App\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08916249-B9BA-4992-97A5-5949A1C6C751}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{23CB08F4-CD86-4F8A-943F-B8813342C979}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -19,11 +19,12 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$J$216</definedName>
   </definedNames>
   <calcPr calcId="0"/>
+  <fileRecoveryPr repairLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="140">
   <si>
     <t>S.No</t>
   </si>
@@ -393,6 +394,137 @@
   </si>
   <si>
     <t>Phases &amp; Runs</t>
+  </si>
+  <si>
+    <t>Enhancement: the create-project page showed a long 'Greenfield starts from a blank profile. Brownfield opens onboarding…' sentence under the track selector; the request was to move it into a tooltip instead.</t>
+  </si>
+  <si>
+    <t>Removed the sentence and surfaced the same explanation as a hover tooltip on the Track selector (an info marker next to the label, plus tooltips on the Greenfield/Brownfield buttons). frontend features/setup/CreateProject.tsx + styles/components.css (.field__tip).</t>
+  </si>
+  <si>
+    <t>After creating a project the profile page showed '✓ Saved · v1' at the top and 'Saving will create v2' at the bottom, even though the profile had never been saved. Confirmed against the backend: a project with no profile yet returns a 404 (no version), and the page was defaulting that missing version to 1 - so it invented 'v1' as already saved, and the next-save hint then said v2.</t>
+  </si>
+  <si>
+    <t>A project with no saved profile is now treated as not-saved (version 0): the top badge shows 'Draft · not saved yet' until the first save, and the save hint correctly reads 'Saving will create v1'. Once saved it shows '✓ Saved · v1', then v2 on the next edit, as expected. frontend features/setup/ProjectProfileEditor.tsx.</t>
+  </si>
+  <si>
+    <t>Clarification: the API GET /api/runners/ is called on a repeating timer on every screen. This is the companion-liveness poll - the app checks whether your machine is still connected. It runs on every screen because the companion status pill lives in the app shell (which is always on screen); it became global as part of the P2 companion-pill fix. React Query de-duplicates all callers under one 'runners' key, so it's a single request per tick, not one per component.</t>
+  </si>
+  <si>
+    <t>Answered, and the background churn was reduced: the poll interval is now configurable, and the always-on app shell polls gently (every ~15s) while the Connect Machine and Phases &amp; Runs screens keep the fast ~4s cadence where live connection status actually matters - about a 4x reduction in background calls on ordinary screens. frontend features/identity/hooks.ts (useRunners interval) + components/AppShell.tsx.</t>
+  </si>
+  <si>
+    <t>On the Connect Machine page the Copy button next to the generated token did nothing when clicked, and on the token card it was barely visible. The button had no click handler at all, and its styling (white text on a translucent background, designed for the dark command block) was almost invisible on the light token card.</t>
+  </si>
+  <si>
+    <t>The Copy buttons on both the token and the command blocks now actually copy to the clipboard (with a fallback for older browsers) and briefly show '✓ Copied!' as confirmation; the button on the light token card was given proper contrast so it's clearly visible. frontend components/ui/index.tsx (new shared CopyButton, used by TokenReveal + CmdBlock) + styles/components.css.</t>
+  </si>
+  <si>
+    <t>On the Connect Machine page, after generating a token, two spinning loaders appeared next to 'Waiting for first check-in…'. The waiting status component already draws its own spinner, and the page was also passing a second spinner into it.</t>
+  </si>
+  <si>
+    <t>Removed the extra spinner; the waiting status now shows a single loader. frontend features/identity/ConnectMachine.tsx.</t>
+  </si>
+  <si>
+    <t>Navigation bar and sidebar showed hardcoded values: the notification bell always showed 4, the companion pill was always green 'Ready' even when not connected, and the sidebar Gates/Clarifications tabs showed fixed default counts.</t>
+  </si>
+  <si>
+    <t>Already resolved as part of the earlier P1/P2 fixes and re-verified here: the sidebar Gates and Clarifications counts and the notification bell are now driven by the real needs-me totals and hide when there's nothing pending; the companion pill (both sidebar and top bar) now shows Ready/Offline from the actual companion status. frontend components/AppShell.tsx.</t>
+  </si>
+  <si>
+    <t>On the Users &amp; Invitations (Workspace Admin) page the subtitle hardcoded 'Acme Corp' as the workspace name instead of the real registered workspace.</t>
+  </si>
+  <si>
+    <t>The subtitle now shows the actual workspace name from the signed-in session (e.g. 'Everyone in the Edven workspace…'). Same fix also covers the Workspace Admin row's hardcoded-name point. frontend features/identity/UsersInvites.tsx.</t>
+  </si>
+  <si>
+    <t>On the Artifacts &amp; Traceability page the search box and the Phase/Type/Status filters did nothing, and the filter dropdowns had no options to pick from.</t>
+  </si>
+  <si>
+    <t>The search box and all three filters now work: search matches on artifact type/phase, and the Phase/Type/Status dropdowns are populated from the artifacts actually present (labels humanised). Filtering is combinable, and a 'No artifacts match these filters' message shows when a combination excludes everything. frontend features/observability/ArtifactsRegistry.tsx.</t>
+  </si>
+  <si>
+    <t>Two problems on the Work Items board. (1) The board only ever showed four phase columns (Ideation, Requirements, Architecture, UX Design) and in the wrong order - PRD was missing - because the columns were a hardcoded list of four rather than the real lifecycle. (2) When a card was waiting for a gate or a clarification, a long status label overflowed and broke the card layout, and gate labels showed a raw phase name with underscores (e.g. '04_architecture gate').</t>
+  </si>
+  <si>
+    <t>(1) The board now builds its columns from the real phase catalog, so every lifecycle phase from Ideation through Deployment shows in correct SDLC order; the board already scrolls sideways so the extra columns just work, and each column title is human-readable. (2) The card header now wraps so a long 'needs' label no longer breaks the layout, and gate labels are humanised (e.g. 'Architecture gate' instead of '04_architecture gate'). Verified: the frontend compiles clean and all 204 UI tests pass, including new tests for the phase-column list and the label humaniser. Files: frontend WorkItemsBoard.tsx, lifecycle/phases.ts (lifecyclePhaseColumns / humanizeLabel), styles/components.css.</t>
+  </si>
+  <si>
+    <t>(1) Generated artifacts are Markdown, but the preview showed the raw Markdown source in a plain text box, and any embedded diagram was unreadable - the preview only knew how to render HTML. (2) Re-running the same work-item phase created a second artifact still labelled v1 instead of v2, and the preview's version history showed v1 for both, because artifact registration always stamped version 1 and never looked at the previous versions.</t>
+  </si>
+  <si>
+    <t>(1) The preview now renders Markdown properly (headings, lists, tables, code) with a real Markdown renderer, and ```mermaid diagram blocks are drawn as actual diagrams instead of shown as text. (2) A newly registered artifact now takes the next version number after the highest existing one for the same project+phase+type, so re-running a phase yields v2, v3, ... Only the version number changes - artifacts stay pointers, not content, and tenant isolation is untouched. Verified LIVE against the running backend: registering the same phase twice returned v1 then v2, the preview reported content type 'text/markdown' with a mermaid diagram in the body, and the version history listed [2, 1]; the single-instance API-contract artifact is unaffected (its tests still pass). Files: frontend components/ui/Markdown.tsx + observability/ArtifactPreviewScreen.tsx; backend mcp_platform_state/tools.py (register_artifact). New dependencies: react-markdown, remark-gfm, mermaid.</t>
+  </si>
+  <si>
+    <t>(1) In the 'Needs me' section of the Workspace Dashboard, phase and role names were shown raw with underscores (e.g. '04_architecture', 'product_owner'). (2) The sidebar and top bar showed hardcoded counts that never changed - Gates always '3', Clarifications always '1', and the notification bell always '4' - regardless of what actually needed the user.</t>
+  </si>
+  <si>
+    <t>(1) The Needs-me tiles and list now show human-readable phase and role names (e.g. 'Architecture', 'Product Owner') via the shared label helpers. (2) The sidebar Gates and Clarifications counts and the notification bell are now driven by the real needs-me totals (bell = gates + clarifications) and hide when nothing is pending, instead of the old fixed 3/1/4. Verified: frontend compiles clean and all 204 UI tests pass. Files: frontend observability/Dashboard.tsx, components/AppShell.tsx (live counts from the existing dashboard rollup).</t>
+  </si>
+  <si>
+    <t>Universal: (1) underscore-style names (phases, roles, statuses) should be human-readable everywhere; (2) values that were hardcoded but should be dynamic should be made dynamic.</t>
+  </si>
+  <si>
+    <t>Bounded sweep across the main in-app screens (brownfield/code-intel screens deferred to their own session, as agreed). (1) Humanised remaining raw phase/role renders on the Gate-role coverage list, Clarifications, Phases &amp; Runs gate tooltip, Work Item Epic/Task clarification rows, Traceability nodes, and the Run transcript title. (2) Made the sidebar/top-bar Companion status pill reflect the real runner status instead of a fixed 'Ready'; the workspace name, nav Gates/Clarifications counts and notification bell were made dynamic in the P1 work and the rows above. Much of this row overlaps the Work Items / Dashboard / Artifacts / Users rows and is cross-referenced there. frontend RolesMatrix.tsx, Clarifications.tsx, PhasesAndRuns.tsx, WorkItemEpic.tsx, WorkItemTask.tsx, TraceabilityView.tsx, RunTranscriptScreen.tsx, AppShell.tsx.</t>
+  </si>
+  <si>
+    <t>Workspace Admin page. (1) Registered and invited users weren't listed - the page showed an 'It's just you so far' empty state, and the users only appeared 'in the background' once the Invite drawer was opened. The empty state was being shown whenever there was at most one user and no still-pending invite, which hid the admin's own row (and any revoked/older invites). (2) The workspace name was hardcoded 'Acme Corp'.</t>
+  </si>
+  <si>
+    <t>(1) The table now shows whenever there's anyone to list (the signed-in admin always is a row); the empty state only appears when the list is genuinely empty. Verified against the live data (workspace 'Edven': the admin user plus a revoked invite) - the admin now shows in the table instead of being hidden. (2) The workspace name is now dynamic (same fix as the Users &amp; Invitations row). frontend features/identity/UsersInvites.tsx.</t>
+  </si>
+  <si>
+    <t>The '← Back to Get started' link kept showing on the Connect Machine / Invite / Integrations screens even after the user had finished setting up. It only hid once the user had a project, a connected machine, AND a second teammate who had accepted an invite - so a solo developer (who never needs to invite anyone) saw the link forever.</t>
+  </si>
+  <si>
+    <t>Per team decision, the link now hides once the user has a project and a connected machine (inviting a team stays optional), so it no longer nags after setup. frontend features/identity/SetupReturnLink.tsx.</t>
+  </si>
+  <si>
+    <t>On Phases &amp; Runs, when the companion isn't connected the screen didn't match the wireframe: the Runs panel still showed hardcoded sample/demo runs instead of an empty state, and the disabled phase list didn't match. (Phase names also needed to be human-readable.)</t>
+  </si>
+  <si>
+    <t>When the companion is offline (or there are simply no runs yet) the Runs panel now shows the 'No runs yet' empty state instead of demo rows, matching the S-18 wireframe, and the disabled phase buttons were aligned to the wireframe (Architecture, UX Design, Task Breakdown). Phase names on this screen go through the shared humaniser. Verified live against the running stack. frontend features/lifecycle/PhasesAndRuns.tsx.</t>
+  </si>
+  <si>
+    <t>In project profile page, the placeholders should be shown for all the fields to be filled, currently only tech stack is available.</t>
+  </si>
+  <si>
+    <t>In the Navigation bar, the companion text not visible clearly and light in color when the companion is offline</t>
+  </si>
+  <si>
+    <t>Navigation Bar</t>
+  </si>
+  <si>
+    <t>While connecting to the Claude Code in the users local system/machine (Companion): Currently the user has to connect to claude code by giving a command containing a token by giving to the claude in local CLI, the user has to be in the backend repository in the CLI to perform this. This is not a user friendly approach
+Enhancement: The approach has to be changed, while fixing this issues discuss with team the best possible way of dealing it.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">When clicked on create work item, the below text appears below the type dropdown. This needs to be updated
+Epic — a large body of work that runs the full plan tier (ideation → architecture). Story — a user-facing slice of an epic, also plan tier. Task — a concrete build-tier unit of work (implementation → review). Defect — a fix that runs the remediation tier.
+</t>
+  </si>
+  <si>
+    <t>bug</t>
+  </si>
+  <si>
+    <t>In the integration page: The Icons on each card are not visible until the connection is made by the user, but by default the icons should be visible to the user for better understanding.</t>
+  </si>
+  <si>
+    <t>Integrations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">In Integrations - under connect a capability page: 
+1. When provided the creds for Document store and after testing connect and when clicked on save - after successful connection no message is shown to the user - instead it silently performs the save operation which is confusing to the user.
+2. Initially when connection is tested it did not throw any error message and I was able to click on save. Then user clicked on re-test it showed the below response: http://localhost:8000/api/integrations/c362fb06-5c9e-4075-a1a5-6483f8896a98/test-connection/, Response: {
+    "ok": false,
+    "detail": "No connector registered for docstore:Confluence.",
+    "fix_hint": "Choose a supported vendor for this capability."
+}
+</t>
+  </si>
+  <si>
+    <t>In the integration page: For all the capability connectors the same form filling is shown but it should not be the case, because each one of them will have different fileds for creds. And for each connector the respective vendor drop down shown. For example: For doc store: confluence, share point or built-in docs etc. For task traker: JIRA, Trello etc. 
+Also validate: test connection, save functionality and Re-test issues mentioned in Bug/Issue 39 while doing the current issues.</t>
   </si>
 </sst>
 </file>
@@ -1119,6 +1251,106 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>1</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>3553489</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>1705429</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="9" name="Picture 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6BF13599-4F4F-D730-57D1-E1EF7912AAA5}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId14" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7493000" y="78123144"/>
+          <a:ext cx="3553489" cy="1705428"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>3681931</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>1770673</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="14" name="Picture 13">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4BA29DAE-443B-3E0E-5133-72C0A91D4735}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId15" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7485673" y="83246058"/>
+          <a:ext cx="3681931" cy="1770673"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -1539,21 +1771,6 @@
       <c r="H4" s="2"/>
       <c r="I4" s="2"/>
       <c r="J4" s="2"/>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Enhancement: several form fields had no placeholder text to hint the expected input.</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Added placeholders to the remaining form fields (Login password, Accept-Invite name/password, the Invite teammate name field); the signup, create-project and create-work-item forms already had them. frontend features/identity/Login.tsx, AcceptInvite.tsx, UsersInvites.tsx.</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Fixed</t>
-        </is>
-      </c>
     </row>
     <row r="5" spans="1:10" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="2">
@@ -1632,21 +1849,6 @@
       <c r="H7" s="2"/>
       <c r="I7" s="2"/>
       <c r="J7" s="2"/>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">After first login, the get-started panel on the Workspace Dashboard showed a green tick on 'Create your first project' even though no project had been created. Confirmed against the backend: signup creates the workspace and the admin user but no project, so the tick was simply hardcoded as done in that panel.</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The 'Create your first project' step is now shown as the active, not-yet-done step (numbered 1) with a 'Create a project' action, and 'Connect your machine' follows as the next step. frontend features/observability/Dashboard.tsx. (The separate Setup checklist screen was already correct - it computes each step from real data.)</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Fixed</t>
-        </is>
-      </c>
     </row>
     <row r="8" spans="1:10" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="2">
@@ -1692,20 +1894,14 @@
       <c r="G9" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Enhancement: the create-project page showed a long 'Greenfield starts from a blank profile. Brownfield opens onboarding…' sentence under the track selector; the request was to move it into a tooltip instead.</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Removed the sentence and surfaced the same explanation as a hover tooltip on the Track selector (an info marker next to the label, plus tooltips on the Greenfield/Brownfield buttons). frontend features/setup/CreateProject.tsx + styles/components.css (.field__tip).</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Fixed</t>
-        </is>
+      <c r="H9" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="10" spans="1:10" ht="101.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -1725,20 +1921,14 @@
       <c r="G10" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">After creating a project the profile page showed '✓ Saved · v1' at the top and 'Saving will create v2' at the bottom, even though the profile had never been saved. Confirmed against the backend: a project with no profile yet returns a 404 (no version), and the page was defaulting that missing version to 1 - so it invented 'v1' as already saved, and the next-save hint then said v2.</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">A project with no saved profile is now treated as not-saved (version 0): the top badge shows 'Draft · not saved yet' until the first save, and the save hint correctly reads 'Saving will create v1'. Once saved it shows '✓ Saved · v1', then v2 on the next edit, as expected. frontend features/setup/ProjectProfileEditor.tsx.</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Fixed</t>
-        </is>
+      <c r="H10" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="J10" s="2" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="11" spans="1:10" ht="362.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -1812,20 +2002,14 @@
       <c r="G13" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Clarification: the API GET /api/runners/ is called on a repeating timer on every screen. This is the companion-liveness poll - the app checks whether your machine is still connected. It runs on every screen because the companion status pill lives in the app shell (which is always on screen); it became global as part of the P2 companion-pill fix. React Query de-duplicates all callers under one 'runners' key, so it's a single request per tick, not one per component.</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Answered, and the background churn was reduced: the poll interval is now configurable, and the always-on app shell polls gently (every ~15s) while the Connect Machine and Phases &amp; Runs screens keep the fast ~4s cadence where live connection status actually matters - about a 4x reduction in background calls on ordinary screens. frontend features/identity/hooks.ts (useRunners interval) + components/AppShell.tsx.</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Fixed</t>
-        </is>
+      <c r="H13" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="J13" s="2" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="14" spans="1:10" ht="72.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -1845,20 +2029,14 @@
       <c r="G14" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">On the Connect Machine page the Copy button next to the generated token did nothing when clicked, and on the token card it was barely visible. The button had no click handler at all, and its styling (white text on a translucent background, designed for the dark command block) was almost invisible on the light token card.</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The Copy buttons on both the token and the command blocks now actually copy to the clipboard (with a fallback for older browsers) and briefly show '✓ Copied!' as confirmation; the button on the light token card was given proper contrast so it's clearly visible. frontend components/ui/index.tsx (new shared CopyButton, used by TokenReveal + CmdBlock) + styles/components.css.</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Fixed</t>
-        </is>
+      <c r="H14" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="J14" s="2" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="15" spans="1:10" ht="58" customHeight="1" x14ac:dyDescent="0.35">
@@ -1905,20 +2083,14 @@
       <c r="G16" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">On the Connect Machine page, after generating a token, two spinning loaders appeared next to 'Waiting for first check-in…'. The waiting status component already draws its own spinner, and the page was also passing a second spinner into it.</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Removed the extra spinner; the waiting status now shows a single loader. frontend features/identity/ConnectMachine.tsx.</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Fixed</t>
-        </is>
+      <c r="H16" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="I16" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="J16" s="2" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="17" spans="1:10" ht="116" customHeight="1" x14ac:dyDescent="0.35">
@@ -1992,23 +2164,17 @@
       <c r="G19" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Navigation bar and sidebar showed hardcoded values: the notification bell always showed 4, the companion pill was always green 'Ready' even when not connected, and the sidebar Gates/Clarifications tabs showed fixed default counts.</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Already resolved as part of the earlier P1/P2 fixes and re-verified here: the sidebar Gates and Clarifications counts and the notification bell are now driven by the real needs-me totals and hide when there's nothing pending; the companion pill (both sidebar and top bar) now shows Ready/Offline from the actual companion status. frontend components/AppShell.tsx.</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Fixed</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" spans="1:10" ht="116" x14ac:dyDescent="0.35">
+      <c r="H19" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="I19" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="J19" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" ht="145" x14ac:dyDescent="0.35">
       <c r="A20" s="2">
         <v>19</v>
       </c>
@@ -2024,20 +2190,14 @@
       <c r="G20" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">On the Users &amp; Invitations (Workspace Admin) page the subtitle hardcoded 'Acme Corp' as the workspace name instead of the real registered workspace.</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The subtitle now shows the actual workspace name from the signed-in session (e.g. 'Everyone in the Edven workspace…'). Same fix also covers the Workspace Admin row's hardcoded-name point. frontend features/identity/UsersInvites.tsx.</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Fixed</t>
-        </is>
+      <c r="H20" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="I20" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="J20" s="2" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="21" spans="1:10" ht="188.5" x14ac:dyDescent="0.35">
@@ -2134,20 +2294,14 @@
       <c r="G24" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">On the Artifacts &amp; Traceability page the search box and the Phase/Type/Status filters did nothing, and the filter dropdowns had no options to pick from.</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The search box and all three filters now work: search matches on artifact type/phase, and the Phase/Type/Status dropdowns are populated from the artifacts actually present (labels humanised). Filtering is combinable, and a 'No artifacts match these filters' message shows when a combination excludes everything. frontend features/observability/ArtifactsRegistry.tsx.</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Fixed</t>
-        </is>
+      <c r="H24" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="I24" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="J24" s="2" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="25" spans="1:10" ht="145" x14ac:dyDescent="0.35">
@@ -2218,20 +2372,14 @@
       <c r="G27" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Two problems on the Work Items board. (1) The board only ever showed four phase columns (Ideation, Requirements, Architecture, UX Design) and in the wrong order - PRD was missing - because the columns were a hardcoded list of four rather than the real lifecycle. (2) When a card was waiting for a gate or a clarification, a long status label overflowed and broke the card layout, and gate labels showed a raw phase name with underscores (e.g. '04_architecture gate').</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(1) The board now builds its columns from the real phase catalog, so every lifecycle phase from Ideation through Deployment shows in correct SDLC order; the board already scrolls sideways so the extra columns just work, and each column title is human-readable. (2) The card header now wraps so a long 'needs' label no longer breaks the layout, and gate labels are humanised (e.g. 'Architecture gate' instead of '04_architecture gate'). Verified: the frontend compiles clean and all 204 UI tests pass, including new tests for the phase-column list and the label humaniser. Files: frontend WorkItemsBoard.tsx, lifecycle/phases.ts (lifecyclePhaseColumns / humanizeLabel), styles/components.css.</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Fixed</t>
-        </is>
+      <c r="H27" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="I27" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="J27" s="2" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="28" spans="1:10" ht="333.5" x14ac:dyDescent="0.35">
@@ -2250,20 +2398,14 @@
       <c r="G28" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(1) Generated artifacts are Markdown, but the preview showed the raw Markdown source in a plain text box, and any embedded diagram was unreadable - the preview only knew how to render HTML. (2) Re-running the same work-item phase created a second artifact still labelled v1 instead of v2, and the preview's version history showed v1 for both, because artifact registration always stamped version 1 and never looked at the previous versions.</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(1) The preview now renders Markdown properly (headings, lists, tables, code) with a real Markdown renderer, and ```mermaid diagram blocks are drawn as actual diagrams instead of shown as text. (2) A newly registered artifact now takes the next version number after the highest existing one for the same project+phase+type, so re-running a phase yields v2, v3, ... Only the version number changes - artifacts stay pointers, not content, and tenant isolation is untouched. Verified LIVE against the running backend: registering the same phase twice returned v1 then v2, the preview reported content type 'text/markdown' with a mermaid diagram in the body, and the version history listed [2, 1]; the single-instance API-contract artifact is unaffected (its tests still pass). Files: frontend components/ui/Markdown.tsx + observability/ArtifactPreviewScreen.tsx; backend mcp_platform_state/tools.py (register_artifact). New dependencies: react-markdown, remark-gfm, mermaid.</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Fixed</t>
-        </is>
+      <c r="H28" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="I28" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="J28" s="2" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="29" spans="1:10" ht="319" x14ac:dyDescent="0.35">
@@ -2282,20 +2424,14 @@
       <c r="G29" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(1) In the 'Needs me' section of the Workspace Dashboard, phase and role names were shown raw with underscores (e.g. '04_architecture', 'product_owner'). (2) The sidebar and top bar showed hardcoded counts that never changed - Gates always '3', Clarifications always '1', and the notification bell always '4' - regardless of what actually needed the user.</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(1) The Needs-me tiles and list now show human-readable phase and role names (e.g. 'Architecture', 'Product Owner') via the shared label helpers. (2) The sidebar Gates and Clarifications counts and the notification bell are now driven by the real needs-me totals (bell = gates + clarifications) and hide when nothing is pending, instead of the old fixed 3/1/4. Verified: frontend compiles clean and all 204 UI tests pass. Files: frontend observability/Dashboard.tsx, components/AppShell.tsx (live counts from the existing dashboard rollup).</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Fixed</t>
-        </is>
+      <c r="H29" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="I29" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="J29" s="2" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="30" spans="1:10" ht="203" x14ac:dyDescent="0.35">
@@ -2314,20 +2450,14 @@
       <c r="G30" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Universal: (1) underscore-style names (phases, roles, statuses) should be human-readable everywhere; (2) values that were hardcoded but should be dynamic should be made dynamic.</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bounded sweep across the main in-app screens (brownfield/code-intel screens deferred to their own session, as agreed). (1) Humanised remaining raw phase/role renders on the Gate-role coverage list, Clarifications, Phases &amp; Runs gate tooltip, Work Item Epic/Task clarification rows, Traceability nodes, and the Run transcript title. (2) Made the sidebar/top-bar Companion status pill reflect the real runner status instead of a fixed 'Ready'; the workspace name, nav Gates/Clarifications counts and notification bell were made dynamic in the P1 work and the rows above. Much of this row overlaps the Work Items / Dashboard / Artifacts / Users rows and is cross-referenced there. frontend RolesMatrix.tsx, Clarifications.tsx, PhasesAndRuns.tsx, WorkItemEpic.tsx, WorkItemTask.tsx, TraceabilityView.tsx, RunTranscriptScreen.tsx, AppShell.tsx.</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Fixed</t>
-        </is>
+      <c r="H30" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="I30" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="J30" s="2" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="31" spans="1:10" ht="325" customHeight="1" x14ac:dyDescent="0.35">
@@ -2346,20 +2476,14 @@
       <c r="G31" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="H31" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Workspace Admin page. (1) Registered and invited users weren't listed - the page showed an 'It's just you so far' empty state, and the users only appeared 'in the background' once the Invite drawer was opened. The empty state was being shown whenever there was at most one user and no still-pending invite, which hid the admin's own row (and any revoked/older invites). (2) The workspace name was hardcoded 'Acme Corp'.</t>
-        </is>
-      </c>
-      <c r="I31" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(1) The table now shows whenever there's anyone to list (the signed-in admin always is a row); the empty state only appears when the list is genuinely empty. Verified against the live data (workspace 'Edven': the admin user plus a revoked invite) - the admin now shows in the table instead of being hidden. (2) The workspace name is now dynamic (same fix as the Users &amp; Invitations row). frontend features/identity/UsersInvites.tsx.</t>
-        </is>
-      </c>
-      <c r="J31" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Fixed</t>
-        </is>
+      <c r="H31" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="I31" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="J31" s="2" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="32" spans="1:10" ht="261" x14ac:dyDescent="0.35">
@@ -2378,23 +2502,17 @@
       <c r="G32" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The '← Back to Get started' link kept showing on the Connect Machine / Invite / Integrations screens even after the user had finished setting up. It only hid once the user had a project, a connected machine, AND a second teammate who had accepted an invite - so a solo developer (who never needs to invite anyone) saw the link forever.</t>
-        </is>
-      </c>
-      <c r="I32" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Per team decision, the link now hides once the user has a project and a connected machine (inviting a team stays optional), so it no longer nags after setup. frontend features/identity/SetupReturnLink.tsx.</t>
-        </is>
-      </c>
-      <c r="J32" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Fixed</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" spans="1:7" ht="116" x14ac:dyDescent="0.35">
+      <c r="H32" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="I32" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="J32" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" ht="232" x14ac:dyDescent="0.35">
       <c r="A33" s="2">
         <v>32</v>
       </c>
@@ -2410,93 +2528,192 @@
       <c r="G33" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="H33" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">On Phases &amp; Runs, when the companion isn't connected the screen didn't match the wireframe: the Runs panel still showed hardcoded sample/demo runs instead of an empty state, and the disabled phase list didn't match. (Phase names also needed to be human-readable.)</t>
-        </is>
-      </c>
-      <c r="I33" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">When the companion is offline (or there are simply no runs yet) the Runs panel now shows the 'No runs yet' empty state instead of demo rows, matching the S-18 wireframe, and the disabled phase buttons were aligned to the wireframe (Architecture, UX Design, Task Breakdown). Phase names on this screen go through the shared humaniser. Verified live against the running stack. frontend features/lifecycle/PhasesAndRuns.tsx.</t>
-        </is>
-      </c>
-      <c r="J33" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Fixed</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H33" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="I33" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="J33" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A34" s="2">
         <v>33</v>
       </c>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="B34" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G34" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="J34" s="2" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" ht="58" x14ac:dyDescent="0.35">
       <c r="A35" s="2">
         <v>34</v>
       </c>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="B35" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G35" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="J35" s="2" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" ht="261" x14ac:dyDescent="0.35">
       <c r="A36" s="2">
         <v>35</v>
       </c>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="B36" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G36" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J36" s="2" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" ht="232" x14ac:dyDescent="0.35">
       <c r="A37" s="2">
         <v>36</v>
       </c>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="B37" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="G37" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="J37" s="2" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A38" s="2">
         <v>37</v>
       </c>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="B38" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G38" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J38" s="2" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A39" s="2">
         <v>38</v>
       </c>
-    </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="B39" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G39" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="J39" s="2" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" ht="275.5" x14ac:dyDescent="0.35">
       <c r="A40" s="2">
         <v>39</v>
       </c>
-    </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="B40" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G40" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="J40" s="2" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A41" s="2">
         <v>40</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A42" s="2">
         <v>41</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A43" s="2">
         <v>42</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A44" s="2">
         <v>43</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A45" s="2">
         <v>44</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A46" s="2">
         <v>45</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A47" s="2">
         <v>46</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A48" s="2">
         <v>47</v>
       </c>

--- a/docs/Bugs.xlsx
+++ b/docs/Bugs.xlsx
@@ -2690,9 +2690,19 @@
           <t>P1</t>
         </is>
       </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>The connect form saved the vendor's display name ('Confluence') as the connector, but the backend connector registry is keyed by lowercase slugs ('confluence'), so test-connection failed with "No connector registered for docstore:Confluence." Separately, Save gave no confirmation - it mutated silently.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>The form now sends the registered connector slug (from a backend catalog that only lists builder-wired vendors, so this mismatch can't happen), and Save shows an explicit success or error banner (e.g. 'Jira saved. Test the connection to verify it.' / 'already connected'). The grid now shows 'Connected' once a connection is configured. Also fixed a hydration bug so opening an already-connected capability pre-fills its saved vendor/binding and edits via PATCH instead of a duplicate POST. (backend apps/integrations/catalog.py + api/serializers.py + api/views.py catalog endpoint; frontend features/setup/ConnectCapability.tsx + hooks.ts + api.ts + types.ts.) Verified live: Save -&gt; 'Saved' -&gt; Test -&gt; 'Connection OK'.</t>
+        </is>
+      </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Fixed</t>
         </is>
       </c>
     </row>
@@ -2721,9 +2731,19 @@
           <t>P1</t>
         </is>
       </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>The Connect-a-capability form was hardcoded to Confluence-only fields (Space key, Base URL) and a Confluence vendor dropdown for every capability, so all six connectors showed the same form.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Added a backend connector catalog (capability -&gt; its vendors -&gt; that vendor's binding + secret fields) exposed at GET /api/integrations/catalog/. The form now renders the correct vendor list and the correct per-vendor fields for each capability - e.g. Task tracker shows Jira with Project key / Base URL / API token; Design source shows Figma with File key / Access token; Test management shows Xray with Client ID / Client secret; Code intelligence shows the Built-in analyzer with no credentials. The #39 test/save/re-test flow was validated as part of this. (backend apps/integrations/catalog.py; frontend features/setup/ConnectCapability.tsx.)</t>
+        </is>
+      </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Fixed</t>
         </is>
       </c>
     </row>

--- a/docs/Bugs.xlsx
+++ b/docs/Bugs.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30224"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="53" documentId="11_14FDEAE3397E350B81F2A24CBED9C52169691D91" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B05E9CFA-3679-428B-B14E-E5C119705355}"/>
+  <xr:revisionPtr revIDLastSave="63" documentId="11_14FDEAE3397E350B81F2A24CBED9C52169691D91" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FCA15761-6484-4E45-8C2D-86D2E102998D}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
   <metadataTypes count="1">
     <metadataType name="XLRICHVALUE" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1"/>
   </metadataTypes>
-  <futureMetadata name="XLRICHVALUE" count="6">
+  <futureMetadata name="XLRICHVALUE" count="7">
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
@@ -81,8 +81,15 @@
         </ext>
       </extLst>
     </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="6"/>
+        </ext>
+      </extLst>
+    </bk>
   </futureMetadata>
-  <valueMetadata count="6">
+  <valueMetadata count="7">
     <bk>
       <rc t="1" v="0"/>
     </bk>
@@ -101,12 +108,15 @@
     <bk>
       <rc t="1" v="5"/>
     </bk>
+    <bk>
+      <rc t="1" v="6"/>
+    </bk>
   </valueMetadata>
 </metadata>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="406" uniqueCount="195">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="424" uniqueCount="210">
   <si>
     <t>S.No</t>
   </si>
@@ -459,7 +469,7 @@
   </si>
   <si>
     <t xml:space="preserve">Clarifications Page:
-1. When the phase agent is asking clarification questions, the page is showing the options but when user selects "other(please specify)" options he do not have the option to enter the details. 
+1. When the phase agent is asking clarification questions, the page is showing the options but when user selects "other(please specify)" option, he do not have the option to enter the details. 
 </t>
   </si>
   <si>
@@ -473,7 +483,7 @@
   </si>
   <si>
     <t>Artifacts related:
-1. When registering the generated artifacts, the agent is aking clarification to get the project Id which the user may not know so that should be taken care by the system itself instead of aksing the user.</t>
+1. When registering the generated artifacts, the agent is asking clarification to get the project Id which the user may not know so that should be taken care by the system itself instead of aksing the user.</t>
   </si>
   <si>
     <t>When registering generated artifacts the agent raised a clarification asking the user for the project id, which the user can't know. The registration tool required project_id (and run_id) as inputs, so if the agent didn't have them it asked.</t>
@@ -599,6 +609,12 @@
   </si>
   <si>
     <t>Integrations</t>
+  </si>
+  <si>
+    <t>Each connector card's icon was derived from the vendor name's first letter plus a per-vendor colour class. Before a vendor is connected the vendor is 'Not connected', which matched no colour class (and produced an invalid class with a space), so the icon effectively showed nothing until a connection was made.</t>
+  </si>
+  <si>
+    <t>The card icon is now keyed to the capability (docstore, tasktracker, design source, etc.), so a distinct, coloured 2-letter icon is always visible by default; once a real vendor is connected it still shows the vendor's initial and colour. Verified live: all six capability cards show their icons before any connection. Files: frontend/src/components/ui/index.tsx, frontend/src/features/setup/Integrations.tsx, frontend/src/styles/components.css.</t>
   </si>
   <si>
     <t xml:space="preserve">In Integrations - under connect a capability page: 
@@ -750,15 +766,30 @@
     <t>While a role change is saving, the info banner reads 'Saving role change for Tom Reyes (reviewer @ ...)' regardless of who was actually changed; the project-name fallback is also the sample 'Payment Gateway v2'.</t>
   </si>
   <si>
-    <t>Sample text left in a live view state (RolesMatrix.tsx line 121) and a stale demo default for the project name (line 46).</t>
+    <t>The 'saving' info banner was a static gallery placeholder that always read 'Saving role change for Tom Reyes (reviewer @ ...)' regardless of who was actually changed, and the project-name fell back to the sample 'Payment Gateway v2' when no project name was available.</t>
+  </si>
+  <si>
+    <t>The screen now tracks which user and role are being saved and renders the banner from that real change ('Saving role change for &lt;user&gt; (&lt;role&gt; @ &lt;project&gt;)...'), and the project-name fallback is now a neutral 'this project'. Verified live: toggling the reviewer role showed 'Saving role change for Demo User (Reviewer @ Demo Project)', and the project selector shows the real project name. Files: frontend/src/features/identity/RolesMatrix.tsx.</t>
   </si>
   <si>
     <t>In Clarifications Page: To Register any Phase artifacts, the system is asking the user for project UUID which is not appropriate because it should be dynamically passed. The backend server error:  register_artifact platform-state tool is returning a 500 error: The runner is not injecting the project_id into the call as documented. 
 Note: The same is also put previously in one of the above Bug/Issues but it was not yet fixed. The team wants you to accurately reason the issue and fix it.</t>
   </si>
   <si>
+    <t>Registering a phase artifact 500'd and the agent then fell back to asking the user for the project UUID, because the project id was not being bound on the companion planning/review launch. The earlier fix (row 25) bound the project id on the build path and the two server-side paths, but missed the companion daemon's planning/review path: runner/companion/daemon.py's state_mcp_servers set the run and phase but never RUNNER_PROJECT_ID. So register_artifact sent an empty project id and the backend Project lookup raised a 500 (and the agent, unable to resolve it, asked the human).</t>
+  </si>
+  <si>
+    <t>Bound the project id on that last launch seam too. daemon.py now passes the dispatched project_id into state_mcp_servers, which sets RUNNER_PROJECT_ID in the MCP server's environment exactly like the build path already did, so register_artifact fills the project id (and run id) from the run automatically and never asks the user. Added a regression test asserting the project id reaches the launch env. Files: runner/companion/daemon.py; test in backend/tests/test_companion_daemon.py.</t>
+  </si>
+  <si>
     <t>In Work items page, After a phase is invoked and system is waiting for gate approavl: the work items board card for that phase is showing: Phase Gate gate. The work gate is being repeated two times which is not human friendly.
 Note: The same issues should not persist for any phase board cards when invoked and waiting for gates. Any where in the eniter page: The content which is static and dynamically showing should be properly humanised so the user feels good and understanding the App.</t>
+  </si>
+  <si>
+    <t>The work-items board card built its gate label on the backend as '{gate_type} gate', and the gate_type is 'phase_gate', so after the frontend humanised it the card read 'Phase Gate gate' - the word 'gate' twice.</t>
+  </si>
+  <si>
+    <t>The backend now builds a clean, humanised gate label (humanize_gate in backend/api/views.py) that drops the duplicate word and the underscore, so every board card reads 'Phase gate' - fixed dynamically for all phases, not just this one. Verified live on the board and dashboard. Files: backend/api/views.py, frontend/src/features/lifecycle/phases.ts.</t>
   </si>
   <si>
     <t>In Phases &amp; Runs Page: Under Runs card, 
@@ -773,16 +804,43 @@
 Note: Any where in the eniter page: The content which is static and dynamically showing should be properly humanised so the user feels good and understanding the App.</t>
   </si>
   <si>
+    <t>The Gates approval panel rendered '{gateLabel(gate_type)} gate', and gateLabel('phase_gate') already produced 'Phase Gate', so appending ' gate' gave 'Phase Gate gate' - 'gate' twice.</t>
+  </si>
+  <si>
+    <t>Introduced one shared gateLabel helper (phases.ts) that returns the whole phrase with exactly one lowercase 'gate' and no underscores, and removed the extra ' gate' the panel was appending. The approval box now reads 'Phase gate'. Verified live on the Gates page. Files: frontend/src/features/lifecycle/Gates.tsx, phases.ts.</t>
+  </si>
+  <si>
     <t>In Work Items page, Under work items lifecycle window, to the right hand side the approve gate disply box showing the word "gate" repeated two times and the phase_gate with underscore should also be fixed.
 The latest run options also has the underscore issue under status option (phase_gate) should be humanised
 Note: All fixes should be dynamic and should not persist for any other phases or gates. Any where in the eniter page: The content which is static and dynamically showing should be properly humanised so the user feels good and understanding the App.</t>
   </si>
   <si>
+    <t>Two raw strings leaked on the work-item detail: the approve-gate box showed '{gate_type} gate' ('phase_gate gate'), and the latest run's status was shown as the raw value 'awaiting_gate' with an underscore.</t>
+  </si>
+  <si>
+    <t>Gate labels now go through the shared gateLabel helper (no duplicate 'gate', no underscore) and statuses/states through a new statusLabel helper ('awaiting_gate' -&gt; 'Awaiting gate'). Applied across WorkItemEpic, WorkItemTask, WorkItemDefect, TaskBreakdown and the PhaseConsole status badge, so it is fixed for every phase/gate/status, not just this screen. Verified live on the work-item detail (Status now reads 'Awaiting gate', gate reads 'Phase gate'). Files: frontend/src/features/lifecycle/{phases.ts, WorkItemEpic.tsx, WorkItemTask.tsx, WorkItemDefect.tsx, TaskBreakdown.tsx}, components/PhaseConsole.tsx.</t>
+  </si>
+  <si>
     <t>In the Workspace Dashboard page: Under needs me section, for pahse gates the word "gate" is being repeated two times which need to be fixed dynamically and for phase Runs any gate awaiting is showing "awaiting_gate" with underscore which also needs humanising (No underscores).
 Note: Any where in the eniter page: The content which is static and dynamically showing should be properly humanised so the user feels good and understanding the App.</t>
   </si>
   <si>
     <t>Workspace Dashboard</t>
+  </si>
+  <si>
+    <t>The dashboard 'Needs me' gate item rendered 'phaseLabel(gate) gate' which came out as 'Phase Gate gate', and the runs list showed the raw status 'awaiting_gate' with an underscore.</t>
+  </si>
+  <si>
+    <t>Switched the gate item to the shared gateLabel helper and the run status to statusLabel, so 'Needs me' reads 'Phase gate' and runs read 'Awaiting gate'. Verified live on the Workspace Dashboard. Files: frontend/src/features/observability/Dashboard.tsx, phases.ts.</t>
+  </si>
+  <si>
+    <t>In the Artifacts &amp; Traceability page: 
+1. When a phase run has generated certain artifacts, the user is not able to preview the artifacts in order to review them and approve the gate. When clicked on preview it is loading for a while and showing an error message as: Artifact not found, This artifact doesn't exist, has no body, or you don't have access to it.
+2. The user has connected to confluence, after approving the phase gate will the artifacts be exported to the respective conflucence account? Is there a flexibility for the user to be able to push/export the generated artifacts manually to the respective conntected integrations?
+Note: If you need creds for live testing for the export which the team has used for testing, you must ask the team for creds while fixing this issue!</t>
+  </si>
+  <si>
+    <t>artifacts &amp; Traceability</t>
   </si>
 </sst>
 </file>
@@ -1626,7 +1684,7 @@
 </file>
 
 <file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
-<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="6">
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="7">
   <rv s="0">
     <v>0</v>
     <v>5</v>
@@ -1651,6 +1709,10 @@
     <v>5</v>
     <v>5</v>
   </rv>
+  <rv s="0">
+    <v>6</v>
+    <v>5</v>
+  </rv>
 </rvData>
 </file>
 
@@ -1671,6 +1733,7 @@
   <rel r:id="rId4"/>
   <rel r:id="rId5"/>
   <rel r:id="rId6"/>
+  <rel r:id="rId7"/>
 </richValueRels>
 </file>
 
@@ -2086,8 +2149,18 @@
       <c r="G4" s="2" t="s">
         <v>23</v>
       </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Most forms already had placeholders, but several fields were left blank: all Project Profile fields except tech stack, the free-text clarification answer box, and the repository base-branch input. Nothing guided the user on what to type.</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Added helpful example placeholders to every remaining form field: all seven Project Profile fields, the clarification answer box ('Type your answer...'), and the repository base branch ('main'). Together with row 33 this closes the app-wide placeholder sweep. Files: frontend ProjectProfileEditor.tsx, Clarifications.tsx, Repositories.tsx.</t>
+        </is>
+      </c>
       <c r="J4" s="2" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="29.1" customHeight="1">
@@ -2864,8 +2937,18 @@
       <c r="G34" s="2" t="s">
         <v>23</v>
       </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Only the tech-stack field of the Project Profile carried a placeholder; description, domain, coding standards, NFRs, constraints, glossary and important context gave the user no example of what good input looks like.</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Every Project Profile field now shows a realistic example placeholder (e.g. domain: 'Personal finance, Healthcare, E-commerce'; NFRs: response-time / uptime / accessibility examples). Verified in the browser - all 8 fields show guidance when empty. File: frontend/src/features/setup/ProjectProfileEditor.tsx.</t>
+        </is>
+      </c>
       <c r="J34" s="2" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
     </row>
     <row r="35" spans="1:10" ht="57.95" customHeight="1">
@@ -2884,8 +2967,18 @@
       <c r="G35" s="2" t="s">
         <v>23</v>
       </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The companion status pill used near-white text on the white top bar (it was styled once for the dark sidebar and reused on the light header), so 'Companion: Offline' and 'Companion: Ready' were barely readable in the header.</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The pill now has high-contrast styling in both places: solid white bold text in the dark sidebar, and state-coloured text (red offline, green ready, amber connecting) on a bordered tint in the white top bar. Verified in the browser - the header pill reads clearly in both states. File: frontend/src/styles/components.css.</t>
+        </is>
+      </c>
       <c r="J35" s="2" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
     </row>
     <row r="36" spans="1:10" ht="261" customHeight="1">
@@ -2924,8 +3017,18 @@
       <c r="G37" s="2" t="s">
         <v>23</v>
       </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The Type dropdown's helper text described work-item types with internal jargon ('plan tier', 'build tier', 'remediation tier') that means nothing to a user.</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rewrote the helper in plain language: Epic - a large feature that goes through all the planning phases from Ideation to Task Breakdown; Story - a smaller user-facing piece of an epic; Task - a concrete development job that gets implemented, code-reviewed and tested; Defect - a bug fix on the shorter fix-and-verify flow. Verified in the browser. File: frontend/src/features/lifecycle/WorkItemsBoard.tsx.</t>
+        </is>
+      </c>
       <c r="J37" s="2" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
     </row>
     <row r="38" spans="1:10" ht="101.45" customHeight="1">
@@ -2944,15 +3047,11 @@
       <c r="G38" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="H38" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Each connector card's icon was derived from the vendor name's first letter plus a per-vendor colour class. Before a vendor is connected the vendor is 'Not connected', which matched no colour class (and produced an invalid class with a space), so the icon effectively showed nothing until a connection was made.</t>
-        </is>
-      </c>
-      <c r="I38" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The card icon is now keyed to the capability (docstore, tasktracker, design source, etc.), so a distinct, coloured 2-letter icon is always visible by default; once a real vendor is connected it still shows the vendor's initial and colour. Verified live: all six capability cards show their icons before any connection. Files: frontend/src/components/ui/index.tsx, frontend/src/features/setup/Integrations.tsx, frontend/src/styles/components.css.</t>
-        </is>
+      <c r="H38" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="I38" s="2" t="s">
+        <v>141</v>
       </c>
       <c r="J38" s="2" t="s">
         <v>16</v>
@@ -2963,7 +3062,7 @@
         <v>38</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="D39" s="2" t="s">
         <v>139</v>
@@ -2975,10 +3074,10 @@
         <v>13</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="I39" s="2" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="J39" s="2" t="s">
         <v>16</v>
@@ -2989,7 +3088,7 @@
         <v>39</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="D40" s="2" t="s">
         <v>139</v>
@@ -3001,10 +3100,10 @@
         <v>13</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="I40" s="2" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="J40" s="2" t="s">
         <v>16</v>
@@ -3015,7 +3114,7 @@
         <v>40</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="D41" s="2" t="s">
         <v>71</v>
@@ -3024,16 +3123,16 @@
         <v>12</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="G41" s="2" t="s">
         <v>35</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="I41" s="2" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="J41" s="2" t="s">
         <v>16</v>
@@ -3044,10 +3143,10 @@
         <v>41</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D42" s="2" t="s">
         <v>71</v>
@@ -3056,16 +3155,16 @@
         <v>12</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="G42" s="2" t="s">
         <v>35</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="I42" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="J42" s="2" t="s">
         <v>16</v>
@@ -3076,7 +3175,7 @@
         <v>42</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="D43" s="2" t="s">
         <v>71</v>
@@ -3085,16 +3184,16 @@
         <v>12</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="G43" s="2" t="s">
         <v>35</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="I43" s="2" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="J43" s="2" t="s">
         <v>16</v>
@@ -3105,7 +3204,7 @@
         <v>43</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="D44" s="2" t="s">
         <v>71</v>
@@ -3114,16 +3213,16 @@
         <v>12</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="G44" s="2" t="s">
         <v>35</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="I44" s="2" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="J44" s="2" t="s">
         <v>16</v>
@@ -3134,7 +3233,7 @@
         <v>44</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="D45" s="2" t="s">
         <v>129</v>
@@ -3143,16 +3242,16 @@
         <v>12</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="G45" s="2" t="s">
         <v>35</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="I45" s="2" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="J45" s="2" t="s">
         <v>16</v>
@@ -3163,25 +3262,25 @@
         <v>45</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="E46" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="G46" s="2" t="s">
         <v>35</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="I46" s="2" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="J46" s="2" t="s">
         <v>16</v>
@@ -3192,25 +3291,25 @@
         <v>46</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="E47" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="G47" s="2" t="s">
         <v>35</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="I47" s="2" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="J47" s="2" t="s">
         <v>16</v>
@@ -3221,25 +3320,25 @@
         <v>47</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="E48" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="G48" s="2" t="s">
         <v>23</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="I48" s="2" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="J48" s="2" t="s">
         <v>16</v>
@@ -3250,7 +3349,7 @@
         <v>48</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="D49" s="2" t="s">
         <v>139</v>
@@ -3259,16 +3358,16 @@
         <v>53</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="G49" s="2" t="s">
         <v>23</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="I49" s="2" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="J49" s="2" t="s">
         <v>16</v>
@@ -3279,10 +3378,10 @@
         <v>49</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="D50" s="2" t="s">
         <v>71</v>
@@ -3291,16 +3390,23 @@
         <v>12</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="G50" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="H50" s="2" t="s">
-        <v>179</v>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The search box and the Phase/Role/Status dropdowns were static markup with no state or wiring - only the level chips filtered. The dropdowns also had no options to offer because the board had no notion of an item's current phase.</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">All four controls now work, client-side over the loaded board (same approach as the Artifacts fix, row 24): search matches key/title/type/stream; Phase and Status options are the distinct values actually present; Role filters by the gate role responsible for the item's current phase (from the live phase catalog). Verified in the browser: phase filter narrows to matching cards, a non-matching search empties the board. File: frontend/src/features/lifecycle/WorkItemsBoard.tsx (+ backend current_phase, see row 50).</t>
+        </is>
       </c>
       <c r="J50" s="2" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
     </row>
     <row r="51" spans="1:10" ht="64.5">
@@ -3308,7 +3414,7 @@
         <v>50</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="D51" s="2" t="s">
         <v>71</v>
@@ -3317,16 +3423,23 @@
         <v>12</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="G51" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="H51" s="2" t="s">
-        <v>181</v>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The 'Phase' column (and the board's column placement) used the work item's feature-stream text as if it were a phase - the platform never told the frontend what phase an item was actually in.</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The backend now computes each item's current phase (its latest run's agent phase, one query for the whole board) and serves it on the card payload; the list's Phase column shows that real phase ('PRD', or 'Not started'), and board cards land in their actual phase column. Feature stream is no longer misused as a phase anywhere on the board. Verified live: the story with a PRD run shows Phase 'PRD' and sits in the '3. PRD' column. Files: backend/api/views.py (_card_fields), frontend WorkItemsBoard.tsx, regression test in test_work_items_card_fields.py.</t>
+        </is>
       </c>
       <c r="J51" s="2" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
     </row>
     <row r="52" spans="1:10" ht="81">
@@ -3334,28 +3447,35 @@
         <v>51</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="E52" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="G52" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="H52" s="2" t="s">
-        <v>184</v>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The admin screens fetch the users list, which returns 403 for a non-admin; the screens rendered nothing with the error unhandled - a blank, broken page for anyone who deep-linked to /admin/roles or /admin/users.</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Added a route-level admin guard: all /admin/* routes now render a clear 'Admin access needed' panel (what the page is, who can use it, a back-to-dashboard button) for non-admins instead of mounting the broken screens. Verified live as a non-admin user. File: frontend/src/routes.tsx (RequireAdmin).</t>
+        </is>
       </c>
       <c r="J52" s="2" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
     </row>
     <row r="53" spans="1:10" ht="96.75">
@@ -3363,32 +3483,28 @@
         <v>52</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="E53" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="G53" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="H53" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The 'saving' info banner was a static gallery placeholder that always read 'Saving role change for Tom Reyes (reviewer @ ...)' regardless of who was actually changed, and the project-name fell back to the sample 'Payment Gateway v2' when no project name was available.</t>
-        </is>
-      </c>
-      <c r="I53" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The screen now tracks which user and role are being saved and renders the banner from that real change ('Saving role change for &lt;user&gt; (&lt;role&gt; @ &lt;project&gt;)...'), and the project-name fallback is now a neutral 'this project'. Verified live: toggling the reviewer role showed 'Saving role change for Demo User (Reviewer @ Demo Project)', and the project selector shows the real project name. Files: frontend/src/features/identity/RolesMatrix.tsx.</t>
-        </is>
+      <c r="H53" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="I53" s="2" t="s">
+        <v>190</v>
       </c>
       <c r="J53" s="2" t="s">
         <v>16</v>
@@ -3399,7 +3515,7 @@
         <v>53</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="D54" s="2" t="s">
         <v>99</v>
@@ -3413,15 +3529,11 @@
       <c r="G54" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="H54" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Registering a phase artifact 500'd and the agent then fell back to asking the user for the project UUID, because the project id was not being bound on the companion planning/review launch. The earlier fix (row 25) bound the project id on the build path and the two server-side paths, but missed the companion daemon's planning/review path: runner/companion/daemon.py's state_mcp_servers set the run and phase but never RUNNER_PROJECT_ID. So register_artifact sent an empty project id and the backend Project lookup raised a 500 (and the agent, unable to resolve it, asked the human).</t>
-        </is>
-      </c>
-      <c r="I54" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bound the project id on that last launch seam too. daemon.py now passes the dispatched project_id into state_mcp_servers, which sets RUNNER_PROJECT_ID in the MCP server's environment exactly like the build path already did, so register_artifact fills the project id (and run id) from the run automatically and never asks the user. Added a regression test asserting the project id reaches the launch env. Files: runner/companion/daemon.py; test in backend/tests/test_companion_daemon.py.</t>
-        </is>
+      <c r="H54" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="I54" s="2" t="s">
+        <v>193</v>
       </c>
       <c r="J54" s="2" t="s">
         <v>16</v>
@@ -3432,7 +3544,7 @@
         <v>54</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="D55" s="2" t="s">
         <v>71</v>
@@ -3446,15 +3558,11 @@
       <c r="G55" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="H55" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The work-items board card built its gate label on the backend as '{gate_type} gate', and the gate_type is 'phase_gate', so after the frontend humanised it the card read 'Phase Gate gate' - the word 'gate' twice.</t>
-        </is>
-      </c>
-      <c r="I55" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The backend now builds a clean, humanised gate label (humanize_gate in backend/api/views.py) that drops the duplicate word and the underscore, so every board card reads 'Phase gate' - fixed dynamically for all phases, not just this one. Verified live on the board and dashboard. Files: backend/api/views.py, frontend/src/features/lifecycle/phases.ts.</t>
-        </is>
+      <c r="H55" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="I55" s="2" t="s">
+        <v>196</v>
       </c>
       <c r="J55" s="2" t="s">
         <v>16</v>
@@ -3465,7 +3573,7 @@
         <v>55</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="D56" s="2" t="s">
         <v>129</v>
@@ -3479,8 +3587,18 @@
       <c r="G56" s="2" t="s">
         <v>23</v>
       </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The Runs table rendered raw values straight from the API: the status token ('awaiting_gate'), the full run UUID and Temporal workflow id, and the unformatted ISO timestamp.</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The table is now fully humanised and dynamic for every run: status via the shared statusLabel helper ('Awaiting gate'); the run shows a short reference ('Run 6b6443fa') that links to the run console with the full id on hover; the workflow id is shortened the same way (full value on hover); Created renders as a locale-formatted date ('Jul 7, 2026, 9:38 PM'). Status colours also understand awaiting_gate/approved/rejected now. Verified live. File: frontend/src/features/lifecycle/PhasesAndRuns.tsx.</t>
+        </is>
+      </c>
       <c r="J56" s="2" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
     </row>
     <row r="57" spans="1:10" ht="291.75">
@@ -3488,10 +3606,10 @@
         <v>56</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="E57" s="2" t="s">
         <v>12</v>
@@ -3502,15 +3620,11 @@
       <c r="G57" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="H57" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The Gates approval panel rendered '{gateLabel(gate_type)} gate', and gateLabel('phase_gate') already produced 'Phase Gate', so appending ' gate' gave 'Phase Gate gate' - 'gate' twice.</t>
-        </is>
-      </c>
-      <c r="I57" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Introduced one shared gateLabel helper (phases.ts) that returns the whole phrase with exactly one lowercase 'gate' and no underscores, and removed the extra ' gate' the panel was appending. The approval box now reads 'Phase gate'. Verified live on the Gates page. Files: frontend/src/features/lifecycle/Gates.tsx, phases.ts.</t>
-        </is>
+      <c r="H57" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="I57" s="2" t="s">
+        <v>200</v>
       </c>
       <c r="J57" s="2" t="s">
         <v>16</v>
@@ -3521,7 +3635,7 @@
         <v>57</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="D58" s="2" t="s">
         <v>71</v>
@@ -3535,15 +3649,11 @@
       <c r="G58" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="H58" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Two raw strings leaked on the work-item detail: the approve-gate box showed '{gate_type} gate' ('phase_gate gate'), and the latest run's status was shown as the raw value 'awaiting_gate' with an underscore.</t>
-        </is>
-      </c>
-      <c r="I58" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gate labels now go through the shared gateLabel helper (no duplicate 'gate', no underscore) and statuses/states through a new statusLabel helper ('awaiting_gate' -&gt; 'Awaiting gate'). Applied across WorkItemEpic, WorkItemTask, WorkItemDefect, TaskBreakdown and the PhaseConsole status badge, so it is fixed for every phase/gate/status, not just this screen. Verified live on the work-item detail (Status now reads 'Awaiting gate', gate reads 'Phase gate'). Files: frontend/src/features/lifecycle/{phases.ts, WorkItemEpic.tsx, WorkItemTask.tsx, WorkItemDefect.tsx, TaskBreakdown.tsx}, components/PhaseConsole.tsx.</t>
-        </is>
+      <c r="H58" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="I58" s="2" t="s">
+        <v>203</v>
       </c>
       <c r="J58" s="2" t="s">
         <v>16</v>
@@ -3554,10 +3664,10 @@
         <v>58</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>193</v>
+        <v>204</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>194</v>
+        <v>205</v>
       </c>
       <c r="E59" s="2" t="s">
         <v>12</v>
@@ -3568,23 +3678,47 @@
       <c r="G59" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="H59" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The dashboard 'Needs me' gate item rendered 'phaseLabel(gate) gate' which came out as 'Phase Gate gate', and the runs list showed the raw status 'awaiting_gate' with an underscore.</t>
-        </is>
-      </c>
-      <c r="I59" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Switched the gate item to the shared gateLabel helper and the run status to statusLabel, so 'Needs me' reads 'Phase gate' and runs read 'Awaiting gate'. Verified live on the Workspace Dashboard. Files: frontend/src/features/observability/Dashboard.tsx, phases.ts.</t>
-        </is>
+      <c r="H59" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="I59" s="2" t="s">
+        <v>207</v>
       </c>
       <c r="J59" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="60" spans="1:10">
+    <row r="60" spans="1:10" ht="409.6">
       <c r="A60" s="2">
         <v>59</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="D60" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="E60" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F60" s="2" t="e" vm="7">
+        <v>#VALUE!</v>
+      </c>
+      <c r="G60" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Two compounding defects. (1) Preview: agents register artifacts during a run as pointers only (content hash, no body, no S3 key - correct per the architecture), and the platform step that stages the phase body to S3 (register_phase_result_core) skipped itself whenever the agent had already registered an artifact of the phase's type for that run - its idempotency check treated the agent's pointer row as 'already done'. So the body was never written to S3 and NO artifact of the run had a body anywhere; preview found nothing and returned 404 ('Artifact not found'). The long loading is the frontend retrying before giving up. The full phase output was sitting unused on the run's report. Also, the internal S3 read was unguarded, so a missing object crashed the endpoint with a 500 instead of degrading. (2) Export: auto-export to Confluence on gate approval existed only for docstore-mapped types (requirements/prd/architecture/adr), and the manual Publish endpoint was a stub - it flipped the status and fabricated a link without ever calling the Confluence connector, and it refused artifacts that had already auto-published as internal, so a later 'connect Confluence then push' was impossible.</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(1) Preview now always works: the report step always stages the phase body to S3 and backfills the agent-registered artifact's S3 pointer instead of skipping (orchestration/activities.py); preview falls back through own draft -&gt; inline draft -&gt; the run's staged/reported body, and the S3 read is guarded (integrations/preview.py). The team's existing 7 body-less artifacts preview correctly with no data migration - verified in the browser. (2) Export answers: YES - after gate approval, docstore-mapped artifact types auto-export to the connected Confluence; and YES - manual push now exists for real: the Publish screen calls the Confluence connector, honours the space key, records true provenance (page id + URL), and allows re-export of artifacts that published as internal before a connector existed. Verified live end-to-end with the team's creds: page 'Greenfield MVP - Ideation' created in the SDLC space (page id 11927553) and the returned link opens it. Files: backend/orchestration/activities.py, backend/integrations/preview.py, backend/integrations/publish.py, backend/api/views.py; tests in test_phase_dispatch.py, test_artifact_preview_rest.py, test_frontend_integration.py, journey tests.</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="61" spans="1:10">

--- a/docs/Bugs.xlsx
+++ b/docs/Bugs.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30224"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="63" documentId="11_14FDEAE3397E350B81F2A24CBED9C52169691D91" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FCA15761-6484-4E45-8C2D-86D2E102998D}"/>
+  <xr:revisionPtr revIDLastSave="78" documentId="11_14FDEAE3397E350B81F2A24CBED9C52169691D91" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{456516D8-70B7-4682-A3C6-67807BA1CC65}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
   <metadataTypes count="1">
     <metadataType name="XLRICHVALUE" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1"/>
   </metadataTypes>
-  <futureMetadata name="XLRICHVALUE" count="7">
+  <futureMetadata name="XLRICHVALUE" count="9">
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
@@ -88,8 +88,22 @@
         </ext>
       </extLst>
     </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="7"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="8"/>
+        </ext>
+      </extLst>
+    </bk>
   </futureMetadata>
-  <valueMetadata count="7">
+  <valueMetadata count="9">
     <bk>
       <rc t="1" v="0"/>
     </bk>
@@ -111,12 +125,18 @@
     <bk>
       <rc t="1" v="6"/>
     </bk>
+    <bk>
+      <rc t="1" v="7"/>
+    </bk>
+    <bk>
+      <rc t="1" v="8"/>
+    </bk>
   </valueMetadata>
 </metadata>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="424" uniqueCount="210">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="449" uniqueCount="228">
   <si>
     <t>S.No</t>
   </si>
@@ -190,7 +210,10 @@
     <t>P3</t>
   </si>
   <si>
-    <t>Open</t>
+    <t>Most forms already had placeholders, but several fields were left blank: all Project Profile fields except tech stack, the free-text clarification answer box, and the repository base-branch input. Nothing guided the user on what to type.</t>
+  </si>
+  <si>
+    <t>Added helpful example placeholders to every remaining form field: all seven Project Profile fields, the clarification answer box ('Type your answer...'), and the repository base branch ('main'). Together with row 33 this closes the app-wide placeholder sweep. Files: frontend ProjectProfileEditor.tsx, Clarifications.tsx, Repositories.tsx.</t>
   </si>
   <si>
     <t>Showing default values in Signup form</t>
@@ -587,14 +610,29 @@
     <t>In project profile page, the placeholders should be shown for all the fields to be filled, currently only tech stack is available.</t>
   </si>
   <si>
+    <t>Only the tech-stack field of the Project Profile carried a placeholder; description, domain, coding standards, NFRs, constraints, glossary and important context gave the user no example of what good input looks like.</t>
+  </si>
+  <si>
+    <t>Every Project Profile field now shows a realistic example placeholder (e.g. domain: 'Personal finance, Healthcare, E-commerce'; NFRs: response-time / uptime / accessibility examples). Verified in the browser - all 8 fields show guidance when empty. File: frontend/src/features/setup/ProjectProfileEditor.tsx.</t>
+  </si>
+  <si>
     <t>In the Navigation bar, the companion status text is not clearly visible / too light in colour - not only when the companion is offline but also after it comes online.</t>
   </si>
   <si>
     <t>Navigation Bar</t>
+  </si>
+  <si>
+    <t>The companion status pill used near-white text on the white top bar (it was styled once for the dark sidebar and reused on the light header), so 'Companion: Offline' and 'Companion: Ready' were barely readable in the header.</t>
+  </si>
+  <si>
+    <t>The pill now has high-contrast styling in both places: solid white bold text in the dark sidebar, and state-coloured text (red offline, green ready, amber connecting) on a bordered tint in the white top bar. Verified in the browser - the header pill reads clearly in both states. File: frontend/src/styles/components.css.</t>
   </si>
   <si>
     <t>While connecting to the Claude Code in the users local system/machine (Companion): Currently the user has to connect to claude code by giving a command containing a token by giving to the claude in local CLI, the user has to be in the backend repository in the CLI to perform this. This is not a user friendly approach
 Enhancement: The approach has to be changed, while fixing this issues discuss with team the best possible way of dealing it.</t>
+  </si>
+  <si>
+    <t>Open</t>
   </si>
   <si>
     <t xml:space="preserve">When clicked on create work item, the below text appears below the type dropdown. This needs to be updated
@@ -603,6 +641,12 @@
   </si>
   <si>
     <t>bug</t>
+  </si>
+  <si>
+    <t>The Type dropdown's helper text described work-item types with internal jargon ('plan tier', 'build tier', 'remediation tier') that means nothing to a user.</t>
+  </si>
+  <si>
+    <t>Rewrote the helper in plain language: Epic - a large feature that goes through all the planning phases from Ideation to Task Breakdown; Story - a smaller user-facing piece of an epic; Task - a concrete development job that gets implemented, code-reviewed and tested; Defect - a bug fix on the shorter fix-and-verify flow. Verified in the browser. File: frontend/src/features/lifecycle/WorkItemsBoard.tsx.</t>
   </si>
   <si>
     <t>In the integration page: The Icons on each card are not visible until the connection is made by the user, but by default the icons should be visible to the user for better understanding.</t>
@@ -742,13 +786,19 @@
     <t>Only the level chips (Epics/Tasks/Defects) actually filter; the search box and the three dropdowns are inert. Same class of issue as the Artifacts search/filter fixed under row 24.</t>
   </si>
   <si>
-    <t>The search box and the Phase/Role/Status dropdowns are static markup with no wiring.</t>
+    <t>The search box and the Phase/Role/Status dropdowns were static markup with no state or wiring - only the level chips filtered. The dropdowns also had no options to offer because the board had no notion of an item's current phase.</t>
+  </si>
+  <si>
+    <t>All four controls now work, client-side over the loaded board (same approach as the Artifacts fix, row 24): search matches key/title/type/stream; Phase and Status options are the distinct values actually present; Role filters by the gate role responsible for the item's current phase (from the live phase catalog). Verified in the browser: phase filter narrows to matching cards, a non-matching search empties the board. File: frontend/src/features/lifecycle/WorkItemsBoard.tsx (+ backend current_phase, see row 50).</t>
   </si>
   <si>
     <t>Work Items list 'Phase' column actually shows the feature stream, not the phase</t>
   </si>
   <si>
-    <t>The column headed 'Phase' renders the work item's feature-stream text instead of its current phase.</t>
+    <t>The 'Phase' column (and the board's column placement) used the work item's feature-stream text as if it were a phase - the platform never told the frontend what phase an item was actually in.</t>
+  </si>
+  <si>
+    <t>The backend now computes each item's current phase (its latest run's agent phase, one query for the whole board) and serves it on the card payload; the list's Phase column shows that real phase ('PRD', or 'Not started'), and board cards land in their actual phase column. Feature stream is no longer misused as a phase anywhere on the board. Verified live: the story with a PRD run shows Phase 'PRD' and sits in the '3. PRD' column. Files: backend/api/views.py (_card_fields), frontend WorkItemsBoard.tsx, regression test in test_work_items_card_fields.py.</t>
   </si>
   <si>
     <t>A non-admin who opens the Roles/Users admin pages by URL sees a blank, broken screen</t>
@@ -757,7 +807,10 @@
     <t>Happens for a signed-in non-admin user - the admin nav is correctly hidden, but the /admin/roles and /admin/users URLs are still directly reachable.</t>
   </si>
   <si>
-    <t>The admin screens fetch the users list, which returns 403 for a non-admin; the screen then renders nothing - no rows, no error, no redirect.</t>
+    <t>The admin screens fetch the users list, which returns 403 for a non-admin; the screens rendered nothing with the error unhandled - a blank, broken page for anyone who deep-linked to /admin/roles or /admin/users.</t>
+  </si>
+  <si>
+    <t>Added a route-level admin guard: all /admin/* routes now render a clear 'Admin access needed' panel (what the page is, who can use it, a back-to-dashboard button) for non-admins instead of mounting the broken screens. Verified live as a non-admin user. File: frontend/src/routes.tsx (RequireAdmin).</t>
   </si>
   <si>
     <t>Hardcoded 'Tom Reyes' and 'Payment Gateway v2' in the live Roles &amp; memberships screen</t>
@@ -800,6 +853,12 @@
 Note: Any where in the eniter page: The content which is static and dynamically showing should be properly humanised so the user feels good and understanding the App.</t>
   </si>
   <si>
+    <t>The Runs table rendered raw values straight from the API: the status token ('awaiting_gate'), the full run UUID and Temporal workflow id, and the unformatted ISO timestamp.</t>
+  </si>
+  <si>
+    <t>The table is now fully humanised and dynamic for every run: status via the shared statusLabel helper ('Awaiting gate'); the run shows a short reference ('Run 6b6443fa') that links to the run console with the full id on hover; the workflow id is shortened the same way (full value on hover); Created renders as a locale-formatted date ('Jul 7, 2026, 9:38 PM'). Status colours also understand awaiting_gate/approved/rejected now. Verified live. File: frontend/src/features/lifecycle/PhasesAndRuns.tsx.</t>
+  </si>
+  <si>
     <t>In Gates page: On the right hand side there is a approval box in which the user can enter his approval message, on the top of that box the work "gate is repeated two times which should be fixed and humanised properly.
 Note: Any where in the eniter page: The content which is static and dynamically showing should be properly humanised so the user feels good and understanding the App.</t>
   </si>
@@ -841,6 +900,28 @@
   </si>
   <si>
     <t>artifacts &amp; Traceability</t>
+  </si>
+  <si>
+    <t>Two compounding defects. (1) Preview: agents register artifacts during a run as pointers only (content hash, no body, no S3 key - correct per the architecture), and the platform step that stages the phase body to S3 (register_phase_result_core) skipped itself whenever the agent had already registered an artifact of the phase's type for that run - its idempotency check treated the agent's pointer row as 'already done'. So the body was never written to S3 and NO artifact of the run had a body anywhere; preview found nothing and returned 404 ('Artifact not found'). The long loading is the frontend retrying before giving up. The full phase output was sitting unused on the run's report. Also, the internal S3 read was unguarded, so a missing object crashed the endpoint with a 500 instead of degrading. (2) Export: auto-export to Confluence on gate approval existed only for docstore-mapped types (requirements/prd/architecture/adr), and the manual Publish endpoint was a stub - it flipped the status and fabricated a link without ever calling the Confluence connector, and it refused artifacts that had already auto-published as internal, so a later 'connect Confluence then push' was impossible.</t>
+  </si>
+  <si>
+    <t>(1) Preview now always works: the report step always stages the phase body to S3 and backfills the agent-registered artifact's S3 pointer instead of skipping (orchestration/activities.py); preview falls back through own draft -&gt; inline draft -&gt; the run's staged/reported body, and the S3 read is guarded (integrations/preview.py). The team's existing 7 body-less artifacts preview correctly with no data migration - verified in the browser. (2) Export answers: YES - after gate approval, docstore-mapped artifact types auto-export to the connected Confluence; and YES - manual push now exists for real: the Publish screen calls the Confluence connector, honours the space key, records true provenance (page id + URL), and allows re-export of artifacts that published as internal before a connector existed. Verified live end-to-end with the team's creds: page 'Greenfield MVP - Ideation' created in the SDLC space (page id 11927553) and the returned link opens it. Files: backend/orchestration/activities.py, backend/integrations/preview.py, backend/integrations/publish.py, backend/api/views.py; tests in test_phase_dispatch.py, test_artifact_preview_rest.py, test_frontend_integration.py, journey tests.</t>
+  </si>
+  <si>
+    <t>In the clarifications page: 
+Once a phase is run and the system asks for clarifications (questions) to be answered by the user, here the team wants to know the following to do brain storming with claude code and then proceed with a definetive approave on how to present the clarifications to the user to be answered: 
+1. How the clarifications are displayed to the user(flow), meaning are we directly rendering the message from the claude code output? if that is the case, some times there are options to choose from and while choosing the options - There is also an option called "Others" for some questions but when selected a text box is not presented to the user for entering his option text manually to submit!
+2. The clarifications (questions) format is not humanised meaning - the questions are written with options in them and again those options are available to pick - options present in the questions is confusing and not readable for the user.
+3. The presentation format is also not good and confusing to the team whether they are directly rendered as output or any manipulations being done while presenting the clarifications by our engine?</t>
+  </si>
+  <si>
+    <t>In the Connect Machine page: 
+When the user has connected his local companion and created a work item and executed/run a phase for example: Ideation, after sometime the engine is showing companion disconnect and saying to connect again wih error message. Sharing you the reference images, clearly go through and findout the root cause first and report it to the team working on this issue and take their approval before fixing.
+Due to this issue, even when the team is running the next phase i.e requirements, the UI showing that phase is running but never got any artifacts as ouptut or any gate for that run. This is very serious issue and need to be analysed accurately.
+In phases and runs page: The same companion machine is offline message (also confirm this and anywhere else the issue displays)</t>
+  </si>
+  <si>
+    <t>Connet Machine</t>
   </si>
 </sst>
 </file>
@@ -1684,7 +1765,7 @@
 </file>
 
 <file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
-<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="7">
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="9">
   <rv s="0">
     <v>0</v>
     <v>5</v>
@@ -1713,6 +1794,14 @@
     <v>6</v>
     <v>5</v>
   </rv>
+  <rv s="0">
+    <v>7</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>8</v>
+    <v>5</v>
+  </rv>
 </rvData>
 </file>
 
@@ -1734,6 +1823,8 @@
   <rel r:id="rId5"/>
   <rel r:id="rId6"/>
   <rel r:id="rId7"/>
+  <rel r:id="rId8"/>
+  <rel r:id="rId9"/>
 </richValueRels>
 </file>
 
@@ -2149,15 +2240,11 @@
       <c r="G4" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Most forms already had placeholders, but several fields were left blank: all Project Profile fields except tech stack, the free-text clarification answer box, and the repository base-branch input. Nothing guided the user on what to type.</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Added helpful example placeholders to every remaining form field: all seven Project Profile fields, the clarification answer box ('Type your answer...'), and the repository base branch ('main'). Together with row 33 this closes the app-wide placeholder sweep. Files: frontend ProjectProfileEditor.tsx, Clarifications.tsx, Repositories.tsx.</t>
-        </is>
+      <c r="H4" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>16</v>
@@ -2168,13 +2255,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>12</v>
@@ -2183,10 +2270,10 @@
         <v>13</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>16</v>
@@ -2197,10 +2284,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>12</v>
@@ -2209,10 +2296,10 @@
         <v>13</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>16</v>
@@ -2223,22 +2310,22 @@
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>12</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>16</v>
@@ -2249,10 +2336,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>12</v>
@@ -2261,10 +2348,10 @@
         <v>13</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>16</v>
@@ -2275,22 +2362,22 @@
         <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>22</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>16</v>
@@ -2301,10 +2388,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>12</v>
@@ -2313,10 +2400,10 @@
         <v>23</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>16</v>
@@ -2327,25 +2414,25 @@
         <v>10</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>13</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>16</v>
@@ -2356,22 +2443,22 @@
         <v>11</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>13</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>16</v>
@@ -2382,19 +2469,19 @@
         <v>12</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>23</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>16</v>
@@ -2405,10 +2492,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>12</v>
@@ -2417,10 +2504,10 @@
         <v>23</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>16</v>
@@ -2431,10 +2518,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>12</v>
@@ -2443,10 +2530,10 @@
         <v>13</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>16</v>
@@ -2457,22 +2544,22 @@
         <v>15</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>12</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>16</v>
@@ -2483,10 +2570,10 @@
         <v>16</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>12</v>
@@ -2495,10 +2582,10 @@
         <v>13</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>16</v>
@@ -2509,10 +2596,10 @@
         <v>17</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>22</v>
@@ -2521,10 +2608,10 @@
         <v>13</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>16</v>
@@ -2535,10 +2622,10 @@
         <v>18</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>12</v>
@@ -2548,10 +2635,10 @@
         <v>23</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>16</v>
@@ -2562,22 +2649,22 @@
         <v>19</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>12</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>16</v>
@@ -2588,10 +2675,10 @@
         <v>20</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>12</v>
@@ -2600,10 +2687,10 @@
         <v>13</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>16</v>
@@ -2614,10 +2701,10 @@
         <v>21</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>12</v>
@@ -2626,10 +2713,10 @@
         <v>13</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>16</v>
@@ -2640,10 +2727,10 @@
         <v>22</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>12</v>
@@ -2652,10 +2739,10 @@
         <v>13</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>16</v>
@@ -2666,22 +2753,22 @@
         <v>23</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>12</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>16</v>
@@ -2692,10 +2779,10 @@
         <v>24</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>12</v>
@@ -2704,10 +2791,10 @@
         <v>13</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>16</v>
@@ -2718,10 +2805,10 @@
         <v>25</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>12</v>
@@ -2730,10 +2817,10 @@
         <v>13</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>16</v>
@@ -2744,10 +2831,10 @@
         <v>26</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>12</v>
@@ -2756,10 +2843,10 @@
         <v>13</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>16</v>
@@ -2770,10 +2857,10 @@
         <v>27</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>12</v>
@@ -2782,10 +2869,10 @@
         <v>13</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>16</v>
@@ -2796,10 +2883,10 @@
         <v>28</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>12</v>
@@ -2808,10 +2895,10 @@
         <v>13</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>16</v>
@@ -2822,22 +2909,22 @@
         <v>29</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>12</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>16</v>
@@ -2848,22 +2935,22 @@
         <v>30</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>12</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>16</v>
@@ -2874,10 +2961,10 @@
         <v>31</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>12</v>
@@ -2886,10 +2973,10 @@
         <v>23</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="I32" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="J32" s="2" t="s">
         <v>16</v>
@@ -2900,22 +2987,22 @@
         <v>32</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>12</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="I33" s="2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="J33" s="2" t="s">
         <v>16</v>
@@ -2926,10 +3013,10 @@
         <v>33</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>22</v>
@@ -2937,15 +3024,11 @@
       <c r="G34" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Only the tech-stack field of the Project Profile carried a placeholder; description, domain, coding standards, NFRs, constraints, glossary and important context gave the user no example of what good input looks like.</t>
-        </is>
-      </c>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Every Project Profile field now shows a realistic example placeholder (e.g. domain: 'Personal finance, Healthcare, E-commerce'; NFRs: response-time / uptime / accessibility examples). Verified in the browser - all 8 fields show guidance when empty. File: frontend/src/features/setup/ProjectProfileEditor.tsx.</t>
-        </is>
+      <c r="H34" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="I34" s="2" t="s">
+        <v>135</v>
       </c>
       <c r="J34" s="2" t="s">
         <v>16</v>
@@ -2956,10 +3039,10 @@
         <v>34</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>22</v>
@@ -2967,15 +3050,11 @@
       <c r="G35" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="H35" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The companion status pill used near-white text on the white top bar (it was styled once for the dark sidebar and reused on the light header), so 'Companion: Offline' and 'Companion: Ready' were barely readable in the header.</t>
-        </is>
-      </c>
-      <c r="I35" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The pill now has high-contrast styling in both places: solid white bold text in the dark sidebar, and state-coloured text (red offline, green ready, amber connecting) on a bordered tint in the white top bar. Verified in the browser - the header pill reads clearly in both states. File: frontend/src/styles/components.css.</t>
-        </is>
+      <c r="H35" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="I35" s="2" t="s">
+        <v>139</v>
       </c>
       <c r="J35" s="2" t="s">
         <v>16</v>
@@ -2986,19 +3065,19 @@
         <v>35</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>22</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J36" s="2" t="s">
-        <v>24</v>
+        <v>141</v>
       </c>
     </row>
     <row r="37" spans="1:10" ht="231.95" customHeight="1">
@@ -3006,26 +3085,22 @@
         <v>36</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="G37" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="H37" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The Type dropdown's helper text described work-item types with internal jargon ('plan tier', 'build tier', 'remediation tier') that means nothing to a user.</t>
-        </is>
-      </c>
-      <c r="I37" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Rewrote the helper in plain language: Epic - a large feature that goes through all the planning phases from Ideation to Task Breakdown; Story - a smaller user-facing piece of an epic; Task - a concrete development job that gets implemented, code-reviewed and tested; Defect - a bug fix on the shorter fix-and-verify flow. Verified in the browser. File: frontend/src/features/lifecycle/WorkItemsBoard.tsx.</t>
-        </is>
+      <c r="H37" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="I37" s="2" t="s">
+        <v>145</v>
       </c>
       <c r="J37" s="2" t="s">
         <v>16</v>
@@ -3036,22 +3111,22 @@
         <v>37</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>12</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>140</v>
+        <v>148</v>
       </c>
       <c r="I38" s="2" t="s">
-        <v>141</v>
+        <v>149</v>
       </c>
       <c r="J38" s="2" t="s">
         <v>16</v>
@@ -3062,10 +3137,10 @@
         <v>38</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>12</v>
@@ -3074,10 +3149,10 @@
         <v>13</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="I39" s="2" t="s">
-        <v>144</v>
+        <v>152</v>
       </c>
       <c r="J39" s="2" t="s">
         <v>16</v>
@@ -3088,10 +3163,10 @@
         <v>39</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>145</v>
+        <v>153</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>12</v>
@@ -3100,10 +3175,10 @@
         <v>13</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="I40" s="2" t="s">
-        <v>147</v>
+        <v>155</v>
       </c>
       <c r="J40" s="2" t="s">
         <v>16</v>
@@ -3114,25 +3189,25 @@
         <v>40</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>148</v>
+        <v>156</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="I41" s="2" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="J41" s="2" t="s">
         <v>16</v>
@@ -3143,28 +3218,28 @@
         <v>41</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>153</v>
+        <v>161</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>154</v>
+        <v>162</v>
       </c>
       <c r="I42" s="2" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="J42" s="2" t="s">
         <v>16</v>
@@ -3175,25 +3250,25 @@
         <v>42</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>156</v>
+        <v>164</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E43" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="I43" s="2" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="J43" s="2" t="s">
         <v>16</v>
@@ -3204,25 +3279,25 @@
         <v>43</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>159</v>
+        <v>167</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E44" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>160</v>
+        <v>168</v>
       </c>
       <c r="I44" s="2" t="s">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="J44" s="2" t="s">
         <v>16</v>
@@ -3233,25 +3308,25 @@
         <v>44</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>162</v>
+        <v>170</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E45" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>163</v>
+        <v>171</v>
       </c>
       <c r="I45" s="2" t="s">
-        <v>164</v>
+        <v>172</v>
       </c>
       <c r="J45" s="2" t="s">
         <v>16</v>
@@ -3262,25 +3337,25 @@
         <v>45</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>165</v>
+        <v>173</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>166</v>
+        <v>174</v>
       </c>
       <c r="E46" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="I46" s="2" t="s">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="J46" s="2" t="s">
         <v>16</v>
@@ -3291,25 +3366,25 @@
         <v>46</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>169</v>
+        <v>177</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="E47" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>171</v>
+        <v>179</v>
       </c>
       <c r="I47" s="2" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="J47" s="2" t="s">
         <v>16</v>
@@ -3320,25 +3395,25 @@
         <v>47</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>166</v>
+        <v>174</v>
       </c>
       <c r="E48" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
       <c r="G48" s="2" t="s">
         <v>23</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>174</v>
+        <v>182</v>
       </c>
       <c r="I48" s="2" t="s">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="J48" s="2" t="s">
         <v>16</v>
@@ -3349,25 +3424,25 @@
         <v>48</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
       <c r="G49" s="2" t="s">
         <v>23</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="I49" s="2" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="J49" s="2" t="s">
         <v>16</v>
@@ -3378,32 +3453,28 @@
         <v>49</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>179</v>
+        <v>187</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E50" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
       <c r="G50" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="H50" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The search box and the Phase/Role/Status dropdowns were static markup with no state or wiring - only the level chips filtered. The dropdowns also had no options to offer because the board had no notion of an item's current phase.</t>
-        </is>
-      </c>
-      <c r="I50" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">All four controls now work, client-side over the loaded board (same approach as the Artifacts fix, row 24): search matches key/title/type/stream; Phase and Status options are the distinct values actually present; Role filters by the gate role responsible for the item's current phase (from the live phase catalog). Verified in the browser: phase filter narrows to matching cards, a non-matching search empties the board. File: frontend/src/features/lifecycle/WorkItemsBoard.tsx (+ backend current_phase, see row 50).</t>
-        </is>
+      <c r="H50" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="I50" s="2" t="s">
+        <v>190</v>
       </c>
       <c r="J50" s="2" t="s">
         <v>16</v>
@@ -3414,29 +3485,25 @@
         <v>50</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>182</v>
+        <v>191</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E51" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
       <c r="G51" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="H51" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The 'Phase' column (and the board's column placement) used the work item's feature-stream text as if it were a phase - the platform never told the frontend what phase an item was actually in.</t>
-        </is>
-      </c>
-      <c r="I51" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The backend now computes each item's current phase (its latest run's agent phase, one query for the whole board) and serves it on the card payload; the list's Phase column shows that real phase ('PRD', or 'Not started'), and board cards land in their actual phase column. Feature stream is no longer misused as a phase anywhere on the board. Verified live: the story with a PRD run shows Phase 'PRD' and sits in the '3. PRD' column. Files: backend/api/views.py (_card_fields), frontend WorkItemsBoard.tsx, regression test in test_work_items_card_fields.py.</t>
-        </is>
+      <c r="H51" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="I51" s="2" t="s">
+        <v>193</v>
       </c>
       <c r="J51" s="2" t="s">
         <v>16</v>
@@ -3447,32 +3514,28 @@
         <v>51</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>184</v>
+        <v>194</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>185</v>
+        <v>195</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="E52" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
       <c r="G52" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="H52" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The admin screens fetch the users list, which returns 403 for a non-admin; the screens rendered nothing with the error unhandled - a blank, broken page for anyone who deep-linked to /admin/roles or /admin/users.</t>
-        </is>
-      </c>
-      <c r="I52" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Added a route-level admin guard: all /admin/* routes now render a clear 'Admin access needed' panel (what the page is, who can use it, a back-to-dashboard button) for non-admins instead of mounting the broken screens. Verified live as a non-admin user. File: frontend/src/routes.tsx (RequireAdmin).</t>
-        </is>
+      <c r="H52" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="I52" s="2" t="s">
+        <v>197</v>
       </c>
       <c r="J52" s="2" t="s">
         <v>16</v>
@@ -3483,28 +3546,28 @@
         <v>52</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>187</v>
+        <v>198</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>188</v>
+        <v>199</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="E53" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H53" s="2" t="s">
-        <v>189</v>
+        <v>200</v>
       </c>
       <c r="I53" s="2" t="s">
-        <v>190</v>
+        <v>201</v>
       </c>
       <c r="J53" s="2" t="s">
         <v>16</v>
@@ -3515,10 +3578,10 @@
         <v>53</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>191</v>
+        <v>202</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E54" s="2" t="s">
         <v>12</v>
@@ -3530,10 +3593,10 @@
         <v>13</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>192</v>
+        <v>203</v>
       </c>
       <c r="I54" s="2" t="s">
-        <v>193</v>
+        <v>204</v>
       </c>
       <c r="J54" s="2" t="s">
         <v>16</v>
@@ -3544,10 +3607,10 @@
         <v>54</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>194</v>
+        <v>205</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E55" s="2" t="s">
         <v>12</v>
@@ -3556,13 +3619,13 @@
         <v>#VALUE!</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H55" s="2" t="s">
-        <v>195</v>
+        <v>206</v>
       </c>
       <c r="I55" s="2" t="s">
-        <v>196</v>
+        <v>207</v>
       </c>
       <c r="J55" s="2" t="s">
         <v>16</v>
@@ -3573,10 +3636,10 @@
         <v>55</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>197</v>
+        <v>208</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E56" s="2" t="s">
         <v>12</v>
@@ -3587,15 +3650,11 @@
       <c r="G56" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="H56" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The Runs table rendered raw values straight from the API: the status token ('awaiting_gate'), the full run UUID and Temporal workflow id, and the unformatted ISO timestamp.</t>
-        </is>
-      </c>
-      <c r="I56" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The table is now fully humanised and dynamic for every run: status via the shared statusLabel helper ('Awaiting gate'); the run shows a short reference ('Run 6b6443fa') that links to the run console with the full id on hover; the workflow id is shortened the same way (full value on hover); Created renders as a locale-formatted date ('Jul 7, 2026, 9:38 PM'). Status colours also understand awaiting_gate/approved/rejected now. Verified live. File: frontend/src/features/lifecycle/PhasesAndRuns.tsx.</t>
-        </is>
+      <c r="H56" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="I56" s="2" t="s">
+        <v>210</v>
       </c>
       <c r="J56" s="2" t="s">
         <v>16</v>
@@ -3606,10 +3665,10 @@
         <v>56</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>198</v>
+        <v>211</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>166</v>
+        <v>174</v>
       </c>
       <c r="E57" s="2" t="s">
         <v>12</v>
@@ -3618,13 +3677,13 @@
         <v>#VALUE!</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H57" s="2" t="s">
-        <v>199</v>
+        <v>212</v>
       </c>
       <c r="I57" s="2" t="s">
-        <v>200</v>
+        <v>213</v>
       </c>
       <c r="J57" s="2" t="s">
         <v>16</v>
@@ -3635,10 +3694,10 @@
         <v>57</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>201</v>
+        <v>214</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E58" s="2" t="s">
         <v>12</v>
@@ -3647,13 +3706,13 @@
         <v>#VALUE!</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H58" s="2" t="s">
-        <v>202</v>
+        <v>215</v>
       </c>
       <c r="I58" s="2" t="s">
-        <v>203</v>
+        <v>216</v>
       </c>
       <c r="J58" s="2" t="s">
         <v>16</v>
@@ -3664,10 +3723,10 @@
         <v>58</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>205</v>
+        <v>218</v>
       </c>
       <c r="E59" s="2" t="s">
         <v>12</v>
@@ -3676,13 +3735,13 @@
         <v>#VALUE!</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H59" s="2" t="s">
-        <v>206</v>
+        <v>219</v>
       </c>
       <c r="I59" s="2" t="s">
-        <v>207</v>
+        <v>220</v>
       </c>
       <c r="J59" s="2" t="s">
         <v>16</v>
@@ -3693,10 +3752,10 @@
         <v>59</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>208</v>
+        <v>221</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>209</v>
+        <v>222</v>
       </c>
       <c r="E60" s="2" t="s">
         <v>12</v>
@@ -3707,28 +3766,80 @@
       <c r="G60" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="H60" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Two compounding defects. (1) Preview: agents register artifacts during a run as pointers only (content hash, no body, no S3 key - correct per the architecture), and the platform step that stages the phase body to S3 (register_phase_result_core) skipped itself whenever the agent had already registered an artifact of the phase's type for that run - its idempotency check treated the agent's pointer row as 'already done'. So the body was never written to S3 and NO artifact of the run had a body anywhere; preview found nothing and returned 404 ('Artifact not found'). The long loading is the frontend retrying before giving up. The full phase output was sitting unused on the run's report. Also, the internal S3 read was unguarded, so a missing object crashed the endpoint with a 500 instead of degrading. (2) Export: auto-export to Confluence on gate approval existed only for docstore-mapped types (requirements/prd/architecture/adr), and the manual Publish endpoint was a stub - it flipped the status and fabricated a link without ever calling the Confluence connector, and it refused artifacts that had already auto-published as internal, so a later 'connect Confluence then push' was impossible.</t>
-        </is>
-      </c>
-      <c r="I60" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(1) Preview now always works: the report step always stages the phase body to S3 and backfills the agent-registered artifact's S3 pointer instead of skipping (orchestration/activities.py); preview falls back through own draft -&gt; inline draft -&gt; the run's staged/reported body, and the S3 read is guarded (integrations/preview.py). The team's existing 7 body-less artifacts preview correctly with no data migration - verified in the browser. (2) Export answers: YES - after gate approval, docstore-mapped artifact types auto-export to the connected Confluence; and YES - manual push now exists for real: the Publish screen calls the Confluence connector, honours the space key, records true provenance (page id + URL), and allows re-export of artifacts that published as internal before a connector existed. Verified live end-to-end with the team's creds: page 'Greenfield MVP - Ideation' created in the SDLC space (page id 11927553) and the returned link opens it. Files: backend/orchestration/activities.py, backend/integrations/preview.py, backend/integrations/publish.py, backend/api/views.py; tests in test_phase_dispatch.py, test_artifact_preview_rest.py, test_frontend_integration.py, journey tests.</t>
-        </is>
+      <c r="H60" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="I60" s="2" t="s">
+        <v>224</v>
       </c>
       <c r="J60" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="61" spans="1:10">
+    <row r="61" spans="1:10" ht="409.6">
       <c r="A61" s="2">
         <v>60</v>
       </c>
-    </row>
-    <row r="62" spans="1:10">
+      <c r="B61" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="D61" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="E61" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F61" s="2" t="e" vm="8">
+        <v>#VALUE!</v>
+      </c>
+      <c r="G61" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="J61" s="2" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10" ht="409.6">
       <c r="A62" s="2">
         <v>61</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="D62" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="E62" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F62" s="2" t="e" vm="9">
+        <v>#VALUE!</v>
+      </c>
+      <c r="G62" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Every 'Companion Offline' indicator (global pill, Connect Machine page, Phases &amp; Runs) is driven by ONE derived flag: enrollment.online = (now - last_seen) &lt;= 2 min (apps/runs/enrollment.py). last_seen is refreshed only when the companion calls an authenticated endpoint. Four defects made it go stale / stuck:
+RC-1 (PRIMARY): The companion daemon CRASHED after the first phase. The old assert_subscription_billing() halted the daemon whenever a phase reported a non-zero cost. Current Claude Code reports a computed subscription-equivalent cost (~$1) even on a Max subscription (which is NOT billed per token), so the guard false-positived and killed the daemon right after Ideation reported. A dead daemon stops refreshing last_seen -&gt; UI shows 'Offline / daemon stopped' within 2 min. It ALSO explains 'Requirements runs but never produces artifacts/gate': after the crash no daemon was alive to run the next phase (or it claimed then died), leaving the run stuck 'running'/'claimed' with no report.
+RC-2: Heartbeat starvation. The serve loop is single-threaded (claim -&gt; run_task blocks for the WHOLE phase -&gt; report). While a phase runs the loop never re-polls, so last_seen only refreshes if the agent happens to call a platform-state tool. Any phase quiet for &gt;2 min flips the companion to a FALSE 'Offline' mid-run and disables triggers, though it is healthy and busy.
+RC-3: No re-queue on daemon death. Claiming atomically flips dispatch pending-&gt;claimed with no lease. If the daemon dies before reporting, the run is stranded 'claimed'/'running' forever - no other daemon re-claims it (poll filters status=pending) - no artifacts, no gate, no recovery.
+RC-4: Misleading UI. Offline copy always said 'daemon stopped' with a HARDCODED 'last seen 5m ago' (ConnectMachine.tsx), and label-less re-enrollments each showed as a separate phantom machine card.</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RC-1 (shipped): removed the assert_subscription_billing halt in runner/companion/daemon.py; ensure_local_engine_auth (env + ~/.claude.json + OAuth checks) is now the SOLE subscription-only guard. Engine cost is reported for reference only, never used as an API-key signal.
+RC-2: added POST /api/runner/heartbeat/ (RunnerHeartbeatView) + a background heartbeat thread in the daemon (CompanionDaemon._run_heartbeat_loop; --heartbeat-interval, default 30s) that refreshes last_seen every 30s independent of run_task, so the companion stays 'online' throughout long phases.
+RC-3: work claims are now a LEASE. RunnerWorkClaimView stamps claimed_at + claim_count on claim; a poll re-claims any run left 'claimed' past CLAIM_LEASE (15 min, &gt; longest phase) with no report, logging phase.reclaimed - so a dead companion's run recovers instead of stranding.
+RC-4: ConnectMachine.tsx now shows the REAL relative last_seen (sinceLabel) and reworded copy ('not reachable - reconnects if mid-phase; else restart'); list_developer_enrollments collapses label-less re-enrollments for the same project into ONE card (represented by the most-recently-seen enrollment) instead of N phantoms.
+TESTS: backend 101 passed / 3 skipped (new: heartbeat endpoint, stale-claim reclaim, enrollment dedup); daemon unit 16 passed (heartbeat posts + failure-safe); frontend 209 passed; tsc clean. Verified in the backend container against Postgres.</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fixed</t>
+        </is>
       </c>
     </row>
     <row r="63" spans="1:10">

--- a/docs/Bugs.xlsx
+++ b/docs/Bugs.xlsx
@@ -3842,9 +3842,61 @@
         </is>
       </c>
     </row>
-    <row r="63" spans="1:10">
+    <row r="63" spans="1:10" ht="409.6">
       <c r="A63" s="2">
         <v>62</v>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Requirements phase ran a second time by itself — a duplicate 'v2' draft of the same artifact appeared and the companion went offline.</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Found during live testing of the Bug #61 (S.No 61) fix. The Requirements phase completed normally: its artifact (version 1) was previewed, approved at the gate, and the phase showed as done. A few minutes later, without anyone triggering it, the SAME Requirements artifact was generated again as a 'version 2' draft on the Artifacts &amp; Traceability page, and the companion daemon then crashed and showed offline. The approved version 1 was never affected — the only impact was one spurious duplicate draft and the daemon stopping.</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Companion Runner (Phases &amp; Runs)</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bug — regression from the Bug #61 fix</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Regression introduced by the Bug #61 (S.No 61) fix, specifically its RC-3 'claim-lease' auto-recovery. Same run: Requirements run 607d0245; the duplicate was the requirements version-2 draft.</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P1</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The Bug #61 fix added a 'claim lease' safety net: if a companion dies in the middle of a phase without reporting, another poll re-claims the run after 15 minutes so it is not stuck forever. This had a timing race.
+The Requirements phase ran about 17 minutes — longer than the 15-minute lease. When the companion finished and sent its report, the separate step that marks the run as 'reported' happened a moment later (asynchronously, inside the workflow). In that brief gap the run still looked 'claimed', and because the claim was now older than 15 minutes, the companion's very next poll judged it 'stale' and re-claimed its OWN just-finished run — running Requirements a second time and creating the version-2 draft.
+That second run then reported to a workflow that had already completed, which returned a server error the daemon treated as fatal — so the daemon crashed and went offline.</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Three-part hardening (all shipped, tested, and deployed):
+1) The report step now marks the run 'reported' immediately (synchronously) the moment the companion reports, so the very next poll can never still see it as 'claimed'. This closes the re-run race no matter how long the phase ran.
+2) The auto-recovery re-claim now only applies to runs that are still genuinely running — never one that already reached a gate or completed.
+3) The daemon no longer crashes on a late or duplicate report: the backend responds gracefully (not a server error) when a report arrives after its workflow has already finished, and the daemon logs the failed report and keeps running instead of stopping.
+Added automated regression tests for all three. Confirmed behavior for the team: for a normal long phase (e.g. a 30-minute UX Design or Implementation run) on a single companion, no re-claim ever happens — a busy companion is not polling for work, and on finishing it marks the run 'reported' before its next poll. A re-claim triggers ONLY when a companion genuinely dies before reporting. The spurious version-2 draft was removed; only the approved version 1 remains.
+Files: orchestration/phase_report.py, api/runner_views.py, runner/companion/daemon.py. Tests: daemon unit 18 passed; backend suite 134 passed / 2 skipped.</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fixed</t>
+        </is>
       </c>
     </row>
     <row r="64" spans="1:10">

--- a/docs/Bugs.xlsx
+++ b/docs/Bugs.xlsx
@@ -3899,14 +3899,108 @@
         </is>
       </c>
     </row>
-    <row r="64" spans="1:10">
+    <row r="64" spans="1:10" ht="409.6">
       <c r="A64" s="2">
         <v>63</v>
       </c>
-    </row>
-    <row r="65" spans="1:1">
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Planning-phase agent runs with more tools than it should — it can spawn subagents and use Read/Bash/Glob, which leads to slow, non-deterministic runs that register no artifacts (and gives the agent unintended access to the local machine).</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Seen while re-running the Requirements phase on a work item during testing. Unlike the first run — which registered each artifact incrementally, so they appeared in the UI within minutes — this run spent 20+ minutes drafting everything internally by spawning 8 subagents and registered NOTHING to the platform, so the Artifacts page stayed empty and it looked stalled. Reading the engine transcript showed the planning agent using Read, Glob, Bash, ToolSearch and Agent (subagents) — none of which it is supposed to have. A planning phase is meant to run with ONLY the platform-state tools (read the registered context, register its artifacts); it must not spawn subagents or touch the local filesystem/shell.</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Companion Runner / Planning Agent (ClaudeDriver)</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bug</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Observed on Requirements re-run 2cf17e68 (work item 8d6f3b7d) during live testing. Engine transcript showed 8 Agent(subagent) calls and 0 register_artifact calls. Relevant code: backend/drivers/claude_driver.py (allowed_tools / permission_mode) and runner/companion/daemon.py (PLAN_ALLOWED_TOOLS).</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P2</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The planning/review agent is launched with its tool allowlist restricted to the platform-state MCP tools (PLAN_ALLOWED_TOOLS in runner/companion/daemon.py) and permission_mode='default' (backend/drivers/claude_driver.py). In practice that allowlist is NOT actually restricting the engine: the Claude Code engine still lets the agent use its built-in tools (Read, Glob, Bash) and, crucially, spawn subagents (the Agent/Task tool). So the planning agent is not sandboxed to 'reason over registered context and register artifacts' as intended.
+Consequences: (1) when the model happens to pick a subagent-heavy strategy (non-deterministic), it drafts all artifacts in memory via subagents and registers them late — or not at all — producing empty/slow runs and no incremental progress in the UI; (2) the planning agent has unintended filesystem and shell access on the user's machine, which is a sandboxing/security concern.</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OPEN — not yet fixed. Proposed direction: enforce the tool allowlist for planning and review phases so ONLY the platform-state MCP tools are available. For example, pass an explicit blocked/disallowed-tools list (Agent/Task, Bash, Read, Write, Edit, Glob, Grep, WebFetch, ToolSearch, ...) and/or set the permission mode so any non-allowed tool is denied rather than silently permitted, in backend/drivers/claude_driver.py. Then verify with a test that a planning run cannot spawn a subagent or run Bash, and that it registers artifacts incrementally via register_artifact. Needs a short investigation into how the installed Claude Agent SDK version enforces allowed_tools versus the engine's built-in tools and subagents.</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" spans="1:10" ht="409.6">
       <c r="A65" s="2">
         <v>64</v>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UX Design phase failed right after starting with 'Claude Code not found' — even though the engine was installed and working (earlier phases ran fine).</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Seen while re-running the UX Design phase during testing. The phase started, then immediately failed with 'Claude Code not found at: …\claude.exe'. Two earlier attempts did NOT help because they targeted the wrong cause: (1) switching from the engine's bundled copy to the user's own copy on PATH, and (2) adding an automatic launch retry. The error came back identically both times. Adding a diagnostic that revealed the real operating-system error finally exposed the true cause (see Root Cause).</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Companion Runner / Engine launch (ClaudeDriver)</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bug</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UX Design runs during live testing (work item 8d6f3b7d). The failure was specific to the UX Design agent; Requirements/other phases were unaffected. Confirmed by a launch diagnostic reporting Windows error 206 ('The filename or extension is too long').</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P1</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">To start a phase, the platform launches the engine and passes the agent its full set of instructions (the 'system prompt') as a COMMAND-LINE argument. Windows limits how long a command line can be — about 32,000 characters total. The UX Design agent's instructions are unusually large (~36,000 characters), so they didn't fit. Windows refused to start the process with a generic 'arguments too long' error (Windows error 206), and the engine library reported that up as the misleading 'Claude Code not found' — even though the engine was right there.
+This is why ONLY the UX Design phase failed: other phases (Requirements, etc.) have smaller instruction sets that fit within the limit. It had nothing to do with a missing engine, the wrong copy of the engine, or antivirus — those earlier theories were wrong.
+Important: this is NOT a 'context too large' problem. The heavy run context (the PRD, past artifacts, code) is already delivered the correct way — as files the agent reads and via on-demand retrieval tools — never on the command line. Only the agent's own static instruction body was being put on the command line, and only the UX one was big enough to overflow it.</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Team-approved fix (Option A): the platform now delivers a large agent's instruction body as a FILE that the engine reads from its working folder (AGENTS.md, which Claude Code loads automatically), instead of squeezing it onto the command line. Small instruction sets are unchanged (still passed as the system prompt). This removes the length limit entirely, so any agent — however large its instructions — starts reliably. Because the big run context already flows through files and retrieval tools, even very large (100K-token) phases are unaffected; the real ceiling there is the model's context window, not the command line.
+Also: kept a launch diagnostic that logs the real operating-system error, so any future launch problem is immediately visible instead of hidden behind 'Claude Code not found'. The earlier launch-retry remains only as a harmless generic safety net — it was not the fix. Added an automated test that a large body is delivered via the file, not the command line. No user setup needed; a freshly started companion gets this automatically. File changed: backend/drivers/claude_driver.py.</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fixed</t>
+        </is>
       </c>
     </row>
     <row r="66" spans="1:1">

--- a/docs/Bugs.xlsx
+++ b/docs/Bugs.xlsx
@@ -3935,18 +3935,17 @@
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">The planning/review agent is launched with its tool allowlist restricted to the platform-state MCP tools (PLAN_ALLOWED_TOOLS in runner/companion/daemon.py) and permission_mode='default' (backend/drivers/claude_driver.py). In practice that allowlist is NOT actually restricting the engine: the Claude Code engine still lets the agent use its built-in tools (Read, Glob, Bash) and, crucially, spawn subagents (the Agent/Task tool). So the planning agent is not sandboxed to 'reason over registered context and register artifacts' as intended.
-Consequences: (1) when the model happens to pick a subagent-heavy strategy (non-deterministic), it drafts all artifacts in memory via subagents and registers them late — or not at all — producing empty/slow runs and no incremental progress in the UI; (2) the planning agent has unintended filesystem and shell access on the user's machine, which is a sandboxing/security concern.</t>
+          <t xml:space="preserve">The planning/review agent was launched with its tool allowlist set to only the platform-state tools, but that allowlist does NOT actually restrict the engine: with the default permission mode, Claude Code still exposes ALL its built-in tools (Read, Write, Edit, Bash, Grep, Glob), the subagent tool (Agent/Task), web search, and — because the companion loaded the user's global Claude Code config — the user's personal skills and extra tools. Planning and review phases run in a fresh EMPTY temporary folder with no repository checked out, so those filesystem/shell/subagent tools can reach nothing useful; they only let the agent wander. In live testing a UX Design run spent its first minutes spawning a subagent to grep an empty folder for artifact IDs instead of using the platform tools, and a Requirements re-run spent 20+ minutes drafting via 8 subagents and registered nothing. It is also a sandboxing/security concern: a planning agent should never have shell/file access to the user's machine.</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">OPEN — not yet fixed. Proposed direction: enforce the tool allowlist for planning and review phases so ONLY the platform-state MCP tools are available. For example, pass an explicit blocked/disallowed-tools list (Agent/Task, Bash, Read, Write, Edit, Glob, Grep, WebFetch, ToolSearch, ...) and/or set the permission mode so any non-allowed tool is denied rather than silently permitted, in backend/drivers/claude_driver.py. Then verify with a test that a planning run cannot spawn a subagent or run Bash, and that it registers artifacts incrementally via register_artifact. Needs a short investigation into how the installed Claude Agent SDK version enforces allowed_tools versus the engine's built-in tools and subagents.</t>
+          <t xml:space="preserve">Phase-scoped sandbox in backend/drivers/claude_driver.py. Planning and review phases now pass an explicit disallowed-tools list (Agent/Task, Bash, Read, Write, Edit, Glob, Grep, WebFetch, WebSearch, ToolSearch, Skill, TodoWrite, ...) AND setting_sources=['project'] so the engine loads settings only from the empty run folder — never the user's global skills/subagents/MCP. Result: a planning/review agent can use ONLY the platform-state tools it was granted, so it reads context and registers artifacts directly instead of wandering. Implementation/build is deliberately NOT sandboxed — it runs in the real git worktree and must keep Read/Write/Edit/Bash/Grep/Glob to develop code (different code path, BUILD_ALLOWED_TOOLS). Verified live: a full-denylist engine probe returned SANDBOX_LOCKED (subagent + file read + bash all blocked), and a clean UX Design re-run used only platform-state tools (get_context/get_artifact/register_artifact), no subagents, artifacts registering promptly. Tests assert planning/review are sandboxed and build is not.</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Open</t>
+          <t xml:space="preserve">Fixed</t>
         </is>
       </c>
     </row>
@@ -3993,8 +3992,7 @@
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Team-approved fix (Option A): the platform now delivers a large agent's instruction body as a FILE that the engine reads from its working folder (AGENTS.md, which Claude Code loads automatically), instead of squeezing it onto the command line. Small instruction sets are unchanged (still passed as the system prompt). This removes the length limit entirely, so any agent — however large its instructions — starts reliably. Because the big run context already flows through files and retrieval tools, even very large (100K-token) phases are unaffected; the real ceiling there is the model's context window, not the command line.
-Also: kept a launch diagnostic that logs the real operating-system error, so any future launch problem is immediately visible instead of hidden behind 'Claude Code not found'. The earlier launch-retry remains only as a harmless generic safety net — it was not the fix. Added an automated test that a large body is delivered via the file, not the command line. No user setup needed; a freshly started companion gets this automatically. File changed: backend/drivers/claude_driver.py.</t>
+          <t xml:space="preserve">Root cause was correct (Windows command-line length limit, error 206). The first fix delivered the large body as an AGENTS.md file — this stopped the crash, but was later found INSUFFICIENT: Claude Code does not auto-load AGENTS.md (only CLAUDE.md, and only with project setting-sources), and a planning agent has no file-reading tool, so the body still did not reach the model. Superseded by the correct, permanent fix: deliver the agent body + run manifest as a true FILE-BASED SYSTEM PROMPT via the CLI's --system-prompt-file flag (see S.No 65). That removes the command-line limit for any body size AND guarantees the instructions actually reach the model. The 'Claude Code not found' crash is fully resolved.</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
@@ -4003,19 +4001,154 @@
         </is>
       </c>
     </row>
-    <row r="66" spans="1:1">
+    <row r="66" spans="1:10" ht="409.6">
       <c r="A66" s="2">
         <v>65</v>
       </c>
-    </row>
-    <row r="67" spans="1:1">
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Large agent phases ran WITHOUT their role instructions and context — the agent produced generic or empty output instead of the platform-grade work it was built for. Affected 7 of the 16 agents whose instruction body exceeds ~24,000 characters, including UX Design, Architecture, Security, Code Review, Testing, and — critically — Implementation and Task Breakdown.</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Found while investigating why the UX Design phase behaved oddly. The platform delivers each agent two things: its role/process instructions (the agent 'body') and its run context (the composed manifest: project profile, upstream artifacts, rules). A recent fix for the UX 'Claude Code not found' crash (S.No 64) had moved large bodies into an AGENTS.md file — but Claude Code never loads AGENTS.md, and planning agents have no file-reading tool, so for every large agent the role body reached the model through NO channel at all. Separately, the composed manifest had also only ever been written to that unloaded AGENTS.md, so its Rules section never reached the model either. The agents limped along on a context-fetch tool but were not getting their authoritative instructions. Affects any project type.</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Companion Runner / Engine launch (ClaudeDriver)</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bug</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Root-caused during UX Design live testing (work item 8d6f3b7d). Verified against the installed Claude Agent SDK 0.1.0 and Claude CLI 2.1.205. Code: backend/drivers/claude_driver.py.</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P1</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The agent's instructions were delivered by the wrong channel. They were normally passed as the engine's 'system prompt', which the SDK puts on the command line — capped at ~32,000 characters on Windows, so the ~36KB UX body overflowed (S.No 64). The interim workaround wrote the body to an AGENTS.md file, but Claude Code does not auto-load AGENTS.md (only CLAUDE.md, with project setting-sources) and a sandboxed planning agent has no file-reading tool — so the body reached the model through no path. The manifest had the same problem. Net effect: 7 large agents ran without their role, and the interim fix silently regressed 6 phases that previously worked (their bodies had fit on the command line).</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Deliver the agent body + full run manifest as a TRUE FILE-BASED SYSTEM PROMPT via the CLI flag --system-prompt-file (passed through the SDK's extra_args, since the pinned SDK 0.1.0 doesn't type the flag; the pinned CLI 2.1.205 supports it — verified). The driver writes body+manifest to SYSTEM_PROMPT.md in the run folder and hands the engine its absolute path. Size-independent (no command-line limit for any agent), a real system prompt (strongest adherence — bodies are authored as system prompts), needs no CLAUDE.md/setting-sources trickery, and no client-repo collision in build. One uniform code path replaced the old size-threshold branching; dead AGENTS.md writes were removed. The manifest (incl. its Rules section and, for review, the inlined PR diff) now genuinely reaches the model for the first time. Verified live: a 40KB system-prompt file launched the real engine and the model followed instructions inside the file; a UX Design re-run produced correct, role-appropriate artifacts. Tests rewritten to assert body+manifest reach the CLI via --system-prompt-file for every body size.</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fixed</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" spans="1:10" ht="409.6">
       <c r="A67" s="2">
         <v>66</v>
       </c>
-    </row>
-    <row r="68" spans="1:1">
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A phase run failed in Phases &amp; Runs with 'Run failed — Unknown message type: rate_limit_event', even though the agent and companion were healthy.</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hit during UX Design live testing. Part-way through a run the engine emitted a 'rate_limit_event' notification message; the SDK's message reader didn't recognise that message type and raised an error, which aborted the entire phase. This would strike ANY phase, at random, whenever the engine sends a rate-limit notice.</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Companion Runner / Engine (ClaudeDriver)</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bug</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Observed on a UX Design run during live testing. Caused by version skew between the pinned Claude Agent SDK 0.1.0 and the newer Claude CLI 2.1.205. Code: backend/drivers/claude_driver.py.</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P1</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The installed Claude CLI (2.1.205) is newer than the pinned Claude Agent SDK (0.1.0) and emits notification message types the SDK's parser has no case for — here, 'rate_limit_event'. On an unknown type the SDK's parser raises a fatal 'Unknown message type' error, which propagates out and kills the run. These messages are non-essential telemetry; the run's real output still arrives as the normal assistant/result messages. The SDK simply treated an unknown notification as fatal.</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Made message parsing tolerant of unknown types. The driver wraps the SDK's parser: an unknown message type becomes a harmless, ignored message instead of crashing the run — while genuinely malformed messages (e.g. missing type) still raise, so real errors are not hidden. Forward-robust: it tolerates ANY future unknown notification type from a newer CLI, not just rate_limit_event, without a risky SDK upgrade. Verified: fed a real rate_limit_event through the actual SDK parser (benign, no crash), confirmed malformed messages still raise, and confirmed a stream containing the event still produces a valid result. New tests cover all three cases.</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fixed</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" spans="1:10" ht="409.6">
       <c r="A68" s="2">
         <v>67</v>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Some generated artifacts could not be previewed for review — preview showed 'artifact has no body to preview' even though the artifact clearly had content, blocking the user from reviewing and approving the gate.</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Seen on the SpendLog test project. Planning agents register many artifacts (assumptions register, user journeys, stakeholder map, accessibility spec, etc.) whose CONTENT is structured data stored in the artifact's external_ref field — because the register tool is pointers-only and there is no other place for that content to live. The preview endpoint only knew how to show a plain-text/markdown body from S3 or an inline 'body' field; it had no way to render structured external_ref content, so those artifacts previewed as empty.</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Artifacts &amp; Traceability (preview)</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bug</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Root-caused on SpendLog run 7f67d88a; all 7 artifacts of the run previewed empty. Code: backend/integrations/preview.py, backend/orchestration/activities.py.</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P1</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Artifact content lives in one of a few places: an S3 draft body, an inline external_ref 'body' field, the run's staged phase draft, or — for many planning sub-artifacts — as structured JSON in external_ref (the register tool is pointers-only, so structured data there is the only home for that content). The preview read-through handled the first three but had no renderer for structured external_ref, so those artifacts returned 'no body'. It is type- and phase-agnostic: it affects any artifact whose content is structured data, in any phase.</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Added a generic, type/phase-agnostic renderer in backend/integrations/preview.py that turns any structured external_ref into readable markdown (title heading, labelled fields, lists as bullets, lists of records as titled sections), and ranked the artifact's OWN structured content above the run-level fallbacks so a sub-artifact previews its own content rather than the whole phase document. Known pointer fields (ids, URLs, project refs) are excluded so no UUID noise leaks in. Also merged (not overwrote) the run outputs so the companion's raw report survives as the last-resort fallback, and made the driver report abnormal/empty engine endings instead of silently staging a blank draft. Verified live: all 7 previously-blank artifacts of the test run now preview as readable documents; today's UX Design artifacts preview correctly. New tests cover the renderer and the fallback ordering.</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fixed</t>
+        </is>
       </c>
     </row>
     <row r="69" spans="1:1">

--- a/docs/Bugs.xlsx
+++ b/docs/Bugs.xlsx
@@ -4151,19 +4151,154 @@
         </is>
       </c>
     </row>
-    <row r="69" spans="1:1">
+    <row r="69" spans="1:10">
       <c r="A69" s="2">
         <v>68</v>
       </c>
-    </row>
-    <row r="70" spans="1:1">
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The UX Design agent generated full HTML wireframe screens but they were never saved — the wireframe artifacts ended up empty (only a short text description), so no one could preview the screens and the implementation phase had nothing to read.</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Seen on the SpendLog-Test-2.1 UX Design run. The agent authored ~25 self-contained HTML state documents (default/loading/empty/error/success per screen) exactly as instructed, and registered one wireframe artifact per screen — but the HTML had no channel to reach storage, so each artifact carried only prose 'layout_notes'. The rendered screens were effectively lost.</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Platform-State MCP + Artifacts (UX Design wireframes)</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bug</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Observed on the SpendLog-Test-2.1 UX Design run. Code: mcp_platform_state/tools.py, mcp_platform_state/server.py, runner/companion/state_mcp.py, runner/companion/runner.py, backend/api/runner_views.py, backend/orchestration/activities.py, backend/integrations/preview.py, frontend/src/features/observability/ArtifactPreviewScreen.tsx, agents/05_ux_design/agent.md.</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P1</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">register_artifact is deliberately pointers-only (state stays pointers, bodies live in the object store), and there was NO tool to hand a large body to the platform to persist. Inline external_ref bodies can't carry big HTML because the single MCP call is token-capped (a ~401K-char register call was rejected), and the sandboxed planning agent has no Write/S3 access to stage a snapshot itself. get_artifact also returned pointers only, so even the implementation agent could not read a screen's HTML. Net: the UX agent's central deliverable had nowhere to go and degraded to prose. Affects any phase that must persist a large body, not just wireframes.</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Added the missing persistence primitive: a stage_artifact_body MCP tool that streams one body (e.g. one HTML state) to the object store as a run/phase-scoped draft and returns its s3_key+hash — sandbox-safe (a platform capability, not local Write), one document per call so it never hits the token cap. The UX agent now stages each state then registers one wireframe artifact per screen with external_ref.states = [{name, s3_key, content_hash}] (primary s3_key = default state); register_artifact stays pointers-only. Added a get_artifact_body read tool (one state at a time) so the task-breakdown/implementation agents can read the actual HTML. Preview now surfaces all states read-through and the UI shows a state switcher rendering each screen in an isolated iframe, so the user previews and approves the real screens; Figma export rides the existing export-policy seam. Also bound project_id from the launch in get_context/list_artifacts (agents were passing the project NAME → backend 500). Verified: new unit tests for staging, one-state read, and multi-state preview pass; existing suites green (4 preview failures are MinIO-not-reachable env only).</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fixed</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" spans="1:10">
       <c r="A70" s="2">
         <v>69</v>
       </c>
-    </row>
-    <row r="71" spans="1:1">
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UX Design ran ~15 min and registered NOTHING. The agent generated and staged its HTML screens fine, but could not read its own project context — every get_context / list_artifacts call came back too big and failed, so the agent looped without ever registering an artifact.</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hit on the SpendLog-Test-2.1 UX re-run right after the wireframe-persistence fix. As upstream phases (requirements, PRD, architecture) accumulated artifacts, the context/list tools returned the FULL content of up to 50 artifacts at once (their structured bodies live in external_ref), producing 400,000+ character responses that blow the engine's per-tool token limit. The agent then grabbed shortened artifact ids from the truncated output and called the read tools with them, which 500'd.</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Platform-State MCP (get_context / list_artifacts / get_artifact_body)</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bug</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Observed on UX Design run f8966dd4: list_artifacts=401,397 chars, get_context(prd)=420,594 chars, plus get_artifact_body 500 'is not a valid UUID' on shortened ids. 0 artifacts registered after 15 min (11 HTML states DID stage to S3 successfully - staging was not the problem). Code: mcp_platform_state/tools.py.</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P1</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">get_context and list_artifacts serialized each artifact's ENTIRE external_ref - which for many artifact types holds the structured body/content, not just pointers. Returning up to 50 of those in one response exceeded the MCP token budget, so the whole call failed. This is a listing that must carry pointers only (platform owns STATE as pointers; CONTENT is fetched on demand) but was leaking bodies. A secondary effect: with the list truncated to a saved file, the agent improvised 8-character ids, and get_artifact_body/get_artifact raised an unhandled 500 on a non-UUID instead of a friendly message. Pre-existing latent issue that became fatal once the project had several large upstream artifacts.</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Made get_context and list_artifacts return POINTER-ONLY artifacts: a new lean serializer strips large/structured values out of external_ref, keeping only small metadata (id, type, route, screen id, sor, and for wireframes the states' name+s3_key+hash). Bodies are now fetched on demand with get_artifact_body(full_id). Measured on the real project: list_artifacts dropped 401,397 -&gt; 20,725 chars, get_context(prd) 420,594 -&gt; 35,702 chars - both safely under the limit. Also hardened get_artifact and get_artifact_body to return a clear 'pass the full id' message instead of a 500 on a malformed/shortened id (which also removes the source of the bad ids, since the agent now receives full ids in a small listing). Verified live against the DB; backend + worker restarted to load it.</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fixed</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" spans="1:10">
       <c r="A71" s="2">
         <v>70</v>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The UX Design gate could not be approved: clicking Approve returned 'cannot approve: 9 required gate condition(s) unmet' and there was no way in the UI to satisfy them, blocking the whole design gate.</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hit approving the UX Design gate on SpendLog-Test-2.1. By design the UX/accessibility gate carries a required WCAG 2.1 AA checklist (9 criteria) that the reviewer must mark satisfied before Approve. But the Gates approval panel showed only Comment + Approve/Reject with no checklist, and its inline Approve sent no condition updates - so the required criteria could never be ticked and the gate was un-approvable. The checklist component (CriteriaGate) existed but was never wired into a route or the panel.</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gates (approval UI)</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bug</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Observed approving UX Design gate (approval bc7e6a13, gate_type phase_gate, role designer, 9 WCAG conditions). First surfaced now - first UX gate approval attempt (prior UX run was deleted before its gate). Code: frontend/src/features/lifecycle/Gates.tsx; backend enforcement backend/apps/gates/services.py + wcag.py (unchanged, working as designed).</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P1</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The ux_design gate opens with conditions_for_phase('ux_design') = 9 WCAG 2.1 AA criteria (all required, satisfied=false). services.decide_gate blocks the APPROVE decision while any required condition is unsatisfied; the reviewer satisfies them by sending conditions=[{key,satisfied}] with the decision. The Gates panel's inline Approve never sent conditions and rendered no checklist, and the dedicated CriteriaGate checklist screen was orphaned (present only in tests, no route). So there was no path in the app to satisfy the criteria. Backend + gate design are correct; the gap was purely the missing checklist UI on the approval panel.</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Wired the WCAG checklist into the Gates approval panel (frontend/src/features/lifecycle/Gates.tsx). When the selected gate has conditions, the panel now fetches them via the existing useGateCriteria hook and renders each criterion as a togglable checkbox (reusing CriteriaList/CriteriaItem), shows an 'X of N met' progress, keeps the Approve button disabled until every required criterion is ticked, and includes the reviewer's conditions=[{key,satisfied}] in the decide call. Gates with no conditions are unchanged (decide directly). Verified: the pending approval carries the 9 WCAG conditions; frontend typechecks clean; reuses the same proven decide path the CriteriaGate screen already used. Reviewer can now tick the WCAG criteria and approve.</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fixed</t>
+        </is>
       </c>
     </row>
     <row r="72" spans="1:1">

--- a/docs/Bugs.xlsx
+++ b/docs/Bugs.xlsx
@@ -4301,79 +4301,754 @@
         </is>
       </c>
     </row>
-    <row r="72" spans="1:1">
+    <row r="72" spans="1:10" ht="409.6">
       <c r="A72" s="2">
         <v>71</v>
       </c>
-    </row>
-    <row r="73" spans="1:1">
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Task Breakdown agent told to fetch artifact bodies with the wrong tool (get_artifact instead of get_artifact_body)</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The task-breakdown agent instructions told it to fetch upstream artifact bodies (PRD / requirements / architecture / per-screen wireframes) using get_artifact. Since the pointer-only refactor (S.No 69), get_artifact returns only pointers/provenance with NO body. As written the agent would receive no content to decompose and would stall or hallucinate a backlog — the same failure mode that stalled the UX Design phase until its tool wiring was fixed.</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Task Breakdown / Agents</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bug</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">agents/06_task_breakdown/agent.md (lines 28 and 145); tool split in mcp_platform_state/tools.py get_artifact vs get_artifact_body</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P1</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">agent.md was not updated when get_artifact/get_artifact_body were split last session (S.No 68-69). The verbatim instruction kept naming a tool that is now pointer-only, so the agent had no way to read the bodies it must decompose.</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Updated both references in agents/06_task_breakdown/agent.md to get_artifact_body (which reads one state at a time for multi-state wireframes) and noted that get_artifact returns pointers only. To take effect the backend/worker/companion must be restarted so the new agent body is delivered; verified against a live task-breakdown run.</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fixed</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" spans="1:10" ht="409.6">
       <c r="A73" s="2">
         <v>72</v>
       </c>
-    </row>
-    <row r="74" spans="1:1">
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No REST endpoint to start implementation (build) on a work item</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The implementation BuildWorkflow saga (orchestration.trigger.trigger_build) had no HTTP surface — it was only callable from tests. A user therefore could not start implementation on a work item from the platform, blocking the 'run implementation on one task' flow (both the internal-managed and Jira-managed cases still start the code work through this path).</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Implementation / Work Items</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bug</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">backend/api/views.py (WorkItemViewSet — only the phase trigger action existed); backend/orchestration/trigger.py trigger_build</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P1</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Only the phase trigger (trigger_phase) was wired to a viewset action; trigger_build was fully implemented but was never exposed via a DRF @action/route.</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Added POST /api/work-items/{id}/build/ (WorkItemViewSet.build) plus BuildTriggerSerializer (agent_key defaults to 07_implementation; optional repo/base default from the work item's Repository; required_role; user_id for companion routing). Returns 202 {run_id, workflow_id}; returns 400 with a friendly message when the work item has no target repository. New focused test backend/tests/test_build_trigger_api.py (2 tests: happy-path start + no-repo rejection).</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fixed</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" spans="1:10" ht="409.6">
       <c r="A74" s="2">
         <v>73</v>
       </c>
-    </row>
-    <row r="75" spans="1:1">
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Companion never git-pushes the worktree branch, so opening the PR fails against a live GitHub repo</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">During implementation the companion writes code into a local git worktree on branch feature/WI-&lt;n&gt; but never pushes that branch to origin. codehost.open_pull_request then calls the GitHub REST POST /pulls assuming the head branch already exists on the remote, so against a live GitHub repository the PR step returns 404/422. Code still lands in the developer's local worktree; only the PR / merge / merge-gate steps are blocked.</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Implementation / CodeHost</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bug</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">runner/companion/runner.py (no push by design D2); runner/companion/worktree.py (teardown leaves branch local); backend/orchestration/build_activities.py open_build_pr_core; integrations/github/codehost.py open_pull_request</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P1</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Design D2 keeps all Git side-effects on the platform, but the actual branch-push step was implemented on neither side — the worktree branch is created and left purely local.</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FIXED (Option B). The companion now performs the Git side-effects (D2): after the build agent writes code and the secret scan passes, run_build commits the change to feature/WI-&lt;key&gt; with a derived Conventional-Commit message and pushes the branch to origin, reporting head_sha so the platform's open_build_pr opens the draft PR against a real ref. New worktree helpers commit_all/push_branch/head_sha (runner/companion/worktree.py); BuildTask carries work_item_title/type and dispatch_build_core ships them for the commit subject. Nothing is committed/pushed when the secret scan blocks or the agent produced no change. Tests: 3 new in test_companion_runner.py (commit+push to a bare remote, subject-from-title, secret-block no-push) + dispatch payload assertion in test_build_activities.py; all pass. The full path (GitHub CodeHost connect + PR -&gt; review -&gt; merge-gate -&gt; done) is now unblocked.</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fixed</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" spans="1:10" ht="409.6">
       <c r="A75" s="2">
         <v>74</v>
       </c>
-    </row>
-    <row r="76" spans="1:1">
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Integration credentials entered in the UI are never used; connectors authenticate from server .env</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IntegrationConnection.secret_encrypted (the credentials a tenant enters when connecting Jira / Confluence / etc.) is written but never decrypted at runtime — decrypt_secrets is only called in tests. Every Atlassian connector resolves its credentials via AtlassianConfig.from_settings() (the server .env). So a tenant that 'connects Jira' and passes the wiring check still authenticates with the single .env Atlassian account; scopes.project_key IS read from the connection, but the secret is not. Effectively single-tenant and a multi-tenant credential-leak risk. The connection also shows Healthy without any live network probe.</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Integrations / Connectors</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bug</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">backend/integrations/registry.py (_atlassian_config / _build_jira / _build_confluence); backend/apps/integrations/services.py (test_integration_connection is wiring-only); apps/integrations/crypto.decrypt_secrets (tests only)</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P2</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The token_ref indirection is a documented Phase-5 seam; Phase 1 hardcoded from_settings() and decrypt_secrets was never wired into the connector builders.</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Deferred (Phase-5 seam). Fix = wire decrypt_secrets(conn) into the connector builders so per-tenant creds are used and retire the .env fallback; make test-connection a real reachability probe. For the current greenfield test, Jira is connected exactly like Confluence: the Integrations connection supplies scopes.project_key and the shared Atlassian creds live in .env.</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" spans="1:10" ht="409.6">
       <c r="A76" s="2">
         <v>75</v>
       </c>
-    </row>
-    <row r="77" spans="1:1">
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No dedicated Task Breakdown review screen; dependencies and estimates are not surfaced before the gate</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The four planning artifacts (backlog / sprint_plan / definition_of_done / dependency_map) render only as plain markdown via the generic artifact preview, and the proposed work items appear separately on the Work Items board as generic 'Draft' badges. depends_on is serialized but read by zero frontend files (no dependency graph), and there is NO estimate/story-points field on WorkItem at all — so a reviewer cannot see hierarchy, dependencies and estimates in one place before approving the task-breakdown gate.</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Task Breakdown / Work Items UI</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Enhancement</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">frontend TaskBreakdown.tsx (after-the-fact summary), WorkItemsBoard.tsx (depends_on unused); backend/integrations/preview.py (no backlog renderer); backend/apps/workitems/models.py (no estimate field)</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P2</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The task-breakdown preview UI was never built to the depth of other phases, and an estimate/story-points field was never modeled on WorkItem.</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Accepted as-is for this test (markdown preview + Work Items board). Later: a dedicated proposed-backlog review screen showing epic-&gt;story-&gt;task hierarchy + depends_on graph + estimates; add WorkItem.estimate; add a backlog-specific preview renderer.</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" spans="1:10" ht="409.6">
       <c r="A77" s="2">
         <v>76</v>
       </c>
-    </row>
-    <row r="78" spans="1:1">
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No UI to edit the generated user stories/tasks before the gate</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Users cannot edit the stories/tasks the Task Breakdown agent generates. A backend edit surface already exists (WorkItemPatchSerializer allows PATCH of title/description/type), but there is no frontend for it, and state / estimate / dependencies are not editable.</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Task Breakdown / Work Items UI</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Enhancement</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">backend/api/serializers.py WorkItemPatchSerializer (exists, title/description/type); no frontend edit UI</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P3</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The edit UI was never built; only the PATCH serializer was scaffolded.</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Deferred (later-phase optimization, per team decision). Add an edit UI over the existing PATCH endpoint; consider making dependencies and estimate editable too.</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" spans="1:10" ht="409.6">
       <c r="A78" s="2">
         <v>77</v>
       </c>
-    </row>
-    <row r="79" spans="1:1">
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Re-running Task Breakdown duplicates the whole backlog (create_work_item has no idempotency)</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">create_work_item unconditionally creates a new WorkItem — there is no natural-key / get_or_create dedupe. Re-dispatching the task-breakdown phase (for example after a stalled run) creates duplicate epics/stories/tasks and duplicate WI numbers. Re-run hygiene currently requires manually deleting the partial batch first (as was done for the UX phase).</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Platform State / Work Items</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bug</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mcp_platform_state/tools.py create_work_item (contrast register_artifact which auto-versions)</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P2</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No idempotency/natural key on work-item creation, unlike register_artifact which versions siblings.</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Deferred. Add an idempotency key (e.g. project+phase+title, or an agent-supplied external key) so a re-run upserts rather than duplicates. For today's run, delete any partial batch before re-triggering.</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" spans="1:10" ht="409.6">
       <c r="A79" s="2">
         <v>78</v>
       </c>
-    </row>
-    <row r="80" spans="1:1">
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Jira integration is one-way (create-only): no inbound webhook, no status sync, dropped fields</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Reconcile creates Jira issues (summary/description/parent only) and stores the Jira key in WorkItem.external_ref, but: (a) there is no inbound Jira webhook and no Jira-status -&gt; WorkItem.State mapping, so a Jira transition (In Progress/Done) is invisible to the platform; (b) transition_issue is implemented but never called in production, so platform-side transitions are not pushed back to Jira; (c) depends_on edges, acceptance criteria, story points and wireframe refs are not pushed. Completion is detected ONLY via the GitHub PR-merge webhook — never via Jira. So a Jira-managed task is a visibility mirror, not a two-way work surface.</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Integrations / TaskTracker (Jira)</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Enhancement</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">backend/integrations/reconcile.py (create-only, minimal fields); integrations/atlassian/tasktracker.py transition_issue (dormant); backend/integrations/webhooks.py (GitHub inbound only)</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P2</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bi-directional Jira sync is a future seam; reconcile is create-only and maps neither dependency links nor rich issue fields.</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Deferred. Add an inbound Jira webhook + status-&gt;state mapping, wire transition_issue on WorkItem transitions, and map depends_on (Jira issue links) plus acceptance criteria / story points / wireframe ref in reconcile.</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" spans="1:10" ht="409.6">
       <c r="A80" s="2">
         <v>79</v>
       </c>
-    </row>
-    <row r="81" spans="1:1">
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No in-context 'Push to Jira' action on the Task Breakdown screen; publish reconciles ALL proposed work items at once</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The Jira push lives on the generic Artifact Publish screen keyed off the backlog artifact — there is no 'push these tasks to Jira' button on the Task Breakdown screen or the Work Items board where a reviewer is actually looking at the composed stories/tasks. Worse, publishing calls reconcile_backlog(project_id), which pushes EVERY proposed work item in the project in one go — there is no per-item review-and-confirm or subset selection before the push. A reviewer cannot push a reviewed subset or see, in context, exactly what will go to Jira.</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Task Breakdown / Integrations UI</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Enhancement</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">frontend ExportPublish.tsx (push on artifact publish); backend/api/views.py _publish_tasktracker -&gt; reconcile_backlog(project_id); no push button on TaskBreakdown.tsx or WorkItemsBoard.tsx</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P2</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The Jira push was wired only to the generic per-artifact publish path (which reconciles the whole project's proposed items), never to an in-context task-review action with selection/confirm.</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Deferred (accepted for this test). Later: add a 'Push to Jira' action on the Task Breakdown review screen with a per-item / selection confirm step, backed by a scoped reconcile (push the reviewed subset, not the whole project blindly).</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" spans="1:10" ht="409.6">
       <c r="A81" s="2">
         <v>80</v>
       </c>
-    </row>
-    <row r="82" spans="1:1">
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SYSTEMIC (fresh-run blocker): manifest composer + 15 of 16 agent bodies tell every agent to fetch artifact bodies with get_artifact (pointer-only)</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The manifest composer's 'Relevant Artifacts' section instructed EVERY agent to 'fetch full bodies with get_artifact(artifact_id)', and 15 of 16 agent bodies repeated the same stale instruction. Since get_artifact became pointer-only (S.No 68-69, commit d7c27d6), it returns NO S3 body — so under the current pointer-only get_context/list_artifacts regime an agent cannot read its upstream inputs and stalls or hallucinates (the exact UX-phase failure). Earlier phases (ideation..architecture) appeared to work only because they ran on 2026-07-08 BEFORE get_context went pointer-only (context then carried full bodies inline) and because some upstream bodies happened to be stored inline in external_ref. A fresh end-to-end run puts every phase under the pointer-only regime and would hit the failure. Same class as S.No 71 (task breakdown) but suite-wide.</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Agents / Manifest / Platform State</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bug</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">backend/manifest/composer.py:161 (Relevant Artifacts instruction); 15 agent bodies: 00_onboarding, 00b_context_bridge, 00c_context_extractor, 01_ideation, 02_requirements, 03_prd, 04_architecture, 05_ux_design, 07_implementation, 08_code_review, 09_testing, 09b_test_automation, 10_security, 11_cicd, 12_deployment; get_artifact vs get_artifact_body in mcp_platform_state/tools.py</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P1</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The get_artifact/get_artifact_body tool split (S.No 68-69) made get_artifact pointer-only, but the composer instruction and every pre-existing agent body still named get_artifact for body fetches. They were authored/tested before get_context went pointer-only (2026-07-09, d7c27d6), so the regression stayed latent until a phase ran under the new regime (UX was first).</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Swept all 27 body-fetch references to get_artifact_body (word-boundary replace; get_artifact_body's fallback chain in integrations/preview.py handles S3 + inline external_ref.body + structured external_ref + run-draft bodies): composer.py:161 plus the 15 agent bodies (06_task_breakdown was already fixed under S.No 71). Verified: 0 bare body-fetch get_artifact remain (only 06's accurate 'get_artifact returns pointers' note); composer compiles; agent-migration CONTENT tests pass. Backend + worker restarted to reload the composer.</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fixed</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" spans="1:10" ht="409.6">
       <c r="A82" s="2">
         <v>81</v>
       </c>
-    </row>
-    <row r="83" spans="1:1">
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Two agent-migration tests assert on options.system_prompt, obsolete since file-based system-prompt delivery</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">test_prd_run_reads_inputs_from_platform and test_ux_run_reads_inputs_from_platform assert against captured options.system_prompt, but the driver now delivers the agent body via a --system-prompt-file (SYSTEM_PROMPT.md in the run workdir, commit 98200ae), so options.system_prompt is None and the tests raise TypeError. Confirmed pre-existing: they fail identically on clean HEAD, independent of the get_artifact_body sweep. Runtime is unaffected; only the tests are stale.</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tests / Engine driver</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bug</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">backend/tests/test_agents_migration.py:146; backend/tests/test_design_test_agents_migration.py:213; driver delivery in backend/drivers/claude_driver.py (--system-prompt-file, 98200ae)</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P3</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The tests were written against the old inline options.system_prompt delivery and were not updated when delivery moved to a file (98200ae).</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not yet fixed. Update both tests to read the written SYSTEM_PROMPT.md (run workdir) instead of options.system_prompt, or assert on the file-based delivery path.</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" spans="1:10" ht="409.6">
       <c r="A83" s="2">
         <v>82</v>
       </c>
-    </row>
-    <row r="84" spans="1:1">
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Task Breakdown agent had no body-persistence protocol — its 4 planning artifacts (backlog/sprint_plan/DoD/dependency_map) would not reliably persist</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The task-breakdown agent was told 'register it with register_artifact ... the platform persists the bodies', but register_artifact is pointers-only and the agent had NO stage_artifact_body protocol (UX has 3 such calls; task breakdown had 0). So on a run its four full-document deliverables risked not persisting: at best the primary previews via the run-report fallback, the rest show empty — the same class as the UX wireframe loss (S.No 68) before UX got its staging protocol.</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Task Breakdown / Agents</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bug</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">agents/06_task_breakdown/agent.md (Output section); stage_artifact_body in mcp_platform_state/tools.py; _PLATFORM_TOOL_NAMES in backend/orchestration/activities.py</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P1</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The agent body predates the stage_artifact_body tool (S.No 68) and kept the old, now-false 'the platform persists the bodies' wording; only 05_ux_design was updated with a staging protocol at the time.</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Added a 'How bodies are persisted' protocol to agents/06_task_breakdown/agent.md mirroring UX: each full deliverable (backlog/sprint_plan/definition_of_done/dependency_map) is staged with stage_artifact_body(filename, body) (one document per call), then registered with register_artifact using the returned s3_key/content_hash; the assumption register may stay inline in external_ref. Verified stage_artifact_body is in the planning allowlist and not sandbox-blocked; container sees the update.</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fixed</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" spans="1:10" ht="409.6">
       <c r="A84" s="2">
         <v>83</v>
       </c>
-    </row>
-    <row r="85" spans="1:1">
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI phase trigger ran BUILD phases as planning runs — clicking Implementation could not produce code (no worktree/commit/PR)</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The Work Items / Phases &amp; Runs UI triggers every phase through POST /work-items/{id}/trigger/ -&gt; trigger_phase -&gt; AgentRunWorkflow (planning: sandboxed, no filesystem/git/worktree). But build phases must run through the BuildWorkflow (worktree -&gt; commit -&gt; push -&gt; PR -&gt; review -&gt; merge gate). So clicking 'Implementation' (or CI/CD, Test Automation) on a task would start a sandboxed planning run that cannot write code, commit, push, or open a PR — nothing would land in the repo. There was no build-vs-plan routing anywhere: only trigger_build (used by tests) reached the build path, and it had no UI entry. Affects every current and future build agent, not just implementation.</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Implementation / Phases &amp; Runs / Work Items</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bug</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">backend/api/views.py WorkItemViewSet.trigger; backend/orchestration/trigger.py (trigger_phase vs trigger_build); backend/apps/registry/catalog.py; frontend triggers via /trigger/ (PhasesAndRuns.tsx / WorkItemTask.tsx / WorkItemDefect.tsx)</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P1</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">trigger_phase always started an AgentRunWorkflow regardless of agent; build routing existed only implicitly (which function a test happened to call). No source of truth marked which agents ride the BuildWorkflow, and the single UI trigger had no branch for it.</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Added an explicit rides_build flag to AgentDefinition (single source of truth), set True only for the agents whose migrated body states the platform commits/pushes/opens the PR: 07_implementation, 09b_test_automation, 11_cicd. Planning phases (05_ux_design, 06_task_breakdown, 09_testing, 10_security, 12_deployment) stay False; 08_code_review runs inside the build loop (dispatched automatically, not a standalone user trigger). WorkItemViewSet.trigger now routes rides_build agents to trigger_build, else trigger_phase — so the existing UI buttons work for both plan and build with NO frontend change, and a future build agent only sets the flag. trigger_build now falls back to the project's default repository when the work item has none (proposed tasks). Tests: routing (07-&gt;build-run, 06-&gt;agent-run), rides_build flag set, project-default-repo fallback — all pass; agentspec-migration + frontend trigger/catalog tests still green. Backend restarted; flags verified live in-container.</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fixed</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" spans="1:10" ht="409.6">
       <c r="A85" s="2">
         <v>84</v>
       </c>
-    </row>
-    <row r="86" spans="1:1">
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Trigger routes to the newest enrollment even if it never connected — dispatch can land on a dead enrollment while the live companion gets 204 (stuck run)</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">_resolve_enrollment picks the most recent RunnerEnrollment for the triggering user regardless of whether that enrollment has ever checked in (last_seen). When a machine has several enrollments (e.g. opening Connect Machine to copy a token while the daemon runs on an older token, or repeated reconnects), the trigger can route the dispatch to an enrollment whose daemon never ran, while the live companion polls under a different enrollment and receives 204 No Content. Observed live on the first WI-18 build: dispatch stuck 'pending' on a never-checked-in enrollment (last_seen null) while the running companion polled a different one; the build never started. Workaround used: wipe stale enrollments so only one fresh enrollment exists.</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Companion / Runner enrollment</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bug</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">backend/orchestration/trigger.py _resolve_enrollment (used by trigger_phase + trigger_build); apps/runs/models.py RunnerEnrollment.last_seen; runner_views.py RunnerWorkClaimView</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P2</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">_resolve_enrollment orders enrollments by recency and does not prefer ones that have actually checked in (last_seen recent / within the online window). RC-4 collapses re-enrollments by project but the selection still ignores liveness.</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not yet fixed (deferred to avoid a backend restart mid-build). Fix: _resolve_enrollment should prefer the newest enrollment with a recent last_seen (online) and ignore never-checked-in / stale ones; optionally fail-fast or re-point a dispatch whose target enrollment is offline. Interim mitigation: keep a single fresh enrollment (wipe stale ones before triggering).</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" spans="1:10" ht="409.6">
       <c r="A86" s="2">
         <v>85</v>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">09_testing / 10_security bodies reference the git worktree but are classified as planning (sandboxed, no filesystem) — may be starved of code when actually run</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">During the build-routing audit, 09_testing and 10_security were classified as planning phases: their bodies say 'when artifacts are registered, stop; the platform opens the review gate' — no commit/push/PR, so correctly NOT routed to the BuildWorkflow. But both bodies also reference the companion git worktree several times (they read the codebase to test/scan it). Planning phases run through the AgentRunWorkflow sandbox (no filesystem/Bash), so if these agents genuinely need to read the worktree code, they would be starved when run. There is currently no third execution mode ('reads the worktree but produces no PR'). Unverified — these phases have not been run yet.</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Testing / Security / Orchestration</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bug</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">agents/09_testing/agent.md, agents/10_security/agent.md (worktree references); backend/orchestration routing (BuildWorkflow vs sandboxed AgentRunWorkflow); apps/registry/catalog.py rides_build</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P3</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Only two execution paths exist (build = worktree + PR + merge gate; plan = sandboxed + register + review gate). 09_testing/10_security need to read code (worktree) but emit review-gated artifacts, not a PR — a shape neither path serves cleanly.</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not yet investigated. When these phases are first run, verify the agent can access the code it needs; if not, either add a 'worktree-read, no-PR' execution mode (build-mode filesystem access without the commit/push/merge gate) or feed the needed code context via platform-state tools instead of the worktree. Left on the planning path for now (correct re: no PR).</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
       </c>
     </row>
     <row r="87" spans="1:1">

--- a/docs/Bugs.xlsx
+++ b/docs/Bugs.xlsx
@@ -5051,19 +5051,154 @@
         </is>
       </c>
     </row>
-    <row r="87" spans="1:1">
+    <row r="87" spans="1:10" ht="409.6">
       <c r="A87" s="2">
         <v>86</v>
       </c>
-    </row>
-    <row r="88" spans="1:1">
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Build fails after push: agent's pre-PR 'code' pointer makes open_build_pr skip opening the real PR, then code review crashes (KeyError 'repo')</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The 07_implementation agent registers a pre-PR 'code' pointer (branch/files_changed, no PR) which its body says 'the platform reconciles with the PR it opens'. But open_build_pr_core treated ANY existing code artifact with a truthy external_ref as 'PR already opened' and returned early, so it never opened the real PR; then run_code_review_core read code.external_ref['repo'] and raised KeyError('repo'). Observed live on WI-18: code committed and pushed to feature/WI-aa6020d0 on GitHub, but NO PR opened and the run failed — blocking PR to review to merge.</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Implementation / Build pipeline</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bug</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">backend/orchestration/build_activities.py open_build_pr_core + run_code_review_core; agents/07_implementation/agent.md (~line 264 register code pointer)</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P1</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">open_build_pr's idempotency check mistook the agent's pre-PR pointer for an opened PR; the documented 'platform reconciles the pointer with the PR' behaviour was never implemented.</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Added _is_pr_ref (a real PR ref carries repo+number). open_build_pr short-circuits only on a real opened PR; when the agent's pre-PR pointer exists it OPENS the PR and reconciles that artifact in place (update_artifact with the PR external_ref + STAGED) instead of skipping/duplicating. run_code_review guards on _is_pr_ref (clear error, not KeyError). New test test_open_pr_reconciles_agent_pre_pr_pointer + 10 existing build-activities tests pass. Worker reloaded; failed WI-18 run cleaned for a fresh re-trigger.</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fixed</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" spans="1:10" ht="409.6">
       <c r="A88" s="2">
         <v>87</v>
       </c>
-    </row>
-    <row r="89" spans="1:1">
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Implementation agent can transition the WorkItem to 'done' itself (mid-build), bypassing the platform merge gate that owns completion</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">During the WI-18 build, the WorkItem was set to state='done' at 12:25:51 — a full minute BEFORE the PR opened (12:26:51), with no merge-gate approval and no webhook. The only actor with the tool and that timing is the 07_implementation agent: transition_work_item is in the build-phase tool allowlist (BUILD_STATE_TOOLS), so the agent marked its own task 'done' as it finished. This violates control-plane ownership of completion (non-negotiable: gates live in the control plane) — the platform should set 'done' only after the merge gate is approved and the PR merged. Effect: WorkItem state becomes premature/unreliable and the merge gate is cosmetic for state purposes.</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Implementation / Guardrails / Work Items</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bug</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">runner/companion/runner.py BUILD_STATE_TOOLS ('transition_work_item'); backend/api/runner_views.py allowlist; mcp_platform_state/tools.py transition_work_item; backend/orchestration/build_workflow.py owns the done transition (~line 150)</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P2</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">transition_work_item is exposed to the build agent (needed for remediation child items) but nothing stops it from transitioning the MAIN WorkItem into a gated/terminal state. The platform's post-merge completion transition and the agent's tool access overlap.</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open — team to address later. Options: remove transition_work_item from the build agent's allowlist (platform owns all WorkItem state); or scope it so the agent may only transition remediation child items it owns; or reject agent-initiated transitions to gated states ('accepted'/'done') server-side.</t>
+        </is>
+      </c>
+      <c r="J88" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" spans="1:10" ht="409.6">
       <c r="A89" s="2">
         <v>88</v>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Merging the PR directly on GitHub bypasses the platform merge gate and orphans the BuildWorkflow (no reachable webhook to reconcile the external merge)</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The intended completion flow is: PR -&gt; platform code review -&gt; merge gate approved in the platform -&gt; platform merges via CodeHost -&gt; WorkItem done. On WI-18 the developer merged PR #1 directly on GitHub instead. Because the platform runs on localhost and no GitHub webhook is configured/reachable (GITHUB_WEBHOOK_SECRET empty; GitHub cannot reach localhost), the platform never learned of the merge. Result: the BuildWorkflow (build-run-dbf76d68) is left RUNNING, parked at the review/merge-gate step for a PR that is already merged, and will never complete on its own. The code did land on main (the developer's merge), but the platform workflow and gate are out of sync.</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Build pipeline / CodeHost / Webhooks</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bug</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">backend/integrations/webhooks.py (GitHub PR-merge -&gt; transition done, needs a reachable endpoint + GITHUB_WEBHOOK_SECRET); backend/orchestration/build_workflow.py (merge gate expects the platform to merge); settings.GITHUB_WEBHOOK_SECRET (empty)</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P2</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The platform-driven merge (via the merge gate) and an external GitHub merge are two paths; only the platform-driven one completes the workflow. The inbound webhook that would reconcile an external merge is not configured/reachable in local dev, so external merges strand the workflow.</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open — team to address later. Either drive merges through the platform merge gate (Gates page) so the platform merges + completes the workflow, OR expose the platform on a reachable URL (tunnel/deploy) + configure the GitHub webhook with GITHUB_WEBHOOK_SECRET so external merges reconcile (transition done + let the workflow finish). Interim: terminate the currently-orphaned build-run-dbf76d68 workflow.</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
       </c>
     </row>
     <row r="90" spans="1:1">

--- a/docs/Bugs.xlsx
+++ b/docs/Bugs.xlsx
@@ -6101,14 +6101,104 @@
         </is>
       </c>
     </row>
-    <row r="108" spans="1:1">
+    <row r="108" spans="1:10" ht="409.6">
       <c r="A108" s="2">
         <v>107</v>
       </c>
-    </row>
-    <row r="109" spans="1:1">
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Implementation/build companion was single-repo by construction - could not land code in the correct repo on a multi-repo project (Hybrid Option C blocker)</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pre-build audit before the SpendLog-1 (frontend+backend) implementation run: the backend routes every build to work_item.repo and opens/merges the PR against that exact repo (trigger.py:171-186, build_activities.py open_build_pr/merge), and build is fully SoR-agnostic (internal + Jira both build off platform WorkItem rows with repo intact). BUT the local companion daemon held ONE --repo-path for its whole lifetime and forked every work item's worktree from it, pushing to that clone's origin - ignoring BuildTask.repo entirely (daemon.py:119/195-208, runner.py:152-164; task.repo referenced nowhere in runner/). On a 2-repo project the repo NOT wired into --repo-path would either fail at 'git worktree add' (base branch absent) or, worse, silently push to the wrong repo if a same-named branch existed, after which open_build_pr 404s looking for the head under the correct repo. Violates the non-negotiable 'code lands in the correct GitHub repo'.</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Runner / Companion / Build (implementation phase)</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bug</t>
+        </is>
+      </c>
+      <c r="F108" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">runner/companion/__main__.py (serve --repo NAME=PATH); runner/companion/daemon.py (_resolve_repo_path, _run_build); runner/companion/runner.py (assert_remote_matches before push); runner/companion/worktree.py (assert_remote_matches); backend/tests/test_companion_daemon.py + test_companion_runner.py; docs/PHASE_2_BUILD_SPEC.md</t>
+        </is>
+      </c>
+      <c r="G108" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P1</t>
+        </is>
+      </c>
+      <c r="H108" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The companion build mode was written for the pre-multi-repo (single-repo) world: one --repo-path clone served every task. BuildTask.repo (work_item.repo) was delivered in the dispatch payload but never consumed to pick a clone; there was no repo-&gt;local-path resolver and no clone-on-demand.</t>
+        </is>
+      </c>
+      <c r="I108" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FIXED. Added a repeatable 'serve --repo owner/name=/path' mapping; the daemon now resolves the clone per BuildTask.repo (_resolve_repo_path) and FAILS LOUD on an unmapped repo instead of falling back to a wrong clone (that build is reported failed, the daemon keeps serving). --repo-path kept as the single-repo shorthand (backward compatible). Defense-in-depth: assert_remote_matches refuses to push if the clone's origin doesn't match the routed repo (hosted remotes only; local/test remotes skipped). Docs updated (PHASE_2_BUILD_SPEC 3) incl. the single GITHUB_TOKEN must cover all mapped repos (see S.No 103). 36 companion tests pass (added: mapped-clone routing, unmapped fail-loud, shorthand back-compat, origin match/mismatch/local-skip, repo-map parse).</t>
+        </is>
+      </c>
+      <c r="J108" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fixed</t>
+        </is>
+      </c>
+    </row>
+    <row r="109" spans="1:10" ht="330">
       <c r="A109" s="2">
         <v>108</v>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Multi-repo: a work item with no repo assigned silently built into the project default repo (e.g. backend code PR'd into the frontend repo) instead of failing</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">trigger_build fell back to the project's is_default Repository whenever a work item had no repo pinned (trigger.py:173-183). Correct for single-repo projects, but on a multi-repo project (Hybrid Option C) an unpinned work item means the Task Breakdown gate assignment was missed - silently defaulting routes it into whatever repo happens to be default (often the frontend), landing code in the wrong GitHub repo. A mis-route, not a hard failure, so it would pass unnoticed.</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Backend / Orchestration / Build trigger</t>
+        </is>
+      </c>
+      <c r="E109" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bug</t>
+        </is>
+      </c>
+      <c r="F109" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">backend/orchestration/trigger.py; backend/tests/test_build_trigger_api.py</t>
+        </is>
+      </c>
+      <c r="G109" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P2</t>
+        </is>
+      </c>
+      <c r="H109" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The default-repo fallback predates multi-repo. It was written so a task could be built from the UI without pinning a repo (single-repo projects, proposed items). It didn't distinguish single-repo (safe to default) from multi-repo (must be explicitly assigned).</t>
+        </is>
+      </c>
+      <c r="I109" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FIXED. trigger_build now counts the project's repositories: for a multi-repo project (repo_count &gt; 1) an unpinned work item raises a clear TriggerError telling the user to assign its repo (confirm at the Task Breakdown gate or set the work item's repo) - never silently defaults. Single-repo projects keep the default-repo fallback unchanged. Tests added: multi-repo unpinned -&gt; 400 'multiple repositories'; multi-repo pinned to the non-default repo -&gt; builds into that repo with its base. 7/7 build-trigger tests pass.</t>
+        </is>
+      </c>
+      <c r="J109" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fixed</t>
+        </is>
       </c>
     </row>
     <row r="110" spans="1:1">

--- a/docs/Bugs.xlsx
+++ b/docs/Bugs.xlsx
@@ -136,7 +136,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="449" uniqueCount="228">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="455" uniqueCount="230">
   <si>
     <t>S.No</t>
   </si>
@@ -922,6 +922,12 @@
   </si>
   <si>
     <t>Connet Machine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FIXED (2026-07-14). _resolve_enrollment in backend/orchestration/trigger.py no longer picks purely by recency. It now prefers, in order: (1) the newest ACTIVE enrollment that is ONLINE (last_seen within the 2-minute ONLINE_THRESHOLD from apps/runs/enrollment.py - i.e. a companion is heartbeating/polling with that token right now); (2) the newest that has EVER checked in; (3) the newest overall (nothing connected yet - e.g. the user triggers before starting the companion; the dispatch waits, same as before). Applies to BOTH trigger_phase and trigger_build (they share the helper). Result: a Connect-Machine visit that mints a newer-but-never-connected enrollment can no longer capture a dispatch while the live companion polls 204s. Tests: backend/tests/test_build_trigger_api.py::test_resolve_enrollment_prefers_newest_online_over_newer_dead_one and test_resolve_enrollment_falls_back_seen_then_newest. Revoking stale enrollments is still good hygiene but no longer required for a correct dispatch.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FIXED (2026-07-14). The companion now survives a backend/worker restart instead of silently dying (a docker restart surfaces as a connection error/OSError on the long-poll, not an HTTP status - previously that escaped the serve loop and killed the daemon). Changes in runner/companion/daemon.py: (1) serve() catches connection-level errors from the work-poll and retries forever with capped exponential backoff (poll interval doubling up to 60s), logging 'backend unreachable... reconnecting in Ns' and 'backend reconnected; resuming'; (2) _report() retries a finished phase/build report through a transient outage (~2 min of backoff) so completed work is not lost to a restart at report time; HTTP 4xx/5xx answers still fail immediately. The 30s heartbeat already swallowed its own failures and resumes by itself. Tests: backend/tests/test_companion_daemon.py::test_claim_survives_backend_outage_and_resumes, test_report_retries_through_transient_outage, test_report_gives_up_after_bounded_retries. Operational note: a plain backend/worker restart now needs NO manual companion action; reconnecting with the SAME token only matters if the companion process itself is killed.</t>
   </si>
 </sst>
 </file>
@@ -4990,15 +4996,11 @@
           <t xml:space="preserve">_resolve_enrollment orders enrollments by recency and does not prefer ones that have actually checked in (last_seen recent / within the online window). RC-4 collapses re-enrollments by project but the selection still ignores liveness.</t>
         </is>
       </c>
-      <c r="I85" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Not yet fixed (deferred to avoid a backend restart mid-build). Fix: _resolve_enrollment should prefer the newest enrollment with a recent last_seen (online) and ignore never-checked-in / stale ones; optionally fail-fast or re-point a dispatch whose target enrollment is offline. Interim mitigation: keep a single fresh enrollment (wipe stale ones before triggering).</t>
-        </is>
-      </c>
-      <c r="J85" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Open</t>
-        </is>
+      <c r="I85" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="J85" s="2" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="86" spans="1:10" ht="409.6">
@@ -6040,15 +6042,11 @@
           <t xml:space="preserve">The companion's heartbeat/work-poll loop doesn't robustly survive the backend going away and returning (transient connection loss on restart) - it stops rather than retrying until reconnected.</t>
         </is>
       </c>
-      <c r="I106" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Open - P2, later. Make the companion resilient to a transient backend outage: retry/reconnect the heartbeat + work-poll with backoff instead of stopping; show a clear reconnecting state. Interim workaround: after any backend/worker restart, manually reconnect the companion with the SAME token (a new token would orphan an already-dispatched run - row 84).</t>
-        </is>
-      </c>
-      <c r="J106" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Open</t>
-        </is>
+      <c r="I106" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="J106" s="2" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="107" spans="1:10" ht="409.6">

--- a/docs/Bugs.xlsx
+++ b/docs/Bugs.xlsx
@@ -6199,14 +6199,104 @@
         </is>
       </c>
     </row>
-    <row r="110" spans="1:1">
+    <row r="110" spans="1:10" ht="380">
       <c r="A110" s="2">
         <v>109</v>
       </c>
-    </row>
-    <row r="111" spans="1:1">
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Repo-assignment review panel resurfaces on non-Task-Breakdown gates (the merge gate, and any later phase gate) - it must render ONLY on the Task Breakdown gate</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Live on SpendLog-1: the implementation MERGE gate for TASK-001 rendered the Task Breakdown repo-assignment review panel ('31 tasks, backend 14 / frontend 15, 2 need review - confirm or change the repo'). Proposed sibling tasks keep their planner repo_assignment long after Task Breakdown, so the panel wrongly reappears on the merge gate - and would also reappear on a later testing/security/deployment phase gate opened while tasks are still proposed.</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Frontend / Gates / Multi-repo (Option C)</t>
+        </is>
+      </c>
+      <c r="E110" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bug (regression)</t>
+        </is>
+      </c>
+      <c r="F110" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">frontend/src/features/lifecycle/Gates.tsx (showReview); backend/api/serializers.py (ApprovalSerializer); frontend/src/types.ts (Approval); follow-up to S.No 106</t>
+        </is>
+      </c>
+      <c r="G110" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P1</t>
+        </is>
+      </c>
+      <c r="H110" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">S.No 106 made the review full-width and wired it into Gates.tsx, but the render condition (showReview = multiRepo &amp;&amp; assignmentItems.length&gt;0) never checked WHICH gate is selected. All planning gates share gate_type 'phase_gate' (only the build gate is 'merge_gate'), so gate_type alone is not a safe discriminator - a testing/security/deployment phase gate would also resurface it.</t>
+        </is>
+      </c>
+      <c r="I110" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FIXED (2026-07-14). The Approval API now exposes `phase` (the gate run's agent key, e.g. 06_task_breakdown) via ApprovalSerializer; the frontend Approval type carries it; Gates.tsx gates the panel on isTaskBreakdownGate = (selected?.phase === '06_task_breakdown'), so showReview = multiRepo &amp;&amp; isTaskBreakdownGate &amp;&amp; assignmentItems.length&gt;0. The review now renders ONLY on the Task Breakdown gate - never on the merge gate or any future phase gate. Tests: backend test_frontend_integration approval-shape + new phase-field test (3 pass); frontend tsc clean; RepoAssignmentReview.test.tsx (3 pass). To view: backend uvicorn --reload picks up serializers.py automatically; restart ONLY the frontend container (bind-mounted ./frontend) so the companion is not dropped.</t>
+        </is>
+      </c>
+      <c r="J110" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fixed</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" spans="1:10" ht="380">
       <c r="A111" s="2">
         <v>110</v>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08 code review poll times out (480s) and a late/absent review report is not reconciled - the merge gate opens via the fail-safe with ZERO findings even though the review never completed</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Live on SpendLog-1 TASK-001: the 08 review task was dispatched and CLAIMED by the companion (06:07:33 UTC) but no verdict was ever posted within the 480s poll window; review.timeout fired at 06:15:52 and the merge gate opened at 06:15:54 with 0 findings and no code_review artifact. poll_review_body treats a timeout as 'no findings' so the build never hangs (by design) - but the reviewer then approves with NO automated review having run. A review report arriving after the timeout (record_review_report) writes review_body once the poll has already returned, so it is orphaned - never parsed into findings. Parallels S.No 89 (a late report cannot reconcile a closed step).</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Orchestration / Code review (08) / Build pipeline</t>
+        </is>
+      </c>
+      <c r="E111" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bug</t>
+        </is>
+      </c>
+      <c r="F111" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">backend/orchestration/review_provider.py (CompanionReviewProvider timeout=480.0 / poll_review_body / record_review_report); backend/orchestration/build_workflow.py (run_code_review loop); related S.No 89</t>
+        </is>
+      </c>
+      <c r="G111" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P1</t>
+        </is>
+      </c>
+      <c r="H111" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The review poll timeout (480s / 8 min) is shorter than a realistic FIRST companion review (cold engine start + context compaction can add ~7 min). When it trips, timeout is treated as zero blocking findings and the merge gate opens; a review report arriving after the timeout is recorded but never re-parsed, so its findings are silently lost.</t>
+        </is>
+      </c>
+      <c r="I111" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open - team to address. Options: (1) raise the review poll timeout and/or make it configurable per phase; (2) reconcile a late review.reported into findings (re-evaluate/block the merge gate until the review actually reports) - the same reconcile gap as S.No 89; (3) surface 'automated review did not complete' on the merge gate so a reviewer knows the review is absent, not clean. Interim: treat this run's merge gate as human-review-only, and check the companion console to confirm whether 08 is still running or errored.</t>
+        </is>
+      </c>
+      <c r="J111" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
       </c>
     </row>
     <row r="112" spans="1:1">

--- a/docs/Bugs.xlsx
+++ b/docs/Bugs.xlsx
@@ -6290,18 +6290,63 @@
       </c>
       <c r="I111" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Open - team to address. Options: (1) raise the review poll timeout and/or make it configurable per phase; (2) reconcile a late review.reported into findings (re-evaluate/block the merge gate until the review actually reports) - the same reconcile gap as S.No 89; (3) surface 'automated review did not complete' on the merge gate so a reviewer knows the review is absent, not clean. Interim: treat this run's merge gate as human-review-only, and check the companion console to confirm whether 08 is still running or errored.</t>
+          <t xml:space="preserve">FIXED (2026-07-14, committed a582737). Three-part fix in the review path: (1) BuildInput.review_timeout_seconds is now per-run configurable with a realistic default of 1800s (was a hard-coded 480s that was shorter than a first cold-companion review); (2) poll_review_body does one final grace read on timeout, so a verdict that lands moments after the last poll tick still drives the 07&lt;-&gt;08 remediation loop instead of being orphaned in run.outputs while the merge gate opens blind; (3) build_workflow.py sets the run_code_review activity start_to_close = review_timeout_seconds + 600s, so the Temporal activity timeout always exceeds the internal poll window (otherwise Temporal would kill and retry the activity mid-review, re-dispatching it). The companion provider reads getattr(inp,'review_timeout_seconds') and falls back to its own default, so an older backend that predates the field is safe. Tests: test_review_dispatch (grace-read + per-run-timeout), ruff clean. This is the review-side analog of S.No 89 (phase-side late-report reconcile, still open for the co-dev team).</t>
         </is>
       </c>
       <c r="J111" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="112" spans="1:1">
+          <t xml:space="preserve">Fixed</t>
+        </is>
+      </c>
+    </row>
+    <row r="112" spans="1:10" ht="380">
       <c r="A112" s="2">
         <v>111</v>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Claim lease vs review window: a phase that legitimately runs longer than the 15-min work-claim lease (e.g. a code review now allowed up to 30 min) is re-claimed mid-flight from a LIVE, heartbeating companion -&gt; duplicate/empty artifacts + a failed re-review, and the merge gate opens blind</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Surfaced right after the S.No 110 fix, on SpendLog-1 TASK-001 (run e2c57de8). The 08 review legitimately took ~19 min (S.No 110 raised the review poll window to 30 min), exceeding the 15-min CLAIM_LEASE. The still-running review's claim went stale so a later /api/runner/work/ poll RE-CLAIMED it (phase.reclaimed x2) even though the companion was alive and heartbeating (last_seen fresh). The churn produced (a) a duplicate EMPTY 'assumption' artifact (external_ref null, no s3_key -&gt; would not preview) and (b) a FAILED final review report (review_status='failed', empty body) -&gt; 0 findings -&gt; the merge gate opened without a valid review.</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Companion / Runner / Claim lease vs review window</t>
+        </is>
+      </c>
+      <c r="E112" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bug (regression from S.No 110)</t>
+        </is>
+      </c>
+      <c r="F112" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">backend/api/runner_views.py (CLAIM_LEASE, RunnerWorkClaimView re-claim, RunnerHeartbeatView, _renew_claims_for); backend/orchestration/review_provider.py (review_timeout_seconds=1800); related S.No 110, 89, RC-2/RC-3</t>
+        </is>
+      </c>
+      <c r="G112" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P1</t>
+        </is>
+      </c>
+      <c r="H112" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The 15-min claim lease is meant to detect a DEAD companion, but it keyed off 'time since the claim was stamped', not liveness. S.No 110 legitimately extended the review to run up to 30 min &gt; the 15-min lease, so a live companion's claim expired mid-review and the run was re-claimed. The heartbeat kept last_seen fresh (liveness) but did NOT refresh claimed_at, so the lease expired despite the companion being provably alive - the lease comment even says it 'MUST exceed the longest real phase'.</t>
+        </is>
+      </c>
+      <c r="I112" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FIXED (2026-07-14). The heartbeat now renews claimed_at for the companion's in-flight (PENDING/RUNNING, still 'claimed') runs (_renew_claims_for in runner_views.py, called by RunnerHeartbeatView; returns claims_renewed). So a heartbeating companion's claim never goes stale no matter how long the phase runs, while a truly dead companion still gets re-claimed ~15 min after its LAST heartbeat (dead-companion recovery preserved). Only in-flight claimed runs are touched - a reported/gated run is never revived. This ties the lease to LIVENESS, not task duration, so it is robust for any long phase, not just reviews. Tests: test_phase_dispatch::test_heartbeat_renews_claim_so_a_long_live_phase_is_not_reclaimed + test_heartbeat_does_not_renew_a_reported_claim (19 pass, ruff clean). Backend auto-reloads runner_views.py (uvicorn --reload) so no container restart / no companion drop. NOTE: the compromised run e2c57de8 must be disposed + re-run (its gate opened on a failed review).</t>
+        </is>
+      </c>
+      <c r="J112" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fixed</t>
+        </is>
       </c>
     </row>
     <row r="113" spans="1:1">

--- a/docs/Bugs.xlsx
+++ b/docs/Bugs.xlsx
@@ -6349,14 +6349,104 @@
         </is>
       </c>
     </row>
-    <row r="113" spans="1:1">
+    <row r="113" spans="1:10" ht="380">
       <c r="A113" s="2">
         <v>112</v>
       </c>
-    </row>
-    <row r="114" spans="1:1">
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Shared Temporal queue + per-worker GitHub token: with two dev workers on the shared 'sdlc-planning' queue, a build's open_build_pr activity can run on the OTHER dev's worker, which uses THAT worker's server .env GITHUB_TOKEN -&gt; 404 on the target repo -&gt; build marked failed even though the code built + pushed fine</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Observed on SpendLog-1 (multi-user shared-AWS): TASK-001 build (run 5bc08ea2, RAGUWING369/SpendLogTest-1-backend) failed at 'pr/gate setup failed'. The worker logs showed the 404 was for a DIFFERENT tenant's repo (Tarun51/medslot-single-repo, run 3187519e) - proving the two dev workers cross-executed each other's build activities. Each worker authenticates GitHub from its own .env token (settings.GITHUB_TOKEN) scoped to that dev's repos, so a build landing on the wrong worker 404s. The companion build itself succeeded (report ok, branch pushed); only the platform-side PR step failed.</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Integrations / Code host / Multi-user / Shared Temporal</t>
+        </is>
+      </c>
+      <c r="E113" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bug</t>
+        </is>
+      </c>
+      <c r="F113" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">backend/integrations/registry.py (_build_github); backend/integrations/github/config.py (GithubConfig.from_connection); deploy/shared-aws (two workers, one queue); related S.No 74</t>
+        </is>
+      </c>
+      <c r="G113" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P1</t>
+        </is>
+      </c>
+      <c r="H113" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The codehost authenticated from the server .env (settings.GITHUB_TOKEN), NOT the tenant's own stored credential. On a shared task queue an activity runs on whichever worker is free, so the wrong dev's token was used. The per-tenant token was already stored in the shared DB (IntegrationConnection.secret_encrypted) but was never read (this is S.No 74 for the codehost).</t>
+        </is>
+      </c>
+      <c r="I113" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FIXED (2026-07-14, Phase A). _build_github now builds the config via GithubConfig.from_connection(conn), which decrypts the tenant's own IntegrationConnection.secret_encrypted (the access_token the connect form stored) and uses it; falls back to settings.GITHUB_TOKEN only when no per-tenant secret exists (local/CI/back-compat). Because the credential lives in the SHARED DB and travels with the tenant, ANY worker that runs a build for that tenant uses the correct token - the cross-worker mismatch is now structurally impossible, so multiple devs can run workflows concurrently without stopping each other's worker. Core logic verified (per-tenant token used / settings fallback / two-tenant isolation all pass) + 3 new tests in test_capability_registry + ruff clean; full DB-backed test run pending local Docker (was down at fix time). Requires the tenant to have connected its Code host with a token - SpendLog-1 already has one stored (has_secret=True).</t>
+        </is>
+      </c>
+      <c r="J113" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fixed</t>
+        </is>
+      </c>
+    </row>
+    <row r="114" spans="1:10" ht="380">
       <c r="A114" s="2">
         <v>113</v>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Phase B (extend S.No 74): wire per-tenant credentials into the remaining connectors (Atlassian Confluence/Jira, Figma, Xray) so planning-phase system-of-record pushes also use the tenant's stored token on any worker, not the server .env</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Phase A (S.No 112) fixed the codehost (GitHub) to use per-tenant credentials from the shared DB. The other connectors still authenticate from the server .env (AtlassianConfig / FigmaConfig / XrayConfig .from_settings()), so on a shared multi-worker setup a planning-phase SoR push (publish to Confluence/Jira, Figma read, Xray import) could use the wrong tenant's creds or fail - the same class of bug as S.No 112, for the non-codehost capabilities.</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Integrations / Connectors / Multi-user</t>
+        </is>
+      </c>
+      <c r="E114" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Enhancement (follow-up)</t>
+        </is>
+      </c>
+      <c r="F114" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">backend/integrations/registry.py (_build_confluence/_build_jira/_build_figma/_build_xray + _atlassian_config); backend/apps/integrations/catalog.py; related S.No 74, S.No 112</t>
+        </is>
+      </c>
+      <c r="G114" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P2</t>
+        </is>
+      </c>
+      <c r="H114" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Same root cause as S.No 112 (connectors authenticate from the server .env, not per-tenant DB creds). Phase A did only the codehost because it was the build-workflow blocker. The Atlassian connectors also need email + site_url, which are NOT in the connect form's catalog yet, so this is a larger change (catalog + form fields + config wiring) - hence deferred.</t>
+        </is>
+      </c>
+      <c r="I114" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open - follow-up to Phase A. Plan: (1) add email/site_url (or equivalent) fields to the Atlassian vendors in catalog.py + the connect form; (2) change _atlassian_config to take the conn and decrypt api_token + read email/site_url from scopes; (3) same decrypt-and-use for Figma access_token and Xray client_id/client_secret; (4) keep the settings fallback for back-compat; (5) tests per connector + a two-tenant isolation test. Not blocking now - SpendLog-1 is sor=internal with no non-codehost connections configured.</t>
+        </is>
+      </c>
+      <c r="J114" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
       </c>
     </row>
     <row r="115" spans="1:1">

--- a/docs/Bugs.xlsx
+++ b/docs/Bugs.xlsx
@@ -6449,9 +6449,54 @@
         </is>
       </c>
     </row>
-    <row r="115" spans="1:1">
+    <row r="115" spans="1:10" ht="380">
       <c r="A115" s="2">
         <v>114</v>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Blocking code review silently 'passes' (fail-OPEN): the 07&lt;-&gt;08 remediation loop reads blocking findings ONLY from the json verdict block in the 08 agent's FINAL message. When the agent's final message is prose (its machine-readable json block missing / not last / delivered via a separate event) the platform parses 0 findings, counts 0 blocking, SKIPS remediation and opens the merge gate on an unreviewed downgrade.</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Observed live on SpendLog-1 (multi-repo), run 8ab6f89a, PR RAGUWING369/SpendLogTest-1-backend#3. The 08 review ran fine and produced a real verdict: review.completed logged status=CHANGES_REQUIRED with 5 blocking_findings (REM-C1 + REM-W1..W4, incl. PR-&gt;main-not-develop, /docs live in prod, no global exception handler, unbounded SECRET_KEY). But the review_body the companion posted back was only a 1,723-char prose executive summary with ZERO ```json blocks, so parse_findings returned [] -&gt; build.reviewed logged {blocking:0, findings:0} -&gt; gate.opened (merge) with no remediation loop. Distinct from S.No 110/111 (those were review-window/claim-lease timing); here the review reported in-window, claim_count stayed 1 - the defect is verdict serialization + a fail-OPEN default.</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Orchestration / Code review / 07&lt;-&gt;08 remediation loop</t>
+        </is>
+      </c>
+      <c r="E115" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bug</t>
+        </is>
+      </c>
+      <c r="F115" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">backend/orchestration/review_provider.py (parse_findings/_extract_verdict/_looks_blocking/parse_and_guard, ReviewContractError); backend/orchestration/build_activities.py (run_code_review_core); backend/orchestration/build_workflow.py (run_code_review activity -&gt; mark_build_failed on ActivityError); agents/08_code_review/agent.md (Output contract); runner/companion/daemon.py (posts result text as review_body); related S.No 110</t>
+        </is>
+      </c>
+      <c r="G115" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P1</t>
+        </is>
+      </c>
+      <c r="H115" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Two compounding defects. (1) Fragile contract: the platform sources blocking findings from the agent's free-text final message (daemon posts outputs.result as review_body; parse_findings scans only that for the LAST ```json block). Any run where the agent puts prose last, or emits the verdict via a tool/event, silently breaks the parse. (2) Fail-OPEN default: when the parse yields nothing the loop treats it as 'clean' (open_blocking==0) and opens the merge gate - the WRONG direction (same lesson as S.No 110, opposite failure).</t>
+        </is>
+      </c>
+      <c r="I115" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FIXED (2026-07-14). Three-layer fix + tests. (Fix 1 - agent) agents/08_code_review/agent.md Output section hardened: the FINAL message MUST end with exactly one fenced json verdict block and NOTHING after it; forbids delivering the verdict only via a tool/event or appending a prose summary; both the code_review artifact body AND the final-message json are required. (Fix 2 - robust parse) _extract_verdict scans ALL json blocks and takes the last that parses AND looks like a verdict (has status/findings), tolerant of illustrative json + trailing prose. (Fix 3 - FAIL CLOSED) new parse_and_guard: if the body signals blocking (a REM-C/REM-W id or CHANGES_REQUIRED) but 0 blocking findings parse, it logs review.parse_mismatch and raises ReviewContractError; run_code_review retries (cap 3) then BuildWorkflow catches ActivityError -&gt; mark_build_failed, so the merge gate is NEVER opened on an unreviewed downgrade. Empty body (review timeout) keeps returning [] (human gate still applies, S.No 110). Tests: 7 new in test_review_dispatch (robust parse, clean pass-through, empty-body, fail-closed + event, provider-level fail-closed) + test_agents_migration (08 states the final-message json contract); all pass, ruff clean. Both companion + server providers guarded. Run 8ab6f89a disposed + PR #3 closed; team re-runs the phase.</t>
+        </is>
+      </c>
+      <c r="J115" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fixed</t>
+        </is>
       </c>
     </row>
     <row r="116" spans="1:1">

--- a/docs/Bugs.xlsx
+++ b/docs/Bugs.xlsx
@@ -6499,9 +6499,54 @@
         </is>
       </c>
     </row>
-    <row r="116" spans="1:1">
+    <row r="116" spans="1:10" ht="380">
       <c r="A116" s="2">
         <v>115</v>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">07&lt;-&gt;08 remediation loop hangs forever: when the code review returns blocking findings, dispatch_remediation re-runs the implementation agent (07) on the same branch to fix them. But the remediation dispatch never re-armed the companion claim block, so the companion had nothing to pull -&gt; the 07 agent never re-ran -&gt; no second build report -&gt; the BuildWorkflow waited on build_reported until timeout -&gt; mark_takeover. The remediation cycle could never complete.</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Found by studying live cloud Temporal history (13.203.56.29:7233) for two devs' concurrent build runs. build-run-fe891eb9 sequence: dispatch_build -&gt; open_build_pr -&gt; run_code_review -&gt; dispatch_remediation -&gt; mark_takeover, with EXACTLY ONE build_reported signal (the initial build only). build-run-8f9dec1d (other tenant) identical, still stuck waiting after dispatch_remediation. Crucially 8f9dec1d ran on a SINGLE worker yet is stuck identically to the two-worker fe891eb9 - disproving the team's 'workers cross-pick activities' theory. Temporal replays workflow state consistently regardless of which worker runs each activity; multi-worker execution is normal and harmless. The two devs saw two faces of the same broken loop: Dev A stuck/takeover (this bug); Dev B gate opened with no remediation (S.No 114 fail-open, fixed same day).</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Orchestration / Build / 07&lt;-&gt;08 remediation loop / Companion dispatch</t>
+        </is>
+      </c>
+      <c r="E116" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bug</t>
+        </is>
+      </c>
+      <c r="F116" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">backend/orchestration/build_activities.py (dispatch_remediation_core + new _render_remediation_section); compares dispatch_build_core; backend/api/runner_views.py (RunnerWorkClaimView claim filter status in pending/claimed); runner/companion/daemon.py (poll-&gt;claim-&gt;run-&gt;report loop, no self-loop); related S.No 114</t>
+        </is>
+      </c>
+      <c r="G116" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P1</t>
+        </is>
+      </c>
+      <c r="H116" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dispatch_remediation_core wrote only inputs['remediation'] + status=RUNNING; it never set inputs['dispatch'] to a pending BUILD claim block (left as the review's kind=review/status=reported, which the claim query ignores) and never rebuilt build_task with the remediation brief. The companion daemon is a strict poll-&gt;claim-&gt;run-&gt;report loop with no remediation self-loop, so /api/runner/work/ returned 204 forever. The 07&lt;-&gt;08 companion handoff for remediation was simply never wired. It escaped tests because test_review_dispatch only exercised run_code_review_core opening child WorkItems, never the dispatch-&gt;claim-&gt;report cycle. Blocker surfaced only after S.No 114 (fail-open) was fixed - fixing 114 makes a blocking review correctly ENTER the remediation branch, which then hit 115.</t>
+        </is>
+      </c>
+      <c r="I116" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FIXED (2026-07-15). dispatch_remediation_core now mirrors dispatch_build_core's companion handoff: recomposes the 07 manifest via compose_manifest_core and appends a '# Remediation Items' section rendering the open REM brief (rem/severity/title/file:line) - same idea as the reviewer's PR-diff section; rebuilds the full build_task payload (manifest+agent_body+model+repo/base/work_item title/type, remediation:True); and sets inputs['dispatch']={kind:build, enrollment_id:inp.enrollment_id, status:pending} so the companion claims it via /api/runner/work/ and re-runs 07 on the SAME branch. open_build_pr stays outside the loop (idempotent) so the existing PR just gets new commits. Companion side needed NO change: worktree path is deterministic per WI, teardown after each build, provision_worktree re-attaches the existing feature branch, push is a fast-forward. No workflow change: build_workflow already dispatches then waits for build_reported. Tests: 2 new in test_review_dispatch (dispatch arms pending build claim + REM brief in manifest; /api/runner/work/ returns the remediation build) - 19 pass; test_build_activities 11 pass (no regression); ruff clean. Verification watches for a SECOND build_reported signal in the workflow history (absent in every run to date) = proof the handoff works.</t>
+        </is>
+      </c>
+      <c r="J116" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fixed</t>
+        </is>
       </c>
     </row>
     <row r="117" spans="1:1">

--- a/docs/Bugs.xlsx
+++ b/docs/Bugs.xlsx
@@ -6549,9 +6549,54 @@
         </is>
       </c>
     </row>
-    <row r="117" spans="1:1">
+    <row r="117" spans="1:10" ht="380">
       <c r="A117" s="2">
         <v>116</v>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Code review flags PR-size (and other Step-1 hygiene checks) as a blocking CRITICAL, driving an UNWINNABLE 07&lt;-&gt;08 remediation loop: the 08 agent's Step-1 PR Hygiene gate treats any failing check (PR size &gt;400 lines, commit-message format, branch name, PR description, linear history) as a blocking REM-C. But the platform re-runs the IMPLEMENTATION agent on the SAME branch for every blocking finding, and it cannot split a PR, rename a branch, rewrite the platform-generated commit message, or otherwise fix a hygiene issue in code -&gt; the finding recurs every cycle -&gt; the loop churns until max_remediation_cycles (3) exhausts -&gt; the build FAILS, even though the code is fine.</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Observed live on SpendLog-1 build run 1377dee3 (TASK-001 .venv/FastAPI scaffold). Review cycle 1 = 4 blocking (REM-C1 PR-size ~590 lines, REM-C2 CORS, REM-W1 no-op test, REM-W2 python-jose). The 3 real code defects were fixed across cycles (done); REM-C1 'PR size ~590 lines exceeds 400-line threshold' stayed blocking every cycle (blocking count stuck at 1: cycle1=4 -&gt; cycle2=1 -&gt; cycle3=1) because a legitimate bootstrap scaffold cannot be shrunk below 400 lines. Heading to 'remediation cycles exhausted' at cycle 4. The 08 agent even acknowledges (run 8ab6f89a) PR-size for a bootstrap scaffold is 'justified ... document as a permitted exception rather than triggering a code remediation loop' - yet still emitted it as blocking. Confirmed S.No 114 + 115 fixes worked (2-3 build_reported, loop converged 4-&gt;1); this is a DISTINCT design bug the working loop exposed.</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Agents / 08 Code Review / Remediation loop classification</t>
+        </is>
+      </c>
+      <c r="E117" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bug</t>
+        </is>
+      </c>
+      <c r="F117" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">agents/08_code_review/agent.md (Step 1 PR Hygiene gate, lines ~62-76: 'Any check that fails -&gt; CRITICAL'); backend/orchestration/build_activities.py (_BLOCKING treats REM-C/REM-W as blocking); related S.No 114, 115</t>
+        </is>
+      </c>
+      <c r="G117" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P1</t>
+        </is>
+      </c>
+      <c r="H117" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Step 1 hygiene checks are either platform-OWNED (D2: the platform generates the commit message, branch name, PR description, and keeps history linear - the 07 agent never touches git) or NON-CODE (PR size). None can be remediated by re-running 07 on the same branch, so classifying them as blocking REM-C/REM-W guarantees an unwinnable loop. PR size is inherently a human/process judgment (split the PR) or a justified exception (scaffold/migration), not a code defect - it belongs at the human merge gate, not in the automated loop.</t>
+        </is>
+      </c>
+      <c r="I117" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FIXED (2026-07-15). agents/08_code_review/agent.md Step 1 reclassified: a failing hygiene check is now a NON-BLOCKING Suggestion (REM-S) for the human merge-gate reviewer, never a blocking REM-C/REM-W. The body now states the rationale (platform-owned or non-code -&gt; the 07 loop cannot fix them -&gt; blocking would create an unwinnable loop that exhausts the cap) and directs a genuinely un-reviewable PR to be RETURNED BY THE HUMAN reviewer at the gate, not the automated loop; PR-size overage is still reported (with generated/lock/migration exemptions + justified-or-not note) but as a Suggestion. Framework note aligned. Tests: test_agents_migration.test_code_review_hygiene_findings_are_non_blocking (asserts non-blocking-suggestion classification + rationale present + old 'any check that fails -&gt; CRITICAL' gone) - 2 pass. Agent body is file-loaded (_load_agent_body) so the fix is live on the next dispatch, no re-seed/worker restart. Run 1377dee3 terminated + PR#4 closed + branch deleted + DB reset (WI proposed) for a fresh re-run.</t>
+        </is>
+      </c>
+      <c r="J117" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fixed</t>
+        </is>
       </c>
     </row>
     <row r="118" spans="1:1">

--- a/docs/Bugs.xlsx
+++ b/docs/Bugs.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30224"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30306"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="78" documentId="11_14FDEAE3397E350B81F2A24CBED9C52169691D91" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{456516D8-70B7-4682-A3C6-67807BA1CC65}"/>
+  <xr:revisionPtr revIDLastSave="102" documentId="11_14FDEAE3397E350B81F2A24CBED9C52169691D91" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C231EF7A-42E9-490A-B4B0-64F9F645D887}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
   <metadataTypes count="1">
     <metadataType name="XLRICHVALUE" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1"/>
   </metadataTypes>
-  <futureMetadata name="XLRICHVALUE" count="9">
+  <futureMetadata name="XLRICHVALUE" count="13">
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
@@ -102,8 +102,36 @@
         </ext>
       </extLst>
     </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="9"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="10"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="11"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="12"/>
+        </ext>
+      </extLst>
+    </bk>
   </futureMetadata>
-  <valueMetadata count="9">
+  <valueMetadata count="13">
     <bk>
       <rc t="1" v="0"/>
     </bk>
@@ -131,12 +159,24 @@
     <bk>
       <rc t="1" v="8"/>
     </bk>
+    <bk>
+      <rc t="1" v="9"/>
+    </bk>
+    <bk>
+      <rc t="1" v="10"/>
+    </bk>
+    <bk>
+      <rc t="1" v="11"/>
+    </bk>
+    <bk>
+      <rc t="1" v="12"/>
+    </bk>
   </valueMetadata>
 </metadata>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="455" uniqueCount="230">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="966" uniqueCount="575">
   <si>
     <t>S.No</t>
   </si>
@@ -924,10 +964,1068 @@
     <t>Connet Machine</t>
   </si>
   <si>
-    <t xml:space="preserve">FIXED (2026-07-14). _resolve_enrollment in backend/orchestration/trigger.py no longer picks purely by recency. It now prefers, in order: (1) the newest ACTIVE enrollment that is ONLINE (last_seen within the 2-minute ONLINE_THRESHOLD from apps/runs/enrollment.py - i.e. a companion is heartbeating/polling with that token right now); (2) the newest that has EVER checked in; (3) the newest overall (nothing connected yet - e.g. the user triggers before starting the companion; the dispatch waits, same as before). Applies to BOTH trigger_phase and trigger_build (they share the helper). Result: a Connect-Machine visit that mints a newer-but-never-connected enrollment can no longer capture a dispatch while the live companion polls 204s. Tests: backend/tests/test_build_trigger_api.py::test_resolve_enrollment_prefers_newest_online_over_newer_dead_one and test_resolve_enrollment_falls_back_seen_then_newest. Revoking stale enrollments is still good hygiene but no longer required for a correct dispatch.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FIXED (2026-07-14). The companion now survives a backend/worker restart instead of silently dying (a docker restart surfaces as a connection error/OSError on the long-poll, not an HTTP status - previously that escaped the serve loop and killed the daemon). Changes in runner/companion/daemon.py: (1) serve() catches connection-level errors from the work-poll and retries forever with capped exponential backoff (poll interval doubling up to 60s), logging 'backend unreachable... reconnecting in Ns' and 'backend reconnected; resuming'; (2) _report() retries a finished phase/build report through a transient outage (~2 min of backoff) so completed work is not lost to a restart at report time; HTTP 4xx/5xx answers still fail immediately. The 30s heartbeat already swallowed its own failures and resumes by itself. Tests: backend/tests/test_companion_daemon.py::test_claim_survives_backend_outage_and_resumes, test_report_retries_through_transient_outage, test_report_gives_up_after_bounded_retries. Operational note: a plain backend/worker restart now needs NO manual companion action; reconnecting with the SAME token only matters if the companion process itself is killed.</t>
+    <t>Every 'Companion Offline' indicator (global pill, Connect Machine page, Phases &amp; Runs) is driven by ONE derived flag: enrollment.online = (now - last_seen) &lt;= 2 min (apps/runs/enrollment.py). last_seen is refreshed only when the companion calls an authenticated endpoint. Four defects made it go stale / stuck:
+RC-1 (PRIMARY): The companion daemon CRASHED after the first phase. The old assert_subscription_billing() halted the daemon whenever a phase reported a non-zero cost. Current Claude Code reports a computed subscription-equivalent cost (~$1) even on a Max subscription (which is NOT billed per token), so the guard false-positived and killed the daemon right after Ideation reported. A dead daemon stops refreshing last_seen -&gt; UI shows 'Offline / daemon stopped' within 2 min. It ALSO explains 'Requirements runs but never produces artifacts/gate': after the crash no daemon was alive to run the next phase (or it claimed then died), leaving the run stuck 'running'/'claimed' with no report.
+RC-2: Heartbeat starvation. The serve loop is single-threaded (claim -&gt; run_task blocks for the WHOLE phase -&gt; report). While a phase runs the loop never re-polls, so last_seen only refreshes if the agent happens to call a platform-state tool. Any phase quiet for &gt;2 min flips the companion to a FALSE 'Offline' mid-run and disables triggers, though it is healthy and busy.
+RC-3: No re-queue on daemon death. Claiming atomically flips dispatch pending-&gt;claimed with no lease. If the daemon dies before reporting, the run is stranded 'claimed'/'running' forever - no other daemon re-claims it (poll filters status=pending) - no artifacts, no gate, no recovery.
+RC-4: Misleading UI. Offline copy always said 'daemon stopped' with a HARDCODED 'last seen 5m ago' (ConnectMachine.tsx), and label-less re-enrollments each showed as a separate phantom machine card.</t>
+  </si>
+  <si>
+    <t>RC-1 (shipped): removed the assert_subscription_billing halt in runner/companion/daemon.py; ensure_local_engine_auth (env + ~/.claude.json + OAuth checks) is now the SOLE subscription-only guard. Engine cost is reported for reference only, never used as an API-key signal.
+RC-2: added POST /api/runner/heartbeat/ (RunnerHeartbeatView) + a background heartbeat thread in the daemon (CompanionDaemon._run_heartbeat_loop; --heartbeat-interval, default 30s) that refreshes last_seen every 30s independent of run_task, so the companion stays 'online' throughout long phases.
+RC-3: work claims are now a LEASE. RunnerWorkClaimView stamps claimed_at + claim_count on claim; a poll re-claims any run left 'claimed' past CLAIM_LEASE (15 min, &gt; longest phase) with no report, logging phase.reclaimed - so a dead companion's run recovers instead of stranding.
+RC-4: ConnectMachine.tsx now shows the REAL relative last_seen (sinceLabel) and reworded copy ('not reachable - reconnects if mid-phase; else restart'); list_developer_enrollments collapses label-less re-enrollments for the same project into ONE card (represented by the most-recently-seen enrollment) instead of N phantoms.
+TESTS: backend 101 passed / 3 skipped (new: heartbeat endpoint, stale-claim reclaim, enrollment dedup); daemon unit 16 passed (heartbeat posts + failure-safe); frontend 209 passed; tsc clean. Verified in the backend container against Postgres.</t>
+  </si>
+  <si>
+    <t>Requirements phase ran a second time by itself — a duplicate 'v2' draft of the same artifact appeared and the companion went offline.</t>
+  </si>
+  <si>
+    <t>Found during live testing of the Bug #61 (S.No 61) fix. The Requirements phase completed normally: its artifact (version 1) was previewed, approved at the gate, and the phase showed as done. A few minutes later, without anyone triggering it, the SAME Requirements artifact was generated again as a 'version 2' draft on the Artifacts &amp; Traceability page, and the companion daemon then crashed and showed offline. The approved version 1 was never affected — the only impact was one spurious duplicate draft and the daemon stopping.</t>
+  </si>
+  <si>
+    <t>Companion Runner (Phases &amp; Runs)</t>
+  </si>
+  <si>
+    <t>Bug — regression from the Bug #61 fix</t>
+  </si>
+  <si>
+    <t>Regression introduced by the Bug #61 (S.No 61) fix, specifically its RC-3 'claim-lease' auto-recovery. Same run: Requirements run 607d0245; the duplicate was the requirements version-2 draft.</t>
+  </si>
+  <si>
+    <t>The Bug #61 fix added a 'claim lease' safety net: if a companion dies in the middle of a phase without reporting, another poll re-claims the run after 15 minutes so it is not stuck forever. This had a timing race.
+The Requirements phase ran about 17 minutes — longer than the 15-minute lease. When the companion finished and sent its report, the separate step that marks the run as 'reported' happened a moment later (asynchronously, inside the workflow). In that brief gap the run still looked 'claimed', and because the claim was now older than 15 minutes, the companion's very next poll judged it 'stale' and re-claimed its OWN just-finished run — running Requirements a second time and creating the version-2 draft.
+That second run then reported to a workflow that had already completed, which returned a server error the daemon treated as fatal — so the daemon crashed and went offline.</t>
+  </si>
+  <si>
+    <t>Three-part hardening (all shipped, tested, and deployed):
+1) The report step now marks the run 'reported' immediately (synchronously) the moment the companion reports, so the very next poll can never still see it as 'claimed'. This closes the re-run race no matter how long the phase ran.
+2) The auto-recovery re-claim now only applies to runs that are still genuinely running — never one that already reached a gate or completed.
+3) The daemon no longer crashes on a late or duplicate report: the backend responds gracefully (not a server error) when a report arrives after its workflow has already finished, and the daemon logs the failed report and keeps running instead of stopping.
+Added automated regression tests for all three. Confirmed behavior for the team: for a normal long phase (e.g. a 30-minute UX Design or Implementation run) on a single companion, no re-claim ever happens — a busy companion is not polling for work, and on finishing it marks the run 'reported' before its next poll. A re-claim triggers ONLY when a companion genuinely dies before reporting. The spurious version-2 draft was removed; only the approved version 1 remains.
+Files: orchestration/phase_report.py, api/runner_views.py, runner/companion/daemon.py. Tests: daemon unit 18 passed; backend suite 134 passed / 2 skipped.</t>
+  </si>
+  <si>
+    <t>Planning-phase agent runs with more tools than it should — it can spawn subagents and use Read/Bash/Glob, which leads to slow, non-deterministic runs that register no artifacts (and gives the agent unintended access to the local machine).</t>
+  </si>
+  <si>
+    <t>Seen while re-running the Requirements phase on a work item during testing. Unlike the first run — which registered each artifact incrementally, so they appeared in the UI within minutes — this run spent 20+ minutes drafting everything internally by spawning 8 subagents and registered NOTHING to the platform, so the Artifacts page stayed empty and it looked stalled. Reading the engine transcript showed the planning agent using Read, Glob, Bash, ToolSearch and Agent (subagents) — none of which it is supposed to have. A planning phase is meant to run with ONLY the platform-state tools (read the registered context, register its artifacts); it must not spawn subagents or touch the local filesystem/shell.</t>
+  </si>
+  <si>
+    <t>Companion Runner / Planning Agent (ClaudeDriver)</t>
+  </si>
+  <si>
+    <t>Observed on Requirements re-run 2cf17e68 (work item 8d6f3b7d) during live testing. Engine transcript showed 8 Agent(subagent) calls and 0 register_artifact calls. Relevant code: backend/drivers/claude_driver.py (allowed_tools / permission_mode) and runner/companion/daemon.py (PLAN_ALLOWED_TOOLS).</t>
+  </si>
+  <si>
+    <t>The planning/review agent was launched with its tool allowlist set to only the platform-state tools, but that allowlist does NOT actually restrict the engine: with the default permission mode, Claude Code still exposes ALL its built-in tools (Read, Write, Edit, Bash, Grep, Glob), the subagent tool (Agent/Task), web search, and — because the companion loaded the user's global Claude Code config — the user's personal skills and extra tools. Planning and review phases run in a fresh EMPTY temporary folder with no repository checked out, so those filesystem/shell/subagent tools can reach nothing useful; they only let the agent wander. In live testing a UX Design run spent its first minutes spawning a subagent to grep an empty folder for artifact IDs instead of using the platform tools, and a Requirements re-run spent 20+ minutes drafting via 8 subagents and registered nothing. It is also a sandboxing/security concern: a planning agent should never have shell/file access to the user's machine.</t>
+  </si>
+  <si>
+    <t>Phase-scoped sandbox in backend/drivers/claude_driver.py. Planning and review phases now pass an explicit disallowed-tools list (Agent/Task, Bash, Read, Write, Edit, Glob, Grep, WebFetch, WebSearch, ToolSearch, Skill, TodoWrite, ...) AND setting_sources=['project'] so the engine loads settings only from the empty run folder — never the user's global skills/subagents/MCP. Result: a planning/review agent can use ONLY the platform-state tools it was granted, so it reads context and registers artifacts directly instead of wandering. Implementation/build is deliberately NOT sandboxed — it runs in the real git worktree and must keep Read/Write/Edit/Bash/Grep/Glob to develop code (different code path, BUILD_ALLOWED_TOOLS). Verified live: a full-denylist engine probe returned SANDBOX_LOCKED (subagent + file read + bash all blocked), and a clean UX Design re-run used only platform-state tools (get_context/get_artifact/register_artifact), no subagents, artifacts registering promptly. Tests assert planning/review are sandboxed and build is not.</t>
+  </si>
+  <si>
+    <t>UX Design phase failed right after starting with 'Claude Code not found' — even though the engine was installed and working (earlier phases ran fine).</t>
+  </si>
+  <si>
+    <t>Seen while re-running the UX Design phase during testing. The phase started, then immediately failed with 'Claude Code not found at: …\claude.exe'. Two earlier attempts did NOT help because they targeted the wrong cause: (1) switching from the engine's bundled copy to the user's own copy on PATH, and (2) adding an automatic launch retry. The error came back identically both times. Adding a diagnostic that revealed the real operating-system error finally exposed the true cause (see Root Cause).</t>
+  </si>
+  <si>
+    <t>Companion Runner / Engine launch (ClaudeDriver)</t>
+  </si>
+  <si>
+    <t>UX Design runs during live testing (work item 8d6f3b7d). The failure was specific to the UX Design agent; Requirements/other phases were unaffected. Confirmed by a launch diagnostic reporting Windows error 206 ('The filename or extension is too long').</t>
+  </si>
+  <si>
+    <t>To start a phase, the platform launches the engine and passes the agent its full set of instructions (the 'system prompt') as a COMMAND-LINE argument. Windows limits how long a command line can be — about 32,000 characters total. The UX Design agent's instructions are unusually large (~36,000 characters), so they didn't fit. Windows refused to start the process with a generic 'arguments too long' error (Windows error 206), and the engine library reported that up as the misleading 'Claude Code not found' — even though the engine was right there.
+This is why ONLY the UX Design phase failed: other phases (Requirements, etc.) have smaller instruction sets that fit within the limit. It had nothing to do with a missing engine, the wrong copy of the engine, or antivirus — those earlier theories were wrong.
+Important: this is NOT a 'context too large' problem. The heavy run context (the PRD, past artifacts, code) is already delivered the correct way — as files the agent reads and via on-demand retrieval tools — never on the command line. Only the agent's own static instruction body was being put on the command line, and only the UX one was big enough to overflow it.</t>
+  </si>
+  <si>
+    <t>Root cause was correct (Windows command-line length limit, error 206). The first fix delivered the large body as an AGENTS.md file — this stopped the crash, but was later found INSUFFICIENT: Claude Code does not auto-load AGENTS.md (only CLAUDE.md, and only with project setting-sources), and a planning agent has no file-reading tool, so the body still did not reach the model. Superseded by the correct, permanent fix: deliver the agent body + run manifest as a true FILE-BASED SYSTEM PROMPT via the CLI's --system-prompt-file flag (see S.No 65). That removes the command-line limit for any body size AND guarantees the instructions actually reach the model. The 'Claude Code not found' crash is fully resolved.</t>
+  </si>
+  <si>
+    <t>Large agent phases ran WITHOUT their role instructions and context — the agent produced generic or empty output instead of the platform-grade work it was built for. Affected 7 of the 16 agents whose instruction body exceeds ~24,000 characters, including UX Design, Architecture, Security, Code Review, Testing, and — critically — Implementation and Task Breakdown.</t>
+  </si>
+  <si>
+    <t>Found while investigating why the UX Design phase behaved oddly. The platform delivers each agent two things: its role/process instructions (the agent 'body') and its run context (the composed manifest: project profile, upstream artifacts, rules). A recent fix for the UX 'Claude Code not found' crash (S.No 64) had moved large bodies into an AGENTS.md file — but Claude Code never loads AGENTS.md, and planning agents have no file-reading tool, so for every large agent the role body reached the model through NO channel at all. Separately, the composed manifest had also only ever been written to that unloaded AGENTS.md, so its Rules section never reached the model either. The agents limped along on a context-fetch tool but were not getting their authoritative instructions. Affects any project type.</t>
+  </si>
+  <si>
+    <t>Root-caused during UX Design live testing (work item 8d6f3b7d). Verified against the installed Claude Agent SDK 0.1.0 and Claude CLI 2.1.205. Code: backend/drivers/claude_driver.py.</t>
+  </si>
+  <si>
+    <t>The agent's instructions were delivered by the wrong channel. They were normally passed as the engine's 'system prompt', which the SDK puts on the command line — capped at ~32,000 characters on Windows, so the ~36KB UX body overflowed (S.No 64). The interim workaround wrote the body to an AGENTS.md file, but Claude Code does not auto-load AGENTS.md (only CLAUDE.md, with project setting-sources) and a sandboxed planning agent has no file-reading tool — so the body reached the model through no path. The manifest had the same problem. Net effect: 7 large agents ran without their role, and the interim fix silently regressed 6 phases that previously worked (their bodies had fit on the command line).</t>
+  </si>
+  <si>
+    <t>Deliver the agent body + full run manifest as a TRUE FILE-BASED SYSTEM PROMPT via the CLI flag --system-prompt-file (passed through the SDK's extra_args, since the pinned SDK 0.1.0 doesn't type the flag; the pinned CLI 2.1.205 supports it — verified). The driver writes body+manifest to SYSTEM_PROMPT.md in the run folder and hands the engine its absolute path. Size-independent (no command-line limit for any agent), a real system prompt (strongest adherence — bodies are authored as system prompts), needs no CLAUDE.md/setting-sources trickery, and no client-repo collision in build. One uniform code path replaced the old size-threshold branching; dead AGENTS.md writes were removed. The manifest (incl. its Rules section and, for review, the inlined PR diff) now genuinely reaches the model for the first time. Verified live: a 40KB system-prompt file launched the real engine and the model followed instructions inside the file; a UX Design re-run produced correct, role-appropriate artifacts. Tests rewritten to assert body+manifest reach the CLI via --system-prompt-file for every body size.</t>
+  </si>
+  <si>
+    <t>A phase run failed in Phases &amp; Runs with 'Run failed — Unknown message type: rate_limit_event', even though the agent and companion were healthy.</t>
+  </si>
+  <si>
+    <t>Hit during UX Design live testing. Part-way through a run the engine emitted a 'rate_limit_event' notification message; the SDK's message reader didn't recognise that message type and raised an error, which aborted the entire phase. This would strike ANY phase, at random, whenever the engine sends a rate-limit notice.</t>
+  </si>
+  <si>
+    <t>Companion Runner / Engine (ClaudeDriver)</t>
+  </si>
+  <si>
+    <t>Observed on a UX Design run during live testing. Caused by version skew between the pinned Claude Agent SDK 0.1.0 and the newer Claude CLI 2.1.205. Code: backend/drivers/claude_driver.py.</t>
+  </si>
+  <si>
+    <t>The installed Claude CLI (2.1.205) is newer than the pinned Claude Agent SDK (0.1.0) and emits notification message types the SDK's parser has no case for — here, 'rate_limit_event'. On an unknown type the SDK's parser raises a fatal 'Unknown message type' error, which propagates out and kills the run. These messages are non-essential telemetry; the run's real output still arrives as the normal assistant/result messages. The SDK simply treated an unknown notification as fatal.</t>
+  </si>
+  <si>
+    <t>Made message parsing tolerant of unknown types. The driver wraps the SDK's parser: an unknown message type becomes a harmless, ignored message instead of crashing the run — while genuinely malformed messages (e.g. missing type) still raise, so real errors are not hidden. Forward-robust: it tolerates ANY future unknown notification type from a newer CLI, not just rate_limit_event, without a risky SDK upgrade. Verified: fed a real rate_limit_event through the actual SDK parser (benign, no crash), confirmed malformed messages still raise, and confirmed a stream containing the event still produces a valid result. New tests cover all three cases.</t>
+  </si>
+  <si>
+    <t>Some generated artifacts could not be previewed for review — preview showed 'artifact has no body to preview' even though the artifact clearly had content, blocking the user from reviewing and approving the gate.</t>
+  </si>
+  <si>
+    <t>Seen on the SpendLog test project. Planning agents register many artifacts (assumptions register, user journeys, stakeholder map, accessibility spec, etc.) whose CONTENT is structured data stored in the artifact's external_ref field — because the register tool is pointers-only and there is no other place for that content to live. The preview endpoint only knew how to show a plain-text/markdown body from S3 or an inline 'body' field; it had no way to render structured external_ref content, so those artifacts previewed as empty.</t>
+  </si>
+  <si>
+    <t>Artifacts &amp; Traceability (preview)</t>
+  </si>
+  <si>
+    <t>Root-caused on SpendLog run 7f67d88a; all 7 artifacts of the run previewed empty. Code: backend/integrations/preview.py, backend/orchestration/activities.py.</t>
+  </si>
+  <si>
+    <t>Artifact content lives in one of a few places: an S3 draft body, an inline external_ref 'body' field, the run's staged phase draft, or — for many planning sub-artifacts — as structured JSON in external_ref (the register tool is pointers-only, so structured data there is the only home for that content). The preview read-through handled the first three but had no renderer for structured external_ref, so those artifacts returned 'no body'. It is type- and phase-agnostic: it affects any artifact whose content is structured data, in any phase.</t>
+  </si>
+  <si>
+    <t>Added a generic, type/phase-agnostic renderer in backend/integrations/preview.py that turns any structured external_ref into readable markdown (title heading, labelled fields, lists as bullets, lists of records as titled sections), and ranked the artifact's OWN structured content above the run-level fallbacks so a sub-artifact previews its own content rather than the whole phase document. Known pointer fields (ids, URLs, project refs) are excluded so no UUID noise leaks in. Also merged (not overwrote) the run outputs so the companion's raw report survives as the last-resort fallback, and made the driver report abnormal/empty engine endings instead of silently staging a blank draft. Verified live: all 7 previously-blank artifacts of the test run now preview as readable documents; today's UX Design artifacts preview correctly. New tests cover the renderer and the fallback ordering.</t>
+  </si>
+  <si>
+    <t>The UX Design agent generated full HTML wireframe screens but they were never saved — the wireframe artifacts ended up empty (only a short text description), so no one could preview the screens and the implementation phase had nothing to read.</t>
+  </si>
+  <si>
+    <t>Seen on the SpendLog-Test-2.1 UX Design run. The agent authored ~25 self-contained HTML state documents (default/loading/empty/error/success per screen) exactly as instructed, and registered one wireframe artifact per screen — but the HTML had no channel to reach storage, so each artifact carried only prose 'layout_notes'. The rendered screens were effectively lost.</t>
+  </si>
+  <si>
+    <t>Platform-State MCP + Artifacts (UX Design wireframes)</t>
+  </si>
+  <si>
+    <t>Observed on the SpendLog-Test-2.1 UX Design run. Code: mcp_platform_state/tools.py, mcp_platform_state/server.py, runner/companion/state_mcp.py, runner/companion/runner.py, backend/api/runner_views.py, backend/orchestration/activities.py, backend/integrations/preview.py, frontend/src/features/observability/ArtifactPreviewScreen.tsx, agents/05_ux_design/agent.md.</t>
+  </si>
+  <si>
+    <t>register_artifact is deliberately pointers-only (state stays pointers, bodies live in the object store), and there was NO tool to hand a large body to the platform to persist. Inline external_ref bodies can't carry big HTML because the single MCP call is token-capped (a ~401K-char register call was rejected), and the sandboxed planning agent has no Write/S3 access to stage a snapshot itself. get_artifact also returned pointers only, so even the implementation agent could not read a screen's HTML. Net: the UX agent's central deliverable had nowhere to go and degraded to prose. Affects any phase that must persist a large body, not just wireframes.</t>
+  </si>
+  <si>
+    <t>Added the missing persistence primitive: a stage_artifact_body MCP tool that streams one body (e.g. one HTML state) to the object store as a run/phase-scoped draft and returns its s3_key+hash — sandbox-safe (a platform capability, not local Write), one document per call so it never hits the token cap. The UX agent now stages each state then registers one wireframe artifact per screen with external_ref.states = [{name, s3_key, content_hash}] (primary s3_key = default state); register_artifact stays pointers-only. Added a get_artifact_body read tool (one state at a time) so the task-breakdown/implementation agents can read the actual HTML. Preview now surfaces all states read-through and the UI shows a state switcher rendering each screen in an isolated iframe, so the user previews and approves the real screens; Figma export rides the existing export-policy seam. Also bound project_id from the launch in get_context/list_artifacts (agents were passing the project NAME → backend 500). Verified: new unit tests for staging, one-state read, and multi-state preview pass; existing suites green (4 preview failures are MinIO-not-reachable env only).</t>
+  </si>
+  <si>
+    <t>UX Design ran ~15 min and registered NOTHING. The agent generated and staged its HTML screens fine, but could not read its own project context — every get_context / list_artifacts call came back too big and failed, so the agent looped without ever registering an artifact.</t>
+  </si>
+  <si>
+    <t>Hit on the SpendLog-Test-2.1 UX re-run right after the wireframe-persistence fix. As upstream phases (requirements, PRD, architecture) accumulated artifacts, the context/list tools returned the FULL content of up to 50 artifacts at once (their structured bodies live in external_ref), producing 400,000+ character responses that blow the engine's per-tool token limit. The agent then grabbed shortened artifact ids from the truncated output and called the read tools with them, which 500'd.</t>
+  </si>
+  <si>
+    <t>Platform-State MCP (get_context / list_artifacts / get_artifact_body)</t>
+  </si>
+  <si>
+    <t>Observed on UX Design run f8966dd4: list_artifacts=401,397 chars, get_context(prd)=420,594 chars, plus get_artifact_body 500 'is not a valid UUID' on shortened ids. 0 artifacts registered after 15 min (11 HTML states DID stage to S3 successfully - staging was not the problem). Code: mcp_platform_state/tools.py.</t>
+  </si>
+  <si>
+    <t>get_context and list_artifacts serialized each artifact's ENTIRE external_ref - which for many artifact types holds the structured body/content, not just pointers. Returning up to 50 of those in one response exceeded the MCP token budget, so the whole call failed. This is a listing that must carry pointers only (platform owns STATE as pointers; CONTENT is fetched on demand) but was leaking bodies. A secondary effect: with the list truncated to a saved file, the agent improvised 8-character ids, and get_artifact_body/get_artifact raised an unhandled 500 on a non-UUID instead of a friendly message. Pre-existing latent issue that became fatal once the project had several large upstream artifacts.</t>
+  </si>
+  <si>
+    <t>Made get_context and list_artifacts return POINTER-ONLY artifacts: a new lean serializer strips large/structured values out of external_ref, keeping only small metadata (id, type, route, screen id, sor, and for wireframes the states' name+s3_key+hash). Bodies are now fetched on demand with get_artifact_body(full_id). Measured on the real project: list_artifacts dropped 401,397 -&gt; 20,725 chars, get_context(prd) 420,594 -&gt; 35,702 chars - both safely under the limit. Also hardened get_artifact and get_artifact_body to return a clear 'pass the full id' message instead of a 500 on a malformed/shortened id (which also removes the source of the bad ids, since the agent now receives full ids in a small listing). Verified live against the DB; backend + worker restarted to load it.</t>
+  </si>
+  <si>
+    <t>The UX Design gate could not be approved: clicking Approve returned 'cannot approve: 9 required gate condition(s) unmet' and there was no way in the UI to satisfy them, blocking the whole design gate.</t>
+  </si>
+  <si>
+    <t>Hit approving the UX Design gate on SpendLog-Test-2.1. By design the UX/accessibility gate carries a required WCAG 2.1 AA checklist (9 criteria) that the reviewer must mark satisfied before Approve. But the Gates approval panel showed only Comment + Approve/Reject with no checklist, and its inline Approve sent no condition updates - so the required criteria could never be ticked and the gate was un-approvable. The checklist component (CriteriaGate) existed but was never wired into a route or the panel.</t>
+  </si>
+  <si>
+    <t>Gates (approval UI)</t>
+  </si>
+  <si>
+    <t>Observed approving UX Design gate (approval bc7e6a13, gate_type phase_gate, role designer, 9 WCAG conditions). First surfaced now - first UX gate approval attempt (prior UX run was deleted before its gate). Code: frontend/src/features/lifecycle/Gates.tsx; backend enforcement backend/apps/gates/services.py + wcag.py (unchanged, working as designed).</t>
+  </si>
+  <si>
+    <t>The ux_design gate opens with conditions_for_phase('ux_design') = 9 WCAG 2.1 AA criteria (all required, satisfied=false). services.decide_gate blocks the APPROVE decision while any required condition is unsatisfied; the reviewer satisfies them by sending conditions=[{key,satisfied}] with the decision. The Gates panel's inline Approve never sent conditions and rendered no checklist, and the dedicated CriteriaGate checklist screen was orphaned (present only in tests, no route). So there was no path in the app to satisfy the criteria. Backend + gate design are correct; the gap was purely the missing checklist UI on the approval panel.</t>
+  </si>
+  <si>
+    <t>Wired the WCAG checklist into the Gates approval panel (frontend/src/features/lifecycle/Gates.tsx). When the selected gate has conditions, the panel now fetches them via the existing useGateCriteria hook and renders each criterion as a togglable checkbox (reusing CriteriaList/CriteriaItem), shows an 'X of N met' progress, keeps the Approve button disabled until every required criterion is ticked, and includes the reviewer's conditions=[{key,satisfied}] in the decide call. Gates with no conditions are unchanged (decide directly). Verified: the pending approval carries the 9 WCAG conditions; frontend typechecks clean; reuses the same proven decide path the CriteriaGate screen already used. Reviewer can now tick the WCAG criteria and approve.</t>
+  </si>
+  <si>
+    <t>Task Breakdown agent told to fetch artifact bodies with the wrong tool (get_artifact instead of get_artifact_body)</t>
+  </si>
+  <si>
+    <t>The task-breakdown agent instructions told it to fetch upstream artifact bodies (PRD / requirements / architecture / per-screen wireframes) using get_artifact. Since the pointer-only refactor (S.No 69), get_artifact returns only pointers/provenance with NO body. As written the agent would receive no content to decompose and would stall or hallucinate a backlog — the same failure mode that stalled the UX Design phase until its tool wiring was fixed.</t>
+  </si>
+  <si>
+    <t>Task Breakdown / Agents</t>
+  </si>
+  <si>
+    <t>agents/06_task_breakdown/agent.md (lines 28 and 145); tool split in mcp_platform_state/tools.py get_artifact vs get_artifact_body</t>
+  </si>
+  <si>
+    <t>agent.md was not updated when get_artifact/get_artifact_body were split last session (S.No 68-69). The verbatim instruction kept naming a tool that is now pointer-only, so the agent had no way to read the bodies it must decompose.</t>
+  </si>
+  <si>
+    <t>Updated both references in agents/06_task_breakdown/agent.md to get_artifact_body (which reads one state at a time for multi-state wireframes) and noted that get_artifact returns pointers only. To take effect the backend/worker/companion must be restarted so the new agent body is delivered; verified against a live task-breakdown run.</t>
+  </si>
+  <si>
+    <t>No REST endpoint to start implementation (build) on a work item</t>
+  </si>
+  <si>
+    <t>The implementation BuildWorkflow saga (orchestration.trigger.trigger_build) had no HTTP surface — it was only callable from tests. A user therefore could not start implementation on a work item from the platform, blocking the 'run implementation on one task' flow (both the internal-managed and Jira-managed cases still start the code work through this path).</t>
+  </si>
+  <si>
+    <t>Implementation / Work Items</t>
+  </si>
+  <si>
+    <t>backend/api/views.py (WorkItemViewSet — only the phase trigger action existed); backend/orchestration/trigger.py trigger_build</t>
+  </si>
+  <si>
+    <t>Only the phase trigger (trigger_phase) was wired to a viewset action; trigger_build was fully implemented but was never exposed via a DRF @action/route.</t>
+  </si>
+  <si>
+    <t>Added POST /api/work-items/{id}/build/ (WorkItemViewSet.build) plus BuildTriggerSerializer (agent_key defaults to 07_implementation; optional repo/base default from the work item's Repository; required_role; user_id for companion routing). Returns 202 {run_id, workflow_id}; returns 400 with a friendly message when the work item has no target repository. New focused test backend/tests/test_build_trigger_api.py (2 tests: happy-path start + no-repo rejection).</t>
+  </si>
+  <si>
+    <t>Companion never git-pushes the worktree branch, so opening the PR fails against a live GitHub repo</t>
+  </si>
+  <si>
+    <t>During implementation the companion writes code into a local git worktree on branch feature/WI-&lt;n&gt; but never pushes that branch to origin. codehost.open_pull_request then calls the GitHub REST POST /pulls assuming the head branch already exists on the remote, so against a live GitHub repository the PR step returns 404/422. Code still lands in the developer's local worktree; only the PR / merge / merge-gate steps are blocked.</t>
+  </si>
+  <si>
+    <t>Implementation / CodeHost</t>
+  </si>
+  <si>
+    <t>runner/companion/runner.py (no push by design D2); runner/companion/worktree.py (teardown leaves branch local); backend/orchestration/build_activities.py open_build_pr_core; integrations/github/codehost.py open_pull_request</t>
+  </si>
+  <si>
+    <t>Design D2 keeps all Git side-effects on the platform, but the actual branch-push step was implemented on neither side — the worktree branch is created and left purely local.</t>
+  </si>
+  <si>
+    <t>FIXED (Option B). The companion now performs the Git side-effects (D2): after the build agent writes code and the secret scan passes, run_build commits the change to feature/WI-&lt;key&gt; with a derived Conventional-Commit message and pushes the branch to origin, reporting head_sha so the platform's open_build_pr opens the draft PR against a real ref. New worktree helpers commit_all/push_branch/head_sha (runner/companion/worktree.py); BuildTask carries work_item_title/type and dispatch_build_core ships them for the commit subject. Nothing is committed/pushed when the secret scan blocks or the agent produced no change. Tests: 3 new in test_companion_runner.py (commit+push to a bare remote, subject-from-title, secret-block no-push) + dispatch payload assertion in test_build_activities.py; all pass. The full path (GitHub CodeHost connect + PR -&gt; review -&gt; merge-gate -&gt; done) is now unblocked.</t>
+  </si>
+  <si>
+    <t>Integration credentials entered in the UI are never used; connectors authenticate from server .env</t>
+  </si>
+  <si>
+    <t>IntegrationConnection.secret_encrypted (the credentials a tenant enters when connecting Jira / Confluence / etc.) is written but never decrypted at runtime — decrypt_secrets is only called in tests. Every Atlassian connector resolves its credentials via AtlassianConfig.from_settings() (the server .env). So a tenant that 'connects Jira' and passes the wiring check still authenticates with the single .env Atlassian account; scopes.project_key IS read from the connection, but the secret is not. Effectively single-tenant and a multi-tenant credential-leak risk. The connection also shows Healthy without any live network probe.</t>
+  </si>
+  <si>
+    <t>Integrations / Connectors</t>
+  </si>
+  <si>
+    <t>backend/integrations/registry.py (_atlassian_config / _build_jira / _build_confluence); backend/apps/integrations/services.py (test_integration_connection is wiring-only); apps/integrations/crypto.decrypt_secrets (tests only)</t>
+  </si>
+  <si>
+    <t>The token_ref indirection is a documented Phase-5 seam; Phase 1 hardcoded from_settings() and decrypt_secrets was never wired into the connector builders.</t>
+  </si>
+  <si>
+    <t>Deferred (Phase-5 seam). Fix = wire decrypt_secrets(conn) into the connector builders so per-tenant creds are used and retire the .env fallback; make test-connection a real reachability probe. For the current greenfield test, Jira is connected exactly like Confluence: the Integrations connection supplies scopes.project_key and the shared Atlassian creds live in .env.</t>
+  </si>
+  <si>
+    <t>No dedicated Task Breakdown review screen; dependencies and estimates are not surfaced before the gate</t>
+  </si>
+  <si>
+    <t>The four planning artifacts (backlog / sprint_plan / definition_of_done / dependency_map) render only as plain markdown via the generic artifact preview, and the proposed work items appear separately on the Work Items board as generic 'Draft' badges. depends_on is serialized but read by zero frontend files (no dependency graph), and there is NO estimate/story-points field on WorkItem at all — so a reviewer cannot see hierarchy, dependencies and estimates in one place before approving the task-breakdown gate.</t>
+  </si>
+  <si>
+    <t>Task Breakdown / Work Items UI</t>
+  </si>
+  <si>
+    <t>frontend TaskBreakdown.tsx (after-the-fact summary), WorkItemsBoard.tsx (depends_on unused); backend/integrations/preview.py (no backlog renderer); backend/apps/workitems/models.py (no estimate field)</t>
+  </si>
+  <si>
+    <t>The task-breakdown preview UI was never built to the depth of other phases, and an estimate/story-points field was never modeled on WorkItem.</t>
+  </si>
+  <si>
+    <t>Accepted as-is for this test (markdown preview + Work Items board). Later: a dedicated proposed-backlog review screen showing epic-&gt;story-&gt;task hierarchy + depends_on graph + estimates; add WorkItem.estimate; add a backlog-specific preview renderer.</t>
+  </si>
+  <si>
+    <t>No UI to edit the generated user stories/tasks before the gate</t>
+  </si>
+  <si>
+    <t>Users cannot edit the stories/tasks the Task Breakdown agent generates. A backend edit surface already exists (WorkItemPatchSerializer allows PATCH of title/description/type), but there is no frontend for it, and state / estimate / dependencies are not editable.</t>
+  </si>
+  <si>
+    <t>backend/api/serializers.py WorkItemPatchSerializer (exists, title/description/type); no frontend edit UI</t>
+  </si>
+  <si>
+    <t>The edit UI was never built; only the PATCH serializer was scaffolded.</t>
+  </si>
+  <si>
+    <t>Deferred (later-phase optimization, per team decision). Add an edit UI over the existing PATCH endpoint; consider making dependencies and estimate editable too.</t>
+  </si>
+  <si>
+    <t>Re-running Task Breakdown duplicates the whole backlog (create_work_item has no idempotency)</t>
+  </si>
+  <si>
+    <t>create_work_item unconditionally creates a new WorkItem — there is no natural-key / get_or_create dedupe. Re-dispatching the task-breakdown phase (for example after a stalled run) creates duplicate epics/stories/tasks and duplicate WI numbers. Re-run hygiene currently requires manually deleting the partial batch first (as was done for the UX phase).</t>
+  </si>
+  <si>
+    <t>Platform State / Work Items</t>
+  </si>
+  <si>
+    <t>mcp_platform_state/tools.py create_work_item (contrast register_artifact which auto-versions)</t>
+  </si>
+  <si>
+    <t>No idempotency/natural key on work-item creation, unlike register_artifact which versions siblings.</t>
+  </si>
+  <si>
+    <t>Deferred. Add an idempotency key (e.g. project+phase+title, or an agent-supplied external key) so a re-run upserts rather than duplicates. For today's run, delete any partial batch before re-triggering.</t>
+  </si>
+  <si>
+    <t>Jira integration is one-way (create-only): no inbound webhook, no status sync, dropped fields</t>
+  </si>
+  <si>
+    <t>Reconcile creates Jira issues (summary/description/parent only) and stores the Jira key in WorkItem.external_ref, but: (a) there is no inbound Jira webhook and no Jira-status -&gt; WorkItem.State mapping, so a Jira transition (In Progress/Done) is invisible to the platform; (b) transition_issue is implemented but never called in production, so platform-side transitions are not pushed back to Jira; (c) depends_on edges, acceptance criteria, story points and wireframe refs are not pushed. Completion is detected ONLY via the GitHub PR-merge webhook — never via Jira. So a Jira-managed task is a visibility mirror, not a two-way work surface.</t>
+  </si>
+  <si>
+    <t>Integrations / TaskTracker (Jira)</t>
+  </si>
+  <si>
+    <t>backend/integrations/reconcile.py (create-only, minimal fields); integrations/atlassian/tasktracker.py transition_issue (dormant); backend/integrations/webhooks.py (GitHub inbound only)</t>
+  </si>
+  <si>
+    <t>Bi-directional Jira sync is a future seam; reconcile is create-only and maps neither dependency links nor rich issue fields.</t>
+  </si>
+  <si>
+    <t>Deferred. Add an inbound Jira webhook + status-&gt;state mapping, wire transition_issue on WorkItem transitions, and map depends_on (Jira issue links) plus acceptance criteria / story points / wireframe ref in reconcile.</t>
+  </si>
+  <si>
+    <t>No in-context 'Push to Jira' action on the Task Breakdown screen; publish reconciles ALL proposed work items at once</t>
+  </si>
+  <si>
+    <t>The Jira push lives on the generic Artifact Publish screen keyed off the backlog artifact — there is no 'push these tasks to Jira' button on the Task Breakdown screen or the Work Items board where a reviewer is actually looking at the composed stories/tasks. Worse, publishing calls reconcile_backlog(project_id), which pushes EVERY proposed work item in the project in one go — there is no per-item review-and-confirm or subset selection before the push. A reviewer cannot push a reviewed subset or see, in context, exactly what will go to Jira.</t>
+  </si>
+  <si>
+    <t>Task Breakdown / Integrations UI</t>
+  </si>
+  <si>
+    <t>frontend ExportPublish.tsx (push on artifact publish); backend/api/views.py _publish_tasktracker -&gt; reconcile_backlog(project_id); no push button on TaskBreakdown.tsx or WorkItemsBoard.tsx</t>
+  </si>
+  <si>
+    <t>The Jira push was wired only to the generic per-artifact publish path (which reconciles the whole project's proposed items), never to an in-context task-review action with selection/confirm.</t>
+  </si>
+  <si>
+    <t>Deferred (accepted for this test). Later: add a 'Push to Jira' action on the Task Breakdown review screen with a per-item / selection confirm step, backed by a scoped reconcile (push the reviewed subset, not the whole project blindly).</t>
+  </si>
+  <si>
+    <t>SYSTEMIC (fresh-run blocker): manifest composer + 15 of 16 agent bodies tell every agent to fetch artifact bodies with get_artifact (pointer-only)</t>
+  </si>
+  <si>
+    <t>The manifest composer's 'Relevant Artifacts' section instructed EVERY agent to 'fetch full bodies with get_artifact(artifact_id)', and 15 of 16 agent bodies repeated the same stale instruction. Since get_artifact became pointer-only (S.No 68-69, commit d7c27d6), it returns NO S3 body — so under the current pointer-only get_context/list_artifacts regime an agent cannot read its upstream inputs and stalls or hallucinates (the exact UX-phase failure). Earlier phases (ideation..architecture) appeared to work only because they ran on 2026-07-08 BEFORE get_context went pointer-only (context then carried full bodies inline) and because some upstream bodies happened to be stored inline in external_ref. A fresh end-to-end run puts every phase under the pointer-only regime and would hit the failure. Same class as S.No 71 (task breakdown) but suite-wide.</t>
+  </si>
+  <si>
+    <t>Agents / Manifest / Platform State</t>
+  </si>
+  <si>
+    <t>backend/manifest/composer.py:161 (Relevant Artifacts instruction); 15 agent bodies: 00_onboarding, 00b_context_bridge, 00c_context_extractor, 01_ideation, 02_requirements, 03_prd, 04_architecture, 05_ux_design, 07_implementation, 08_code_review, 09_testing, 09b_test_automation, 10_security, 11_cicd, 12_deployment; get_artifact vs get_artifact_body in mcp_platform_state/tools.py</t>
+  </si>
+  <si>
+    <t>The get_artifact/get_artifact_body tool split (S.No 68-69) made get_artifact pointer-only, but the composer instruction and every pre-existing agent body still named get_artifact for body fetches. They were authored/tested before get_context went pointer-only (2026-07-09, d7c27d6), so the regression stayed latent until a phase ran under the new regime (UX was first).</t>
+  </si>
+  <si>
+    <t>Swept all 27 body-fetch references to get_artifact_body (word-boundary replace; get_artifact_body's fallback chain in integrations/preview.py handles S3 + inline external_ref.body + structured external_ref + run-draft bodies): composer.py:161 plus the 15 agent bodies (06_task_breakdown was already fixed under S.No 71). Verified: 0 bare body-fetch get_artifact remain (only 06's accurate 'get_artifact returns pointers' note); composer compiles; agent-migration CONTENT tests pass. Backend + worker restarted to reload the composer.</t>
+  </si>
+  <si>
+    <t>Two agent-migration tests assert on options.system_prompt, obsolete since file-based system-prompt delivery</t>
+  </si>
+  <si>
+    <t>test_prd_run_reads_inputs_from_platform and test_ux_run_reads_inputs_from_platform assert against captured options.system_prompt, but the driver now delivers the agent body via a --system-prompt-file (SYSTEM_PROMPT.md in the run workdir, commit 98200ae), so options.system_prompt is None and the tests raise TypeError. Confirmed pre-existing: they fail identically on clean HEAD, independent of the get_artifact_body sweep. Runtime is unaffected; only the tests are stale.</t>
+  </si>
+  <si>
+    <t>Tests / Engine driver</t>
+  </si>
+  <si>
+    <t>backend/tests/test_agents_migration.py:146; backend/tests/test_design_test_agents_migration.py:213; driver delivery in backend/drivers/claude_driver.py (--system-prompt-file, 98200ae)</t>
+  </si>
+  <si>
+    <t>The tests were written against the old inline options.system_prompt delivery and were not updated when delivery moved to a file (98200ae).</t>
+  </si>
+  <si>
+    <t>Not yet fixed. Update both tests to read the written SYSTEM_PROMPT.md (run workdir) instead of options.system_prompt, or assert on the file-based delivery path.</t>
+  </si>
+  <si>
+    <t>Task Breakdown agent had no body-persistence protocol — its 4 planning artifacts (backlog/sprint_plan/DoD/dependency_map) would not reliably persist</t>
+  </si>
+  <si>
+    <t>The task-breakdown agent was told 'register it with register_artifact ... the platform persists the bodies', but register_artifact is pointers-only and the agent had NO stage_artifact_body protocol (UX has 3 such calls; task breakdown had 0). So on a run its four full-document deliverables risked not persisting: at best the primary previews via the run-report fallback, the rest show empty — the same class as the UX wireframe loss (S.No 68) before UX got its staging protocol.</t>
+  </si>
+  <si>
+    <t>agents/06_task_breakdown/agent.md (Output section); stage_artifact_body in mcp_platform_state/tools.py; _PLATFORM_TOOL_NAMES in backend/orchestration/activities.py</t>
+  </si>
+  <si>
+    <t>The agent body predates the stage_artifact_body tool (S.No 68) and kept the old, now-false 'the platform persists the bodies' wording; only 05_ux_design was updated with a staging protocol at the time.</t>
+  </si>
+  <si>
+    <t>Added a 'How bodies are persisted' protocol to agents/06_task_breakdown/agent.md mirroring UX: each full deliverable (backlog/sprint_plan/definition_of_done/dependency_map) is staged with stage_artifact_body(filename, body) (one document per call), then registered with register_artifact using the returned s3_key/content_hash; the assumption register may stay inline in external_ref. Verified stage_artifact_body is in the planning allowlist and not sandbox-blocked; container sees the update.</t>
+  </si>
+  <si>
+    <t>UI phase trigger ran BUILD phases as planning runs — clicking Implementation could not produce code (no worktree/commit/PR)</t>
+  </si>
+  <si>
+    <t>The Work Items / Phases &amp; Runs UI triggers every phase through POST /work-items/{id}/trigger/ -&gt; trigger_phase -&gt; AgentRunWorkflow (planning: sandboxed, no filesystem/git/worktree). But build phases must run through the BuildWorkflow (worktree -&gt; commit -&gt; push -&gt; PR -&gt; review -&gt; merge gate). So clicking 'Implementation' (or CI/CD, Test Automation) on a task would start a sandboxed planning run that cannot write code, commit, push, or open a PR — nothing would land in the repo. There was no build-vs-plan routing anywhere: only trigger_build (used by tests) reached the build path, and it had no UI entry. Affects every current and future build agent, not just implementation.</t>
+  </si>
+  <si>
+    <t>Implementation / Phases &amp; Runs / Work Items</t>
+  </si>
+  <si>
+    <t>backend/api/views.py WorkItemViewSet.trigger; backend/orchestration/trigger.py (trigger_phase vs trigger_build); backend/apps/registry/catalog.py; frontend triggers via /trigger/ (PhasesAndRuns.tsx / WorkItemTask.tsx / WorkItemDefect.tsx)</t>
+  </si>
+  <si>
+    <t>trigger_phase always started an AgentRunWorkflow regardless of agent; build routing existed only implicitly (which function a test happened to call). No source of truth marked which agents ride the BuildWorkflow, and the single UI trigger had no branch for it.</t>
+  </si>
+  <si>
+    <t>Added an explicit rides_build flag to AgentDefinition (single source of truth), set True only for the agents whose migrated body states the platform commits/pushes/opens the PR: 07_implementation, 09b_test_automation, 11_cicd. Planning phases (05_ux_design, 06_task_breakdown, 09_testing, 10_security, 12_deployment) stay False; 08_code_review runs inside the build loop (dispatched automatically, not a standalone user trigger). WorkItemViewSet.trigger now routes rides_build agents to trigger_build, else trigger_phase — so the existing UI buttons work for both plan and build with NO frontend change, and a future build agent only sets the flag. trigger_build now falls back to the project's default repository when the work item has none (proposed tasks). Tests: routing (07-&gt;build-run, 06-&gt;agent-run), rides_build flag set, project-default-repo fallback — all pass; agentspec-migration + frontend trigger/catalog tests still green. Backend restarted; flags verified live in-container.</t>
+  </si>
+  <si>
+    <t>Trigger routes to the newest enrollment even if it never connected — dispatch can land on a dead enrollment while the live companion gets 204 (stuck run)</t>
+  </si>
+  <si>
+    <t>_resolve_enrollment picks the most recent RunnerEnrollment for the triggering user regardless of whether that enrollment has ever checked in (last_seen). When a machine has several enrollments (e.g. opening Connect Machine to copy a token while the daemon runs on an older token, or repeated reconnects), the trigger can route the dispatch to an enrollment whose daemon never ran, while the live companion polls under a different enrollment and receives 204 No Content. Observed live on the first WI-18 build: dispatch stuck 'pending' on a never-checked-in enrollment (last_seen null) while the running companion polled a different one; the build never started. Workaround used: wipe stale enrollments so only one fresh enrollment exists.</t>
+  </si>
+  <si>
+    <t>Companion / Runner enrollment</t>
+  </si>
+  <si>
+    <t>backend/orchestration/trigger.py _resolve_enrollment (used by trigger_phase + trigger_build); apps/runs/models.py RunnerEnrollment.last_seen; runner_views.py RunnerWorkClaimView</t>
+  </si>
+  <si>
+    <t>_resolve_enrollment orders enrollments by recency and does not prefer ones that have actually checked in (last_seen recent / within the online window). RC-4 collapses re-enrollments by project but the selection still ignores liveness.</t>
+  </si>
+  <si>
+    <t>FIXED (2026-07-14). _resolve_enrollment in backend/orchestration/trigger.py no longer picks purely by recency. It now prefers, in order: (1) the newest ACTIVE enrollment that is ONLINE (last_seen within the 2-minute ONLINE_THRESHOLD from apps/runs/enrollment.py - i.e. a companion is heartbeating/polling with that token right now); (2) the newest that has EVER checked in; (3) the newest overall (nothing connected yet - e.g. the user triggers before starting the companion; the dispatch waits, same as before). Applies to BOTH trigger_phase and trigger_build (they share the helper). Result: a Connect-Machine visit that mints a newer-but-never-connected enrollment can no longer capture a dispatch while the live companion polls 204s. Tests: backend/tests/test_build_trigger_api.py::test_resolve_enrollment_prefers_newest_online_over_newer_dead_one and test_resolve_enrollment_falls_back_seen_then_newest. Revoking stale enrollments is still good hygiene but no longer required for a correct dispatch.</t>
+  </si>
+  <si>
+    <t>09_testing / 10_security bodies reference the git worktree but are classified as planning (sandboxed, no filesystem) — may be starved of code when actually run</t>
+  </si>
+  <si>
+    <t>During the build-routing audit, 09_testing and 10_security were classified as planning phases: their bodies say 'when artifacts are registered, stop; the platform opens the review gate' — no commit/push/PR, so correctly NOT routed to the BuildWorkflow. But both bodies also reference the companion git worktree several times (they read the codebase to test/scan it). Planning phases run through the AgentRunWorkflow sandbox (no filesystem/Bash), so if these agents genuinely need to read the worktree code, they would be starved when run. There is currently no third execution mode ('reads the worktree but produces no PR'). Unverified — these phases have not been run yet.</t>
+  </si>
+  <si>
+    <t>Testing / Security / Orchestration</t>
+  </si>
+  <si>
+    <t>agents/09_testing/agent.md, agents/10_security/agent.md (worktree references); backend/orchestration routing (BuildWorkflow vs sandboxed AgentRunWorkflow); apps/registry/catalog.py rides_build</t>
+  </si>
+  <si>
+    <t>Only two execution paths exist (build = worktree + PR + merge gate; plan = sandboxed + register + review gate). 09_testing/10_security need to read code (worktree) but emit review-gated artifacts, not a PR — a shape neither path serves cleanly.</t>
+  </si>
+  <si>
+    <t>Not yet investigated. When these phases are first run, verify the agent can access the code it needs; if not, either add a 'worktree-read, no-PR' execution mode (build-mode filesystem access without the commit/push/merge gate) or feed the needed code context via platform-state tools instead of the worktree. Left on the planning path for now (correct re: no PR).</t>
+  </si>
+  <si>
+    <t>Build fails after push: agent's pre-PR 'code' pointer makes open_build_pr skip opening the real PR, then code review crashes (KeyError 'repo')</t>
+  </si>
+  <si>
+    <t>The 07_implementation agent registers a pre-PR 'code' pointer (branch/files_changed, no PR) which its body says 'the platform reconciles with the PR it opens'. But open_build_pr_core treated ANY existing code artifact with a truthy external_ref as 'PR already opened' and returned early, so it never opened the real PR; then run_code_review_core read code.external_ref['repo'] and raised KeyError('repo'). Observed live on WI-18: code committed and pushed to feature/WI-aa6020d0 on GitHub, but NO PR opened and the run failed — blocking PR to review to merge.</t>
+  </si>
+  <si>
+    <t>Implementation / Build pipeline</t>
+  </si>
+  <si>
+    <t>backend/orchestration/build_activities.py open_build_pr_core + run_code_review_core; agents/07_implementation/agent.md (~line 264 register code pointer)</t>
+  </si>
+  <si>
+    <t>open_build_pr's idempotency check mistook the agent's pre-PR pointer for an opened PR; the documented 'platform reconciles the pointer with the PR' behaviour was never implemented.</t>
+  </si>
+  <si>
+    <t>Added _is_pr_ref (a real PR ref carries repo+number). open_build_pr short-circuits only on a real opened PR; when the agent's pre-PR pointer exists it OPENS the PR and reconciles that artifact in place (update_artifact with the PR external_ref + STAGED) instead of skipping/duplicating. run_code_review guards on _is_pr_ref (clear error, not KeyError). New test test_open_pr_reconciles_agent_pre_pr_pointer + 10 existing build-activities tests pass. Worker reloaded; failed WI-18 run cleaned for a fresh re-trigger.</t>
+  </si>
+  <si>
+    <t>Implementation agent can transition the WorkItem to 'done' itself (mid-build), bypassing the platform merge gate that owns completion</t>
+  </si>
+  <si>
+    <t>During the WI-18 build, the WorkItem was set to state='done' at 12:25:51 — a full minute BEFORE the PR opened (12:26:51), with no merge-gate approval and no webhook. The only actor with the tool and that timing is the 07_implementation agent: transition_work_item is in the build-phase tool allowlist (BUILD_STATE_TOOLS), so the agent marked its own task 'done' as it finished. This violates control-plane ownership of completion (non-negotiable: gates live in the control plane) — the platform should set 'done' only after the merge gate is approved and the PR merged. Effect: WorkItem state becomes premature/unreliable and the merge gate is cosmetic for state purposes.</t>
+  </si>
+  <si>
+    <t>Implementation / Guardrails / Work Items</t>
+  </si>
+  <si>
+    <t>runner/companion/runner.py BUILD_STATE_TOOLS ('transition_work_item'); backend/api/runner_views.py allowlist; mcp_platform_state/tools.py transition_work_item; backend/orchestration/build_workflow.py owns the done transition (~line 150)</t>
+  </si>
+  <si>
+    <t>transition_work_item is exposed to the build agent (needed for remediation child items) but nothing stops it from transitioning the MAIN WorkItem into a gated/terminal state. The platform's post-merge completion transition and the agent's tool access overlap.</t>
+  </si>
+  <si>
+    <t>Open — team to address later. Options: remove transition_work_item from the build agent's allowlist (platform owns all WorkItem state); or scope it so the agent may only transition remediation child items it owns; or reject agent-initiated transitions to gated states ('accepted'/'done') server-side.</t>
+  </si>
+  <si>
+    <t>Merging the PR directly on GitHub bypasses the platform merge gate and orphans the BuildWorkflow (no reachable webhook to reconcile the external merge)</t>
+  </si>
+  <si>
+    <t>The intended completion flow is: PR -&gt; platform code review -&gt; merge gate approved in the platform -&gt; platform merges via CodeHost -&gt; WorkItem done. On WI-18 the developer merged PR #1 directly on GitHub instead. Because the platform runs on localhost and no GitHub webhook is configured/reachable (GITHUB_WEBHOOK_SECRET empty; GitHub cannot reach localhost), the platform never learned of the merge. Result: the BuildWorkflow (build-run-dbf76d68) is left RUNNING, parked at the review/merge-gate step for a PR that is already merged, and will never complete on its own. The code did land on main (the developer's merge), but the platform workflow and gate are out of sync.</t>
+  </si>
+  <si>
+    <t>Build pipeline / CodeHost / Webhooks</t>
+  </si>
+  <si>
+    <t>backend/integrations/webhooks.py (GitHub PR-merge -&gt; transition done, needs a reachable endpoint + GITHUB_WEBHOOK_SECRET); backend/orchestration/build_workflow.py (merge gate expects the platform to merge); settings.GITHUB_WEBHOOK_SECRET (empty)</t>
+  </si>
+  <si>
+    <t>The platform-driven merge (via the merge gate) and an external GitHub merge are two paths; only the platform-driven one completes the workflow. The inbound webhook that would reconcile an external merge is not configured/reachable in local dev, so external merges strand the workflow.</t>
+  </si>
+  <si>
+    <t>Open — team to address later. Either drive merges through the platform merge gate (Gates page) so the platform merges + completes the workflow, OR expose the platform on a reachable URL (tunnel/deploy) + configure the GitHub webhook with GITHUB_WEBHOOK_SECRET so external merges reconcile (transition done + let the workflow finish). Interim: terminate the currently-orphaned build-run-dbf76d68 workflow.</t>
+  </si>
+  <si>
+    <t>Takeover-timeout marks a companion phase run terminally 'failed' even when the companion later reports success; the closed workflow then blocks the review gate's Approve</t>
+  </si>
+  <si>
+    <t>A companion goes offline after a phase is dispatched; the report-timeout fires and mark_phase_takeover sets the run to terminal FAILED; AgentRunWorkflow returns {status: takeover} so the workflow COMPLETES. If the companion later returns, registers artifacts, and POSTs report status=ok, that late success does NOT reconcile the run out of FAILED - UI shows 'Failed / engine exited before reporting, no artifact registered' (false: artifacts WERE registered). Second face: the workflow already completed, so decide_gate's signal has no live workflow and Approve cannot publish. Observed on SpendLog Architecture run 8738d4ba (tenant 212395b8): dispatched 2026-07-12 19:49Z, laptop asleep ~7.5h, takeover 03:27Z (run-&gt;failed), 11 artifacts registered 03:55Z, report ok 03:56Z. Related to rows 61/62.</t>
+  </si>
+  <si>
+    <t>Orchestration / Companion runs / Gates</t>
+  </si>
+  <si>
+    <t>backend/orchestration/workflows.py AgentRunWorkflow.run (report wait ~L52, takeover return ~L61); activities.py mark_phase_takeover_core ~L389; phase_report.py report_phase (no reconcile when workflow gone); apps/gates/services.py decide_gate ~L133-159 (raises if COMPLETED); UI copy 'engine exited before reporting'</t>
+  </si>
+  <si>
+    <t>FAILED is treated as terminal and a late successful phase.reported does not reconcile it; report_timeout (7200s wall-clock from dispatch) trips on an asleep companion that later completes fine. Once run() returns on takeover the workflow is gone, so both phase_report and decide_gate have no live workflow to signal.</t>
+  </si>
+  <si>
+    <t>Open - co-dev (tarun's team) to fix. Proposed: (1) a late phase.reported ok reconciles the run to awaiting_gate + opens the gate; (2) treat takeover as a reclaimable 'parked' state, not terminal, while the companion still heartbeats; (3) decide_gate tolerates an absent/closed workflow and drives publish_artifacts + transition_work_item directly; (4) fix the misleading UI copy. Run 8738d4ba manually reconciled to awaiting_gate 2026-07-13.</t>
+  </si>
+  <si>
+    <t>EPIC: Multi-repo work-item assignment (Hybrid Option C) - agent proposes a repo per work item, human confirms/overrides at the Task Breakdown gate, then implementation routes each task to its repo</t>
+  </si>
+  <si>
+    <t>Approved design (team, 2026-07-13). Task Breakdown auto-suggests a repository for every work item (with rationale + confidence); the reviewer confirms or overrides at the gate before assignment is locked; implementation opens each PR in the assigned repo; a user can redirect any task until its build starts. Single-repo projects skip the review (all tasks -&gt; the one repo). Mockup: docs/design/screens/S-23b-repo-assignment-flow.html. Decomposed into rows 91-102 (A1-A5, B1-B4, C1-C2, E1). Follows the platform law draft-&gt;reviewed-&gt;gated-&gt;published.</t>
+  </si>
+  <si>
+    <t>Task Breakdown / Multi-repo / Build routing</t>
+  </si>
+  <si>
+    <t>Enhancement (Epic)</t>
+  </si>
+  <si>
+    <t>docs/design/screens/S-23b-repo-assignment-flow.html; verified gaps across mcp_platform_state/tools.py, backend/manifest/composer.py, backend/api/*, agents/06_task_breakdown/agent.md, frontend S-13/S-23/S-16</t>
+  </si>
+  <si>
+    <t>Multi-repo infra (WorkItem.repo FK, repo-scoped context, repo_topology, per-repo manifest, build routing on work_item.repo) exists, but nothing lets Task Breakdown assign a repo, nor a user set/override it - so multi-repo routing was impossible end-to-end.</t>
+  </si>
+  <si>
+    <t>Open - build in order A1-&gt;A4, B1-&gt;B3, C1, E1, then D1 verify. Backward-compatible: repo_id optional, single-repo unchanged.</t>
+  </si>
+  <si>
+    <t>In Progress</t>
+  </si>
+  <si>
+    <t>A1: get_context does not return the project's repository list for project-level/planning runs - only repo_topology + the single scoped repo. Task Breakdown can't see the repos to assign them</t>
+  </si>
+  <si>
+    <t>For a project-level run (no repo_id/work_item repo), get_context returns profile.repo_topology and repo=null, but never enumerates the project's repositories. The Task Breakdown agent therefore has no list of frontend/backend/infra repos (id, name, role) to classify against.</t>
+  </si>
+  <si>
+    <t>Platform-State MCP / Context</t>
+  </si>
+  <si>
+    <t>mcp_platform_state/tools.py get_context (~L172-224); mirror runner/companion/state_mcp.py</t>
+  </si>
+  <si>
+    <t>get_context was written for repo-scoped runs (D5) and never surfaced the repo set for project-level planning runs.</t>
+  </si>
+  <si>
+    <t>Open. Add a repositories[] list (id, name, role, default_base, is_default) to get_context's return for project-level runs; mirror in the companion state_mcp proxy.</t>
+  </si>
+  <si>
+    <t>A2: create_work_item has no repo_id parameter - the Task Breakdown agent cannot pin a work item to a repo when proposing it</t>
+  </si>
+  <si>
+    <t>create_work_item(tenant, project, type, title, description, parent_id, feature_stream, depends_on) omits repo_id, so every proposed work item is created with repo=null regardless of topology. The agent literally cannot assign a repo.</t>
+  </si>
+  <si>
+    <t>Platform-State MCP / Work Items</t>
+  </si>
+  <si>
+    <t>mcp_platform_state/tools.py create_work_item (~L343); server.py tool registration; runner/companion/state_mcp.py; backend/api/runner_views.py allowlist</t>
+  </si>
+  <si>
+    <t>Signature predates multi-repo assignment.</t>
+  </si>
+  <si>
+    <t>Open. Add optional repo_id (validated to a Repository in the same tenant/project); propagate the signature through server.py, state_mcp.py, and the runner_views allowlist. Keep optional -&gt; single-repo/repo-less unchanged.</t>
+  </si>
+  <si>
+    <t>A3: the Manifest Composer renders '# Repository' only for a single repo-scoped run - a multi-repo project-level manifest never lists the repos for the agent</t>
+  </si>
+  <si>
+    <t>composer._render_repository renders one repo (context.repo) for repo-scoped runs; for a project-level multi-repo run context.repo is null, so the manifest shows repo_topology: multi but no repository list. Even with A1, the agent's manifest wouldn't show the repos to choose from.</t>
+  </si>
+  <si>
+    <t>Manifest Composer</t>
+  </si>
+  <si>
+    <t>backend/manifest/composer.py _render_repository (~L89), compose (~L218)</t>
+  </si>
+  <si>
+    <t>Per-repo section was designed for the single repo a run targets, not the full set for a planning run.</t>
+  </si>
+  <si>
+    <t>Open. Render a '# Repositories' (plural) section (name + role per repo) when a project-level run is multi-repo; keep the singular section for repo-scoped runs.</t>
+  </si>
+  <si>
+    <t>A4: the 06 Task Breakdown agent is not taught to classify work items by repo, pass repo_id, or emit a rationale + confidence</t>
+  </si>
+  <si>
+    <t>The migrated agent body proposes work items but has no repo-assignment protocol. Teach it to read the repositories from context, classify each item (frontend/backend/infra/shared) with a one-line rationale + confidence, pass repo_id to create_work_item, and route all items to the single repo when topology=single.</t>
+  </si>
+  <si>
+    <t>Agents / Task Breakdown</t>
+  </si>
+  <si>
+    <t>Enhancement (Agent)</t>
+  </si>
+  <si>
+    <t>agents/06_task_breakdown/agent.md; per docs/AGENT_MIGRATION_SPEC.md (reuse reasoning, rewrite data refs)</t>
+  </si>
+  <si>
+    <t>Agent predates multi-repo; no assignment reasoning existed.</t>
+  </si>
+  <si>
+    <t>Open. Add the repo-assignment protocol + emit assignment {repo_id, rationale, confidence} per item (pairs with A5 storage).</t>
+  </si>
+  <si>
+    <t>A5 (decision): where to store each item's repo-assignment rationale + confidence so the review UI can show them</t>
+  </si>
+  <si>
+    <t>The review screen (B2) shows the agent's reason + confidence per work item. Decide the storage: a new WorkItem field vs. a structured payload in external_ref vs. a sidecar assignment record. Recommendation: keep it on the work item (e.g. external_ref.repo_assignment = {rationale, confidence, suggested_repo_id}) so it travels with the item and survives reconciliation.</t>
+  </si>
+  <si>
+    <t>Data model / Work Items</t>
+  </si>
+  <si>
+    <t>Enhancement (Design decision)</t>
+  </si>
+  <si>
+    <t>backend/apps/workitems/models.py; mcp_platform_state/tools.py create_work_item; consumed by frontend S-23</t>
+  </si>
+  <si>
+    <t>No field currently carries an agent suggestion + confidence for review.</t>
+  </si>
+  <si>
+    <t>Open - pending team's answer (keep rationale/confidence? yes recommended). Then implement the chosen storage.</t>
+  </si>
+  <si>
+    <t>B1: WorkItem.repo is not editable via the API - the work-item PATCH allows only title/description/type, so a user cannot assign or redirect a task's repo</t>
+  </si>
+  <si>
+    <t>WorkItemPatchSerializer fields = [title, description, type]. There is no way to set WorkItem.repo through the API/UI, so neither the review-screen override nor the per-task redirect can persist.</t>
+  </si>
+  <si>
+    <t>Work Items / API</t>
+  </si>
+  <si>
+    <t>Enhancement (API gap)</t>
+  </si>
+  <si>
+    <t>backend/api/serializers.py WorkItemPatchSerializer (~L255); backend/api/views.py partial_update</t>
+  </si>
+  <si>
+    <t>Patch surface was scoped to human text edits (S-15/S-16), never repo.</t>
+  </si>
+  <si>
+    <t>Open. Allow repo on the work-item PATCH, validated to a Repository in the same tenant/project. Build routing already honors work_item.repo (verified trigger_build).</t>
+  </si>
+  <si>
+    <t>B2 (new component): Task Breakdown repo-assignment REVIEW screen - grouped-by-repo, agent suggestion + reason + confidence, override dropdown, 'X of N confirmed', flagged-first, Approve</t>
+  </si>
+  <si>
+    <t>New review surface on S-23 where the reviewer confirms/overrides the agent's repo suggestions before the gate. Low-confidence items surfaced first; overrides visually marked; progress toward 'all confirmed'; Approve wires to the gate decision (C1). Design locked in docs/design/screens/S-23b-repo-assignment-flow.html.</t>
+  </si>
+  <si>
+    <t>Frontend / Task Breakdown</t>
+  </si>
+  <si>
+    <t>New Component</t>
+  </si>
+  <si>
+    <t>frontend S-23 (features/lifecycle or task-breakdown); consumes A5 payload + B1 PATCH; mockup S-23b</t>
+  </si>
+  <si>
+    <t>No UI exists to review/assign repos.</t>
+  </si>
+  <si>
+    <t>Open - build to the approved mockup after team sign-off (see decisions: review-at-gate vs separate screen; grouping; bulk actions).</t>
+  </si>
+  <si>
+    <t>B3 (new component): repo selector on the work item / board to redirect a task to another repo until its build starts</t>
+  </si>
+  <si>
+    <t>A repo dropdown on the work-item detail (S-16) and/or board (S-14), populated from the repositories endpoint, calling B1's PATCH. Editable until the task's build starts; read-only once the PR opens. This is the 'redirect any task' escape hatch.</t>
+  </si>
+  <si>
+    <t>Frontend / Work Items</t>
+  </si>
+  <si>
+    <t>frontend S-16, S-14; consumes B1 PATCH + repositories GET</t>
+  </si>
+  <si>
+    <t>No per-item repo control exists.</t>
+  </si>
+  <si>
+    <t>Open - build after B1. Show assigned repo + role; disable after build start.</t>
+  </si>
+  <si>
+    <t>B4 (verify): confirm the Repositories setup UI captures each repo's role (frontend/backend/infra) in the live app</t>
+  </si>
+  <si>
+    <t>Auto-assign keys off Repository.role. The mockup S-13 and the model support role; verify the live Repositories.tsx add-repo form actually captures and persists role, and fix if missing.</t>
+  </si>
+  <si>
+    <t>Frontend / Setup</t>
+  </si>
+  <si>
+    <t>Issue (Verify)</t>
+  </si>
+  <si>
+    <t>frontend/src/features/setup/Repositories.tsx; backend RepositoryCreateSerializer</t>
+  </si>
+  <si>
+    <t>Role is optional on the model; UI may not surface it.</t>
+  </si>
+  <si>
+    <t>Open - verify in the running app; add the role field if absent.</t>
+  </si>
+  <si>
+    <t>C1: wire 'Approve assignment &amp; continue' as the Task Breakdown gate decision - approving locks the repo assignments</t>
+  </si>
+  <si>
+    <t>The review screen's Approve must be the Task Breakdown gate decision: on approve, the assignments are locked and the phase proceeds. Ties B2 (UI) to the gate services so the assignment is committed exactly once, with human sign-off (matches draft-&gt;reviewed-&gt;gated-&gt;published).</t>
+  </si>
+  <si>
+    <t>Gates / Task Breakdown</t>
+  </si>
+  <si>
+    <t>backend/apps/gates/services.py + models; backend/api/views.py; frontend gate (S-21/S-23)</t>
+  </si>
+  <si>
+    <t>Gate decision currently approves the backlog, not the repo assignment.</t>
+  </si>
+  <si>
+    <t>Open. On approve, lock assignments (freeze repo per item); proceed. Pairs with C2 decision.</t>
+  </si>
+  <si>
+    <t>C2 (decision): should the gate BLOCK approval while low-confidence items are unreviewed, or only warn?</t>
+  </si>
+  <si>
+    <t>Business rule for C1: either hard-block Approve until every flagged (low-confidence) item is confirmed, or allow approval with a warning. Recommendation: warn + require an explicit 'confirm all' rather than hard-block, to avoid dead-ends on large backlogs.</t>
+  </si>
+  <si>
+    <t>backend/apps/gates/services.py decide_gate; frontend S-23 Approve enablement</t>
+  </si>
+  <si>
+    <t>No policy defined yet for unreviewed suggestions at the gate.</t>
+  </si>
+  <si>
+    <t>Open - pending team's answer (block vs warn).</t>
+  </si>
+  <si>
+    <t>E1 (tooling): cross-tenant upstream-artifact clone command (ideation-&gt;architecture + their S3 bodies) for the multi-repo test - write-only to the new tenant</t>
+  </si>
+  <si>
+    <t>For the multi-repo test, copy the prior-phase artifacts (ideation, requirements, PRD, architecture) + their S3 bodies from the old tenant into the new multi-repo tenant, so UX + Task Breakdown can run natively there. Reads the old tenant, writes only the new one (old tenant untouched). Remaps tenant/project/run + UUIDs; copies S3 objects to new keys + rewrites pointers. Transactional with --dry-run + tests.</t>
+  </si>
+  <si>
+    <t>Tooling / Tenancy / Registry</t>
+  </si>
+  <si>
+    <t>New Component (tooling)</t>
+  </si>
+  <si>
+    <t>new backend Django management command; reads apps/registry + S3 (drafts/{tenant}/{project}/{run}/{phase}/{file}); run as sdlc_migrator</t>
+  </si>
+  <si>
+    <t>No tenant/project clone capability exists; DB-only copy is insufficient (S3 bodies + ID remap).</t>
+  </si>
+  <si>
+    <t>Open - build after A/B/C; needs the team's new tenant + project ids.</t>
+  </si>
+  <si>
+    <t>Code host connect form shows a single 'Repository' field on multi-repo projects - reads as single-repo; should be labeled 'Default repository' with a hint that the token must cover ALL repos</t>
+  </si>
+  <si>
+    <t>On a multi-repo project, Integrations &gt; Code host presents one 'Repository' input. The codehost capability is tenant-wide (one connection/token covers every repo; each build targets its own repo via work_item.repo), so this field is only a fallback default - not a per-repo binding. But the lone field looks single-repo and leaves users unsure which repo to enter or whether both are covered. UX-only; functionally correct (both repos flip to 'connected' once any code-host connection is configured).</t>
+  </si>
+  <si>
+    <t>Integrations / Code host / Multi-repo</t>
+  </si>
+  <si>
+    <t>Enhancement (UX)</t>
+  </si>
+  <si>
+    <t>frontend Integrations code-host connect form (S-12 Connect capability); backend/apps/projects/repos.py _codehost_status (tenant-wide status); backend/integrations/registry.py _build_github (default_repo fallback)</t>
+  </si>
+  <si>
+    <t>The code-host connect form predates multi-repo. The 'Repository' field is the connection's default/fallback repo, but is not labeled as such, so on a multi-repo project it looks like you must pick one repo.</t>
+  </si>
+  <si>
+    <t>Open - P2, team to address later. Relabel to 'Default repository (optional)'; add a hint that ONE token must reach ALL of the project's repos (a classic PAT with repo scope, or a fine-grained token listing each repo); optionally list the project's repos + connected status inline so it's clear all are covered.</t>
+  </si>
+  <si>
+    <t>Project topology auto-derives from repo count (2=split, 3+=multi) and overrides the user's explicit 'Multi-repo' choice; the create form offers only Single/Multi (2 options) while the model has 3 (single/split/multi)</t>
+  </si>
+  <si>
+    <t>On create the user picks Single or Multi-repo (sets project.repo_topology). But adding repositories recomputes it via _topology_for (count&gt;=3 -&gt; multi, ==2 -&gt; split, else single). So a user who explicitly chose 'Multi-repo' and added 2 repos ends up with topology='split' in the DB, while the create choice (and at least one screen) showed 'multi'. Effects: (a) the explicit choice is silently overridden; (b) the 2-option create UI never exposes 'split'; (c) features gated on topology=='multi' (e.g. API-contract/drift checks - per the Repositories page copy) would NOT fire for a 2-repo 'split' project (may be intended - confirm). NOTE: does NOT affect the repo-assignment feature (Option C), which keys off repo COUNT&gt;1, so 2 repos work regardless.</t>
+  </si>
+  <si>
+    <t>Projects / Repositories / Topology</t>
+  </si>
+  <si>
+    <t>Issue (Consistency/UX)</t>
+  </si>
+  <si>
+    <t>frontend CreateProject (Single/Multi toggle); backend/apps/projects/repos.py _topology_for (recompute on add/remove); projects_project.repo_topology; Repositories page Topology chip + 'Multi-repo drives API-contract &amp; drift checks' copy</t>
+  </si>
+  <si>
+    <t>Two sources of truth for topology: the create-form choice and the count-derived value. Adding repos recomputes and can override the explicit pick; the create UI exposes 2 options while the model has 3.</t>
+  </si>
+  <si>
+    <t>Open - P3, later. Pick one source of truth: (a) honor the user's explicit choice and stop auto-deriving, or (b) always derive from count and clarify the labels so a 2-repo project still reads as multi to the user. Confirm whether API-contract/drift checks intentionally require 3+ repos ('multi') vs 2 ('split').</t>
+  </si>
+  <si>
+    <t>A backend/worker restart drops the local companion and it does NOT auto-reconnect - the companion stops heartbeating/polling, and a run dispatched right after is left unclaimed until the companion is manually restarted</t>
+  </si>
+  <si>
+    <t>Observed on SpendLog-1 (new multi-repo tenant): after a 'docker restart backend worker' (needed to load mcp_platform_state changes), the companion last_seen froze at the restart time and never resumed. A Task Breakdown triggered right after was dispatched but its dispatch stayed status=pending (never claimed) and the agent never started. Manually reconnecting with the SAME token restored it (enrollment cc5de985 re-claimed the pending run and proceeded). Recoverable, but the companion should survive / auto-reconnect a transient backend restart instead of dying silently. Related to rows 61 (companion false-offline) and 89 (takeover-timeout).</t>
+  </si>
+  <si>
+    <t>Companion / Runner / Reliability</t>
+  </si>
+  <si>
+    <t>runner/companion daemon (serve loop + 30s heartbeat thread); a backend restart drops the HTTP connection; runs_runnerenrollment.last_seen freezes; run dispatch stays status=pending (never claimed)</t>
+  </si>
+  <si>
+    <t>The companion's heartbeat/work-poll loop doesn't robustly survive the backend going away and returning (transient connection loss on restart) - it stops rather than retrying until reconnected.</t>
+  </si>
+  <si>
+    <t>FIXED (2026-07-14). The companion now survives a backend/worker restart instead of silently dying (a docker restart surfaces as a connection error/OSError on the long-poll, not an HTTP status - previously that escaped the serve loop and killed the daemon). Changes in runner/companion/daemon.py: (1) serve() catches connection-level errors from the work-poll and retries forever with capped exponential backoff (poll interval doubling up to 60s), logging 'backend unreachable... reconnecting in Ns' and 'backend reconnected; resuming'; (2) _report() retries a finished phase/build report through a transient outage (~2 min of backoff) so completed work is not lost to a restart at report time; HTTP 4xx/5xx answers still fail immediately. The 30s heartbeat already swallowed its own failures and resumes by itself. Tests: backend/tests/test_companion_daemon.py::test_claim_survives_backend_outage_and_resumes, test_report_retries_through_transient_outage, test_report_gives_up_after_bounded_retries. Operational note: a plain backend/worker restart now needs NO manual companion action; reconnecting with the SAME token only matters if the companion process itself is killed.</t>
+  </si>
+  <si>
+    <t>Task Breakdown gate repo-assignment review (B2) renders cramped in the narrow gate sidebar (titles wrap one word per line, dropdown overlaps) and lists all 32 tasks with full reasons instead of collapsing the confident groups - does not match the approved full-width mockup S-23b</t>
+  </si>
+  <si>
+    <t>Live on SpendLog-1: the Task Breakdown gate opened and the review panel (RepoAssignmentReview) rendered, but (a) it was wired INTO the narrow right-hand gate decision Card (the right column of grid--detail), so at that width task titles + reason + repo dropdown wrap one word/char per line and overlap - not human readable; (b) it renders EVERY one of the 32 tasks with its full rationale rather than surfacing the 2 low-confidence tasks and collapsing the confident backend/frontend groups (the S-23b mockup collapses them with '+N more'). Net: broken layout + verbose noise, doesn't match the developed screen. Underlying data is correct (32/32 assigned, 17 backend / 15 frontend, correct classification).</t>
+  </si>
+  <si>
+    <t>Frontend / Gates / Task Breakdown review</t>
+  </si>
+  <si>
+    <t>frontend/src/features/lifecycle/Gates.tsx (review rendered inside the narrow grid--detail right card); frontend/src/features/lifecycle/RepoAssignmentReview.tsx (renders all rows, no group collapse); mockup docs/design/screens/S-23b-repo-assignment-flow.html (full-width, collapsed confident groups)</t>
+  </si>
+  <si>
+    <t>B2 was wired into the existing narrow gate decision card instead of a full-width surface, and the component renders all rows without the mockup's confident-group collapse. The mockup was designed full-width; the integration was not.</t>
+  </si>
+  <si>
+    <t>Fixing now: render the review FULL-WIDTH when present (stack, not the narrow grid column); add a summary (split counts) + COLLAPSE the confident repo groups (expand on click) + keep the low-confidence flagged tasks expanded at the top; tighten rows so title + repo dropdown sit side by side.</t>
+  </si>
+  <si>
+    <t>Implementation/build companion was single-repo by construction - could not land code in the correct repo on a multi-repo project (Hybrid Option C blocker)</t>
+  </si>
+  <si>
+    <t>Pre-build audit before the SpendLog-1 (frontend+backend) implementation run: the backend routes every build to work_item.repo and opens/merges the PR against that exact repo (trigger.py:171-186, build_activities.py open_build_pr/merge), and build is fully SoR-agnostic (internal + Jira both build off platform WorkItem rows with repo intact). BUT the local companion daemon held ONE --repo-path for its whole lifetime and forked every work item's worktree from it, pushing to that clone's origin - ignoring BuildTask.repo entirely (daemon.py:119/195-208, runner.py:152-164; task.repo referenced nowhere in runner/). On a 2-repo project the repo NOT wired into --repo-path would either fail at 'git worktree add' (base branch absent) or, worse, silently push to the wrong repo if a same-named branch existed, after which open_build_pr 404s looking for the head under the correct repo. Violates the non-negotiable 'code lands in the correct GitHub repo'.</t>
+  </si>
+  <si>
+    <t>Runner / Companion / Build (implementation phase)</t>
+  </si>
+  <si>
+    <t>runner/companion/__main__.py (serve --repo NAME=PATH); runner/companion/daemon.py (_resolve_repo_path, _run_build); runner/companion/runner.py (assert_remote_matches before push); runner/companion/worktree.py (assert_remote_matches); backend/tests/test_companion_daemon.py + test_companion_runner.py; docs/PHASE_2_BUILD_SPEC.md</t>
+  </si>
+  <si>
+    <t>The companion build mode was written for the pre-multi-repo (single-repo) world: one --repo-path clone served every task. BuildTask.repo (work_item.repo) was delivered in the dispatch payload but never consumed to pick a clone; there was no repo-&gt;local-path resolver and no clone-on-demand.</t>
+  </si>
+  <si>
+    <t>FIXED. Added a repeatable 'serve --repo owner/name=/path' mapping; the daemon now resolves the clone per BuildTask.repo (_resolve_repo_path) and FAILS LOUD on an unmapped repo instead of falling back to a wrong clone (that build is reported failed, the daemon keeps serving). --repo-path kept as the single-repo shorthand (backward compatible). Defense-in-depth: assert_remote_matches refuses to push if the clone's origin doesn't match the routed repo (hosted remotes only; local/test remotes skipped). Docs updated (PHASE_2_BUILD_SPEC 3) incl. the single GITHUB_TOKEN must cover all mapped repos (see S.No 103). 36 companion tests pass (added: mapped-clone routing, unmapped fail-loud, shorthand back-compat, origin match/mismatch/local-skip, repo-map parse).</t>
+  </si>
+  <si>
+    <t>Multi-repo: a work item with no repo assigned silently built into the project default repo (e.g. backend code PR'd into the frontend repo) instead of failing</t>
+  </si>
+  <si>
+    <t>trigger_build fell back to the project's is_default Repository whenever a work item had no repo pinned (trigger.py:173-183). Correct for single-repo projects, but on a multi-repo project (Hybrid Option C) an unpinned work item means the Task Breakdown gate assignment was missed - silently defaulting routes it into whatever repo happens to be default (often the frontend), landing code in the wrong GitHub repo. A mis-route, not a hard failure, so it would pass unnoticed.</t>
+  </si>
+  <si>
+    <t>Backend / Orchestration / Build trigger</t>
+  </si>
+  <si>
+    <t>backend/orchestration/trigger.py; backend/tests/test_build_trigger_api.py</t>
+  </si>
+  <si>
+    <t>The default-repo fallback predates multi-repo. It was written so a task could be built from the UI without pinning a repo (single-repo projects, proposed items). It didn't distinguish single-repo (safe to default) from multi-repo (must be explicitly assigned).</t>
+  </si>
+  <si>
+    <t>FIXED. trigger_build now counts the project's repositories: for a multi-repo project (repo_count &gt; 1) an unpinned work item raises a clear TriggerError telling the user to assign its repo (confirm at the Task Breakdown gate or set the work item's repo) - never silently defaults. Single-repo projects keep the default-repo fallback unchanged. Tests added: multi-repo unpinned -&gt; 400 'multiple repositories'; multi-repo pinned to the non-default repo -&gt; builds into that repo with its base. 7/7 build-trigger tests pass.</t>
+  </si>
+  <si>
+    <t>Repo-assignment review panel resurfaces on non-Task-Breakdown gates (the merge gate, and any later phase gate) - it must render ONLY on the Task Breakdown gate</t>
+  </si>
+  <si>
+    <t>Live on SpendLog-1: the implementation MERGE gate for TASK-001 rendered the Task Breakdown repo-assignment review panel ('31 tasks, backend 14 / frontend 15, 2 need review - confirm or change the repo'). Proposed sibling tasks keep their planner repo_assignment long after Task Breakdown, so the panel wrongly reappears on the merge gate - and would also reappear on a later testing/security/deployment phase gate opened while tasks are still proposed.</t>
+  </si>
+  <si>
+    <t>Frontend / Gates / Multi-repo (Option C)</t>
+  </si>
+  <si>
+    <t>Bug (regression)</t>
+  </si>
+  <si>
+    <t>frontend/src/features/lifecycle/Gates.tsx (showReview); backend/api/serializers.py (ApprovalSerializer); frontend/src/types.ts (Approval); follow-up to S.No 106</t>
+  </si>
+  <si>
+    <t>S.No 106 made the review full-width and wired it into Gates.tsx, but the render condition (showReview = multiRepo &amp;&amp; assignmentItems.length&gt;0) never checked WHICH gate is selected. All planning gates share gate_type 'phase_gate' (only the build gate is 'merge_gate'), so gate_type alone is not a safe discriminator - a testing/security/deployment phase gate would also resurface it.</t>
+  </si>
+  <si>
+    <t>FIXED (2026-07-14). The Approval API now exposes `phase` (the gate run's agent key, e.g. 06_task_breakdown) via ApprovalSerializer; the frontend Approval type carries it; Gates.tsx gates the panel on isTaskBreakdownGate = (selected?.phase === '06_task_breakdown'), so showReview = multiRepo &amp;&amp; isTaskBreakdownGate &amp;&amp; assignmentItems.length&gt;0. The review now renders ONLY on the Task Breakdown gate - never on the merge gate or any future phase gate. Tests: backend test_frontend_integration approval-shape + new phase-field test (3 pass); frontend tsc clean; RepoAssignmentReview.test.tsx (3 pass). To view: backend uvicorn --reload picks up serializers.py automatically; restart ONLY the frontend container (bind-mounted ./frontend) so the companion is not dropped.</t>
+  </si>
+  <si>
+    <t>08 code review poll times out (480s) and a late/absent review report is not reconciled - the merge gate opens via the fail-safe with ZERO findings even though the review never completed</t>
+  </si>
+  <si>
+    <t>Live on SpendLog-1 TASK-001: the 08 review task was dispatched and CLAIMED by the companion (06:07:33 UTC) but no verdict was ever posted within the 480s poll window; review.timeout fired at 06:15:52 and the merge gate opened at 06:15:54 with 0 findings and no code_review artifact. poll_review_body treats a timeout as 'no findings' so the build never hangs (by design) - but the reviewer then approves with NO automated review having run. A review report arriving after the timeout (record_review_report) writes review_body once the poll has already returned, so it is orphaned - never parsed into findings. Parallels S.No 89 (a late report cannot reconcile a closed step).</t>
+  </si>
+  <si>
+    <t>Orchestration / Code review (08) / Build pipeline</t>
+  </si>
+  <si>
+    <t>backend/orchestration/review_provider.py (CompanionReviewProvider timeout=480.0 / poll_review_body / record_review_report); backend/orchestration/build_workflow.py (run_code_review loop); related S.No 89</t>
+  </si>
+  <si>
+    <t>The review poll timeout (480s / 8 min) is shorter than a realistic FIRST companion review (cold engine start + context compaction can add ~7 min). When it trips, timeout is treated as zero blocking findings and the merge gate opens; a review report arriving after the timeout is recorded but never re-parsed, so its findings are silently lost.</t>
+  </si>
+  <si>
+    <t>FIXED (2026-07-14, committed a582737). Three-part fix in the review path: (1) BuildInput.review_timeout_seconds is now per-run configurable with a realistic default of 1800s (was a hard-coded 480s that was shorter than a first cold-companion review); (2) poll_review_body does one final grace read on timeout, so a verdict that lands moments after the last poll tick still drives the 07&lt;-&gt;08 remediation loop instead of being orphaned in run.outputs while the merge gate opens blind; (3) build_workflow.py sets the run_code_review activity start_to_close = review_timeout_seconds + 600s, so the Temporal activity timeout always exceeds the internal poll window (otherwise Temporal would kill and retry the activity mid-review, re-dispatching it). The companion provider reads getattr(inp,'review_timeout_seconds') and falls back to its own default, so an older backend that predates the field is safe. Tests: test_review_dispatch (grace-read + per-run-timeout), ruff clean. This is the review-side analog of S.No 89 (phase-side late-report reconcile, still open for the co-dev team).</t>
+  </si>
+  <si>
+    <t>Claim lease vs review window: a phase that legitimately runs longer than the 15-min work-claim lease (e.g. a code review now allowed up to 30 min) is re-claimed mid-flight from a LIVE, heartbeating companion -&gt; duplicate/empty artifacts + a failed re-review, and the merge gate opens blind</t>
+  </si>
+  <si>
+    <t>Surfaced right after the S.No 110 fix, on SpendLog-1 TASK-001 (run e2c57de8). The 08 review legitimately took ~19 min (S.No 110 raised the review poll window to 30 min), exceeding the 15-min CLAIM_LEASE. The still-running review's claim went stale so a later /api/runner/work/ poll RE-CLAIMED it (phase.reclaimed x2) even though the companion was alive and heartbeating (last_seen fresh). The churn produced (a) a duplicate EMPTY 'assumption' artifact (external_ref null, no s3_key -&gt; would not preview) and (b) a FAILED final review report (review_status='failed', empty body) -&gt; 0 findings -&gt; the merge gate opened without a valid review.</t>
+  </si>
+  <si>
+    <t>Companion / Runner / Claim lease vs review window</t>
+  </si>
+  <si>
+    <t>Bug (regression from S.No 110)</t>
+  </si>
+  <si>
+    <t>backend/api/runner_views.py (CLAIM_LEASE, RunnerWorkClaimView re-claim, RunnerHeartbeatView, _renew_claims_for); backend/orchestration/review_provider.py (review_timeout_seconds=1800); related S.No 110, 89, RC-2/RC-3</t>
+  </si>
+  <si>
+    <t>The 15-min claim lease is meant to detect a DEAD companion, but it keyed off 'time since the claim was stamped', not liveness. S.No 110 legitimately extended the review to run up to 30 min &gt; the 15-min lease, so a live companion's claim expired mid-review and the run was re-claimed. The heartbeat kept last_seen fresh (liveness) but did NOT refresh claimed_at, so the lease expired despite the companion being provably alive - the lease comment even says it 'MUST exceed the longest real phase'.</t>
+  </si>
+  <si>
+    <t>FIXED (2026-07-14). The heartbeat now renews claimed_at for the companion's in-flight (PENDING/RUNNING, still 'claimed') runs (_renew_claims_for in runner_views.py, called by RunnerHeartbeatView; returns claims_renewed). So a heartbeating companion's claim never goes stale no matter how long the phase runs, while a truly dead companion still gets re-claimed ~15 min after its LAST heartbeat (dead-companion recovery preserved). Only in-flight claimed runs are touched - a reported/gated run is never revived. This ties the lease to LIVENESS, not task duration, so it is robust for any long phase, not just reviews. Tests: test_phase_dispatch::test_heartbeat_renews_claim_so_a_long_live_phase_is_not_reclaimed + test_heartbeat_does_not_renew_a_reported_claim (19 pass, ruff clean). Backend auto-reloads runner_views.py (uvicorn --reload) so no container restart / no companion drop. NOTE: the compromised run e2c57de8 must be disposed + re-run (its gate opened on a failed review).</t>
+  </si>
+  <si>
+    <t>Shared Temporal queue + per-worker GitHub token: with two dev workers on the shared 'sdlc-planning' queue, a build's open_build_pr activity can run on the OTHER dev's worker, which uses THAT worker's server .env GITHUB_TOKEN -&gt; 404 on the target repo -&gt; build marked failed even though the code built + pushed fine</t>
+  </si>
+  <si>
+    <t>Observed on SpendLog-1 (multi-user shared-AWS): TASK-001 build (run 5bc08ea2, RAGUWING369/SpendLogTest-1-backend) failed at 'pr/gate setup failed'. The worker logs showed the 404 was for a DIFFERENT tenant's repo (Tarun51/medslot-single-repo, run 3187519e) - proving the two dev workers cross-executed each other's build activities. Each worker authenticates GitHub from its own .env token (settings.GITHUB_TOKEN) scoped to that dev's repos, so a build landing on the wrong worker 404s. The companion build itself succeeded (report ok, branch pushed); only the platform-side PR step failed.</t>
+  </si>
+  <si>
+    <t>Integrations / Code host / Multi-user / Shared Temporal</t>
+  </si>
+  <si>
+    <t>backend/integrations/registry.py (_build_github); backend/integrations/github/config.py (GithubConfig.from_connection); deploy/shared-aws (two workers, one queue); related S.No 74</t>
+  </si>
+  <si>
+    <t>The codehost authenticated from the server .env (settings.GITHUB_TOKEN), NOT the tenant's own stored credential. On a shared task queue an activity runs on whichever worker is free, so the wrong dev's token was used. The per-tenant token was already stored in the shared DB (IntegrationConnection.secret_encrypted) but was never read (this is S.No 74 for the codehost).</t>
+  </si>
+  <si>
+    <t>FIXED (2026-07-14, Phase A). _build_github now builds the config via GithubConfig.from_connection(conn), which decrypts the tenant's own IntegrationConnection.secret_encrypted (the access_token the connect form stored) and uses it; falls back to settings.GITHUB_TOKEN only when no per-tenant secret exists (local/CI/back-compat). Because the credential lives in the SHARED DB and travels with the tenant, ANY worker that runs a build for that tenant uses the correct token - the cross-worker mismatch is now structurally impossible, so multiple devs can run workflows concurrently without stopping each other's worker. Core logic verified (per-tenant token used / settings fallback / two-tenant isolation all pass) + 3 new tests in test_capability_registry + ruff clean; full DB-backed test run pending local Docker (was down at fix time). Requires the tenant to have connected its Code host with a token - SpendLog-1 already has one stored (has_secret=True).</t>
+  </si>
+  <si>
+    <t>Phase B (extend S.No 74): wire per-tenant credentials into the remaining connectors (Atlassian Confluence/Jira, Figma, Xray) so planning-phase system-of-record pushes also use the tenant's stored token on any worker, not the server .env</t>
+  </si>
+  <si>
+    <t>Phase A (S.No 112) fixed the codehost (GitHub) to use per-tenant credentials from the shared DB. The other connectors still authenticate from the server .env (AtlassianConfig / FigmaConfig / XrayConfig .from_settings()), so on a shared multi-worker setup a planning-phase SoR push (publish to Confluence/Jira, Figma read, Xray import) could use the wrong tenant's creds or fail - the same class of bug as S.No 112, for the non-codehost capabilities.</t>
+  </si>
+  <si>
+    <t>Integrations / Connectors / Multi-user</t>
+  </si>
+  <si>
+    <t>Enhancement (follow-up)</t>
+  </si>
+  <si>
+    <t>backend/integrations/registry.py (_build_confluence/_build_jira/_build_figma/_build_xray + _atlassian_config); backend/apps/integrations/catalog.py; related S.No 74, S.No 112</t>
+  </si>
+  <si>
+    <t>Same root cause as S.No 112 (connectors authenticate from the server .env, not per-tenant DB creds). Phase A did only the codehost because it was the build-workflow blocker. The Atlassian connectors also need email + site_url, which are NOT in the connect form's catalog yet, so this is a larger change (catalog + form fields + config wiring) - hence deferred.</t>
+  </si>
+  <si>
+    <t>Open - follow-up to Phase A. Plan: (1) add email/site_url (or equivalent) fields to the Atlassian vendors in catalog.py + the connect form; (2) change _atlassian_config to take the conn and decrypt api_token + read email/site_url from scopes; (3) same decrypt-and-use for Figma access_token and Xray client_id/client_secret; (4) keep the settings fallback for back-compat; (5) tests per connector + a two-tenant isolation test. Not blocking now - SpendLog-1 is sor=internal with no non-codehost connections configured.</t>
+  </si>
+  <si>
+    <t>Blocking code review silently 'passes' (fail-OPEN): the 07&lt;-&gt;08 remediation loop reads blocking findings ONLY from the json verdict block in the 08 agent's FINAL message. When the agent's final message is prose (its machine-readable json block missing / not last / delivered via a separate event) the platform parses 0 findings, counts 0 blocking, SKIPS remediation and opens the merge gate on an unreviewed downgrade.</t>
+  </si>
+  <si>
+    <t>Observed live on SpendLog-1 (multi-repo), run 8ab6f89a, PR RAGUWING369/SpendLogTest-1-backend#3. The 08 review ran fine and produced a real verdict: review.completed logged status=CHANGES_REQUIRED with 5 blocking_findings (REM-C1 + REM-W1..W4, incl. PR-&gt;main-not-develop, /docs live in prod, no global exception handler, unbounded SECRET_KEY). But the review_body the companion posted back was only a 1,723-char prose executive summary with ZERO ```json blocks, so parse_findings returned [] -&gt; build.reviewed logged {blocking:0, findings:0} -&gt; gate.opened (merge) with no remediation loop. Distinct from S.No 110/111 (those were review-window/claim-lease timing); here the review reported in-window, claim_count stayed 1 - the defect is verdict serialization + a fail-OPEN default.</t>
+  </si>
+  <si>
+    <t>Orchestration / Code review / 07&lt;-&gt;08 remediation loop</t>
+  </si>
+  <si>
+    <t>backend/orchestration/review_provider.py (parse_findings/_extract_verdict/_looks_blocking/parse_and_guard, ReviewContractError); backend/orchestration/build_activities.py (run_code_review_core); backend/orchestration/build_workflow.py (run_code_review activity -&gt; mark_build_failed on ActivityError); agents/08_code_review/agent.md (Output contract); runner/companion/daemon.py (posts result text as review_body); related S.No 110</t>
+  </si>
+  <si>
+    <t>Two compounding defects. (1) Fragile contract: the platform sources blocking findings from the agent's free-text final message (daemon posts outputs.result as review_body; parse_findings scans only that for the LAST ```json block). Any run where the agent puts prose last, or emits the verdict via a tool/event, silently breaks the parse. (2) Fail-OPEN default: when the parse yields nothing the loop treats it as 'clean' (open_blocking==0) and opens the merge gate - the WRONG direction (same lesson as S.No 110, opposite failure).</t>
+  </si>
+  <si>
+    <t>FIXED (2026-07-14). Three-layer fix + tests. (Fix 1 - agent) agents/08_code_review/agent.md Output section hardened: the FINAL message MUST end with exactly one fenced json verdict block and NOTHING after it; forbids delivering the verdict only via a tool/event or appending a prose summary; both the code_review artifact body AND the final-message json are required. (Fix 2 - robust parse) _extract_verdict scans ALL json blocks and takes the last that parses AND looks like a verdict (has status/findings), tolerant of illustrative json + trailing prose. (Fix 3 - FAIL CLOSED) new parse_and_guard: if the body signals blocking (a REM-C/REM-W id or CHANGES_REQUIRED) but 0 blocking findings parse, it logs review.parse_mismatch and raises ReviewContractError; run_code_review retries (cap 3) then BuildWorkflow catches ActivityError -&gt; mark_build_failed, so the merge gate is NEVER opened on an unreviewed downgrade. Empty body (review timeout) keeps returning [] (human gate still applies, S.No 110). Tests: 7 new in test_review_dispatch (robust parse, clean pass-through, empty-body, fail-closed + event, provider-level fail-closed) + test_agents_migration (08 states the final-message json contract); all pass, ruff clean. Both companion + server providers guarded. Run 8ab6f89a disposed + PR #3 closed; team re-runs the phase.</t>
+  </si>
+  <si>
+    <t>07&lt;-&gt;08 remediation loop hangs forever: when the code review returns blocking findings, dispatch_remediation re-runs the implementation agent (07) on the same branch to fix them. But the remediation dispatch never re-armed the companion claim block, so the companion had nothing to pull -&gt; the 07 agent never re-ran -&gt; no second build report -&gt; the BuildWorkflow waited on build_reported until timeout -&gt; mark_takeover. The remediation cycle could never complete.</t>
+  </si>
+  <si>
+    <t>Found by studying live cloud Temporal history (13.203.56.29:7233) for two devs' concurrent build runs. build-run-fe891eb9 sequence: dispatch_build -&gt; open_build_pr -&gt; run_code_review -&gt; dispatch_remediation -&gt; mark_takeover, with EXACTLY ONE build_reported signal (the initial build only). build-run-8f9dec1d (other tenant) identical, still stuck waiting after dispatch_remediation. Crucially 8f9dec1d ran on a SINGLE worker yet is stuck identically to the two-worker fe891eb9 - disproving the team's 'workers cross-pick activities' theory. Temporal replays workflow state consistently regardless of which worker runs each activity; multi-worker execution is normal and harmless. The two devs saw two faces of the same broken loop: Dev A stuck/takeover (this bug); Dev B gate opened with no remediation (S.No 114 fail-open, fixed same day).</t>
+  </si>
+  <si>
+    <t>Orchestration / Build / 07&lt;-&gt;08 remediation loop / Companion dispatch</t>
+  </si>
+  <si>
+    <t>backend/orchestration/build_activities.py (dispatch_remediation_core + new _render_remediation_section); compares dispatch_build_core; backend/api/runner_views.py (RunnerWorkClaimView claim filter status in pending/claimed); runner/companion/daemon.py (poll-&gt;claim-&gt;run-&gt;report loop, no self-loop); related S.No 114</t>
+  </si>
+  <si>
+    <t>dispatch_remediation_core wrote only inputs['remediation'] + status=RUNNING; it never set inputs['dispatch'] to a pending BUILD claim block (left as the review's kind=review/status=reported, which the claim query ignores) and never rebuilt build_task with the remediation brief. The companion daemon is a strict poll-&gt;claim-&gt;run-&gt;report loop with no remediation self-loop, so /api/runner/work/ returned 204 forever. The 07&lt;-&gt;08 companion handoff for remediation was simply never wired. It escaped tests because test_review_dispatch only exercised run_code_review_core opening child WorkItems, never the dispatch-&gt;claim-&gt;report cycle. Blocker surfaced only after S.No 114 (fail-open) was fixed - fixing 114 makes a blocking review correctly ENTER the remediation branch, which then hit 115.</t>
+  </si>
+  <si>
+    <t>FIXED (2026-07-15). dispatch_remediation_core now mirrors dispatch_build_core's companion handoff: recomposes the 07 manifest via compose_manifest_core and appends a '# Remediation Items' section rendering the open REM brief (rem/severity/title/file:line) - same idea as the reviewer's PR-diff section; rebuilds the full build_task payload (manifest+agent_body+model+repo/base/work_item title/type, remediation:True); and sets inputs['dispatch']={kind:build, enrollment_id:inp.enrollment_id, status:pending} so the companion claims it via /api/runner/work/ and re-runs 07 on the SAME branch. open_build_pr stays outside the loop (idempotent) so the existing PR just gets new commits. Companion side needed NO change: worktree path is deterministic per WI, teardown after each build, provision_worktree re-attaches the existing feature branch, push is a fast-forward. No workflow change: build_workflow already dispatches then waits for build_reported. Tests: 2 new in test_review_dispatch (dispatch arms pending build claim + REM brief in manifest; /api/runner/work/ returns the remediation build) - 19 pass; test_build_activities 11 pass (no regression); ruff clean. Verification watches for a SECOND build_reported signal in the workflow history (absent in every run to date) = proof the handoff works.</t>
+  </si>
+  <si>
+    <t>Code review flags PR-size (and other Step-1 hygiene checks) as a blocking CRITICAL, driving an UNWINNABLE 07&lt;-&gt;08 remediation loop: the 08 agent's Step-1 PR Hygiene gate treats any failing check (PR size &gt;400 lines, commit-message format, branch name, PR description, linear history) as a blocking REM-C. But the platform re-runs the IMPLEMENTATION agent on the SAME branch for every blocking finding, and it cannot split a PR, rename a branch, rewrite the platform-generated commit message, or otherwise fix a hygiene issue in code -&gt; the finding recurs every cycle -&gt; the loop churns until max_remediation_cycles (3) exhausts -&gt; the build FAILS, even though the code is fine.</t>
+  </si>
+  <si>
+    <t>Observed live on SpendLog-1 build run 1377dee3 (TASK-001 .venv/FastAPI scaffold). Review cycle 1 = 4 blocking (REM-C1 PR-size ~590 lines, REM-C2 CORS, REM-W1 no-op test, REM-W2 python-jose). The 3 real code defects were fixed across cycles (done); REM-C1 'PR size ~590 lines exceeds 400-line threshold' stayed blocking every cycle (blocking count stuck at 1: cycle1=4 -&gt; cycle2=1 -&gt; cycle3=1) because a legitimate bootstrap scaffold cannot be shrunk below 400 lines. Heading to 'remediation cycles exhausted' at cycle 4. The 08 agent even acknowledges (run 8ab6f89a) PR-size for a bootstrap scaffold is 'justified ... document as a permitted exception rather than triggering a code remediation loop' - yet still emitted it as blocking. Confirmed S.No 114 + 115 fixes worked (2-3 build_reported, loop converged 4-&gt;1); this is a DISTINCT design bug the working loop exposed.</t>
+  </si>
+  <si>
+    <t>Agents / 08 Code Review / Remediation loop classification</t>
+  </si>
+  <si>
+    <t>agents/08_code_review/agent.md (Step 1 PR Hygiene gate, lines ~62-76: 'Any check that fails -&gt; CRITICAL'); backend/orchestration/build_activities.py (_BLOCKING treats REM-C/REM-W as blocking); related S.No 114, 115</t>
+  </si>
+  <si>
+    <t>Step 1 hygiene checks are either platform-OWNED (D2: the platform generates the commit message, branch name, PR description, and keeps history linear - the 07 agent never touches git) or NON-CODE (PR size). None can be remediated by re-running 07 on the same branch, so classifying them as blocking REM-C/REM-W guarantees an unwinnable loop. PR size is inherently a human/process judgment (split the PR) or a justified exception (scaffold/migration), not a code defect - it belongs at the human merge gate, not in the automated loop.</t>
+  </si>
+  <si>
+    <t>FIXED (2026-07-15). agents/08_code_review/agent.md Step 1 reclassified: a failing hygiene check is now a NON-BLOCKING Suggestion (REM-S) for the human merge-gate reviewer, never a blocking REM-C/REM-W. The body now states the rationale (platform-owned or non-code -&gt; the 07 loop cannot fix them -&gt; blocking would create an unwinnable loop that exhausts the cap) and directs a genuinely un-reviewable PR to be RETURNED BY THE HUMAN reviewer at the gate, not the automated loop; PR-size overage is still reported (with generated/lock/migration exemptions + justified-or-not note) but as a Suggestion. Framework note aligned. Tests: test_agents_migration.test_code_review_hygiene_findings_are_non_blocking (asserts non-blocking-suggestion classification + rationale present + old 'any check that fails -&gt; CRITICAL' gone) - 2 pass. Agent body is file-loaded (_load_agent_body) so the fix is live on the next dispatch, no re-seed/worker restart. Run 1377dee3 terminated + PR#4 closed + branch deleted + DB reset (WI proposed) for a fresh re-run.</t>
+  </si>
+  <si>
+    <t>In Work Items Page: 
+After the task breakdown phase is run and the work items are created and shown in work items page, the work items are shown in the Ideation phase of work item dashboard. When selected filter ‘tasks’, all the work items are shown in implementation phase.</t>
+  </si>
+  <si>
+    <t>Work Items</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Epics, user stories and tasks description, Acceptance criteria which were created in the task breakdown artifacts should be Humanized.
+In detail: The task breakdown agent is creating the artifacts too technically which a normal user cannot understand and for even technical persons it is written on a high level. The description, acceptance criteria should be understandable and written in detail so that a developer should be able to implement the task manually by reading them if required.
+Note: Because of the inconsistancies in the task break down agent artifacts generation the same issue persists in displaying of the artifacts content in work items and wherever these details are shown for the user/developer.
+</t>
+  </si>
+  <si>
+    <t>In the work items board when clicked on either epic or user story it shows children(3 or 4), instead when clicked on the childern it should show those tasks</t>
+  </si>
+  <si>
+    <t>In Artifacts &amp; Traceability Page:
+The generated artifact names for each phase should be humanised – the current names which are visible in the page are not human readable, Ex: Wireframe is repeated for all wireframes but no mentioning of which screen it is. sample human readable: Wireframe (login-page)
+Note: The same issues applies to the internal artifact content when the user clicked on the preview. You must read all the phase agents to identify what are all the artifacts it generates and how they are represented as names or disply or written.</t>
   </si>
 </sst>
 </file>
@@ -1771,7 +2869,7 @@
 </file>
 
 <file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
-<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="9">
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="13">
   <rv s="0">
     <v>0</v>
     <v>5</v>
@@ -1808,6 +2906,22 @@
     <v>8</v>
     <v>5</v>
   </rv>
+  <rv s="0">
+    <v>9</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>10</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>11</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>12</v>
+    <v>5</v>
+  </rv>
 </rvData>
 </file>
 
@@ -1831,6 +2945,10 @@
   <rel r:id="rId7"/>
   <rel r:id="rId8"/>
   <rel r:id="rId9"/>
+  <rel r:id="rId10"/>
+  <rel r:id="rId11"/>
+  <rel r:id="rId12"/>
+  <rel r:id="rId13"/>
 </richValueRels>
 </file>
 
@@ -3824,1180 +4942,747 @@
       <c r="G62" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="H62" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Every 'Companion Offline' indicator (global pill, Connect Machine page, Phases &amp; Runs) is driven by ONE derived flag: enrollment.online = (now - last_seen) &lt;= 2 min (apps/runs/enrollment.py). last_seen is refreshed only when the companion calls an authenticated endpoint. Four defects made it go stale / stuck:
-RC-1 (PRIMARY): The companion daemon CRASHED after the first phase. The old assert_subscription_billing() halted the daemon whenever a phase reported a non-zero cost. Current Claude Code reports a computed subscription-equivalent cost (~$1) even on a Max subscription (which is NOT billed per token), so the guard false-positived and killed the daemon right after Ideation reported. A dead daemon stops refreshing last_seen -&gt; UI shows 'Offline / daemon stopped' within 2 min. It ALSO explains 'Requirements runs but never produces artifacts/gate': after the crash no daemon was alive to run the next phase (or it claimed then died), leaving the run stuck 'running'/'claimed' with no report.
-RC-2: Heartbeat starvation. The serve loop is single-threaded (claim -&gt; run_task blocks for the WHOLE phase -&gt; report). While a phase runs the loop never re-polls, so last_seen only refreshes if the agent happens to call a platform-state tool. Any phase quiet for &gt;2 min flips the companion to a FALSE 'Offline' mid-run and disables triggers, though it is healthy and busy.
-RC-3: No re-queue on daemon death. Claiming atomically flips dispatch pending-&gt;claimed with no lease. If the daemon dies before reporting, the run is stranded 'claimed'/'running' forever - no other daemon re-claims it (poll filters status=pending) - no artifacts, no gate, no recovery.
-RC-4: Misleading UI. Offline copy always said 'daemon stopped' with a HARDCODED 'last seen 5m ago' (ConnectMachine.tsx), and label-less re-enrollments each showed as a separate phantom machine card.</t>
-        </is>
-      </c>
-      <c r="I62" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">RC-1 (shipped): removed the assert_subscription_billing halt in runner/companion/daemon.py; ensure_local_engine_auth (env + ~/.claude.json + OAuth checks) is now the SOLE subscription-only guard. Engine cost is reported for reference only, never used as an API-key signal.
-RC-2: added POST /api/runner/heartbeat/ (RunnerHeartbeatView) + a background heartbeat thread in the daemon (CompanionDaemon._run_heartbeat_loop; --heartbeat-interval, default 30s) that refreshes last_seen every 30s independent of run_task, so the companion stays 'online' throughout long phases.
-RC-3: work claims are now a LEASE. RunnerWorkClaimView stamps claimed_at + claim_count on claim; a poll re-claims any run left 'claimed' past CLAIM_LEASE (15 min, &gt; longest phase) with no report, logging phase.reclaimed - so a dead companion's run recovers instead of stranding.
-RC-4: ConnectMachine.tsx now shows the REAL relative last_seen (sinceLabel) and reworded copy ('not reachable - reconnects if mid-phase; else restart'); list_developer_enrollments collapses label-less re-enrollments for the same project into ONE card (represented by the most-recently-seen enrollment) instead of N phantoms.
-TESTS: backend 101 passed / 3 skipped (new: heartbeat endpoint, stale-claim reclaim, enrollment dedup); daemon unit 16 passed (heartbeat posts + failure-safe); frontend 209 passed; tsc clean. Verified in the backend container against Postgres.</t>
-        </is>
-      </c>
-      <c r="J62" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Fixed</t>
-        </is>
+      <c r="H62" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="I62" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="J62" s="2" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="63" spans="1:10" ht="409.6">
       <c r="A63" s="2">
         <v>62</v>
       </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Requirements phase ran a second time by itself — a duplicate 'v2' draft of the same artifact appeared and the companion went offline.</t>
-        </is>
-      </c>
-      <c r="C63" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Found during live testing of the Bug #61 (S.No 61) fix. The Requirements phase completed normally: its artifact (version 1) was previewed, approved at the gate, and the phase showed as done. A few minutes later, without anyone triggering it, the SAME Requirements artifact was generated again as a 'version 2' draft on the Artifacts &amp; Traceability page, and the companion daemon then crashed and showed offline. The approved version 1 was never affected — the only impact was one spurious duplicate draft and the daemon stopping.</t>
-        </is>
-      </c>
-      <c r="D63" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Companion Runner (Phases &amp; Runs)</t>
-        </is>
-      </c>
-      <c r="E63" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bug — regression from the Bug #61 fix</t>
-        </is>
-      </c>
-      <c r="F63" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Regression introduced by the Bug #61 (S.No 61) fix, specifically its RC-3 'claim-lease' auto-recovery. Same run: Requirements run 607d0245; the duplicate was the requirements version-2 draft.</t>
-        </is>
-      </c>
-      <c r="G63" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P1</t>
-        </is>
-      </c>
-      <c r="H63" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The Bug #61 fix added a 'claim lease' safety net: if a companion dies in the middle of a phase without reporting, another poll re-claims the run after 15 minutes so it is not stuck forever. This had a timing race.
-The Requirements phase ran about 17 minutes — longer than the 15-minute lease. When the companion finished and sent its report, the separate step that marks the run as 'reported' happened a moment later (asynchronously, inside the workflow). In that brief gap the run still looked 'claimed', and because the claim was now older than 15 minutes, the companion's very next poll judged it 'stale' and re-claimed its OWN just-finished run — running Requirements a second time and creating the version-2 draft.
-That second run then reported to a workflow that had already completed, which returned a server error the daemon treated as fatal — so the daemon crashed and went offline.</t>
-        </is>
-      </c>
-      <c r="I63" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Three-part hardening (all shipped, tested, and deployed):
-1) The report step now marks the run 'reported' immediately (synchronously) the moment the companion reports, so the very next poll can never still see it as 'claimed'. This closes the re-run race no matter how long the phase ran.
-2) The auto-recovery re-claim now only applies to runs that are still genuinely running — never one that already reached a gate or completed.
-3) The daemon no longer crashes on a late or duplicate report: the backend responds gracefully (not a server error) when a report arrives after its workflow has already finished, and the daemon logs the failed report and keeps running instead of stopping.
-Added automated regression tests for all three. Confirmed behavior for the team: for a normal long phase (e.g. a 30-minute UX Design or Implementation run) on a single companion, no re-claim ever happens — a busy companion is not polling for work, and on finishing it marks the run 'reported' before its next poll. A re-claim triggers ONLY when a companion genuinely dies before reporting. The spurious version-2 draft was removed; only the approved version 1 remains.
-Files: orchestration/phase_report.py, api/runner_views.py, runner/companion/daemon.py. Tests: daemon unit 18 passed; backend suite 134 passed / 2 skipped.</t>
-        </is>
-      </c>
-      <c r="J63" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Fixed</t>
-        </is>
+      <c r="B63" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="D63" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="E63" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="F63" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="G63" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H63" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="I63" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="J63" s="2" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="64" spans="1:10" ht="409.6">
       <c r="A64" s="2">
         <v>63</v>
       </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Planning-phase agent runs with more tools than it should — it can spawn subagents and use Read/Bash/Glob, which leads to slow, non-deterministic runs that register no artifacts (and gives the agent unintended access to the local machine).</t>
-        </is>
-      </c>
-      <c r="C64" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Seen while re-running the Requirements phase on a work item during testing. Unlike the first run — which registered each artifact incrementally, so they appeared in the UI within minutes — this run spent 20+ minutes drafting everything internally by spawning 8 subagents and registered NOTHING to the platform, so the Artifacts page stayed empty and it looked stalled. Reading the engine transcript showed the planning agent using Read, Glob, Bash, ToolSearch and Agent (subagents) — none of which it is supposed to have. A planning phase is meant to run with ONLY the platform-state tools (read the registered context, register its artifacts); it must not spawn subagents or touch the local filesystem/shell.</t>
-        </is>
-      </c>
-      <c r="D64" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Companion Runner / Planning Agent (ClaudeDriver)</t>
-        </is>
-      </c>
-      <c r="E64" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bug</t>
-        </is>
-      </c>
-      <c r="F64" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Observed on Requirements re-run 2cf17e68 (work item 8d6f3b7d) during live testing. Engine transcript showed 8 Agent(subagent) calls and 0 register_artifact calls. Relevant code: backend/drivers/claude_driver.py (allowed_tools / permission_mode) and runner/companion/daemon.py (PLAN_ALLOWED_TOOLS).</t>
-        </is>
-      </c>
-      <c r="G64" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P2</t>
-        </is>
-      </c>
-      <c r="H64" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The planning/review agent was launched with its tool allowlist set to only the platform-state tools, but that allowlist does NOT actually restrict the engine: with the default permission mode, Claude Code still exposes ALL its built-in tools (Read, Write, Edit, Bash, Grep, Glob), the subagent tool (Agent/Task), web search, and — because the companion loaded the user's global Claude Code config — the user's personal skills and extra tools. Planning and review phases run in a fresh EMPTY temporary folder with no repository checked out, so those filesystem/shell/subagent tools can reach nothing useful; they only let the agent wander. In live testing a UX Design run spent its first minutes spawning a subagent to grep an empty folder for artifact IDs instead of using the platform tools, and a Requirements re-run spent 20+ minutes drafting via 8 subagents and registered nothing. It is also a sandboxing/security concern: a planning agent should never have shell/file access to the user's machine.</t>
-        </is>
-      </c>
-      <c r="I64" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Phase-scoped sandbox in backend/drivers/claude_driver.py. Planning and review phases now pass an explicit disallowed-tools list (Agent/Task, Bash, Read, Write, Edit, Glob, Grep, WebFetch, WebSearch, ToolSearch, Skill, TodoWrite, ...) AND setting_sources=['project'] so the engine loads settings only from the empty run folder — never the user's global skills/subagents/MCP. Result: a planning/review agent can use ONLY the platform-state tools it was granted, so it reads context and registers artifacts directly instead of wandering. Implementation/build is deliberately NOT sandboxed — it runs in the real git worktree and must keep Read/Write/Edit/Bash/Grep/Glob to develop code (different code path, BUILD_ALLOWED_TOOLS). Verified live: a full-denylist engine probe returned SANDBOX_LOCKED (subagent + file read + bash all blocked), and a clean UX Design re-run used only platform-state tools (get_context/get_artifact/register_artifact), no subagents, artifacts registering promptly. Tests assert planning/review are sandboxed and build is not.</t>
-        </is>
-      </c>
-      <c r="J64" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Fixed</t>
-        </is>
+      <c r="B64" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="D64" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="E64" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F64" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="G64" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="H64" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="I64" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="J64" s="2" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="65" spans="1:10" ht="409.6">
       <c r="A65" s="2">
         <v>64</v>
       </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">UX Design phase failed right after starting with 'Claude Code not found' — even though the engine was installed and working (earlier phases ran fine).</t>
-        </is>
-      </c>
-      <c r="C65" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Seen while re-running the UX Design phase during testing. The phase started, then immediately failed with 'Claude Code not found at: …\claude.exe'. Two earlier attempts did NOT help because they targeted the wrong cause: (1) switching from the engine's bundled copy to the user's own copy on PATH, and (2) adding an automatic launch retry. The error came back identically both times. Adding a diagnostic that revealed the real operating-system error finally exposed the true cause (see Root Cause).</t>
-        </is>
-      </c>
-      <c r="D65" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Companion Runner / Engine launch (ClaudeDriver)</t>
-        </is>
-      </c>
-      <c r="E65" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bug</t>
-        </is>
-      </c>
-      <c r="F65" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">UX Design runs during live testing (work item 8d6f3b7d). The failure was specific to the UX Design agent; Requirements/other phases were unaffected. Confirmed by a launch diagnostic reporting Windows error 206 ('The filename or extension is too long').</t>
-        </is>
-      </c>
-      <c r="G65" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P1</t>
-        </is>
-      </c>
-      <c r="H65" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">To start a phase, the platform launches the engine and passes the agent its full set of instructions (the 'system prompt') as a COMMAND-LINE argument. Windows limits how long a command line can be — about 32,000 characters total. The UX Design agent's instructions are unusually large (~36,000 characters), so they didn't fit. Windows refused to start the process with a generic 'arguments too long' error (Windows error 206), and the engine library reported that up as the misleading 'Claude Code not found' — even though the engine was right there.
-This is why ONLY the UX Design phase failed: other phases (Requirements, etc.) have smaller instruction sets that fit within the limit. It had nothing to do with a missing engine, the wrong copy of the engine, or antivirus — those earlier theories were wrong.
-Important: this is NOT a 'context too large' problem. The heavy run context (the PRD, past artifacts, code) is already delivered the correct way — as files the agent reads and via on-demand retrieval tools — never on the command line. Only the agent's own static instruction body was being put on the command line, and only the UX one was big enough to overflow it.</t>
-        </is>
-      </c>
-      <c r="I65" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Root cause was correct (Windows command-line length limit, error 206). The first fix delivered the large body as an AGENTS.md file — this stopped the crash, but was later found INSUFFICIENT: Claude Code does not auto-load AGENTS.md (only CLAUDE.md, and only with project setting-sources), and a planning agent has no file-reading tool, so the body still did not reach the model. Superseded by the correct, permanent fix: deliver the agent body + run manifest as a true FILE-BASED SYSTEM PROMPT via the CLI's --system-prompt-file flag (see S.No 65). That removes the command-line limit for any body size AND guarantees the instructions actually reach the model. The 'Claude Code not found' crash is fully resolved.</t>
-        </is>
-      </c>
-      <c r="J65" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Fixed</t>
-        </is>
+      <c r="B65" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="D65" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="E65" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F65" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="G65" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H65" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="I65" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="J65" s="2" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="66" spans="1:10" ht="409.6">
       <c r="A66" s="2">
         <v>65</v>
       </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Large agent phases ran WITHOUT their role instructions and context — the agent produced generic or empty output instead of the platform-grade work it was built for. Affected 7 of the 16 agents whose instruction body exceeds ~24,000 characters, including UX Design, Architecture, Security, Code Review, Testing, and — critically — Implementation and Task Breakdown.</t>
-        </is>
-      </c>
-      <c r="C66" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Found while investigating why the UX Design phase behaved oddly. The platform delivers each agent two things: its role/process instructions (the agent 'body') and its run context (the composed manifest: project profile, upstream artifacts, rules). A recent fix for the UX 'Claude Code not found' crash (S.No 64) had moved large bodies into an AGENTS.md file — but Claude Code never loads AGENTS.md, and planning agents have no file-reading tool, so for every large agent the role body reached the model through NO channel at all. Separately, the composed manifest had also only ever been written to that unloaded AGENTS.md, so its Rules section never reached the model either. The agents limped along on a context-fetch tool but were not getting their authoritative instructions. Affects any project type.</t>
-        </is>
-      </c>
-      <c r="D66" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Companion Runner / Engine launch (ClaudeDriver)</t>
-        </is>
-      </c>
-      <c r="E66" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bug</t>
-        </is>
-      </c>
-      <c r="F66" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Root-caused during UX Design live testing (work item 8d6f3b7d). Verified against the installed Claude Agent SDK 0.1.0 and Claude CLI 2.1.205. Code: backend/drivers/claude_driver.py.</t>
-        </is>
-      </c>
-      <c r="G66" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P1</t>
-        </is>
-      </c>
-      <c r="H66" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The agent's instructions were delivered by the wrong channel. They were normally passed as the engine's 'system prompt', which the SDK puts on the command line — capped at ~32,000 characters on Windows, so the ~36KB UX body overflowed (S.No 64). The interim workaround wrote the body to an AGENTS.md file, but Claude Code does not auto-load AGENTS.md (only CLAUDE.md, with project setting-sources) and a sandboxed planning agent has no file-reading tool — so the body reached the model through no path. The manifest had the same problem. Net effect: 7 large agents ran without their role, and the interim fix silently regressed 6 phases that previously worked (their bodies had fit on the command line).</t>
-        </is>
-      </c>
-      <c r="I66" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Deliver the agent body + full run manifest as a TRUE FILE-BASED SYSTEM PROMPT via the CLI flag --system-prompt-file (passed through the SDK's extra_args, since the pinned SDK 0.1.0 doesn't type the flag; the pinned CLI 2.1.205 supports it — verified). The driver writes body+manifest to SYSTEM_PROMPT.md in the run folder and hands the engine its absolute path. Size-independent (no command-line limit for any agent), a real system prompt (strongest adherence — bodies are authored as system prompts), needs no CLAUDE.md/setting-sources trickery, and no client-repo collision in build. One uniform code path replaced the old size-threshold branching; dead AGENTS.md writes were removed. The manifest (incl. its Rules section and, for review, the inlined PR diff) now genuinely reaches the model for the first time. Verified live: a 40KB system-prompt file launched the real engine and the model followed instructions inside the file; a UX Design re-run produced correct, role-appropriate artifacts. Tests rewritten to assert body+manifest reach the CLI via --system-prompt-file for every body size.</t>
-        </is>
-      </c>
-      <c r="J66" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Fixed</t>
-        </is>
+      <c r="B66" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="D66" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="E66" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F66" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="G66" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H66" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="I66" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="J66" s="2" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="67" spans="1:10" ht="409.6">
       <c r="A67" s="2">
         <v>66</v>
       </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">A phase run failed in Phases &amp; Runs with 'Run failed — Unknown message type: rate_limit_event', even though the agent and companion were healthy.</t>
-        </is>
-      </c>
-      <c r="C67" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Hit during UX Design live testing. Part-way through a run the engine emitted a 'rate_limit_event' notification message; the SDK's message reader didn't recognise that message type and raised an error, which aborted the entire phase. This would strike ANY phase, at random, whenever the engine sends a rate-limit notice.</t>
-        </is>
-      </c>
-      <c r="D67" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Companion Runner / Engine (ClaudeDriver)</t>
-        </is>
-      </c>
-      <c r="E67" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bug</t>
-        </is>
-      </c>
-      <c r="F67" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Observed on a UX Design run during live testing. Caused by version skew between the pinned Claude Agent SDK 0.1.0 and the newer Claude CLI 2.1.205. Code: backend/drivers/claude_driver.py.</t>
-        </is>
-      </c>
-      <c r="G67" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P1</t>
-        </is>
-      </c>
-      <c r="H67" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The installed Claude CLI (2.1.205) is newer than the pinned Claude Agent SDK (0.1.0) and emits notification message types the SDK's parser has no case for — here, 'rate_limit_event'. On an unknown type the SDK's parser raises a fatal 'Unknown message type' error, which propagates out and kills the run. These messages are non-essential telemetry; the run's real output still arrives as the normal assistant/result messages. The SDK simply treated an unknown notification as fatal.</t>
-        </is>
-      </c>
-      <c r="I67" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Made message parsing tolerant of unknown types. The driver wraps the SDK's parser: an unknown message type becomes a harmless, ignored message instead of crashing the run — while genuinely malformed messages (e.g. missing type) still raise, so real errors are not hidden. Forward-robust: it tolerates ANY future unknown notification type from a newer CLI, not just rate_limit_event, without a risky SDK upgrade. Verified: fed a real rate_limit_event through the actual SDK parser (benign, no crash), confirmed malformed messages still raise, and confirmed a stream containing the event still produces a valid result. New tests cover all three cases.</t>
-        </is>
-      </c>
-      <c r="J67" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Fixed</t>
-        </is>
+      <c r="B67" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="C67" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="D67" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="E67" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F67" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="G67" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H67" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="I67" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="J67" s="2" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="68" spans="1:10" ht="409.6">
       <c r="A68" s="2">
         <v>67</v>
       </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Some generated artifacts could not be previewed for review — preview showed 'artifact has no body to preview' even though the artifact clearly had content, blocking the user from reviewing and approving the gate.</t>
-        </is>
-      </c>
-      <c r="C68" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Seen on the SpendLog test project. Planning agents register many artifacts (assumptions register, user journeys, stakeholder map, accessibility spec, etc.) whose CONTENT is structured data stored in the artifact's external_ref field — because the register tool is pointers-only and there is no other place for that content to live. The preview endpoint only knew how to show a plain-text/markdown body from S3 or an inline 'body' field; it had no way to render structured external_ref content, so those artifacts previewed as empty.</t>
-        </is>
-      </c>
-      <c r="D68" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Artifacts &amp; Traceability (preview)</t>
-        </is>
-      </c>
-      <c r="E68" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bug</t>
-        </is>
-      </c>
-      <c r="F68" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Root-caused on SpendLog run 7f67d88a; all 7 artifacts of the run previewed empty. Code: backend/integrations/preview.py, backend/orchestration/activities.py.</t>
-        </is>
-      </c>
-      <c r="G68" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P1</t>
-        </is>
-      </c>
-      <c r="H68" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Artifact content lives in one of a few places: an S3 draft body, an inline external_ref 'body' field, the run's staged phase draft, or — for many planning sub-artifacts — as structured JSON in external_ref (the register tool is pointers-only, so structured data there is the only home for that content). The preview read-through handled the first three but had no renderer for structured external_ref, so those artifacts returned 'no body'. It is type- and phase-agnostic: it affects any artifact whose content is structured data, in any phase.</t>
-        </is>
-      </c>
-      <c r="I68" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Added a generic, type/phase-agnostic renderer in backend/integrations/preview.py that turns any structured external_ref into readable markdown (title heading, labelled fields, lists as bullets, lists of records as titled sections), and ranked the artifact's OWN structured content above the run-level fallbacks so a sub-artifact previews its own content rather than the whole phase document. Known pointer fields (ids, URLs, project refs) are excluded so no UUID noise leaks in. Also merged (not overwrote) the run outputs so the companion's raw report survives as the last-resort fallback, and made the driver report abnormal/empty engine endings instead of silently staging a blank draft. Verified live: all 7 previously-blank artifacts of the test run now preview as readable documents; today's UX Design artifacts preview correctly. New tests cover the renderer and the fallback ordering.</t>
-        </is>
-      </c>
-      <c r="J68" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Fixed</t>
-        </is>
+      <c r="B68" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="D68" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="E68" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F68" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="G68" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H68" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="I68" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="J68" s="2" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="69" spans="1:10">
       <c r="A69" s="2">
         <v>68</v>
       </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The UX Design agent generated full HTML wireframe screens but they were never saved — the wireframe artifacts ended up empty (only a short text description), so no one could preview the screens and the implementation phase had nothing to read.</t>
-        </is>
-      </c>
-      <c r="C69" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Seen on the SpendLog-Test-2.1 UX Design run. The agent authored ~25 self-contained HTML state documents (default/loading/empty/error/success per screen) exactly as instructed, and registered one wireframe artifact per screen — but the HTML had no channel to reach storage, so each artifact carried only prose 'layout_notes'. The rendered screens were effectively lost.</t>
-        </is>
-      </c>
-      <c r="D69" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Platform-State MCP + Artifacts (UX Design wireframes)</t>
-        </is>
-      </c>
-      <c r="E69" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bug</t>
-        </is>
-      </c>
-      <c r="F69" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Observed on the SpendLog-Test-2.1 UX Design run. Code: mcp_platform_state/tools.py, mcp_platform_state/server.py, runner/companion/state_mcp.py, runner/companion/runner.py, backend/api/runner_views.py, backend/orchestration/activities.py, backend/integrations/preview.py, frontend/src/features/observability/ArtifactPreviewScreen.tsx, agents/05_ux_design/agent.md.</t>
-        </is>
-      </c>
-      <c r="G69" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P1</t>
-        </is>
-      </c>
-      <c r="H69" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">register_artifact is deliberately pointers-only (state stays pointers, bodies live in the object store), and there was NO tool to hand a large body to the platform to persist. Inline external_ref bodies can't carry big HTML because the single MCP call is token-capped (a ~401K-char register call was rejected), and the sandboxed planning agent has no Write/S3 access to stage a snapshot itself. get_artifact also returned pointers only, so even the implementation agent could not read a screen's HTML. Net: the UX agent's central deliverable had nowhere to go and degraded to prose. Affects any phase that must persist a large body, not just wireframes.</t>
-        </is>
-      </c>
-      <c r="I69" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Added the missing persistence primitive: a stage_artifact_body MCP tool that streams one body (e.g. one HTML state) to the object store as a run/phase-scoped draft and returns its s3_key+hash — sandbox-safe (a platform capability, not local Write), one document per call so it never hits the token cap. The UX agent now stages each state then registers one wireframe artifact per screen with external_ref.states = [{name, s3_key, content_hash}] (primary s3_key = default state); register_artifact stays pointers-only. Added a get_artifact_body read tool (one state at a time) so the task-breakdown/implementation agents can read the actual HTML. Preview now surfaces all states read-through and the UI shows a state switcher rendering each screen in an isolated iframe, so the user previews and approves the real screens; Figma export rides the existing export-policy seam. Also bound project_id from the launch in get_context/list_artifacts (agents were passing the project NAME → backend 500). Verified: new unit tests for staging, one-state read, and multi-state preview pass; existing suites green (4 preview failures are MinIO-not-reachable env only).</t>
-        </is>
-      </c>
-      <c r="J69" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Fixed</t>
-        </is>
+      <c r="B69" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="C69" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="D69" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="E69" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F69" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="G69" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H69" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="I69" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="J69" s="2" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="70" spans="1:10">
       <c r="A70" s="2">
         <v>69</v>
       </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">UX Design ran ~15 min and registered NOTHING. The agent generated and staged its HTML screens fine, but could not read its own project context — every get_context / list_artifacts call came back too big and failed, so the agent looped without ever registering an artifact.</t>
-        </is>
-      </c>
-      <c r="C70" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Hit on the SpendLog-Test-2.1 UX re-run right after the wireframe-persistence fix. As upstream phases (requirements, PRD, architecture) accumulated artifacts, the context/list tools returned the FULL content of up to 50 artifacts at once (their structured bodies live in external_ref), producing 400,000+ character responses that blow the engine's per-tool token limit. The agent then grabbed shortened artifact ids from the truncated output and called the read tools with them, which 500'd.</t>
-        </is>
-      </c>
-      <c r="D70" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Platform-State MCP (get_context / list_artifacts / get_artifact_body)</t>
-        </is>
-      </c>
-      <c r="E70" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bug</t>
-        </is>
-      </c>
-      <c r="F70" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Observed on UX Design run f8966dd4: list_artifacts=401,397 chars, get_context(prd)=420,594 chars, plus get_artifact_body 500 'is not a valid UUID' on shortened ids. 0 artifacts registered after 15 min (11 HTML states DID stage to S3 successfully - staging was not the problem). Code: mcp_platform_state/tools.py.</t>
-        </is>
-      </c>
-      <c r="G70" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P1</t>
-        </is>
-      </c>
-      <c r="H70" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">get_context and list_artifacts serialized each artifact's ENTIRE external_ref - which for many artifact types holds the structured body/content, not just pointers. Returning up to 50 of those in one response exceeded the MCP token budget, so the whole call failed. This is a listing that must carry pointers only (platform owns STATE as pointers; CONTENT is fetched on demand) but was leaking bodies. A secondary effect: with the list truncated to a saved file, the agent improvised 8-character ids, and get_artifact_body/get_artifact raised an unhandled 500 on a non-UUID instead of a friendly message. Pre-existing latent issue that became fatal once the project had several large upstream artifacts.</t>
-        </is>
-      </c>
-      <c r="I70" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Made get_context and list_artifacts return POINTER-ONLY artifacts: a new lean serializer strips large/structured values out of external_ref, keeping only small metadata (id, type, route, screen id, sor, and for wireframes the states' name+s3_key+hash). Bodies are now fetched on demand with get_artifact_body(full_id). Measured on the real project: list_artifacts dropped 401,397 -&gt; 20,725 chars, get_context(prd) 420,594 -&gt; 35,702 chars - both safely under the limit. Also hardened get_artifact and get_artifact_body to return a clear 'pass the full id' message instead of a 500 on a malformed/shortened id (which also removes the source of the bad ids, since the agent now receives full ids in a small listing). Verified live against the DB; backend + worker restarted to load it.</t>
-        </is>
-      </c>
-      <c r="J70" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Fixed</t>
-        </is>
+      <c r="B70" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="C70" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="D70" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="E70" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F70" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="G70" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H70" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="I70" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="J70" s="2" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="71" spans="1:10">
       <c r="A71" s="2">
         <v>70</v>
       </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The UX Design gate could not be approved: clicking Approve returned 'cannot approve: 9 required gate condition(s) unmet' and there was no way in the UI to satisfy them, blocking the whole design gate.</t>
-        </is>
-      </c>
-      <c r="C71" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Hit approving the UX Design gate on SpendLog-Test-2.1. By design the UX/accessibility gate carries a required WCAG 2.1 AA checklist (9 criteria) that the reviewer must mark satisfied before Approve. But the Gates approval panel showed only Comment + Approve/Reject with no checklist, and its inline Approve sent no condition updates - so the required criteria could never be ticked and the gate was un-approvable. The checklist component (CriteriaGate) existed but was never wired into a route or the panel.</t>
-        </is>
-      </c>
-      <c r="D71" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gates (approval UI)</t>
-        </is>
-      </c>
-      <c r="E71" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bug</t>
-        </is>
-      </c>
-      <c r="F71" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Observed approving UX Design gate (approval bc7e6a13, gate_type phase_gate, role designer, 9 WCAG conditions). First surfaced now - first UX gate approval attempt (prior UX run was deleted before its gate). Code: frontend/src/features/lifecycle/Gates.tsx; backend enforcement backend/apps/gates/services.py + wcag.py (unchanged, working as designed).</t>
-        </is>
-      </c>
-      <c r="G71" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P1</t>
-        </is>
-      </c>
-      <c r="H71" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The ux_design gate opens with conditions_for_phase('ux_design') = 9 WCAG 2.1 AA criteria (all required, satisfied=false). services.decide_gate blocks the APPROVE decision while any required condition is unsatisfied; the reviewer satisfies them by sending conditions=[{key,satisfied}] with the decision. The Gates panel's inline Approve never sent conditions and rendered no checklist, and the dedicated CriteriaGate checklist screen was orphaned (present only in tests, no route). So there was no path in the app to satisfy the criteria. Backend + gate design are correct; the gap was purely the missing checklist UI on the approval panel.</t>
-        </is>
-      </c>
-      <c r="I71" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Wired the WCAG checklist into the Gates approval panel (frontend/src/features/lifecycle/Gates.tsx). When the selected gate has conditions, the panel now fetches them via the existing useGateCriteria hook and renders each criterion as a togglable checkbox (reusing CriteriaList/CriteriaItem), shows an 'X of N met' progress, keeps the Approve button disabled until every required criterion is ticked, and includes the reviewer's conditions=[{key,satisfied}] in the decide call. Gates with no conditions are unchanged (decide directly). Verified: the pending approval carries the 9 WCAG conditions; frontend typechecks clean; reuses the same proven decide path the CriteriaGate screen already used. Reviewer can now tick the WCAG criteria and approve.</t>
-        </is>
-      </c>
-      <c r="J71" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Fixed</t>
-        </is>
+      <c r="B71" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="C71" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="D71" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="E71" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F71" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="G71" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H71" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="I71" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="J71" s="2" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="72" spans="1:10" ht="409.6">
       <c r="A72" s="2">
         <v>71</v>
       </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Task Breakdown agent told to fetch artifact bodies with the wrong tool (get_artifact instead of get_artifact_body)</t>
-        </is>
-      </c>
-      <c r="C72" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The task-breakdown agent instructions told it to fetch upstream artifact bodies (PRD / requirements / architecture / per-screen wireframes) using get_artifact. Since the pointer-only refactor (S.No 69), get_artifact returns only pointers/provenance with NO body. As written the agent would receive no content to decompose and would stall or hallucinate a backlog — the same failure mode that stalled the UX Design phase until its tool wiring was fixed.</t>
-        </is>
-      </c>
-      <c r="D72" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Task Breakdown / Agents</t>
-        </is>
-      </c>
-      <c r="E72" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bug</t>
-        </is>
-      </c>
-      <c r="F72" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">agents/06_task_breakdown/agent.md (lines 28 and 145); tool split in mcp_platform_state/tools.py get_artifact vs get_artifact_body</t>
-        </is>
-      </c>
-      <c r="G72" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P1</t>
-        </is>
-      </c>
-      <c r="H72" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">agent.md was not updated when get_artifact/get_artifact_body were split last session (S.No 68-69). The verbatim instruction kept naming a tool that is now pointer-only, so the agent had no way to read the bodies it must decompose.</t>
-        </is>
-      </c>
-      <c r="I72" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Updated both references in agents/06_task_breakdown/agent.md to get_artifact_body (which reads one state at a time for multi-state wireframes) and noted that get_artifact returns pointers only. To take effect the backend/worker/companion must be restarted so the new agent body is delivered; verified against a live task-breakdown run.</t>
-        </is>
-      </c>
-      <c r="J72" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Fixed</t>
-        </is>
+      <c r="B72" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="C72" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="D72" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="E72" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F72" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="G72" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H72" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="I72" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="J72" s="2" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="73" spans="1:10" ht="409.6">
       <c r="A73" s="2">
         <v>72</v>
       </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">No REST endpoint to start implementation (build) on a work item</t>
-        </is>
-      </c>
-      <c r="C73" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The implementation BuildWorkflow saga (orchestration.trigger.trigger_build) had no HTTP surface — it was only callable from tests. A user therefore could not start implementation on a work item from the platform, blocking the 'run implementation on one task' flow (both the internal-managed and Jira-managed cases still start the code work through this path).</t>
-        </is>
-      </c>
-      <c r="D73" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Implementation / Work Items</t>
-        </is>
-      </c>
-      <c r="E73" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bug</t>
-        </is>
-      </c>
-      <c r="F73" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">backend/api/views.py (WorkItemViewSet — only the phase trigger action existed); backend/orchestration/trigger.py trigger_build</t>
-        </is>
-      </c>
-      <c r="G73" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P1</t>
-        </is>
-      </c>
-      <c r="H73" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Only the phase trigger (trigger_phase) was wired to a viewset action; trigger_build was fully implemented but was never exposed via a DRF @action/route.</t>
-        </is>
-      </c>
-      <c r="I73" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Added POST /api/work-items/{id}/build/ (WorkItemViewSet.build) plus BuildTriggerSerializer (agent_key defaults to 07_implementation; optional repo/base default from the work item's Repository; required_role; user_id for companion routing). Returns 202 {run_id, workflow_id}; returns 400 with a friendly message when the work item has no target repository. New focused test backend/tests/test_build_trigger_api.py (2 tests: happy-path start + no-repo rejection).</t>
-        </is>
-      </c>
-      <c r="J73" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Fixed</t>
-        </is>
+      <c r="B73" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="C73" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="D73" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="E73" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F73" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="G73" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H73" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="I73" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="J73" s="2" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="74" spans="1:10" ht="409.6">
       <c r="A74" s="2">
         <v>73</v>
       </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Companion never git-pushes the worktree branch, so opening the PR fails against a live GitHub repo</t>
-        </is>
-      </c>
-      <c r="C74" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">During implementation the companion writes code into a local git worktree on branch feature/WI-&lt;n&gt; but never pushes that branch to origin. codehost.open_pull_request then calls the GitHub REST POST /pulls assuming the head branch already exists on the remote, so against a live GitHub repository the PR step returns 404/422. Code still lands in the developer's local worktree; only the PR / merge / merge-gate steps are blocked.</t>
-        </is>
-      </c>
-      <c r="D74" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Implementation / CodeHost</t>
-        </is>
-      </c>
-      <c r="E74" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bug</t>
-        </is>
-      </c>
-      <c r="F74" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">runner/companion/runner.py (no push by design D2); runner/companion/worktree.py (teardown leaves branch local); backend/orchestration/build_activities.py open_build_pr_core; integrations/github/codehost.py open_pull_request</t>
-        </is>
-      </c>
-      <c r="G74" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P1</t>
-        </is>
-      </c>
-      <c r="H74" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Design D2 keeps all Git side-effects on the platform, but the actual branch-push step was implemented on neither side — the worktree branch is created and left purely local.</t>
-        </is>
-      </c>
-      <c r="I74" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">FIXED (Option B). The companion now performs the Git side-effects (D2): after the build agent writes code and the secret scan passes, run_build commits the change to feature/WI-&lt;key&gt; with a derived Conventional-Commit message and pushes the branch to origin, reporting head_sha so the platform's open_build_pr opens the draft PR against a real ref. New worktree helpers commit_all/push_branch/head_sha (runner/companion/worktree.py); BuildTask carries work_item_title/type and dispatch_build_core ships them for the commit subject. Nothing is committed/pushed when the secret scan blocks or the agent produced no change. Tests: 3 new in test_companion_runner.py (commit+push to a bare remote, subject-from-title, secret-block no-push) + dispatch payload assertion in test_build_activities.py; all pass. The full path (GitHub CodeHost connect + PR -&gt; review -&gt; merge-gate -&gt; done) is now unblocked.</t>
-        </is>
-      </c>
-      <c r="J74" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Fixed</t>
-        </is>
+      <c r="B74" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="C74" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="D74" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="E74" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F74" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="G74" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H74" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="I74" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="J74" s="2" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="75" spans="1:10" ht="409.6">
       <c r="A75" s="2">
         <v>74</v>
       </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Integration credentials entered in the UI are never used; connectors authenticate from server .env</t>
-        </is>
-      </c>
-      <c r="C75" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">IntegrationConnection.secret_encrypted (the credentials a tenant enters when connecting Jira / Confluence / etc.) is written but never decrypted at runtime — decrypt_secrets is only called in tests. Every Atlassian connector resolves its credentials via AtlassianConfig.from_settings() (the server .env). So a tenant that 'connects Jira' and passes the wiring check still authenticates with the single .env Atlassian account; scopes.project_key IS read from the connection, but the secret is not. Effectively single-tenant and a multi-tenant credential-leak risk. The connection also shows Healthy without any live network probe.</t>
-        </is>
-      </c>
-      <c r="D75" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Integrations / Connectors</t>
-        </is>
-      </c>
-      <c r="E75" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bug</t>
-        </is>
-      </c>
-      <c r="F75" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">backend/integrations/registry.py (_atlassian_config / _build_jira / _build_confluence); backend/apps/integrations/services.py (test_integration_connection is wiring-only); apps/integrations/crypto.decrypt_secrets (tests only)</t>
-        </is>
-      </c>
-      <c r="G75" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P2</t>
-        </is>
-      </c>
-      <c r="H75" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The token_ref indirection is a documented Phase-5 seam; Phase 1 hardcoded from_settings() and decrypt_secrets was never wired into the connector builders.</t>
-        </is>
-      </c>
-      <c r="I75" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Deferred (Phase-5 seam). Fix = wire decrypt_secrets(conn) into the connector builders so per-tenant creds are used and retire the .env fallback; make test-connection a real reachability probe. For the current greenfield test, Jira is connected exactly like Confluence: the Integrations connection supplies scopes.project_key and the shared Atlassian creds live in .env.</t>
-        </is>
-      </c>
-      <c r="J75" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Open</t>
-        </is>
+      <c r="B75" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="C75" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="D75" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="E75" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F75" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="G75" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="H75" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="I75" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="J75" s="2" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="76" spans="1:10" ht="409.6">
       <c r="A76" s="2">
         <v>75</v>
       </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">No dedicated Task Breakdown review screen; dependencies and estimates are not surfaced before the gate</t>
-        </is>
-      </c>
-      <c r="C76" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The four planning artifacts (backlog / sprint_plan / definition_of_done / dependency_map) render only as plain markdown via the generic artifact preview, and the proposed work items appear separately on the Work Items board as generic 'Draft' badges. depends_on is serialized but read by zero frontend files (no dependency graph), and there is NO estimate/story-points field on WorkItem at all — so a reviewer cannot see hierarchy, dependencies and estimates in one place before approving the task-breakdown gate.</t>
-        </is>
-      </c>
-      <c r="D76" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Task Breakdown / Work Items UI</t>
-        </is>
-      </c>
-      <c r="E76" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Enhancement</t>
-        </is>
-      </c>
-      <c r="F76" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">frontend TaskBreakdown.tsx (after-the-fact summary), WorkItemsBoard.tsx (depends_on unused); backend/integrations/preview.py (no backlog renderer); backend/apps/workitems/models.py (no estimate field)</t>
-        </is>
-      </c>
-      <c r="G76" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P2</t>
-        </is>
-      </c>
-      <c r="H76" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The task-breakdown preview UI was never built to the depth of other phases, and an estimate/story-points field was never modeled on WorkItem.</t>
-        </is>
-      </c>
-      <c r="I76" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Accepted as-is for this test (markdown preview + Work Items board). Later: a dedicated proposed-backlog review screen showing epic-&gt;story-&gt;task hierarchy + depends_on graph + estimates; add WorkItem.estimate; add a backlog-specific preview renderer.</t>
-        </is>
-      </c>
-      <c r="J76" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Open</t>
-        </is>
+      <c r="B76" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="C76" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="D76" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="E76" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F76" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="G76" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="H76" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="I76" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="J76" s="2" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="77" spans="1:10" ht="409.6">
       <c r="A77" s="2">
         <v>76</v>
       </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">No UI to edit the generated user stories/tasks before the gate</t>
-        </is>
-      </c>
-      <c r="C77" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Users cannot edit the stories/tasks the Task Breakdown agent generates. A backend edit surface already exists (WorkItemPatchSerializer allows PATCH of title/description/type), but there is no frontend for it, and state / estimate / dependencies are not editable.</t>
-        </is>
-      </c>
-      <c r="D77" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Task Breakdown / Work Items UI</t>
-        </is>
-      </c>
-      <c r="E77" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Enhancement</t>
-        </is>
-      </c>
-      <c r="F77" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">backend/api/serializers.py WorkItemPatchSerializer (exists, title/description/type); no frontend edit UI</t>
-        </is>
-      </c>
-      <c r="G77" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P3</t>
-        </is>
-      </c>
-      <c r="H77" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The edit UI was never built; only the PATCH serializer was scaffolded.</t>
-        </is>
-      </c>
-      <c r="I77" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Deferred (later-phase optimization, per team decision). Add an edit UI over the existing PATCH endpoint; consider making dependencies and estimate editable too.</t>
-        </is>
-      </c>
-      <c r="J77" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Open</t>
-        </is>
+      <c r="B77" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="C77" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="D77" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="E77" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F77" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="G77" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H77" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="I77" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="J77" s="2" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="78" spans="1:10" ht="409.6">
       <c r="A78" s="2">
         <v>77</v>
       </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Re-running Task Breakdown duplicates the whole backlog (create_work_item has no idempotency)</t>
-        </is>
-      </c>
-      <c r="C78" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">create_work_item unconditionally creates a new WorkItem — there is no natural-key / get_or_create dedupe. Re-dispatching the task-breakdown phase (for example after a stalled run) creates duplicate epics/stories/tasks and duplicate WI numbers. Re-run hygiene currently requires manually deleting the partial batch first (as was done for the UX phase).</t>
-        </is>
-      </c>
-      <c r="D78" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Platform State / Work Items</t>
-        </is>
-      </c>
-      <c r="E78" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bug</t>
-        </is>
-      </c>
-      <c r="F78" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mcp_platform_state/tools.py create_work_item (contrast register_artifact which auto-versions)</t>
-        </is>
-      </c>
-      <c r="G78" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P2</t>
-        </is>
-      </c>
-      <c r="H78" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">No idempotency/natural key on work-item creation, unlike register_artifact which versions siblings.</t>
-        </is>
-      </c>
-      <c r="I78" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Deferred. Add an idempotency key (e.g. project+phase+title, or an agent-supplied external key) so a re-run upserts rather than duplicates. For today's run, delete any partial batch before re-triggering.</t>
-        </is>
-      </c>
-      <c r="J78" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Open</t>
-        </is>
+      <c r="B78" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="C78" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="D78" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="E78" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F78" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="G78" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="H78" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="I78" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="J78" s="2" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="79" spans="1:10" ht="409.6">
       <c r="A79" s="2">
         <v>78</v>
       </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Jira integration is one-way (create-only): no inbound webhook, no status sync, dropped fields</t>
-        </is>
-      </c>
-      <c r="C79" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Reconcile creates Jira issues (summary/description/parent only) and stores the Jira key in WorkItem.external_ref, but: (a) there is no inbound Jira webhook and no Jira-status -&gt; WorkItem.State mapping, so a Jira transition (In Progress/Done) is invisible to the platform; (b) transition_issue is implemented but never called in production, so platform-side transitions are not pushed back to Jira; (c) depends_on edges, acceptance criteria, story points and wireframe refs are not pushed. Completion is detected ONLY via the GitHub PR-merge webhook — never via Jira. So a Jira-managed task is a visibility mirror, not a two-way work surface.</t>
-        </is>
-      </c>
-      <c r="D79" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Integrations / TaskTracker (Jira)</t>
-        </is>
-      </c>
-      <c r="E79" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Enhancement</t>
-        </is>
-      </c>
-      <c r="F79" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">backend/integrations/reconcile.py (create-only, minimal fields); integrations/atlassian/tasktracker.py transition_issue (dormant); backend/integrations/webhooks.py (GitHub inbound only)</t>
-        </is>
-      </c>
-      <c r="G79" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P2</t>
-        </is>
-      </c>
-      <c r="H79" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bi-directional Jira sync is a future seam; reconcile is create-only and maps neither dependency links nor rich issue fields.</t>
-        </is>
-      </c>
-      <c r="I79" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Deferred. Add an inbound Jira webhook + status-&gt;state mapping, wire transition_issue on WorkItem transitions, and map depends_on (Jira issue links) plus acceptance criteria / story points / wireframe ref in reconcile.</t>
-        </is>
-      </c>
-      <c r="J79" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Open</t>
-        </is>
+      <c r="B79" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="C79" s="2" t="s">
+        <v>326</v>
+      </c>
+      <c r="D79" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="E79" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F79" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="G79" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="H79" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="I79" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="J79" s="2" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="80" spans="1:10" ht="409.6">
       <c r="A80" s="2">
         <v>79</v>
       </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">No in-context 'Push to Jira' action on the Task Breakdown screen; publish reconciles ALL proposed work items at once</t>
-        </is>
-      </c>
-      <c r="C80" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The Jira push lives on the generic Artifact Publish screen keyed off the backlog artifact — there is no 'push these tasks to Jira' button on the Task Breakdown screen or the Work Items board where a reviewer is actually looking at the composed stories/tasks. Worse, publishing calls reconcile_backlog(project_id), which pushes EVERY proposed work item in the project in one go — there is no per-item review-and-confirm or subset selection before the push. A reviewer cannot push a reviewed subset or see, in context, exactly what will go to Jira.</t>
-        </is>
-      </c>
-      <c r="D80" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Task Breakdown / Integrations UI</t>
-        </is>
-      </c>
-      <c r="E80" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Enhancement</t>
-        </is>
-      </c>
-      <c r="F80" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">frontend ExportPublish.tsx (push on artifact publish); backend/api/views.py _publish_tasktracker -&gt; reconcile_backlog(project_id); no push button on TaskBreakdown.tsx or WorkItemsBoard.tsx</t>
-        </is>
-      </c>
-      <c r="G80" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P2</t>
-        </is>
-      </c>
-      <c r="H80" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The Jira push was wired only to the generic per-artifact publish path (which reconciles the whole project's proposed items), never to an in-context task-review action with selection/confirm.</t>
-        </is>
-      </c>
-      <c r="I80" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Deferred (accepted for this test). Later: add a 'Push to Jira' action on the Task Breakdown review screen with a per-item / selection confirm step, backed by a scoped reconcile (push the reviewed subset, not the whole project blindly).</t>
-        </is>
-      </c>
-      <c r="J80" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Open</t>
-        </is>
+      <c r="B80" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="C80" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="D80" s="2" t="s">
+        <v>333</v>
+      </c>
+      <c r="E80" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F80" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="G80" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="H80" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="I80" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="J80" s="2" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="81" spans="1:10" ht="409.6">
       <c r="A81" s="2">
         <v>80</v>
       </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">SYSTEMIC (fresh-run blocker): manifest composer + 15 of 16 agent bodies tell every agent to fetch artifact bodies with get_artifact (pointer-only)</t>
-        </is>
-      </c>
-      <c r="C81" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The manifest composer's 'Relevant Artifacts' section instructed EVERY agent to 'fetch full bodies with get_artifact(artifact_id)', and 15 of 16 agent bodies repeated the same stale instruction. Since get_artifact became pointer-only (S.No 68-69, commit d7c27d6), it returns NO S3 body — so under the current pointer-only get_context/list_artifacts regime an agent cannot read its upstream inputs and stalls or hallucinates (the exact UX-phase failure). Earlier phases (ideation..architecture) appeared to work only because they ran on 2026-07-08 BEFORE get_context went pointer-only (context then carried full bodies inline) and because some upstream bodies happened to be stored inline in external_ref. A fresh end-to-end run puts every phase under the pointer-only regime and would hit the failure. Same class as S.No 71 (task breakdown) but suite-wide.</t>
-        </is>
-      </c>
-      <c r="D81" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Agents / Manifest / Platform State</t>
-        </is>
-      </c>
-      <c r="E81" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bug</t>
-        </is>
-      </c>
-      <c r="F81" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">backend/manifest/composer.py:161 (Relevant Artifacts instruction); 15 agent bodies: 00_onboarding, 00b_context_bridge, 00c_context_extractor, 01_ideation, 02_requirements, 03_prd, 04_architecture, 05_ux_design, 07_implementation, 08_code_review, 09_testing, 09b_test_automation, 10_security, 11_cicd, 12_deployment; get_artifact vs get_artifact_body in mcp_platform_state/tools.py</t>
-        </is>
-      </c>
-      <c r="G81" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P1</t>
-        </is>
-      </c>
-      <c r="H81" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The get_artifact/get_artifact_body tool split (S.No 68-69) made get_artifact pointer-only, but the composer instruction and every pre-existing agent body still named get_artifact for body fetches. They were authored/tested before get_context went pointer-only (2026-07-09, d7c27d6), so the regression stayed latent until a phase ran under the new regime (UX was first).</t>
-        </is>
-      </c>
-      <c r="I81" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Swept all 27 body-fetch references to get_artifact_body (word-boundary replace; get_artifact_body's fallback chain in integrations/preview.py handles S3 + inline external_ref.body + structured external_ref + run-draft bodies): composer.py:161 plus the 15 agent bodies (06_task_breakdown was already fixed under S.No 71). Verified: 0 bare body-fetch get_artifact remain (only 06's accurate 'get_artifact returns pointers' note); composer compiles; agent-migration CONTENT tests pass. Backend + worker restarted to reload the composer.</t>
-        </is>
-      </c>
-      <c r="J81" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Fixed</t>
-        </is>
+      <c r="B81" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="C81" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="D81" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="E81" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F81" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="G81" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H81" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="I81" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="J81" s="2" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="82" spans="1:10" ht="409.6">
       <c r="A82" s="2">
         <v>81</v>
       </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Two agent-migration tests assert on options.system_prompt, obsolete since file-based system-prompt delivery</t>
-        </is>
-      </c>
-      <c r="C82" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">test_prd_run_reads_inputs_from_platform and test_ux_run_reads_inputs_from_platform assert against captured options.system_prompt, but the driver now delivers the agent body via a --system-prompt-file (SYSTEM_PROMPT.md in the run workdir, commit 98200ae), so options.system_prompt is None and the tests raise TypeError. Confirmed pre-existing: they fail identically on clean HEAD, independent of the get_artifact_body sweep. Runtime is unaffected; only the tests are stale.</t>
-        </is>
-      </c>
-      <c r="D82" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Tests / Engine driver</t>
-        </is>
-      </c>
-      <c r="E82" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bug</t>
-        </is>
-      </c>
-      <c r="F82" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">backend/tests/test_agents_migration.py:146; backend/tests/test_design_test_agents_migration.py:213; driver delivery in backend/drivers/claude_driver.py (--system-prompt-file, 98200ae)</t>
-        </is>
-      </c>
-      <c r="G82" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P3</t>
-        </is>
-      </c>
-      <c r="H82" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The tests were written against the old inline options.system_prompt delivery and were not updated when delivery moved to a file (98200ae).</t>
-        </is>
-      </c>
-      <c r="I82" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Not yet fixed. Update both tests to read the written SYSTEM_PROMPT.md (run workdir) instead of options.system_prompt, or assert on the file-based delivery path.</t>
-        </is>
-      </c>
-      <c r="J82" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Open</t>
-        </is>
+      <c r="B82" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="C82" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="D82" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="E82" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F82" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="G82" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H82" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="I82" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="J82" s="2" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="83" spans="1:10" ht="409.6">
       <c r="A83" s="2">
         <v>82</v>
       </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Task Breakdown agent had no body-persistence protocol — its 4 planning artifacts (backlog/sprint_plan/DoD/dependency_map) would not reliably persist</t>
-        </is>
-      </c>
-      <c r="C83" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The task-breakdown agent was told 'register it with register_artifact ... the platform persists the bodies', but register_artifact is pointers-only and the agent had NO stage_artifact_body protocol (UX has 3 such calls; task breakdown had 0). So on a run its four full-document deliverables risked not persisting: at best the primary previews via the run-report fallback, the rest show empty — the same class as the UX wireframe loss (S.No 68) before UX got its staging protocol.</t>
-        </is>
-      </c>
-      <c r="D83" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Task Breakdown / Agents</t>
-        </is>
-      </c>
-      <c r="E83" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bug</t>
-        </is>
-      </c>
-      <c r="F83" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">agents/06_task_breakdown/agent.md (Output section); stage_artifact_body in mcp_platform_state/tools.py; _PLATFORM_TOOL_NAMES in backend/orchestration/activities.py</t>
-        </is>
-      </c>
-      <c r="G83" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P1</t>
-        </is>
-      </c>
-      <c r="H83" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The agent body predates the stage_artifact_body tool (S.No 68) and kept the old, now-false 'the platform persists the bodies' wording; only 05_ux_design was updated with a staging protocol at the time.</t>
-        </is>
-      </c>
-      <c r="I83" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Added a 'How bodies are persisted' protocol to agents/06_task_breakdown/agent.md mirroring UX: each full deliverable (backlog/sprint_plan/definition_of_done/dependency_map) is staged with stage_artifact_body(filename, body) (one document per call), then registered with register_artifact using the returned s3_key/content_hash; the assumption register may stay inline in external_ref. Verified stage_artifact_body is in the planning allowlist and not sandbox-blocked; container sees the update.</t>
-        </is>
-      </c>
-      <c r="J83" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Fixed</t>
-        </is>
+      <c r="B83" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="C83" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="D83" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="E83" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F83" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="G83" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H83" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="I83" s="2" t="s">
+        <v>353</v>
+      </c>
+      <c r="J83" s="2" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="84" spans="1:10" ht="409.6">
       <c r="A84" s="2">
         <v>83</v>
       </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">UI phase trigger ran BUILD phases as planning runs — clicking Implementation could not produce code (no worktree/commit/PR)</t>
-        </is>
-      </c>
-      <c r="C84" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The Work Items / Phases &amp; Runs UI triggers every phase through POST /work-items/{id}/trigger/ -&gt; trigger_phase -&gt; AgentRunWorkflow (planning: sandboxed, no filesystem/git/worktree). But build phases must run through the BuildWorkflow (worktree -&gt; commit -&gt; push -&gt; PR -&gt; review -&gt; merge gate). So clicking 'Implementation' (or CI/CD, Test Automation) on a task would start a sandboxed planning run that cannot write code, commit, push, or open a PR — nothing would land in the repo. There was no build-vs-plan routing anywhere: only trigger_build (used by tests) reached the build path, and it had no UI entry. Affects every current and future build agent, not just implementation.</t>
-        </is>
-      </c>
-      <c r="D84" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Implementation / Phases &amp; Runs / Work Items</t>
-        </is>
-      </c>
-      <c r="E84" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bug</t>
-        </is>
-      </c>
-      <c r="F84" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">backend/api/views.py WorkItemViewSet.trigger; backend/orchestration/trigger.py (trigger_phase vs trigger_build); backend/apps/registry/catalog.py; frontend triggers via /trigger/ (PhasesAndRuns.tsx / WorkItemTask.tsx / WorkItemDefect.tsx)</t>
-        </is>
-      </c>
-      <c r="G84" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P1</t>
-        </is>
-      </c>
-      <c r="H84" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">trigger_phase always started an AgentRunWorkflow regardless of agent; build routing existed only implicitly (which function a test happened to call). No source of truth marked which agents ride the BuildWorkflow, and the single UI trigger had no branch for it.</t>
-        </is>
-      </c>
-      <c r="I84" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Added an explicit rides_build flag to AgentDefinition (single source of truth), set True only for the agents whose migrated body states the platform commits/pushes/opens the PR: 07_implementation, 09b_test_automation, 11_cicd. Planning phases (05_ux_design, 06_task_breakdown, 09_testing, 10_security, 12_deployment) stay False; 08_code_review runs inside the build loop (dispatched automatically, not a standalone user trigger). WorkItemViewSet.trigger now routes rides_build agents to trigger_build, else trigger_phase — so the existing UI buttons work for both plan and build with NO frontend change, and a future build agent only sets the flag. trigger_build now falls back to the project's default repository when the work item has none (proposed tasks). Tests: routing (07-&gt;build-run, 06-&gt;agent-run), rides_build flag set, project-default-repo fallback — all pass; agentspec-migration + frontend trigger/catalog tests still green. Backend restarted; flags verified live in-container.</t>
-        </is>
-      </c>
-      <c r="J84" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Fixed</t>
-        </is>
+      <c r="B84" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="C84" s="2" t="s">
+        <v>355</v>
+      </c>
+      <c r="D84" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="E84" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F84" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="G84" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H84" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="I84" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="J84" s="2" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="85" spans="1:10" ht="409.6">
       <c r="A85" s="2">
         <v>84</v>
       </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Trigger routes to the newest enrollment even if it never connected — dispatch can land on a dead enrollment while the live companion gets 204 (stuck run)</t>
-        </is>
-      </c>
-      <c r="C85" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">_resolve_enrollment picks the most recent RunnerEnrollment for the triggering user regardless of whether that enrollment has ever checked in (last_seen). When a machine has several enrollments (e.g. opening Connect Machine to copy a token while the daemon runs on an older token, or repeated reconnects), the trigger can route the dispatch to an enrollment whose daemon never ran, while the live companion polls under a different enrollment and receives 204 No Content. Observed live on the first WI-18 build: dispatch stuck 'pending' on a never-checked-in enrollment (last_seen null) while the running companion polled a different one; the build never started. Workaround used: wipe stale enrollments so only one fresh enrollment exists.</t>
-        </is>
-      </c>
-      <c r="D85" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Companion / Runner enrollment</t>
-        </is>
-      </c>
-      <c r="E85" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bug</t>
-        </is>
-      </c>
-      <c r="F85" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">backend/orchestration/trigger.py _resolve_enrollment (used by trigger_phase + trigger_build); apps/runs/models.py RunnerEnrollment.last_seen; runner_views.py RunnerWorkClaimView</t>
-        </is>
-      </c>
-      <c r="G85" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P2</t>
-        </is>
-      </c>
-      <c r="H85" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">_resolve_enrollment orders enrollments by recency and does not prefer ones that have actually checked in (last_seen recent / within the online window). RC-4 collapses re-enrollments by project but the selection still ignores liveness.</t>
-        </is>
+      <c r="B85" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="C85" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="D85" s="2" t="s">
+        <v>362</v>
+      </c>
+      <c r="E85" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F85" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="G85" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="H85" s="2" t="s">
+        <v>364</v>
       </c>
       <c r="I85" s="2" t="s">
-        <v>228</v>
+        <v>365</v>
       </c>
       <c r="J85" s="2" t="s">
         <v>16</v>
@@ -5007,1043 +5692,669 @@
       <c r="A86" s="2">
         <v>85</v>
       </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">09_testing / 10_security bodies reference the git worktree but are classified as planning (sandboxed, no filesystem) — may be starved of code when actually run</t>
-        </is>
-      </c>
-      <c r="C86" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">During the build-routing audit, 09_testing and 10_security were classified as planning phases: their bodies say 'when artifacts are registered, stop; the platform opens the review gate' — no commit/push/PR, so correctly NOT routed to the BuildWorkflow. But both bodies also reference the companion git worktree several times (they read the codebase to test/scan it). Planning phases run through the AgentRunWorkflow sandbox (no filesystem/Bash), so if these agents genuinely need to read the worktree code, they would be starved when run. There is currently no third execution mode ('reads the worktree but produces no PR'). Unverified — these phases have not been run yet.</t>
-        </is>
-      </c>
-      <c r="D86" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Testing / Security / Orchestration</t>
-        </is>
-      </c>
-      <c r="E86" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bug</t>
-        </is>
-      </c>
-      <c r="F86" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">agents/09_testing/agent.md, agents/10_security/agent.md (worktree references); backend/orchestration routing (BuildWorkflow vs sandboxed AgentRunWorkflow); apps/registry/catalog.py rides_build</t>
-        </is>
-      </c>
-      <c r="G86" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P3</t>
-        </is>
-      </c>
-      <c r="H86" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Only two execution paths exist (build = worktree + PR + merge gate; plan = sandboxed + register + review gate). 09_testing/10_security need to read code (worktree) but emit review-gated artifacts, not a PR — a shape neither path serves cleanly.</t>
-        </is>
-      </c>
-      <c r="I86" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Not yet investigated. When these phases are first run, verify the agent can access the code it needs; if not, either add a 'worktree-read, no-PR' execution mode (build-mode filesystem access without the commit/push/merge gate) or feed the needed code context via platform-state tools instead of the worktree. Left on the planning path for now (correct re: no PR).</t>
-        </is>
-      </c>
-      <c r="J86" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Open</t>
-        </is>
+      <c r="B86" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="C86" s="2" t="s">
+        <v>367</v>
+      </c>
+      <c r="D86" s="2" t="s">
+        <v>368</v>
+      </c>
+      <c r="E86" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F86" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="G86" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H86" s="2" t="s">
+        <v>370</v>
+      </c>
+      <c r="I86" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="J86" s="2" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="87" spans="1:10" ht="409.6">
       <c r="A87" s="2">
         <v>86</v>
       </c>
-      <c r="B87" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Build fails after push: agent's pre-PR 'code' pointer makes open_build_pr skip opening the real PR, then code review crashes (KeyError 'repo')</t>
-        </is>
-      </c>
-      <c r="C87" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The 07_implementation agent registers a pre-PR 'code' pointer (branch/files_changed, no PR) which its body says 'the platform reconciles with the PR it opens'. But open_build_pr_core treated ANY existing code artifact with a truthy external_ref as 'PR already opened' and returned early, so it never opened the real PR; then run_code_review_core read code.external_ref['repo'] and raised KeyError('repo'). Observed live on WI-18: code committed and pushed to feature/WI-aa6020d0 on GitHub, but NO PR opened and the run failed — blocking PR to review to merge.</t>
-        </is>
-      </c>
-      <c r="D87" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Implementation / Build pipeline</t>
-        </is>
-      </c>
-      <c r="E87" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bug</t>
-        </is>
-      </c>
-      <c r="F87" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">backend/orchestration/build_activities.py open_build_pr_core + run_code_review_core; agents/07_implementation/agent.md (~line 264 register code pointer)</t>
-        </is>
-      </c>
-      <c r="G87" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P1</t>
-        </is>
-      </c>
-      <c r="H87" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">open_build_pr's idempotency check mistook the agent's pre-PR pointer for an opened PR; the documented 'platform reconciles the pointer with the PR' behaviour was never implemented.</t>
-        </is>
-      </c>
-      <c r="I87" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Added _is_pr_ref (a real PR ref carries repo+number). open_build_pr short-circuits only on a real opened PR; when the agent's pre-PR pointer exists it OPENS the PR and reconciles that artifact in place (update_artifact with the PR external_ref + STAGED) instead of skipping/duplicating. run_code_review guards on _is_pr_ref (clear error, not KeyError). New test test_open_pr_reconciles_agent_pre_pr_pointer + 10 existing build-activities tests pass. Worker reloaded; failed WI-18 run cleaned for a fresh re-trigger.</t>
-        </is>
-      </c>
-      <c r="J87" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Fixed</t>
-        </is>
+      <c r="B87" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="C87" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="D87" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="E87" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F87" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="G87" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H87" s="2" t="s">
+        <v>376</v>
+      </c>
+      <c r="I87" s="2" t="s">
+        <v>377</v>
+      </c>
+      <c r="J87" s="2" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="88" spans="1:10" ht="409.6">
       <c r="A88" s="2">
         <v>87</v>
       </c>
-      <c r="B88" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Implementation agent can transition the WorkItem to 'done' itself (mid-build), bypassing the platform merge gate that owns completion</t>
-        </is>
-      </c>
-      <c r="C88" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">During the WI-18 build, the WorkItem was set to state='done' at 12:25:51 — a full minute BEFORE the PR opened (12:26:51), with no merge-gate approval and no webhook. The only actor with the tool and that timing is the 07_implementation agent: transition_work_item is in the build-phase tool allowlist (BUILD_STATE_TOOLS), so the agent marked its own task 'done' as it finished. This violates control-plane ownership of completion (non-negotiable: gates live in the control plane) — the platform should set 'done' only after the merge gate is approved and the PR merged. Effect: WorkItem state becomes premature/unreliable and the merge gate is cosmetic for state purposes.</t>
-        </is>
-      </c>
-      <c r="D88" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Implementation / Guardrails / Work Items</t>
-        </is>
-      </c>
-      <c r="E88" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bug</t>
-        </is>
-      </c>
-      <c r="F88" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">runner/companion/runner.py BUILD_STATE_TOOLS ('transition_work_item'); backend/api/runner_views.py allowlist; mcp_platform_state/tools.py transition_work_item; backend/orchestration/build_workflow.py owns the done transition (~line 150)</t>
-        </is>
-      </c>
-      <c r="G88" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P2</t>
-        </is>
-      </c>
-      <c r="H88" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">transition_work_item is exposed to the build agent (needed for remediation child items) but nothing stops it from transitioning the MAIN WorkItem into a gated/terminal state. The platform's post-merge completion transition and the agent's tool access overlap.</t>
-        </is>
-      </c>
-      <c r="I88" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Open — team to address later. Options: remove transition_work_item from the build agent's allowlist (platform owns all WorkItem state); or scope it so the agent may only transition remediation child items it owns; or reject agent-initiated transitions to gated states ('accepted'/'done') server-side.</t>
-        </is>
-      </c>
-      <c r="J88" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Open</t>
-        </is>
+      <c r="B88" s="2" t="s">
+        <v>378</v>
+      </c>
+      <c r="C88" s="2" t="s">
+        <v>379</v>
+      </c>
+      <c r="D88" s="2" t="s">
+        <v>380</v>
+      </c>
+      <c r="E88" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F88" s="2" t="s">
+        <v>381</v>
+      </c>
+      <c r="G88" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="H88" s="2" t="s">
+        <v>382</v>
+      </c>
+      <c r="I88" s="2" t="s">
+        <v>383</v>
+      </c>
+      <c r="J88" s="2" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="89" spans="1:10" ht="409.6">
       <c r="A89" s="2">
         <v>88</v>
       </c>
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Merging the PR directly on GitHub bypasses the platform merge gate and orphans the BuildWorkflow (no reachable webhook to reconcile the external merge)</t>
-        </is>
-      </c>
-      <c r="C89" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The intended completion flow is: PR -&gt; platform code review -&gt; merge gate approved in the platform -&gt; platform merges via CodeHost -&gt; WorkItem done. On WI-18 the developer merged PR #1 directly on GitHub instead. Because the platform runs on localhost and no GitHub webhook is configured/reachable (GITHUB_WEBHOOK_SECRET empty; GitHub cannot reach localhost), the platform never learned of the merge. Result: the BuildWorkflow (build-run-dbf76d68) is left RUNNING, parked at the review/merge-gate step for a PR that is already merged, and will never complete on its own. The code did land on main (the developer's merge), but the platform workflow and gate are out of sync.</t>
-        </is>
-      </c>
-      <c r="D89" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Build pipeline / CodeHost / Webhooks</t>
-        </is>
-      </c>
-      <c r="E89" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bug</t>
-        </is>
-      </c>
-      <c r="F89" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">backend/integrations/webhooks.py (GitHub PR-merge -&gt; transition done, needs a reachable endpoint + GITHUB_WEBHOOK_SECRET); backend/orchestration/build_workflow.py (merge gate expects the platform to merge); settings.GITHUB_WEBHOOK_SECRET (empty)</t>
-        </is>
-      </c>
-      <c r="G89" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P2</t>
-        </is>
-      </c>
-      <c r="H89" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The platform-driven merge (via the merge gate) and an external GitHub merge are two paths; only the platform-driven one completes the workflow. The inbound webhook that would reconcile an external merge is not configured/reachable in local dev, so external merges strand the workflow.</t>
-        </is>
-      </c>
-      <c r="I89" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Open — team to address later. Either drive merges through the platform merge gate (Gates page) so the platform merges + completes the workflow, OR expose the platform on a reachable URL (tunnel/deploy) + configure the GitHub webhook with GITHUB_WEBHOOK_SECRET so external merges reconcile (transition done + let the workflow finish). Interim: terminate the currently-orphaned build-run-dbf76d68 workflow.</t>
-        </is>
-      </c>
-      <c r="J89" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Open</t>
-        </is>
+      <c r="B89" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="C89" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="D89" s="2" t="s">
+        <v>386</v>
+      </c>
+      <c r="E89" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F89" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="G89" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="H89" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="I89" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="J89" s="2" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="90" spans="1:10" ht="409.6">
       <c r="A90" s="2">
         <v>89</v>
       </c>
-      <c r="B90" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Takeover-timeout marks a companion phase run terminally 'failed' even when the companion later reports success; the closed workflow then blocks the review gate's Approve</t>
-        </is>
-      </c>
-      <c r="C90" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">A companion goes offline after a phase is dispatched; the report-timeout fires and mark_phase_takeover sets the run to terminal FAILED; AgentRunWorkflow returns {status: takeover} so the workflow COMPLETES. If the companion later returns, registers artifacts, and POSTs report status=ok, that late success does NOT reconcile the run out of FAILED - UI shows 'Failed / engine exited before reporting, no artifact registered' (false: artifacts WERE registered). Second face: the workflow already completed, so decide_gate's signal has no live workflow and Approve cannot publish. Observed on SpendLog Architecture run 8738d4ba (tenant 212395b8): dispatched 2026-07-12 19:49Z, laptop asleep ~7.5h, takeover 03:27Z (run-&gt;failed), 11 artifacts registered 03:55Z, report ok 03:56Z. Related to rows 61/62.</t>
-        </is>
-      </c>
-      <c r="D90" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Orchestration / Companion runs / Gates</t>
-        </is>
-      </c>
-      <c r="E90" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bug</t>
-        </is>
-      </c>
-      <c r="F90" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">backend/orchestration/workflows.py AgentRunWorkflow.run (report wait ~L52, takeover return ~L61); activities.py mark_phase_takeover_core ~L389; phase_report.py report_phase (no reconcile when workflow gone); apps/gates/services.py decide_gate ~L133-159 (raises if COMPLETED); UI copy 'engine exited before reporting'</t>
-        </is>
-      </c>
-      <c r="G90" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P1</t>
-        </is>
-      </c>
-      <c r="H90" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">FAILED is treated as terminal and a late successful phase.reported does not reconcile it; report_timeout (7200s wall-clock from dispatch) trips on an asleep companion that later completes fine. Once run() returns on takeover the workflow is gone, so both phase_report and decide_gate have no live workflow to signal.</t>
-        </is>
-      </c>
-      <c r="I90" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Open - co-dev (tarun's team) to fix. Proposed: (1) a late phase.reported ok reconciles the run to awaiting_gate + opens the gate; (2) treat takeover as a reclaimable 'parked' state, not terminal, while the companion still heartbeats; (3) decide_gate tolerates an absent/closed workflow and drives publish_artifacts + transition_work_item directly; (4) fix the misleading UI copy. Run 8738d4ba manually reconciled to awaiting_gate 2026-07-13.</t>
-        </is>
-      </c>
-      <c r="J90" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Open</t>
-        </is>
+      <c r="B90" s="2" t="s">
+        <v>390</v>
+      </c>
+      <c r="C90" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="D90" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="E90" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F90" s="2" t="s">
+        <v>393</v>
+      </c>
+      <c r="G90" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H90" s="2" t="s">
+        <v>394</v>
+      </c>
+      <c r="I90" s="2" t="s">
+        <v>395</v>
+      </c>
+      <c r="J90" s="2" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="91" spans="1:10" ht="409.6">
       <c r="A91" s="2">
         <v>90</v>
       </c>
-      <c r="B91" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">EPIC: Multi-repo work-item assignment (Hybrid Option C) - agent proposes a repo per work item, human confirms/overrides at the Task Breakdown gate, then implementation routes each task to its repo</t>
-        </is>
-      </c>
-      <c r="C91" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Approved design (team, 2026-07-13). Task Breakdown auto-suggests a repository for every work item (with rationale + confidence); the reviewer confirms or overrides at the gate before assignment is locked; implementation opens each PR in the assigned repo; a user can redirect any task until its build starts. Single-repo projects skip the review (all tasks -&gt; the one repo). Mockup: docs/design/screens/S-23b-repo-assignment-flow.html. Decomposed into rows 91-102 (A1-A5, B1-B4, C1-C2, E1). Follows the platform law draft-&gt;reviewed-&gt;gated-&gt;published.</t>
-        </is>
-      </c>
-      <c r="D91" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Task Breakdown / Multi-repo / Build routing</t>
-        </is>
-      </c>
-      <c r="E91" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Enhancement (Epic)</t>
-        </is>
-      </c>
-      <c r="F91" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">docs/design/screens/S-23b-repo-assignment-flow.html; verified gaps across mcp_platform_state/tools.py, backend/manifest/composer.py, backend/api/*, agents/06_task_breakdown/agent.md, frontend S-13/S-23/S-16</t>
-        </is>
-      </c>
-      <c r="G91" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P1</t>
-        </is>
-      </c>
-      <c r="H91" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Multi-repo infra (WorkItem.repo FK, repo-scoped context, repo_topology, per-repo manifest, build routing on work_item.repo) exists, but nothing lets Task Breakdown assign a repo, nor a user set/override it - so multi-repo routing was impossible end-to-end.</t>
-        </is>
-      </c>
-      <c r="I91" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Open - build in order A1-&gt;A4, B1-&gt;B3, C1, E1, then D1 verify. Backward-compatible: repo_id optional, single-repo unchanged.</t>
-        </is>
-      </c>
-      <c r="J91" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">In Progress</t>
-        </is>
+      <c r="B91" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="C91" s="2" t="s">
+        <v>397</v>
+      </c>
+      <c r="D91" s="2" t="s">
+        <v>398</v>
+      </c>
+      <c r="E91" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="F91" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="G91" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H91" s="2" t="s">
+        <v>401</v>
+      </c>
+      <c r="I91" s="2" t="s">
+        <v>402</v>
+      </c>
+      <c r="J91" s="2" t="s">
+        <v>403</v>
       </c>
     </row>
     <row r="92" spans="1:10" ht="409.6">
       <c r="A92" s="2">
         <v>91</v>
       </c>
-      <c r="B92" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">A1: get_context does not return the project's repository list for project-level/planning runs - only repo_topology + the single scoped repo. Task Breakdown can't see the repos to assign them</t>
-        </is>
-      </c>
-      <c r="C92" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">For a project-level run (no repo_id/work_item repo), get_context returns profile.repo_topology and repo=null, but never enumerates the project's repositories. The Task Breakdown agent therefore has no list of frontend/backend/infra repos (id, name, role) to classify against.</t>
-        </is>
-      </c>
-      <c r="D92" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Platform-State MCP / Context</t>
-        </is>
-      </c>
-      <c r="E92" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Enhancement</t>
-        </is>
-      </c>
-      <c r="F92" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mcp_platform_state/tools.py get_context (~L172-224); mirror runner/companion/state_mcp.py</t>
-        </is>
-      </c>
-      <c r="G92" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P1</t>
-        </is>
-      </c>
-      <c r="H92" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">get_context was written for repo-scoped runs (D5) and never surfaced the repo set for project-level planning runs.</t>
-        </is>
-      </c>
-      <c r="I92" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Open. Add a repositories[] list (id, name, role, default_base, is_default) to get_context's return for project-level runs; mirror in the companion state_mcp proxy.</t>
-        </is>
-      </c>
-      <c r="J92" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Fixed</t>
-        </is>
+      <c r="B92" s="2" t="s">
+        <v>404</v>
+      </c>
+      <c r="C92" s="2" t="s">
+        <v>405</v>
+      </c>
+      <c r="D92" s="2" t="s">
+        <v>406</v>
+      </c>
+      <c r="E92" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F92" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="G92" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H92" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="I92" s="2" t="s">
+        <v>409</v>
+      </c>
+      <c r="J92" s="2" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="93" spans="1:10" ht="409.6">
       <c r="A93" s="2">
         <v>92</v>
       </c>
-      <c r="B93" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">A2: create_work_item has no repo_id parameter - the Task Breakdown agent cannot pin a work item to a repo when proposing it</t>
-        </is>
-      </c>
-      <c r="C93" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">create_work_item(tenant, project, type, title, description, parent_id, feature_stream, depends_on) omits repo_id, so every proposed work item is created with repo=null regardless of topology. The agent literally cannot assign a repo.</t>
-        </is>
-      </c>
-      <c r="D93" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Platform-State MCP / Work Items</t>
-        </is>
-      </c>
-      <c r="E93" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Enhancement</t>
-        </is>
-      </c>
-      <c r="F93" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mcp_platform_state/tools.py create_work_item (~L343); server.py tool registration; runner/companion/state_mcp.py; backend/api/runner_views.py allowlist</t>
-        </is>
-      </c>
-      <c r="G93" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P1</t>
-        </is>
-      </c>
-      <c r="H93" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Signature predates multi-repo assignment.</t>
-        </is>
-      </c>
-      <c r="I93" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Open. Add optional repo_id (validated to a Repository in the same tenant/project); propagate the signature through server.py, state_mcp.py, and the runner_views allowlist. Keep optional -&gt; single-repo/repo-less unchanged.</t>
-        </is>
-      </c>
-      <c r="J93" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Fixed</t>
-        </is>
+      <c r="B93" s="2" t="s">
+        <v>410</v>
+      </c>
+      <c r="C93" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="D93" s="2" t="s">
+        <v>412</v>
+      </c>
+      <c r="E93" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F93" s="2" t="s">
+        <v>413</v>
+      </c>
+      <c r="G93" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H93" s="2" t="s">
+        <v>414</v>
+      </c>
+      <c r="I93" s="2" t="s">
+        <v>415</v>
+      </c>
+      <c r="J93" s="2" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="94" spans="1:10" ht="409.6">
       <c r="A94" s="2">
         <v>93</v>
       </c>
-      <c r="B94" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">A3: the Manifest Composer renders '# Repository' only for a single repo-scoped run - a multi-repo project-level manifest never lists the repos for the agent</t>
-        </is>
-      </c>
-      <c r="C94" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">composer._render_repository renders one repo (context.repo) for repo-scoped runs; for a project-level multi-repo run context.repo is null, so the manifest shows repo_topology: multi but no repository list. Even with A1, the agent's manifest wouldn't show the repos to choose from.</t>
-        </is>
-      </c>
-      <c r="D94" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Manifest Composer</t>
-        </is>
-      </c>
-      <c r="E94" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Enhancement</t>
-        </is>
-      </c>
-      <c r="F94" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">backend/manifest/composer.py _render_repository (~L89), compose (~L218)</t>
-        </is>
-      </c>
-      <c r="G94" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P1</t>
-        </is>
-      </c>
-      <c r="H94" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Per-repo section was designed for the single repo a run targets, not the full set for a planning run.</t>
-        </is>
-      </c>
-      <c r="I94" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Open. Render a '# Repositories' (plural) section (name + role per repo) when a project-level run is multi-repo; keep the singular section for repo-scoped runs.</t>
-        </is>
-      </c>
-      <c r="J94" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Fixed</t>
-        </is>
+      <c r="B94" s="2" t="s">
+        <v>416</v>
+      </c>
+      <c r="C94" s="2" t="s">
+        <v>417</v>
+      </c>
+      <c r="D94" s="2" t="s">
+        <v>418</v>
+      </c>
+      <c r="E94" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F94" s="2" t="s">
+        <v>419</v>
+      </c>
+      <c r="G94" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H94" s="2" t="s">
+        <v>420</v>
+      </c>
+      <c r="I94" s="2" t="s">
+        <v>421</v>
+      </c>
+      <c r="J94" s="2" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="95" spans="1:10" ht="409.6">
       <c r="A95" s="2">
         <v>94</v>
       </c>
-      <c r="B95" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">A4: the 06 Task Breakdown agent is not taught to classify work items by repo, pass repo_id, or emit a rationale + confidence</t>
-        </is>
-      </c>
-      <c r="C95" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The migrated agent body proposes work items but has no repo-assignment protocol. Teach it to read the repositories from context, classify each item (frontend/backend/infra/shared) with a one-line rationale + confidence, pass repo_id to create_work_item, and route all items to the single repo when topology=single.</t>
-        </is>
-      </c>
-      <c r="D95" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Agents / Task Breakdown</t>
-        </is>
-      </c>
-      <c r="E95" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Enhancement (Agent)</t>
-        </is>
-      </c>
-      <c r="F95" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">agents/06_task_breakdown/agent.md; per docs/AGENT_MIGRATION_SPEC.md (reuse reasoning, rewrite data refs)</t>
-        </is>
-      </c>
-      <c r="G95" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P1</t>
-        </is>
-      </c>
-      <c r="H95" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Agent predates multi-repo; no assignment reasoning existed.</t>
-        </is>
-      </c>
-      <c r="I95" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Open. Add the repo-assignment protocol + emit assignment {repo_id, rationale, confidence} per item (pairs with A5 storage).</t>
-        </is>
-      </c>
-      <c r="J95" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Fixed</t>
-        </is>
+      <c r="B95" s="2" t="s">
+        <v>422</v>
+      </c>
+      <c r="C95" s="2" t="s">
+        <v>423</v>
+      </c>
+      <c r="D95" s="2" t="s">
+        <v>424</v>
+      </c>
+      <c r="E95" s="2" t="s">
+        <v>425</v>
+      </c>
+      <c r="F95" s="2" t="s">
+        <v>426</v>
+      </c>
+      <c r="G95" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H95" s="2" t="s">
+        <v>427</v>
+      </c>
+      <c r="I95" s="2" t="s">
+        <v>428</v>
+      </c>
+      <c r="J95" s="2" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="96" spans="1:10" ht="409.6">
       <c r="A96" s="2">
         <v>95</v>
       </c>
-      <c r="B96" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">A5 (decision): where to store each item's repo-assignment rationale + confidence so the review UI can show them</t>
-        </is>
-      </c>
-      <c r="C96" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The review screen (B2) shows the agent's reason + confidence per work item. Decide the storage: a new WorkItem field vs. a structured payload in external_ref vs. a sidecar assignment record. Recommendation: keep it on the work item (e.g. external_ref.repo_assignment = {rationale, confidence, suggested_repo_id}) so it travels with the item and survives reconciliation.</t>
-        </is>
-      </c>
-      <c r="D96" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Data model / Work Items</t>
-        </is>
-      </c>
-      <c r="E96" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Enhancement (Design decision)</t>
-        </is>
-      </c>
-      <c r="F96" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">backend/apps/workitems/models.py; mcp_platform_state/tools.py create_work_item; consumed by frontend S-23</t>
-        </is>
-      </c>
-      <c r="G96" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P1</t>
-        </is>
-      </c>
-      <c r="H96" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">No field currently carries an agent suggestion + confidence for review.</t>
-        </is>
-      </c>
-      <c r="I96" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Open - pending team's answer (keep rationale/confidence? yes recommended). Then implement the chosen storage.</t>
-        </is>
-      </c>
-      <c r="J96" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Fixed</t>
-        </is>
+      <c r="B96" s="2" t="s">
+        <v>429</v>
+      </c>
+      <c r="C96" s="2" t="s">
+        <v>430</v>
+      </c>
+      <c r="D96" s="2" t="s">
+        <v>431</v>
+      </c>
+      <c r="E96" s="2" t="s">
+        <v>432</v>
+      </c>
+      <c r="F96" s="2" t="s">
+        <v>433</v>
+      </c>
+      <c r="G96" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H96" s="2" t="s">
+        <v>434</v>
+      </c>
+      <c r="I96" s="2" t="s">
+        <v>435</v>
+      </c>
+      <c r="J96" s="2" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="97" spans="1:10" ht="409.6">
       <c r="A97" s="2">
         <v>96</v>
       </c>
-      <c r="B97" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">B1: WorkItem.repo is not editable via the API - the work-item PATCH allows only title/description/type, so a user cannot assign or redirect a task's repo</t>
-        </is>
-      </c>
-      <c r="C97" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WorkItemPatchSerializer fields = [title, description, type]. There is no way to set WorkItem.repo through the API/UI, so neither the review-screen override nor the per-task redirect can persist.</t>
-        </is>
-      </c>
-      <c r="D97" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Work Items / API</t>
-        </is>
-      </c>
-      <c r="E97" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Enhancement (API gap)</t>
-        </is>
-      </c>
-      <c r="F97" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">backend/api/serializers.py WorkItemPatchSerializer (~L255); backend/api/views.py partial_update</t>
-        </is>
-      </c>
-      <c r="G97" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P1</t>
-        </is>
-      </c>
-      <c r="H97" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Patch surface was scoped to human text edits (S-15/S-16), never repo.</t>
-        </is>
-      </c>
-      <c r="I97" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Open. Allow repo on the work-item PATCH, validated to a Repository in the same tenant/project. Build routing already honors work_item.repo (verified trigger_build).</t>
-        </is>
-      </c>
-      <c r="J97" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Fixed</t>
-        </is>
+      <c r="B97" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="C97" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="D97" s="2" t="s">
+        <v>438</v>
+      </c>
+      <c r="E97" s="2" t="s">
+        <v>439</v>
+      </c>
+      <c r="F97" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="G97" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H97" s="2" t="s">
+        <v>441</v>
+      </c>
+      <c r="I97" s="2" t="s">
+        <v>442</v>
+      </c>
+      <c r="J97" s="2" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="98" spans="1:10" ht="409.6">
       <c r="A98" s="2">
         <v>97</v>
       </c>
-      <c r="B98" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">B2 (new component): Task Breakdown repo-assignment REVIEW screen - grouped-by-repo, agent suggestion + reason + confidence, override dropdown, 'X of N confirmed', flagged-first, Approve</t>
-        </is>
-      </c>
-      <c r="C98" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">New review surface on S-23 where the reviewer confirms/overrides the agent's repo suggestions before the gate. Low-confidence items surfaced first; overrides visually marked; progress toward 'all confirmed'; Approve wires to the gate decision (C1). Design locked in docs/design/screens/S-23b-repo-assignment-flow.html.</t>
-        </is>
-      </c>
-      <c r="D98" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Frontend / Task Breakdown</t>
-        </is>
-      </c>
-      <c r="E98" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">New Component</t>
-        </is>
-      </c>
-      <c r="F98" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">frontend S-23 (features/lifecycle or task-breakdown); consumes A5 payload + B1 PATCH; mockup S-23b</t>
-        </is>
-      </c>
-      <c r="G98" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P1</t>
-        </is>
-      </c>
-      <c r="H98" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">No UI exists to review/assign repos.</t>
-        </is>
-      </c>
-      <c r="I98" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Open - build to the approved mockup after team sign-off (see decisions: review-at-gate vs separate screen; grouping; bulk actions).</t>
-        </is>
-      </c>
-      <c r="J98" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Fixed</t>
-        </is>
+      <c r="B98" s="2" t="s">
+        <v>443</v>
+      </c>
+      <c r="C98" s="2" t="s">
+        <v>444</v>
+      </c>
+      <c r="D98" s="2" t="s">
+        <v>445</v>
+      </c>
+      <c r="E98" s="2" t="s">
+        <v>446</v>
+      </c>
+      <c r="F98" s="2" t="s">
+        <v>447</v>
+      </c>
+      <c r="G98" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H98" s="2" t="s">
+        <v>448</v>
+      </c>
+      <c r="I98" s="2" t="s">
+        <v>449</v>
+      </c>
+      <c r="J98" s="2" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="99" spans="1:10" ht="409.6">
       <c r="A99" s="2">
         <v>98</v>
       </c>
-      <c r="B99" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">B3 (new component): repo selector on the work item / board to redirect a task to another repo until its build starts</t>
-        </is>
-      </c>
-      <c r="C99" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">A repo dropdown on the work-item detail (S-16) and/or board (S-14), populated from the repositories endpoint, calling B1's PATCH. Editable until the task's build starts; read-only once the PR opens. This is the 'redirect any task' escape hatch.</t>
-        </is>
-      </c>
-      <c r="D99" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Frontend / Work Items</t>
-        </is>
-      </c>
-      <c r="E99" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">New Component</t>
-        </is>
-      </c>
-      <c r="F99" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">frontend S-16, S-14; consumes B1 PATCH + repositories GET</t>
-        </is>
-      </c>
-      <c r="G99" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P1</t>
-        </is>
-      </c>
-      <c r="H99" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">No per-item repo control exists.</t>
-        </is>
-      </c>
-      <c r="I99" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Open - build after B1. Show assigned repo + role; disable after build start.</t>
-        </is>
-      </c>
-      <c r="J99" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Fixed</t>
-        </is>
+      <c r="B99" s="2" t="s">
+        <v>450</v>
+      </c>
+      <c r="C99" s="2" t="s">
+        <v>451</v>
+      </c>
+      <c r="D99" s="2" t="s">
+        <v>452</v>
+      </c>
+      <c r="E99" s="2" t="s">
+        <v>446</v>
+      </c>
+      <c r="F99" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="G99" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H99" s="2" t="s">
+        <v>454</v>
+      </c>
+      <c r="I99" s="2" t="s">
+        <v>455</v>
+      </c>
+      <c r="J99" s="2" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="100" spans="1:10" ht="409.6">
       <c r="A100" s="2">
         <v>99</v>
       </c>
-      <c r="B100" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">B4 (verify): confirm the Repositories setup UI captures each repo's role (frontend/backend/infra) in the live app</t>
-        </is>
-      </c>
-      <c r="C100" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Auto-assign keys off Repository.role. The mockup S-13 and the model support role; verify the live Repositories.tsx add-repo form actually captures and persists role, and fix if missing.</t>
-        </is>
-      </c>
-      <c r="D100" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Frontend / Setup</t>
-        </is>
-      </c>
-      <c r="E100" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Issue (Verify)</t>
-        </is>
-      </c>
-      <c r="F100" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">frontend/src/features/setup/Repositories.tsx; backend RepositoryCreateSerializer</t>
-        </is>
-      </c>
-      <c r="G100" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P2</t>
-        </is>
-      </c>
-      <c r="H100" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Role is optional on the model; UI may not surface it.</t>
-        </is>
-      </c>
-      <c r="I100" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Open - verify in the running app; add the role field if absent.</t>
-        </is>
-      </c>
-      <c r="J100" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Open</t>
-        </is>
+      <c r="B100" s="2" t="s">
+        <v>456</v>
+      </c>
+      <c r="C100" s="2" t="s">
+        <v>457</v>
+      </c>
+      <c r="D100" s="2" t="s">
+        <v>458</v>
+      </c>
+      <c r="E100" s="2" t="s">
+        <v>459</v>
+      </c>
+      <c r="F100" s="2" t="s">
+        <v>460</v>
+      </c>
+      <c r="G100" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="H100" s="2" t="s">
+        <v>461</v>
+      </c>
+      <c r="I100" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="J100" s="2" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="101" spans="1:10" ht="409.6">
       <c r="A101" s="2">
         <v>100</v>
       </c>
-      <c r="B101" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">C1: wire 'Approve assignment &amp; continue' as the Task Breakdown gate decision - approving locks the repo assignments</t>
-        </is>
-      </c>
-      <c r="C101" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The review screen's Approve must be the Task Breakdown gate decision: on approve, the assignments are locked and the phase proceeds. Ties B2 (UI) to the gate services so the assignment is committed exactly once, with human sign-off (matches draft-&gt;reviewed-&gt;gated-&gt;published).</t>
-        </is>
-      </c>
-      <c r="D101" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gates / Task Breakdown</t>
-        </is>
-      </c>
-      <c r="E101" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Enhancement</t>
-        </is>
-      </c>
-      <c r="F101" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">backend/apps/gates/services.py + models; backend/api/views.py; frontend gate (S-21/S-23)</t>
-        </is>
-      </c>
-      <c r="G101" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P1</t>
-        </is>
-      </c>
-      <c r="H101" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gate decision currently approves the backlog, not the repo assignment.</t>
-        </is>
-      </c>
-      <c r="I101" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Open. On approve, lock assignments (freeze repo per item); proceed. Pairs with C2 decision.</t>
-        </is>
-      </c>
-      <c r="J101" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Fixed</t>
-        </is>
+      <c r="B101" s="2" t="s">
+        <v>463</v>
+      </c>
+      <c r="C101" s="2" t="s">
+        <v>464</v>
+      </c>
+      <c r="D101" s="2" t="s">
+        <v>465</v>
+      </c>
+      <c r="E101" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F101" s="2" t="s">
+        <v>466</v>
+      </c>
+      <c r="G101" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H101" s="2" t="s">
+        <v>467</v>
+      </c>
+      <c r="I101" s="2" t="s">
+        <v>468</v>
+      </c>
+      <c r="J101" s="2" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="102" spans="1:10" ht="409.6">
       <c r="A102" s="2">
         <v>101</v>
       </c>
-      <c r="B102" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">C2 (decision): should the gate BLOCK approval while low-confidence items are unreviewed, or only warn?</t>
-        </is>
-      </c>
-      <c r="C102" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Business rule for C1: either hard-block Approve until every flagged (low-confidence) item is confirmed, or allow approval with a warning. Recommendation: warn + require an explicit 'confirm all' rather than hard-block, to avoid dead-ends on large backlogs.</t>
-        </is>
-      </c>
-      <c r="D102" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gates / Task Breakdown</t>
-        </is>
-      </c>
-      <c r="E102" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Enhancement (Design decision)</t>
-        </is>
-      </c>
-      <c r="F102" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">backend/apps/gates/services.py decide_gate; frontend S-23 Approve enablement</t>
-        </is>
-      </c>
-      <c r="G102" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P1</t>
-        </is>
-      </c>
-      <c r="H102" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">No policy defined yet for unreviewed suggestions at the gate.</t>
-        </is>
-      </c>
-      <c r="I102" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Open - pending team's answer (block vs warn).</t>
-        </is>
-      </c>
-      <c r="J102" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Fixed</t>
-        </is>
+      <c r="B102" s="2" t="s">
+        <v>469</v>
+      </c>
+      <c r="C102" s="2" t="s">
+        <v>470</v>
+      </c>
+      <c r="D102" s="2" t="s">
+        <v>465</v>
+      </c>
+      <c r="E102" s="2" t="s">
+        <v>432</v>
+      </c>
+      <c r="F102" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="G102" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H102" s="2" t="s">
+        <v>472</v>
+      </c>
+      <c r="I102" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="J102" s="2" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="103" spans="1:10" ht="409.6">
       <c r="A103" s="2">
         <v>102</v>
       </c>
-      <c r="B103" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">E1 (tooling): cross-tenant upstream-artifact clone command (ideation-&gt;architecture + their S3 bodies) for the multi-repo test - write-only to the new tenant</t>
-        </is>
-      </c>
-      <c r="C103" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">For the multi-repo test, copy the prior-phase artifacts (ideation, requirements, PRD, architecture) + their S3 bodies from the old tenant into the new multi-repo tenant, so UX + Task Breakdown can run natively there. Reads the old tenant, writes only the new one (old tenant untouched). Remaps tenant/project/run + UUIDs; copies S3 objects to new keys + rewrites pointers. Transactional with --dry-run + tests.</t>
-        </is>
-      </c>
-      <c r="D103" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Tooling / Tenancy / Registry</t>
-        </is>
-      </c>
-      <c r="E103" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">New Component (tooling)</t>
-        </is>
-      </c>
-      <c r="F103" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">new backend Django management command; reads apps/registry + S3 (drafts/{tenant}/{project}/{run}/{phase}/{file}); run as sdlc_migrator</t>
-        </is>
-      </c>
-      <c r="G103" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P2</t>
-        </is>
-      </c>
-      <c r="H103" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">No tenant/project clone capability exists; DB-only copy is insufficient (S3 bodies + ID remap).</t>
-        </is>
-      </c>
-      <c r="I103" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Open - build after A/B/C; needs the team's new tenant + project ids.</t>
-        </is>
-      </c>
-      <c r="J103" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Fixed</t>
-        </is>
+      <c r="B103" s="2" t="s">
+        <v>474</v>
+      </c>
+      <c r="C103" s="2" t="s">
+        <v>475</v>
+      </c>
+      <c r="D103" s="2" t="s">
+        <v>476</v>
+      </c>
+      <c r="E103" s="2" t="s">
+        <v>477</v>
+      </c>
+      <c r="F103" s="2" t="s">
+        <v>478</v>
+      </c>
+      <c r="G103" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="H103" s="2" t="s">
+        <v>479</v>
+      </c>
+      <c r="I103" s="2" t="s">
+        <v>480</v>
+      </c>
+      <c r="J103" s="2" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="104" spans="1:10" ht="409.6">
       <c r="A104" s="2">
         <v>103</v>
       </c>
-      <c r="B104" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Code host connect form shows a single 'Repository' field on multi-repo projects - reads as single-repo; should be labeled 'Default repository' with a hint that the token must cover ALL repos</t>
-        </is>
-      </c>
-      <c r="C104" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">On a multi-repo project, Integrations &gt; Code host presents one 'Repository' input. The codehost capability is tenant-wide (one connection/token covers every repo; each build targets its own repo via work_item.repo), so this field is only a fallback default - not a per-repo binding. But the lone field looks single-repo and leaves users unsure which repo to enter or whether both are covered. UX-only; functionally correct (both repos flip to 'connected' once any code-host connection is configured).</t>
-        </is>
-      </c>
-      <c r="D104" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Integrations / Code host / Multi-repo</t>
-        </is>
-      </c>
-      <c r="E104" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Enhancement (UX)</t>
-        </is>
-      </c>
-      <c r="F104" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">frontend Integrations code-host connect form (S-12 Connect capability); backend/apps/projects/repos.py _codehost_status (tenant-wide status); backend/integrations/registry.py _build_github (default_repo fallback)</t>
-        </is>
-      </c>
-      <c r="G104" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P2</t>
-        </is>
-      </c>
-      <c r="H104" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The code-host connect form predates multi-repo. The 'Repository' field is the connection's default/fallback repo, but is not labeled as such, so on a multi-repo project it looks like you must pick one repo.</t>
-        </is>
-      </c>
-      <c r="I104" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Open - P2, team to address later. Relabel to 'Default repository (optional)'; add a hint that ONE token must reach ALL of the project's repos (a classic PAT with repo scope, or a fine-grained token listing each repo); optionally list the project's repos + connected status inline so it's clear all are covered.</t>
-        </is>
-      </c>
-      <c r="J104" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Open</t>
-        </is>
+      <c r="B104" s="2" t="s">
+        <v>481</v>
+      </c>
+      <c r="C104" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="D104" s="2" t="s">
+        <v>483</v>
+      </c>
+      <c r="E104" s="2" t="s">
+        <v>484</v>
+      </c>
+      <c r="F104" s="2" t="s">
+        <v>485</v>
+      </c>
+      <c r="G104" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="H104" s="2" t="s">
+        <v>486</v>
+      </c>
+      <c r="I104" s="2" t="s">
+        <v>487</v>
+      </c>
+      <c r="J104" s="2" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="105" spans="1:10" ht="409.6">
       <c r="A105" s="2">
         <v>104</v>
       </c>
-      <c r="B105" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Project topology auto-derives from repo count (2=split, 3+=multi) and overrides the user's explicit 'Multi-repo' choice; the create form offers only Single/Multi (2 options) while the model has 3 (single/split/multi)</t>
-        </is>
-      </c>
-      <c r="C105" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">On create the user picks Single or Multi-repo (sets project.repo_topology). But adding repositories recomputes it via _topology_for (count&gt;=3 -&gt; multi, ==2 -&gt; split, else single). So a user who explicitly chose 'Multi-repo' and added 2 repos ends up with topology='split' in the DB, while the create choice (and at least one screen) showed 'multi'. Effects: (a) the explicit choice is silently overridden; (b) the 2-option create UI never exposes 'split'; (c) features gated on topology=='multi' (e.g. API-contract/drift checks - per the Repositories page copy) would NOT fire for a 2-repo 'split' project (may be intended - confirm). NOTE: does NOT affect the repo-assignment feature (Option C), which keys off repo COUNT&gt;1, so 2 repos work regardless.</t>
-        </is>
-      </c>
-      <c r="D105" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Projects / Repositories / Topology</t>
-        </is>
-      </c>
-      <c r="E105" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Issue (Consistency/UX)</t>
-        </is>
-      </c>
-      <c r="F105" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">frontend CreateProject (Single/Multi toggle); backend/apps/projects/repos.py _topology_for (recompute on add/remove); projects_project.repo_topology; Repositories page Topology chip + 'Multi-repo drives API-contract &amp; drift checks' copy</t>
-        </is>
-      </c>
-      <c r="G105" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P3</t>
-        </is>
-      </c>
-      <c r="H105" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Two sources of truth for topology: the create-form choice and the count-derived value. Adding repos recomputes and can override the explicit pick; the create UI exposes 2 options while the model has 3.</t>
-        </is>
-      </c>
-      <c r="I105" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Open - P3, later. Pick one source of truth: (a) honor the user's explicit choice and stop auto-deriving, or (b) always derive from count and clarify the labels so a 2-repo project still reads as multi to the user. Confirm whether API-contract/drift checks intentionally require 3+ repos ('multi') vs 2 ('split').</t>
-        </is>
-      </c>
-      <c r="J105" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Open</t>
-        </is>
+      <c r="B105" s="2" t="s">
+        <v>488</v>
+      </c>
+      <c r="C105" s="2" t="s">
+        <v>489</v>
+      </c>
+      <c r="D105" s="2" t="s">
+        <v>490</v>
+      </c>
+      <c r="E105" s="2" t="s">
+        <v>491</v>
+      </c>
+      <c r="F105" s="2" t="s">
+        <v>492</v>
+      </c>
+      <c r="G105" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H105" s="2" t="s">
+        <v>493</v>
+      </c>
+      <c r="I105" s="2" t="s">
+        <v>494</v>
+      </c>
+      <c r="J105" s="2" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="106" spans="1:10" ht="409.6">
       <c r="A106" s="2">
         <v>105</v>
       </c>
-      <c r="B106" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">A backend/worker restart drops the local companion and it does NOT auto-reconnect - the companion stops heartbeating/polling, and a run dispatched right after is left unclaimed until the companion is manually restarted</t>
-        </is>
-      </c>
-      <c r="C106" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Observed on SpendLog-1 (new multi-repo tenant): after a 'docker restart backend worker' (needed to load mcp_platform_state changes), the companion last_seen froze at the restart time and never resumed. A Task Breakdown triggered right after was dispatched but its dispatch stayed status=pending (never claimed) and the agent never started. Manually reconnecting with the SAME token restored it (enrollment cc5de985 re-claimed the pending run and proceeded). Recoverable, but the companion should survive / auto-reconnect a transient backend restart instead of dying silently. Related to rows 61 (companion false-offline) and 89 (takeover-timeout).</t>
-        </is>
-      </c>
-      <c r="D106" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Companion / Runner / Reliability</t>
-        </is>
-      </c>
-      <c r="E106" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bug</t>
-        </is>
-      </c>
-      <c r="F106" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">runner/companion daemon (serve loop + 30s heartbeat thread); a backend restart drops the HTTP connection; runs_runnerenrollment.last_seen freezes; run dispatch stays status=pending (never claimed)</t>
-        </is>
-      </c>
-      <c r="G106" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P2</t>
-        </is>
-      </c>
-      <c r="H106" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The companion's heartbeat/work-poll loop doesn't robustly survive the backend going away and returning (transient connection loss on restart) - it stops rather than retrying until reconnected.</t>
-        </is>
+      <c r="B106" s="2" t="s">
+        <v>495</v>
+      </c>
+      <c r="C106" s="2" t="s">
+        <v>496</v>
+      </c>
+      <c r="D106" s="2" t="s">
+        <v>497</v>
+      </c>
+      <c r="E106" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F106" s="2" t="s">
+        <v>498</v>
+      </c>
+      <c r="G106" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="H106" s="2" t="s">
+        <v>499</v>
       </c>
       <c r="I106" s="2" t="s">
-        <v>229</v>
+        <v>500</v>
       </c>
       <c r="J106" s="2" t="s">
         <v>16</v>
@@ -6053,603 +6364,477 @@
       <c r="A107" s="2">
         <v>106</v>
       </c>
-      <c r="B107" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Task Breakdown gate repo-assignment review (B2) renders cramped in the narrow gate sidebar (titles wrap one word per line, dropdown overlaps) and lists all 32 tasks with full reasons instead of collapsing the confident groups - does not match the approved full-width mockup S-23b</t>
-        </is>
-      </c>
-      <c r="C107" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Live on SpendLog-1: the Task Breakdown gate opened and the review panel (RepoAssignmentReview) rendered, but (a) it was wired INTO the narrow right-hand gate decision Card (the right column of grid--detail), so at that width task titles + reason + repo dropdown wrap one word/char per line and overlap - not human readable; (b) it renders EVERY one of the 32 tasks with its full rationale rather than surfacing the 2 low-confidence tasks and collapsing the confident backend/frontend groups (the S-23b mockup collapses them with '+N more'). Net: broken layout + verbose noise, doesn't match the developed screen. Underlying data is correct (32/32 assigned, 17 backend / 15 frontend, correct classification).</t>
-        </is>
-      </c>
-      <c r="D107" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Frontend / Gates / Task Breakdown review</t>
-        </is>
-      </c>
-      <c r="E107" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bug</t>
-        </is>
-      </c>
-      <c r="F107" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">frontend/src/features/lifecycle/Gates.tsx (review rendered inside the narrow grid--detail right card); frontend/src/features/lifecycle/RepoAssignmentReview.tsx (renders all rows, no group collapse); mockup docs/design/screens/S-23b-repo-assignment-flow.html (full-width, collapsed confident groups)</t>
-        </is>
-      </c>
-      <c r="G107" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P1</t>
-        </is>
-      </c>
-      <c r="H107" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">B2 was wired into the existing narrow gate decision card instead of a full-width surface, and the component renders all rows without the mockup's confident-group collapse. The mockup was designed full-width; the integration was not.</t>
-        </is>
-      </c>
-      <c r="I107" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Fixing now: render the review FULL-WIDTH when present (stack, not the narrow grid column); add a summary (split counts) + COLLAPSE the confident repo groups (expand on click) + keep the low-confidence flagged tasks expanded at the top; tighten rows so title + repo dropdown sit side by side.</t>
-        </is>
-      </c>
-      <c r="J107" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Fixed</t>
-        </is>
+      <c r="B107" s="2" t="s">
+        <v>501</v>
+      </c>
+      <c r="C107" s="2" t="s">
+        <v>502</v>
+      </c>
+      <c r="D107" s="2" t="s">
+        <v>503</v>
+      </c>
+      <c r="E107" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F107" s="2" t="s">
+        <v>504</v>
+      </c>
+      <c r="G107" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H107" s="2" t="s">
+        <v>505</v>
+      </c>
+      <c r="I107" s="2" t="s">
+        <v>506</v>
+      </c>
+      <c r="J107" s="2" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="108" spans="1:10" ht="409.6">
       <c r="A108" s="2">
         <v>107</v>
       </c>
-      <c r="B108" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Implementation/build companion was single-repo by construction - could not land code in the correct repo on a multi-repo project (Hybrid Option C blocker)</t>
-        </is>
-      </c>
-      <c r="C108" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Pre-build audit before the SpendLog-1 (frontend+backend) implementation run: the backend routes every build to work_item.repo and opens/merges the PR against that exact repo (trigger.py:171-186, build_activities.py open_build_pr/merge), and build is fully SoR-agnostic (internal + Jira both build off platform WorkItem rows with repo intact). BUT the local companion daemon held ONE --repo-path for its whole lifetime and forked every work item's worktree from it, pushing to that clone's origin - ignoring BuildTask.repo entirely (daemon.py:119/195-208, runner.py:152-164; task.repo referenced nowhere in runner/). On a 2-repo project the repo NOT wired into --repo-path would either fail at 'git worktree add' (base branch absent) or, worse, silently push to the wrong repo if a same-named branch existed, after which open_build_pr 404s looking for the head under the correct repo. Violates the non-negotiable 'code lands in the correct GitHub repo'.</t>
-        </is>
-      </c>
-      <c r="D108" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Runner / Companion / Build (implementation phase)</t>
-        </is>
-      </c>
-      <c r="E108" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bug</t>
-        </is>
-      </c>
-      <c r="F108" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">runner/companion/__main__.py (serve --repo NAME=PATH); runner/companion/daemon.py (_resolve_repo_path, _run_build); runner/companion/runner.py (assert_remote_matches before push); runner/companion/worktree.py (assert_remote_matches); backend/tests/test_companion_daemon.py + test_companion_runner.py; docs/PHASE_2_BUILD_SPEC.md</t>
-        </is>
-      </c>
-      <c r="G108" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P1</t>
-        </is>
-      </c>
-      <c r="H108" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The companion build mode was written for the pre-multi-repo (single-repo) world: one --repo-path clone served every task. BuildTask.repo (work_item.repo) was delivered in the dispatch payload but never consumed to pick a clone; there was no repo-&gt;local-path resolver and no clone-on-demand.</t>
-        </is>
-      </c>
-      <c r="I108" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">FIXED. Added a repeatable 'serve --repo owner/name=/path' mapping; the daemon now resolves the clone per BuildTask.repo (_resolve_repo_path) and FAILS LOUD on an unmapped repo instead of falling back to a wrong clone (that build is reported failed, the daemon keeps serving). --repo-path kept as the single-repo shorthand (backward compatible). Defense-in-depth: assert_remote_matches refuses to push if the clone's origin doesn't match the routed repo (hosted remotes only; local/test remotes skipped). Docs updated (PHASE_2_BUILD_SPEC 3) incl. the single GITHUB_TOKEN must cover all mapped repos (see S.No 103). 36 companion tests pass (added: mapped-clone routing, unmapped fail-loud, shorthand back-compat, origin match/mismatch/local-skip, repo-map parse).</t>
-        </is>
-      </c>
-      <c r="J108" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Fixed</t>
-        </is>
+      <c r="B108" s="2" t="s">
+        <v>507</v>
+      </c>
+      <c r="C108" s="2" t="s">
+        <v>508</v>
+      </c>
+      <c r="D108" s="2" t="s">
+        <v>509</v>
+      </c>
+      <c r="E108" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F108" s="2" t="s">
+        <v>510</v>
+      </c>
+      <c r="G108" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H108" s="2" t="s">
+        <v>511</v>
+      </c>
+      <c r="I108" s="2" t="s">
+        <v>512</v>
+      </c>
+      <c r="J108" s="2" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="109" spans="1:10" ht="330">
       <c r="A109" s="2">
         <v>108</v>
       </c>
-      <c r="B109" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Multi-repo: a work item with no repo assigned silently built into the project default repo (e.g. backend code PR'd into the frontend repo) instead of failing</t>
-        </is>
-      </c>
-      <c r="C109" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">trigger_build fell back to the project's is_default Repository whenever a work item had no repo pinned (trigger.py:173-183). Correct for single-repo projects, but on a multi-repo project (Hybrid Option C) an unpinned work item means the Task Breakdown gate assignment was missed - silently defaulting routes it into whatever repo happens to be default (often the frontend), landing code in the wrong GitHub repo. A mis-route, not a hard failure, so it would pass unnoticed.</t>
-        </is>
-      </c>
-      <c r="D109" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Backend / Orchestration / Build trigger</t>
-        </is>
-      </c>
-      <c r="E109" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bug</t>
-        </is>
-      </c>
-      <c r="F109" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">backend/orchestration/trigger.py; backend/tests/test_build_trigger_api.py</t>
-        </is>
-      </c>
-      <c r="G109" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P2</t>
-        </is>
-      </c>
-      <c r="H109" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The default-repo fallback predates multi-repo. It was written so a task could be built from the UI without pinning a repo (single-repo projects, proposed items). It didn't distinguish single-repo (safe to default) from multi-repo (must be explicitly assigned).</t>
-        </is>
-      </c>
-      <c r="I109" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">FIXED. trigger_build now counts the project's repositories: for a multi-repo project (repo_count &gt; 1) an unpinned work item raises a clear TriggerError telling the user to assign its repo (confirm at the Task Breakdown gate or set the work item's repo) - never silently defaults. Single-repo projects keep the default-repo fallback unchanged. Tests added: multi-repo unpinned -&gt; 400 'multiple repositories'; multi-repo pinned to the non-default repo -&gt; builds into that repo with its base. 7/7 build-trigger tests pass.</t>
-        </is>
-      </c>
-      <c r="J109" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Fixed</t>
-        </is>
-      </c>
-    </row>
-    <row r="110" spans="1:10" ht="380">
+      <c r="B109" s="2" t="s">
+        <v>513</v>
+      </c>
+      <c r="C109" s="2" t="s">
+        <v>514</v>
+      </c>
+      <c r="D109" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="E109" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F109" s="2" t="s">
+        <v>516</v>
+      </c>
+      <c r="G109" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="H109" s="2" t="s">
+        <v>517</v>
+      </c>
+      <c r="I109" s="2" t="s">
+        <v>518</v>
+      </c>
+      <c r="J109" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="110" spans="1:10" ht="380.1">
       <c r="A110" s="2">
         <v>109</v>
       </c>
-      <c r="B110" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Repo-assignment review panel resurfaces on non-Task-Breakdown gates (the merge gate, and any later phase gate) - it must render ONLY on the Task Breakdown gate</t>
-        </is>
-      </c>
-      <c r="C110" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Live on SpendLog-1: the implementation MERGE gate for TASK-001 rendered the Task Breakdown repo-assignment review panel ('31 tasks, backend 14 / frontend 15, 2 need review - confirm or change the repo'). Proposed sibling tasks keep their planner repo_assignment long after Task Breakdown, so the panel wrongly reappears on the merge gate - and would also reappear on a later testing/security/deployment phase gate opened while tasks are still proposed.</t>
-        </is>
-      </c>
-      <c r="D110" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Frontend / Gates / Multi-repo (Option C)</t>
-        </is>
-      </c>
-      <c r="E110" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bug (regression)</t>
-        </is>
-      </c>
-      <c r="F110" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">frontend/src/features/lifecycle/Gates.tsx (showReview); backend/api/serializers.py (ApprovalSerializer); frontend/src/types.ts (Approval); follow-up to S.No 106</t>
-        </is>
-      </c>
-      <c r="G110" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P1</t>
-        </is>
-      </c>
-      <c r="H110" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">S.No 106 made the review full-width and wired it into Gates.tsx, but the render condition (showReview = multiRepo &amp;&amp; assignmentItems.length&gt;0) never checked WHICH gate is selected. All planning gates share gate_type 'phase_gate' (only the build gate is 'merge_gate'), so gate_type alone is not a safe discriminator - a testing/security/deployment phase gate would also resurface it.</t>
-        </is>
-      </c>
-      <c r="I110" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">FIXED (2026-07-14). The Approval API now exposes `phase` (the gate run's agent key, e.g. 06_task_breakdown) via ApprovalSerializer; the frontend Approval type carries it; Gates.tsx gates the panel on isTaskBreakdownGate = (selected?.phase === '06_task_breakdown'), so showReview = multiRepo &amp;&amp; isTaskBreakdownGate &amp;&amp; assignmentItems.length&gt;0. The review now renders ONLY on the Task Breakdown gate - never on the merge gate or any future phase gate. Tests: backend test_frontend_integration approval-shape + new phase-field test (3 pass); frontend tsc clean; RepoAssignmentReview.test.tsx (3 pass). To view: backend uvicorn --reload picks up serializers.py automatically; restart ONLY the frontend container (bind-mounted ./frontend) so the companion is not dropped.</t>
-        </is>
-      </c>
-      <c r="J110" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Fixed</t>
-        </is>
-      </c>
-    </row>
-    <row r="111" spans="1:10" ht="380">
+      <c r="B110" s="2" t="s">
+        <v>519</v>
+      </c>
+      <c r="C110" s="2" t="s">
+        <v>520</v>
+      </c>
+      <c r="D110" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="E110" s="2" t="s">
+        <v>522</v>
+      </c>
+      <c r="F110" s="2" t="s">
+        <v>523</v>
+      </c>
+      <c r="G110" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H110" s="2" t="s">
+        <v>524</v>
+      </c>
+      <c r="I110" s="2" t="s">
+        <v>525</v>
+      </c>
+      <c r="J110" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="111" spans="1:10" ht="380.1">
       <c r="A111" s="2">
         <v>110</v>
       </c>
-      <c r="B111" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">08 code review poll times out (480s) and a late/absent review report is not reconciled - the merge gate opens via the fail-safe with ZERO findings even though the review never completed</t>
-        </is>
-      </c>
-      <c r="C111" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Live on SpendLog-1 TASK-001: the 08 review task was dispatched and CLAIMED by the companion (06:07:33 UTC) but no verdict was ever posted within the 480s poll window; review.timeout fired at 06:15:52 and the merge gate opened at 06:15:54 with 0 findings and no code_review artifact. poll_review_body treats a timeout as 'no findings' so the build never hangs (by design) - but the reviewer then approves with NO automated review having run. A review report arriving after the timeout (record_review_report) writes review_body once the poll has already returned, so it is orphaned - never parsed into findings. Parallels S.No 89 (a late report cannot reconcile a closed step).</t>
-        </is>
-      </c>
-      <c r="D111" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Orchestration / Code review (08) / Build pipeline</t>
-        </is>
-      </c>
-      <c r="E111" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bug</t>
-        </is>
-      </c>
-      <c r="F111" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">backend/orchestration/review_provider.py (CompanionReviewProvider timeout=480.0 / poll_review_body / record_review_report); backend/orchestration/build_workflow.py (run_code_review loop); related S.No 89</t>
-        </is>
-      </c>
-      <c r="G111" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P1</t>
-        </is>
-      </c>
-      <c r="H111" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The review poll timeout (480s / 8 min) is shorter than a realistic FIRST companion review (cold engine start + context compaction can add ~7 min). When it trips, timeout is treated as zero blocking findings and the merge gate opens; a review report arriving after the timeout is recorded but never re-parsed, so its findings are silently lost.</t>
-        </is>
-      </c>
-      <c r="I111" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">FIXED (2026-07-14, committed a582737). Three-part fix in the review path: (1) BuildInput.review_timeout_seconds is now per-run configurable with a realistic default of 1800s (was a hard-coded 480s that was shorter than a first cold-companion review); (2) poll_review_body does one final grace read on timeout, so a verdict that lands moments after the last poll tick still drives the 07&lt;-&gt;08 remediation loop instead of being orphaned in run.outputs while the merge gate opens blind; (3) build_workflow.py sets the run_code_review activity start_to_close = review_timeout_seconds + 600s, so the Temporal activity timeout always exceeds the internal poll window (otherwise Temporal would kill and retry the activity mid-review, re-dispatching it). The companion provider reads getattr(inp,'review_timeout_seconds') and falls back to its own default, so an older backend that predates the field is safe. Tests: test_review_dispatch (grace-read + per-run-timeout), ruff clean. This is the review-side analog of S.No 89 (phase-side late-report reconcile, still open for the co-dev team).</t>
-        </is>
-      </c>
-      <c r="J111" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Fixed</t>
-        </is>
-      </c>
-    </row>
-    <row r="112" spans="1:10" ht="380">
+      <c r="B111" s="2" t="s">
+        <v>526</v>
+      </c>
+      <c r="C111" s="2" t="s">
+        <v>527</v>
+      </c>
+      <c r="D111" s="2" t="s">
+        <v>528</v>
+      </c>
+      <c r="E111" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F111" s="2" t="s">
+        <v>529</v>
+      </c>
+      <c r="G111" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H111" s="2" t="s">
+        <v>530</v>
+      </c>
+      <c r="I111" s="2" t="s">
+        <v>531</v>
+      </c>
+      <c r="J111" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="112" spans="1:10" ht="380.1">
       <c r="A112" s="2">
         <v>111</v>
       </c>
-      <c r="B112" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Claim lease vs review window: a phase that legitimately runs longer than the 15-min work-claim lease (e.g. a code review now allowed up to 30 min) is re-claimed mid-flight from a LIVE, heartbeating companion -&gt; duplicate/empty artifacts + a failed re-review, and the merge gate opens blind</t>
-        </is>
-      </c>
-      <c r="C112" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Surfaced right after the S.No 110 fix, on SpendLog-1 TASK-001 (run e2c57de8). The 08 review legitimately took ~19 min (S.No 110 raised the review poll window to 30 min), exceeding the 15-min CLAIM_LEASE. The still-running review's claim went stale so a later /api/runner/work/ poll RE-CLAIMED it (phase.reclaimed x2) even though the companion was alive and heartbeating (last_seen fresh). The churn produced (a) a duplicate EMPTY 'assumption' artifact (external_ref null, no s3_key -&gt; would not preview) and (b) a FAILED final review report (review_status='failed', empty body) -&gt; 0 findings -&gt; the merge gate opened without a valid review.</t>
-        </is>
-      </c>
-      <c r="D112" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Companion / Runner / Claim lease vs review window</t>
-        </is>
-      </c>
-      <c r="E112" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bug (regression from S.No 110)</t>
-        </is>
-      </c>
-      <c r="F112" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">backend/api/runner_views.py (CLAIM_LEASE, RunnerWorkClaimView re-claim, RunnerHeartbeatView, _renew_claims_for); backend/orchestration/review_provider.py (review_timeout_seconds=1800); related S.No 110, 89, RC-2/RC-3</t>
-        </is>
-      </c>
-      <c r="G112" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P1</t>
-        </is>
-      </c>
-      <c r="H112" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The 15-min claim lease is meant to detect a DEAD companion, but it keyed off 'time since the claim was stamped', not liveness. S.No 110 legitimately extended the review to run up to 30 min &gt; the 15-min lease, so a live companion's claim expired mid-review and the run was re-claimed. The heartbeat kept last_seen fresh (liveness) but did NOT refresh claimed_at, so the lease expired despite the companion being provably alive - the lease comment even says it 'MUST exceed the longest real phase'.</t>
-        </is>
-      </c>
-      <c r="I112" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">FIXED (2026-07-14). The heartbeat now renews claimed_at for the companion's in-flight (PENDING/RUNNING, still 'claimed') runs (_renew_claims_for in runner_views.py, called by RunnerHeartbeatView; returns claims_renewed). So a heartbeating companion's claim never goes stale no matter how long the phase runs, while a truly dead companion still gets re-claimed ~15 min after its LAST heartbeat (dead-companion recovery preserved). Only in-flight claimed runs are touched - a reported/gated run is never revived. This ties the lease to LIVENESS, not task duration, so it is robust for any long phase, not just reviews. Tests: test_phase_dispatch::test_heartbeat_renews_claim_so_a_long_live_phase_is_not_reclaimed + test_heartbeat_does_not_renew_a_reported_claim (19 pass, ruff clean). Backend auto-reloads runner_views.py (uvicorn --reload) so no container restart / no companion drop. NOTE: the compromised run e2c57de8 must be disposed + re-run (its gate opened on a failed review).</t>
-        </is>
-      </c>
-      <c r="J112" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Fixed</t>
-        </is>
-      </c>
-    </row>
-    <row r="113" spans="1:10" ht="380">
+      <c r="B112" s="2" t="s">
+        <v>532</v>
+      </c>
+      <c r="C112" s="2" t="s">
+        <v>533</v>
+      </c>
+      <c r="D112" s="2" t="s">
+        <v>534</v>
+      </c>
+      <c r="E112" s="2" t="s">
+        <v>535</v>
+      </c>
+      <c r="F112" s="2" t="s">
+        <v>536</v>
+      </c>
+      <c r="G112" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H112" s="2" t="s">
+        <v>537</v>
+      </c>
+      <c r="I112" s="2" t="s">
+        <v>538</v>
+      </c>
+      <c r="J112" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="113" spans="1:10" ht="380.1">
       <c r="A113" s="2">
         <v>112</v>
       </c>
-      <c r="B113" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Shared Temporal queue + per-worker GitHub token: with two dev workers on the shared 'sdlc-planning' queue, a build's open_build_pr activity can run on the OTHER dev's worker, which uses THAT worker's server .env GITHUB_TOKEN -&gt; 404 on the target repo -&gt; build marked failed even though the code built + pushed fine</t>
-        </is>
-      </c>
-      <c r="C113" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Observed on SpendLog-1 (multi-user shared-AWS): TASK-001 build (run 5bc08ea2, RAGUWING369/SpendLogTest-1-backend) failed at 'pr/gate setup failed'. The worker logs showed the 404 was for a DIFFERENT tenant's repo (Tarun51/medslot-single-repo, run 3187519e) - proving the two dev workers cross-executed each other's build activities. Each worker authenticates GitHub from its own .env token (settings.GITHUB_TOKEN) scoped to that dev's repos, so a build landing on the wrong worker 404s. The companion build itself succeeded (report ok, branch pushed); only the platform-side PR step failed.</t>
-        </is>
-      </c>
-      <c r="D113" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Integrations / Code host / Multi-user / Shared Temporal</t>
-        </is>
-      </c>
-      <c r="E113" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bug</t>
-        </is>
-      </c>
-      <c r="F113" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">backend/integrations/registry.py (_build_github); backend/integrations/github/config.py (GithubConfig.from_connection); deploy/shared-aws (two workers, one queue); related S.No 74</t>
-        </is>
-      </c>
-      <c r="G113" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P1</t>
-        </is>
-      </c>
-      <c r="H113" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The codehost authenticated from the server .env (settings.GITHUB_TOKEN), NOT the tenant's own stored credential. On a shared task queue an activity runs on whichever worker is free, so the wrong dev's token was used. The per-tenant token was already stored in the shared DB (IntegrationConnection.secret_encrypted) but was never read (this is S.No 74 for the codehost).</t>
-        </is>
-      </c>
-      <c r="I113" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">FIXED (2026-07-14, Phase A). _build_github now builds the config via GithubConfig.from_connection(conn), which decrypts the tenant's own IntegrationConnection.secret_encrypted (the access_token the connect form stored) and uses it; falls back to settings.GITHUB_TOKEN only when no per-tenant secret exists (local/CI/back-compat). Because the credential lives in the SHARED DB and travels with the tenant, ANY worker that runs a build for that tenant uses the correct token - the cross-worker mismatch is now structurally impossible, so multiple devs can run workflows concurrently without stopping each other's worker. Core logic verified (per-tenant token used / settings fallback / two-tenant isolation all pass) + 3 new tests in test_capability_registry + ruff clean; full DB-backed test run pending local Docker (was down at fix time). Requires the tenant to have connected its Code host with a token - SpendLog-1 already has one stored (has_secret=True).</t>
-        </is>
-      </c>
-      <c r="J113" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Fixed</t>
-        </is>
-      </c>
-    </row>
-    <row r="114" spans="1:10" ht="380">
+      <c r="B113" s="2" t="s">
+        <v>539</v>
+      </c>
+      <c r="C113" s="2" t="s">
+        <v>540</v>
+      </c>
+      <c r="D113" s="2" t="s">
+        <v>541</v>
+      </c>
+      <c r="E113" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F113" s="2" t="s">
+        <v>542</v>
+      </c>
+      <c r="G113" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H113" s="2" t="s">
+        <v>543</v>
+      </c>
+      <c r="I113" s="2" t="s">
+        <v>544</v>
+      </c>
+      <c r="J113" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="114" spans="1:10" ht="380.1">
       <c r="A114" s="2">
         <v>113</v>
       </c>
-      <c r="B114" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Phase B (extend S.No 74): wire per-tenant credentials into the remaining connectors (Atlassian Confluence/Jira, Figma, Xray) so planning-phase system-of-record pushes also use the tenant's stored token on any worker, not the server .env</t>
-        </is>
-      </c>
-      <c r="C114" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Phase A (S.No 112) fixed the codehost (GitHub) to use per-tenant credentials from the shared DB. The other connectors still authenticate from the server .env (AtlassianConfig / FigmaConfig / XrayConfig .from_settings()), so on a shared multi-worker setup a planning-phase SoR push (publish to Confluence/Jira, Figma read, Xray import) could use the wrong tenant's creds or fail - the same class of bug as S.No 112, for the non-codehost capabilities.</t>
-        </is>
-      </c>
-      <c r="D114" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Integrations / Connectors / Multi-user</t>
-        </is>
-      </c>
-      <c r="E114" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Enhancement (follow-up)</t>
-        </is>
-      </c>
-      <c r="F114" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">backend/integrations/registry.py (_build_confluence/_build_jira/_build_figma/_build_xray + _atlassian_config); backend/apps/integrations/catalog.py; related S.No 74, S.No 112</t>
-        </is>
-      </c>
-      <c r="G114" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P2</t>
-        </is>
-      </c>
-      <c r="H114" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Same root cause as S.No 112 (connectors authenticate from the server .env, not per-tenant DB creds). Phase A did only the codehost because it was the build-workflow blocker. The Atlassian connectors also need email + site_url, which are NOT in the connect form's catalog yet, so this is a larger change (catalog + form fields + config wiring) - hence deferred.</t>
-        </is>
-      </c>
-      <c r="I114" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Open - follow-up to Phase A. Plan: (1) add email/site_url (or equivalent) fields to the Atlassian vendors in catalog.py + the connect form; (2) change _atlassian_config to take the conn and decrypt api_token + read email/site_url from scopes; (3) same decrypt-and-use for Figma access_token and Xray client_id/client_secret; (4) keep the settings fallback for back-compat; (5) tests per connector + a two-tenant isolation test. Not blocking now - SpendLog-1 is sor=internal with no non-codehost connections configured.</t>
-        </is>
-      </c>
-      <c r="J114" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="115" spans="1:10" ht="380">
+      <c r="B114" s="2" t="s">
+        <v>545</v>
+      </c>
+      <c r="C114" s="2" t="s">
+        <v>546</v>
+      </c>
+      <c r="D114" s="2" t="s">
+        <v>547</v>
+      </c>
+      <c r="E114" s="2" t="s">
+        <v>548</v>
+      </c>
+      <c r="F114" s="2" t="s">
+        <v>549</v>
+      </c>
+      <c r="G114" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="H114" s="2" t="s">
+        <v>550</v>
+      </c>
+      <c r="I114" s="2" t="s">
+        <v>551</v>
+      </c>
+      <c r="J114" s="2" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="115" spans="1:10" ht="380.1">
       <c r="A115" s="2">
         <v>114</v>
       </c>
-      <c r="B115" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Blocking code review silently 'passes' (fail-OPEN): the 07&lt;-&gt;08 remediation loop reads blocking findings ONLY from the json verdict block in the 08 agent's FINAL message. When the agent's final message is prose (its machine-readable json block missing / not last / delivered via a separate event) the platform parses 0 findings, counts 0 blocking, SKIPS remediation and opens the merge gate on an unreviewed downgrade.</t>
-        </is>
-      </c>
-      <c r="C115" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Observed live on SpendLog-1 (multi-repo), run 8ab6f89a, PR RAGUWING369/SpendLogTest-1-backend#3. The 08 review ran fine and produced a real verdict: review.completed logged status=CHANGES_REQUIRED with 5 blocking_findings (REM-C1 + REM-W1..W4, incl. PR-&gt;main-not-develop, /docs live in prod, no global exception handler, unbounded SECRET_KEY). But the review_body the companion posted back was only a 1,723-char prose executive summary with ZERO ```json blocks, so parse_findings returned [] -&gt; build.reviewed logged {blocking:0, findings:0} -&gt; gate.opened (merge) with no remediation loop. Distinct from S.No 110/111 (those were review-window/claim-lease timing); here the review reported in-window, claim_count stayed 1 - the defect is verdict serialization + a fail-OPEN default.</t>
-        </is>
-      </c>
-      <c r="D115" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Orchestration / Code review / 07&lt;-&gt;08 remediation loop</t>
-        </is>
-      </c>
-      <c r="E115" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bug</t>
-        </is>
-      </c>
-      <c r="F115" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">backend/orchestration/review_provider.py (parse_findings/_extract_verdict/_looks_blocking/parse_and_guard, ReviewContractError); backend/orchestration/build_activities.py (run_code_review_core); backend/orchestration/build_workflow.py (run_code_review activity -&gt; mark_build_failed on ActivityError); agents/08_code_review/agent.md (Output contract); runner/companion/daemon.py (posts result text as review_body); related S.No 110</t>
-        </is>
-      </c>
-      <c r="G115" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P1</t>
-        </is>
-      </c>
-      <c r="H115" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Two compounding defects. (1) Fragile contract: the platform sources blocking findings from the agent's free-text final message (daemon posts outputs.result as review_body; parse_findings scans only that for the LAST ```json block). Any run where the agent puts prose last, or emits the verdict via a tool/event, silently breaks the parse. (2) Fail-OPEN default: when the parse yields nothing the loop treats it as 'clean' (open_blocking==0) and opens the merge gate - the WRONG direction (same lesson as S.No 110, opposite failure).</t>
-        </is>
-      </c>
-      <c r="I115" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">FIXED (2026-07-14). Three-layer fix + tests. (Fix 1 - agent) agents/08_code_review/agent.md Output section hardened: the FINAL message MUST end with exactly one fenced json verdict block and NOTHING after it; forbids delivering the verdict only via a tool/event or appending a prose summary; both the code_review artifact body AND the final-message json are required. (Fix 2 - robust parse) _extract_verdict scans ALL json blocks and takes the last that parses AND looks like a verdict (has status/findings), tolerant of illustrative json + trailing prose. (Fix 3 - FAIL CLOSED) new parse_and_guard: if the body signals blocking (a REM-C/REM-W id or CHANGES_REQUIRED) but 0 blocking findings parse, it logs review.parse_mismatch and raises ReviewContractError; run_code_review retries (cap 3) then BuildWorkflow catches ActivityError -&gt; mark_build_failed, so the merge gate is NEVER opened on an unreviewed downgrade. Empty body (review timeout) keeps returning [] (human gate still applies, S.No 110). Tests: 7 new in test_review_dispatch (robust parse, clean pass-through, empty-body, fail-closed + event, provider-level fail-closed) + test_agents_migration (08 states the final-message json contract); all pass, ruff clean. Both companion + server providers guarded. Run 8ab6f89a disposed + PR #3 closed; team re-runs the phase.</t>
-        </is>
-      </c>
-      <c r="J115" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Fixed</t>
-        </is>
-      </c>
-    </row>
-    <row r="116" spans="1:10" ht="380">
+      <c r="B115" s="2" t="s">
+        <v>552</v>
+      </c>
+      <c r="C115" s="2" t="s">
+        <v>553</v>
+      </c>
+      <c r="D115" s="2" t="s">
+        <v>554</v>
+      </c>
+      <c r="E115" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F115" s="2" t="s">
+        <v>555</v>
+      </c>
+      <c r="G115" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H115" s="2" t="s">
+        <v>556</v>
+      </c>
+      <c r="I115" s="2" t="s">
+        <v>557</v>
+      </c>
+      <c r="J115" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="116" spans="1:10" ht="380.1">
       <c r="A116" s="2">
         <v>115</v>
       </c>
-      <c r="B116" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">07&lt;-&gt;08 remediation loop hangs forever: when the code review returns blocking findings, dispatch_remediation re-runs the implementation agent (07) on the same branch to fix them. But the remediation dispatch never re-armed the companion claim block, so the companion had nothing to pull -&gt; the 07 agent never re-ran -&gt; no second build report -&gt; the BuildWorkflow waited on build_reported until timeout -&gt; mark_takeover. The remediation cycle could never complete.</t>
-        </is>
-      </c>
-      <c r="C116" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Found by studying live cloud Temporal history (13.203.56.29:7233) for two devs' concurrent build runs. build-run-fe891eb9 sequence: dispatch_build -&gt; open_build_pr -&gt; run_code_review -&gt; dispatch_remediation -&gt; mark_takeover, with EXACTLY ONE build_reported signal (the initial build only). build-run-8f9dec1d (other tenant) identical, still stuck waiting after dispatch_remediation. Crucially 8f9dec1d ran on a SINGLE worker yet is stuck identically to the two-worker fe891eb9 - disproving the team's 'workers cross-pick activities' theory. Temporal replays workflow state consistently regardless of which worker runs each activity; multi-worker execution is normal and harmless. The two devs saw two faces of the same broken loop: Dev A stuck/takeover (this bug); Dev B gate opened with no remediation (S.No 114 fail-open, fixed same day).</t>
-        </is>
-      </c>
-      <c r="D116" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Orchestration / Build / 07&lt;-&gt;08 remediation loop / Companion dispatch</t>
-        </is>
-      </c>
-      <c r="E116" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bug</t>
-        </is>
-      </c>
-      <c r="F116" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">backend/orchestration/build_activities.py (dispatch_remediation_core + new _render_remediation_section); compares dispatch_build_core; backend/api/runner_views.py (RunnerWorkClaimView claim filter status in pending/claimed); runner/companion/daemon.py (poll-&gt;claim-&gt;run-&gt;report loop, no self-loop); related S.No 114</t>
-        </is>
-      </c>
-      <c r="G116" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P1</t>
-        </is>
-      </c>
-      <c r="H116" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">dispatch_remediation_core wrote only inputs['remediation'] + status=RUNNING; it never set inputs['dispatch'] to a pending BUILD claim block (left as the review's kind=review/status=reported, which the claim query ignores) and never rebuilt build_task with the remediation brief. The companion daemon is a strict poll-&gt;claim-&gt;run-&gt;report loop with no remediation self-loop, so /api/runner/work/ returned 204 forever. The 07&lt;-&gt;08 companion handoff for remediation was simply never wired. It escaped tests because test_review_dispatch only exercised run_code_review_core opening child WorkItems, never the dispatch-&gt;claim-&gt;report cycle. Blocker surfaced only after S.No 114 (fail-open) was fixed - fixing 114 makes a blocking review correctly ENTER the remediation branch, which then hit 115.</t>
-        </is>
-      </c>
-      <c r="I116" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">FIXED (2026-07-15). dispatch_remediation_core now mirrors dispatch_build_core's companion handoff: recomposes the 07 manifest via compose_manifest_core and appends a '# Remediation Items' section rendering the open REM brief (rem/severity/title/file:line) - same idea as the reviewer's PR-diff section; rebuilds the full build_task payload (manifest+agent_body+model+repo/base/work_item title/type, remediation:True); and sets inputs['dispatch']={kind:build, enrollment_id:inp.enrollment_id, status:pending} so the companion claims it via /api/runner/work/ and re-runs 07 on the SAME branch. open_build_pr stays outside the loop (idempotent) so the existing PR just gets new commits. Companion side needed NO change: worktree path is deterministic per WI, teardown after each build, provision_worktree re-attaches the existing feature branch, push is a fast-forward. No workflow change: build_workflow already dispatches then waits for build_reported. Tests: 2 new in test_review_dispatch (dispatch arms pending build claim + REM brief in manifest; /api/runner/work/ returns the remediation build) - 19 pass; test_build_activities 11 pass (no regression); ruff clean. Verification watches for a SECOND build_reported signal in the workflow history (absent in every run to date) = proof the handoff works.</t>
-        </is>
-      </c>
-      <c r="J116" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Fixed</t>
-        </is>
-      </c>
-    </row>
-    <row r="117" spans="1:10" ht="380">
+      <c r="B116" s="2" t="s">
+        <v>558</v>
+      </c>
+      <c r="C116" s="2" t="s">
+        <v>559</v>
+      </c>
+      <c r="D116" s="2" t="s">
+        <v>560</v>
+      </c>
+      <c r="E116" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F116" s="2" t="s">
+        <v>561</v>
+      </c>
+      <c r="G116" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H116" s="2" t="s">
+        <v>562</v>
+      </c>
+      <c r="I116" s="2" t="s">
+        <v>563</v>
+      </c>
+      <c r="J116" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="117" spans="1:10" ht="380.1">
       <c r="A117" s="2">
         <v>116</v>
       </c>
-      <c r="B117" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Code review flags PR-size (and other Step-1 hygiene checks) as a blocking CRITICAL, driving an UNWINNABLE 07&lt;-&gt;08 remediation loop: the 08 agent's Step-1 PR Hygiene gate treats any failing check (PR size &gt;400 lines, commit-message format, branch name, PR description, linear history) as a blocking REM-C. But the platform re-runs the IMPLEMENTATION agent on the SAME branch for every blocking finding, and it cannot split a PR, rename a branch, rewrite the platform-generated commit message, or otherwise fix a hygiene issue in code -&gt; the finding recurs every cycle -&gt; the loop churns until max_remediation_cycles (3) exhausts -&gt; the build FAILS, even though the code is fine.</t>
-        </is>
-      </c>
-      <c r="C117" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Observed live on SpendLog-1 build run 1377dee3 (TASK-001 .venv/FastAPI scaffold). Review cycle 1 = 4 blocking (REM-C1 PR-size ~590 lines, REM-C2 CORS, REM-W1 no-op test, REM-W2 python-jose). The 3 real code defects were fixed across cycles (done); REM-C1 'PR size ~590 lines exceeds 400-line threshold' stayed blocking every cycle (blocking count stuck at 1: cycle1=4 -&gt; cycle2=1 -&gt; cycle3=1) because a legitimate bootstrap scaffold cannot be shrunk below 400 lines. Heading to 'remediation cycles exhausted' at cycle 4. The 08 agent even acknowledges (run 8ab6f89a) PR-size for a bootstrap scaffold is 'justified ... document as a permitted exception rather than triggering a code remediation loop' - yet still emitted it as blocking. Confirmed S.No 114 + 115 fixes worked (2-3 build_reported, loop converged 4-&gt;1); this is a DISTINCT design bug the working loop exposed.</t>
-        </is>
-      </c>
-      <c r="D117" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Agents / 08 Code Review / Remediation loop classification</t>
-        </is>
-      </c>
-      <c r="E117" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bug</t>
-        </is>
-      </c>
-      <c r="F117" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">agents/08_code_review/agent.md (Step 1 PR Hygiene gate, lines ~62-76: 'Any check that fails -&gt; CRITICAL'); backend/orchestration/build_activities.py (_BLOCKING treats REM-C/REM-W as blocking); related S.No 114, 115</t>
-        </is>
-      </c>
-      <c r="G117" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P1</t>
-        </is>
-      </c>
-      <c r="H117" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Step 1 hygiene checks are either platform-OWNED (D2: the platform generates the commit message, branch name, PR description, and keeps history linear - the 07 agent never touches git) or NON-CODE (PR size). None can be remediated by re-running 07 on the same branch, so classifying them as blocking REM-C/REM-W guarantees an unwinnable loop. PR size is inherently a human/process judgment (split the PR) or a justified exception (scaffold/migration), not a code defect - it belongs at the human merge gate, not in the automated loop.</t>
-        </is>
-      </c>
-      <c r="I117" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">FIXED (2026-07-15). agents/08_code_review/agent.md Step 1 reclassified: a failing hygiene check is now a NON-BLOCKING Suggestion (REM-S) for the human merge-gate reviewer, never a blocking REM-C/REM-W. The body now states the rationale (platform-owned or non-code -&gt; the 07 loop cannot fix them -&gt; blocking would create an unwinnable loop that exhausts the cap) and directs a genuinely un-reviewable PR to be RETURNED BY THE HUMAN reviewer at the gate, not the automated loop; PR-size overage is still reported (with generated/lock/migration exemptions + justified-or-not note) but as a Suggestion. Framework note aligned. Tests: test_agents_migration.test_code_review_hygiene_findings_are_non_blocking (asserts non-blocking-suggestion classification + rationale present + old 'any check that fails -&gt; CRITICAL' gone) - 2 pass. Agent body is file-loaded (_load_agent_body) so the fix is live on the next dispatch, no re-seed/worker restart. Run 1377dee3 terminated + PR#4 closed + branch deleted + DB reset (WI proposed) for a fresh re-run.</t>
-        </is>
-      </c>
-      <c r="J117" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Fixed</t>
-        </is>
-      </c>
-    </row>
-    <row r="118" spans="1:1">
+      <c r="B117" s="2" t="s">
+        <v>564</v>
+      </c>
+      <c r="C117" s="2" t="s">
+        <v>565</v>
+      </c>
+      <c r="D117" s="2" t="s">
+        <v>566</v>
+      </c>
+      <c r="E117" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F117" s="2" t="s">
+        <v>567</v>
+      </c>
+      <c r="G117" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H117" s="2" t="s">
+        <v>568</v>
+      </c>
+      <c r="I117" s="2" t="s">
+        <v>569</v>
+      </c>
+      <c r="J117" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="118" spans="1:10" ht="194.25">
       <c r="A118" s="2">
         <v>117</v>
       </c>
-    </row>
-    <row r="119" spans="1:1">
+      <c r="B118" s="2" t="s">
+        <v>570</v>
+      </c>
+      <c r="D118" s="2" t="s">
+        <v>571</v>
+      </c>
+      <c r="E118" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F118" s="2" t="e" vm="10">
+        <v>#VALUE!</v>
+      </c>
+      <c r="G118" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J118" s="2" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="119" spans="1:10" ht="409.6">
       <c r="A119" s="2">
         <v>118</v>
       </c>
-    </row>
-    <row r="120" spans="1:1">
+      <c r="B119" s="2" t="s">
+        <v>572</v>
+      </c>
+      <c r="D119" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="E119" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F119" s="2" t="e" vm="11">
+        <v>#VALUE!</v>
+      </c>
+      <c r="G119" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="J119" s="2" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="120" spans="1:10" ht="113.25">
       <c r="A120" s="2">
         <v>119</v>
       </c>
-    </row>
-    <row r="121" spans="1:1">
+      <c r="B120" s="2" t="s">
+        <v>573</v>
+      </c>
+      <c r="D120" s="2" t="s">
+        <v>571</v>
+      </c>
+      <c r="E120" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F120" s="2" t="e" vm="12">
+        <v>#VALUE!</v>
+      </c>
+      <c r="G120" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J120" s="2" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="121" spans="1:10" ht="409.6">
       <c r="A121" s="2">
         <v>120</v>
       </c>
-    </row>
-    <row r="122" spans="1:1">
+      <c r="B121" s="2" t="s">
+        <v>574</v>
+      </c>
+      <c r="D121" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="E121" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F121" s="2" t="e" vm="13">
+        <v>#VALUE!</v>
+      </c>
+      <c r="G121" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="J121" s="2" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="122" spans="1:10">
       <c r="A122" s="2">
         <v>121</v>
       </c>
     </row>
-    <row r="123" spans="1:1">
+    <row r="123" spans="1:10">
       <c r="A123" s="2">
         <v>122</v>
       </c>
     </row>
-    <row r="124" spans="1:1">
+    <row r="124" spans="1:10">
       <c r="A124" s="2">
         <v>123</v>
       </c>
     </row>
-    <row r="125" spans="1:1">
+    <row r="125" spans="1:10">
       <c r="A125" s="2">
         <v>124</v>
       </c>
     </row>
-    <row r="126" spans="1:1">
+    <row r="126" spans="1:10">
       <c r="A126" s="2">
         <v>125</v>
       </c>
     </row>
-    <row r="127" spans="1:1">
+    <row r="127" spans="1:10">
       <c r="A127" s="2">
         <v>126</v>
       </c>
     </row>
-    <row r="128" spans="1:1">
+    <row r="128" spans="1:10">
       <c r="A128" s="2">
         <v>127</v>
       </c>

--- a/docs/Bugs.xlsx
+++ b/docs/Bugs.xlsx
@@ -6754,8 +6754,15 @@
       <c r="G119" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="J119" s="2" t="s">
-        <v>141</v>
+      <c r="I119" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FIXED (2026-07-15). agents/06_task_breakdown/agent.md: added a 'Writing standard' requiring every Epic/Story/Task Description + Acceptance Criterion to be plain-language-with-technical-nuance, detailed and self-contained enough that a developer can implement by reading it ALONE (behaviour, inputs/outputs, states, edge cases), with concrete hand-verifiable acceptance criteria and no bare placeholders; modelled the standard in all three template placeholders. Improvement flows to the Work Items board + artifact previews automatically. Test: test_agents_migration.test_task_breakdown_descriptions_and_ac_are_humanized. Per team decision the blast radius today was 06 only; the SAME defect in 02/09/00c/04/03/10 is logged as S.No 121-126 (register-condition per audience: technical-humanized for testing/security, plain+nuance for the rest) and NOT fixed this session.</t>
+        </is>
+      </c>
+      <c r="J119" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fixed</t>
+        </is>
       </c>
     </row>
     <row r="120" spans="1:10" ht="113.25">
@@ -6800,38 +6807,303 @@
       <c r="G121" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="J121" s="2" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="122" spans="1:10">
-      <c r="A122" s="2">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="123" spans="1:10">
-      <c r="A123" s="2">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="124" spans="1:10">
-      <c r="A124" s="2">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="125" spans="1:10">
-      <c r="A125" s="2">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="126" spans="1:10">
-      <c r="A126" s="2">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="127" spans="1:10">
-      <c r="A127" s="2">
-        <v>126</v>
+      <c r="I121" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FIXED (2026-07-15) - FULL blast radius + Part C (team-approved re-scope). (1) Artifact.title field + migration 0003_artifact_title (nullable, backward-safe). (2) register_artifact/update_artifact gain a title param, plus MCP server + companion wrappers, tool docstrings say 'ALWAYS pass a title'. (3) Part C-1 versioning-collision FIXED: version scoped by (project,phase,type,title) when titled, so per-item siblings (adr/test_case/security_finding/code/code_review/test_report) each start v1 instead of falsely superseding; untitled/singletons keep old behaviour. (4) Platform code/code_review get titles (WI key). (5) Serializers/consumers: DRF ArtifactSerializer + MCP _artifact/_lean_ref + preview payload + traceability node + dashboard + publish title expose/prefer title. (6) Frontend: new artifactLabel(title,type) helper (falls back to humanized type) in Artifacts registry list+search, preview H1/row, Traceability node (was raw type), Export/Publish. (7) 7 agents 04/05/07/08/09/09b/10 author human titles (Wireframe - Login Page, ADR-003 - Event Sourcing, TC-014 - ...). (8) Part C-2 ContractsDrift FIXED: no JSON.stringify dump (humanized scalar summary); DriftRecordSerializer enriches impacted with node_title+repo_name (batched) so no raw UUIDs. Wireframe STATES stay a separate label axis by design. Tests: test_mcp_platform_state (title + per-item independent versions), test_agents_migration (06 + per-item titles), test_review_dispatch/test_api_contract green; frontend tsc clean; ruff clean. Migration NOT yet applied to shared cloud DB - held for a coordinated make migrate (nullable=back-compat).</t>
+        </is>
+      </c>
+      <c r="J121" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fixed</t>
+        </is>
+      </c>
+    </row>
+    <row r="122" spans="1:10" ht="380">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">121</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Requirements agent (02) authors user stories, functional requirements, acceptance criteria and NFRs too technically/formally for its reviewer. Same defect class as S.No 118 (06 task breakdown): the content is engineer/QA-precision only with no human-readability bar, yet the Product Owner reviews it. HUMANIZATION REGISTER for the fix = PLAIN LANGUAGE retaining the technical nuance (broader audience: PO + developer).</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Investigation (session 2026-07-15) edge-case sweep of all 16 phase agents for the S.No 118 pattern. 02 is the closest structural analog to 06.</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Agents / 02 Requirements / content humanization</t>
+        </is>
+      </c>
+      <c r="E122" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bug</t>
+        </is>
+      </c>
+      <c r="F122" s="2"/>
+      <c r="G122" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P1</t>
+        </is>
+      </c>
+      <c r="H122" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Quality bar is 'a QA engineer can execute without a follow-up question' (agents/02_requirements/agent.md:10); FR format is formal SHALL boilerplate (:115); acceptance criteria are bare BDD stubs (:85-97); user-story descriptions have no plain-language directive; reviewer is the Product Owner (:357). Related S.No 118, 120.</t>
+        </is>
+      </c>
+      <c r="I122" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OPEN - NOT fixed this session. Team scoped today's fix to S.No 118 (06 task breakdown) only. Planned: add a plain-language-with-technical-nuance authoring bar to user-story descriptions, FR statements and acceptance criteria - mirror 06's assignment_rationale directive (:280) and the good patterns in 05_ux_design/12_deployment/08_code_review.</t>
+        </is>
+      </c>
+      <c r="J122" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="123" spans="1:10" ht="380">
+      <c r="A123" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">122</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Testing agent (09) authors UAT scenarios FOR the Product Owner, plus defect reports and test-case descriptions, with an engineer-precision bar only. Same defect class as S.No 118. HUMANIZATION REGISTER for the fix = HUMANIZED-TECHNICAL (keep the technical register but make it clear and well-structured) - NOT plain language, because QA/UAT personnel must interpret the technical detail correctly; plain language would cause misinterpretation.</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Investigation edge-case sweep. UAT is a business-verification event handed to a non-engineer, yet authored with two-engineer precision.</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Agents / 09 Testing / content humanization</t>
+        </is>
+      </c>
+      <c r="E123" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bug</t>
+        </is>
+      </c>
+      <c r="F123" s="2"/>
+      <c r="G123" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P1</t>
+        </is>
+      </c>
+      <c r="H123" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UAT scenarios authored for the PO (agents/09_testing/agent.md:483-494) and defect descriptions (:433-459) use a two-engineer precision bar (:212) with no readability directive for the PO-facing UAT. Test-case Expected Result/Description carry the same risk. Related S.No 118, 120.</t>
+        </is>
+      </c>
+      <c r="I123" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OPEN - NOT fixed this session (team scope = 06 only). Planned: add a HUMANIZED-TECHNICAL clarity bar (structured, understandable, technical register retained) to UAT scenarios, defect reports and test-case descriptions - not plain language.</t>
+        </is>
+      </c>
+      <c r="J123" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="124" spans="1:10" ht="380">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">123</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Intelligent Context Extractor agent (00c) authors the codebase_intelligence Executive Summary, health dashboard and module-documentation prose read by humans onboarding to a project, with no plain-language directive - jargon-prone. Same defect class as S.No 118. HUMANIZATION REGISTER = PLAIN LANGUAGE retaining technical nuance.</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Investigation edge-case sweep.</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Agents / 00c Context Extractor / content humanization</t>
+        </is>
+      </c>
+      <c r="E124" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bug</t>
+        </is>
+      </c>
+      <c r="F124" s="2"/>
+      <c r="G124" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P2</t>
+        </is>
+      </c>
+      <c r="H124" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Agent 'writes the prose' (agents/00c_intelligent_context_extractor/agent.md:44; artifact spec :93-106) with no directive to keep it plain for onboarding readers. Related S.No 118, 120.</t>
+        </is>
+      </c>
+      <c r="I124" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OPEN - NOT fixed this session (team scope = 06 only). Planned: add a plain-language-with-technical-nuance bar to the exec summary and module-doc prose.</t>
+        </is>
+      </c>
+      <c r="J124" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="125" spans="1:10" ht="380">
+      <c r="A125" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">124</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Architecture agent (04) authors ADR Rationale/Context/Consequences prose and the architecture Executive Summary as human-read decision records, but only the Level-1 context diagram carries a 'readable by a non-technical stakeholder' bar - the ADR narrative and exec summary do not. Same defect class as S.No 118. HUMANIZATION REGISTER = PLAIN LANGUAGE retaining technical nuance.</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Investigation edge-case sweep.</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Agents / 04 Architecture / content humanization</t>
+        </is>
+      </c>
+      <c r="E125" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bug</t>
+        </is>
+      </c>
+      <c r="F125" s="2"/>
+      <c r="G125" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P2</t>
+        </is>
+      </c>
+      <c r="H125" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Context diagram must be 'readable by a non-technical stakeholder' (agents/04_architecture/agent.md:119) but ADR rationale (:373) and exec summary (:291) have no plain-language bar. Related S.No 118, 120.</t>
+        </is>
+      </c>
+      <c r="I125" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OPEN - NOT fixed this session (team scope = 06 only). Planned: extend the existing non-technical-readability bar to ADR narrative fields and the exec summary.</t>
+        </is>
+      </c>
+      <c r="J125" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="126" spans="1:10" ht="380">
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">125</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PRD agent (03) is mostly well-humanized, but the per-feature ACCEPTANCE CRITERIA remain terse placeholders - the same artifact type flagged in S.No 118. HUMANIZATION REGISTER = PLAIN LANGUAGE retaining technical nuance.</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Investigation edge-case sweep. Partially self-mitigated (strong readability directives elsewhere).</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Agents / 03 PRD / content humanization</t>
+        </is>
+      </c>
+      <c r="E126" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bug</t>
+        </is>
+      </c>
+      <c r="F126" s="2"/>
+      <c r="G126" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P2</t>
+        </is>
+      </c>
+      <c r="H126" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Strong readability directives overall (agents/03_prd/agent.md:15,76,354) but per-feature acceptance criteria are terse placeholders (:224-227). Related S.No 118, 120.</t>
+        </is>
+      </c>
+      <c r="I126" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OPEN - NOT fixed this session (team scope = 06 only). Planned: apply the same detailed, plain-language-with-nuance bar to per-feature acceptance criteria.</t>
+        </is>
+      </c>
+      <c r="J126" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="127" spans="1:10" ht="380">
+      <c r="A127" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">126</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Security agent (10) authors the Executive Summary and finding Impact statements that reach stakeholders with no plain-language bar. Same defect class as S.No 118. HUMANIZATION REGISTER = HUMANIZED-TECHNICAL for findings (security engineers must read the technical detail correctly); the stakeholder exec summary may be plain-language-with-nuance.</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Investigation edge-case sweep. Primary audience is technical; remediation guidance is already appropriately specific.</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Agents / 10 Security / content humanization</t>
+        </is>
+      </c>
+      <c r="E127" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bug</t>
+        </is>
+      </c>
+      <c r="F127" s="2"/>
+      <c r="G127" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P2</t>
+        </is>
+      </c>
+      <c r="H127" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Exec summary and finding Impact (agents/10_security/agent.md:339-340,395-398) reach stakeholders without a readability bar. Related S.No 118, 120.</t>
+        </is>
+      </c>
+      <c r="I127" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OPEN - NOT fixed this session (team scope = 06 only). Planned: humanized-technical clarity bar on findings; plain-language-with-nuance on the stakeholder exec summary.</t>
+        </is>
+      </c>
+      <c r="J127" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
       </c>
     </row>
     <row r="128" spans="1:10">

--- a/docs/Bugs.xlsx
+++ b/docs/Bugs.xlsx
@@ -176,7 +176,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="966" uniqueCount="575">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="966" uniqueCount="576">
   <si>
     <t>S.No</t>
   </si>
@@ -2026,6 +2026,9 @@
     <t>In Artifacts &amp; Traceability Page:
 The generated artifact names for each phase should be humanised – the current names which are visible in the page are not human readable, Ex: Wireframe is repeated for all wireframes but no mentioning of which screen it is. sample human readable: Wireframe (login-page)
 Note: The same issues applies to the internal artifact content when the user clicked on the preview. You must read all the phase agents to identify what are all the artifacts it generates and how they are represented as names or disply or written.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fixed (session 2026-07-15). Report-timeout takeover is now NON-terminal and reconcilable. (1) New Run.Status.STALLED (runs migration 0006) replaces terminal FAILED on timeout: mark_phase_takeover_core parks the run as STALLED + sets the WorkItem takeover_flag. (2) AgentRunWorkflow no longer returns on timeout: it marks the soft takeover then KEEPS waiting for the report, so a companion that only slept returns and flows through register -&gt; verify_writes -&gt; open_gate -&gt; approve -&gt; publish. This fixes BOTH faces: the run no longer sticks in terminal FAILED (no false 'no artifact registered'), and the gate Approve works because the workflow is still alive. (3) register_phase_result_core clears takeover_flag on a successful late report (un-parks). (4) New abandon_run workflow signal + orchestration.takeover.abandon_stalled_run, wired into the run-level /runs/{id}/take-over/ endpoint, so an explicit human takeover ('Take over manually' / 'Reconnect &amp; re-run') ends the still-waiting run terminally (no lingering workflow). (5) UI: 'stalled' renders as 'Parked for takeover' (RunConsole) and OfflineTakeover recognizes it + explains auto-reconcile. Tests (test_phase_dispatch): STALLED park, late-report reconcile clears the flag, abandon-only-when-parked, offline-then-abandoned + recovers-after-takeover (both against real Temporal). Files: backend/apps/runs/models.py, backend/apps/runs/migrations/0006_run_stalled_status.py, backend/orchestration/{workflows,activities,takeover}.py, backend/api/views.py, frontend/src/features/lifecycle/RunConsole.tsx, frontend/src/features/observability/OfflineTakeover.tsx.</t>
   </si>
 </sst>
 </file>
@@ -5842,10 +5845,10 @@
         <v>394</v>
       </c>
       <c r="I90" s="2" t="s">
-        <v>395</v>
+        <v>575</v>
       </c>
       <c r="J90" s="2" t="s">
-        <v>141</v>
+        <v>16</v>
       </c>
     </row>
     <row r="91" spans="1:10" ht="409.6">

--- a/docs/Bugs.xlsx
+++ b/docs/Bugs.xlsx
@@ -7109,69 +7109,654 @@
         </is>
       </c>
     </row>
-    <row r="128" spans="1:10">
+    <row r="128" spans="1:10" ht="460.0" customHeight="1">
       <c r="A128" s="2">
         <v>127</v>
       </c>
-    </row>
-    <row r="129" spans="1:1">
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Merging an approved build fails with HTTP 405 because the pull request is still a draft (the final blocker)</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">After a human approves the merge gate, the platform tries to merge the build's PR but GitHub rejects it, so the work item never reaches 'done'.</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Build pipeline / Merge gate</t>
+        </is>
+      </c>
+      <c r="E128" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bug</t>
+        </is>
+      </c>
+      <c r="F128" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1258d85</t>
+        </is>
+      </c>
+      <c r="G128" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P1</t>
+        </is>
+      </c>
+      <c r="H128" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">During the automated 07&lt;-&gt;08 review-and-fix loop the platform opens the build's pull request as a GitHub 'draft' PR (a draft blocks a premature human merge while review is still running). GitHub does not allow a draft PR to be merged - its merge API returns HTTP 405 (Method Not Allowed). So the moment a human approved the merge gate, the final merge step always failed. The work item got stuck at the very last step, never transitioned to done, and nothing downstream could complete. This was the single blocker stopping any build from finishing.</t>
+        </is>
+      </c>
+      <c r="I128" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FIXED (commit 1258d85). Added a mark_ready_for_review step that takes the PR out of draft immediately before merging, which is the one legitimate moment to un-draft (gate already approved). merge_build_pr_core now does: get the PR; if it is not already merged and is still a draft, call codehost.mark_ready_for_review(pr_ref) which runs GitHub's markPullRequestReadyForReview GraphQL mutation and re-checks (short retries) that it un-drafted, then merge. Supporting additions: a graphql() helper (integrations/github/rest.py), a graphql_url property (config.py), and the CodeHost.mark_ready_for_review capability (capabilities.py + github/codehost.py). Regression test added in test_build_activities.py (draft PR is un-drafted before merge).</t>
+        </is>
+      </c>
+      <c r="J128" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fixed</t>
+        </is>
+      </c>
+    </row>
+    <row r="129" spans="1:10" ht="460.0" customHeight="1">
       <c r="A129" s="2">
         <v>128</v>
       </c>
-    </row>
-    <row r="130" spans="1:1">
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Reviewer gets 'no opened PR to review' during the fix-and-re-review loop (wrong code pointer picked)</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">During remediation the platform sometimes points the reviewer at an empty pre-PR placeholder instead of the real pull request.</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Build pipeline / Review loop</t>
+        </is>
+      </c>
+      <c r="E129" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bug</t>
+        </is>
+      </c>
+      <c r="F129" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1258d85</t>
+        </is>
+      </c>
+      <c r="G129" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P1</t>
+        </is>
+      </c>
+      <c r="H129" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The helper that looks up a build's code artifact (_code_artifact) fetched 'the first matching artifact' with no defined ordering. A single work item can have more than one code-artifact row: an early placeholder the agent registers before the PR exists, and the real one that carries the pull-request reference (repo/number/url). With no ORDER BY, the database returned rows in an arbitrary order, so the code sometimes picked the early placeholder that has no PR link. The reviewer then had nothing to look at and reported 'no opened PR to review', which broke the remediation cycle.</t>
+        </is>
+      </c>
+      <c r="I129" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FIXED (commit 1258d85). _code_artifact now orders artifacts by created_at and explicitly prefers the one whose external_ref is a real PR reference: it returns the first PR-ref-bearing artifact and only falls back to the earliest row if none carries a PR ref. Regression test added in test_build_activities.py (duplicate-code-artifact prefers the PR-ref pointer).</t>
+        </is>
+      </c>
+      <c r="J129" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fixed</t>
+        </is>
+      </c>
+    </row>
+    <row r="130" spans="1:10" ht="460.0" customHeight="1">
       <c r="A130" s="2">
         <v>129</v>
       </c>
-    </row>
-    <row r="131" spans="1:1">
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A genuinely 'Approved' code review is wrongly blocked by the fail-closed review guard (false positive on a resolved finding ID)</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The safety guard that blocks bad code mis-reads an approved review and rejects it, stalling the pipeline for no real reason.</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Build pipeline / Review guard (S.No 114 guard)</t>
+        </is>
+      </c>
+      <c r="E130" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bug</t>
+        </is>
+      </c>
+      <c r="F130" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">a2deeae</t>
+        </is>
+      </c>
+      <c r="G130" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P1</t>
+        </is>
+      </c>
+      <c r="H130" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The review guard is deliberately 'fail-closed': if a review's prose looks like it demands changes but the structured verdict does not clearly say so, it blocks - to stop bad code slipping through. The old prose matcher (_looks_blocking) scanned the entire review text for blocking-sounding words. An APPROVED review referenced an already-RESOLVED finding by its ID (for example 'REM-W1'), and the matcher saw that mention and concluded the review was demanding changes. Result: a legitimately approved review was blocked and the build could not proceed - a false positive that halted good work.</t>
+        </is>
+      </c>
+      <c r="I130" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FIXED (commit a2deeae). Rewrote parse_and_guard to trust a present, structured APPROVED verdict. Added _verdict_demands_changes(): a verdict is treated as demanding changes only when a verdict is actually present AND its status matches a negative pattern (change/reject/denied/blocked/fail, via _NEGATIVE_STATUS regex). The loose prose scan is now only a fallback used when there is NO structured verdict at all. Net effect: an approved verdict is honoured even if its prose happens to mention resolved finding IDs, while a review that truly downgrades still fails closed. Regression tests added in test_review_dispatch.py (trusts approved verdict with resolved REM ids; in-JSON downgrade still fails closed).</t>
+        </is>
+      </c>
+      <c r="J130" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fixed</t>
+        </is>
+      </c>
+    </row>
+    <row r="131" spans="1:10" ht="460.0" customHeight="1">
       <c r="A131" s="2">
         <v>130</v>
       </c>
-    </row>
-    <row r="132" spans="1:1">
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">When the secret scanner blocks a push, the failure is invisible - only a bare count is shown, not what/where</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A blocked hardcoded secret produces a silent 'build failed' with just a number; nobody can tell which secret, file or line.</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Companion / Pre-push secret scan</t>
+        </is>
+      </c>
+      <c r="E131" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bug</t>
+        </is>
+      </c>
+      <c r="F131" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">52533c4</t>
+        </is>
+      </c>
+      <c r="G131" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P2</t>
+        </is>
+      </c>
+      <c r="H131" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Before pushing code the companion (the worker on the developer machine) scans the changed files for hardcoded secrets (passwords, API keys, tokens, private keys). When it finds one it correctly blocks the push and reports the build as failed - but it only reported a bare count ('N finding(s)'). It did not surface which secret type, which file, or which line, and it then tore down the temporary work folder, so the evidence was gone. Operators saw 'build failed' with no way to know why or how to fix it, making the block undiagnosable.</t>
+        </is>
+      </c>
+      <c r="I131" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FIXED (commit 52533c4). The companion now prints a redacted summary to its own terminal ('[companion] SECRET SCAN BLOCKED push (N finding(s)) - branch NOT pushed') listing each finding as '[kind] path:line - preview', and the same redacted detail travels in the build.failed reason so it also appears in the platform run console. Only the already-redacted preview is shown - never the raw secret value - and the list is capped at 8 findings with a '(+N more)' tail so the message stays bounded. Added the _format_secret_findings helper (runner/companion/runner.py) and regression tests in test_companion_runner.py (redacted findings surface; cap at 8).</t>
+        </is>
+      </c>
+      <c r="J131" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fixed</t>
+        </is>
+      </c>
+    </row>
+    <row r="132" spans="1:10" ht="460.0" customHeight="1">
       <c r="A132" s="2">
         <v>131</v>
       </c>
-    </row>
-    <row r="133" spans="1:1">
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The code-review result (code_review artifact) cannot be opened or read from the web UI</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The 08 review report is produced and registered but there is no view/link in the product to read it.</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI / Review experience</t>
+        </is>
+      </c>
+      <c r="E132" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bug</t>
+        </is>
+      </c>
+      <c r="F132" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G132" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P2</t>
+        </is>
+      </c>
+      <c r="H132" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The 08 review agent produces a code_review artifact holding the review findings and verdict, and the platform registers it as an artifact (pointer + provenance). However the web interface offers no view or link that opens the artifact body, so a human reviewer or manager cannot actually read the review inside the product - they would have to query the database or dig through logs. This undermines the human review gate: the gate exists but the evidence behind it is not surfaced to the person approving.</t>
+        </is>
+      </c>
+      <c r="I132" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OPEN - not fixed this session. Recommended fix: add a UI affordance (a link/panel on the Work Item or Run screen) that fetches the code_review artifact body via get_artifact_body and renders it (Markdown), and make sure the artifact is associated to the run so the front end can locate it. Verify at registration time that the artifact's body pointer (S3/stage) is populated so there is something to fetch. Acceptance: from a run that has been reviewed, a human can click through and read the full review text and verdict without leaving the UI.</t>
+        </is>
+      </c>
+      <c r="J132" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="133" spans="1:10" ht="460.0" customHeight="1">
       <c r="A133" s="2">
         <v>132</v>
       </c>
-    </row>
-    <row r="134" spans="1:1">
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The 'sdlc/build' commit status is set to 'pending' when the PR opens and is never updated - it stays pending forever (latent)</t>
+        </is>
+      </c>
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A dormant flaw: the build commit status posted to GitHub is never moved off 'pending', which will block merges if branch protection ever requires it.</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Build pipeline / Commit status reporting</t>
+        </is>
+      </c>
+      <c r="E133" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bug</t>
+        </is>
+      </c>
+      <c r="F133" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">build_activities.py:140</t>
+        </is>
+      </c>
+      <c r="G133" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P3</t>
+        </is>
+      </c>
+      <c r="H133" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">When the build PR is opened, the platform posts a GitHub commit status with context 'sdlc/build' and state 'pending' against the head commit (build_activities.py line 140, best-effort - exceptions are swallowed). Nothing anywhere later updates that status to 'success' or 'failure'. So every build's commit shows the 'sdlc/build' check stuck on pending indefinitely. It is dormant today only because no branch-protection rule on the repo currently requires the 'sdlc/build' context to be green before merging. The day someone enables such a required check, merges will be blocked forever because the status can never reach success - a latent time-bomb, and misleading status UI in the meantime.</t>
+        </is>
+      </c>
+      <c r="I133" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OPEN - not fixed this session. Recommended fix: complete the status lifecycle. Set 'sdlc/build' to 'success' once the build+review pass (or at merge), and to 'failure' on the mark_build_failed / secret-block / merge-failed paths, using the same head SHA. Keep it best-effort (do not fail the saga on a status-post error), but ensure a terminal state is always posted so the check does not dangle. Acceptance: after a run reaches a terminal outcome, the commit's 'sdlc/build' status reflects success or failure, never a permanent pending.</t>
+        </is>
+      </c>
+      <c r="J133" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="134" spans="1:10" ht="460.0" customHeight="1">
       <c r="A134" s="2">
         <v>133</v>
       </c>
-    </row>
-    <row r="135" spans="1:1">
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The companion crashes hard (fatal, exit 1) when the build agent errors, instead of failing gracefully and reporting back</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">If the AI build agent fails, the whole companion worker dies and needs a manual restart, stalling the build.</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Companion / Build execution resilience</t>
+        </is>
+      </c>
+      <c r="E134" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bug</t>
+        </is>
+      </c>
+      <c r="F134" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G134" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P1</t>
+        </is>
+      </c>
+      <c r="H134" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">When the build agent (the Claude Agent SDK run inside the companion) exits with an error, the exception propagates all the way up and the companion process terminates fatally (Command failed / exit code 1). Because the companion runs one build at a time and is a long-lived poller, a single agent error takes the whole worker down: it stops polling, the current run is left dangling (claimed but not reported), and a human has to notice and restart the companion before any further work can proceed. Observed repeatedly this session (e.g. when a mid-build backend restart broke the agent's MCP calls, and when an environment/dependency mismatch made the agent exit).</t>
+        </is>
+      </c>
+      <c r="I134" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OPEN - not fixed this session. Recommended fix: wrap the per-build agent execution in a try/except so an agent failure is converted into a failed BuildReport (status=failed with the error reason) that is posted back to the platform, then the companion continues polling for the next job instead of exiting. Add a top-level supervisor loop so any unexpected exception is logged and the poller restarts rather than the process dying. Acceptance: kill/emulate an agent error and confirm the companion reports build.failed with a reason and keeps running.</t>
+        </is>
+      </c>
+      <c r="J134" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="135" spans="1:10" ht="460.0" customHeight="1">
       <c r="A135" s="2">
         <v>134</v>
       </c>
-    </row>
-    <row r="136" spans="1:1">
+      <c r="B135" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A worker can deadlock a job by self-renewing its own claim while making no progress (stuck job never released)</t>
+        </is>
+      </c>
+      <c r="C135" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A worker keeps renewing its hold (heartbeat) on a job it isn't actually advancing, so the job sits claimed forever and nothing else can take it.</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Build pipeline / Claim + heartbeat (S.No 111)</t>
+        </is>
+      </c>
+      <c r="E135" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bug</t>
+        </is>
+      </c>
+      <c r="F135" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G135" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P1</t>
+        </is>
+      </c>
+      <c r="H135" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Jobs are handed to a worker via a claim, and a heartbeat (S.No 111) periodically renews that claim so the platform knows the worker is alive. The problem: the heartbeat renews the claim based on the worker still running, not on the work actually progressing. If the worker gets wedged (e.g. the agent hangs, or a step is stuck) but the heartbeat thread keeps ticking, the claim is renewed indefinitely. The job stays 'claimed', the report-timeout takeover cannot fire (the claim looks fresh), and no other worker can pick it up - a silent deadlock that only a human notices. Seen this session as the 'companion claimed but never built' deadlock.</t>
+        </is>
+      </c>
+      <c r="I135" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OPEN - not fixed this session. Recommended fix: tie claim renewal to demonstrable progress, not just process liveness - e.g. only renew while the run is advancing through phases/events, and cap the total claimed-without-progress duration so the report-timeout takeover (S.No 89) can reclaim a wedged job. Consider a max claim age / max renewals bound. Acceptance: a wedged worker's job is automatically reclaimed after the bound and can be re-dispatched without human intervention.</t>
+        </is>
+      </c>
+      <c r="J135" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="136" spans="1:10" ht="460.0" customHeight="1">
       <c r="A136" s="2">
         <v>135</v>
       </c>
-    </row>
-    <row r="137" spans="1:1">
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Dependency version skew: pinned claude-agent-sdk / anyio in the repo are behind what the runtime actually needs</t>
+        </is>
+      </c>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The project's pinned library versions lag what the running machine requires; fixed by hand on the machine but not locked in the repo, so it will break for the next person.</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Companion / Dependency management</t>
+        </is>
+      </c>
+      <c r="E136" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bug</t>
+        </is>
+      </c>
+      <c r="F136" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G136" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P2</t>
+        </is>
+      </c>
+      <c r="H136" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The companion depends on claude-agent-sdk, which in turn requires a newer anyio (the anyio.open_process 'user' keyword arrives in anyio 4.5.0; claude-agent-sdk 0.1.72 needs it). The repo's pins were stale (an old claude-agent-sdk pin and no floor on anyio), so a fresh environment installed anyio 4.4.0 and the agent crashed with "anyio.open_process() got an unexpected keyword argument 'user'". This session it was worked around by manually upgrading anyio on the host (pip install -U 'anyio&gt;=4.5' -&gt; 4.14.2), but that fix lives only on this machine - the repo still pins the broken combination, so the next developer or a rebuilt container will hit the same crash.</t>
+        </is>
+      </c>
+      <c r="I136" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OPEN - not fixed this session (env-patched only). Recommended fix: pin the correct, mutually compatible versions in the repo lockfile/requirements - bump claude-agent-sdk to the version actually in use and add an explicit anyio&gt;=4.5 floor - then rebuild the companion/worker images from the lockfile so a clean install reproduces the working environment. Acceptance: a from-scratch install (no manual pip upgrades) runs a build without the open_process 'user' error.</t>
+        </is>
+      </c>
+      <c r="J136" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="137" spans="1:10" ht="460.0" customHeight="1">
       <c r="A137" s="2">
         <v>136</v>
       </c>
-    </row>
-    <row r="138" spans="1:1">
+      <c r="B137" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Build branches are merged without first being updated against their base, causing merge conflicts at the gate</t>
+        </is>
+      </c>
+      <c r="C137" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The platform merges a feature branch without rebasing/updating it against the current base, so it hits conflicts (mergeable_state=dirty) and the merge fails.</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Build pipeline / Merge gate</t>
+        </is>
+      </c>
+      <c r="E137" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bug</t>
+        </is>
+      </c>
+      <c r="F137" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G137" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P1</t>
+        </is>
+      </c>
+      <c r="H137" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">When the merge gate is approved, the platform merges the feature branch as-is. It never updates the branch against the latest base first. If the base has moved on since the branch was cut - which is normal in a multi-developer repo - the PR can be in a conflicted state (GitHub mergeable_state = 'dirty'), and the merge API then returns HTTP 405 just like the draft case. This session WI-29 hit exactly this: an add/add conflict on frontend/.env.example left the PR dirty and the merge failed; it had to be resolved by hand. The pipeline has no step to bring a branch up to date with its base before attempting the merge.</t>
+        </is>
+      </c>
+      <c r="I137" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OPEN - not fixed this session (WI-29 resolved manually). Recommended fix: before merging, update the branch against its base (e.g. update-branch / merge base into head, or rebase) and re-check mergeability; if still conflicted after the update, fail the gate with a clear 'merge conflict - needs manual resolution' reason rather than a raw 405. Acceptance: a branch whose base advanced merges cleanly, and a genuinely conflicting branch produces a plain-language conflict reason. Related to S.No 137 (planning overlap) and S.No 139 (failure reasons).</t>
+        </is>
+      </c>
+      <c r="J137" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="138" spans="1:10" ht="460.0" customHeight="1">
       <c r="A138" s="2">
         <v>137</v>
       </c>
-    </row>
-    <row r="139" spans="1:1">
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Planning overlap: two separate work items are both told to create the same file (frontend/.env.example), guaranteeing a conflict</t>
+        </is>
+      </c>
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TASK-003 and TASK-005 each create frontend/.env.example, so when both build they collide - a work-breakdown/planning defect.</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Planning / Work-item decomposition</t>
+        </is>
+      </c>
+      <c r="E138" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bug</t>
+        </is>
+      </c>
+      <c r="F138" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G138" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P2</t>
+        </is>
+      </c>
+      <c r="H138" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Two independently-dispatched work items (TASK-003 and TASK-005) were each planned to create the same file, frontend/.env.example. When both branches are built and then merged, they produce an add/add conflict on that file - there is no shared ownership or de-duplication in the planning step. This is the upstream cause of the WI-29 merge conflict (S.No 136): the pipeline had no branch-update step to catch it, but the conflict should not have been planned in the first place. It points to a gap in how the planner assigns file ownership across parallel work items.</t>
+        </is>
+      </c>
+      <c r="I138" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OPEN - not fixed this session. Recommended fix: during decomposition, detect and prevent two work items from owning/creating the same file - assign single ownership of shared scaffolding files (like .env.example) to one work item, or sequence dependent items. Add a planning-time check that flags overlapping create-targets across sibling work items. Acceptance: sibling work items in a plan have disjoint create-file sets, or overlaps are explicitly sequenced. Related to S.No 136.</t>
+        </is>
+      </c>
+      <c r="J138" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="139" spans="1:10" ht="460.0" customHeight="1">
       <c r="A139" s="2">
         <v>138</v>
       </c>
-    </row>
-    <row r="140" spans="1:1">
+      <c r="B139" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Two developers share a single enrollment record, risking incorrect work attribution and tenant isolation</t>
+        </is>
+      </c>
+      <c r="C139" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Two devs point at the same enrollment identity (32db7f5f), so runs/work may be attributed or isolated to the wrong person.</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tenancy / Enrollment identity</t>
+        </is>
+      </c>
+      <c r="E139" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bug</t>
+        </is>
+      </c>
+      <c r="F139" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">enrollment 32db7f5f</t>
+        </is>
+      </c>
+      <c r="G139" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P2</t>
+        </is>
+      </c>
+      <c r="H139" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">During testing it was found that two different developers are operating under the same enrollment record (enrollment id 32db7f5f, under tenant 212395b8). Enrollment is meant to identify a single developer's participation in a project; sharing one record between two people means their runs, claims and attribution can be conflated, and any per-developer isolation or accounting keyed on enrollment is wrong. It also muddies debugging (whose companion claimed what) and could let one developer's actions appear under the other's identity.</t>
+        </is>
+      </c>
+      <c r="I139" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OPEN - not fixed this session (flagged during testing). Recommended fix: give each developer their own enrollment record under the tenant/project, and ensure the companion is launched with the correct per-developer enrollment/credentials so claims and events attribute to the right person. Audit existing runs that used the shared enrollment. Acceptance: each developer has a distinct enrollment and their runs attribute correctly.</t>
+        </is>
+      </c>
+      <c r="J139" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="140" spans="1:10" ht="460.0" customHeight="1">
       <c r="A140" s="2">
         <v>139</v>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Build failures don't explain why - most failures show a generic 'build failed' or a raw, cryptic error instead of a clear reason</t>
+        </is>
+      </c>
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">When a build fails for reasons other than a blocked secret (token/permission error, merge conflict, agent error, empty build), the platform shows 'build failed' or a raw exception string, not a plain classified reason.</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Build pipeline / Failure observability</t>
+        </is>
+      </c>
+      <c r="E140" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bug</t>
+        </is>
+      </c>
+      <c r="F140" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G140" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P1</t>
+        </is>
+      </c>
+      <c r="H140" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The build.failed reason is populated inconsistently across the different failure paths (build_workflow.py). A companion report failure falls back to the generic literal 'build reported failed' when no message is set. Remediation-exhausted is the hardcoded 'remediation cycles exhausted'. The PR/gate-setup and merge paths embed a raw Python/Temporal exception string ('pr/gate setup failed: {exc}', 'merge failed: {exc}') - so a token-permission (403) error or a merge conflict (405) is technically present but buried in a cryptic stack string, not classified as 'token permission issue' or 'merge conflict'. Only the secret-scan case (S.No 130) was made human-readable. Net effect: for most failure kinds an operator sees 'build failed' with no actionable reason and must dig through logs to triage.</t>
+        </is>
+      </c>
+      <c r="I140" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OPEN - not fixed this session (only the secret-scan slice, S.No 130, is done). Recommended fix: add a single failure-reason classifier that maps each failure path to a plain-language, classified reason - token/permission error (403), merge conflict (405/dirty), empty build (no changes), agent error, remediation exhausted, secret blocked - and surface that classified reason in the build.failed event and the run console (and ensure the UI displays the reason payload, cf. S.No 131). Acceptance: each distinct failure kind shows a clear, non-technical reason a non-engineer can understand. Related to S.No 130, S.No 132, S.No 136.</t>
+        </is>
+      </c>
+      <c r="J140" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
       </c>
     </row>
     <row r="141" spans="1:1">

--- a/docs/Bugs.xlsx
+++ b/docs/Bugs.xlsx
@@ -5876,11 +5876,15 @@
       <c r="H91" s="2" t="s">
         <v>401</v>
       </c>
-      <c r="I91" s="2" t="s">
-        <v>402</v>
-      </c>
-      <c r="J91" s="2" t="s">
-        <v>403</v>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fixed / validated end-to-end (2026-07-15/16). Multi-repo Hybrid Option C proven live: TASK-001 built on SpendLogTest-1-backend, 08 review + 07&lt;-&gt;08 remediation loop ran, merge gate approved, squash-merged to main, WorkItem -&gt; done; multi-repo routing, per-repo PRs and single-repo backward-compat all confirmed. All decomposed sub-tasks A1-E1 complete.</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fixed</t>
+        </is>
       </c>
     </row>
     <row r="92" spans="1:10" ht="409.6">
@@ -7450,12 +7454,12 @@
       </c>
       <c r="I134" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">OPEN - not fixed this session. Recommended fix: wrap the per-build agent execution in a try/except so an agent failure is converted into a failed BuildReport (status=failed with the error reason) that is posted back to the platform, then the companion continues polling for the next job instead of exiting. Add a top-level supervisor loop so any unexpected exception is logged and the poller restarts rather than the process dying. Acceptance: kill/emulate an agent error and confirm the companion reports build.failed with a reason and keeps running.</t>
+          <t xml:space="preserve">Fixed (2026-07-16). runner/companion/daemon.py _run_build now catches a generic build-agent error, posts a failed BuildReport (status=failed + message) to /api/runner/builds/&lt;run&gt;/report/, and keeps polling (mirrors the plan/review path _run_engine_phase) instead of the exception propagating out of serve and killing the long-lived companion. EngineAuthError still fail-closes (explicit re-raise) so a subscription/auth halt is never downgraded to a per-build failure. Tests: test_companion_daemon (agent-error reported + no crash; auth-error still halts).</t>
         </is>
       </c>
       <c r="J134" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Open</t>
+          <t xml:space="preserve">Fixed</t>
         </is>
       </c>
     </row>
@@ -7500,12 +7504,12 @@
       </c>
       <c r="I135" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">OPEN - not fixed this session. Recommended fix: tie claim renewal to demonstrable progress, not just process liveness - e.g. only renew while the run is advancing through phases/events, and cap the total claimed-without-progress duration so the report-timeout takeover (S.No 89) can reclaim a wedged job. Consider a max claim age / max renewals bound. Acceptance: a wedged worker's job is automatically reclaimed after the bound and can be re-dispatched without human intervention.</t>
+          <t xml:space="preserve">Fixed (2026-07-16). Cross-verified first: _renew_claims_for renewed the claim on process liveness alone (no progress signal, no cap), so a wedged-but-heartbeating worker held its claim until only the 2h workflow report-timeout (S.No 89) freed it. Fix: backend/api/runner_views.py stamps first_claimed_at at each claim (reset per claim, never touched by heartbeat) and MAX_CLAIM_AGE=60min caps renewal - past it the heartbeat stops renewing so the lease ages out and the run is recoverable well before the 2h backstop. Cap set above the longest legit build (&lt;60min, team-confirmed) so a healthy long build is never capped (no S.No 111 regression). Note: a companion progress-signal is the fundamentally optimal fix (distinguishes wedged-vs-working at any duration) - logged as the future upgrade if builds ever exceed ~1h. Tests: test_phase_dispatch (cap stops renewal; young claim still renews).</t>
         </is>
       </c>
       <c r="J135" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Open</t>
+          <t xml:space="preserve">Fixed</t>
         </is>
       </c>
     </row>
@@ -7600,12 +7604,12 @@
       </c>
       <c r="I137" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">OPEN - not fixed this session (WI-29 resolved manually). Recommended fix: before merging, update the branch against its base (e.g. update-branch / merge base into head, or rebase) and re-check mergeability; if still conflicted after the update, fail the gate with a clear 'merge conflict - needs manual resolution' reason rather than a raw 405. Acceptance: a branch whose base advanced merges cleanly, and a genuinely conflicting branch produces a plain-language conflict reason. Related to S.No 137 (planning overlap) and S.No 139 (failure reasons).</t>
+          <t xml:space="preserve">Fixed (2026-07-16). The merge gate merged the feature branch as-is, so a base that moved since the branch was cut left the PR mergeable_state=dirty and the GitHub merge API returned a raw 405. Fix: integrations/types.py PullRequest gains mergeable/mergeable_state; github/codehost.py adds update_branch (GitHub Update-branch; swallow 422 already-up-to-date) + ensure_mergeable (bounded re-read for GitHub's async mergeability); build_activities.py merge_build_pr_core now, before merging: if 'behind' -&gt; update branch against base then re-check; if 'dirty'/not mergeable -&gt; fail fast (non-retryable ApplicationError) with a clear 'merge conflict - needs manual resolution' reason instead of a cryptic 405; merges only when mergeable. Idempotent behind the existing 'if not pr.merged' guard. Tests: test_build_activities (behind-&gt;update-&gt;merge; dirty-&gt;clean fail, never merged).</t>
         </is>
       </c>
       <c r="J137" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Open</t>
+          <t xml:space="preserve">Fixed</t>
         </is>
       </c>
     </row>
@@ -7750,12 +7754,12 @@
       </c>
       <c r="I140" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">OPEN - not fixed this session (only the secret-scan slice, S.No 130, is done). Recommended fix: add a single failure-reason classifier that maps each failure path to a plain-language, classified reason - token/permission error (403), merge conflict (405/dirty), empty build (no changes), agent error, remediation exhausted, secret blocked - and surface that classified reason in the build.failed event and the run console (and ensure the UI displays the reason payload, cf. S.No 131). Acceptance: each distinct failure kind shows a clear, non-technical reason a non-engineer can understand. Related to S.No 130, S.No 132, S.No 136.</t>
+          <t xml:space="preserve">Fixed (2026-07-16). build.failed reasons were inconsistent (bare 'build reported failed', hardcoded 'remediation cycles exhausted', raw exception strings 'merge failed: {exc}') AND - a hidden gap - the EventSerializer never surfaced the 'reason' payload key, so the run console showed only 'Build failed'. Fix: build_activities.py classify_build_failure maps every failure path to a plain-language classified reason (merge conflict / permission-403 / remediation exhausted / empty build / agent error; the good S.No 130 secret-scan message passes through); mark_build_failed_core writes it to run.outputs.error (where the run console reads the failure line) and the build.failed event; api/serializers.py adds 'reason' to the event message keys. Composes with S.No 136 (single canonical 'merge conflict' reason). Tests: test_build_activities (classifier mappings; reason on run.outputs.error).</t>
         </is>
       </c>
       <c r="J140" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Open</t>
+          <t xml:space="preserve">Fixed</t>
         </is>
       </c>
     </row>

--- a/docs/Bugs.xlsx
+++ b/docs/Bugs.xlsx
@@ -7604,7 +7604,7 @@
       </c>
       <c r="I137" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fixed (2026-07-16). The merge gate merged the feature branch as-is, so a base that moved since the branch was cut left the PR mergeable_state=dirty and the GitHub merge API returned a raw 405. Fix: integrations/types.py PullRequest gains mergeable/mergeable_state; github/codehost.py adds update_branch (GitHub Update-branch; swallow 422 already-up-to-date) + ensure_mergeable (bounded re-read for GitHub's async mergeability); build_activities.py merge_build_pr_core now, before merging: if 'behind' -&gt; update branch against base then re-check; if 'dirty'/not mergeable -&gt; fail fast (non-retryable ApplicationError) with a clear 'merge conflict - needs manual resolution' reason instead of a cryptic 405; merges only when mergeable. Idempotent behind the existing 'if not pr.merged' guard. Tests: test_build_activities (behind-&gt;update-&gt;merge; dirty-&gt;clean fail, never merged).</t>
+          <t xml:space="preserve">Fixed (2026-07-16). The merge gate merged the feature branch as-is, so a base that moved since the branch was cut left the PR mergeable_state=dirty and the GitHub merge API returned a raw 405. Fix: integrations/types.py PullRequest gains mergeable/mergeable_state; github/codehost.py adds update_branch (GitHub Update-branch; swallow 422 already-up-to-date) + ensure_mergeable (bounded re-read for GitHub's async mergeability); build_activities.py merge_build_pr_core now, before merging: if 'behind' -&gt; update branch against base then re-check; if 'dirty'/not mergeable -&gt; fail fast (non-retryable ApplicationError) with a clear 'merge conflict - needs manual resolution' reason instead of a cryptic 405; merges only when mergeable. Idempotent behind the existing 'if not pr.merged' guard. Tests: test_build_activities (behind-&gt;update-&gt;merge; dirty-&gt;clean fail, never merged). Reason surfacing verified in live test: the classified reason reaches the user via the S.No 139 ActivityError-cause unwrap (build_workflow uses build_types.failure_reason), since str(ActivityError) is the opaque "Activity task failed".</t>
         </is>
       </c>
       <c r="J137" s="2" t="inlineStr">
@@ -7754,7 +7754,7 @@
       </c>
       <c r="I140" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fixed (2026-07-16). build.failed reasons were inconsistent (bare 'build reported failed', hardcoded 'remediation cycles exhausted', raw exception strings 'merge failed: {exc}') AND - a hidden gap - the EventSerializer never surfaced the 'reason' payload key, so the run console showed only 'Build failed'. Fix: build_activities.py classify_build_failure maps every failure path to a plain-language classified reason (merge conflict / permission-403 / remediation exhausted / empty build / agent error; the good S.No 130 secret-scan message passes through); mark_build_failed_core writes it to run.outputs.error (where the run console reads the failure line) and the build.failed event; api/serializers.py adds 'reason' to the event message keys. Composes with S.No 136 (single canonical 'merge conflict' reason). Tests: test_build_activities (classifier mappings; reason on run.outputs.error).</t>
+          <t xml:space="preserve">Fixed (2026-07-16). build.failed reasons were inconsistent (bare 'build reported failed', hardcoded 'remediation cycles exhausted', raw exception strings 'merge failed: {exc}') AND - a hidden gap - the EventSerializer never surfaced the 'reason' payload key, so the run console showed only 'Build failed'. Fix: build_activities.py classify_build_failure maps every failure path to a plain-language classified reason (merge conflict / permission-403 / remediation exhausted / empty build / agent error; the good S.No 130 secret-scan message passes through); mark_build_failed_core writes it to run.outputs.error (where the run console reads the failure line) and the build.failed event; api/serializers.py adds 'reason' to the event message keys. Composes with S.No 136 (single canonical 'merge conflict' reason). Tests: test_build_activities (classifier mappings; reason on run.outputs.error). CORRECTION (same session, caught by live test): the workflow now UNWRAPS the ActivityError .cause via build_types.failure_reason so the classifier sees the real message (Temporal str(ActivityError)="Activity task failed" otherwise hides the 405/422/conflict); AND open_build_pr_core fails an EMPTY build fast (non-retryable ApplicationError "empty build: no changes") instead of a cryptic 422 after 3 retries - an empty build still FAILS (clear reason), it does not auto-succeed. Tests: failure_reason unwrap + empty-build fast-fail + classifier mappings.</t>
         </is>
       </c>
       <c r="J140" s="2" t="inlineStr">

--- a/docs/Bugs.xlsx
+++ b/docs/Bugs.xlsx
@@ -7763,9 +7763,54 @@
         </is>
       </c>
     </row>
-    <row r="141" spans="1:1">
+    <row r="141" spans="1:10">
       <c r="A141" s="2">
         <v>140</v>
+      </c>
+      <c r="B141" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No human action to resolve a non-mergeable / redundant / failed WorkItem: a task can only reach 'done' via a successful automated build+merge. A build that fails (empty/redundant build, or a merge conflict needing manual resolution) leaves the WorkItem stuck at in_progress with no product path for a human to mark it done, skip it, or close it as redundant.</t>
+        </is>
+      </c>
+      <c r="C141" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Surfaced 2026-07-16 while testing S.No 136/139: TASK-002 (redundant with TASK-001) produced an empty build that correctly FAILED with 'Empty build: no changes to commit'. The WorkItem then sits at in_progress with the branch/draft PR left in place, and the only offered action is Retry - which re-fails for a genuinely redundant task. A human can freely trigger the NEXT task (tasks are independent unless depends_on) but cannot close/resolve the failed one. Today the only ways to reach done are the happy-path orchestrator flow or an admin DB state change.</t>
+        </is>
+      </c>
+      <c r="D141" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Work Items / Build recovery UX</t>
+        </is>
+      </c>
+      <c r="E141" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Enhancement</t>
+        </is>
+      </c>
+      <c r="F141" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">backend/apps/workitems/models.py (State: proposed/accepted/in_progress/in_review/blocked/done, no transition validation); backend/api/serializers.py WorkItemPatchSerializer (state NOT writable) + read_only state; backend/api/views.py WorkItemViewSet (trigger/build/take-over/lifecycle - no transition/mark-done action); mcp_platform_state/tools.py transition_work_item (any-&gt;any, internal only); frontend RunConsole.tsx (Retry only) / WorkItemTask.tsx (done is display-only) / OfflineTakeover.tsx</t>
+        </is>
+      </c>
+      <c r="G141" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P2</t>
+        </is>
+      </c>
+      <c r="H141" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WorkItem.state is read-only on the API (excluded from WorkItemPatchSerializer; read_only on the read serializer) and mutated ONLY internally by the orchestrator (successful build+merge / gate / reject / takeover). No human-facing transition/mark-done/close/skip action or endpoint exists; the frontend offers only Retry / Trigger phase / manual takeover (sets takeover_flag, not state). transition_work_item allows any-&gt;any but is unexposed to users.</t>
+        </is>
+      </c>
+      <c r="I141" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OPEN - proposed: add a GATED human action + API endpoint to move a WorkItem to a terminal state outside the happy path (e.g. 'Mark done', 'Close as redundant / won't-do', or 'Skip'), surfaced on the Work Items board + task page, with an audit Event. Decide whether to reuse 'done' or add a distinct terminal state (e.g. 'closed'/'cancelled') to distinguish completed-by-build from human-closed; guard with role/permission. Related S.No 76 (no task-edit UI; state not editable).</t>
+        </is>
+      </c>
+      <c r="J141" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
       </c>
     </row>
     <row r="142" spans="1:1">

--- a/docs/Bugs.xlsx
+++ b/docs/Bugs.xlsx
@@ -7813,9 +7813,54 @@
         </is>
       </c>
     </row>
-    <row r="142" spans="1:1">
+    <row r="142" spans="1:10">
       <c r="A142" s="2">
         <v>141</v>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Merge gate can't recover from a conflict without redoing the whole build. TWO related enhancements (logged together): (ENH-2, IMPLEMENT NOW) Merge-only retry / re-openable merge gate - when a merge hits a conflict, PAUSE at the merge step and let the user retry the merge after fixing the conflict, WITHOUT re-running the whole build. (ENH-1, FUTURE / only if needed) Reconcile the Run status on an EXTERNAL merge - when a user merges the PR by hand in GitHub, also flip the Run from failed to done (today the webhook updates the WorkItem + artifact but leaves the Run 'failed').</t>
+        </is>
+      </c>
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Today a merge conflict marks the ENTIRE build failed and ends the workflow, so finishing means re-running everything (AI re-writes the code, re-reviews, re-opens the PR) just to retry one merge. ENH-2 fixes this: keep the build paused at the merge gate; after the user resolves the conflict in GitHub they press Merge/Approve again and the platform completes the merge through its OWN flow (run + gate + work-item all stay correct automatically, no rebuild). ENH-1 covers a DIFFERENT path - the user merges by hand in GitHub instead of letting the platform do it; then the platform only learns via webhook (S.No 88) and today leaves the Run status stale. TEAM PLAN (2026-07-16): implement ENH-2 now; keep ENH-1 for future - it overlaps S.No 88 and is only needed if users merge OUTSIDE the platform. If ENH-2 is used, ENH-1 is largely unnecessary. Same 'soft, reconcilable' idea as the S.No 89 fix, applied to merge conflicts.</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Build pipeline / Merge gate recovery</t>
+        </is>
+      </c>
+      <c r="E142" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Enhancement</t>
+        </is>
+      </c>
+      <c r="F142" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">backend/orchestration/build_workflow.py (merge gate + ActivityError-&gt;mark_build_failed is TERMINAL on a conflict); backend/orchestration/build_activities.py merge_build_pr_core (S.No 136 dirty-&gt;fail); backend/integrations/webhooks.py _reconcile_pull_request (updates WorkItem+artifact on an external merge, NOT the Run); frontend Gates.tsx (merge gate) + RunConsole.tsx. Related: S.No 88 (external merge / missing webhook), S.No 89 (soft-reconcilable pattern), S.No 136 (conflict detection).</t>
+        </is>
+      </c>
+      <c r="G142" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P2</t>
+        </is>
+      </c>
+      <c r="H142" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">On a merge conflict the BuildWorkflow catches the ActivityError and calls mark_build_failed, which is TERMINAL - the workflow ends, so there is no live workflow to retry the merge and the merge-gate Approval is already spent. The only ways forward today are a full re-trigger (rebuilds from 07) or an external GitHub merge (needs the S.No 88 webhook, which also does not reconcile the Run status).</t>
+        </is>
+      </c>
+      <c r="I142" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OPEN. PLAN: implement ENH-2 now = make a merge conflict NON-terminal - pause the build at the merge gate (re-openable) and add a merge-only retry so the user, after resolving the conflict, can complete the merge THROUGH the platform without a rebuild (mirror the S.No 89 soft-reconcile approach: keep the workflow alive / re-openable instead of dead). ENH-1 (reconcile Run status on an external merge) kept for FUTURE / if-needed - it is part of the S.No 88 external-merge story and largely unnecessary once ENH-2 exists.</t>
+        </is>
+      </c>
+      <c r="J142" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
       </c>
     </row>
     <row r="143" spans="1:1">

--- a/docs/Bugs.xlsx
+++ b/docs/Bugs.xlsx
@@ -4922,8 +4922,15 @@
       <c r="G61" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="J61" s="2" t="s">
-        <v>141</v>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fixed on two fronts. (1) UI: the 'Other' free-text box no longer fails to appear when the agent labels an option with a letter prefix (e.g. 'd) Other') — the reveal now strips a leading enumerator before matching. Verified LIVE against the running app (served bundle). (2) Authoring: the ask_human tool contract now tells every phase agent to write ONE short plain-language question and put choices ONLY in the structured options, never inline them in the question text — stopping the duplicated-options / uppercase wall-of-text. Frontend + agent-contract change; regression test added.</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fixed</t>
+        </is>
       </c>
     </row>
     <row r="62" spans="1:10" ht="409.6">
@@ -5364,11 +5371,15 @@
       <c r="H75" s="2" t="s">
         <v>306</v>
       </c>
-      <c r="I75" s="2" t="s">
-        <v>307</v>
-      </c>
-      <c r="J75" s="2" t="s">
-        <v>141</v>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Per-tenant credentials are now actually used at runtime. Figma, Xray and Atlassian (Confluence/Jira) resolve credentials from the tenant's own IntegrationConnection (decrypt_secrets) instead of the shared server .env — closing the multi-tenant credential-leak class already fixed for GitHub (S.No 112). Per-field .env fallback kept so CI/tests are unchanged. Done together with S.No 113. Config tests added.</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fixed</t>
+        </is>
       </c>
     </row>
     <row r="76" spans="1:10" ht="409.6">
@@ -5460,11 +5471,15 @@
       <c r="H78" s="2" t="s">
         <v>323</v>
       </c>
-      <c r="I78" s="2" t="s">
-        <v>324</v>
-      </c>
-      <c r="J78" s="2" t="s">
-        <v>141</v>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Three-part fix. (A) create_work_item is now idempotent: re-running Task Breakdown REPLACES matching proposed work items (natural key project+type+title+parent) instead of duplicating the whole backlog; already-accepted/in-progress/done items are never touched. (B) A concurrent-run guard blocks a second trigger while a run is live (HTTP 409), for both phase and build triggers. (C) A confirm dialog on both trigger surfaces (Phases &amp; Runs and the Task page): Case 1 (completed) warns 're-running restarts and replaces THIS phase's artifacts, no duplicates'; Case 2 (in progress) blocks with a clear message. Idempotency + guard tests added.</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fixed</t>
+        </is>
       </c>
     </row>
     <row r="79" spans="1:10" ht="409.6">
@@ -6168,11 +6183,15 @@
       <c r="H100" s="2" t="s">
         <v>461</v>
       </c>
-      <c r="I100" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="J100" s="2" t="s">
-        <v>141</v>
+      <c r="I100" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Verified working — no code change needed. The live 'Add repository' form captures each repo's Role (backend/frontend/infra) via a real selector, sends it to the backend, and persists it on Repository.role (shown back as a chip). Auto-assign keys off this role correctly. Closed as verified.</t>
+        </is>
+      </c>
+      <c r="J100" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fixed</t>
+        </is>
       </c>
     </row>
     <row r="101" spans="1:10" ht="409.6">
@@ -6296,11 +6315,15 @@
       <c r="H104" s="2" t="s">
         <v>486</v>
       </c>
-      <c r="I104" s="2" t="s">
-        <v>487</v>
-      </c>
-      <c r="J104" s="2" t="s">
-        <v>141</v>
+      <c r="I104" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The code-host connect form's single 'Repository' field (which read as single-repo on multi-repo projects) is now labelled 'Default repository', made OPTIONAL, and carries a hint: 'Each build targets its own repo; this is only a fallback default. The token must have access to ALL repos in this project.' The connection is tenant-wide and each build already targets its work-item repo, so Save no longer gates on this field. Backend catalog + frontend render change.</t>
+        </is>
+      </c>
+      <c r="J104" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fixed</t>
+        </is>
       </c>
     </row>
     <row r="105" spans="1:10" ht="409.6">
@@ -6616,11 +6639,15 @@
       <c r="H114" s="2" t="s">
         <v>550</v>
       </c>
-      <c r="I114" s="2" t="s">
-        <v>551</v>
-      </c>
-      <c r="J114" s="2" t="s">
-        <v>141</v>
+      <c r="I114" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Phase B done (extends S.No 74/112). The remaining connectors — Atlassian Confluence/Jira, Figma, Xray — now authenticate with the tenant's own stored credentials on ANY worker, not the server .env. Atlassian needed a new 'Atlassian account email' field on the Confluence/Jira connect form (basic auth = email + token); the site URL is normalised to the bare site. Per-field .env fallback retained. Config tests added.</t>
+        </is>
+      </c>
+      <c r="J114" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fixed</t>
+        </is>
       </c>
     </row>
     <row r="115" spans="1:10" ht="380.1">
@@ -7354,12 +7381,12 @@
       </c>
       <c r="I132" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">OPEN - not fixed this session. Recommended fix: add a UI affordance (a link/panel on the Work Item or Run screen) that fetches the code_review artifact body via get_artifact_body and renders it (Markdown), and make sure the artifact is associated to the run so the front end can locate it. Verify at registration time that the artifact's body pointer (S3/stage) is populated so there is something to fetch. Acceptance: from a run that has been reviewed, a human can click through and read the full review text and verdict without leaving the UI.</t>
+          <t xml:space="preserve">Verified already fixed — no code change needed. Cross-checked against a live run: the code_review artifact IS registered with a rendered report body (the companion uploads the .md to S3 — confirmed a ~22 KB report object exists for the latest run), and the generic artifact preview reads it, so the report opens and reads in the UI. The earlier 'no body' analysis looked only at the platform-side fallback registration and missed the companion upload. Closed as verified.</t>
         </is>
       </c>
       <c r="J132" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Open</t>
+          <t xml:space="preserve">Fixed</t>
         </is>
       </c>
     </row>
@@ -7654,12 +7681,12 @@
       </c>
       <c r="I138" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">OPEN - not fixed this session. Recommended fix: during decomposition, detect and prevent two work items from owning/creating the same file - assign single ownership of shared scaffolding files (like .env.example) to one work item, or sequence dependent items. Add a planning-time check that flags overlapping create-targets across sibling work items. Acceptance: sibling work items in a plan have disjoint create-file sets, or overlaps are explicitly sequenced. Related to S.No 136.</t>
+          <t xml:space="preserve">Not reproducible / not a bug — verified against stored work-item data. TASK-003 creates the FRONTEND .env.example (frontend repo); TASK-005 is a backend SQLAlchemy/Alembic task (backend repo) — different files, different repos, no collision. The likely confusion: TASK-002 (backend .env.example) and TASK-003 (frontend .env.example) are two correctly-separate files that merely share a name. Closed.</t>
         </is>
       </c>
       <c r="J138" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Open</t>
+          <t xml:space="preserve">Fixed</t>
         </is>
       </c>
     </row>

--- a/docs/Bugs.xlsx
+++ b/docs/Bugs.xlsx
@@ -7881,12 +7881,12 @@
       </c>
       <c r="I142" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">OPEN. PLAN: implement ENH-2 now = make a merge conflict NON-terminal - pause the build at the merge gate (re-openable) and add a merge-only retry so the user, after resolving the conflict, can complete the merge THROUGH the platform without a rebuild (mirror the S.No 89 soft-reconcile approach: keep the workflow alive / re-openable instead of dead). ENH-1 (reconcile Run status on an external merge) kept for FUTURE / if-needed - it is part of the S.No 88 external-merge story and largely unnecessary once ENH-2 exists.</t>
+          <t xml:space="preserve">ENH-2 IMPLEMENTED &amp; VALIDATED LIVE (@ 66b70c8, + gate banner). A merge conflict is now NON-terminal: merge_build_pr detects a dirty PR and raises a typed MergeConflict; the BuildWorkflow catches it, RE-OPENS the merge gate (resets the approval to pending, records outputs.merge_conflict + a build.merge_conflict event) and waits — instead of failing the build. The user resolves the conflict in GitHub and approves again; the platform retries ONLY the merge (no rebuild, no re-review). Proven live on TASK-003 (run 1d1dd943): injected an add/add conflict on .env.example -&gt; approve -&gt; gate re-opened (once per remaining conflict) -&gt; resolved -&gt; approve -&gt; platform merged PR#1 (merge commit c1d7552a) -&gt; WorkItem done -&gt; run completed, with NO rebuild across retries. The merge gate now shows a warning banner explaining the conflict + retry (ApprovalSerializer.merge_conflict; shown ONLY on a re-opened merge gate, never other gates). ENH-1 (reconcile Run status on an EXTERNAL GitHub merge) remains FUTURE / optional — it overlaps S.No 88 and is only needed if users merge outside the platform, which ENH-2 makes largely unnecessary.</t>
         </is>
       </c>
       <c r="J142" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Open</t>
+          <t xml:space="preserve">Fixed</t>
         </is>
       </c>
     </row>

--- a/docs/Bugs.xlsx
+++ b/docs/Bugs.xlsx
@@ -7894,10 +7894,100 @@
       <c r="A143" s="2">
         <v>142</v>
       </c>
+      <c r="B143" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Backlog push to Jira: tasks never reach Jira — each Task is created with its Story as parent, which Jira rejects</t>
+        </is>
+      </c>
+      <c r="C143" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">During a live Jira push of the SpendLog-1 backlog, all 5 epics + 15 stories were created but 0 of 29 tasks landed. reconcile creates each task with parent = its story's Jira key; Jira rejects a standard Task parented to a Story (400 'Please select valid parent issue') — only Sub-tasks can live under a Story (Jira hierarchy: Epic &gt; Story/Task, and Epic &gt; Story &gt; Sub-task).</t>
+        </is>
+      </c>
+      <c r="D143" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Integrations / TaskTracker (Jira)</t>
+        </is>
+      </c>
+      <c r="E143" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bug</t>
+        </is>
+      </c>
+      <c r="F143" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G143" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P2</t>
+        </is>
+      </c>
+      <c r="H143" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">reconcile.reconcile_work_item mapped WorkItem.type 'task' -&gt; Jira 'Task' and set parent={key: story}. Jira does not allow a standard Task under a Story. Stories succeeded because Story-under-Epic via the parent field IS valid; tasks-under-stories are not.</t>
+        </is>
+      </c>
+      <c r="I143" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Map the platform's Epic&gt;Story&gt;Task to Jira's native Epic&gt;Story&gt;Sub-task. In reconcile: a task WITH a reconciled parent (its story) is now created as a Jira SUB-TASK under that story, using the project's actual sub-task issue-type name (resolved from Jira via AtlassianTaskTracker.subtask_type_name(), cached, fallback 'Subtask'); a task with NO reconciled parent is created as a top-level Task with no parent (sub-tasks require a parent). Epics/stories unchanged. Validated LIVE against the ST project (Sub-task-under-Story create succeeds; Task-under-Story returns 400). Tests added in test_reconcile (subtask mapping + parentless task).</t>
+        </is>
+      </c>
+      <c r="J143" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fixed</t>
+        </is>
+      </c>
     </row>
     <row r="144" spans="1:1">
       <c r="A144" s="2">
         <v>143</v>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Backlog publish reports a green 'Published' while items silently fail to reach the system of record</t>
+        </is>
+      </c>
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The same Jira push showed 'Published — 49 work items reconciled (20 created)' even though 29 tasks failed. reconcile_backlog ran each item with no per-item error handling and the publish response/dialog surfaced only reconciled/created — so partial failures were invisible and the reconciled count over-reported what actually landed.</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Integrations / Publish</t>
+        </is>
+      </c>
+      <c r="E144" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bug</t>
+        </is>
+      </c>
+      <c r="F144" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G144" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P2</t>
+        </is>
+      </c>
+      <c r="H144" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">reconcile_backlog processed items in a list comprehension with no try/except, and _publish_tasktracker + the ExportPublish dialog reported only reconciled/created counts — never failures. A partial push read as a full success.</t>
+        </is>
+      </c>
+      <c r="I144" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">reconcile_backlog now isolates each item in try/except: a single item's SoR rejection is recorded (logged as a workitem.reconcile_failed event + returned in a 'failed' list) and the run continues, instead of aborting or being swallowed. The publish API returns status 'partial' plus the failed items; the artifact stores a failed count; the ExportPublish dialog now shows 'Published with some failures — N created, M failed' + the first error, instead of an all-green success. Test added in test_reconcile (per-item failure captured; epic/story still land).</t>
+        </is>
+      </c>
+      <c r="J144" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fixed</t>
+        </is>
       </c>
     </row>
     <row r="145" spans="1:1">

--- a/docs/Bugs.xlsx
+++ b/docs/Bugs.xlsx
@@ -7931,7 +7931,7 @@
       </c>
       <c r="I143" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Map the platform's Epic&gt;Story&gt;Task to Jira's native Epic&gt;Story&gt;Sub-task. In reconcile: a task WITH a reconciled parent (its story) is now created as a Jira SUB-TASK under that story, using the project's actual sub-task issue-type name (resolved from Jira via AtlassianTaskTracker.subtask_type_name(), cached, fallback 'Subtask'); a task with NO reconciled parent is created as a top-level Task with no parent (sub-tasks require a parent). Epics/stories unchanged. Validated LIVE against the ST project (Sub-task-under-Story create succeeds; Task-under-Story returns 400). Tests added in test_reconcile (subtask mapping + parentless task).</t>
+          <t xml:space="preserve">TWO layered causes, both fixed. (1) REAL ROOT CAUSE: reconcile's idempotency guard 'if wi.external_ref' wrongly treated a repo-assigned task as already-reconciled. Multi-repo tasks carry external_ref.repo_assignment (the planner's repo pick, Option C) with NO SoR id, so on the live push every task was SKIPPED before reaching Jira (export showed created:0, reconciled:29, no error — not a Jira rejection at all). Fixed: the guard now checks for a real SoR key (external_ref.id), and the SoR ref is MERGED into external_ref so the repo_assignment is preserved. (2) HIERARCHY (latent, also fixed): once tasks reach Jira, a standard Task can't be a child of a Story, so a task with a reconciled story parent is created as a SUB-TASK under it (the project's real sub-task issue-type name, resolved via AtlassianTaskTracker.subtask_type_name() + cached), and a parentless task as a top-level Task. Validated live (Sub-task-under-Story create succeeds; Task-under-Story returns 400). Tests in test_reconcile: repo-assigned task not-skipped + repo_assignment preserved, subtask mapping, parentless task, per-item failure capture. NOTE: my first commit fixed only the hierarchy; the guard/repo_assignment fix (the true blocker) landed in the follow-up commit after the re-push showed created:0.</t>
         </is>
       </c>
       <c r="J143" s="2" t="inlineStr">

--- a/docs/Bugs.xlsx
+++ b/docs/Bugs.xlsx
@@ -7990,9 +7990,54 @@
         </is>
       </c>
     </row>
-    <row r="145" spans="1:1">
+    <row r="145" spans="1:10" ht="460.0" customHeight="1">
       <c r="A145" s="2">
         <v>144</v>
+      </c>
+      <c r="B145" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Secret scanner false-positives on hyphenated placeholders (e.g. change-me-...) in .env.example, blocking legitimate builds</t>
+        </is>
+      </c>
+      <c r="C145" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The pre-push secret scan flagged an obvious placeholder value as a real secret, so the push was blocked and the build failed.</t>
+        </is>
+      </c>
+      <c r="D145" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Companion / Pre-push secret scan</t>
+        </is>
+      </c>
+      <c r="E145" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bug</t>
+        </is>
+      </c>
+      <c r="F145" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3c33554</t>
+        </is>
+      </c>
+      <c r="G145" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P1</t>
+        </is>
+      </c>
+      <c r="H145" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The companion's pre-push secret scanner (runner/companion/guardrails.py) blocks a push when it finds anything that looks like a hardcoded secret. Its placeholder allow-list recognised the literal token 'changeme' but NOT the far more common hyphenated/underscored form 'change-me'. So a legitimate .env.example placeholder - JWT_SECRET=change-me-minimum-32-characters-long (36 chars, Shannon entropy 3.875) - was not recognised as a placeholder, tripped the generic high-entropy heuristic, and was flagged as a 'high_entropy_secret'. The push was blocked and the build failed. This is a FALSE POSITIVE: the value is an obvious placeholder, not a real secret. It blocked WI-32 and would block any task whose example env file uses the very common change-me convention. The build agent did nothing wrong - the scanner was too aggressive.</t>
+        </is>
+      </c>
+      <c r="I145" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FIXED (commit 3c33554). Two changes in runner/companion/guardrails.py: (1) broadened the placeholder allow-list to cover change[-_ ]?me / replace[-_ ]?me / to-be-(changed|set|replaced|filled|generated) / secret-(here|goes) / dummy / sample / redacted, so hyphenated placeholders are recognised. (2) Committed template files (.env.example, *.sample, *.template, *.dist, *.tpl) now skip the generic entropy heuristic - placeholders are expected there - while STILL running the high-precision key-format patterns (AWS AKIA..., GitHub ghp_..., PEM private keys, JWT), so a real key shape pasted into an example file is still blocked. Regression tests in backend/tests/test_guardrails.py: the exact WI-32 value + change_me/replace-me variants pass clean; a real random token in real source still blocks; AWS/GitHub key shapes inside .env.example still block; non-template source keeps the full entropy scan. 12/12 scanner tests pass.</t>
+        </is>
+      </c>
+      <c r="J145" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fixed</t>
+        </is>
       </c>
     </row>
     <row r="146" spans="1:1">
@@ -8000,9 +8045,54 @@
         <v>145</v>
       </c>
     </row>
-    <row r="147" spans="1:1">
+    <row r="147" spans="1:10" ht="460.0" customHeight="1">
       <c r="A147" s="2">
         <v>146</v>
+      </c>
+      <c r="B147" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AI-engine build failures (usage/rate limit, agent CLI exit 1) show a raw, unreadable message instead of a clear reason</t>
+        </is>
+      </c>
+      <c r="C147" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">When the agent CLI fails (e.g. the Anthropic usage limit is reached) the run console shows 'Command failed with exit code 1 ... Check stderr output for details' - opaque and non-actionable.</t>
+        </is>
+      </c>
+      <c r="D147" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Build pipeline / Failure observability + Companion</t>
+        </is>
+      </c>
+      <c r="E147" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bug</t>
+        </is>
+      </c>
+      <c r="F147" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">daemon.py:271</t>
+        </is>
+      </c>
+      <c r="G147" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P1</t>
+        </is>
+      </c>
+      <c r="H147" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">When the AI build agent fails to run - most commonly because the Anthropic usage/rate limit is reached, but also on any agent CLI non-zero exit - the companion's error handler (runner/companion/daemon.py ~line 271) captures only the engine driver's generic wrapper string and reports it verbatim: 'Command failed with exit code 1 (exit code: 1) / Error output: Check stderr output for details'. The platform's classify_build_failure (backend/orchestration/build_activities.py) does not recognise this signature, so the raw string passes straight through to the build.failed reason and the run console. The user sees an opaque error with no indication that the real cause was a usage limit and no guidance on what to do. This bit WI-32: the usage limit was hit during the cycle-2 remediation build and the console showed only 'Command failed with exit code 1'. Same defect class as S.No 139 (classified reasons) but for the engine/usage-limit failure path, which was not covered.</t>
+        </is>
+      </c>
+      <c r="I147" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OPEN - Fix A planned this session (this row's owner). Two parts: (1) Companion (daemon.py): capture the agent process's stderr tail and put the actual cause in the report message instead of the placeholder 'Check stderr output for details'. (2) Platform (classify_build_failure): recognise engine / usage-limit / rate-limit signatures ('exit code 1', 'usage limit', 'rate limit', '429', 'overloaded', 'quota', 'Failed to start Claude Code') and map them to a plain-language reason, e.g. 'The AI engine hit its usage limit - the build stopped; retry when the limit resets.' NOTE: true resume-from-checkpoint on a transient failure (so a re-run continues from the last cycle instead of rebuilding) is tracked separately as S.No 147 and is owned by the other developer. Acceptance: a usage-limit failure shows a clear, non-technical reason naming the usage limit, not a raw exit-code string.</t>
+        </is>
+      </c>
+      <c r="J147" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
       </c>
     </row>
     <row r="148" spans="1:1">

--- a/docs/Bugs.xlsx
+++ b/docs/Bugs.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30306"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="102" documentId="11_14FDEAE3397E350B81F2A24CBED9C52169691D91" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C231EF7A-42E9-490A-B4B0-64F9F645D887}"/>
+  <xr:revisionPtr revIDLastSave="166" documentId="11_14FDEAE3397E350B81F2A24CBED9C52169691D91" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{285B08F5-3480-48DB-957D-3CBD7D1D2C50}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
   <metadataTypes count="1">
     <metadataType name="XLRICHVALUE" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1"/>
   </metadataTypes>
-  <futureMetadata name="XLRICHVALUE" count="13">
+  <futureMetadata name="XLRICHVALUE" count="16">
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
@@ -130,8 +130,29 @@
         </ext>
       </extLst>
     </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="13"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="14"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="15"/>
+        </ext>
+      </extLst>
+    </bk>
   </futureMetadata>
-  <valueMetadata count="13">
+  <valueMetadata count="16">
     <bk>
       <rc t="1" v="0"/>
     </bk>
@@ -171,12 +192,21 @@
     <bk>
       <rc t="1" v="12"/>
     </bk>
+    <bk>
+      <rc t="1" v="13"/>
+    </bk>
+    <bk>
+      <rc t="1" v="14"/>
+    </bk>
+    <bk>
+      <rc t="1" v="15"/>
+    </bk>
   </valueMetadata>
 </metadata>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="966" uniqueCount="576">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1249" uniqueCount="729">
   <si>
     <t>S.No</t>
   </si>
@@ -955,6 +985,9 @@
 3. The presentation format is also not good and confusing to the team whether they are directly rendered as output or any manipulations being done while presenting the clarifications by our engine?</t>
   </si>
   <si>
+    <t>Fixed on two fronts. (1) UI: the 'Other' free-text box no longer fails to appear when the agent labels an option with a letter prefix (e.g. 'd) Other') — the reveal now strips a leading enumerator before matching. Verified LIVE against the running app (served bundle). (2) Authoring: the ask_human tool contract now tells every phase agent to write ONE short plain-language question and put choices ONLY in the structured options, never inline them in the question text — stopping the duplicated-options / uppercase wall-of-text. Frontend + agent-contract change; regression test added.</t>
+  </si>
+  <si>
     <t>In the Connect Machine page: 
 When the user has connected his local companion and created a work item and executed/run a phase for example: Ideation, after sometime the engine is showing companion disconnect and saying to connect again wih error message. Sharing you the reference images, clearly go through and findout the root cause first and report it to the team working on this issue and take their approval before fixing.
 Due to this issue, even when the team is running the next phase i.e requirements, the UI showing that phase is running but never got any artifacts as ouptut or any gate for that run. This is very serious issue and need to be analysed accurately.
@@ -1218,7 +1251,7 @@
     <t>The token_ref indirection is a documented Phase-5 seam; Phase 1 hardcoded from_settings() and decrypt_secrets was never wired into the connector builders.</t>
   </si>
   <si>
-    <t>Deferred (Phase-5 seam). Fix = wire decrypt_secrets(conn) into the connector builders so per-tenant creds are used and retire the .env fallback; make test-connection a real reachability probe. For the current greenfield test, Jira is connected exactly like Confluence: the Integrations connection supplies scopes.project_key and the shared Atlassian creds live in .env.</t>
+    <t>Per-tenant credentials are now actually used at runtime. Figma, Xray and Atlassian (Confluence/Jira) resolve credentials from the tenant's own IntegrationConnection (decrypt_secrets) instead of the shared server .env — closing the multi-tenant credential-leak class already fixed for GitHub (S.No 112). Per-field .env fallback kept so CI/tests are unchanged. Done together with S.No 113. Config tests added.</t>
   </si>
   <si>
     <t>No dedicated Task Breakdown review screen; dependencies and estimates are not surfaced before the gate</t>
@@ -1269,7 +1302,7 @@
     <t>No idempotency/natural key on work-item creation, unlike register_artifact which versions siblings.</t>
   </si>
   <si>
-    <t>Deferred. Add an idempotency key (e.g. project+phase+title, or an agent-supplied external key) so a re-run upserts rather than duplicates. For today's run, delete any partial batch before re-triggering.</t>
+    <t>Three-part fix. (A) create_work_item is now idempotent: re-running Task Breakdown REPLACES matching proposed work items (natural key project+type+title+parent) instead of duplicating the whole backlog; already-accepted/in-progress/done items are never touched. (B) A concurrent-run guard blocks a second trigger while a run is live (HTTP 409), for both phase and build triggers. (C) A confirm dialog on both trigger surfaces (Phases &amp; Runs and the Task page): Case 1 (completed) warns 're-running restarts and replaces THIS phase's artifacts, no duplicates'; Case 2 (in progress) blocks with a clear message. Idempotency + guard tests added.</t>
   </si>
   <si>
     <t>Jira integration is one-way (create-only): no inbound webhook, no status sync, dropped fields</t>
@@ -1482,7 +1515,7 @@
     <t>FAILED is treated as terminal and a late successful phase.reported does not reconcile it; report_timeout (7200s wall-clock from dispatch) trips on an asleep companion that later completes fine. Once run() returns on takeover the workflow is gone, so both phase_report and decide_gate have no live workflow to signal.</t>
   </si>
   <si>
-    <t>Open - co-dev (tarun's team) to fix. Proposed: (1) a late phase.reported ok reconciles the run to awaiting_gate + opens the gate; (2) treat takeover as a reclaimable 'parked' state, not terminal, while the companion still heartbeats; (3) decide_gate tolerates an absent/closed workflow and drives publish_artifacts + transition_work_item directly; (4) fix the misleading UI copy. Run 8738d4ba manually reconciled to awaiting_gate 2026-07-13.</t>
+    <t>Fixed (session 2026-07-15). Report-timeout takeover is now NON-terminal and reconcilable. (1) New Run.Status.STALLED (runs migration 0006) replaces terminal FAILED on timeout: mark_phase_takeover_core parks the run as STALLED + sets the WorkItem takeover_flag. (2) AgentRunWorkflow no longer returns on timeout: it marks the soft takeover then KEEPS waiting for the report, so a companion that only slept returns and flows through register -&gt; verify_writes -&gt; open_gate -&gt; approve -&gt; publish. This fixes BOTH faces: the run no longer sticks in terminal FAILED (no false 'no artifact registered'), and the gate Approve works because the workflow is still alive. (3) register_phase_result_core clears takeover_flag on a successful late report (un-parks). (4) New abandon_run workflow signal + orchestration.takeover.abandon_stalled_run, wired into the run-level /runs/{id}/take-over/ endpoint, so an explicit human takeover ('Take over manually' / 'Reconnect &amp; re-run') ends the still-waiting run terminally (no lingering workflow). (5) UI: 'stalled' renders as 'Parked for takeover' (RunConsole) and OfflineTakeover recognizes it + explains auto-reconcile. Tests (test_phase_dispatch): STALLED park, late-report reconcile clears the flag, abandon-only-when-parked, offline-then-abandoned + recovers-after-takeover (both against real Temporal). Files: backend/apps/runs/models.py, backend/apps/runs/migrations/0006_run_stalled_status.py, backend/orchestration/{workflows,activities,takeover}.py, backend/api/views.py, frontend/src/features/lifecycle/RunConsole.tsx, frontend/src/features/observability/OfflineTakeover.tsx.</t>
   </si>
   <si>
     <t>EPIC: Multi-repo work-item assignment (Hybrid Option C) - agent proposes a repo per work item, human confirms/overrides at the Task Breakdown gate, then implementation routes each task to its repo</t>
@@ -1503,10 +1536,7 @@
     <t>Multi-repo infra (WorkItem.repo FK, repo-scoped context, repo_topology, per-repo manifest, build routing on work_item.repo) exists, but nothing lets Task Breakdown assign a repo, nor a user set/override it - so multi-repo routing was impossible end-to-end.</t>
   </si>
   <si>
-    <t>Open - build in order A1-&gt;A4, B1-&gt;B3, C1, E1, then D1 verify. Backward-compatible: repo_id optional, single-repo unchanged.</t>
-  </si>
-  <si>
-    <t>In Progress</t>
+    <t>Fixed / validated end-to-end (2026-07-15/16). Multi-repo Hybrid Option C proven live: TASK-001 built on SpendLogTest-1-backend, 08 review + 07&lt;-&gt;08 remediation loop ran, merge gate approved, squash-merged to main, WorkItem -&gt; done; multi-repo routing, per-repo PRs and single-repo backward-compat all confirmed. All decomposed sub-tasks A1-E1 complete.</t>
   </si>
   <si>
     <t>A1: get_context does not return the project's repository list for project-level/planning runs - only repo_topology + the single scoped repo. Task Breakdown can't see the repos to assign them</t>
@@ -1683,7 +1713,7 @@
     <t>Role is optional on the model; UI may not surface it.</t>
   </si>
   <si>
-    <t>Open - verify in the running app; add the role field if absent.</t>
+    <t>Verified working — no code change needed. The live 'Add repository' form captures each repo's Role (backend/frontend/infra) via a real selector, sends it to the backend, and persists it on Repository.role (shown back as a chip). Auto-assign keys off this role correctly. Closed as verified.</t>
   </si>
   <si>
     <t>C1: wire 'Approve assignment &amp; continue' as the Task Breakdown gate decision - approving locks the repo assignments</t>
@@ -1758,7 +1788,7 @@
     <t>The code-host connect form predates multi-repo. The 'Repository' field is the connection's default/fallback repo, but is not labeled as such, so on a multi-repo project it looks like you must pick one repo.</t>
   </si>
   <si>
-    <t>Open - P2, team to address later. Relabel to 'Default repository (optional)'; add a hint that ONE token must reach ALL of the project's repos (a classic PAT with repo scope, or a fine-grained token listing each repo); optionally list the project's repos + connected status inline so it's clear all are covered.</t>
+    <t>The code-host connect form's single 'Repository' field (which read as single-repo on multi-repo projects) is now labelled 'Default repository', made OPTIONAL, and carries a hint: 'Each build targets its own repo; this is only a fallback default. The token must have access to ALL repos in this project.' The connection is tenant-wide and each build already targets its work-item repo, so Save no longer gates on this field. Backend catalog + frontend render change.</t>
   </si>
   <si>
     <t>Project topology auto-derives from repo count (2=split, 3+=multi) and overrides the user's explicit 'Multi-repo' choice; the create form offers only Single/Multi (2 options) while the model has 3 (single/split/multi)</t>
@@ -1950,7 +1980,7 @@
     <t>Same root cause as S.No 112 (connectors authenticate from the server .env, not per-tenant DB creds). Phase A did only the codehost because it was the build-workflow blocker. The Atlassian connectors also need email + site_url, which are NOT in the connect form's catalog yet, so this is a larger change (catalog + form fields + config wiring) - hence deferred.</t>
   </si>
   <si>
-    <t>Open - follow-up to Phase A. Plan: (1) add email/site_url (or equivalent) fields to the Atlassian vendors in catalog.py + the connect form; (2) change _atlassian_config to take the conn and decrypt api_token + read email/site_url from scopes; (3) same decrypt-and-use for Figma access_token and Xray client_id/client_secret; (4) keep the settings fallback for back-compat; (5) tests per connector + a two-tenant isolation test. Not blocking now - SpendLog-1 is sor=internal with no non-codehost connections configured.</t>
+    <t>Phase B done (extends S.No 74/112). The remaining connectors — Atlassian Confluence/Jira, Figma, Xray — now authenticate with the tenant's own stored credentials on ANY worker, not the server .env. Atlassian needed a new 'Atlassian account email' field on the Confluence/Jira connect form (basic auth = email + token); the site URL is normalised to the bare site. Per-field .env fallback retained. Config tests added.</t>
   </si>
   <si>
     <t>Blocking code review silently 'passes' (fail-OPEN): the 07&lt;-&gt;08 remediation loop reads blocking findings ONLY from the json verdict block in the 08 agent's FINAL message. When the agent's final message is prose (its machine-readable json block missing / not last / delivered via a separate event) the platform parses 0 findings, counts 0 blocking, SKIPS remediation and opens the merge gate on an unreviewed downgrade.</t>
@@ -2020,6 +2050,9 @@
 </t>
   </si>
   <si>
+    <t>FIXED (2026-07-15). agents/06_task_breakdown/agent.md: added a 'Writing standard' requiring every Epic/Story/Task Description + Acceptance Criterion to be plain-language-with-technical-nuance, detailed and self-contained enough that a developer can implement by reading it ALONE (behaviour, inputs/outputs, states, edge cases), with concrete hand-verifiable acceptance criteria and no bare placeholders; modelled the standard in all three template placeholders. Improvement flows to the Work Items board + artifact previews automatically. Test: test_agents_migration.test_task_breakdown_descriptions_and_ac_are_humanized. Per team decision the blast radius today was 06 only; the SAME defect in 02/09/00c/04/03/10 is logged as S.No 121-126 (register-condition per audience: technical-humanized for testing/security, plain+nuance for the rest) and NOT fixed this session.</t>
+  </si>
+  <si>
     <t>In the work items board when clicked on either epic or user story it shows children(3 or 4), instead when clicked on the childern it should show those tasks</t>
   </si>
   <si>
@@ -2028,7 +2061,475 @@
 Note: The same issues applies to the internal artifact content when the user clicked on the preview. You must read all the phase agents to identify what are all the artifacts it generates and how they are represented as names or disply or written.</t>
   </si>
   <si>
-    <t xml:space="preserve">Fixed (session 2026-07-15). Report-timeout takeover is now NON-terminal and reconcilable. (1) New Run.Status.STALLED (runs migration 0006) replaces terminal FAILED on timeout: mark_phase_takeover_core parks the run as STALLED + sets the WorkItem takeover_flag. (2) AgentRunWorkflow no longer returns on timeout: it marks the soft takeover then KEEPS waiting for the report, so a companion that only slept returns and flows through register -&gt; verify_writes -&gt; open_gate -&gt; approve -&gt; publish. This fixes BOTH faces: the run no longer sticks in terminal FAILED (no false 'no artifact registered'), and the gate Approve works because the workflow is still alive. (3) register_phase_result_core clears takeover_flag on a successful late report (un-parks). (4) New abandon_run workflow signal + orchestration.takeover.abandon_stalled_run, wired into the run-level /runs/{id}/take-over/ endpoint, so an explicit human takeover ('Take over manually' / 'Reconnect &amp; re-run') ends the still-waiting run terminally (no lingering workflow). (5) UI: 'stalled' renders as 'Parked for takeover' (RunConsole) and OfflineTakeover recognizes it + explains auto-reconcile. Tests (test_phase_dispatch): STALLED park, late-report reconcile clears the flag, abandon-only-when-parked, offline-then-abandoned + recovers-after-takeover (both against real Temporal). Files: backend/apps/runs/models.py, backend/apps/runs/migrations/0006_run_stalled_status.py, backend/orchestration/{workflows,activities,takeover}.py, backend/api/views.py, frontend/src/features/lifecycle/RunConsole.tsx, frontend/src/features/observability/OfflineTakeover.tsx.</t>
+    <t>FIXED (2026-07-15) - FULL blast radius + Part C (team-approved re-scope). (1) Artifact.title field + migration 0003_artifact_title (nullable, backward-safe). (2) register_artifact/update_artifact gain a title param, plus MCP server + companion wrappers, tool docstrings say 'ALWAYS pass a title'. (3) Part C-1 versioning-collision FIXED: version scoped by (project,phase,type,title) when titled, so per-item siblings (adr/test_case/security_finding/code/code_review/test_report) each start v1 instead of falsely superseding; untitled/singletons keep old behaviour. (4) Platform code/code_review get titles (WI key). (5) Serializers/consumers: DRF ArtifactSerializer + MCP _artifact/_lean_ref + preview payload + traceability node + dashboard + publish title expose/prefer title. (6) Frontend: new artifactLabel(title,type) helper (falls back to humanized type) in Artifacts registry list+search, preview H1/row, Traceability node (was raw type), Export/Publish. (7) 7 agents 04/05/07/08/09/09b/10 author human titles (Wireframe - Login Page, ADR-003 - Event Sourcing, TC-014 - ...). (8) Part C-2 ContractsDrift FIXED: no JSON.stringify dump (humanized scalar summary); DriftRecordSerializer enriches impacted with node_title+repo_name (batched) so no raw UUIDs. Wireframe STATES stay a separate label axis by design. Tests: test_mcp_platform_state (title + per-item independent versions), test_agents_migration (06 + per-item titles), test_review_dispatch/test_api_contract green; frontend tsc clean; ruff clean. Migration NOT yet applied to shared cloud DB - held for a coordinated make migrate (nullable=back-compat).</t>
+  </si>
+  <si>
+    <t>121</t>
+  </si>
+  <si>
+    <t>Requirements agent (02) authors user stories, functional requirements, acceptance criteria and NFRs too technically/formally for its reviewer. Same defect class as S.No 118 (06 task breakdown): the content is engineer/QA-precision only with no human-readability bar, yet the Product Owner reviews it. HUMANIZATION REGISTER for the fix = PLAIN LANGUAGE retaining the technical nuance (broader audience: PO + developer).</t>
+  </si>
+  <si>
+    <t>Investigation (session 2026-07-15) edge-case sweep of all 16 phase agents for the S.No 118 pattern. 02 is the closest structural analog to 06.</t>
+  </si>
+  <si>
+    <t>Agents / 02 Requirements / content humanization</t>
+  </si>
+  <si>
+    <t>Quality bar is 'a QA engineer can execute without a follow-up question' (agents/02_requirements/agent.md:10); FR format is formal SHALL boilerplate (:115); acceptance criteria are bare BDD stubs (:85-97); user-story descriptions have no plain-language directive; reviewer is the Product Owner (:357). Related S.No 118, 120.</t>
+  </si>
+  <si>
+    <t>OPEN - NOT fixed this session. Team scoped today's fix to S.No 118 (06 task breakdown) only. Planned: add a plain-language-with-technical-nuance authoring bar to user-story descriptions, FR statements and acceptance criteria - mirror 06's assignment_rationale directive (:280) and the good patterns in 05_ux_design/12_deployment/08_code_review.</t>
+  </si>
+  <si>
+    <t>122</t>
+  </si>
+  <si>
+    <t>Testing agent (09) authors UAT scenarios FOR the Product Owner, plus defect reports and test-case descriptions, with an engineer-precision bar only. Same defect class as S.No 118. HUMANIZATION REGISTER for the fix = HUMANIZED-TECHNICAL (keep the technical register but make it clear and well-structured) - NOT plain language, because QA/UAT personnel must interpret the technical detail correctly; plain language would cause misinterpretation.</t>
+  </si>
+  <si>
+    <t>Investigation edge-case sweep. UAT is a business-verification event handed to a non-engineer, yet authored with two-engineer precision.</t>
+  </si>
+  <si>
+    <t>Agents / 09 Testing / content humanization</t>
+  </si>
+  <si>
+    <t>UAT scenarios authored for the PO (agents/09_testing/agent.md:483-494) and defect descriptions (:433-459) use a two-engineer precision bar (:212) with no readability directive for the PO-facing UAT. Test-case Expected Result/Description carry the same risk. Related S.No 118, 120.</t>
+  </si>
+  <si>
+    <t>OPEN - NOT fixed this session (team scope = 06 only). Planned: add a HUMANIZED-TECHNICAL clarity bar (structured, understandable, technical register retained) to UAT scenarios, defect reports and test-case descriptions - not plain language.</t>
+  </si>
+  <si>
+    <t>123</t>
+  </si>
+  <si>
+    <t>Intelligent Context Extractor agent (00c) authors the codebase_intelligence Executive Summary, health dashboard and module-documentation prose read by humans onboarding to a project, with no plain-language directive - jargon-prone. Same defect class as S.No 118. HUMANIZATION REGISTER = PLAIN LANGUAGE retaining technical nuance.</t>
+  </si>
+  <si>
+    <t>Investigation edge-case sweep.</t>
+  </si>
+  <si>
+    <t>Agents / 00c Context Extractor / content humanization</t>
+  </si>
+  <si>
+    <t>Agent 'writes the prose' (agents/00c_intelligent_context_extractor/agent.md:44; artifact spec :93-106) with no directive to keep it plain for onboarding readers. Related S.No 118, 120.</t>
+  </si>
+  <si>
+    <t>OPEN - NOT fixed this session (team scope = 06 only). Planned: add a plain-language-with-technical-nuance bar to the exec summary and module-doc prose.</t>
+  </si>
+  <si>
+    <t>124</t>
+  </si>
+  <si>
+    <t>Architecture agent (04) authors ADR Rationale/Context/Consequences prose and the architecture Executive Summary as human-read decision records, but only the Level-1 context diagram carries a 'readable by a non-technical stakeholder' bar - the ADR narrative and exec summary do not. Same defect class as S.No 118. HUMANIZATION REGISTER = PLAIN LANGUAGE retaining technical nuance.</t>
+  </si>
+  <si>
+    <t>Agents / 04 Architecture / content humanization</t>
+  </si>
+  <si>
+    <t>Context diagram must be 'readable by a non-technical stakeholder' (agents/04_architecture/agent.md:119) but ADR rationale (:373) and exec summary (:291) have no plain-language bar. Related S.No 118, 120.</t>
+  </si>
+  <si>
+    <t>OPEN - NOT fixed this session (team scope = 06 only). Planned: extend the existing non-technical-readability bar to ADR narrative fields and the exec summary.</t>
+  </si>
+  <si>
+    <t>125</t>
+  </si>
+  <si>
+    <t>PRD agent (03) is mostly well-humanized, but the per-feature ACCEPTANCE CRITERIA remain terse placeholders - the same artifact type flagged in S.No 118. HUMANIZATION REGISTER = PLAIN LANGUAGE retaining technical nuance.</t>
+  </si>
+  <si>
+    <t>Investigation edge-case sweep. Partially self-mitigated (strong readability directives elsewhere).</t>
+  </si>
+  <si>
+    <t>Agents / 03 PRD / content humanization</t>
+  </si>
+  <si>
+    <t>Strong readability directives overall (agents/03_prd/agent.md:15,76,354) but per-feature acceptance criteria are terse placeholders (:224-227). Related S.No 118, 120.</t>
+  </si>
+  <si>
+    <t>OPEN - NOT fixed this session (team scope = 06 only). Planned: apply the same detailed, plain-language-with-nuance bar to per-feature acceptance criteria.</t>
+  </si>
+  <si>
+    <t>126</t>
+  </si>
+  <si>
+    <t>Security agent (10) authors the Executive Summary and finding Impact statements that reach stakeholders with no plain-language bar. Same defect class as S.No 118. HUMANIZATION REGISTER = HUMANIZED-TECHNICAL for findings (security engineers must read the technical detail correctly); the stakeholder exec summary may be plain-language-with-nuance.</t>
+  </si>
+  <si>
+    <t>Investigation edge-case sweep. Primary audience is technical; remediation guidance is already appropriately specific.</t>
+  </si>
+  <si>
+    <t>Agents / 10 Security / content humanization</t>
+  </si>
+  <si>
+    <t>Exec summary and finding Impact (agents/10_security/agent.md:339-340,395-398) reach stakeholders without a readability bar. Related S.No 118, 120.</t>
+  </si>
+  <si>
+    <t>OPEN - NOT fixed this session (team scope = 06 only). Planned: humanized-technical clarity bar on findings; plain-language-with-nuance on the stakeholder exec summary.</t>
+  </si>
+  <si>
+    <t>Merging an approved build fails with HTTP 405 because the pull request is still a draft (the final blocker)</t>
+  </si>
+  <si>
+    <t>After a human approves the merge gate, the platform tries to merge the build's PR but GitHub rejects it, so the work item never reaches 'done'.</t>
+  </si>
+  <si>
+    <t>Build pipeline / Merge gate</t>
+  </si>
+  <si>
+    <t>1258d85</t>
+  </si>
+  <si>
+    <t>During the automated 07&lt;-&gt;08 review-and-fix loop the platform opens the build's pull request as a GitHub 'draft' PR (a draft blocks a premature human merge while review is still running). GitHub does not allow a draft PR to be merged - its merge API returns HTTP 405 (Method Not Allowed). So the moment a human approved the merge gate, the final merge step always failed. The work item got stuck at the very last step, never transitioned to done, and nothing downstream could complete. This was the single blocker stopping any build from finishing.</t>
+  </si>
+  <si>
+    <t>FIXED (commit 1258d85). Added a mark_ready_for_review step that takes the PR out of draft immediately before merging, which is the one legitimate moment to un-draft (gate already approved). merge_build_pr_core now does: get the PR; if it is not already merged and is still a draft, call codehost.mark_ready_for_review(pr_ref) which runs GitHub's markPullRequestReadyForReview GraphQL mutation and re-checks (short retries) that it un-drafted, then merge. Supporting additions: a graphql() helper (integrations/github/rest.py), a graphql_url property (config.py), and the CodeHost.mark_ready_for_review capability (capabilities.py + github/codehost.py). Regression test added in test_build_activities.py (draft PR is un-drafted before merge).</t>
+  </si>
+  <si>
+    <t>Reviewer gets 'no opened PR to review' during the fix-and-re-review loop (wrong code pointer picked)</t>
+  </si>
+  <si>
+    <t>During remediation the platform sometimes points the reviewer at an empty pre-PR placeholder instead of the real pull request.</t>
+  </si>
+  <si>
+    <t>Build pipeline / Review loop</t>
+  </si>
+  <si>
+    <t>The helper that looks up a build's code artifact (_code_artifact) fetched 'the first matching artifact' with no defined ordering. A single work item can have more than one code-artifact row: an early placeholder the agent registers before the PR exists, and the real one that carries the pull-request reference (repo/number/url). With no ORDER BY, the database returned rows in an arbitrary order, so the code sometimes picked the early placeholder that has no PR link. The reviewer then had nothing to look at and reported 'no opened PR to review', which broke the remediation cycle.</t>
+  </si>
+  <si>
+    <t>FIXED (commit 1258d85). _code_artifact now orders artifacts by created_at and explicitly prefers the one whose external_ref is a real PR reference: it returns the first PR-ref-bearing artifact and only falls back to the earliest row if none carries a PR ref. Regression test added in test_build_activities.py (duplicate-code-artifact prefers the PR-ref pointer).</t>
+  </si>
+  <si>
+    <t>A genuinely 'Approved' code review is wrongly blocked by the fail-closed review guard (false positive on a resolved finding ID)</t>
+  </si>
+  <si>
+    <t>The safety guard that blocks bad code mis-reads an approved review and rejects it, stalling the pipeline for no real reason.</t>
+  </si>
+  <si>
+    <t>Build pipeline / Review guard (S.No 114 guard)</t>
+  </si>
+  <si>
+    <t>a2deeae</t>
+  </si>
+  <si>
+    <t>The review guard is deliberately 'fail-closed': if a review's prose looks like it demands changes but the structured verdict does not clearly say so, it blocks - to stop bad code slipping through. The old prose matcher (_looks_blocking) scanned the entire review text for blocking-sounding words. An APPROVED review referenced an already-RESOLVED finding by its ID (for example 'REM-W1'), and the matcher saw that mention and concluded the review was demanding changes. Result: a legitimately approved review was blocked and the build could not proceed - a false positive that halted good work.</t>
+  </si>
+  <si>
+    <t>FIXED (commit a2deeae). Rewrote parse_and_guard to trust a present, structured APPROVED verdict. Added _verdict_demands_changes(): a verdict is treated as demanding changes only when a verdict is actually present AND its status matches a negative pattern (change/reject/denied/blocked/fail, via _NEGATIVE_STATUS regex). The loose prose scan is now only a fallback used when there is NO structured verdict at all. Net effect: an approved verdict is honoured even if its prose happens to mention resolved finding IDs, while a review that truly downgrades still fails closed. Regression tests added in test_review_dispatch.py (trusts approved verdict with resolved REM ids; in-JSON downgrade still fails closed).</t>
+  </si>
+  <si>
+    <t>When the secret scanner blocks a push, the failure is invisible - only a bare count is shown, not what/where</t>
+  </si>
+  <si>
+    <t>A blocked hardcoded secret produces a silent 'build failed' with just a number; nobody can tell which secret, file or line.</t>
+  </si>
+  <si>
+    <t>Companion / Pre-push secret scan</t>
+  </si>
+  <si>
+    <t>52533c4</t>
+  </si>
+  <si>
+    <t>Before pushing code the companion (the worker on the developer machine) scans the changed files for hardcoded secrets (passwords, API keys, tokens, private keys). When it finds one it correctly blocks the push and reports the build as failed - but it only reported a bare count ('N finding(s)'). It did not surface which secret type, which file, or which line, and it then tore down the temporary work folder, so the evidence was gone. Operators saw 'build failed' with no way to know why or how to fix it, making the block undiagnosable.</t>
+  </si>
+  <si>
+    <t>FIXED (commit 52533c4). The companion now prints a redacted summary to its own terminal ('[companion] SECRET SCAN BLOCKED push (N finding(s)) - branch NOT pushed') listing each finding as '[kind] path:line - preview', and the same redacted detail travels in the build.failed reason so it also appears in the platform run console. Only the already-redacted preview is shown - never the raw secret value - and the list is capped at 8 findings with a '(+N more)' tail so the message stays bounded. Added the _format_secret_findings helper (runner/companion/runner.py) and regression tests in test_companion_runner.py (redacted findings surface; cap at 8).</t>
+  </si>
+  <si>
+    <t>The code-review result (code_review artifact) cannot be opened or read from the web UI</t>
+  </si>
+  <si>
+    <t>The 08 review report is produced and registered but there is no view/link in the product to read it.</t>
+  </si>
+  <si>
+    <t>UI / Review experience</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>The 08 review agent produces a code_review artifact holding the review findings and verdict, and the platform registers it as an artifact (pointer + provenance). However the web interface offers no view or link that opens the artifact body, so a human reviewer or manager cannot actually read the review inside the product - they would have to query the database or dig through logs. This undermines the human review gate: the gate exists but the evidence behind it is not surfaced to the person approving.</t>
+  </si>
+  <si>
+    <t>Verified already fixed — no code change needed. Cross-checked against a live run: the code_review artifact IS registered with a rendered report body (the companion uploads the .md to S3 — confirmed a ~22 KB report object exists for the latest run), and the generic artifact preview reads it, so the report opens and reads in the UI. The earlier 'no body' analysis looked only at the platform-side fallback registration and missed the companion upload. Closed as verified.</t>
+  </si>
+  <si>
+    <t>The 'sdlc/build' commit status is set to 'pending' when the PR opens and is never updated - it stays pending forever (latent)</t>
+  </si>
+  <si>
+    <t>A dormant flaw: the build commit status posted to GitHub is never moved off 'pending', which will block merges if branch protection ever requires it.</t>
+  </si>
+  <si>
+    <t>Build pipeline / Commit status reporting</t>
+  </si>
+  <si>
+    <t>build_activities.py:140</t>
+  </si>
+  <si>
+    <t>When the build PR is opened, the platform posts a GitHub commit status with context 'sdlc/build' and state 'pending' against the head commit (build_activities.py line 140, best-effort - exceptions are swallowed). Nothing anywhere later updates that status to 'success' or 'failure'. So every build's commit shows the 'sdlc/build' check stuck on pending indefinitely. It is dormant today only because no branch-protection rule on the repo currently requires the 'sdlc/build' context to be green before merging. The day someone enables such a required check, merges will be blocked forever because the status can never reach success - a latent time-bomb, and misleading status UI in the meantime.</t>
+  </si>
+  <si>
+    <t>OPEN - not fixed this session. Recommended fix: complete the status lifecycle. Set 'sdlc/build' to 'success' once the build+review pass (or at merge), and to 'failure' on the mark_build_failed / secret-block / merge-failed paths, using the same head SHA. Keep it best-effort (do not fail the saga on a status-post error), but ensure a terminal state is always posted so the check does not dangle. Acceptance: after a run reaches a terminal outcome, the commit's 'sdlc/build' status reflects success or failure, never a permanent pending.</t>
+  </si>
+  <si>
+    <t>The companion crashes hard (fatal, exit 1) when the build agent errors, instead of failing gracefully and reporting back</t>
+  </si>
+  <si>
+    <t>If the AI build agent fails, the whole companion worker dies and needs a manual restart, stalling the build.</t>
+  </si>
+  <si>
+    <t>Companion / Build execution resilience</t>
+  </si>
+  <si>
+    <t>When the build agent (the Claude Agent SDK run inside the companion) exits with an error, the exception propagates all the way up and the companion process terminates fatally (Command failed / exit code 1). Because the companion runs one build at a time and is a long-lived poller, a single agent error takes the whole worker down: it stops polling, the current run is left dangling (claimed but not reported), and a human has to notice and restart the companion before any further work can proceed. Observed repeatedly this session (e.g. when a mid-build backend restart broke the agent's MCP calls, and when an environment/dependency mismatch made the agent exit).</t>
+  </si>
+  <si>
+    <t>Fixed (2026-07-16). runner/companion/daemon.py _run_build now catches a generic build-agent error, posts a failed BuildReport (status=failed + message) to /api/runner/builds/&lt;run&gt;/report/, and keeps polling (mirrors the plan/review path _run_engine_phase) instead of the exception propagating out of serve and killing the long-lived companion. EngineAuthError still fail-closes (explicit re-raise) so a subscription/auth halt is never downgraded to a per-build failure. Tests: test_companion_daemon (agent-error reported + no crash; auth-error still halts).</t>
+  </si>
+  <si>
+    <t>A worker can deadlock a job by self-renewing its own claim while making no progress (stuck job never released)</t>
+  </si>
+  <si>
+    <t>A worker keeps renewing its hold (heartbeat) on a job it isn't actually advancing, so the job sits claimed forever and nothing else can take it.</t>
+  </si>
+  <si>
+    <t>Build pipeline / Claim + heartbeat (S.No 111)</t>
+  </si>
+  <si>
+    <t>Jobs are handed to a worker via a claim, and a heartbeat (S.No 111) periodically renews that claim so the platform knows the worker is alive. The problem: the heartbeat renews the claim based on the worker still running, not on the work actually progressing. If the worker gets wedged (e.g. the agent hangs, or a step is stuck) but the heartbeat thread keeps ticking, the claim is renewed indefinitely. The job stays 'claimed', the report-timeout takeover cannot fire (the claim looks fresh), and no other worker can pick it up - a silent deadlock that only a human notices. Seen this session as the 'companion claimed but never built' deadlock.</t>
+  </si>
+  <si>
+    <t>Fixed (2026-07-16). Cross-verified first: _renew_claims_for renewed the claim on process liveness alone (no progress signal, no cap), so a wedged-but-heartbeating worker held its claim until only the 2h workflow report-timeout (S.No 89) freed it. Fix: backend/api/runner_views.py stamps first_claimed_at at each claim (reset per claim, never touched by heartbeat) and MAX_CLAIM_AGE=60min caps renewal - past it the heartbeat stops renewing so the lease ages out and the run is recoverable well before the 2h backstop. Cap set above the longest legit build (&lt;60min, team-confirmed) so a healthy long build is never capped (no S.No 111 regression). Note: a companion progress-signal is the fundamentally optimal fix (distinguishes wedged-vs-working at any duration) - logged as the future upgrade if builds ever exceed ~1h. Tests: test_phase_dispatch (cap stops renewal; young claim still renews).</t>
+  </si>
+  <si>
+    <t>Dependency version skew: pinned claude-agent-sdk / anyio in the repo are behind what the runtime actually needs</t>
+  </si>
+  <si>
+    <t>The project's pinned library versions lag what the running machine requires; fixed by hand on the machine but not locked in the repo, so it will break for the next person.</t>
+  </si>
+  <si>
+    <t>Companion / Dependency management</t>
+  </si>
+  <si>
+    <t>The companion depends on claude-agent-sdk, which in turn requires a newer anyio (the anyio.open_process 'user' keyword arrives in anyio 4.5.0; claude-agent-sdk 0.1.72 needs it). The repo's pins were stale (an old claude-agent-sdk pin and no floor on anyio), so a fresh environment installed anyio 4.4.0 and the agent crashed with "anyio.open_process() got an unexpected keyword argument 'user'". This session it was worked around by manually upgrading anyio on the host (pip install -U 'anyio&gt;=4.5' -&gt; 4.14.2), but that fix lives only on this machine - the repo still pins the broken combination, so the next developer or a rebuilt container will hit the same crash.</t>
+  </si>
+  <si>
+    <t>OPEN - not fixed this session (env-patched only). Recommended fix: pin the correct, mutually compatible versions in the repo lockfile/requirements - bump claude-agent-sdk to the version actually in use and add an explicit anyio&gt;=4.5 floor - then rebuild the companion/worker images from the lockfile so a clean install reproduces the working environment. Acceptance: a from-scratch install (no manual pip upgrades) runs a build without the open_process 'user' error.</t>
+  </si>
+  <si>
+    <t>Build branches are merged without first being updated against their base, causing merge conflicts at the gate</t>
+  </si>
+  <si>
+    <t>The platform merges a feature branch without rebasing/updating it against the current base, so it hits conflicts (mergeable_state=dirty) and the merge fails.</t>
+  </si>
+  <si>
+    <t>When the merge gate is approved, the platform merges the feature branch as-is. It never updates the branch against the latest base first. If the base has moved on since the branch was cut - which is normal in a multi-developer repo - the PR can be in a conflicted state (GitHub mergeable_state = 'dirty'), and the merge API then returns HTTP 405 just like the draft case. This session WI-29 hit exactly this: an add/add conflict on frontend/.env.example left the PR dirty and the merge failed; it had to be resolved by hand. The pipeline has no step to bring a branch up to date with its base before attempting the merge.</t>
+  </si>
+  <si>
+    <t>Fixed (2026-07-16). The merge gate merged the feature branch as-is, so a base that moved since the branch was cut left the PR mergeable_state=dirty and the GitHub merge API returned a raw 405. Fix: integrations/types.py PullRequest gains mergeable/mergeable_state; github/codehost.py adds update_branch (GitHub Update-branch; swallow 422 already-up-to-date) + ensure_mergeable (bounded re-read for GitHub's async mergeability); build_activities.py merge_build_pr_core now, before merging: if 'behind' -&gt; update branch against base then re-check; if 'dirty'/not mergeable -&gt; fail fast (non-retryable ApplicationError) with a clear 'merge conflict - needs manual resolution' reason instead of a cryptic 405; merges only when mergeable. Idempotent behind the existing 'if not pr.merged' guard. Tests: test_build_activities (behind-&gt;update-&gt;merge; dirty-&gt;clean fail, never merged). Reason surfacing verified in live test: the classified reason reaches the user via the S.No 139 ActivityError-cause unwrap (build_workflow uses build_types.failure_reason), since str(ActivityError) is the opaque "Activity task failed".</t>
+  </si>
+  <si>
+    <t>Planning overlap: two separate work items are both told to create the same file (frontend/.env.example), guaranteeing a conflict</t>
+  </si>
+  <si>
+    <t>TASK-003 and TASK-005 each create frontend/.env.example, so when both build they collide - a work-breakdown/planning defect.</t>
+  </si>
+  <si>
+    <t>Planning / Work-item decomposition</t>
+  </si>
+  <si>
+    <t>Two independently-dispatched work items (TASK-003 and TASK-005) were each planned to create the same file, frontend/.env.example. When both branches are built and then merged, they produce an add/add conflict on that file - there is no shared ownership or de-duplication in the planning step. This is the upstream cause of the WI-29 merge conflict (S.No 136): the pipeline had no branch-update step to catch it, but the conflict should not have been planned in the first place. It points to a gap in how the planner assigns file ownership across parallel work items.</t>
+  </si>
+  <si>
+    <t>Not reproducible / not a bug — verified against stored work-item data. TASK-003 creates the FRONTEND .env.example (frontend repo); TASK-005 is a backend SQLAlchemy/Alembic task (backend repo) — different files, different repos, no collision. The likely confusion: TASK-002 (backend .env.example) and TASK-003 (frontend .env.example) are two correctly-separate files that merely share a name. Closed.</t>
+  </si>
+  <si>
+    <t>Two developers share a single enrollment record, risking incorrect work attribution and tenant isolation</t>
+  </si>
+  <si>
+    <t>Two devs point at the same enrollment identity (32db7f5f), so runs/work may be attributed or isolated to the wrong person.</t>
+  </si>
+  <si>
+    <t>Tenancy / Enrollment identity</t>
+  </si>
+  <si>
+    <t>enrollment 32db7f5f</t>
+  </si>
+  <si>
+    <t>During testing it was found that two different developers are operating under the same enrollment record (enrollment id 32db7f5f, under tenant 212395b8). Enrollment is meant to identify a single developer's participation in a project; sharing one record between two people means their runs, claims and attribution can be conflated, and any per-developer isolation or accounting keyed on enrollment is wrong. It also muddies debugging (whose companion claimed what) and could let one developer's actions appear under the other's identity.</t>
+  </si>
+  <si>
+    <t>OPEN - not fixed this session (flagged during testing). Recommended fix: give each developer their own enrollment record under the tenant/project, and ensure the companion is launched with the correct per-developer enrollment/credentials so claims and events attribute to the right person. Audit existing runs that used the shared enrollment. Acceptance: each developer has a distinct enrollment and their runs attribute correctly.</t>
+  </si>
+  <si>
+    <t>Build failures don't explain why - most failures show a generic 'build failed' or a raw, cryptic error instead of a clear reason</t>
+  </si>
+  <si>
+    <t>When a build fails for reasons other than a blocked secret (token/permission error, merge conflict, agent error, empty build), the platform shows 'build failed' or a raw exception string, not a plain classified reason.</t>
+  </si>
+  <si>
+    <t>Build pipeline / Failure observability</t>
+  </si>
+  <si>
+    <t>The build.failed reason is populated inconsistently across the different failure paths (build_workflow.py). A companion report failure falls back to the generic literal 'build reported failed' when no message is set. Remediation-exhausted is the hardcoded 'remediation cycles exhausted'. The PR/gate-setup and merge paths embed a raw Python/Temporal exception string ('pr/gate setup failed: {exc}', 'merge failed: {exc}') - so a token-permission (403) error or a merge conflict (405) is technically present but buried in a cryptic stack string, not classified as 'token permission issue' or 'merge conflict'. Only the secret-scan case (S.No 130) was made human-readable. Net effect: for most failure kinds an operator sees 'build failed' with no actionable reason and must dig through logs to triage.</t>
+  </si>
+  <si>
+    <t>Fixed (2026-07-16). build.failed reasons were inconsistent (bare 'build reported failed', hardcoded 'remediation cycles exhausted', raw exception strings 'merge failed: {exc}') AND - a hidden gap - the EventSerializer never surfaced the 'reason' payload key, so the run console showed only 'Build failed'. Fix: build_activities.py classify_build_failure maps every failure path to a plain-language classified reason (merge conflict / permission-403 / remediation exhausted / empty build / agent error; the good S.No 130 secret-scan message passes through); mark_build_failed_core writes it to run.outputs.error (where the run console reads the failure line) and the build.failed event; api/serializers.py adds 'reason' to the event message keys. Composes with S.No 136 (single canonical 'merge conflict' reason). Tests: test_build_activities (classifier mappings; reason on run.outputs.error). CORRECTION (same session, caught by live test): the workflow now UNWRAPS the ActivityError .cause via build_types.failure_reason so the classifier sees the real message (Temporal str(ActivityError)="Activity task failed" otherwise hides the 405/422/conflict); AND open_build_pr_core fails an EMPTY build fast (non-retryable ApplicationError "empty build: no changes") instead of a cryptic 422 after 3 retries - an empty build still FAILS (clear reason), it does not auto-succeed. Tests: failure_reason unwrap + empty-build fast-fail + classifier mappings.</t>
+  </si>
+  <si>
+    <t>No human action to resolve a non-mergeable / redundant / failed WorkItem: a task can only reach 'done' via a successful automated build+merge. A build that fails (empty/redundant build, or a merge conflict needing manual resolution) leaves the WorkItem stuck at in_progress with no product path for a human to mark it done, skip it, or close it as redundant.</t>
+  </si>
+  <si>
+    <t>Surfaced 2026-07-16 while testing S.No 136/139: TASK-002 (redundant with TASK-001) produced an empty build that correctly FAILED with 'Empty build: no changes to commit'. The WorkItem then sits at in_progress with the branch/draft PR left in place, and the only offered action is Retry - which re-fails for a genuinely redundant task. A human can freely trigger the NEXT task (tasks are independent unless depends_on) but cannot close/resolve the failed one. Today the only ways to reach done are the happy-path orchestrator flow or an admin DB state change.</t>
+  </si>
+  <si>
+    <t>Work Items / Build recovery UX</t>
+  </si>
+  <si>
+    <t>backend/apps/workitems/models.py (State: proposed/accepted/in_progress/in_review/blocked/done, no transition validation); backend/api/serializers.py WorkItemPatchSerializer (state NOT writable) + read_only state; backend/api/views.py WorkItemViewSet (trigger/build/take-over/lifecycle - no transition/mark-done action); mcp_platform_state/tools.py transition_work_item (any-&gt;any, internal only); frontend RunConsole.tsx (Retry only) / WorkItemTask.tsx (done is display-only) / OfflineTakeover.tsx</t>
+  </si>
+  <si>
+    <t>WorkItem.state is read-only on the API (excluded from WorkItemPatchSerializer; read_only on the read serializer) and mutated ONLY internally by the orchestrator (successful build+merge / gate / reject / takeover). No human-facing transition/mark-done/close/skip action or endpoint exists; the frontend offers only Retry / Trigger phase / manual takeover (sets takeover_flag, not state). transition_work_item allows any-&gt;any but is unexposed to users.</t>
+  </si>
+  <si>
+    <t>OPEN - proposed: add a GATED human action + API endpoint to move a WorkItem to a terminal state outside the happy path (e.g. 'Mark done', 'Close as redundant / won't-do', or 'Skip'), surfaced on the Work Items board + task page, with an audit Event. Decide whether to reuse 'done' or add a distinct terminal state (e.g. 'closed'/'cancelled') to distinguish completed-by-build from human-closed; guard with role/permission. Related S.No 76 (no task-edit UI; state not editable).</t>
+  </si>
+  <si>
+    <t>Merge gate can't recover from a conflict without redoing the whole build. TWO related enhancements (logged together): (ENH-2, IMPLEMENT NOW) Merge-only retry / re-openable merge gate - when a merge hits a conflict, PAUSE at the merge step and let the user retry the merge after fixing the conflict, WITHOUT re-running the whole build. (ENH-1, FUTURE / only if needed) Reconcile the Run status on an EXTERNAL merge - when a user merges the PR by hand in GitHub, also flip the Run from failed to done (today the webhook updates the WorkItem + artifact but leaves the Run 'failed').</t>
+  </si>
+  <si>
+    <t>Today a merge conflict marks the ENTIRE build failed and ends the workflow, so finishing means re-running everything (AI re-writes the code, re-reviews, re-opens the PR) just to retry one merge. ENH-2 fixes this: keep the build paused at the merge gate; after the user resolves the conflict in GitHub they press Merge/Approve again and the platform completes the merge through its OWN flow (run + gate + work-item all stay correct automatically, no rebuild). ENH-1 covers a DIFFERENT path - the user merges by hand in GitHub instead of letting the platform do it; then the platform only learns via webhook (S.No 88) and today leaves the Run status stale. TEAM PLAN (2026-07-16): implement ENH-2 now; keep ENH-1 for future - it overlaps S.No 88 and is only needed if users merge OUTSIDE the platform. If ENH-2 is used, ENH-1 is largely unnecessary. Same 'soft, reconcilable' idea as the S.No 89 fix, applied to merge conflicts.</t>
+  </si>
+  <si>
+    <t>Build pipeline / Merge gate recovery</t>
+  </si>
+  <si>
+    <t>backend/orchestration/build_workflow.py (merge gate + ActivityError-&gt;mark_build_failed is TERMINAL on a conflict); backend/orchestration/build_activities.py merge_build_pr_core (S.No 136 dirty-&gt;fail); backend/integrations/webhooks.py _reconcile_pull_request (updates WorkItem+artifact on an external merge, NOT the Run); frontend Gates.tsx (merge gate) + RunConsole.tsx. Related: S.No 88 (external merge / missing webhook), S.No 89 (soft-reconcilable pattern), S.No 136 (conflict detection).</t>
+  </si>
+  <si>
+    <t>On a merge conflict the BuildWorkflow catches the ActivityError and calls mark_build_failed, which is TERMINAL - the workflow ends, so there is no live workflow to retry the merge and the merge-gate Approval is already spent. The only ways forward today are a full re-trigger (rebuilds from 07) or an external GitHub merge (needs the S.No 88 webhook, which also does not reconcile the Run status).</t>
+  </si>
+  <si>
+    <t>ENH-2 IMPLEMENTED &amp; VALIDATED LIVE (@ 66b70c8, + gate banner). A merge conflict is now NON-terminal: merge_build_pr detects a dirty PR and raises a typed MergeConflict; the BuildWorkflow catches it, RE-OPENS the merge gate (resets the approval to pending, records outputs.merge_conflict + a build.merge_conflict event) and waits — instead of failing the build. The user resolves the conflict in GitHub and approves again; the platform retries ONLY the merge (no rebuild, no re-review). Proven live on TASK-003 (run 1d1dd943): injected an add/add conflict on .env.example -&gt; approve -&gt; gate re-opened (once per remaining conflict) -&gt; resolved -&gt; approve -&gt; platform merged PR#1 (merge commit c1d7552a) -&gt; WorkItem done -&gt; run completed, with NO rebuild across retries. The merge gate now shows a warning banner explaining the conflict + retry (ApprovalSerializer.merge_conflict; shown ONLY on a re-opened merge gate, never other gates). ENH-1 (reconcile Run status on an EXTERNAL GitHub merge) remains FUTURE / optional — it overlaps S.No 88 and is only needed if users merge outside the platform, which ENH-2 makes largely unnecessary.</t>
+  </si>
+  <si>
+    <t>Backlog push to Jira: tasks never reach Jira — each Task is created with its Story as parent, which Jira rejects</t>
+  </si>
+  <si>
+    <t>During a live Jira push of the SpendLog-1 backlog, all 5 epics + 15 stories were created but 0 of 29 tasks landed. reconcile creates each task with parent = its story's Jira key; Jira rejects a standard Task parented to a Story (400 'Please select valid parent issue') — only Sub-tasks can live under a Story (Jira hierarchy: Epic &gt; Story/Task, and Epic &gt; Story &gt; Sub-task).</t>
+  </si>
+  <si>
+    <t>reconcile.reconcile_work_item mapped WorkItem.type 'task' -&gt; Jira 'Task' and set parent={key: story}. Jira does not allow a standard Task under a Story. Stories succeeded because Story-under-Epic via the parent field IS valid; tasks-under-stories are not.</t>
+  </si>
+  <si>
+    <t>TWO layered causes, both fixed. (1) REAL ROOT CAUSE: reconcile's idempotency guard 'if wi.external_ref' wrongly treated a repo-assigned task as already-reconciled. Multi-repo tasks carry external_ref.repo_assignment (the planner's repo pick, Option C) with NO SoR id, so on the live push every task was SKIPPED before reaching Jira (export showed created:0, reconciled:29, no error — not a Jira rejection at all). Fixed: the guard now checks for a real SoR key (external_ref.id), and the SoR ref is MERGED into external_ref so the repo_assignment is preserved. (2) HIERARCHY (latent, also fixed): once tasks reach Jira, a standard Task can't be a child of a Story, so a task with a reconciled story parent is created as a SUB-TASK under it (the project's real sub-task issue-type name, resolved via AtlassianTaskTracker.subtask_type_name() + cached), and a parentless task as a top-level Task. Validated live (Sub-task-under-Story create succeeds; Task-under-Story returns 400). Tests in test_reconcile: repo-assigned task not-skipped + repo_assignment preserved, subtask mapping, parentless task, per-item failure capture. NOTE: my first commit fixed only the hierarchy; the guard/repo_assignment fix (the true blocker) landed in the follow-up commit after the re-push showed created:0.</t>
+  </si>
+  <si>
+    <t>Backlog publish reports a green 'Published' while items silently fail to reach the system of record</t>
+  </si>
+  <si>
+    <t>The same Jira push showed 'Published — 49 work items reconciled (20 created)' even though 29 tasks failed. reconcile_backlog ran each item with no per-item error handling and the publish response/dialog surfaced only reconciled/created — so partial failures were invisible and the reconciled count over-reported what actually landed.</t>
+  </si>
+  <si>
+    <t>Integrations / Publish</t>
+  </si>
+  <si>
+    <t>reconcile_backlog processed items in a list comprehension with no try/except, and _publish_tasktracker + the ExportPublish dialog reported only reconciled/created counts — never failures. A partial push read as a full success.</t>
+  </si>
+  <si>
+    <t>reconcile_backlog now isolates each item in try/except: a single item's SoR rejection is recorded (logged as a workitem.reconcile_failed event + returned in a 'failed' list) and the run continues, instead of aborting or being swallowed. The publish API returns status 'partial' plus the failed items; the artifact stores a failed count; the ExportPublish dialog now shows 'Published with some failures — N created, M failed' + the first error, instead of an all-green success. Test added in test_reconcile (per-item failure captured; epic/story still land).</t>
+  </si>
+  <si>
+    <t>Secret scanner false-positives on hyphenated placeholders (e.g. change-me-...) in .env.example, blocking legitimate builds</t>
+  </si>
+  <si>
+    <t>The pre-push secret scan flagged an obvious placeholder value as a real secret, so the push was blocked and the build failed.</t>
+  </si>
+  <si>
+    <t>3c33554</t>
+  </si>
+  <si>
+    <t>The companion's pre-push secret scanner (runner/companion/guardrails.py) blocks a push when it finds anything that looks like a hardcoded secret. Its placeholder allow-list recognised the literal token 'changeme' but NOT the far more common hyphenated/underscored form 'change-me'. So a legitimate .env.example placeholder - JWT_SECRET=change-me-minimum-32-characters-long (36 chars, Shannon entropy 3.875) - was not recognised as a placeholder, tripped the generic high-entropy heuristic, and was flagged as a 'high_entropy_secret'. The push was blocked and the build failed. This is a FALSE POSITIVE: the value is an obvious placeholder, not a real secret. It blocked WI-32 and would block any task whose example env file uses the very common change-me convention. The build agent did nothing wrong - the scanner was too aggressive.</t>
+  </si>
+  <si>
+    <t>FIXED (commit 3c33554). Two changes in runner/companion/guardrails.py: (1) broadened the placeholder allow-list to cover change[-_ ]?me / replace[-_ ]?me / to-be-(changed|set|replaced|filled|generated) / secret-(here|goes) / dummy / sample / redacted, so hyphenated placeholders are recognised. (2) Committed template files (.env.example, *.sample, *.template, *.dist, *.tpl) now skip the generic entropy heuristic - placeholders are expected there - while STILL running the high-precision key-format patterns (AWS AKIA..., GitHub ghp_..., PEM private keys, JWT), so a real key shape pasted into an example file is still blocked. Regression tests in backend/tests/test_guardrails.py: the exact WI-32 value + change_me/replace-me variants pass clean; a real random token in real source still blocks; AWS/GitHub key shapes inside .env.example still block; non-template source keeps the full entropy scan. 12/12 scanner tests pass.</t>
+  </si>
+  <si>
+    <t>AI-engine build failures (usage/rate limit, agent CLI exit 1) show a raw, unreadable message instead of a clear reason</t>
+  </si>
+  <si>
+    <t>When the agent CLI fails (e.g. the Anthropic usage limit is reached) the run console shows 'Command failed with exit code 1 ... Check stderr output for details' - opaque and non-actionable.</t>
+  </si>
+  <si>
+    <t>Build pipeline / Failure observability + Companion</t>
+  </si>
+  <si>
+    <t>daemon.py:271</t>
+  </si>
+  <si>
+    <t>When the AI build agent fails to run - most commonly because the Anthropic usage/rate limit is reached, but also on any agent CLI non-zero exit - the companion's error handler (runner/companion/daemon.py ~line 271) captures only the engine driver's generic wrapper string and reports it verbatim: 'Command failed with exit code 1 (exit code: 1) / Error output: Check stderr output for details'. The platform's classify_build_failure (backend/orchestration/build_activities.py) does not recognise this signature, so the raw string passes straight through to the build.failed reason and the run console. The user sees an opaque error with no indication that the real cause was a usage limit and no guidance on what to do. This bit WI-32: the usage limit was hit during the cycle-2 remediation build and the console showed only 'Command failed with exit code 1'. Same defect class as S.No 139 (classified reasons) but for the engine/usage-limit failure path, which was not covered.</t>
+  </si>
+  <si>
+    <t>OPEN - Fix A planned this session (this row's owner). Two parts: (1) Companion (daemon.py): capture the agent process's stderr tail and put the actual cause in the report message instead of the placeholder 'Check stderr output for details'. (2) Platform (classify_build_failure): recognise engine / usage-limit / rate-limit signatures ('exit code 1', 'usage limit', 'rate limit', '429', 'overloaded', 'quota', 'Failed to start Claude Code') and map them to a plain-language reason, e.g. 'The AI engine hit its usage limit - the build stopped; retry when the limit resets.' NOTE: true resume-from-checkpoint on a transient failure (so a re-run continues from the last cycle instead of rebuilding) is tracked separately as S.No 147 and is owned by the other developer. Acceptance: a usage-limit failure shows a clear, non-technical reason naming the usage limit, not a raw exit-code string.</t>
+  </si>
+  <si>
+    <t>When the implementation of a Work Item is completed and give it away for the review agent - The review agent is doing its job and creating Remediation Work Items (if blocking or critical issues are present): The created Remediation Work Item Tasks are too technical and not humasined and high level</t>
+  </si>
+  <si>
+    <t>In Implementation Phase:
+1. The implementation agent should ask the user for any clarifications 
+2. The implementation agent should ask the user for edits: should the edits be manual edit or auto mode.
+Note: For this Enhancement of the agent, you must reason and discuss with the team and take their inputs and then proceed.</t>
+  </si>
+  <si>
+    <t>Build Phase</t>
+  </si>
+  <si>
+    <t>This is a recon and report back job:
+In the Bug fixing sesions of the SDLC APP the team conducted so far (Git History and This Bugs sheet is the core evidence): You Must recon each and every single fix that has been done so far which are directly or indirectly related to the Core - Agents - agent.md for all phases and report back based on the evidence - Do any of the agents need optimization?</t>
+  </si>
+  <si>
+    <t>SDLC Phases</t>
+  </si>
+  <si>
+    <t>Optimization/Enhancement</t>
+  </si>
+  <si>
+    <t>In Phases &amp; Runs Page:
+Currently all created Work Items are shown in a drop down but if the created work items count reaches huge number it would be difficult for the user to find his work item. Instead we will give him a search option in the drop down itself - this way he can search for his work item and use the drop down also.</t>
+  </si>
+  <si>
+    <t>In the Artifacts &amp; Traceability page:
+1. The artifacts names for Code review, PR - should have task title/name to identify easily instead of only WI-ID
+Note: See the reference image for clarity</t>
+  </si>
+  <si>
+    <t>When the user approved the gate for implementation pahse - The artifacts: Assumptions, Implementation task/WI are still in draft state not published.
+Note: See the reference image for clarity</t>
+  </si>
+  <si>
+    <t>The user should be able to edit the generated phase artifacts - Task Breakdown phase, requirements phase, PRD phase etc. Right now the edit artifacts capability is missing.</t>
+  </si>
+  <si>
+    <t>The team have observed that each phase execution (mainly the Build phases) of the SDLC app is taking too long to run. The team wants to know the exact reason behind this before brain storming how to optimize it better 
+Note: You must co-ordinate with the team about this</t>
+  </si>
+  <si>
+    <t>In the Integration Mechanism of the SDLC APP: Integrations are per tenant but the team strongly wants the integrations should be per projects not tenant.</t>
+  </si>
+  <si>
+    <t>In the integration page: 
+1. For any integration of a capability - Currently the user cannot edit the saved token but that should be possible
+2. THe user should test the integration connection first and then save the creds not the other way around.</t>
+  </si>
+  <si>
+    <t>In the SDLC APP Phases and Runs: After any phase (mainly Build Phase but applies to all phases) trigger is interrupted due to any error/issue, the user should be able to continue from that point rather than starting from beginning of that phase. 
+Note: This is a very user important fix - should be applied accurately.</t>
+  </si>
+  <si>
+    <t>Phases and Runs</t>
   </si>
 </sst>
 </file>
@@ -2872,7 +3373,7 @@
 </file>
 
 <file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
-<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="13">
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="16">
   <rv s="0">
     <v>0</v>
     <v>5</v>
@@ -2925,6 +3426,18 @@
     <v>12</v>
     <v>5</v>
   </rv>
+  <rv s="0">
+    <v>13</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>14</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>15</v>
+    <v>5</v>
+  </rv>
 </rvData>
 </file>
 
@@ -2952,6 +3465,9 @@
   <rel r:id="rId11"/>
   <rel r:id="rId12"/>
   <rel r:id="rId13"/>
+  <rel r:id="rId14"/>
+  <rel r:id="rId15"/>
+  <rel r:id="rId16"/>
 </richValueRels>
 </file>
 
@@ -4922,15 +5438,11 @@
       <c r="G61" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="I61" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Fixed on two fronts. (1) UI: the 'Other' free-text box no longer fails to appear when the agent labels an option with a letter prefix (e.g. 'd) Other') — the reveal now strips a leading enumerator before matching. Verified LIVE against the running app (served bundle). (2) Authoring: the ask_human tool contract now tells every phase agent to write ONE short plain-language question and put choices ONLY in the structured options, never inline them in the question text — stopping the duplicated-options / uppercase wall-of-text. Frontend + agent-contract change; regression test added.</t>
-        </is>
-      </c>
-      <c r="J61" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Fixed</t>
-        </is>
+      <c r="I61" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="J61" s="2" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="62" spans="1:10" ht="409.6">
@@ -4938,10 +5450,10 @@
         <v>61</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E62" s="2" t="s">
         <v>12</v>
@@ -4953,10 +5465,10 @@
         <v>13</v>
       </c>
       <c r="H62" s="2" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="I62" s="2" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="J62" s="2" t="s">
         <v>16</v>
@@ -4967,28 +5479,28 @@
         <v>62</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="G63" s="2" t="s">
         <v>13</v>
       </c>
       <c r="H63" s="2" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="I63" s="2" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="J63" s="2" t="s">
         <v>16</v>
@@ -4999,28 +5511,28 @@
         <v>63</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="E64" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="G64" s="2" t="s">
         <v>36</v>
       </c>
       <c r="H64" s="2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="I64" s="2" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="J64" s="2" t="s">
         <v>16</v>
@@ -5031,28 +5543,28 @@
         <v>64</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="E65" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="G65" s="2" t="s">
         <v>13</v>
       </c>
       <c r="H65" s="2" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="I65" s="2" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="J65" s="2" t="s">
         <v>16</v>
@@ -5063,28 +5575,28 @@
         <v>65</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="E66" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="G66" s="2" t="s">
         <v>13</v>
       </c>
       <c r="H66" s="2" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="I66" s="2" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="J66" s="2" t="s">
         <v>16</v>
@@ -5095,28 +5607,28 @@
         <v>66</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E67" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="G67" s="2" t="s">
         <v>13</v>
       </c>
       <c r="H67" s="2" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="I67" s="2" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="J67" s="2" t="s">
         <v>16</v>
@@ -5127,28 +5639,28 @@
         <v>67</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="E68" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="G68" s="2" t="s">
         <v>13</v>
       </c>
       <c r="H68" s="2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="I68" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="J68" s="2" t="s">
         <v>16</v>
@@ -5159,28 +5671,28 @@
         <v>68</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="E69" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="G69" s="2" t="s">
         <v>13</v>
       </c>
       <c r="H69" s="2" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="I69" s="2" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="J69" s="2" t="s">
         <v>16</v>
@@ -5191,28 +5703,28 @@
         <v>69</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="E70" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="G70" s="2" t="s">
         <v>13</v>
       </c>
       <c r="H70" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="I70" s="2" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="J70" s="2" t="s">
         <v>16</v>
@@ -5223,28 +5735,28 @@
         <v>70</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="E71" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="G71" s="2" t="s">
         <v>13</v>
       </c>
       <c r="H71" s="2" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="I71" s="2" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="J71" s="2" t="s">
         <v>16</v>
@@ -5255,28 +5767,28 @@
         <v>71</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="E72" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="G72" s="2" t="s">
         <v>13</v>
       </c>
       <c r="H72" s="2" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="I72" s="2" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="J72" s="2" t="s">
         <v>16</v>
@@ -5287,28 +5799,28 @@
         <v>72</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="E73" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="G73" s="2" t="s">
         <v>13</v>
       </c>
       <c r="H73" s="2" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="I73" s="2" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="J73" s="2" t="s">
         <v>16</v>
@@ -5319,28 +5831,28 @@
         <v>73</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="E74" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="G74" s="2" t="s">
         <v>13</v>
       </c>
       <c r="H74" s="2" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="I74" s="2" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="J74" s="2" t="s">
         <v>16</v>
@@ -5351,35 +5863,31 @@
         <v>74</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="E75" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="G75" s="2" t="s">
         <v>36</v>
       </c>
       <c r="H75" s="2" t="s">
-        <v>306</v>
-      </c>
-      <c r="I75" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Per-tenant credentials are now actually used at runtime. Figma, Xray and Atlassian (Confluence/Jira) resolve credentials from the tenant's own IntegrationConnection (decrypt_secrets) instead of the shared server .env — closing the multi-tenant credential-leak class already fixed for GitHub (S.No 112). Per-field .env fallback kept so CI/tests are unchanged. Done together with S.No 113. Config tests added.</t>
-        </is>
-      </c>
-      <c r="J75" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Fixed</t>
-        </is>
+        <v>307</v>
+      </c>
+      <c r="I75" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="J75" s="2" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="76" spans="1:10" ht="409.6">
@@ -5387,28 +5895,28 @@
         <v>75</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="E76" s="2" t="s">
         <v>22</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="G76" s="2" t="s">
         <v>36</v>
       </c>
       <c r="H76" s="2" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="I76" s="2" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="J76" s="2" t="s">
         <v>141</v>
@@ -5419,28 +5927,28 @@
         <v>76</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="E77" s="2" t="s">
         <v>22</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="G77" s="2" t="s">
         <v>23</v>
       </c>
       <c r="H77" s="2" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="I77" s="2" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="J77" s="2" t="s">
         <v>141</v>
@@ -5451,35 +5959,31 @@
         <v>77</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="E78" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="G78" s="2" t="s">
         <v>36</v>
       </c>
       <c r="H78" s="2" t="s">
-        <v>323</v>
-      </c>
-      <c r="I78" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Three-part fix. (A) create_work_item is now idempotent: re-running Task Breakdown REPLACES matching proposed work items (natural key project+type+title+parent) instead of duplicating the whole backlog; already-accepted/in-progress/done items are never touched. (B) A concurrent-run guard blocks a second trigger while a run is live (HTTP 409), for both phase and build triggers. (C) A confirm dialog on both trigger surfaces (Phases &amp; Runs and the Task page): Case 1 (completed) warns 're-running restarts and replaces THIS phase's artifacts, no duplicates'; Case 2 (in progress) blocks with a clear message. Idempotency + guard tests added.</t>
-        </is>
-      </c>
-      <c r="J78" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Fixed</t>
-        </is>
+        <v>324</v>
+      </c>
+      <c r="I78" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="J78" s="2" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="79" spans="1:10" ht="409.6">
@@ -5487,28 +5991,28 @@
         <v>78</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="E79" s="2" t="s">
         <v>22</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="G79" s="2" t="s">
         <v>36</v>
       </c>
       <c r="H79" s="2" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="I79" s="2" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="J79" s="2" t="s">
         <v>141</v>
@@ -5519,28 +6023,28 @@
         <v>79</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="E80" s="2" t="s">
         <v>22</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="G80" s="2" t="s">
         <v>36</v>
       </c>
       <c r="H80" s="2" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="I80" s="2" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="J80" s="2" t="s">
         <v>141</v>
@@ -5551,28 +6055,28 @@
         <v>80</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="E81" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="G81" s="2" t="s">
         <v>13</v>
       </c>
       <c r="H81" s="2" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="I81" s="2" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="J81" s="2" t="s">
         <v>16</v>
@@ -5583,28 +6087,28 @@
         <v>81</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="E82" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F82" s="2" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="G82" s="2" t="s">
         <v>23</v>
       </c>
       <c r="H82" s="2" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="I82" s="2" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="J82" s="2" t="s">
         <v>141</v>
@@ -5615,28 +6119,28 @@
         <v>82</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="E83" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F83" s="2" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="G83" s="2" t="s">
         <v>13</v>
       </c>
       <c r="H83" s="2" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="I83" s="2" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="J83" s="2" t="s">
         <v>16</v>
@@ -5647,28 +6151,28 @@
         <v>83</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="E84" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F84" s="2" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="G84" s="2" t="s">
         <v>13</v>
       </c>
       <c r="H84" s="2" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="I84" s="2" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="J84" s="2" t="s">
         <v>16</v>
@@ -5679,28 +6183,28 @@
         <v>84</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="E85" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F85" s="2" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="G85" s="2" t="s">
         <v>36</v>
       </c>
       <c r="H85" s="2" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="I85" s="2" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="J85" s="2" t="s">
         <v>16</v>
@@ -5711,28 +6215,28 @@
         <v>85</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="E86" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F86" s="2" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="G86" s="2" t="s">
         <v>23</v>
       </c>
       <c r="H86" s="2" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="I86" s="2" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="J86" s="2" t="s">
         <v>141</v>
@@ -5743,28 +6247,28 @@
         <v>86</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="E87" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F87" s="2" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="G87" s="2" t="s">
         <v>13</v>
       </c>
       <c r="H87" s="2" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="I87" s="2" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="J87" s="2" t="s">
         <v>16</v>
@@ -5775,28 +6279,28 @@
         <v>87</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="E88" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F88" s="2" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="G88" s="2" t="s">
         <v>36</v>
       </c>
       <c r="H88" s="2" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="I88" s="2" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="J88" s="2" t="s">
         <v>141</v>
@@ -5807,28 +6311,28 @@
         <v>88</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="E89" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F89" s="2" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="G89" s="2" t="s">
         <v>36</v>
       </c>
       <c r="H89" s="2" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="I89" s="2" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="J89" s="2" t="s">
         <v>141</v>
@@ -5839,28 +6343,28 @@
         <v>89</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="E90" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F90" s="2" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="G90" s="2" t="s">
         <v>13</v>
       </c>
       <c r="H90" s="2" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="I90" s="2" t="s">
-        <v>575</v>
+        <v>396</v>
       </c>
       <c r="J90" s="2" t="s">
         <v>16</v>
@@ -5871,35 +6375,31 @@
         <v>90</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="E91" s="2" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="F91" s="2" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="G91" s="2" t="s">
         <v>13</v>
       </c>
       <c r="H91" s="2" t="s">
-        <v>401</v>
-      </c>
-      <c r="I91" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Fixed / validated end-to-end (2026-07-15/16). Multi-repo Hybrid Option C proven live: TASK-001 built on SpendLogTest-1-backend, 08 review + 07&lt;-&gt;08 remediation loop ran, merge gate approved, squash-merged to main, WorkItem -&gt; done; multi-repo routing, per-repo PRs and single-repo backward-compat all confirmed. All decomposed sub-tasks A1-E1 complete.</t>
-        </is>
-      </c>
-      <c r="J91" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Fixed</t>
-        </is>
+        <v>402</v>
+      </c>
+      <c r="I91" s="2" t="s">
+        <v>403</v>
+      </c>
+      <c r="J91" s="2" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="92" spans="1:10" ht="409.6">
@@ -6183,15 +6683,11 @@
       <c r="H100" s="2" t="s">
         <v>461</v>
       </c>
-      <c r="I100" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Verified working — no code change needed. The live 'Add repository' form captures each repo's Role (backend/frontend/infra) via a real selector, sends it to the backend, and persists it on Repository.role (shown back as a chip). Auto-assign keys off this role correctly. Closed as verified.</t>
-        </is>
-      </c>
-      <c r="J100" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Fixed</t>
-        </is>
+      <c r="I100" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="J100" s="2" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="101" spans="1:10" ht="409.6">
@@ -6315,15 +6811,11 @@
       <c r="H104" s="2" t="s">
         <v>486</v>
       </c>
-      <c r="I104" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The code-host connect form's single 'Repository' field (which read as single-repo on multi-repo projects) is now labelled 'Default repository', made OPTIONAL, and carries a hint: 'Each build targets its own repo; this is only a fallback default. The token must have access to ALL repos in this project.' The connection is tenant-wide and each build already targets its work-item repo, so Save no longer gates on this field. Backend catalog + frontend render change.</t>
-        </is>
-      </c>
-      <c r="J104" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Fixed</t>
-        </is>
+      <c r="I104" s="2" t="s">
+        <v>487</v>
+      </c>
+      <c r="J104" s="2" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="105" spans="1:10" ht="409.6">
@@ -6639,15 +7131,11 @@
       <c r="H114" s="2" t="s">
         <v>550</v>
       </c>
-      <c r="I114" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Phase B done (extends S.No 74/112). The remaining connectors — Atlassian Confluence/Jira, Figma, Xray — now authenticate with the tenant's own stored credentials on ANY worker, not the server .env. Atlassian needed a new 'Atlassian account email' field on the Confluence/Jira connect form (basic auth = email + token); the site URL is normalised to the bare site. Per-field .env fallback retained. Config tests added.</t>
-        </is>
-      </c>
-      <c r="J114" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Fixed</t>
-        </is>
+      <c r="I114" s="2" t="s">
+        <v>551</v>
+      </c>
+      <c r="J114" s="2" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="115" spans="1:10" ht="380.1">
@@ -6788,15 +7276,11 @@
       <c r="G119" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="I119" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">FIXED (2026-07-15). agents/06_task_breakdown/agent.md: added a 'Writing standard' requiring every Epic/Story/Task Description + Acceptance Criterion to be plain-language-with-technical-nuance, detailed and self-contained enough that a developer can implement by reading it ALONE (behaviour, inputs/outputs, states, edge cases), with concrete hand-verifiable acceptance criteria and no bare placeholders; modelled the standard in all three template placeholders. Improvement flows to the Work Items board + artifact previews automatically. Test: test_agents_migration.test_task_breakdown_descriptions_and_ac_are_humanized. Per team decision the blast radius today was 06 only; the SAME defect in 02/09/00c/04/03/10 is logged as S.No 121-126 (register-condition per audience: technical-humanized for testing/security, plain+nuance for the rest) and NOT fixed this session.</t>
-        </is>
-      </c>
-      <c r="J119" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Fixed</t>
-        </is>
+      <c r="I119" s="2" t="s">
+        <v>573</v>
+      </c>
+      <c r="J119" s="2" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="120" spans="1:10" ht="113.25">
@@ -6804,7 +7288,7 @@
         <v>119</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="D120" s="2" t="s">
         <v>571</v>
@@ -6827,7 +7311,7 @@
         <v>120</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="D121" s="2" t="s">
         <v>93</v>
@@ -6841,1321 +7325,1038 @@
       <c r="G121" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="I121" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">FIXED (2026-07-15) - FULL blast radius + Part C (team-approved re-scope). (1) Artifact.title field + migration 0003_artifact_title (nullable, backward-safe). (2) register_artifact/update_artifact gain a title param, plus MCP server + companion wrappers, tool docstrings say 'ALWAYS pass a title'. (3) Part C-1 versioning-collision FIXED: version scoped by (project,phase,type,title) when titled, so per-item siblings (adr/test_case/security_finding/code/code_review/test_report) each start v1 instead of falsely superseding; untitled/singletons keep old behaviour. (4) Platform code/code_review get titles (WI key). (5) Serializers/consumers: DRF ArtifactSerializer + MCP _artifact/_lean_ref + preview payload + traceability node + dashboard + publish title expose/prefer title. (6) Frontend: new artifactLabel(title,type) helper (falls back to humanized type) in Artifacts registry list+search, preview H1/row, Traceability node (was raw type), Export/Publish. (7) 7 agents 04/05/07/08/09/09b/10 author human titles (Wireframe - Login Page, ADR-003 - Event Sourcing, TC-014 - ...). (8) Part C-2 ContractsDrift FIXED: no JSON.stringify dump (humanized scalar summary); DriftRecordSerializer enriches impacted with node_title+repo_name (batched) so no raw UUIDs. Wireframe STATES stay a separate label axis by design. Tests: test_mcp_platform_state (title + per-item independent versions), test_agents_migration (06 + per-item titles), test_review_dispatch/test_api_contract green; frontend tsc clean; ruff clean. Migration NOT yet applied to shared cloud DB - held for a coordinated make migrate (nullable=back-compat).</t>
-        </is>
-      </c>
-      <c r="J121" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Fixed</t>
-        </is>
-      </c>
-    </row>
-    <row r="122" spans="1:10" ht="380">
-      <c r="A122" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">121</t>
-        </is>
-      </c>
-      <c r="B122" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Requirements agent (02) authors user stories, functional requirements, acceptance criteria and NFRs too technically/formally for its reviewer. Same defect class as S.No 118 (06 task breakdown): the content is engineer/QA-precision only with no human-readability bar, yet the Product Owner reviews it. HUMANIZATION REGISTER for the fix = PLAIN LANGUAGE retaining the technical nuance (broader audience: PO + developer).</t>
-        </is>
-      </c>
-      <c r="C122" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Investigation (session 2026-07-15) edge-case sweep of all 16 phase agents for the S.No 118 pattern. 02 is the closest structural analog to 06.</t>
-        </is>
-      </c>
-      <c r="D122" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Agents / 02 Requirements / content humanization</t>
-        </is>
-      </c>
-      <c r="E122" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bug</t>
-        </is>
-      </c>
-      <c r="F122" s="2"/>
-      <c r="G122" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P1</t>
-        </is>
-      </c>
-      <c r="H122" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Quality bar is 'a QA engineer can execute without a follow-up question' (agents/02_requirements/agent.md:10); FR format is formal SHALL boilerplate (:115); acceptance criteria are bare BDD stubs (:85-97); user-story descriptions have no plain-language directive; reviewer is the Product Owner (:357). Related S.No 118, 120.</t>
-        </is>
-      </c>
-      <c r="I122" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">OPEN - NOT fixed this session. Team scoped today's fix to S.No 118 (06 task breakdown) only. Planned: add a plain-language-with-technical-nuance authoring bar to user-story descriptions, FR statements and acceptance criteria - mirror 06's assignment_rationale directive (:280) and the good patterns in 05_ux_design/12_deployment/08_code_review.</t>
-        </is>
-      </c>
-      <c r="J122" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="123" spans="1:10" ht="380">
-      <c r="A123" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">122</t>
-        </is>
-      </c>
-      <c r="B123" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Testing agent (09) authors UAT scenarios FOR the Product Owner, plus defect reports and test-case descriptions, with an engineer-precision bar only. Same defect class as S.No 118. HUMANIZATION REGISTER for the fix = HUMANIZED-TECHNICAL (keep the technical register but make it clear and well-structured) - NOT plain language, because QA/UAT personnel must interpret the technical detail correctly; plain language would cause misinterpretation.</t>
-        </is>
-      </c>
-      <c r="C123" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Investigation edge-case sweep. UAT is a business-verification event handed to a non-engineer, yet authored with two-engineer precision.</t>
-        </is>
-      </c>
-      <c r="D123" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Agents / 09 Testing / content humanization</t>
-        </is>
-      </c>
-      <c r="E123" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bug</t>
-        </is>
-      </c>
-      <c r="F123" s="2"/>
-      <c r="G123" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P1</t>
-        </is>
-      </c>
-      <c r="H123" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">UAT scenarios authored for the PO (agents/09_testing/agent.md:483-494) and defect descriptions (:433-459) use a two-engineer precision bar (:212) with no readability directive for the PO-facing UAT. Test-case Expected Result/Description carry the same risk. Related S.No 118, 120.</t>
-        </is>
-      </c>
-      <c r="I123" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">OPEN - NOT fixed this session (team scope = 06 only). Planned: add a HUMANIZED-TECHNICAL clarity bar (structured, understandable, technical register retained) to UAT scenarios, defect reports and test-case descriptions - not plain language.</t>
-        </is>
-      </c>
-      <c r="J123" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="124" spans="1:10" ht="380">
-      <c r="A124" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">123</t>
-        </is>
-      </c>
-      <c r="B124" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Intelligent Context Extractor agent (00c) authors the codebase_intelligence Executive Summary, health dashboard and module-documentation prose read by humans onboarding to a project, with no plain-language directive - jargon-prone. Same defect class as S.No 118. HUMANIZATION REGISTER = PLAIN LANGUAGE retaining technical nuance.</t>
-        </is>
-      </c>
-      <c r="C124" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Investigation edge-case sweep.</t>
-        </is>
-      </c>
-      <c r="D124" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Agents / 00c Context Extractor / content humanization</t>
-        </is>
-      </c>
-      <c r="E124" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bug</t>
-        </is>
-      </c>
-      <c r="F124" s="2"/>
-      <c r="G124" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P2</t>
-        </is>
-      </c>
-      <c r="H124" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Agent 'writes the prose' (agents/00c_intelligent_context_extractor/agent.md:44; artifact spec :93-106) with no directive to keep it plain for onboarding readers. Related S.No 118, 120.</t>
-        </is>
-      </c>
-      <c r="I124" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">OPEN - NOT fixed this session (team scope = 06 only). Planned: add a plain-language-with-technical-nuance bar to the exec summary and module-doc prose.</t>
-        </is>
-      </c>
-      <c r="J124" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="125" spans="1:10" ht="380">
-      <c r="A125" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">124</t>
-        </is>
-      </c>
-      <c r="B125" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Architecture agent (04) authors ADR Rationale/Context/Consequences prose and the architecture Executive Summary as human-read decision records, but only the Level-1 context diagram carries a 'readable by a non-technical stakeholder' bar - the ADR narrative and exec summary do not. Same defect class as S.No 118. HUMANIZATION REGISTER = PLAIN LANGUAGE retaining technical nuance.</t>
-        </is>
-      </c>
-      <c r="C125" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Investigation edge-case sweep.</t>
-        </is>
-      </c>
-      <c r="D125" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Agents / 04 Architecture / content humanization</t>
-        </is>
-      </c>
-      <c r="E125" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bug</t>
-        </is>
-      </c>
-      <c r="F125" s="2"/>
-      <c r="G125" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P2</t>
-        </is>
-      </c>
-      <c r="H125" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Context diagram must be 'readable by a non-technical stakeholder' (agents/04_architecture/agent.md:119) but ADR rationale (:373) and exec summary (:291) have no plain-language bar. Related S.No 118, 120.</t>
-        </is>
-      </c>
-      <c r="I125" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">OPEN - NOT fixed this session (team scope = 06 only). Planned: extend the existing non-technical-readability bar to ADR narrative fields and the exec summary.</t>
-        </is>
-      </c>
-      <c r="J125" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="126" spans="1:10" ht="380">
-      <c r="A126" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">125</t>
-        </is>
-      </c>
-      <c r="B126" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PRD agent (03) is mostly well-humanized, but the per-feature ACCEPTANCE CRITERIA remain terse placeholders - the same artifact type flagged in S.No 118. HUMANIZATION REGISTER = PLAIN LANGUAGE retaining technical nuance.</t>
-        </is>
-      </c>
-      <c r="C126" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Investigation edge-case sweep. Partially self-mitigated (strong readability directives elsewhere).</t>
-        </is>
-      </c>
-      <c r="D126" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Agents / 03 PRD / content humanization</t>
-        </is>
-      </c>
-      <c r="E126" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bug</t>
-        </is>
-      </c>
-      <c r="F126" s="2"/>
-      <c r="G126" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P2</t>
-        </is>
-      </c>
-      <c r="H126" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Strong readability directives overall (agents/03_prd/agent.md:15,76,354) but per-feature acceptance criteria are terse placeholders (:224-227). Related S.No 118, 120.</t>
-        </is>
-      </c>
-      <c r="I126" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">OPEN - NOT fixed this session (team scope = 06 only). Planned: apply the same detailed, plain-language-with-nuance bar to per-feature acceptance criteria.</t>
-        </is>
-      </c>
-      <c r="J126" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="127" spans="1:10" ht="380">
-      <c r="A127" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">126</t>
-        </is>
-      </c>
-      <c r="B127" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Security agent (10) authors the Executive Summary and finding Impact statements that reach stakeholders with no plain-language bar. Same defect class as S.No 118. HUMANIZATION REGISTER = HUMANIZED-TECHNICAL for findings (security engineers must read the technical detail correctly); the stakeholder exec summary may be plain-language-with-nuance.</t>
-        </is>
-      </c>
-      <c r="C127" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Investigation edge-case sweep. Primary audience is technical; remediation guidance is already appropriately specific.</t>
-        </is>
-      </c>
-      <c r="D127" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Agents / 10 Security / content humanization</t>
-        </is>
-      </c>
-      <c r="E127" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bug</t>
-        </is>
-      </c>
-      <c r="F127" s="2"/>
-      <c r="G127" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P2</t>
-        </is>
-      </c>
-      <c r="H127" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Exec summary and finding Impact (agents/10_security/agent.md:339-340,395-398) reach stakeholders without a readability bar. Related S.No 118, 120.</t>
-        </is>
-      </c>
-      <c r="I127" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">OPEN - NOT fixed this session (team scope = 06 only). Planned: humanized-technical clarity bar on findings; plain-language-with-nuance on the stakeholder exec summary.</t>
-        </is>
-      </c>
-      <c r="J127" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="128" spans="1:10" ht="460.0" customHeight="1">
+      <c r="I121" s="2" t="s">
+        <v>576</v>
+      </c>
+      <c r="J121" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="122" spans="1:10" ht="380.1">
+      <c r="A122" s="2" t="s">
+        <v>577</v>
+      </c>
+      <c r="B122" s="2" t="s">
+        <v>578</v>
+      </c>
+      <c r="C122" s="2" t="s">
+        <v>579</v>
+      </c>
+      <c r="D122" s="2" t="s">
+        <v>580</v>
+      </c>
+      <c r="E122" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G122" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H122" s="2" t="s">
+        <v>581</v>
+      </c>
+      <c r="I122" s="2" t="s">
+        <v>582</v>
+      </c>
+      <c r="J122" s="2" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="123" spans="1:10" ht="380.1">
+      <c r="A123" s="2" t="s">
+        <v>583</v>
+      </c>
+      <c r="B123" s="2" t="s">
+        <v>584</v>
+      </c>
+      <c r="C123" s="2" t="s">
+        <v>585</v>
+      </c>
+      <c r="D123" s="2" t="s">
+        <v>586</v>
+      </c>
+      <c r="E123" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G123" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H123" s="2" t="s">
+        <v>587</v>
+      </c>
+      <c r="I123" s="2" t="s">
+        <v>588</v>
+      </c>
+      <c r="J123" s="2" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="124" spans="1:10" ht="380.1">
+      <c r="A124" s="2" t="s">
+        <v>589</v>
+      </c>
+      <c r="B124" s="2" t="s">
+        <v>590</v>
+      </c>
+      <c r="C124" s="2" t="s">
+        <v>591</v>
+      </c>
+      <c r="D124" s="2" t="s">
+        <v>592</v>
+      </c>
+      <c r="E124" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G124" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="H124" s="2" t="s">
+        <v>593</v>
+      </c>
+      <c r="I124" s="2" t="s">
+        <v>594</v>
+      </c>
+      <c r="J124" s="2" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="125" spans="1:10" ht="380.1">
+      <c r="A125" s="2" t="s">
+        <v>595</v>
+      </c>
+      <c r="B125" s="2" t="s">
+        <v>596</v>
+      </c>
+      <c r="C125" s="2" t="s">
+        <v>591</v>
+      </c>
+      <c r="D125" s="2" t="s">
+        <v>597</v>
+      </c>
+      <c r="E125" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G125" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="H125" s="2" t="s">
+        <v>598</v>
+      </c>
+      <c r="I125" s="2" t="s">
+        <v>599</v>
+      </c>
+      <c r="J125" s="2" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="126" spans="1:10" ht="380.1">
+      <c r="A126" s="2" t="s">
+        <v>600</v>
+      </c>
+      <c r="B126" s="2" t="s">
+        <v>601</v>
+      </c>
+      <c r="C126" s="2" t="s">
+        <v>602</v>
+      </c>
+      <c r="D126" s="2" t="s">
+        <v>603</v>
+      </c>
+      <c r="E126" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G126" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="H126" s="2" t="s">
+        <v>604</v>
+      </c>
+      <c r="I126" s="2" t="s">
+        <v>605</v>
+      </c>
+      <c r="J126" s="2" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="127" spans="1:10" ht="380.1">
+      <c r="A127" s="2" t="s">
+        <v>606</v>
+      </c>
+      <c r="B127" s="2" t="s">
+        <v>607</v>
+      </c>
+      <c r="C127" s="2" t="s">
+        <v>608</v>
+      </c>
+      <c r="D127" s="2" t="s">
+        <v>609</v>
+      </c>
+      <c r="E127" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G127" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="H127" s="2" t="s">
+        <v>610</v>
+      </c>
+      <c r="I127" s="2" t="s">
+        <v>611</v>
+      </c>
+      <c r="J127" s="2" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="128" spans="1:10" ht="409.6" customHeight="1">
       <c r="A128" s="2">
         <v>127</v>
       </c>
-      <c r="B128" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Merging an approved build fails with HTTP 405 because the pull request is still a draft (the final blocker)</t>
-        </is>
-      </c>
-      <c r="C128" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">After a human approves the merge gate, the platform tries to merge the build's PR but GitHub rejects it, so the work item never reaches 'done'.</t>
-        </is>
-      </c>
-      <c r="D128" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Build pipeline / Merge gate</t>
-        </is>
-      </c>
-      <c r="E128" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bug</t>
-        </is>
-      </c>
-      <c r="F128" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1258d85</t>
-        </is>
-      </c>
-      <c r="G128" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P1</t>
-        </is>
-      </c>
-      <c r="H128" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">During the automated 07&lt;-&gt;08 review-and-fix loop the platform opens the build's pull request as a GitHub 'draft' PR (a draft blocks a premature human merge while review is still running). GitHub does not allow a draft PR to be merged - its merge API returns HTTP 405 (Method Not Allowed). So the moment a human approved the merge gate, the final merge step always failed. The work item got stuck at the very last step, never transitioned to done, and nothing downstream could complete. This was the single blocker stopping any build from finishing.</t>
-        </is>
-      </c>
-      <c r="I128" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">FIXED (commit 1258d85). Added a mark_ready_for_review step that takes the PR out of draft immediately before merging, which is the one legitimate moment to un-draft (gate already approved). merge_build_pr_core now does: get the PR; if it is not already merged and is still a draft, call codehost.mark_ready_for_review(pr_ref) which runs GitHub's markPullRequestReadyForReview GraphQL mutation and re-checks (short retries) that it un-drafted, then merge. Supporting additions: a graphql() helper (integrations/github/rest.py), a graphql_url property (config.py), and the CodeHost.mark_ready_for_review capability (capabilities.py + github/codehost.py). Regression test added in test_build_activities.py (draft PR is un-drafted before merge).</t>
-        </is>
-      </c>
-      <c r="J128" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Fixed</t>
-        </is>
-      </c>
-    </row>
-    <row r="129" spans="1:10" ht="460.0" customHeight="1">
+      <c r="B128" s="2" t="s">
+        <v>612</v>
+      </c>
+      <c r="C128" s="2" t="s">
+        <v>613</v>
+      </c>
+      <c r="D128" s="2" t="s">
+        <v>614</v>
+      </c>
+      <c r="E128" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F128" s="2" t="s">
+        <v>615</v>
+      </c>
+      <c r="G128" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H128" s="2" t="s">
+        <v>616</v>
+      </c>
+      <c r="I128" s="2" t="s">
+        <v>617</v>
+      </c>
+      <c r="J128" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="129" spans="1:10" ht="409.6" customHeight="1">
       <c r="A129" s="2">
         <v>128</v>
       </c>
-      <c r="B129" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Reviewer gets 'no opened PR to review' during the fix-and-re-review loop (wrong code pointer picked)</t>
-        </is>
-      </c>
-      <c r="C129" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">During remediation the platform sometimes points the reviewer at an empty pre-PR placeholder instead of the real pull request.</t>
-        </is>
-      </c>
-      <c r="D129" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Build pipeline / Review loop</t>
-        </is>
-      </c>
-      <c r="E129" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bug</t>
-        </is>
-      </c>
-      <c r="F129" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1258d85</t>
-        </is>
-      </c>
-      <c r="G129" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P1</t>
-        </is>
-      </c>
-      <c r="H129" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The helper that looks up a build's code artifact (_code_artifact) fetched 'the first matching artifact' with no defined ordering. A single work item can have more than one code-artifact row: an early placeholder the agent registers before the PR exists, and the real one that carries the pull-request reference (repo/number/url). With no ORDER BY, the database returned rows in an arbitrary order, so the code sometimes picked the early placeholder that has no PR link. The reviewer then had nothing to look at and reported 'no opened PR to review', which broke the remediation cycle.</t>
-        </is>
-      </c>
-      <c r="I129" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">FIXED (commit 1258d85). _code_artifact now orders artifacts by created_at and explicitly prefers the one whose external_ref is a real PR reference: it returns the first PR-ref-bearing artifact and only falls back to the earliest row if none carries a PR ref. Regression test added in test_build_activities.py (duplicate-code-artifact prefers the PR-ref pointer).</t>
-        </is>
-      </c>
-      <c r="J129" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Fixed</t>
-        </is>
-      </c>
-    </row>
-    <row r="130" spans="1:10" ht="460.0" customHeight="1">
+      <c r="B129" s="2" t="s">
+        <v>618</v>
+      </c>
+      <c r="C129" s="2" t="s">
+        <v>619</v>
+      </c>
+      <c r="D129" s="2" t="s">
+        <v>620</v>
+      </c>
+      <c r="E129" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F129" s="2" t="s">
+        <v>615</v>
+      </c>
+      <c r="G129" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H129" s="2" t="s">
+        <v>621</v>
+      </c>
+      <c r="I129" s="2" t="s">
+        <v>622</v>
+      </c>
+      <c r="J129" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="130" spans="1:10" ht="409.6" customHeight="1">
       <c r="A130" s="2">
         <v>129</v>
       </c>
-      <c r="B130" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">A genuinely 'Approved' code review is wrongly blocked by the fail-closed review guard (false positive on a resolved finding ID)</t>
-        </is>
-      </c>
-      <c r="C130" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The safety guard that blocks bad code mis-reads an approved review and rejects it, stalling the pipeline for no real reason.</t>
-        </is>
-      </c>
-      <c r="D130" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Build pipeline / Review guard (S.No 114 guard)</t>
-        </is>
-      </c>
-      <c r="E130" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bug</t>
-        </is>
-      </c>
-      <c r="F130" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">a2deeae</t>
-        </is>
-      </c>
-      <c r="G130" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P1</t>
-        </is>
-      </c>
-      <c r="H130" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The review guard is deliberately 'fail-closed': if a review's prose looks like it demands changes but the structured verdict does not clearly say so, it blocks - to stop bad code slipping through. The old prose matcher (_looks_blocking) scanned the entire review text for blocking-sounding words. An APPROVED review referenced an already-RESOLVED finding by its ID (for example 'REM-W1'), and the matcher saw that mention and concluded the review was demanding changes. Result: a legitimately approved review was blocked and the build could not proceed - a false positive that halted good work.</t>
-        </is>
-      </c>
-      <c r="I130" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">FIXED (commit a2deeae). Rewrote parse_and_guard to trust a present, structured APPROVED verdict. Added _verdict_demands_changes(): a verdict is treated as demanding changes only when a verdict is actually present AND its status matches a negative pattern (change/reject/denied/blocked/fail, via _NEGATIVE_STATUS regex). The loose prose scan is now only a fallback used when there is NO structured verdict at all. Net effect: an approved verdict is honoured even if its prose happens to mention resolved finding IDs, while a review that truly downgrades still fails closed. Regression tests added in test_review_dispatch.py (trusts approved verdict with resolved REM ids; in-JSON downgrade still fails closed).</t>
-        </is>
-      </c>
-      <c r="J130" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Fixed</t>
-        </is>
-      </c>
-    </row>
-    <row r="131" spans="1:10" ht="460.0" customHeight="1">
+      <c r="B130" s="2" t="s">
+        <v>623</v>
+      </c>
+      <c r="C130" s="2" t="s">
+        <v>624</v>
+      </c>
+      <c r="D130" s="2" t="s">
+        <v>625</v>
+      </c>
+      <c r="E130" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F130" s="2" t="s">
+        <v>626</v>
+      </c>
+      <c r="G130" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H130" s="2" t="s">
+        <v>627</v>
+      </c>
+      <c r="I130" s="2" t="s">
+        <v>628</v>
+      </c>
+      <c r="J130" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="131" spans="1:10" ht="409.6" customHeight="1">
       <c r="A131" s="2">
         <v>130</v>
       </c>
-      <c r="B131" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">When the secret scanner blocks a push, the failure is invisible - only a bare count is shown, not what/where</t>
-        </is>
-      </c>
-      <c r="C131" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">A blocked hardcoded secret produces a silent 'build failed' with just a number; nobody can tell which secret, file or line.</t>
-        </is>
-      </c>
-      <c r="D131" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Companion / Pre-push secret scan</t>
-        </is>
-      </c>
-      <c r="E131" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bug</t>
-        </is>
-      </c>
-      <c r="F131" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">52533c4</t>
-        </is>
-      </c>
-      <c r="G131" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P2</t>
-        </is>
-      </c>
-      <c r="H131" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Before pushing code the companion (the worker on the developer machine) scans the changed files for hardcoded secrets (passwords, API keys, tokens, private keys). When it finds one it correctly blocks the push and reports the build as failed - but it only reported a bare count ('N finding(s)'). It did not surface which secret type, which file, or which line, and it then tore down the temporary work folder, so the evidence was gone. Operators saw 'build failed' with no way to know why or how to fix it, making the block undiagnosable.</t>
-        </is>
-      </c>
-      <c r="I131" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">FIXED (commit 52533c4). The companion now prints a redacted summary to its own terminal ('[companion] SECRET SCAN BLOCKED push (N finding(s)) - branch NOT pushed') listing each finding as '[kind] path:line - preview', and the same redacted detail travels in the build.failed reason so it also appears in the platform run console. Only the already-redacted preview is shown - never the raw secret value - and the list is capped at 8 findings with a '(+N more)' tail so the message stays bounded. Added the _format_secret_findings helper (runner/companion/runner.py) and regression tests in test_companion_runner.py (redacted findings surface; cap at 8).</t>
-        </is>
-      </c>
-      <c r="J131" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Fixed</t>
-        </is>
-      </c>
-    </row>
-    <row r="132" spans="1:10" ht="460.0" customHeight="1">
+      <c r="B131" s="2" t="s">
+        <v>629</v>
+      </c>
+      <c r="C131" s="2" t="s">
+        <v>630</v>
+      </c>
+      <c r="D131" s="2" t="s">
+        <v>631</v>
+      </c>
+      <c r="E131" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F131" s="2" t="s">
+        <v>632</v>
+      </c>
+      <c r="G131" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="H131" s="2" t="s">
+        <v>633</v>
+      </c>
+      <c r="I131" s="2" t="s">
+        <v>634</v>
+      </c>
+      <c r="J131" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="132" spans="1:10" ht="409.6" customHeight="1">
       <c r="A132" s="2">
         <v>131</v>
       </c>
-      <c r="B132" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The code-review result (code_review artifact) cannot be opened or read from the web UI</t>
-        </is>
-      </c>
-      <c r="C132" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The 08 review report is produced and registered but there is no view/link in the product to read it.</t>
-        </is>
-      </c>
-      <c r="D132" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">UI / Review experience</t>
-        </is>
-      </c>
-      <c r="E132" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bug</t>
-        </is>
-      </c>
-      <c r="F132" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="G132" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P2</t>
-        </is>
-      </c>
-      <c r="H132" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The 08 review agent produces a code_review artifact holding the review findings and verdict, and the platform registers it as an artifact (pointer + provenance). However the web interface offers no view or link that opens the artifact body, so a human reviewer or manager cannot actually read the review inside the product - they would have to query the database or dig through logs. This undermines the human review gate: the gate exists but the evidence behind it is not surfaced to the person approving.</t>
-        </is>
-      </c>
-      <c r="I132" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Verified already fixed — no code change needed. Cross-checked against a live run: the code_review artifact IS registered with a rendered report body (the companion uploads the .md to S3 — confirmed a ~22 KB report object exists for the latest run), and the generic artifact preview reads it, so the report opens and reads in the UI. The earlier 'no body' analysis looked only at the platform-side fallback registration and missed the companion upload. Closed as verified.</t>
-        </is>
-      </c>
-      <c r="J132" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Fixed</t>
-        </is>
-      </c>
-    </row>
-    <row r="133" spans="1:10" ht="460.0" customHeight="1">
+      <c r="B132" s="2" t="s">
+        <v>635</v>
+      </c>
+      <c r="C132" s="2" t="s">
+        <v>636</v>
+      </c>
+      <c r="D132" s="2" t="s">
+        <v>637</v>
+      </c>
+      <c r="E132" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F132" s="2" t="s">
+        <v>638</v>
+      </c>
+      <c r="G132" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="H132" s="2" t="s">
+        <v>639</v>
+      </c>
+      <c r="I132" s="2" t="s">
+        <v>640</v>
+      </c>
+      <c r="J132" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="133" spans="1:10" ht="409.6" customHeight="1">
       <c r="A133" s="2">
         <v>132</v>
       </c>
-      <c r="B133" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The 'sdlc/build' commit status is set to 'pending' when the PR opens and is never updated - it stays pending forever (latent)</t>
-        </is>
-      </c>
-      <c r="C133" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">A dormant flaw: the build commit status posted to GitHub is never moved off 'pending', which will block merges if branch protection ever requires it.</t>
-        </is>
-      </c>
-      <c r="D133" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Build pipeline / Commit status reporting</t>
-        </is>
-      </c>
-      <c r="E133" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bug</t>
-        </is>
-      </c>
-      <c r="F133" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">build_activities.py:140</t>
-        </is>
-      </c>
-      <c r="G133" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P3</t>
-        </is>
-      </c>
-      <c r="H133" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">When the build PR is opened, the platform posts a GitHub commit status with context 'sdlc/build' and state 'pending' against the head commit (build_activities.py line 140, best-effort - exceptions are swallowed). Nothing anywhere later updates that status to 'success' or 'failure'. So every build's commit shows the 'sdlc/build' check stuck on pending indefinitely. It is dormant today only because no branch-protection rule on the repo currently requires the 'sdlc/build' context to be green before merging. The day someone enables such a required check, merges will be blocked forever because the status can never reach success - a latent time-bomb, and misleading status UI in the meantime.</t>
-        </is>
-      </c>
-      <c r="I133" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">OPEN - not fixed this session. Recommended fix: complete the status lifecycle. Set 'sdlc/build' to 'success' once the build+review pass (or at merge), and to 'failure' on the mark_build_failed / secret-block / merge-failed paths, using the same head SHA. Keep it best-effort (do not fail the saga on a status-post error), but ensure a terminal state is always posted so the check does not dangle. Acceptance: after a run reaches a terminal outcome, the commit's 'sdlc/build' status reflects success or failure, never a permanent pending.</t>
-        </is>
-      </c>
-      <c r="J133" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="134" spans="1:10" ht="460.0" customHeight="1">
+      <c r="B133" s="2" t="s">
+        <v>641</v>
+      </c>
+      <c r="C133" s="2" t="s">
+        <v>642</v>
+      </c>
+      <c r="D133" s="2" t="s">
+        <v>643</v>
+      </c>
+      <c r="E133" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F133" s="2" t="s">
+        <v>644</v>
+      </c>
+      <c r="G133" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H133" s="2" t="s">
+        <v>645</v>
+      </c>
+      <c r="I133" s="2" t="s">
+        <v>646</v>
+      </c>
+      <c r="J133" s="2" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="134" spans="1:10" ht="409.6" customHeight="1">
       <c r="A134" s="2">
         <v>133</v>
       </c>
-      <c r="B134" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The companion crashes hard (fatal, exit 1) when the build agent errors, instead of failing gracefully and reporting back</t>
-        </is>
-      </c>
-      <c r="C134" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">If the AI build agent fails, the whole companion worker dies and needs a manual restart, stalling the build.</t>
-        </is>
-      </c>
-      <c r="D134" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Companion / Build execution resilience</t>
-        </is>
-      </c>
-      <c r="E134" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bug</t>
-        </is>
-      </c>
-      <c r="F134" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="G134" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P1</t>
-        </is>
-      </c>
-      <c r="H134" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">When the build agent (the Claude Agent SDK run inside the companion) exits with an error, the exception propagates all the way up and the companion process terminates fatally (Command failed / exit code 1). Because the companion runs one build at a time and is a long-lived poller, a single agent error takes the whole worker down: it stops polling, the current run is left dangling (claimed but not reported), and a human has to notice and restart the companion before any further work can proceed. Observed repeatedly this session (e.g. when a mid-build backend restart broke the agent's MCP calls, and when an environment/dependency mismatch made the agent exit).</t>
-        </is>
-      </c>
-      <c r="I134" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Fixed (2026-07-16). runner/companion/daemon.py _run_build now catches a generic build-agent error, posts a failed BuildReport (status=failed + message) to /api/runner/builds/&lt;run&gt;/report/, and keeps polling (mirrors the plan/review path _run_engine_phase) instead of the exception propagating out of serve and killing the long-lived companion. EngineAuthError still fail-closes (explicit re-raise) so a subscription/auth halt is never downgraded to a per-build failure. Tests: test_companion_daemon (agent-error reported + no crash; auth-error still halts).</t>
-        </is>
-      </c>
-      <c r="J134" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Fixed</t>
-        </is>
-      </c>
-    </row>
-    <row r="135" spans="1:10" ht="460.0" customHeight="1">
+      <c r="B134" s="2" t="s">
+        <v>647</v>
+      </c>
+      <c r="C134" s="2" t="s">
+        <v>648</v>
+      </c>
+      <c r="D134" s="2" t="s">
+        <v>649</v>
+      </c>
+      <c r="E134" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F134" s="2" t="s">
+        <v>638</v>
+      </c>
+      <c r="G134" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H134" s="2" t="s">
+        <v>650</v>
+      </c>
+      <c r="I134" s="2" t="s">
+        <v>651</v>
+      </c>
+      <c r="J134" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="135" spans="1:10" ht="409.6" customHeight="1">
       <c r="A135" s="2">
         <v>134</v>
       </c>
-      <c r="B135" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">A worker can deadlock a job by self-renewing its own claim while making no progress (stuck job never released)</t>
-        </is>
-      </c>
-      <c r="C135" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">A worker keeps renewing its hold (heartbeat) on a job it isn't actually advancing, so the job sits claimed forever and nothing else can take it.</t>
-        </is>
-      </c>
-      <c r="D135" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Build pipeline / Claim + heartbeat (S.No 111)</t>
-        </is>
-      </c>
-      <c r="E135" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bug</t>
-        </is>
-      </c>
-      <c r="F135" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="G135" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P1</t>
-        </is>
-      </c>
-      <c r="H135" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Jobs are handed to a worker via a claim, and a heartbeat (S.No 111) periodically renews that claim so the platform knows the worker is alive. The problem: the heartbeat renews the claim based on the worker still running, not on the work actually progressing. If the worker gets wedged (e.g. the agent hangs, or a step is stuck) but the heartbeat thread keeps ticking, the claim is renewed indefinitely. The job stays 'claimed', the report-timeout takeover cannot fire (the claim looks fresh), and no other worker can pick it up - a silent deadlock that only a human notices. Seen this session as the 'companion claimed but never built' deadlock.</t>
-        </is>
-      </c>
-      <c r="I135" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Fixed (2026-07-16). Cross-verified first: _renew_claims_for renewed the claim on process liveness alone (no progress signal, no cap), so a wedged-but-heartbeating worker held its claim until only the 2h workflow report-timeout (S.No 89) freed it. Fix: backend/api/runner_views.py stamps first_claimed_at at each claim (reset per claim, never touched by heartbeat) and MAX_CLAIM_AGE=60min caps renewal - past it the heartbeat stops renewing so the lease ages out and the run is recoverable well before the 2h backstop. Cap set above the longest legit build (&lt;60min, team-confirmed) so a healthy long build is never capped (no S.No 111 regression). Note: a companion progress-signal is the fundamentally optimal fix (distinguishes wedged-vs-working at any duration) - logged as the future upgrade if builds ever exceed ~1h. Tests: test_phase_dispatch (cap stops renewal; young claim still renews).</t>
-        </is>
-      </c>
-      <c r="J135" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Fixed</t>
-        </is>
-      </c>
-    </row>
-    <row r="136" spans="1:10" ht="460.0" customHeight="1">
+      <c r="B135" s="2" t="s">
+        <v>652</v>
+      </c>
+      <c r="C135" s="2" t="s">
+        <v>653</v>
+      </c>
+      <c r="D135" s="2" t="s">
+        <v>654</v>
+      </c>
+      <c r="E135" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F135" s="2" t="s">
+        <v>638</v>
+      </c>
+      <c r="G135" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H135" s="2" t="s">
+        <v>655</v>
+      </c>
+      <c r="I135" s="2" t="s">
+        <v>656</v>
+      </c>
+      <c r="J135" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="136" spans="1:10" ht="409.6" customHeight="1">
       <c r="A136" s="2">
         <v>135</v>
       </c>
-      <c r="B136" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Dependency version skew: pinned claude-agent-sdk / anyio in the repo are behind what the runtime actually needs</t>
-        </is>
-      </c>
-      <c r="C136" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The project's pinned library versions lag what the running machine requires; fixed by hand on the machine but not locked in the repo, so it will break for the next person.</t>
-        </is>
-      </c>
-      <c r="D136" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Companion / Dependency management</t>
-        </is>
-      </c>
-      <c r="E136" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bug</t>
-        </is>
-      </c>
-      <c r="F136" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="G136" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P2</t>
-        </is>
-      </c>
-      <c r="H136" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The companion depends on claude-agent-sdk, which in turn requires a newer anyio (the anyio.open_process 'user' keyword arrives in anyio 4.5.0; claude-agent-sdk 0.1.72 needs it). The repo's pins were stale (an old claude-agent-sdk pin and no floor on anyio), so a fresh environment installed anyio 4.4.0 and the agent crashed with "anyio.open_process() got an unexpected keyword argument 'user'". This session it was worked around by manually upgrading anyio on the host (pip install -U 'anyio&gt;=4.5' -&gt; 4.14.2), but that fix lives only on this machine - the repo still pins the broken combination, so the next developer or a rebuilt container will hit the same crash.</t>
-        </is>
-      </c>
-      <c r="I136" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">OPEN - not fixed this session (env-patched only). Recommended fix: pin the correct, mutually compatible versions in the repo lockfile/requirements - bump claude-agent-sdk to the version actually in use and add an explicit anyio&gt;=4.5 floor - then rebuild the companion/worker images from the lockfile so a clean install reproduces the working environment. Acceptance: a from-scratch install (no manual pip upgrades) runs a build without the open_process 'user' error.</t>
-        </is>
-      </c>
-      <c r="J136" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="137" spans="1:10" ht="460.0" customHeight="1">
+      <c r="B136" s="2" t="s">
+        <v>657</v>
+      </c>
+      <c r="C136" s="2" t="s">
+        <v>658</v>
+      </c>
+      <c r="D136" s="2" t="s">
+        <v>659</v>
+      </c>
+      <c r="E136" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F136" s="2" t="s">
+        <v>638</v>
+      </c>
+      <c r="G136" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="H136" s="2" t="s">
+        <v>660</v>
+      </c>
+      <c r="I136" s="2" t="s">
+        <v>661</v>
+      </c>
+      <c r="J136" s="2" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="137" spans="1:10" ht="409.6" customHeight="1">
       <c r="A137" s="2">
         <v>136</v>
       </c>
-      <c r="B137" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Build branches are merged without first being updated against their base, causing merge conflicts at the gate</t>
-        </is>
-      </c>
-      <c r="C137" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The platform merges a feature branch without rebasing/updating it against the current base, so it hits conflicts (mergeable_state=dirty) and the merge fails.</t>
-        </is>
-      </c>
-      <c r="D137" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Build pipeline / Merge gate</t>
-        </is>
-      </c>
-      <c r="E137" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bug</t>
-        </is>
-      </c>
-      <c r="F137" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="G137" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P1</t>
-        </is>
-      </c>
-      <c r="H137" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">When the merge gate is approved, the platform merges the feature branch as-is. It never updates the branch against the latest base first. If the base has moved on since the branch was cut - which is normal in a multi-developer repo - the PR can be in a conflicted state (GitHub mergeable_state = 'dirty'), and the merge API then returns HTTP 405 just like the draft case. This session WI-29 hit exactly this: an add/add conflict on frontend/.env.example left the PR dirty and the merge failed; it had to be resolved by hand. The pipeline has no step to bring a branch up to date with its base before attempting the merge.</t>
-        </is>
-      </c>
-      <c r="I137" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Fixed (2026-07-16). The merge gate merged the feature branch as-is, so a base that moved since the branch was cut left the PR mergeable_state=dirty and the GitHub merge API returned a raw 405. Fix: integrations/types.py PullRequest gains mergeable/mergeable_state; github/codehost.py adds update_branch (GitHub Update-branch; swallow 422 already-up-to-date) + ensure_mergeable (bounded re-read for GitHub's async mergeability); build_activities.py merge_build_pr_core now, before merging: if 'behind' -&gt; update branch against base then re-check; if 'dirty'/not mergeable -&gt; fail fast (non-retryable ApplicationError) with a clear 'merge conflict - needs manual resolution' reason instead of a cryptic 405; merges only when mergeable. Idempotent behind the existing 'if not pr.merged' guard. Tests: test_build_activities (behind-&gt;update-&gt;merge; dirty-&gt;clean fail, never merged). Reason surfacing verified in live test: the classified reason reaches the user via the S.No 139 ActivityError-cause unwrap (build_workflow uses build_types.failure_reason), since str(ActivityError) is the opaque "Activity task failed".</t>
-        </is>
-      </c>
-      <c r="J137" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Fixed</t>
-        </is>
-      </c>
-    </row>
-    <row r="138" spans="1:10" ht="460.0" customHeight="1">
+      <c r="B137" s="2" t="s">
+        <v>662</v>
+      </c>
+      <c r="C137" s="2" t="s">
+        <v>663</v>
+      </c>
+      <c r="D137" s="2" t="s">
+        <v>614</v>
+      </c>
+      <c r="E137" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F137" s="2" t="s">
+        <v>638</v>
+      </c>
+      <c r="G137" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H137" s="2" t="s">
+        <v>664</v>
+      </c>
+      <c r="I137" s="2" t="s">
+        <v>665</v>
+      </c>
+      <c r="J137" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="138" spans="1:10" ht="409.6" customHeight="1">
       <c r="A138" s="2">
         <v>137</v>
       </c>
-      <c r="B138" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Planning overlap: two separate work items are both told to create the same file (frontend/.env.example), guaranteeing a conflict</t>
-        </is>
-      </c>
-      <c r="C138" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TASK-003 and TASK-005 each create frontend/.env.example, so when both build they collide - a work-breakdown/planning defect.</t>
-        </is>
-      </c>
-      <c r="D138" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Planning / Work-item decomposition</t>
-        </is>
-      </c>
-      <c r="E138" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bug</t>
-        </is>
-      </c>
-      <c r="F138" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="G138" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P2</t>
-        </is>
-      </c>
-      <c r="H138" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Two independently-dispatched work items (TASK-003 and TASK-005) were each planned to create the same file, frontend/.env.example. When both branches are built and then merged, they produce an add/add conflict on that file - there is no shared ownership or de-duplication in the planning step. This is the upstream cause of the WI-29 merge conflict (S.No 136): the pipeline had no branch-update step to catch it, but the conflict should not have been planned in the first place. It points to a gap in how the planner assigns file ownership across parallel work items.</t>
-        </is>
-      </c>
-      <c r="I138" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Not reproducible / not a bug — verified against stored work-item data. TASK-003 creates the FRONTEND .env.example (frontend repo); TASK-005 is a backend SQLAlchemy/Alembic task (backend repo) — different files, different repos, no collision. The likely confusion: TASK-002 (backend .env.example) and TASK-003 (frontend .env.example) are two correctly-separate files that merely share a name. Closed.</t>
-        </is>
-      </c>
-      <c r="J138" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Fixed</t>
-        </is>
-      </c>
-    </row>
-    <row r="139" spans="1:10" ht="460.0" customHeight="1">
+      <c r="B138" s="2" t="s">
+        <v>666</v>
+      </c>
+      <c r="C138" s="2" t="s">
+        <v>667</v>
+      </c>
+      <c r="D138" s="2" t="s">
+        <v>668</v>
+      </c>
+      <c r="E138" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F138" s="2" t="s">
+        <v>638</v>
+      </c>
+      <c r="G138" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="H138" s="2" t="s">
+        <v>669</v>
+      </c>
+      <c r="I138" s="2" t="s">
+        <v>670</v>
+      </c>
+      <c r="J138" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="139" spans="1:10" ht="409.6" customHeight="1">
       <c r="A139" s="2">
         <v>138</v>
       </c>
-      <c r="B139" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Two developers share a single enrollment record, risking incorrect work attribution and tenant isolation</t>
-        </is>
-      </c>
-      <c r="C139" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Two devs point at the same enrollment identity (32db7f5f), so runs/work may be attributed or isolated to the wrong person.</t>
-        </is>
-      </c>
-      <c r="D139" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Tenancy / Enrollment identity</t>
-        </is>
-      </c>
-      <c r="E139" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bug</t>
-        </is>
-      </c>
-      <c r="F139" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">enrollment 32db7f5f</t>
-        </is>
-      </c>
-      <c r="G139" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P2</t>
-        </is>
-      </c>
-      <c r="H139" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">During testing it was found that two different developers are operating under the same enrollment record (enrollment id 32db7f5f, under tenant 212395b8). Enrollment is meant to identify a single developer's participation in a project; sharing one record between two people means their runs, claims and attribution can be conflated, and any per-developer isolation or accounting keyed on enrollment is wrong. It also muddies debugging (whose companion claimed what) and could let one developer's actions appear under the other's identity.</t>
-        </is>
-      </c>
-      <c r="I139" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">OPEN - not fixed this session (flagged during testing). Recommended fix: give each developer their own enrollment record under the tenant/project, and ensure the companion is launched with the correct per-developer enrollment/credentials so claims and events attribute to the right person. Audit existing runs that used the shared enrollment. Acceptance: each developer has a distinct enrollment and their runs attribute correctly.</t>
-        </is>
-      </c>
-      <c r="J139" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="140" spans="1:10" ht="460.0" customHeight="1">
+      <c r="B139" s="2" t="s">
+        <v>671</v>
+      </c>
+      <c r="C139" s="2" t="s">
+        <v>672</v>
+      </c>
+      <c r="D139" s="2" t="s">
+        <v>673</v>
+      </c>
+      <c r="E139" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F139" s="2" t="s">
+        <v>674</v>
+      </c>
+      <c r="G139" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="H139" s="2" t="s">
+        <v>675</v>
+      </c>
+      <c r="I139" s="2" t="s">
+        <v>676</v>
+      </c>
+      <c r="J139" s="2" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="140" spans="1:10" ht="409.6" customHeight="1">
       <c r="A140" s="2">
         <v>139</v>
       </c>
-      <c r="B140" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Build failures don't explain why - most failures show a generic 'build failed' or a raw, cryptic error instead of a clear reason</t>
-        </is>
-      </c>
-      <c r="C140" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">When a build fails for reasons other than a blocked secret (token/permission error, merge conflict, agent error, empty build), the platform shows 'build failed' or a raw exception string, not a plain classified reason.</t>
-        </is>
-      </c>
-      <c r="D140" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Build pipeline / Failure observability</t>
-        </is>
-      </c>
-      <c r="E140" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bug</t>
-        </is>
-      </c>
-      <c r="F140" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="G140" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P1</t>
-        </is>
-      </c>
-      <c r="H140" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The build.failed reason is populated inconsistently across the different failure paths (build_workflow.py). A companion report failure falls back to the generic literal 'build reported failed' when no message is set. Remediation-exhausted is the hardcoded 'remediation cycles exhausted'. The PR/gate-setup and merge paths embed a raw Python/Temporal exception string ('pr/gate setup failed: {exc}', 'merge failed: {exc}') - so a token-permission (403) error or a merge conflict (405) is technically present but buried in a cryptic stack string, not classified as 'token permission issue' or 'merge conflict'. Only the secret-scan case (S.No 130) was made human-readable. Net effect: for most failure kinds an operator sees 'build failed' with no actionable reason and must dig through logs to triage.</t>
-        </is>
-      </c>
-      <c r="I140" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Fixed (2026-07-16). build.failed reasons were inconsistent (bare 'build reported failed', hardcoded 'remediation cycles exhausted', raw exception strings 'merge failed: {exc}') AND - a hidden gap - the EventSerializer never surfaced the 'reason' payload key, so the run console showed only 'Build failed'. Fix: build_activities.py classify_build_failure maps every failure path to a plain-language classified reason (merge conflict / permission-403 / remediation exhausted / empty build / agent error; the good S.No 130 secret-scan message passes through); mark_build_failed_core writes it to run.outputs.error (where the run console reads the failure line) and the build.failed event; api/serializers.py adds 'reason' to the event message keys. Composes with S.No 136 (single canonical 'merge conflict' reason). Tests: test_build_activities (classifier mappings; reason on run.outputs.error). CORRECTION (same session, caught by live test): the workflow now UNWRAPS the ActivityError .cause via build_types.failure_reason so the classifier sees the real message (Temporal str(ActivityError)="Activity task failed" otherwise hides the 405/422/conflict); AND open_build_pr_core fails an EMPTY build fast (non-retryable ApplicationError "empty build: no changes") instead of a cryptic 422 after 3 retries - an empty build still FAILS (clear reason), it does not auto-succeed. Tests: failure_reason unwrap + empty-build fast-fail + classifier mappings.</t>
-        </is>
-      </c>
-      <c r="J140" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Fixed</t>
-        </is>
+      <c r="B140" s="2" t="s">
+        <v>677</v>
+      </c>
+      <c r="C140" s="2" t="s">
+        <v>678</v>
+      </c>
+      <c r="D140" s="2" t="s">
+        <v>679</v>
+      </c>
+      <c r="E140" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F140" s="2" t="s">
+        <v>638</v>
+      </c>
+      <c r="G140" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H140" s="2" t="s">
+        <v>680</v>
+      </c>
+      <c r="I140" s="2" t="s">
+        <v>681</v>
+      </c>
+      <c r="J140" s="2" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="141" spans="1:10">
       <c r="A141" s="2">
         <v>140</v>
       </c>
-      <c r="B141" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">No human action to resolve a non-mergeable / redundant / failed WorkItem: a task can only reach 'done' via a successful automated build+merge. A build that fails (empty/redundant build, or a merge conflict needing manual resolution) leaves the WorkItem stuck at in_progress with no product path for a human to mark it done, skip it, or close it as redundant.</t>
-        </is>
-      </c>
-      <c r="C141" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Surfaced 2026-07-16 while testing S.No 136/139: TASK-002 (redundant with TASK-001) produced an empty build that correctly FAILED with 'Empty build: no changes to commit'. The WorkItem then sits at in_progress with the branch/draft PR left in place, and the only offered action is Retry - which re-fails for a genuinely redundant task. A human can freely trigger the NEXT task (tasks are independent unless depends_on) but cannot close/resolve the failed one. Today the only ways to reach done are the happy-path orchestrator flow or an admin DB state change.</t>
-        </is>
-      </c>
-      <c r="D141" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Work Items / Build recovery UX</t>
-        </is>
-      </c>
-      <c r="E141" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Enhancement</t>
-        </is>
-      </c>
-      <c r="F141" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">backend/apps/workitems/models.py (State: proposed/accepted/in_progress/in_review/blocked/done, no transition validation); backend/api/serializers.py WorkItemPatchSerializer (state NOT writable) + read_only state; backend/api/views.py WorkItemViewSet (trigger/build/take-over/lifecycle - no transition/mark-done action); mcp_platform_state/tools.py transition_work_item (any-&gt;any, internal only); frontend RunConsole.tsx (Retry only) / WorkItemTask.tsx (done is display-only) / OfflineTakeover.tsx</t>
-        </is>
-      </c>
-      <c r="G141" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P2</t>
-        </is>
-      </c>
-      <c r="H141" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WorkItem.state is read-only on the API (excluded from WorkItemPatchSerializer; read_only on the read serializer) and mutated ONLY internally by the orchestrator (successful build+merge / gate / reject / takeover). No human-facing transition/mark-done/close/skip action or endpoint exists; the frontend offers only Retry / Trigger phase / manual takeover (sets takeover_flag, not state). transition_work_item allows any-&gt;any but is unexposed to users.</t>
-        </is>
-      </c>
-      <c r="I141" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">OPEN - proposed: add a GATED human action + API endpoint to move a WorkItem to a terminal state outside the happy path (e.g. 'Mark done', 'Close as redundant / won't-do', or 'Skip'), surfaced on the Work Items board + task page, with an audit Event. Decide whether to reuse 'done' or add a distinct terminal state (e.g. 'closed'/'cancelled') to distinguish completed-by-build from human-closed; guard with role/permission. Related S.No 76 (no task-edit UI; state not editable).</t>
-        </is>
-      </c>
-      <c r="J141" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Open</t>
-        </is>
+      <c r="B141" s="2" t="s">
+        <v>682</v>
+      </c>
+      <c r="C141" s="2" t="s">
+        <v>683</v>
+      </c>
+      <c r="D141" s="2" t="s">
+        <v>684</v>
+      </c>
+      <c r="E141" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F141" s="2" t="s">
+        <v>685</v>
+      </c>
+      <c r="G141" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="H141" s="2" t="s">
+        <v>686</v>
+      </c>
+      <c r="I141" s="2" t="s">
+        <v>687</v>
+      </c>
+      <c r="J141" s="2" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="142" spans="1:10">
       <c r="A142" s="2">
         <v>141</v>
       </c>
-      <c r="B142" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Merge gate can't recover from a conflict without redoing the whole build. TWO related enhancements (logged together): (ENH-2, IMPLEMENT NOW) Merge-only retry / re-openable merge gate - when a merge hits a conflict, PAUSE at the merge step and let the user retry the merge after fixing the conflict, WITHOUT re-running the whole build. (ENH-1, FUTURE / only if needed) Reconcile the Run status on an EXTERNAL merge - when a user merges the PR by hand in GitHub, also flip the Run from failed to done (today the webhook updates the WorkItem + artifact but leaves the Run 'failed').</t>
-        </is>
-      </c>
-      <c r="C142" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Today a merge conflict marks the ENTIRE build failed and ends the workflow, so finishing means re-running everything (AI re-writes the code, re-reviews, re-opens the PR) just to retry one merge. ENH-2 fixes this: keep the build paused at the merge gate; after the user resolves the conflict in GitHub they press Merge/Approve again and the platform completes the merge through its OWN flow (run + gate + work-item all stay correct automatically, no rebuild). ENH-1 covers a DIFFERENT path - the user merges by hand in GitHub instead of letting the platform do it; then the platform only learns via webhook (S.No 88) and today leaves the Run status stale. TEAM PLAN (2026-07-16): implement ENH-2 now; keep ENH-1 for future - it overlaps S.No 88 and is only needed if users merge OUTSIDE the platform. If ENH-2 is used, ENH-1 is largely unnecessary. Same 'soft, reconcilable' idea as the S.No 89 fix, applied to merge conflicts.</t>
-        </is>
-      </c>
-      <c r="D142" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Build pipeline / Merge gate recovery</t>
-        </is>
-      </c>
-      <c r="E142" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Enhancement</t>
-        </is>
-      </c>
-      <c r="F142" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">backend/orchestration/build_workflow.py (merge gate + ActivityError-&gt;mark_build_failed is TERMINAL on a conflict); backend/orchestration/build_activities.py merge_build_pr_core (S.No 136 dirty-&gt;fail); backend/integrations/webhooks.py _reconcile_pull_request (updates WorkItem+artifact on an external merge, NOT the Run); frontend Gates.tsx (merge gate) + RunConsole.tsx. Related: S.No 88 (external merge / missing webhook), S.No 89 (soft-reconcilable pattern), S.No 136 (conflict detection).</t>
-        </is>
-      </c>
-      <c r="G142" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P2</t>
-        </is>
-      </c>
-      <c r="H142" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">On a merge conflict the BuildWorkflow catches the ActivityError and calls mark_build_failed, which is TERMINAL - the workflow ends, so there is no live workflow to retry the merge and the merge-gate Approval is already spent. The only ways forward today are a full re-trigger (rebuilds from 07) or an external GitHub merge (needs the S.No 88 webhook, which also does not reconcile the Run status).</t>
-        </is>
-      </c>
-      <c r="I142" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ENH-2 IMPLEMENTED &amp; VALIDATED LIVE (@ 66b70c8, + gate banner). A merge conflict is now NON-terminal: merge_build_pr detects a dirty PR and raises a typed MergeConflict; the BuildWorkflow catches it, RE-OPENS the merge gate (resets the approval to pending, records outputs.merge_conflict + a build.merge_conflict event) and waits — instead of failing the build. The user resolves the conflict in GitHub and approves again; the platform retries ONLY the merge (no rebuild, no re-review). Proven live on TASK-003 (run 1d1dd943): injected an add/add conflict on .env.example -&gt; approve -&gt; gate re-opened (once per remaining conflict) -&gt; resolved -&gt; approve -&gt; platform merged PR#1 (merge commit c1d7552a) -&gt; WorkItem done -&gt; run completed, with NO rebuild across retries. The merge gate now shows a warning banner explaining the conflict + retry (ApprovalSerializer.merge_conflict; shown ONLY on a re-opened merge gate, never other gates). ENH-1 (reconcile Run status on an EXTERNAL GitHub merge) remains FUTURE / optional — it overlaps S.No 88 and is only needed if users merge outside the platform, which ENH-2 makes largely unnecessary.</t>
-        </is>
-      </c>
-      <c r="J142" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Fixed</t>
-        </is>
-      </c>
-    </row>
-    <row r="143" spans="1:1">
+      <c r="B142" s="2" t="s">
+        <v>688</v>
+      </c>
+      <c r="C142" s="2" t="s">
+        <v>689</v>
+      </c>
+      <c r="D142" s="2" t="s">
+        <v>690</v>
+      </c>
+      <c r="E142" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F142" s="2" t="s">
+        <v>691</v>
+      </c>
+      <c r="G142" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="H142" s="2" t="s">
+        <v>692</v>
+      </c>
+      <c r="I142" s="2" t="s">
+        <v>693</v>
+      </c>
+      <c r="J142" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="143" spans="1:10">
       <c r="A143" s="2">
         <v>142</v>
       </c>
-      <c r="B143" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Backlog push to Jira: tasks never reach Jira — each Task is created with its Story as parent, which Jira rejects</t>
-        </is>
-      </c>
-      <c r="C143" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">During a live Jira push of the SpendLog-1 backlog, all 5 epics + 15 stories were created but 0 of 29 tasks landed. reconcile creates each task with parent = its story's Jira key; Jira rejects a standard Task parented to a Story (400 'Please select valid parent issue') — only Sub-tasks can live under a Story (Jira hierarchy: Epic &gt; Story/Task, and Epic &gt; Story &gt; Sub-task).</t>
-        </is>
-      </c>
-      <c r="D143" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Integrations / TaskTracker (Jira)</t>
-        </is>
-      </c>
-      <c r="E143" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bug</t>
-        </is>
-      </c>
-      <c r="F143" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="G143" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P2</t>
-        </is>
-      </c>
-      <c r="H143" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">reconcile.reconcile_work_item mapped WorkItem.type 'task' -&gt; Jira 'Task' and set parent={key: story}. Jira does not allow a standard Task under a Story. Stories succeeded because Story-under-Epic via the parent field IS valid; tasks-under-stories are not.</t>
-        </is>
-      </c>
-      <c r="I143" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TWO layered causes, both fixed. (1) REAL ROOT CAUSE: reconcile's idempotency guard 'if wi.external_ref' wrongly treated a repo-assigned task as already-reconciled. Multi-repo tasks carry external_ref.repo_assignment (the planner's repo pick, Option C) with NO SoR id, so on the live push every task was SKIPPED before reaching Jira (export showed created:0, reconciled:29, no error — not a Jira rejection at all). Fixed: the guard now checks for a real SoR key (external_ref.id), and the SoR ref is MERGED into external_ref so the repo_assignment is preserved. (2) HIERARCHY (latent, also fixed): once tasks reach Jira, a standard Task can't be a child of a Story, so a task with a reconciled story parent is created as a SUB-TASK under it (the project's real sub-task issue-type name, resolved via AtlassianTaskTracker.subtask_type_name() + cached), and a parentless task as a top-level Task. Validated live (Sub-task-under-Story create succeeds; Task-under-Story returns 400). Tests in test_reconcile: repo-assigned task not-skipped + repo_assignment preserved, subtask mapping, parentless task, per-item failure capture. NOTE: my first commit fixed only the hierarchy; the guard/repo_assignment fix (the true blocker) landed in the follow-up commit after the re-push showed created:0.</t>
-        </is>
-      </c>
-      <c r="J143" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Fixed</t>
-        </is>
-      </c>
-    </row>
-    <row r="144" spans="1:1">
+      <c r="B143" s="2" t="s">
+        <v>694</v>
+      </c>
+      <c r="C143" s="2" t="s">
+        <v>695</v>
+      </c>
+      <c r="D143" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="E143" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F143" s="2" t="s">
+        <v>638</v>
+      </c>
+      <c r="G143" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="H143" s="2" t="s">
+        <v>696</v>
+      </c>
+      <c r="I143" s="2" t="s">
+        <v>697</v>
+      </c>
+      <c r="J143" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="144" spans="1:10">
       <c r="A144" s="2">
         <v>143</v>
       </c>
-      <c r="B144" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Backlog publish reports a green 'Published' while items silently fail to reach the system of record</t>
-        </is>
-      </c>
-      <c r="C144" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The same Jira push showed 'Published — 49 work items reconciled (20 created)' even though 29 tasks failed. reconcile_backlog ran each item with no per-item error handling and the publish response/dialog surfaced only reconciled/created — so partial failures were invisible and the reconciled count over-reported what actually landed.</t>
-        </is>
-      </c>
-      <c r="D144" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Integrations / Publish</t>
-        </is>
-      </c>
-      <c r="E144" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bug</t>
-        </is>
-      </c>
-      <c r="F144" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="G144" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P2</t>
-        </is>
-      </c>
-      <c r="H144" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">reconcile_backlog processed items in a list comprehension with no try/except, and _publish_tasktracker + the ExportPublish dialog reported only reconciled/created counts — never failures. A partial push read as a full success.</t>
-        </is>
-      </c>
-      <c r="I144" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">reconcile_backlog now isolates each item in try/except: a single item's SoR rejection is recorded (logged as a workitem.reconcile_failed event + returned in a 'failed' list) and the run continues, instead of aborting or being swallowed. The publish API returns status 'partial' plus the failed items; the artifact stores a failed count; the ExportPublish dialog now shows 'Published with some failures — N created, M failed' + the first error, instead of an all-green success. Test added in test_reconcile (per-item failure captured; epic/story still land).</t>
-        </is>
-      </c>
-      <c r="J144" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Fixed</t>
-        </is>
-      </c>
-    </row>
-    <row r="145" spans="1:10" ht="460.0" customHeight="1">
+      <c r="B144" s="2" t="s">
+        <v>698</v>
+      </c>
+      <c r="C144" s="2" t="s">
+        <v>699</v>
+      </c>
+      <c r="D144" s="2" t="s">
+        <v>700</v>
+      </c>
+      <c r="E144" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F144" s="2" t="s">
+        <v>638</v>
+      </c>
+      <c r="G144" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="H144" s="2" t="s">
+        <v>701</v>
+      </c>
+      <c r="I144" s="2" t="s">
+        <v>702</v>
+      </c>
+      <c r="J144" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="145" spans="1:10" ht="409.6" customHeight="1">
       <c r="A145" s="2">
         <v>144</v>
       </c>
-      <c r="B145" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Secret scanner false-positives on hyphenated placeholders (e.g. change-me-...) in .env.example, blocking legitimate builds</t>
-        </is>
-      </c>
-      <c r="C145" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The pre-push secret scan flagged an obvious placeholder value as a real secret, so the push was blocked and the build failed.</t>
-        </is>
-      </c>
-      <c r="D145" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Companion / Pre-push secret scan</t>
-        </is>
-      </c>
-      <c r="E145" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bug</t>
-        </is>
-      </c>
-      <c r="F145" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3c33554</t>
-        </is>
-      </c>
-      <c r="G145" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P1</t>
-        </is>
-      </c>
-      <c r="H145" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The companion's pre-push secret scanner (runner/companion/guardrails.py) blocks a push when it finds anything that looks like a hardcoded secret. Its placeholder allow-list recognised the literal token 'changeme' but NOT the far more common hyphenated/underscored form 'change-me'. So a legitimate .env.example placeholder - JWT_SECRET=change-me-minimum-32-characters-long (36 chars, Shannon entropy 3.875) - was not recognised as a placeholder, tripped the generic high-entropy heuristic, and was flagged as a 'high_entropy_secret'. The push was blocked and the build failed. This is a FALSE POSITIVE: the value is an obvious placeholder, not a real secret. It blocked WI-32 and would block any task whose example env file uses the very common change-me convention. The build agent did nothing wrong - the scanner was too aggressive.</t>
-        </is>
-      </c>
-      <c r="I145" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">FIXED (commit 3c33554). Two changes in runner/companion/guardrails.py: (1) broadened the placeholder allow-list to cover change[-_ ]?me / replace[-_ ]?me / to-be-(changed|set|replaced|filled|generated) / secret-(here|goes) / dummy / sample / redacted, so hyphenated placeholders are recognised. (2) Committed template files (.env.example, *.sample, *.template, *.dist, *.tpl) now skip the generic entropy heuristic - placeholders are expected there - while STILL running the high-precision key-format patterns (AWS AKIA..., GitHub ghp_..., PEM private keys, JWT), so a real key shape pasted into an example file is still blocked. Regression tests in backend/tests/test_guardrails.py: the exact WI-32 value + change_me/replace-me variants pass clean; a real random token in real source still blocks; AWS/GitHub key shapes inside .env.example still block; non-template source keeps the full entropy scan. 12/12 scanner tests pass.</t>
-        </is>
-      </c>
-      <c r="J145" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Fixed</t>
-        </is>
-      </c>
-    </row>
-    <row r="146" spans="1:1">
+      <c r="B145" s="2" t="s">
+        <v>703</v>
+      </c>
+      <c r="C145" s="2" t="s">
+        <v>704</v>
+      </c>
+      <c r="D145" s="2" t="s">
+        <v>631</v>
+      </c>
+      <c r="E145" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F145" s="2" t="s">
+        <v>705</v>
+      </c>
+      <c r="G145" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H145" s="2" t="s">
+        <v>706</v>
+      </c>
+      <c r="I145" s="2" t="s">
+        <v>707</v>
+      </c>
+      <c r="J145" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="146" spans="1:10">
       <c r="A146" s="2">
         <v>145</v>
       </c>
     </row>
-    <row r="147" spans="1:10" ht="460.0" customHeight="1">
+    <row r="147" spans="1:10" ht="409.6" customHeight="1">
       <c r="A147" s="2">
         <v>146</v>
       </c>
-      <c r="B147" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">AI-engine build failures (usage/rate limit, agent CLI exit 1) show a raw, unreadable message instead of a clear reason</t>
-        </is>
-      </c>
-      <c r="C147" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">When the agent CLI fails (e.g. the Anthropic usage limit is reached) the run console shows 'Command failed with exit code 1 ... Check stderr output for details' - opaque and non-actionable.</t>
-        </is>
-      </c>
-      <c r="D147" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Build pipeline / Failure observability + Companion</t>
-        </is>
-      </c>
-      <c r="E147" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bug</t>
-        </is>
-      </c>
-      <c r="F147" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">daemon.py:271</t>
-        </is>
-      </c>
-      <c r="G147" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P1</t>
-        </is>
-      </c>
-      <c r="H147" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">When the AI build agent fails to run - most commonly because the Anthropic usage/rate limit is reached, but also on any agent CLI non-zero exit - the companion's error handler (runner/companion/daemon.py ~line 271) captures only the engine driver's generic wrapper string and reports it verbatim: 'Command failed with exit code 1 (exit code: 1) / Error output: Check stderr output for details'. The platform's classify_build_failure (backend/orchestration/build_activities.py) does not recognise this signature, so the raw string passes straight through to the build.failed reason and the run console. The user sees an opaque error with no indication that the real cause was a usage limit and no guidance on what to do. This bit WI-32: the usage limit was hit during the cycle-2 remediation build and the console showed only 'Command failed with exit code 1'. Same defect class as S.No 139 (classified reasons) but for the engine/usage-limit failure path, which was not covered.</t>
-        </is>
-      </c>
-      <c r="I147" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">OPEN - Fix A planned this session (this row's owner). Two parts: (1) Companion (daemon.py): capture the agent process's stderr tail and put the actual cause in the report message instead of the placeholder 'Check stderr output for details'. (2) Platform (classify_build_failure): recognise engine / usage-limit / rate-limit signatures ('exit code 1', 'usage limit', 'rate limit', '429', 'overloaded', 'quota', 'Failed to start Claude Code') and map them to a plain-language reason, e.g. 'The AI engine hit its usage limit - the build stopped; retry when the limit resets.' NOTE: true resume-from-checkpoint on a transient failure (so a re-run continues from the last cycle instead of rebuilding) is tracked separately as S.No 147 and is owned by the other developer. Acceptance: a usage-limit failure shows a clear, non-technical reason naming the usage limit, not a raw exit-code string.</t>
-        </is>
-      </c>
-      <c r="J147" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="148" spans="1:1">
+      <c r="B147" s="2" t="s">
+        <v>708</v>
+      </c>
+      <c r="C147" s="2" t="s">
+        <v>709</v>
+      </c>
+      <c r="D147" s="2" t="s">
+        <v>710</v>
+      </c>
+      <c r="E147" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F147" s="2" t="s">
+        <v>711</v>
+      </c>
+      <c r="G147" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H147" s="2" t="s">
+        <v>712</v>
+      </c>
+      <c r="I147" s="2" t="s">
+        <v>713</v>
+      </c>
+      <c r="J147" s="2" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="148" spans="1:10" ht="210.75">
       <c r="A148" s="2">
         <v>147</v>
       </c>
-    </row>
-    <row r="149" spans="1:1">
+      <c r="B148" s="2" t="s">
+        <v>714</v>
+      </c>
+      <c r="D148" s="2" t="s">
+        <v>571</v>
+      </c>
+      <c r="E148" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G148" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="J148" s="2" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="149" spans="1:10" ht="259.5">
       <c r="A149" s="2">
         <v>148</v>
       </c>
-    </row>
-    <row r="150" spans="1:1">
+      <c r="B149" s="2" t="s">
+        <v>715</v>
+      </c>
+      <c r="D149" s="2" t="s">
+        <v>716</v>
+      </c>
+      <c r="E149" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G149" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J149" s="2" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="150" spans="1:10" ht="275.25">
       <c r="A150" s="2">
         <v>149</v>
       </c>
-    </row>
-    <row r="151" spans="1:1">
+      <c r="B150" s="2" t="s">
+        <v>717</v>
+      </c>
+      <c r="D150" s="2" t="s">
+        <v>718</v>
+      </c>
+      <c r="E150" s="2" t="s">
+        <v>719</v>
+      </c>
+      <c r="G150" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J150" s="2" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="151" spans="1:10" ht="226.5">
       <c r="A151" s="2">
         <v>150</v>
       </c>
-    </row>
-    <row r="152" spans="1:1">
+      <c r="B151" s="2" t="s">
+        <v>720</v>
+      </c>
+      <c r="D151" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="E151" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F151" s="2" t="e" vm="14">
+        <v>#VALUE!</v>
+      </c>
+      <c r="G151" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="J151" s="2" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="152" spans="1:10" ht="162">
       <c r="A152" s="2">
         <v>151</v>
       </c>
-    </row>
-    <row r="153" spans="1:1">
+      <c r="B152" s="2" t="s">
+        <v>721</v>
+      </c>
+      <c r="D152" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="E152" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F152" s="2" t="e" vm="15">
+        <v>#VALUE!</v>
+      </c>
+      <c r="G152" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="J152" s="2" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="153" spans="1:10" ht="162">
       <c r="A153" s="2">
         <v>152</v>
       </c>
-    </row>
-    <row r="154" spans="1:1">
+      <c r="B153" s="2" t="s">
+        <v>722</v>
+      </c>
+      <c r="D153" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="E153" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F153" s="2" t="e" vm="15">
+        <v>#VALUE!</v>
+      </c>
+      <c r="G153" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="J153" s="2" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="154" spans="1:10" ht="129">
       <c r="A154" s="2">
         <v>153</v>
       </c>
-    </row>
-    <row r="155" spans="1:1">
+      <c r="B154" s="2" t="s">
+        <v>723</v>
+      </c>
+      <c r="D154" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="E154" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F154" s="2" t="e" vm="16">
+        <v>#VALUE!</v>
+      </c>
+      <c r="G154" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J154" s="2" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="155" spans="1:10" ht="210.75">
       <c r="A155" s="2">
         <v>154</v>
       </c>
-    </row>
-    <row r="156" spans="1:1">
+      <c r="B155" s="2" t="s">
+        <v>724</v>
+      </c>
+      <c r="D155" s="2" t="s">
+        <v>718</v>
+      </c>
+      <c r="E155" s="2" t="s">
+        <v>719</v>
+      </c>
+      <c r="G155" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J155" s="2" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="156" spans="1:10" ht="113.25">
       <c r="A156" s="2">
         <v>155</v>
       </c>
-    </row>
-    <row r="157" spans="1:1">
+      <c r="B156" s="2" t="s">
+        <v>725</v>
+      </c>
+      <c r="D156" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="E156" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G156" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J156" s="2" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="157" spans="1:10" ht="162">
       <c r="A157" s="2">
         <v>156</v>
       </c>
-    </row>
-    <row r="158" spans="1:1">
+      <c r="B157" s="2" t="s">
+        <v>726</v>
+      </c>
+      <c r="D157" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="E157" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G157" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="J157" s="2" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="158" spans="1:10" ht="226.5">
       <c r="A158" s="2">
         <v>157</v>
       </c>
-    </row>
-    <row r="159" spans="1:1">
+      <c r="B158" s="2" t="s">
+        <v>727</v>
+      </c>
+      <c r="D158" s="2" t="s">
+        <v>728</v>
+      </c>
+      <c r="E158" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G158" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="J158" s="2" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="159" spans="1:10">
       <c r="A159" s="2">
         <v>158</v>
       </c>
     </row>
-    <row r="160" spans="1:1">
+    <row r="160" spans="1:10">
       <c r="A160" s="2">
         <v>159</v>
       </c>

--- a/docs/Bugs.xlsx
+++ b/docs/Bugs.xlsx
@@ -8135,8 +8135,20 @@
       <c r="G148" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="J148" s="2" t="s">
-        <v>141</v>
+      <c r="H148" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BOTH sides, and the PLATFORM was the hard blocker. (1) Platform: the remediation child WorkItem was created with title=finding.title and NO description at all (build_activities). Worse, the Finding dataclass had no description field and parse_findings (review_provider) SILENTLY DROPPED the agent's problem/fix/category — so even a perfectly humanized review could never reach the board; the reviewer's words were discarded before they got there. Agent 07's remediation manifest had the same hole: it was asked to fix each finding from its one-line title. (2) Agent: 08_code_review/agent.md asked for 'a concise title' with no readability directive, and its JSON example — which is what the agent actually imitates — showed terse fragments ('unbounded result set').</t>
+        </is>
+      </c>
+      <c r="I148" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mirrors the proven S.No 118 pattern. PLATFORM: Finding now carries description/problem/fix/category and parse_findings maps them through; the WorkItem gets a real humanized brief composed by _remediation_description — a plain-language severity lead, 'What's wrong', 'What to do', and a 'Where' line keeping the technical nuance (file:line, review dimension, severity, REM id). A title-only finding says so honestly instead of implying a fuller brief. _render_remediation_section now folds the same detail into agent 07's manifest. AGENT: added a 'Writing standard' to 08_code_review/agent.md mirroring 06's proven one and scoped to the verdict findings fields (title = a board item's title, problem = what is wrong AND why it matters, fix = what to actually do, self-contained, no 'see above'); made the contract explicit that title/problem/fix are read by people on the Work Items board and are required on every blocking finding; REWROTE the JSON example into properly humanized findings. Audience is a developer, so the bar is 06's: plain language that keeps the technical nuance. Tests: parse_findings carries the fields + tolerates a detail-less finding; the composed description; the child WI end-to-end; the 07 brief.</t>
+        </is>
+      </c>
+      <c r="J148" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fixed</t>
+        </is>
       </c>
     </row>
     <row r="149" spans="1:10" ht="259.5">
@@ -8198,8 +8210,20 @@
       <c r="G151" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="J151" s="2" t="s">
-        <v>141</v>
+      <c r="H151" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PhasesAndRuns rendered a plain native &lt;Select&gt; listing every work item in the project (~54), so finding one meant scrolling and eyeballing the list. The UI kit had only Input and Select — no Combobox/Autocomplete existed, so a searchable picker had to be built, not just wired up.</t>
+        </is>
+      </c>
+      <c r="I151" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Built a small reusable Combobox in the UI kit (team's choice over a filter box or a native &lt;datalist&gt;): type to filter the list in the dropdown itself, arrow keys move, Enter picks, Esc closes/reverts, click-outside closes, and it uses the standard combobox ARIA roles so screen readers announce it. Reuses the .input frame + .select chevron so it looks identical to the other controls, and says 'No work items match' rather than showing an empty box. Swapped into the Phases &amp; Runs work-item picker; available for any other long list. Tests (Combobox.test.tsx): filters as you type + click to pick, keyboard operable, empty-state, and shows the current selection when closed.</t>
+        </is>
+      </c>
+      <c r="J151" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fixed</t>
+        </is>
       </c>
     </row>
     <row r="152" spans="1:10" ht="162">
@@ -8221,8 +8245,20 @@
       <c r="G152" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="J152" s="2" t="s">
-        <v>141</v>
+      <c r="H152" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">work_item_key is a BRANCH SLUG, not a display name (build_types: 'branch name + run prompt'). trigger.py builds it as caller-supplied -&gt; the Jira id (TASK-001) -&gt; a fallback of 'WI-&lt;first 8 chars of the uuid&gt;'. Three places used it as a title: the Code Review artifact, the Code artifact, and the GitHub PR title (so it leaked to the system of record too). Rows that looked fine were agent-authored: open_build_pr / run_code_review are register-don't-recreate and never overwrite the agent's title — so bad names were always the platform's own fallback. The frontend was NOT at fault (artifactLabel already prefers the title).</t>
+        </is>
+      </c>
+      <c r="I152" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Added work_item_title to BuildInput, populated in trigger.py from work_item.title, and a display_name() helper that prefers the title and falls back to the key only when there is no title. The Code artifact, the Code Review artifact and the PR title now read the task title; work_item_key still names the branch, and the PR body carries it for traceability. Passed on the input rather than read from the DB inside the activity, so activities stay deterministic for Temporal replay. Tests: display_name prefers the title / falls back on blank+whitespace; artifacts + PR title carry the task title while the key stays in the body.</t>
+        </is>
+      </c>
+      <c r="J152" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fixed</t>
+        </is>
       </c>
     </row>
     <row r="153" spans="1:10" ht="162">
@@ -8244,8 +8280,20 @@
       <c r="G153" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="J153" s="2" t="s">
-        <v>141</v>
+      <c r="H153" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The BUILD path had no publish step at all. The planning path has publish_artifacts_core, which publishes EVERY artifact of the run; the build path published exactly one — merge_build_pr_core grabbed only the single type='code' row. Grepping Status.PUBLISHED across orchestration returned only those two hits, so nothing else COULD publish them: the Assumptions and Code Review artifacts stayed Draft forever even though their gate was approved. Not intentional — 'internal' is those artifacts' SoR, not a lifecycle status, and the planning path deliberately publishes internal-SoR artifacts. A gap, not a decision.</t>
+        </is>
+      </c>
+      <c r="I153" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Added publish_build_artifacts_core mirroring the planning path's publish_artifacts_core and called it from BuildWorkflow after merge_build_pr: it publishes every artifact of the run, skips already-published ones, and takes an immutable S3 audit snapshot of any body-bearing artifact. It changes ONLY `status` — each artifact already carries its correct SoR from registration (code -&gt; git, review -&gt; internal), so this is structurally incapable of clobbering the code pointer's sor=git. Run.status=COMPLETED and the artifacts.published event moved out of merge into publish, so a run can no longer report 'completed' while its artifacts are still draft; merge now performs only the gated SoR write. Idempotent for Temporal retries/replays. Tests: publishes all three artifact types (not just code), sor=git + the PR pointer survive, snapshot written, idempotent, and the merge/publish split; the phase-2 acceptance replay test was extended through the new step.</t>
+        </is>
+      </c>
+      <c r="J153" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fixed</t>
+        </is>
       </c>
     </row>
     <row r="154" spans="1:10" ht="129">
@@ -8327,8 +8375,20 @@
       <c r="G157" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="J157" s="2" t="s">
-        <v>141</v>
+      <c r="H157" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TWO independent causes, plus a latent data-loss bug found while investigating. (1) ROTATION — a UI deadlock; the backend was always fine (update_integration happily re-encrypts a new secret). ConnectCapability rendered the editable secret input ONLY when secrets[field] was already non-empty — and the only control that could set it was that very input, so it could never appear. The help text 'Enter a new value only to rotate it' described something unreachable. (2) TEST-BEFORE-SAVE — test_integration_connection was NOT a live probe (its own docstring said it proves the capability+vendor pair is constructible and a secret is stored, not that the API is reachable), AND the endpoint was detail=True + get_object(), so it structurally REQUIRED a saved row: that is why saving first was forced. (3) DATA LOSS (latent, proven by a failing test before fixing): the drawer sends secrets:{} whenever an admin edits a configured connection without retyping the token (e.g. changing only the project key). {} is not None, so update_integration re-encrypted an empty dict and SILENTLY WIPED the stored credential — the test showed `configured` flipping to False.</t>
+        </is>
+      </c>
+      <c r="I157" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(1) Rotation: an explicit `rotating` state + a Replace button next to the Configured badge (and Cancel to keep the stored value), which breaks the deadlock; secretsComplete now requires a value only once a rotation is actually opened, so Save is never blocked by a cancelled one. (2) Data loss fixed on BOTH ends: the frontend omits the `secrets` key entirely when nothing was typed, and the server treats an empty object as 'no change' rather than 'erase' (there is deliberately no way to blank a secret via PATCH — disconnect to remove). Regression test added. (3) Test-before-save: extracted a pure probe_connection() that writes nothing to the DB, and added POST /api/integrations/test-credentials/ (detail=False) which probes a throwaway in-memory connection that is NEVER saved; test-connection still probes a saved row and records health. The frontend dropped its !savedId guard and tests as-typed credentials. (4) REAL live probes via a capability-seam ping() on Jira (/rest/api/3/myself), GitHub (/user), Confluence (/rest/api/user/current) and Figma (/v1/me) — cheap, read-only 'who am I' calls that touch no project data; vendor errors are translated into actionable messages (401/403 -&gt; credentials rejected, 404 -&gt; check the site URL, 429 -&gt; rate-limited, 5xx -&gt; vendor down). Xray keeps the wiring-only check and SAYS SO ('no live check for this vendor') rather than implying reachability. NOTE — BEHAVIOR CHANGE: Test connection now makes a real authenticated call, so credentials that used to pass the constructible-only check will now fail if they are wrong; that is the point of the fix. Two pre-existing #39 tests saved dummy creds and asserted ok=True; their intent was 'the catalog slug resolves to a registered, constructible connector', never reachability, so they now assert the failure is not a registry-miss/build error.</t>
+        </is>
+      </c>
+      <c r="J157" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fixed</t>
+        </is>
       </c>
     </row>
     <row r="158" spans="1:10" ht="226.5">
@@ -8347,13 +8407,70 @@
       <c r="G158" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="J158" s="2" t="s">
-        <v>141</v>
+      <c r="H158" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">On any error both workflows called mark_build_failed/fail_run and RETURNED — which CLOSES the Temporal history for good. A closed workflow can never be signalled, so there was nothing left to resume: the only way forward was trigger_build/trigger_phase creating a brand-new Run + workflow from step 1, re-doing the expensive build. No checkpoint existed anywhere (run.inputs is never written). Note Temporal ALREADY retries transient activity errors (3 attempts) — that was never the gap; the gap was the terminally-closed workflow.</t>
+        </is>
+      </c>
+      <c r="I158" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The workflow now PARKS instead of dying — the same pattern already proven three times here (ENH-2's merge-gate loop S.No 141, the S.No 89 non-terminal STALLED park, and the abandon_run signal). New idempotent activities park_build/park_run (STALLED + a classified reason + the step to resume from) and resume_build/resume_run_state (back to RUNNING, markers cleared), plus a _park() helper in both workflows that waits (human-paced, no timeout) for `resume_run` or `abandon_run`. Wired to: BuildWorkflow's PR/review/gate-setup errors and NON-conflict merge errors, and AgentRunWorkflow's verify_writes. dispatch_build sits OUTSIDE the retry loop, so the build itself is NEVER redone; every retried step is idempotent (open_build_pr register-don't-recreate, open_merge_gate get_or_create). A merge error resumes under the SAME approval — clicking Resume IS the human action. ENH-2's conflict loop is preserved untouched, and abandon reuses today's exact terminal path, so the worst case is today's behavior. EmptyBuild stays terminal (is_empty_build): the agent produced no changes, so resuming would fail identically forever. New POST /api/runs/{id}/resume/ + resume_stalled_run (modelled on take-over/; fires only for a run parked at a resumable error, never an S.No 89 companion-offline park). RunConsole shows the reason + 'Resume from where it stopped' / 'Take over instead'. No workflow.patched needed: the changes are on exception paths, and a workflow that had taken one would already have completed. Tests: park/resume idempotency + marker clearing, is_empty_build, resume refusing a companion-offline park, and three live-Temporal saga tests (merge-error -&gt; park -&gt; resume -&gt; merge with no rebuild; abandon -&gt; terminal; empty-build -&gt; never parked).</t>
+        </is>
+      </c>
+      <c r="J158" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fixed</t>
+        </is>
       </c>
     </row>
     <row r="159" spans="1:10">
       <c r="A159" s="2">
         <v>158</v>
+      </c>
+      <c r="B159" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A phase run can fail with no reason shown at all — the run console says it failed but the failure line is empty</t>
+        </is>
+      </c>
+      <c r="C159" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Found while investigating S.No 157. When the write-completeness check (verify_writes) rejects a phase, the run shows as failed but the console shows NO reason — the user is told only that something went wrong, with nothing to act on. Every other failure path records a readable reason; this one recorded nothing.</t>
+        </is>
+      </c>
+      <c r="D159" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Phases &amp; Runs</t>
+        </is>
+      </c>
+      <c r="E159" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bug</t>
+        </is>
+      </c>
+      <c r="F159" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G159" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P2</t>
+        </is>
+      </c>
+      <c r="H159" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">verify_writes runs with RetryPolicy(maximum_attempts=1) and NOTHING caught its error, so the exception propagated and CRASHED AgentRunWorkflow before fail_run could run. fail_run is the only thing that writes run.outputs.error — and RunConsole reads exactly that field for its failure line — so the run was left FAILED with an empty reason. Not a display bug: the reason was never recorded anywhere.</t>
+        </is>
+      </c>
+      <c r="I159" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fixed by the same change as S.No 157: verify_writes is now wrapped, and its failure PARKS the run via park_run, which always records the classified reason on run.outputs.error. So the console now shows the real reason, and the user can Resume to re-check once the missing artifact is registered instead of re-running the whole phase. Test: park_run_core records the reason and stays non-terminal.</t>
+        </is>
+      </c>
+      <c r="J159" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fixed</t>
+        </is>
       </c>
     </row>
     <row r="160" spans="1:10">

--- a/docs/Bugs.xlsx
+++ b/docs/Bugs.xlsx
@@ -7522,8 +7522,10 @@
       <c r="E128" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F128" s="2" t="s">
-        <v>615</v>
+      <c r="F128" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fix landed in commit 1258d85 on develop ("Un-draft build PRs before merge + prefer real PR ref in _code_artifact") · github.com/RAGUWING369/AI-First-SDLC-App/commit/1258d85. Walk it: backend/integrations/github/codehost.py → mark_ready_for_review(); backend/orchestration/build_activities.py → merge_build_pr_core() (un-drafts before merging, because GitHub refuses to merge a draft PR with a 405). Prove it: pytest backend/tests/test_build_activities.py -k draft</t>
+        </is>
       </c>
       <c r="G128" s="2" t="s">
         <v>13</v>
@@ -7554,8 +7556,10 @@
       <c r="E129" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F129" s="2" t="s">
-        <v>615</v>
+      <c r="F129" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Same fix as S.No 127 — commit 1258d85 on develop ("Un-draft build PRs before merge + prefer real PR ref in _code_artifact") · github.com/RAGUWING369/AI-First-SDLC-App/commit/1258d85. Walk it: backend/orchestration/build_activities.py → _code_artifact() (prefers the real PR ref over the agent's pre-PR pointer).</t>
+        </is>
       </c>
       <c r="G129" s="2" t="s">
         <v>13</v>
@@ -7586,8 +7590,10 @@
       <c r="E130" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F130" s="2" t="s">
-        <v>626</v>
+      <c r="F130" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fix landed in commit a2deeae on develop ("Trust a present APPROVED verdict in the review fail-closed guard (S.No 114)") · github.com/RAGUWING369/AI-First-SDLC-App/commit/a2deeae. Walk it: backend/orchestration/review_provider.py → parse_and_guard(). Prove it: pytest backend/tests/test_review_dispatch.py</t>
+        </is>
       </c>
       <c r="G130" s="2" t="s">
         <v>13</v>
@@ -7618,8 +7624,10 @@
       <c r="E131" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F131" s="2" t="s">
-        <v>632</v>
+      <c r="F131" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fix landed in commit 52533c4 on develop ("Surface redacted secret-scan findings on companion + in build.failed reason") · github.com/RAGUWING369/AI-First-SDLC-App/commit/52533c4. Walk it: runner/companion/runner.py (the secret-scan block that reports the redacted finding). Prove it: pytest backend/tests/test_companion_runner.py -k secret</t>
+        </is>
       </c>
       <c r="G131" s="2" t="s">
         <v>36</v>
@@ -7682,8 +7690,10 @@
       <c r="E133" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F133" s="2" t="s">
-        <v>644</v>
+      <c r="F133" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Code location (the old reference said build_activities.py:140, which has since ROTTED — line 140 is now unrelated `except CapabilityError` code; naming the function instead so it cannot rot again): backend/orchestration/build_activities.py → open_build_pr_core() sets set_commit_status(context="sdlc/build", state="pending") and nothing ever sets it to success/failure afterwards. Grep to see it for yourself: grep -rn 'sdlc/build' backend/orchestration/build_activities.py</t>
+        </is>
       </c>
       <c r="G133" s="2" t="s">
         <v>23</v>
@@ -7874,8 +7884,10 @@
       <c r="E139" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F139" s="2" t="s">
-        <v>674</v>
+      <c r="F139" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Evidence: a single RunnerEnrollment row is shared by two developers, so a run started by either is attributed to the same enrollment. See it for yourself — GET /api/runners/ returns one enrollment for the project (the id seen when this was logged was 32db7f5f). Code: backend/apps/runs/models.py → RunnerEnrollment (project + developer), and backend/orchestration/trigger.py → _resolve_enrollment(), which picks the enrollment for the triggering user.</t>
+        </is>
       </c>
       <c r="G139" s="2" t="s">
         <v>36</v>
@@ -8066,8 +8078,10 @@
       <c r="E145" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F145" s="2" t="s">
-        <v>705</v>
+      <c r="F145" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fix landed in commit 3c33554 on develop ("Fix secret-scan false positive on hyphenated placeholders (Bugs S.No 143)") · github.com/RAGUWING369/AI-First-SDLC-App/commit/3c33554 (the commit message says S.No 143; the sheet row is 144 — the sheet is correct). Walk it: runner/companion/guardrails.py (the placeholder allow-list). Prove it: pytest backend/tests/test_guardrails.py -k placeholder  (scoped on purpose — running the whole file also picks up test_run_build_clean_change_reports_ok, which fails for an unrelated, pre-existing reason: it needs real git workspace access. That failure is not this fix.)</t>
+        </is>
       </c>
       <c r="G145" s="2" t="s">
         <v>13</v>
@@ -8103,8 +8117,10 @@
       <c r="E147" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F147" s="2" t="s">
-        <v>711</v>
+      <c r="F147" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fix landed in commit 6f9671f on develop ("Make AI-engine / usage-limit build failures human-readable (Bugs S.No 146)") · github.com/RAGUWING369/AI-First-SDLC-App/commit/6f9671f. NOTE the old reference said daemon.py:271, which has ROTTED (that line is now a bare `except`); the real code is: backend/drivers/claude_driver.py (captures the engine's stderr tail) and backend/orchestration/build_activities.py → classify_build_failure() (turns a raw usage/rate-limit error into a plain-language reason). Prove it: pytest backend/tests/test_build_activities.py -k classify. This row is still marked Open — the code fix has landed but is awaiting the team's live test.</t>
+        </is>
       </c>
       <c r="G147" s="2" t="s">
         <v>13</v>
@@ -8131,6 +8147,11 @@
       </c>
       <c r="E148" s="2" t="s">
         <v>12</v>
+      </c>
+      <c r="F148" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Evidence — reproduce on any build with blocking findings: the remediation child work items on the Work Items board show a bare title and an EMPTY description. Root of the evidence trail, verifiable by reading the code: backend/orchestration/review_provider.py → parse_findings() read only rem/severity/title/file/line and silently dropped the agent's `problem`/`fix`/`category`, and build_activities.py → run_code_review_core() created the WorkItem with no description at all — so the reviewer's words could not reach the board. The agent's own contract already emits those fields: see the verdict JSON example in agents/08_code_review/agent.md.</t>
+        </is>
       </c>
       <c r="G148" s="2" t="s">
         <v>36</v>
@@ -8142,7 +8163,7 @@
       </c>
       <c r="I148" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mirrors the proven S.No 118 pattern. PLATFORM: Finding now carries description/problem/fix/category and parse_findings maps them through; the WorkItem gets a real humanized brief composed by _remediation_description — a plain-language severity lead, 'What's wrong', 'What to do', and a 'Where' line keeping the technical nuance (file:line, review dimension, severity, REM id). A title-only finding says so honestly instead of implying a fuller brief. _render_remediation_section now folds the same detail into agent 07's manifest. AGENT: added a 'Writing standard' to 08_code_review/agent.md mirroring 06's proven one and scoped to the verdict findings fields (title = a board item's title, problem = what is wrong AND why it matters, fix = what to actually do, self-contained, no 'see above'); made the contract explicit that title/problem/fix are read by people on the Work Items board and are required on every blocking finding; REWROTE the JSON example into properly humanized findings. Audience is a developer, so the bar is 06's: plain language that keeps the technical nuance. Tests: parse_findings carries the fields + tolerates a detail-less finding; the composed description; the child WI end-to-end; the 07 brief.</t>
+          <t xml:space="preserve">Mirrors the proven S.No 118 pattern. PLATFORM: Finding now carries description/problem/fix/category and parse_findings maps them through; the WorkItem gets a real humanized brief composed by _remediation_description — a plain-language severity lead, 'What's wrong', 'What to do', and a 'Where' line keeping the technical nuance (file:line, review dimension, severity, REM id). A title-only finding says so honestly instead of implying a fuller brief. _render_remediation_section now folds the same detail into agent 07's manifest. AGENT: added a 'Writing standard' to 08_code_review/agent.md mirroring 06's proven one and scoped to the verdict findings fields (title = a board item's title, problem = what is wrong AND why it matters, fix = what to actually do, self-contained, no 'see above'); made the contract explicit that title/problem/fix are read by people on the Work Items board and are required on every blocking finding; REWROTE the JSON example into properly humanized findings. Audience is a developer, so the bar is 06's: plain language that keeps the technical nuance. Tests: parse_findings carries the fields + tolerates a detail-less finding; the composed description; the child WI end-to-end; the 07 brief. — REVIEW THE FIX: landed in commit 2a8bc23 on develop ("Fix artifact naming, build publish, remediation briefs, WI search, integrations (S.No 151/152/147/150/156)") · github.com/RAGUWING369/AI-First-SDLC-App/commit/2a8bc23. Walk it: backend/orchestration/review_provider.py → parse_findings() (now carries problem/fix/category); backend/orchestration/build_activities.py → Finding, _remediation_description() (builds the brief), _render_remediation_section() (gives agent 07 the same detail); agents/08_code_review/agent.md → 'Writing standard' + the rewritten verdict JSON example. Prove it: pytest backend/tests/test_build_activities.py -k remediation and pytest backend/tests/test_build_agents_migration.py -k parse_findings</t>
         </is>
       </c>
       <c r="J148" s="2" t="inlineStr">
@@ -8217,7 +8238,7 @@
       </c>
       <c r="I151" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Built a small reusable Combobox in the UI kit (team's choice over a filter box or a native &lt;datalist&gt;): type to filter the list in the dropdown itself, arrow keys move, Enter picks, Esc closes/reverts, click-outside closes, and it uses the standard combobox ARIA roles so screen readers announce it. Reuses the .input frame + .select chevron so it looks identical to the other controls, and says 'No work items match' rather than showing an empty box. Swapped into the Phases &amp; Runs work-item picker; available for any other long list. Tests (Combobox.test.tsx): filters as you type + click to pick, keyboard operable, empty-state, and shows the current selection when closed.</t>
+          <t xml:space="preserve">Built a small reusable Combobox in the UI kit (team's choice over a filter box or a native &lt;datalist&gt;): type to filter the list in the dropdown itself, arrow keys move, Enter picks, Esc closes/reverts, click-outside closes, and it uses the standard combobox ARIA roles so screen readers announce it. Reuses the .input frame + .select chevron so it looks identical to the other controls, and says 'No work items match' rather than showing an empty box. Swapped into the Phases &amp; Runs work-item picker; available for any other long list. Tests (Combobox.test.tsx): filters as you type + click to pick, keyboard operable, empty-state, and shows the current selection when closed. — REVIEW THE FIX: landed in commit 2a8bc23 on develop ("Fix artifact naming, build publish, remediation briefs, WI search, integrations (S.No 151/152/147/150/156)") · github.com/RAGUWING369/AI-First-SDLC-App/commit/2a8bc23. Walk it: frontend/src/components/ui/index.tsx → Combobox (new reusable component); frontend/src/features/lifecycle/PhasesAndRuns.tsx (the picker now uses it); frontend/src/styles/components.css (.combobox*). Prove it: cd frontend &amp;&amp; npx vitest run src/components/ui/Combobox.test.tsx</t>
         </is>
       </c>
       <c r="J151" s="2" t="inlineStr">
@@ -8252,7 +8273,7 @@
       </c>
       <c r="I152" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Added work_item_title to BuildInput, populated in trigger.py from work_item.title, and a display_name() helper that prefers the title and falls back to the key only when there is no title. The Code artifact, the Code Review artifact and the PR title now read the task title; work_item_key still names the branch, and the PR body carries it for traceability. Passed on the input rather than read from the DB inside the activity, so activities stay deterministic for Temporal replay. Tests: display_name prefers the title / falls back on blank+whitespace; artifacts + PR title carry the task title while the key stays in the body.</t>
+          <t xml:space="preserve">Added work_item_title to BuildInput, populated in trigger.py from work_item.title, and a display_name() helper that prefers the title and falls back to the key only when there is no title. The Code artifact, the Code Review artifact and the PR title now read the task title; work_item_key still names the branch, and the PR body carries it for traceability. Passed on the input rather than read from the DB inside the activity, so activities stay deterministic for Temporal replay. Tests: display_name prefers the title / falls back on blank+whitespace; artifacts + PR title carry the task title while the key stays in the body. — REVIEW THE FIX: landed in commit 2a8bc23 on develop ("Fix artifact naming, build publish, remediation briefs, WI search, integrations (S.No 151/152/147/150/156)") · github.com/RAGUWING369/AI-First-SDLC-App/commit/2a8bc23. Walk it: backend/orchestration/build_types.py → BuildInput.work_item_title + display_name(); backend/orchestration/trigger.py (populates it from work_item.title); backend/orchestration/build_activities.py → open_build_pr_core() (PR title + Code artifact) and run_code_review_core() (Code Review artifact). Prove it: pytest backend/tests/test_build_activities.py -k "display_name or task_title"</t>
         </is>
       </c>
       <c r="J152" s="2" t="inlineStr">
@@ -8287,7 +8308,7 @@
       </c>
       <c r="I153" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Added publish_build_artifacts_core mirroring the planning path's publish_artifacts_core and called it from BuildWorkflow after merge_build_pr: it publishes every artifact of the run, skips already-published ones, and takes an immutable S3 audit snapshot of any body-bearing artifact. It changes ONLY `status` — each artifact already carries its correct SoR from registration (code -&gt; git, review -&gt; internal), so this is structurally incapable of clobbering the code pointer's sor=git. Run.status=COMPLETED and the artifacts.published event moved out of merge into publish, so a run can no longer report 'completed' while its artifacts are still draft; merge now performs only the gated SoR write. Idempotent for Temporal retries/replays. Tests: publishes all three artifact types (not just code), sor=git + the PR pointer survive, snapshot written, idempotent, and the merge/publish split; the phase-2 acceptance replay test was extended through the new step.</t>
+          <t xml:space="preserve">Added publish_build_artifacts_core mirroring the planning path's publish_artifacts_core and called it from BuildWorkflow after merge_build_pr: it publishes every artifact of the run, skips already-published ones, and takes an immutable S3 audit snapshot of any body-bearing artifact. It changes ONLY `status` — each artifact already carries its correct SoR from registration (code -&gt; git, review -&gt; internal), so this is structurally incapable of clobbering the code pointer's sor=git. Run.status=COMPLETED and the artifacts.published event moved out of merge into publish, so a run can no longer report 'completed' while its artifacts are still draft; merge now performs only the gated SoR write. Idempotent for Temporal retries/replays. Tests: publishes all three artifact types (not just code), sor=git + the PR pointer survive, snapshot written, idempotent, and the merge/publish split; the phase-2 acceptance replay test was extended through the new step. — REVIEW THE FIX: landed in commit 2a8bc23 on develop ("Fix artifact naming, build publish, remediation briefs, WI search, integrations (S.No 151/152/147/150/156)") · github.com/RAGUWING369/AI-First-SDLC-App/commit/2a8bc23. Walk it: backend/orchestration/build_activities.py → publish_build_artifacts_core() (new; mirrors the planning path's publish_artifacts_core in backend/orchestration/activities.py — compare them side-by-side) and merge_build_pr_core() (now does only the gated write); backend/orchestration/build_workflow.py (calls publish_build_artifacts after the merge). Prove it: pytest backend/tests/test_build_activities.py -k publish_build</t>
         </is>
       </c>
       <c r="J153" s="2" t="inlineStr">
@@ -8372,6 +8393,11 @@
       <c r="E157" s="2" t="s">
         <v>12</v>
       </c>
+      <c r="F157" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Evidence (1) rotation deadlock — Integrations → any configured capability → the secret field renders a disabled 'configured' box with no way to type a new value; the input was gated on secrets[field] being non-empty while the only control that could set it was that same input (frontend/src/features/setup/ConnectCapability.tsx). Evidence (2) DATA LOSS, reproduced by a test written BEFORE the fix — PATCH /api/integrations/{id}/ with {"binding": {...}, "secrets": {}} (exactly what the drawer sends when you edit a configured connection without retyping the token) returned 200 with configured=False and the stored token destroyed. Verbatim failure: `assert resp.data["configured"] is True` -&gt; `assert False is True`. Re-run it yourself: pytest backend/tests/test_integrations_admin.py -k empty_secrets_object. Evidence (3) not-a-live-probe — the old docstring on backend/apps/integrations/services.py → test_integration_connection() stated it proves the pair is 'constructible and a secret has been stored, not that the upstream API is currently reachable'.</t>
+        </is>
+      </c>
       <c r="G157" s="2" t="s">
         <v>36</v>
       </c>
@@ -8382,7 +8408,7 @@
       </c>
       <c r="I157" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">(1) Rotation: an explicit `rotating` state + a Replace button next to the Configured badge (and Cancel to keep the stored value), which breaks the deadlock; secretsComplete now requires a value only once a rotation is actually opened, so Save is never blocked by a cancelled one. (2) Data loss fixed on BOTH ends: the frontend omits the `secrets` key entirely when nothing was typed, and the server treats an empty object as 'no change' rather than 'erase' (there is deliberately no way to blank a secret via PATCH — disconnect to remove). Regression test added. (3) Test-before-save: extracted a pure probe_connection() that writes nothing to the DB, and added POST /api/integrations/test-credentials/ (detail=False) which probes a throwaway in-memory connection that is NEVER saved; test-connection still probes a saved row and records health. The frontend dropped its !savedId guard and tests as-typed credentials. (4) REAL live probes via a capability-seam ping() on Jira (/rest/api/3/myself), GitHub (/user), Confluence (/rest/api/user/current) and Figma (/v1/me) — cheap, read-only 'who am I' calls that touch no project data; vendor errors are translated into actionable messages (401/403 -&gt; credentials rejected, 404 -&gt; check the site URL, 429 -&gt; rate-limited, 5xx -&gt; vendor down). Xray keeps the wiring-only check and SAYS SO ('no live check for this vendor') rather than implying reachability. NOTE — BEHAVIOR CHANGE: Test connection now makes a real authenticated call, so credentials that used to pass the constructible-only check will now fail if they are wrong; that is the point of the fix. Two pre-existing #39 tests saved dummy creds and asserted ok=True; their intent was 'the catalog slug resolves to a registered, constructible connector', never reachability, so they now assert the failure is not a registry-miss/build error.</t>
+          <t xml:space="preserve">(1) Rotation: an explicit `rotating` state + a Replace button next to the Configured badge (and Cancel to keep the stored value), which breaks the deadlock; secretsComplete now requires a value only once a rotation is actually opened, so Save is never blocked by a cancelled one. (2) Data loss fixed on BOTH ends: the frontend omits the `secrets` key entirely when nothing was typed, and the server treats an empty object as 'no change' rather than 'erase' (there is deliberately no way to blank a secret via PATCH — disconnect to remove). Regression test added. (3) Test-before-save: extracted a pure probe_connection() that writes nothing to the DB, and added POST /api/integrations/test-credentials/ (detail=False) which probes a throwaway in-memory connection that is NEVER saved; test-connection still probes a saved row and records health. The frontend dropped its !savedId guard and tests as-typed credentials. (4) REAL live probes via a capability-seam ping() on Jira (/rest/api/3/myself), GitHub (/user), Confluence (/rest/api/user/current) and Figma (/v1/me) — cheap, read-only 'who am I' calls that touch no project data; vendor errors are translated into actionable messages (401/403 -&gt; credentials rejected, 404 -&gt; check the site URL, 429 -&gt; rate-limited, 5xx -&gt; vendor down). Xray keeps the wiring-only check and SAYS SO ('no live check for this vendor') rather than implying reachability. NOTE — BEHAVIOR CHANGE: Test connection now makes a real authenticated call, so credentials that used to pass the constructible-only check will now fail if they are wrong; that is the point of the fix. Two pre-existing #39 tests saved dummy creds and asserted ok=True; their intent was 'the catalog slug resolves to a registered, constructible connector', never reachability, so they now assert the failure is not a registry-miss/build error. — REVIEW THE FIX: landed in commit 2a8bc23 on develop ("Fix artifact naming, build publish, remediation briefs, WI search, integrations (S.No 151/152/147/150/156)") · github.com/RAGUWING369/AI-First-SDLC-App/commit/2a8bc23. Walk it: backend/apps/integrations/services.py → probe_connection() (new pure core, no DB writes), test_credentials() (unsaved in-memory probe), update_integration() (empty secrets = no change); backend/api/views.py → IntegrationViewSet.test_credentials_action (POST /api/integrations/test-credentials/); the ping() methods on integrations/atlassian/tasktracker.py, atlassian/docstore.py, github/codehost.py, figma/designsource.py; frontend/src/features/setup/ConnectCapability.tsx (rotating state + Replace). Prove it: pytest backend/tests/test_integrations_admin.py</t>
         </is>
       </c>
       <c r="J157" s="2" t="inlineStr">
@@ -8404,6 +8430,11 @@
       <c r="E158" s="2" t="s">
         <v>12</v>
       </c>
+      <c r="F158" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Evidence — reproduce: trigger a build, make the merge fail for a non-conflict reason (e.g. a branch-protection rule on the base), and the run goes terminally FAILED; the only way forward is re-triggering, which re-runs the WHOLE build from step 1. Why it was unavoidable, verifiable in code: backend/orchestration/build_workflow.py called mark_build_failed and RETURNED, which closes the Temporal workflow — and a closed workflow can never be signalled, so there was nothing left to resume. Check the Temporal history of any failed build: it ends at that activity. Note run.inputs (backend/apps/runs/models.py) is never written — there was no checkpoint anywhere.</t>
+        </is>
+      </c>
       <c r="G158" s="2" t="s">
         <v>13</v>
       </c>
@@ -8414,7 +8445,7 @@
       </c>
       <c r="I158" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">The workflow now PARKS instead of dying — the same pattern already proven three times here (ENH-2's merge-gate loop S.No 141, the S.No 89 non-terminal STALLED park, and the abandon_run signal). New idempotent activities park_build/park_run (STALLED + a classified reason + the step to resume from) and resume_build/resume_run_state (back to RUNNING, markers cleared), plus a _park() helper in both workflows that waits (human-paced, no timeout) for `resume_run` or `abandon_run`. Wired to: BuildWorkflow's PR/review/gate-setup errors and NON-conflict merge errors, and AgentRunWorkflow's verify_writes. dispatch_build sits OUTSIDE the retry loop, so the build itself is NEVER redone; every retried step is idempotent (open_build_pr register-don't-recreate, open_merge_gate get_or_create). A merge error resumes under the SAME approval — clicking Resume IS the human action. ENH-2's conflict loop is preserved untouched, and abandon reuses today's exact terminal path, so the worst case is today's behavior. EmptyBuild stays terminal (is_empty_build): the agent produced no changes, so resuming would fail identically forever. New POST /api/runs/{id}/resume/ + resume_stalled_run (modelled on take-over/; fires only for a run parked at a resumable error, never an S.No 89 companion-offline park). RunConsole shows the reason + 'Resume from where it stopped' / 'Take over instead'. No workflow.patched needed: the changes are on exception paths, and a workflow that had taken one would already have completed. Tests: park/resume idempotency + marker clearing, is_empty_build, resume refusing a companion-offline park, and three live-Temporal saga tests (merge-error -&gt; park -&gt; resume -&gt; merge with no rebuild; abandon -&gt; terminal; empty-build -&gt; never parked).</t>
+          <t xml:space="preserve">The workflow now PARKS instead of dying — the same pattern already proven three times here (ENH-2's merge-gate loop S.No 141, the S.No 89 non-terminal STALLED park, and the abandon_run signal). New idempotent activities park_build/park_run (STALLED + a classified reason + the step to resume from) and resume_build/resume_run_state (back to RUNNING, markers cleared), plus a _park() helper in both workflows that waits (human-paced, no timeout) for `resume_run` or `abandon_run`. Wired to: BuildWorkflow's PR/review/gate-setup errors and NON-conflict merge errors, and AgentRunWorkflow's verify_writes. dispatch_build sits OUTSIDE the retry loop, so the build itself is NEVER redone; every retried step is idempotent (open_build_pr register-don't-recreate, open_merge_gate get_or_create). A merge error resumes under the SAME approval — clicking Resume IS the human action. ENH-2's conflict loop is preserved untouched, and abandon reuses today's exact terminal path, so the worst case is today's behavior. EmptyBuild stays terminal (is_empty_build): the agent produced no changes, so resuming would fail identically forever. New POST /api/runs/{id}/resume/ + resume_stalled_run (modelled on take-over/; fires only for a run parked at a resumable error, never an S.No 89 companion-offline park). RunConsole shows the reason + 'Resume from where it stopped' / 'Take over instead'. No workflow.patched needed: the changes are on exception paths, and a workflow that had taken one would already have completed. Tests: park/resume idempotency + marker clearing, is_empty_build, resume refusing a companion-offline park, and three live-Temporal saga tests (merge-error -&gt; park -&gt; resume -&gt; merge with no rebuild; abandon -&gt; terminal; empty-build -&gt; never parked). — REVIEW THE FIX: landed in commit d12d9c7 on develop ("Resume an interrupted phase instead of restarting it (Bugs S.No 157)") · github.com/RAGUWING369/AI-First-SDLC-App/commit/d12d9c7. Walk it: backend/orchestration/build_workflow.py → BuildWorkflow._park() + the resume_run/abandon_run signals; backend/orchestration/build_activities.py → park_build_core()/resume_build_core(); backend/orchestration/workflows.py → AgentRunWorkflow._park(); backend/orchestration/activities.py → park_run_core()/resume_run_state_core(); backend/orchestration/takeover.py → resume_stalled_run(); backend/api/views.py → RunViewSet.resume (POST /api/runs/{id}/resume/); build_types.py → is_empty_build(); frontend/src/features/lifecycle/RunConsole.tsx (Resume button). Prove it: pytest backend/tests/test_build_activities.py -k "park or resume or empty_build" and pytest backend/tests/test_phase_dispatch.py -k "park or resume". Live saga tests (need Temporal on localhost:7233, run ONE at a time — the file OOMs if run whole): pytest backend/tests/test_build_workflow.py::test_build_workflow_merge_error_parks_then_resumes_without_rebuilding</t>
         </is>
       </c>
       <c r="J158" s="2" t="inlineStr">
@@ -8449,7 +8480,7 @@
       </c>
       <c r="F159" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Evidence — reproduce: run a phase whose expected artifact is not registered, so the write-completeness check rejects it. The run console shows the run FAILED with an empty failure line — no reason at all. Verifiable in code: backend/orchestration/workflows.py ran verify_writes with RetryPolicy(maximum_attempts=1) and nothing caught its error, so the workflow crashed before fail_run — and fail_run is the only thing that writes run.outputs.error, which is exactly the field frontend/src/features/lifecycle/RunConsole.tsx reads for that line. Not a display bug: the reason was never recorded. Found while investigating S.No 157.</t>
         </is>
       </c>
       <c r="G159" s="2" t="inlineStr">
@@ -8464,7 +8495,7 @@
       </c>
       <c r="I159" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fixed by the same change as S.No 157: verify_writes is now wrapped, and its failure PARKS the run via park_run, which always records the classified reason on run.outputs.error. So the console now shows the real reason, and the user can Resume to re-check once the missing artifact is registered instead of re-running the whole phase. Test: park_run_core records the reason and stays non-terminal.</t>
+          <t xml:space="preserve">Fixed by the same change as S.No 157: verify_writes is now wrapped, and its failure PARKS the run via park_run, which always records the classified reason on run.outputs.error. So the console now shows the real reason, and the user can Resume to re-check once the missing artifact is registered instead of re-running the whole phase. Test: park_run_core records the reason and stays non-terminal. — REVIEW THE FIX: landed in commit d12d9c7 on develop ("Resume an interrupted phase instead of restarting it (Bugs S.No 157)") · github.com/RAGUWING369/AI-First-SDLC-App/commit/d12d9c7 (same change as S.No 157). Walk it: backend/orchestration/workflows.py (verify_writes is now wrapped in try/except and parks instead of crashing) → backend/orchestration/activities.py → park_run_core() (always records the classified reason on run.outputs.error). Prove it: pytest backend/tests/test_phase_dispatch.py -k park_run_core</t>
         </is>
       </c>
       <c r="J159" s="2" t="inlineStr">

--- a/docs/Bugs.xlsx
+++ b/docs/Bugs.xlsx
@@ -8508,6 +8508,58 @@
       <c r="A160" s="2">
         <v>159</v>
       </c>
+      <c r="B160" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Test connection reports OK without checking the repo address it was given - a mistyped repo still shows a green tick, and nothing validates it until the build phase fails</t>
+        </is>
+      </c>
+      <c r="C160" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Found live on 2026-07-17 while setting up tenant SpendLog-2 (Edvensoft-2) for the fresh single-repo end-to-end retest. The Code Host repo was saved as 'RAGUWING369/ SpendLog-2-single-repo-refresh-test' - a stray SPACE after the slash. Test connection reported success and health was written 'healthy', because the probe only asks GitHub 'who am I' (GET /user) and, by its own docstring, 'touches no repository'. The repo address - the one field the whole build depends on - is never resolved. The typo is harmless through ideation / requirements / PRD / architecture / UX / task breakdown (none of them touch the repo), and would only surface at the build phase, AFTER a full planning run, when GitHubCodeHost._repo() passes the string straight into the request path (GET /repos/RAGUWING369/ SpendLog-2-single-repo-refresh-test/branches/main) with no strip/normalisation - a 404 on a malformed URL. Same class of defect as S.No 156, one level up: 156 upgraded the probe from 'is the connector constructible' to 'is the token real' precisely because the old check 'reported OK for a mistyped token, which is exactly what a connection test exists to catch'. A mistyped REPO now reports OK for the same reason. Not GitHub-specific: the same gap applies to any connector with a configured target (Jira project key, Confluence space, Figma file, Xray).</t>
+        </is>
+      </c>
+      <c r="D160" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Integrations / Code Host / Connection test</t>
+        </is>
+      </c>
+      <c r="E160" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Enhancement</t>
+        </is>
+      </c>
+      <c r="F160" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Evidence - reproduce: in Integrations &gt; Code Host, save a repo with a typo (e.g. a space after the slash: 'OWNER/ repo-name'), then click Test connection.
+Observed: Test connection PASSES ('Signed in to GitHub as RAGUWING369.') and IntegrationConnection.health is written 'healthy', while scopes['repo'] still holds the invalid address. No warning anywhere. Live record on tenant 7828e953-987e-43b2-8d5f-c8a45bfa8c6a at 11:17-11:59 held scopes={'repo': 'RAGUWING369/ SpendLog-2-single-repo-refresh-test'} with health reported OK.
+Proof the probe cannot catch it - GitHubCodeHost.ping() in backend/integrations/github/codehost.py issues only GET /user and its docstring states it 'touches no repository'. probe_connection() in backend/apps/integrations/services.py calls exactly that ping() and returns {ok: True} on success.
+Proof the address is never normalised - GitHubCodeHost._repo() returns the configured string unchanged (no .strip()); callers such as get_branch() / open_pull_request() interpolate it directly into '/repos/{repo}/...'.
+Proof a real check is cheap and would have caught it - with the space removed, the same connector resolves the repo for real:
+  ch.ping()             -&gt; 'Signed in to GitHub as RAGUWING369.'
+  ch.get_branch(name='main') -&gt; BranchRef(sha=e252eaedb3, url=https://github.com/RAGUWING369/SpendLog-2-single-repo-refresh-test/tree/main)
+The identical call against the space version raises a 404. One extra read-only call is the whole difference.</t>
+        </is>
+      </c>
+      <c r="G160" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P3</t>
+        </is>
+      </c>
+      <c r="H160" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">probe_connection() validates CREDENTIALS only; it has no notion of the connection's configured TARGET. ping() is deliberately scoped to a cheap 'who am I' that touches no repository, and nothing else in the setup path resolves scopes['repo']. The first code that touches the repo address is the build phase, so a setup typo stays invisible until then. Compounding it, GitHubCodeHost._repo() does not strip or validate the string, so whitespace survives into the URL.</t>
+        </is>
+      </c>
+      <c r="I160" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OPEN - not fixed, logged for completeness at the team's request (2026-07-17); typo corrected by hand on SpendLog-2 so the retest could proceed. Proposed: extend probe_connection() so that where a connection carries a configured target, the probe resolves THAT too, not just /user - for codehost, a read-only get_branch(default_base) or GET /repos/{repo}; the connector already exposes everything needed. Report it as its own line ('Signed in as X; repo Y found') so the admin sees both facts. Keep it capability-generic (Jira project key, Confluence space, Figma file), not a GitHub special case, and reuse _probe_failure_detail() - its existing 404 wording ('Authenticated, but that address isn't right - check for typos') is already almost exactly the message this needs. Cheap hardening worth doing at the same time: strip the repo string on save in create_integration()/update_integration() and in GitHubCodeHost._repo(), and reject an address that is not OWNER/NAME shaped. Related: S.No 156 (same principle, one level down).</t>
+        </is>
+      </c>
+      <c r="J160" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
     </row>
     <row r="161" spans="1:1">
       <c r="A161" s="2">

--- a/docs/Bugs.xlsx
+++ b/docs/Bugs.xlsx
@@ -8561,9 +8561,75 @@
         </is>
       </c>
     </row>
-    <row r="161" spans="1:1">
+    <row r="161" spans="1:10">
       <c r="A161" s="2">
         <v>160</v>
+      </c>
+      <c r="B161" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The platform silently DISCARDS the agent's entire phase document and reports its cost as zero: every artifact the platform files itself is 0 bytes, and the gate opens on a blank page</t>
+        </is>
+      </c>
+      <c r="C161" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Found live on 2026-07-17 on tenant SpendLog-2 (Edvensoft-2), run 2894a1e0 - the first ideation of the fresh single-repo retest. The companion ran the 01_ideation agent for ~6 minutes and reported a 34,474-character document costing $0.397562. The platform stored a 0-BYTE draft, content_hash = sha256 of the empty string, and run.cost_usd = 0.0. verify_writes then PASSED (it only checks that an artifact of the expected TYPE exists, never that it has content) and the gate opened on a blank document, asking a human to approve nothing. Temporal shows a clean history with no failure anywhere: the run looks perfect from every angle the platform reports on.
+SCOPE - this bites ONLY the platform's own fallback registration, which is why it hid for so long. When the agent registers its artifacts itself (register_artifact + stage_artifact_body over MCP), that path stages the body and the artifact is fine. Across the three live tenants: SpendLog-1 56 artifacts / 1 empty; Edvensoft 170 / 2 empty; SpendLog-2 1 / 1 empty. The empties are exactly the phase-typed artifacts the platform created itself - e.g. Edvensoft 'testing/testing' empty at 08:26 on 2026-07-17 while its sibling test_case / test_report artifacts, which the agent registered, have real bodies. On run 2894a1e0 the agent registered NOTHING, so the broken fallback carried the whole phase and the loss was total.
+AGGRAVATING - the phase.empty_result event blames the ENGINE for the platform's own bug: 'companion reported ok but the engine returned no final text', when the engine had in fact returned 34,474 characters. That message sent this investigation down the wrong path for a considerable time.</t>
+        </is>
+      </c>
+      <c r="D161" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Orchestration / Phase result registration / Artifacts</t>
+        </is>
+      </c>
+      <c r="E161" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bug</t>
+        </is>
+      </c>
+      <c r="F161" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Evidence - reproduce: run any planning phase on the companion in which the agent does not register the phase artifact itself. The staged draft is 0 bytes and the run's cost is 0.0, while the companion's report holds the real body and cost.
+Observed live (run 2894a1e0, tenant 7828e953-987e-43b2-8d5f-c8a45bfa8c6a):
+  run.outputs['report'] = {'status':'ok', 'body': &lt;34474 chars&gt;, 'cost_usd': 0.397562, 'message': ''}
+  run.outputs['cost_usd'] = 0.0                    &lt;- should be 0.397562
+  run.cost_usd            = 0.0000                 &lt;- should be 0.3976
+  artifact e619681e: content_hash = sha256:e3b0c44298fc1c149afbf4c8996fb92427ae41e4649b934ca495991b7852b855
+                     (that is the sha256 of the EMPTY string), title = '', status = draft
+  S3 drafts/&lt;tenant&gt;/&lt;project&gt;/2894a1e0-.../ideation.md -&gt; get() returns b'', length 0
+The COST is the decisive proof: 0.397562 arrived and 0.0 was stored. Only a defaulted read explains both fields going wrong at once, from one line.
+Ledger events for the run, in order: run.triggered 12:09:24 / phase.dispatched 12:09:28 / phase.reported 12:15:32 {'status':'ok'} / run.executed 12:15:36 / phase.empty_result 12:15:36 'companion reported ok but the engine returned no final text; the staged phase draft is empty' (FALSE - see Description) / gate.opened 12:15:38.
+Temporal history (agent-run-2894a1e0-6b6f-4772-9b0a-cc7ad8d4376f on 13.203.56.29:7233): #5 compose_manifest, #11 dispatch_phase, #18 SIGNAL phase_reported, #23 register_phase_result, #29 verify_writes, #35 open_gate. No failures.
+Code location - register_phase_result_core() in backend/orchestration/activities.py read the report with getattr(report,'body',''), getattr(report,'cost_usd',0.0) and getattr(report,'message',''), while register_phase_result_activity(inp: AgentRunInput, report) left `report` UNANNOTATED. It was the ONLY unannotated activity parameter in backend/orchestration (whole package scanned).
+Why the tests never caught it - every existing test in backend/tests/test_phase_dispatch.py passes a real PhaseReport dataclass straight into the core, a shape production never sends; the dict only appears once the argument crosses Temporal. Proof the new regression test reproduces it: on the pre-fix code it fails with  assert b'' == b'# PRD\nreal body'.</t>
+        </is>
+      </c>
+      <c r="G161" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P1</t>
+        </is>
+      </c>
+      <c r="H161" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Temporal's data converter converts an activity argument to the type its parameter is ANNOTATED with, and hands an UNANNOTATED parameter back as the raw decoded JSON - a plain dict. register_phase_result_activity annotated `inp: AgentRunInput` (which is exactly why inp always worked) but left `report` bare, so the PhaseReport arrived as a dict. register_phase_result_core then read it with getattr, which looks up an ATTRIBUTE - a dict has none - so getattr returned its DEFAULT for every field: body '' and cost_usd 0.0. Nothing raised. The defaults are indistinguishable from an engine that genuinely produced nothing, which is precisely what the phase.empty_result message then asserted.
+verify_writes could not save it either: verify_write_completeness_core asserts only that an artifact of the expected TYPE exists, never that its body is non-empty - so the platform's own 0-byte row satisfied the last check before the gate.</t>
+        </is>
+      </c>
+      <c r="I161" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IN PROGRESS (2026-07-17) - fixed locally, NOT committed, pending team test. Three parts, all in backend/orchestration/activities.py:
+1. ROOT FIX - annotate the activity: register_phase_result_activity(inp: AgentRunInput, report: PhaseReport). Temporal now converts the payload to a PhaseReport, matching the `inp` parameter that always worked. A test asserts the annotation stays put, so it cannot be silently dropped again.
+2. DEFENCE - new _as_phase_report() coerces dict / PhaseReport / duck-typed object to a PhaseReport, and the core reads report.body / report.cost_usd / report.message directly - no getattr on a possible dict anywhere in the path. The cores are also called directly by tests and by the takeover path, so both shapes must keep working.
+3. HONESTY - the phase.empty_result message no longer reads the report via getattr, so it can no longer blame the engine for the platform's own defaulted read.
+Tests (backend/tests/test_phase_dispatch.py): test_register_phase_result_core_reads_a_dict_report sends the exact wire shape Temporal delivers and asserts the body is staged, the hash is not the empty-file hash, and the cost survives (run.cost_usd is a 4dp Decimal column, so the stored value is the rounded 0.3976). test_register_phase_result_activity_annotates_its_report_param guards the root fix. Both fail on the pre-fix code and pass after.
+Verified: test_phase_dispatch 26 passed / 3 skipped; test_orchestration_activities + test_acceptance_phase45 + test_acceptance_phase47 = 14 passed / 1 failed, that 1 being the PRE-EXISTING test_offline_companion_parks_for_takeover, which fails identically without this change (logged as S.No 161).
+NOT fixed here, deliberately: verify_writes still passes an empty artifact (it checks type presence, not content). Logged separately so the last line of defence is fixed on its own merits rather than as a side effect. Related: S.No 59 (the other half of this seam - pointer-only artifacts never staged), S.No 158 (verify_writes crash).</t>
+        </is>
+      </c>
+      <c r="J161" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">In Progress</t>
+        </is>
       </c>
     </row>
     <row r="162" spans="1:1">

--- a/docs/Bugs.xlsx
+++ b/docs/Bugs.xlsx
@@ -8642,14 +8642,104 @@
         <v>162</v>
       </c>
     </row>
-    <row r="164" spans="1:1">
+    <row r="164" spans="1:10">
       <c r="A164" s="2">
         <v>163</v>
       </c>
-    </row>
-    <row r="165" spans="1:1">
+      <c r="B164" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Clarification gate surfaced only Tier-1 (must-ask) questions - Tier-2 suggestions and Tier-3 inferences never reached the user</t>
+        </is>
+      </c>
+      <c r="C164" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The SDLC app promises a human is always in the loop and the platform never silently assumes. But agents classified each context gap into three tiers and only surfaced Tier 1 through the clarifications gate. Tier 2 (the agent's own suggestions) was written inline inside the deliverable, and Tier 3 (industry-standard inferences) was logged silently as assumptions the user never saw. So the user could not confirm or override the agent's Tier-2/3 choices, and the 'no silent assumptions' assurance was only partly true.</t>
+        </is>
+      </c>
+      <c r="D164" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Clarifications / Context Gap Scan</t>
+        </is>
+      </c>
+      <c r="E164" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Enhancement</t>
+        </is>
+      </c>
+      <c r="F164" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Observed live across Ideation, Requirements and PRD runs on tenant Edvensoft-2: every phase logged Tier-3 items as assumptions and opened 0 clarifications, so the user never saw the agent's inferences. Verified in code: ask_human was the only human-question touchpoint and the shared rules told agents to front-load only Tier 1 and Tier 2. Retested after the fix on a live UX-design run - a single gate now shows Tier 1/2/3 sections.</t>
+        </is>
+      </c>
+      <c r="G164" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P2</t>
+        </is>
+      </c>
+      <c r="H164" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The behaviour lived in the shared agent rules (backend/manifest/rules/prompt_rules.py): agents were told to 'front-load ALL Tier-1 and Tier-2 questions' and to record every Tier-3 inference silently as an assumption. Only Tier 1 was required/blocking; nothing surfaced Tier 2 or Tier 3 through the clarifications gate. The tier definitions were also thin (one line each), so classification was inconsistent.</t>
+        </is>
+      </c>
+      <c r="I164" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Reworked the shared rules so the agent front-loads ALL three tiers into ONE clarifications gate before starting work, each question tagged with its tier. Tier 1 stays required; Tier 2/3 are optional and carry the agent's proposed answer as a pre-filled 'suggestion' the user can accept, edit or override, with an 'Accept all' one-click. Any untouched Tier-2/3 item falls back to the suggestion, and the confirmed Tier-3 values are still recorded as assumptions for provenance. Also strengthened the tier definitions (a four-question test plus concrete examples per tier). The web gate groups questions under Tier 1/2/3 headers. No DB migration (questions are stored as JSON). Landed on develop in commit 0c19292; backend + frontend tests, type-checks and lint all pass; user-tested on a live UX-design run.</t>
+        </is>
+      </c>
+      <c r="J164" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fixed</t>
+        </is>
+      </c>
+    </row>
+    <row r="165" spans="1:10">
       <c r="A165" s="2">
         <v>164</v>
+      </c>
+      <c r="B165" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Platform does not verify the agent's tier classification - a mislabelled Tier-1 gap can still slip through as a Tier-3 guess</t>
+        </is>
+      </c>
+      <c r="C165" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Even with all three tiers now surfaced in the gate, the platform trusts the agent's own Tier 1/2/3 labelling. If the agent wrongly files a business-critical gap (for example pricing, compliance or a third-party integration) as a Tier-3 inference, it is shown pre-filled and quietly accepted rather than hard-asked. So the 'never assume' assurance still depends on the agent classifying correctly and the human reviewer noticing at the gate.</t>
+        </is>
+      </c>
+      <c r="D165" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Clarifications / Context Gap Scan</t>
+        </is>
+      </c>
+      <c r="E165" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Enhancement</t>
+        </is>
+      </c>
+      <c r="F165" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Design gap, not a live failure. ask_human and create_clarification carry no tier logic (runner/companion/state_mcp.py, backend/apps/clarifications/services.py); the tier reasoning lives only in the agent prompt (backend/manifest/rules/prompt_rules.py). No validator checks a question or assumption against the hard-coded Tier-1 'never infer' category list.</t>
+        </is>
+      </c>
+      <c r="G165" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P3</t>
+        </is>
+      </c>
+      <c r="H165" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">By design, tier classification is the agent's own reasoning; there is no control-plane check. The platform records and delivers whatever tiers the agent labels, and only a human reviewer reading the gate or the Assumptions Log can catch a misclassification.</t>
+        </is>
+      </c>
+      <c r="I165" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Proposed (future): a platform-side validator that scans each phase's questions and assumptions for the Tier-1 'never infer' categories and auto-promotes any match to a required Tier-1 question before the gate can close - turning tier classification from 'trust the agent' into 'the platform double-checks the high-risk categories'. Not yet implemented.</t>
+        </is>
+      </c>
+      <c r="J165" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
       </c>
     </row>
     <row r="166" spans="1:1">

--- a/docs/Bugs.xlsx
+++ b/docs/Bugs.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30306"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30305"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="166" documentId="11_14FDEAE3397E350B81F2A24CBED9C52169691D91" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{285B08F5-3480-48DB-957D-3CBD7D1D2C50}"/>
+  <xr:revisionPtr revIDLastSave="175" documentId="11_14FDEAE3397E350B81F2A24CBED9C52169691D91" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{77C94B95-75A2-4B7D-95F4-DEC09B2B7B6F}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
   <metadataTypes count="1">
     <metadataType name="XLRICHVALUE" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1"/>
   </metadataTypes>
-  <futureMetadata name="XLRICHVALUE" count="16">
+  <futureMetadata name="XLRICHVALUE" count="17">
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
@@ -151,8 +151,15 @@
         </ext>
       </extLst>
     </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="16"/>
+        </ext>
+      </extLst>
+    </bk>
   </futureMetadata>
-  <valueMetadata count="16">
+  <valueMetadata count="17">
     <bk>
       <rc t="1" v="0"/>
     </bk>
@@ -201,12 +208,15 @@
     <bk>
       <rc t="1" v="15"/>
     </bk>
+    <bk>
+      <rc t="1" v="16"/>
+    </bk>
   </valueMetadata>
 </metadata>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1249" uniqueCount="729">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1314" uniqueCount="775">
   <si>
     <t>S.No</t>
   </si>
@@ -2178,7 +2188,7 @@
     <t>Build pipeline / Merge gate</t>
   </si>
   <si>
-    <t>1258d85</t>
+    <t>Fix landed in commit 1258d85 on develop ("Un-draft build PRs before merge + prefer real PR ref in _code_artifact") · github.com/RAGUWING369/AI-First-SDLC-App/commit/1258d85. Walk it: backend/integrations/github/codehost.py → mark_ready_for_review(); backend/orchestration/build_activities.py → merge_build_pr_core() (un-drafts before merging, because GitHub refuses to merge a draft PR with a 405). Prove it: pytest backend/tests/test_build_activities.py -k draft</t>
   </si>
   <si>
     <t>During the automated 07&lt;-&gt;08 review-and-fix loop the platform opens the build's pull request as a GitHub 'draft' PR (a draft blocks a premature human merge while review is still running). GitHub does not allow a draft PR to be merged - its merge API returns HTTP 405 (Method Not Allowed). So the moment a human approved the merge gate, the final merge step always failed. The work item got stuck at the very last step, never transitioned to done, and nothing downstream could complete. This was the single blocker stopping any build from finishing.</t>
@@ -2196,6 +2206,9 @@
     <t>Build pipeline / Review loop</t>
   </si>
   <si>
+    <t>Same fix as S.No 127 — commit 1258d85 on develop ("Un-draft build PRs before merge + prefer real PR ref in _code_artifact") · github.com/RAGUWING369/AI-First-SDLC-App/commit/1258d85. Walk it: backend/orchestration/build_activities.py → _code_artifact() (prefers the real PR ref over the agent's pre-PR pointer).</t>
+  </si>
+  <si>
     <t>The helper that looks up a build's code artifact (_code_artifact) fetched 'the first matching artifact' with no defined ordering. A single work item can have more than one code-artifact row: an early placeholder the agent registers before the PR exists, and the real one that carries the pull-request reference (repo/number/url). With no ORDER BY, the database returned rows in an arbitrary order, so the code sometimes picked the early placeholder that has no PR link. The reviewer then had nothing to look at and reported 'no opened PR to review', which broke the remediation cycle.</t>
   </si>
   <si>
@@ -2211,7 +2224,7 @@
     <t>Build pipeline / Review guard (S.No 114 guard)</t>
   </si>
   <si>
-    <t>a2deeae</t>
+    <t>Fix landed in commit a2deeae on develop ("Trust a present APPROVED verdict in the review fail-closed guard (S.No 114)") · github.com/RAGUWING369/AI-First-SDLC-App/commit/a2deeae. Walk it: backend/orchestration/review_provider.py → parse_and_guard(). Prove it: pytest backend/tests/test_review_dispatch.py</t>
   </si>
   <si>
     <t>The review guard is deliberately 'fail-closed': if a review's prose looks like it demands changes but the structured verdict does not clearly say so, it blocks - to stop bad code slipping through. The old prose matcher (_looks_blocking) scanned the entire review text for blocking-sounding words. An APPROVED review referenced an already-RESOLVED finding by its ID (for example 'REM-W1'), and the matcher saw that mention and concluded the review was demanding changes. Result: a legitimately approved review was blocked and the build could not proceed - a false positive that halted good work.</t>
@@ -2229,7 +2242,7 @@
     <t>Companion / Pre-push secret scan</t>
   </si>
   <si>
-    <t>52533c4</t>
+    <t>Fix landed in commit 52533c4 on develop ("Surface redacted secret-scan findings on companion + in build.failed reason") · github.com/RAGUWING369/AI-First-SDLC-App/commit/52533c4. Walk it: runner/companion/runner.py (the secret-scan block that reports the redacted finding). Prove it: pytest backend/tests/test_companion_runner.py -k secret</t>
   </si>
   <si>
     <t>Before pushing code the companion (the worker on the developer machine) scans the changed files for hardcoded secrets (passwords, API keys, tokens, private keys). When it finds one it correctly blocks the push and reports the build as failed - but it only reported a bare count ('N finding(s)'). It did not surface which secret type, which file, or which line, and it then tore down the temporary work folder, so the evidence was gone. Operators saw 'build failed' with no way to know why or how to fix it, making the block undiagnosable.</t>
@@ -2265,7 +2278,7 @@
     <t>Build pipeline / Commit status reporting</t>
   </si>
   <si>
-    <t>build_activities.py:140</t>
+    <t>Code location (the old reference said build_activities.py:140, which has since ROTTED — line 140 is now unrelated `except CapabilityError` code; naming the function instead so it cannot rot again): backend/orchestration/build_activities.py → open_build_pr_core() sets set_commit_status(context="sdlc/build", state="pending") and nothing ever sets it to success/failure afterwards. Grep to see it for yourself: grep -rn 'sdlc/build' backend/orchestration/build_activities.py</t>
   </si>
   <si>
     <t>When the build PR is opened, the platform posts a GitHub commit status with context 'sdlc/build' and state 'pending' against the head commit (build_activities.py line 140, best-effort - exceptions are swallowed). Nothing anywhere later updates that status to 'success' or 'failure'. So every build's commit shows the 'sdlc/build' check stuck on pending indefinitely. It is dormant today only because no branch-protection rule on the repo currently requires the 'sdlc/build' context to be green before merging. The day someone enables such a required check, merges will be blocked forever because the status can never reach success - a latent time-bomb, and misleading status UI in the meantime.</t>
@@ -2355,7 +2368,7 @@
     <t>Tenancy / Enrollment identity</t>
   </si>
   <si>
-    <t>enrollment 32db7f5f</t>
+    <t>Evidence: a single RunnerEnrollment row is shared by two developers, so a run started by either is attributed to the same enrollment. See it for yourself — GET /api/runners/ returns one enrollment for the project (the id seen when this was logged was 32db7f5f). Code: backend/apps/runs/models.py → RunnerEnrollment (project + developer), and backend/orchestration/trigger.py → _resolve_enrollment(), which picks the enrollment for the triggering user.</t>
   </si>
   <si>
     <t>During testing it was found that two different developers are operating under the same enrollment record (enrollment id 32db7f5f, under tenant 212395b8). Enrollment is meant to identify a single developer's participation in a project; sharing one record between two people means their runs, claims and attribution can be conflated, and any per-developer isolation or accounting keyed on enrollment is wrong. It also muddies debugging (whose companion claimed what) and could let one developer's actions appear under the other's identity.</t>
@@ -2448,7 +2461,7 @@
     <t>The pre-push secret scan flagged an obvious placeholder value as a real secret, so the push was blocked and the build failed.</t>
   </si>
   <si>
-    <t>3c33554</t>
+    <t>Fix landed in commit 3c33554 on develop ("Fix secret-scan false positive on hyphenated placeholders (Bugs S.No 143)") · github.com/RAGUWING369/AI-First-SDLC-App/commit/3c33554 (the commit message says S.No 143; the sheet row is 144 — the sheet is correct). Walk it: runner/companion/guardrails.py (the placeholder allow-list). Prove it: pytest backend/tests/test_guardrails.py -k placeholder  (scoped on purpose — running the whole file also picks up test_run_build_clean_change_reports_ok, which fails for an unrelated, pre-existing reason: it needs real git workspace access. That failure is not this fix.)</t>
   </si>
   <si>
     <t>The companion's pre-push secret scanner (runner/companion/guardrails.py) blocks a push when it finds anything that looks like a hardcoded secret. Its placeholder allow-list recognised the literal token 'changeme' but NOT the far more common hyphenated/underscored form 'change-me'. So a legitimate .env.example placeholder - JWT_SECRET=change-me-minimum-32-characters-long (36 chars, Shannon entropy 3.875) - was not recognised as a placeholder, tripped the generic high-entropy heuristic, and was flagged as a 'high_entropy_secret'. The push was blocked and the build failed. This is a FALSE POSITIVE: the value is an obvious placeholder, not a real secret. It blocked WI-32 and would block any task whose example env file uses the very common change-me convention. The build agent did nothing wrong - the scanner was too aggressive.</t>
@@ -2466,7 +2479,7 @@
     <t>Build pipeline / Failure observability + Companion</t>
   </si>
   <si>
-    <t>daemon.py:271</t>
+    <t>Fix landed in commit 6f9671f on develop ("Make AI-engine / usage-limit build failures human-readable (Bugs S.No 146)") · github.com/RAGUWING369/AI-First-SDLC-App/commit/6f9671f. NOTE the old reference said daemon.py:271, which has ROTTED (that line is now a bare `except`); the real code is: backend/drivers/claude_driver.py (captures the engine's stderr tail) and backend/orchestration/build_activities.py → classify_build_failure() (turns a raw usage/rate-limit error into a plain-language reason). Prove it: pytest backend/tests/test_build_activities.py -k classify. This row is still marked Open — the code fix has landed but is awaiting the team's live test.</t>
   </si>
   <si>
     <t>When the AI build agent fails to run - most commonly because the Anthropic usage/rate limit is reached, but also on any agent CLI non-zero exit - the companion's error handler (runner/companion/daemon.py ~line 271) captures only the engine driver's generic wrapper string and reports it verbatim: 'Command failed with exit code 1 (exit code: 1) / Error output: Check stderr output for details'. The platform's classify_build_failure (backend/orchestration/build_activities.py) does not recognise this signature, so the raw string passes straight through to the build.failed reason and the run console. The user sees an opaque error with no indication that the real cause was a usage limit and no guidance on what to do. This bit WI-32: the usage limit was hit during the cycle-2 remediation build and the console showed only 'Command failed with exit code 1'. Same defect class as S.No 139 (classified reasons) but for the engine/usage-limit failure path, which was not covered.</t>
@@ -2476,6 +2489,15 @@
   </si>
   <si>
     <t>When the implementation of a Work Item is completed and give it away for the review agent - The review agent is doing its job and creating Remediation Work Items (if blocking or critical issues are present): The created Remediation Work Item Tasks are too technical and not humasined and high level</t>
+  </si>
+  <si>
+    <t>Evidence — reproduce on any build with blocking findings: the remediation child work items on the Work Items board show a bare title and an EMPTY description. Root of the evidence trail, verifiable by reading the code: backend/orchestration/review_provider.py → parse_findings() read only rem/severity/title/file/line and silently dropped the agent's `problem`/`fix`/`category`, and build_activities.py → run_code_review_core() created the WorkItem with no description at all — so the reviewer's words could not reach the board. The agent's own contract already emits those fields: see the verdict JSON example in agents/08_code_review/agent.md.</t>
+  </si>
+  <si>
+    <t>BOTH sides, and the PLATFORM was the hard blocker. (1) Platform: the remediation child WorkItem was created with title=finding.title and NO description at all (build_activities). Worse, the Finding dataclass had no description field and parse_findings (review_provider) SILENTLY DROPPED the agent's problem/fix/category — so even a perfectly humanized review could never reach the board; the reviewer's words were discarded before they got there. Agent 07's remediation manifest had the same hole: it was asked to fix each finding from its one-line title. (2) Agent: 08_code_review/agent.md asked for 'a concise title' with no readability directive, and its JSON example — which is what the agent actually imitates — showed terse fragments ('unbounded result set').</t>
+  </si>
+  <si>
+    <t>Mirrors the proven S.No 118 pattern. PLATFORM: Finding now carries description/problem/fix/category and parse_findings maps them through; the WorkItem gets a real humanized brief composed by _remediation_description — a plain-language severity lead, 'What's wrong', 'What to do', and a 'Where' line keeping the technical nuance (file:line, review dimension, severity, REM id). A title-only finding says so honestly instead of implying a fuller brief. _render_remediation_section now folds the same detail into agent 07's manifest. AGENT: added a 'Writing standard' to 08_code_review/agent.md mirroring 06's proven one and scoped to the verdict findings fields (title = a board item's title, problem = what is wrong AND why it matters, fix = what to actually do, self-contained, no 'see above'); made the contract explicit that title/problem/fix are read by people on the Work Items board and are required on every blocking finding; REWROTE the JSON example into properly humanized findings. Audience is a developer, so the bar is 06's: plain language that keeps the technical nuance. Tests: parse_findings carries the fields + tolerates a detail-less finding; the composed description; the child WI end-to-end; the 07 brief. — REVIEW THE FIX: landed in commit 2a8bc23 on develop ("Fix artifact naming, build publish, remediation briefs, WI search, integrations (S.No 151/152/147/150/156)") · github.com/RAGUWING369/AI-First-SDLC-App/commit/2a8bc23. Walk it: backend/orchestration/review_provider.py → parse_findings() (now carries problem/fix/category); backend/orchestration/build_activities.py → Finding, _remediation_description() (builds the brief), _render_remediation_section() (gives agent 07 the same detail); agents/08_code_review/agent.md → 'Writing standard' + the rewritten verdict JSON example. Prove it: pytest backend/tests/test_build_activities.py -k remediation and pytest backend/tests/test_build_agents_migration.py -k parse_findings</t>
   </si>
   <si>
     <t>In Implementation Phase:
@@ -2501,13 +2523,31 @@
 Currently all created Work Items are shown in a drop down but if the created work items count reaches huge number it would be difficult for the user to find his work item. Instead we will give him a search option in the drop down itself - this way he can search for his work item and use the drop down also.</t>
   </si>
   <si>
+    <t>PhasesAndRuns rendered a plain native &lt;Select&gt; listing every work item in the project (~54), so finding one meant scrolling and eyeballing the list. The UI kit had only Input and Select — no Combobox/Autocomplete existed, so a searchable picker had to be built, not just wired up.</t>
+  </si>
+  <si>
+    <t>Built a small reusable Combobox in the UI kit (team's choice over a filter box or a native &lt;datalist&gt;): type to filter the list in the dropdown itself, arrow keys move, Enter picks, Esc closes/reverts, click-outside closes, and it uses the standard combobox ARIA roles so screen readers announce it. Reuses the .input frame + .select chevron so it looks identical to the other controls, and says 'No work items match' rather than showing an empty box. Swapped into the Phases &amp; Runs work-item picker; available for any other long list. Tests (Combobox.test.tsx): filters as you type + click to pick, keyboard operable, empty-state, and shows the current selection when closed. — REVIEW THE FIX: landed in commit 2a8bc23 on develop ("Fix artifact naming, build publish, remediation briefs, WI search, integrations (S.No 151/152/147/150/156)") · github.com/RAGUWING369/AI-First-SDLC-App/commit/2a8bc23. Walk it: frontend/src/components/ui/index.tsx → Combobox (new reusable component); frontend/src/features/lifecycle/PhasesAndRuns.tsx (the picker now uses it); frontend/src/styles/components.css (.combobox*). Prove it: cd frontend &amp;&amp; npx vitest run src/components/ui/Combobox.test.tsx</t>
+  </si>
+  <si>
     <t>In the Artifacts &amp; Traceability page:
 1. The artifacts names for Code review, PR - should have task title/name to identify easily instead of only WI-ID
 Note: See the reference image for clarity</t>
   </si>
   <si>
+    <t>work_item_key is a BRANCH SLUG, not a display name (build_types: 'branch name + run prompt'). trigger.py builds it as caller-supplied -&gt; the Jira id (TASK-001) -&gt; a fallback of 'WI-&lt;first 8 chars of the uuid&gt;'. Three places used it as a title: the Code Review artifact, the Code artifact, and the GitHub PR title (so it leaked to the system of record too). Rows that looked fine were agent-authored: open_build_pr / run_code_review are register-don't-recreate and never overwrite the agent's title — so bad names were always the platform's own fallback. The frontend was NOT at fault (artifactLabel already prefers the title).</t>
+  </si>
+  <si>
+    <t>Added work_item_title to BuildInput, populated in trigger.py from work_item.title, and a display_name() helper that prefers the title and falls back to the key only when there is no title. The Code artifact, the Code Review artifact and the PR title now read the task title; work_item_key still names the branch, and the PR body carries it for traceability. Passed on the input rather than read from the DB inside the activity, so activities stay deterministic for Temporal replay. Tests: display_name prefers the title / falls back on blank+whitespace; artifacts + PR title carry the task title while the key stays in the body. — REVIEW THE FIX: landed in commit 2a8bc23 on develop ("Fix artifact naming, build publish, remediation briefs, WI search, integrations (S.No 151/152/147/150/156)") · github.com/RAGUWING369/AI-First-SDLC-App/commit/2a8bc23. Walk it: backend/orchestration/build_types.py → BuildInput.work_item_title + display_name(); backend/orchestration/trigger.py (populates it from work_item.title); backend/orchestration/build_activities.py → open_build_pr_core() (PR title + Code artifact) and run_code_review_core() (Code Review artifact). Prove it: pytest backend/tests/test_build_activities.py -k "display_name or task_title"</t>
+  </si>
+  <si>
     <t>When the user approved the gate for implementation pahse - The artifacts: Assumptions, Implementation task/WI are still in draft state not published.
 Note: See the reference image for clarity</t>
+  </si>
+  <si>
+    <t>The BUILD path had no publish step at all. The planning path has publish_artifacts_core, which publishes EVERY artifact of the run; the build path published exactly one — merge_build_pr_core grabbed only the single type='code' row. Grepping Status.PUBLISHED across orchestration returned only those two hits, so nothing else COULD publish them: the Assumptions and Code Review artifacts stayed Draft forever even though their gate was approved. Not intentional — 'internal' is those artifacts' SoR, not a lifecycle status, and the planning path deliberately publishes internal-SoR artifacts. A gap, not a decision.</t>
+  </si>
+  <si>
+    <t>Added publish_build_artifacts_core mirroring the planning path's publish_artifacts_core and called it from BuildWorkflow after merge_build_pr: it publishes every artifact of the run, skips already-published ones, and takes an immutable S3 audit snapshot of any body-bearing artifact. It changes ONLY `status` — each artifact already carries its correct SoR from registration (code -&gt; git, review -&gt; internal), so this is structurally incapable of clobbering the code pointer's sor=git. Run.status=COMPLETED and the artifacts.published event moved out of merge into publish, so a run can no longer report 'completed' while its artifacts are still draft; merge now performs only the gated SoR write. Idempotent for Temporal retries/replays. Tests: publishes all three artifact types (not just code), sor=git + the PR pointer survive, snapshot written, idempotent, and the merge/publish split; the phase-2 acceptance replay test was extended through the new step. — REVIEW THE FIX: landed in commit 2a8bc23 on develop ("Fix artifact naming, build publish, remediation briefs, WI search, integrations (S.No 151/152/147/150/156)") · github.com/RAGUWING369/AI-First-SDLC-App/commit/2a8bc23. Walk it: backend/orchestration/build_activities.py → publish_build_artifacts_core() (new; mirrors the planning path's publish_artifacts_core in backend/orchestration/activities.py — compare them side-by-side) and merge_build_pr_core() (now does only the gated write); backend/orchestration/build_workflow.py (calls publish_build_artifacts after the merge). Prove it: pytest backend/tests/test_build_activities.py -k publish_build</t>
   </si>
   <si>
     <t>The user should be able to edit the generated phase artifacts - Task Breakdown phase, requirements phase, PRD phase etc. Right now the edit artifacts capability is missing.</t>
@@ -2525,11 +2565,149 @@
 2. THe user should test the integration connection first and then save the creds not the other way around.</t>
   </si>
   <si>
+    <t>Evidence (1) rotation deadlock — Integrations → any configured capability → the secret field renders a disabled 'configured' box with no way to type a new value; the input was gated on secrets[field] being non-empty while the only control that could set it was that same input (frontend/src/features/setup/ConnectCapability.tsx). Evidence (2) DATA LOSS, reproduced by a test written BEFORE the fix — PATCH /api/integrations/{id}/ with {"binding": {...}, "secrets": {}} (exactly what the drawer sends when you edit a configured connection without retyping the token) returned 200 with configured=False and the stored token destroyed. Verbatim failure: `assert resp.data["configured"] is True` -&gt; `assert False is True`. Re-run it yourself: pytest backend/tests/test_integrations_admin.py -k empty_secrets_object. Evidence (3) not-a-live-probe — the old docstring on backend/apps/integrations/services.py → test_integration_connection() stated it proves the pair is 'constructible and a secret has been stored, not that the upstream API is currently reachable'.</t>
+  </si>
+  <si>
+    <t>TWO independent causes, plus a latent data-loss bug found while investigating. (1) ROTATION — a UI deadlock; the backend was always fine (update_integration happily re-encrypts a new secret). ConnectCapability rendered the editable secret input ONLY when secrets[field] was already non-empty — and the only control that could set it was that very input, so it could never appear. The help text 'Enter a new value only to rotate it' described something unreachable. (2) TEST-BEFORE-SAVE — test_integration_connection was NOT a live probe (its own docstring said it proves the capability+vendor pair is constructible and a secret is stored, not that the API is reachable), AND the endpoint was detail=True + get_object(), so it structurally REQUIRED a saved row: that is why saving first was forced. (3) DATA LOSS (latent, proven by a failing test before fixing): the drawer sends secrets:{} whenever an admin edits a configured connection without retyping the token (e.g. changing only the project key). {} is not None, so update_integration re-encrypted an empty dict and SILENTLY WIPED the stored credential — the test showed `configured` flipping to False.</t>
+  </si>
+  <si>
+    <t>(1) Rotation: an explicit `rotating` state + a Replace button next to the Configured badge (and Cancel to keep the stored value), which breaks the deadlock; secretsComplete now requires a value only once a rotation is actually opened, so Save is never blocked by a cancelled one. (2) Data loss fixed on BOTH ends: the frontend omits the `secrets` key entirely when nothing was typed, and the server treats an empty object as 'no change' rather than 'erase' (there is deliberately no way to blank a secret via PATCH — disconnect to remove). Regression test added. (3) Test-before-save: extracted a pure probe_connection() that writes nothing to the DB, and added POST /api/integrations/test-credentials/ (detail=False) which probes a throwaway in-memory connection that is NEVER saved; test-connection still probes a saved row and records health. The frontend dropped its !savedId guard and tests as-typed credentials. (4) REAL live probes via a capability-seam ping() on Jira (/rest/api/3/myself), GitHub (/user), Confluence (/rest/api/user/current) and Figma (/v1/me) — cheap, read-only 'who am I' calls that touch no project data; vendor errors are translated into actionable messages (401/403 -&gt; credentials rejected, 404 -&gt; check the site URL, 429 -&gt; rate-limited, 5xx -&gt; vendor down). Xray keeps the wiring-only check and SAYS SO ('no live check for this vendor') rather than implying reachability. NOTE — BEHAVIOR CHANGE: Test connection now makes a real authenticated call, so credentials that used to pass the constructible-only check will now fail if they are wrong; that is the point of the fix. Two pre-existing #39 tests saved dummy creds and asserted ok=True; their intent was 'the catalog slug resolves to a registered, constructible connector', never reachability, so they now assert the failure is not a registry-miss/build error. — REVIEW THE FIX: landed in commit 2a8bc23 on develop ("Fix artifact naming, build publish, remediation briefs, WI search, integrations (S.No 151/152/147/150/156)") · github.com/RAGUWING369/AI-First-SDLC-App/commit/2a8bc23. Walk it: backend/apps/integrations/services.py → probe_connection() (new pure core, no DB writes), test_credentials() (unsaved in-memory probe), update_integration() (empty secrets = no change); backend/api/views.py → IntegrationViewSet.test_credentials_action (POST /api/integrations/test-credentials/); the ping() methods on integrations/atlassian/tasktracker.py, atlassian/docstore.py, github/codehost.py, figma/designsource.py; frontend/src/features/setup/ConnectCapability.tsx (rotating state + Replace). Prove it: pytest backend/tests/test_integrations_admin.py</t>
+  </si>
+  <si>
     <t>In the SDLC APP Phases and Runs: After any phase (mainly Build Phase but applies to all phases) trigger is interrupted due to any error/issue, the user should be able to continue from that point rather than starting from beginning of that phase. 
 Note: This is a very user important fix - should be applied accurately.</t>
   </si>
   <si>
     <t>Phases and Runs</t>
+  </si>
+  <si>
+    <t>Evidence — reproduce: trigger a build, make the merge fail for a non-conflict reason (e.g. a branch-protection rule on the base), and the run goes terminally FAILED; the only way forward is re-triggering, which re-runs the WHOLE build from step 1. Why it was unavoidable, verifiable in code: backend/orchestration/build_workflow.py called mark_build_failed and RETURNED, which closes the Temporal workflow — and a closed workflow can never be signalled, so there was nothing left to resume. Check the Temporal history of any failed build: it ends at that activity. Note run.inputs (backend/apps/runs/models.py) is never written — there was no checkpoint anywhere.</t>
+  </si>
+  <si>
+    <t>On any error both workflows called mark_build_failed/fail_run and RETURNED — which CLOSES the Temporal history for good. A closed workflow can never be signalled, so there was nothing left to resume: the only way forward was trigger_build/trigger_phase creating a brand-new Run + workflow from step 1, re-doing the expensive build. No checkpoint existed anywhere (run.inputs is never written). Note Temporal ALREADY retries transient activity errors (3 attempts) — that was never the gap; the gap was the terminally-closed workflow.</t>
+  </si>
+  <si>
+    <t>The workflow now PARKS instead of dying — the same pattern already proven three times here (ENH-2's merge-gate loop S.No 141, the S.No 89 non-terminal STALLED park, and the abandon_run signal). New idempotent activities park_build/park_run (STALLED + a classified reason + the step to resume from) and resume_build/resume_run_state (back to RUNNING, markers cleared), plus a _park() helper in both workflows that waits (human-paced, no timeout) for `resume_run` or `abandon_run`. Wired to: BuildWorkflow's PR/review/gate-setup errors and NON-conflict merge errors, and AgentRunWorkflow's verify_writes. dispatch_build sits OUTSIDE the retry loop, so the build itself is NEVER redone; every retried step is idempotent (open_build_pr register-don't-recreate, open_merge_gate get_or_create). A merge error resumes under the SAME approval — clicking Resume IS the human action. ENH-2's conflict loop is preserved untouched, and abandon reuses today's exact terminal path, so the worst case is today's behavior. EmptyBuild stays terminal (is_empty_build): the agent produced no changes, so resuming would fail identically forever. New POST /api/runs/{id}/resume/ + resume_stalled_run (modelled on take-over/; fires only for a run parked at a resumable error, never an S.No 89 companion-offline park). RunConsole shows the reason + 'Resume from where it stopped' / 'Take over instead'. No workflow.patched needed: the changes are on exception paths, and a workflow that had taken one would already have completed. Tests: park/resume idempotency + marker clearing, is_empty_build, resume refusing a companion-offline park, and three live-Temporal saga tests (merge-error -&gt; park -&gt; resume -&gt; merge with no rebuild; abandon -&gt; terminal; empty-build -&gt; never parked). — REVIEW THE FIX: landed in commit d12d9c7 on develop ("Resume an interrupted phase instead of restarting it (Bugs S.No 157)") · github.com/RAGUWING369/AI-First-SDLC-App/commit/d12d9c7. Walk it: backend/orchestration/build_workflow.py → BuildWorkflow._park() + the resume_run/abandon_run signals; backend/orchestration/build_activities.py → park_build_core()/resume_build_core(); backend/orchestration/workflows.py → AgentRunWorkflow._park(); backend/orchestration/activities.py → park_run_core()/resume_run_state_core(); backend/orchestration/takeover.py → resume_stalled_run(); backend/api/views.py → RunViewSet.resume (POST /api/runs/{id}/resume/); build_types.py → is_empty_build(); frontend/src/features/lifecycle/RunConsole.tsx (Resume button). Prove it: pytest backend/tests/test_build_activities.py -k "park or resume or empty_build" and pytest backend/tests/test_phase_dispatch.py -k "park or resume". Live saga tests (need Temporal on localhost:7233, run ONE at a time — the file OOMs if run whole): pytest backend/tests/test_build_workflow.py::test_build_workflow_merge_error_parks_then_resumes_without_rebuilding</t>
+  </si>
+  <si>
+    <t>A phase run can fail with no reason shown at all — the run console says it failed but the failure line is empty</t>
+  </si>
+  <si>
+    <t>Found while investigating S.No 157. When the write-completeness check (verify_writes) rejects a phase, the run shows as failed but the console shows NO reason — the user is told only that something went wrong, with nothing to act on. Every other failure path records a readable reason; this one recorded nothing.</t>
+  </si>
+  <si>
+    <t>Evidence — reproduce: run a phase whose expected artifact is not registered, so the write-completeness check rejects it. The run console shows the run FAILED with an empty failure line — no reason at all. Verifiable in code: backend/orchestration/workflows.py ran verify_writes with RetryPolicy(maximum_attempts=1) and nothing caught its error, so the workflow crashed before fail_run — and fail_run is the only thing that writes run.outputs.error, which is exactly the field frontend/src/features/lifecycle/RunConsole.tsx reads for that line. Not a display bug: the reason was never recorded. Found while investigating S.No 157.</t>
+  </si>
+  <si>
+    <t>verify_writes runs with RetryPolicy(maximum_attempts=1) and NOTHING caught its error, so the exception propagated and CRASHED AgentRunWorkflow before fail_run could run. fail_run is the only thing that writes run.outputs.error — and RunConsole reads exactly that field for its failure line — so the run was left FAILED with an empty reason. Not a display bug: the reason was never recorded anywhere.</t>
+  </si>
+  <si>
+    <t>Fixed by the same change as S.No 157: verify_writes is now wrapped, and its failure PARKS the run via park_run, which always records the classified reason on run.outputs.error. So the console now shows the real reason, and the user can Resume to re-check once the missing artifact is registered instead of re-running the whole phase. Test: park_run_core records the reason and stays non-terminal. — REVIEW THE FIX: landed in commit d12d9c7 on develop ("Resume an interrupted phase instead of restarting it (Bugs S.No 157)") · github.com/RAGUWING369/AI-First-SDLC-App/commit/d12d9c7 (same change as S.No 157). Walk it: backend/orchestration/workflows.py (verify_writes is now wrapped in try/except and parks instead of crashing) → backend/orchestration/activities.py → park_run_core() (always records the classified reason on run.outputs.error). Prove it: pytest backend/tests/test_phase_dispatch.py -k park_run_core</t>
+  </si>
+  <si>
+    <t>Test connection reports OK without checking the repo address it was given - a mistyped repo still shows a green tick, and nothing validates it until the build phase fails</t>
+  </si>
+  <si>
+    <t>Found live on 2026-07-17 while setting up tenant SpendLog-2 (Edvensoft-2) for the fresh single-repo end-to-end retest. The Code Host repo was saved as 'RAGUWING369/ SpendLog-2-single-repo-refresh-test' - a stray SPACE after the slash. Test connection reported success and health was written 'healthy', because the probe only asks GitHub 'who am I' (GET /user) and, by its own docstring, 'touches no repository'. The repo address - the one field the whole build depends on - is never resolved. The typo is harmless through ideation / requirements / PRD / architecture / UX / task breakdown (none of them touch the repo), and would only surface at the build phase, AFTER a full planning run, when GitHubCodeHost._repo() passes the string straight into the request path (GET /repos/RAGUWING369/ SpendLog-2-single-repo-refresh-test/branches/main) with no strip/normalisation - a 404 on a malformed URL. Same class of defect as S.No 156, one level up: 156 upgraded the probe from 'is the connector constructible' to 'is the token real' precisely because the old check 'reported OK for a mistyped token, which is exactly what a connection test exists to catch'. A mistyped REPO now reports OK for the same reason. Not GitHub-specific: the same gap applies to any connector with a configured target (Jira project key, Confluence space, Figma file, Xray).</t>
+  </si>
+  <si>
+    <t>Integrations / Code Host / Connection test</t>
+  </si>
+  <si>
+    <t>Evidence - reproduce: in Integrations &gt; Code Host, save a repo with a typo (e.g. a space after the slash: 'OWNER/ repo-name'), then click Test connection.
+Observed: Test connection PASSES ('Signed in to GitHub as RAGUWING369.') and IntegrationConnection.health is written 'healthy', while scopes['repo'] still holds the invalid address. No warning anywhere. Live record on tenant 7828e953-987e-43b2-8d5f-c8a45bfa8c6a at 11:17-11:59 held scopes={'repo': 'RAGUWING369/ SpendLog-2-single-repo-refresh-test'} with health reported OK.
+Proof the probe cannot catch it - GitHubCodeHost.ping() in backend/integrations/github/codehost.py issues only GET /user and its docstring states it 'touches no repository'. probe_connection() in backend/apps/integrations/services.py calls exactly that ping() and returns {ok: True} on success.
+Proof the address is never normalised - GitHubCodeHost._repo() returns the configured string unchanged (no .strip()); callers such as get_branch() / open_pull_request() interpolate it directly into '/repos/{repo}/...'.
+Proof a real check is cheap and would have caught it - with the space removed, the same connector resolves the repo for real:
+  ch.ping()             -&gt; 'Signed in to GitHub as RAGUWING369.'
+  ch.get_branch(name='main') -&gt; BranchRef(sha=e252eaedb3, url=https://github.com/RAGUWING369/SpendLog-2-single-repo-refresh-test/tree/main)
+The identical call against the space version raises a 404. One extra read-only call is the whole difference.</t>
+  </si>
+  <si>
+    <t>probe_connection() validates CREDENTIALS only; it has no notion of the connection's configured TARGET. ping() is deliberately scoped to a cheap 'who am I' that touches no repository, and nothing else in the setup path resolves scopes['repo']. The first code that touches the repo address is the build phase, so a setup typo stays invisible until then. Compounding it, GitHubCodeHost._repo() does not strip or validate the string, so whitespace survives into the URL.</t>
+  </si>
+  <si>
+    <t>OPEN - not fixed, logged for completeness at the team's request (2026-07-17); typo corrected by hand on SpendLog-2 so the retest could proceed. Proposed: extend probe_connection() so that where a connection carries a configured target, the probe resolves THAT too, not just /user - for codehost, a read-only get_branch(default_base) or GET /repos/{repo}; the connector already exposes everything needed. Report it as its own line ('Signed in as X; repo Y found') so the admin sees both facts. Keep it capability-generic (Jira project key, Confluence space, Figma file), not a GitHub special case, and reuse _probe_failure_detail() - its existing 404 wording ('Authenticated, but that address isn't right - check for typos') is already almost exactly the message this needs. Cheap hardening worth doing at the same time: strip the repo string on save in create_integration()/update_integration() and in GitHubCodeHost._repo(), and reject an address that is not OWNER/NAME shaped. Related: S.No 156 (same principle, one level down).</t>
+  </si>
+  <si>
+    <t>The platform silently DISCARDS the agent's entire phase document and reports its cost as zero: every artifact the platform files itself is 0 bytes, and the gate opens on a blank page</t>
+  </si>
+  <si>
+    <t>Found live on 2026-07-17 on tenant SpendLog-2 (Edvensoft-2), run 2894a1e0 - the first ideation of the fresh single-repo retest. The companion ran the 01_ideation agent for ~6 minutes and reported a 34,474-character document costing $0.397562. The platform stored a 0-BYTE draft, content_hash = sha256 of the empty string, and run.cost_usd = 0.0. verify_writes then PASSED (it only checks that an artifact of the expected TYPE exists, never that it has content) and the gate opened on a blank document, asking a human to approve nothing. Temporal shows a clean history with no failure anywhere: the run looks perfect from every angle the platform reports on.
+SCOPE - this bites ONLY the platform's own fallback registration, which is why it hid for so long. When the agent registers its artifacts itself (register_artifact + stage_artifact_body over MCP), that path stages the body and the artifact is fine. Across the three live tenants: SpendLog-1 56 artifacts / 1 empty; Edvensoft 170 / 2 empty; SpendLog-2 1 / 1 empty. The empties are exactly the phase-typed artifacts the platform created itself - e.g. Edvensoft 'testing/testing' empty at 08:26 on 2026-07-17 while its sibling test_case / test_report artifacts, which the agent registered, have real bodies. On run 2894a1e0 the agent registered NOTHING, so the broken fallback carried the whole phase and the loss was total.
+AGGRAVATING - the phase.empty_result event blames the ENGINE for the platform's own bug: 'companion reported ok but the engine returned no final text', when the engine had in fact returned 34,474 characters. That message sent this investigation down the wrong path for a considerable time.</t>
+  </si>
+  <si>
+    <t>Orchestration / Phase result registration / Artifacts</t>
+  </si>
+  <si>
+    <t>Evidence - reproduce: run any planning phase on the companion in which the agent does not register the phase artifact itself. The staged draft is 0 bytes and the run's cost is 0.0, while the companion's report holds the real body and cost.
+Observed live (run 2894a1e0, tenant 7828e953-987e-43b2-8d5f-c8a45bfa8c6a):
+  run.outputs['report'] = {'status':'ok', 'body': &lt;34474 chars&gt;, 'cost_usd': 0.397562, 'message': ''}
+  run.outputs['cost_usd'] = 0.0                    &lt;- should be 0.397562
+  run.cost_usd            = 0.0000                 &lt;- should be 0.3976
+  artifact e619681e: content_hash = sha256:e3b0c44298fc1c149afbf4c8996fb92427ae41e4649b934ca495991b7852b855
+                     (that is the sha256 of the EMPTY string), title = '', status = draft
+  S3 drafts/&lt;tenant&gt;/&lt;project&gt;/2894a1e0-.../ideation.md -&gt; get() returns b'', length 0
+The COST is the decisive proof: 0.397562 arrived and 0.0 was stored. Only a defaulted read explains both fields going wrong at once, from one line.
+Ledger events for the run, in order: run.triggered 12:09:24 / phase.dispatched 12:09:28 / phase.reported 12:15:32 {'status':'ok'} / run.executed 12:15:36 / phase.empty_result 12:15:36 'companion reported ok but the engine returned no final text; the staged phase draft is empty' (FALSE - see Description) / gate.opened 12:15:38.
+Temporal history (agent-run-2894a1e0-6b6f-4772-9b0a-cc7ad8d4376f on 13.203.56.29:7233): #5 compose_manifest, #11 dispatch_phase, #18 SIGNAL phase_reported, #23 register_phase_result, #29 verify_writes, #35 open_gate. No failures.
+Code location - register_phase_result_core() in backend/orchestration/activities.py read the report with getattr(report,'body',''), getattr(report,'cost_usd',0.0) and getattr(report,'message',''), while register_phase_result_activity(inp: AgentRunInput, report) left `report` UNANNOTATED. It was the ONLY unannotated activity parameter in backend/orchestration (whole package scanned).
+Why the tests never caught it - every existing test in backend/tests/test_phase_dispatch.py passes a real PhaseReport dataclass straight into the core, a shape production never sends; the dict only appears once the argument crosses Temporal. Proof the new regression test reproduces it: on the pre-fix code it fails with  assert b'' == b'# PRD\nreal body'.</t>
+  </si>
+  <si>
+    <t>Temporal's data converter converts an activity argument to the type its parameter is ANNOTATED with, and hands an UNANNOTATED parameter back as the raw decoded JSON - a plain dict. register_phase_result_activity annotated `inp: AgentRunInput` (which is exactly why inp always worked) but left `report` bare, so the PhaseReport arrived as a dict. register_phase_result_core then read it with getattr, which looks up an ATTRIBUTE - a dict has none - so getattr returned its DEFAULT for every field: body '' and cost_usd 0.0. Nothing raised. The defaults are indistinguishable from an engine that genuinely produced nothing, which is precisely what the phase.empty_result message then asserted.
+verify_writes could not save it either: verify_write_completeness_core asserts only that an artifact of the expected TYPE exists, never that its body is non-empty - so the platform's own 0-byte row satisfied the last check before the gate.</t>
+  </si>
+  <si>
+    <t>IN PROGRESS (2026-07-17) - fixed locally, NOT committed, pending team test. Three parts, all in backend/orchestration/activities.py:
+1. ROOT FIX - annotate the activity: register_phase_result_activity(inp: AgentRunInput, report: PhaseReport). Temporal now converts the payload to a PhaseReport, matching the `inp` parameter that always worked. A test asserts the annotation stays put, so it cannot be silently dropped again.
+2. DEFENCE - new _as_phase_report() coerces dict / PhaseReport / duck-typed object to a PhaseReport, and the core reads report.body / report.cost_usd / report.message directly - no getattr on a possible dict anywhere in the path. The cores are also called directly by tests and by the takeover path, so both shapes must keep working.
+3. HONESTY - the phase.empty_result message no longer reads the report via getattr, so it can no longer blame the engine for the platform's own defaulted read.
+Tests (backend/tests/test_phase_dispatch.py): test_register_phase_result_core_reads_a_dict_report sends the exact wire shape Temporal delivers and asserts the body is staged, the hash is not the empty-file hash, and the cost survives (run.cost_usd is a 4dp Decimal column, so the stored value is the rounded 0.3976). test_register_phase_result_activity_annotates_its_report_param guards the root fix. Both fail on the pre-fix code and pass after.
+Verified: test_phase_dispatch 26 passed / 3 skipped; test_orchestration_activities + test_acceptance_phase45 + test_acceptance_phase47 = 14 passed / 1 failed, that 1 being the PRE-EXISTING test_offline_companion_parks_for_takeover, which fails identically without this change (logged as S.No 161).
+NOT fixed here, deliberately: verify_writes still passes an empty artifact (it checks type presence, not content). Logged separately so the last line of defence is fixed on its own merits rather than as a side effect. Related: S.No 59 (the other half of this seam - pointer-only artifacts never staged), S.No 158 (verify_writes crash).</t>
+  </si>
+  <si>
+    <t>In Progress</t>
+  </si>
+  <si>
+    <t>Clarification gate surfaced only Tier-1 (must-ask) questions - Tier-2 suggestions and Tier-3 inferences never reached the user</t>
+  </si>
+  <si>
+    <t>The SDLC app promises a human is always in the loop and the platform never silently assumes. But agents classified each context gap into three tiers and only surfaced Tier 1 through the clarifications gate. Tier 2 (the agent's own suggestions) was written inline inside the deliverable, and Tier 3 (industry-standard inferences) was logged silently as assumptions the user never saw. So the user could not confirm or override the agent's Tier-2/3 choices, and the 'no silent assumptions' assurance was only partly true.</t>
+  </si>
+  <si>
+    <t>Clarifications / Context Gap Scan</t>
+  </si>
+  <si>
+    <t>Observed live across Ideation, Requirements and PRD runs on tenant Edvensoft-2: every phase logged Tier-3 items as assumptions and opened 0 clarifications, so the user never saw the agent's inferences. Verified in code: ask_human was the only human-question touchpoint and the shared rules told agents to front-load only Tier 1 and Tier 2. Retested after the fix on a live UX-design run - a single gate now shows Tier 1/2/3 sections.</t>
+  </si>
+  <si>
+    <t>The behaviour lived in the shared agent rules (backend/manifest/rules/prompt_rules.py): agents were told to 'front-load ALL Tier-1 and Tier-2 questions' and to record every Tier-3 inference silently as an assumption. Only Tier 1 was required/blocking; nothing surfaced Tier 2 or Tier 3 through the clarifications gate. The tier definitions were also thin (one line each), so classification was inconsistent.</t>
+  </si>
+  <si>
+    <t>Reworked the shared rules so the agent front-loads ALL three tiers into ONE clarifications gate before starting work, each question tagged with its tier. Tier 1 stays required; Tier 2/3 are optional and carry the agent's proposed answer as a pre-filled 'suggestion' the user can accept, edit or override, with an 'Accept all' one-click. Any untouched Tier-2/3 item falls back to the suggestion, and the confirmed Tier-3 values are still recorded as assumptions for provenance. Also strengthened the tier definitions (a four-question test plus concrete examples per tier). The web gate groups questions under Tier 1/2/3 headers. No DB migration (questions are stored as JSON). Landed on develop in commit 0c19292; backend + frontend tests, type-checks and lint all pass; user-tested on a live UX-design run.</t>
+  </si>
+  <si>
+    <t>Platform does not verify the agent's tier classification - a mislabelled Tier-1 gap can still slip through as a Tier-3 guess</t>
+  </si>
+  <si>
+    <t>Even with all three tiers now surfaced in the gate, the platform trusts the agent's own Tier 1/2/3 labelling. If the agent wrongly files a business-critical gap (for example pricing, compliance or a third-party integration) as a Tier-3 inference, it is shown pre-filled and quietly accepted rather than hard-asked. So the 'never assume' assurance still depends on the agent classifying correctly and the human reviewer noticing at the gate.</t>
+  </si>
+  <si>
+    <t>Design gap, not a live failure. ask_human and create_clarification carry no tier logic (runner/companion/state_mcp.py, backend/apps/clarifications/services.py); the tier reasoning lives only in the agent prompt (backend/manifest/rules/prompt_rules.py). No validator checks a question or assumption against the hard-coded Tier-1 'never infer' category list.</t>
+  </si>
+  <si>
+    <t>By design, tier classification is the agent's own reasoning; there is no control-plane check. The platform records and delivers whatever tiers the agent labels, and only a human reviewer reading the gate or the Assumptions Log can catch a misclassification.</t>
+  </si>
+  <si>
+    <t>Proposed (future): a platform-side validator that scans each phase's questions and assumptions for the Tier-1 'never infer' categories and auto-promotes any match to a required Tier-1 question before the gate can close - turning tier classification from 'trust the agent' into 'the platform double-checks the high-risk categories'. Not yet implemented.</t>
+  </si>
+  <si>
+    <t>The team has observed that in the Architecture phase of System Architecure artifact: The container and component diagrams are not rendered properly and also NFR-to-Architecture Traceability Matrix Table is over entended not fitted in the designated window. 
+Note: The above issue is observed for tenant - test2@edvensoft.com but the same issues are not present for the tenant - test@edvensoft.com. You must go through both the tenant Architecture Phase - System architecture artifact to confirm and come up with the best fix.
+Important Note: The same issues might be come up in later phases or will be observed (definitive chance) - so we need a surgical fix not temporary.</t>
   </si>
 </sst>
 </file>
@@ -3373,7 +3551,7 @@
 </file>
 
 <file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
-<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="16">
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="17">
   <rv s="0">
     <v>0</v>
     <v>5</v>
@@ -3438,6 +3616,10 @@
     <v>15</v>
     <v>5</v>
   </rv>
+  <rv s="0">
+    <v>16</v>
+    <v>5</v>
+  </rv>
 </rvData>
 </file>
 
@@ -3468,6 +3650,7 @@
   <rel r:id="rId14"/>
   <rel r:id="rId15"/>
   <rel r:id="rId16"/>
+  <rel r:id="rId17"/>
 </richValueRels>
 </file>
 
@@ -7522,10 +7705,8 @@
       <c r="E128" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F128" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Fix landed in commit 1258d85 on develop ("Un-draft build PRs before merge + prefer real PR ref in _code_artifact") · github.com/RAGUWING369/AI-First-SDLC-App/commit/1258d85. Walk it: backend/integrations/github/codehost.py → mark_ready_for_review(); backend/orchestration/build_activities.py → merge_build_pr_core() (un-drafts before merging, because GitHub refuses to merge a draft PR with a 405). Prove it: pytest backend/tests/test_build_activities.py -k draft</t>
-        </is>
+      <c r="F128" s="2" t="s">
+        <v>615</v>
       </c>
       <c r="G128" s="2" t="s">
         <v>13</v>
@@ -7556,19 +7737,17 @@
       <c r="E129" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F129" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Same fix as S.No 127 — commit 1258d85 on develop ("Un-draft build PRs before merge + prefer real PR ref in _code_artifact") · github.com/RAGUWING369/AI-First-SDLC-App/commit/1258d85. Walk it: backend/orchestration/build_activities.py → _code_artifact() (prefers the real PR ref over the agent's pre-PR pointer).</t>
-        </is>
+      <c r="F129" s="2" t="s">
+        <v>621</v>
       </c>
       <c r="G129" s="2" t="s">
         <v>13</v>
       </c>
       <c r="H129" s="2" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="I129" s="2" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="J129" s="2" t="s">
         <v>16</v>
@@ -7579,30 +7758,28 @@
         <v>129</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="D130" s="2" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="E130" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F130" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Fix landed in commit a2deeae on develop ("Trust a present APPROVED verdict in the review fail-closed guard (S.No 114)") · github.com/RAGUWING369/AI-First-SDLC-App/commit/a2deeae. Walk it: backend/orchestration/review_provider.py → parse_and_guard(). Prove it: pytest backend/tests/test_review_dispatch.py</t>
-        </is>
+      <c r="F130" s="2" t="s">
+        <v>627</v>
       </c>
       <c r="G130" s="2" t="s">
         <v>13</v>
       </c>
       <c r="H130" s="2" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="I130" s="2" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="J130" s="2" t="s">
         <v>16</v>
@@ -7613,30 +7790,28 @@
         <v>130</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="C131" s="2" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="D131" s="2" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="E131" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F131" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Fix landed in commit 52533c4 on develop ("Surface redacted secret-scan findings on companion + in build.failed reason") · github.com/RAGUWING369/AI-First-SDLC-App/commit/52533c4. Walk it: runner/companion/runner.py (the secret-scan block that reports the redacted finding). Prove it: pytest backend/tests/test_companion_runner.py -k secret</t>
-        </is>
+      <c r="F131" s="2" t="s">
+        <v>633</v>
       </c>
       <c r="G131" s="2" t="s">
         <v>36</v>
       </c>
       <c r="H131" s="2" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="I131" s="2" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="J131" s="2" t="s">
         <v>16</v>
@@ -7647,28 +7822,28 @@
         <v>131</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="C132" s="2" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="D132" s="2" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="E132" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F132" s="2" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="G132" s="2" t="s">
         <v>36</v>
       </c>
       <c r="H132" s="2" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="I132" s="2" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="J132" s="2" t="s">
         <v>16</v>
@@ -7679,30 +7854,28 @@
         <v>132</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="C133" s="2" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="D133" s="2" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="E133" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F133" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Code location (the old reference said build_activities.py:140, which has since ROTTED — line 140 is now unrelated `except CapabilityError` code; naming the function instead so it cannot rot again): backend/orchestration/build_activities.py → open_build_pr_core() sets set_commit_status(context="sdlc/build", state="pending") and nothing ever sets it to success/failure afterwards. Grep to see it for yourself: grep -rn 'sdlc/build' backend/orchestration/build_activities.py</t>
-        </is>
+      <c r="F133" s="2" t="s">
+        <v>645</v>
       </c>
       <c r="G133" s="2" t="s">
         <v>23</v>
       </c>
       <c r="H133" s="2" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="I133" s="2" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="J133" s="2" t="s">
         <v>141</v>
@@ -7713,28 +7886,28 @@
         <v>133</v>
       </c>
       <c r="B134" s="2" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="C134" s="2" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="D134" s="2" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="E134" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F134" s="2" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="G134" s="2" t="s">
         <v>13</v>
       </c>
       <c r="H134" s="2" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="I134" s="2" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="J134" s="2" t="s">
         <v>16</v>
@@ -7745,28 +7918,28 @@
         <v>134</v>
       </c>
       <c r="B135" s="2" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="C135" s="2" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="D135" s="2" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="E135" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F135" s="2" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="G135" s="2" t="s">
         <v>13</v>
       </c>
       <c r="H135" s="2" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="I135" s="2" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="J135" s="2" t="s">
         <v>16</v>
@@ -7777,28 +7950,28 @@
         <v>135</v>
       </c>
       <c r="B136" s="2" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="C136" s="2" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="D136" s="2" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="E136" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F136" s="2" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="G136" s="2" t="s">
         <v>36</v>
       </c>
       <c r="H136" s="2" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="I136" s="2" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="J136" s="2" t="s">
         <v>141</v>
@@ -7809,10 +7982,10 @@
         <v>136</v>
       </c>
       <c r="B137" s="2" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="C137" s="2" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="D137" s="2" t="s">
         <v>614</v>
@@ -7821,16 +7994,16 @@
         <v>12</v>
       </c>
       <c r="F137" s="2" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="G137" s="2" t="s">
         <v>13</v>
       </c>
       <c r="H137" s="2" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="I137" s="2" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="J137" s="2" t="s">
         <v>16</v>
@@ -7841,28 +8014,28 @@
         <v>137</v>
       </c>
       <c r="B138" s="2" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="C138" s="2" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="D138" s="2" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="E138" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F138" s="2" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="G138" s="2" t="s">
         <v>36</v>
       </c>
       <c r="H138" s="2" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="I138" s="2" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="J138" s="2" t="s">
         <v>16</v>
@@ -7873,30 +8046,28 @@
         <v>138</v>
       </c>
       <c r="B139" s="2" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="C139" s="2" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="D139" s="2" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="E139" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F139" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Evidence: a single RunnerEnrollment row is shared by two developers, so a run started by either is attributed to the same enrollment. See it for yourself — GET /api/runners/ returns one enrollment for the project (the id seen when this was logged was 32db7f5f). Code: backend/apps/runs/models.py → RunnerEnrollment (project + developer), and backend/orchestration/trigger.py → _resolve_enrollment(), which picks the enrollment for the triggering user.</t>
-        </is>
+      <c r="F139" s="2" t="s">
+        <v>675</v>
       </c>
       <c r="G139" s="2" t="s">
         <v>36</v>
       </c>
       <c r="H139" s="2" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="I139" s="2" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="J139" s="2" t="s">
         <v>141</v>
@@ -7907,28 +8078,28 @@
         <v>139</v>
       </c>
       <c r="B140" s="2" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="C140" s="2" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="D140" s="2" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="E140" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F140" s="2" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="G140" s="2" t="s">
         <v>13</v>
       </c>
       <c r="H140" s="2" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="I140" s="2" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="J140" s="2" t="s">
         <v>16</v>
@@ -7939,28 +8110,28 @@
         <v>140</v>
       </c>
       <c r="B141" s="2" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="C141" s="2" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="D141" s="2" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="E141" s="2" t="s">
         <v>22</v>
       </c>
       <c r="F141" s="2" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="G141" s="2" t="s">
         <v>36</v>
       </c>
       <c r="H141" s="2" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="I141" s="2" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="J141" s="2" t="s">
         <v>141</v>
@@ -7971,28 +8142,28 @@
         <v>141</v>
       </c>
       <c r="B142" s="2" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="C142" s="2" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="D142" s="2" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="E142" s="2" t="s">
         <v>22</v>
       </c>
       <c r="F142" s="2" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="G142" s="2" t="s">
         <v>36</v>
       </c>
       <c r="H142" s="2" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="I142" s="2" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="J142" s="2" t="s">
         <v>16</v>
@@ -8003,10 +8174,10 @@
         <v>142</v>
       </c>
       <c r="B143" s="2" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="C143" s="2" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="D143" s="2" t="s">
         <v>328</v>
@@ -8015,16 +8186,16 @@
         <v>12</v>
       </c>
       <c r="F143" s="2" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="G143" s="2" t="s">
         <v>36</v>
       </c>
       <c r="H143" s="2" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="I143" s="2" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="J143" s="2" t="s">
         <v>16</v>
@@ -8035,28 +8206,28 @@
         <v>143</v>
       </c>
       <c r="B144" s="2" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="C144" s="2" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="D144" s="2" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="E144" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F144" s="2" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="G144" s="2" t="s">
         <v>36</v>
       </c>
       <c r="H144" s="2" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="I144" s="2" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="J144" s="2" t="s">
         <v>16</v>
@@ -8067,30 +8238,28 @@
         <v>144</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="C145" s="2" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="D145" s="2" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="E145" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F145" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Fix landed in commit 3c33554 on develop ("Fix secret-scan false positive on hyphenated placeholders (Bugs S.No 143)") · github.com/RAGUWING369/AI-First-SDLC-App/commit/3c33554 (the commit message says S.No 143; the sheet row is 144 — the sheet is correct). Walk it: runner/companion/guardrails.py (the placeholder allow-list). Prove it: pytest backend/tests/test_guardrails.py -k placeholder  (scoped on purpose — running the whole file also picks up test_run_build_clean_change_reports_ok, which fails for an unrelated, pre-existing reason: it needs real git workspace access. That failure is not this fix.)</t>
-        </is>
+      <c r="F145" s="2" t="s">
+        <v>706</v>
       </c>
       <c r="G145" s="2" t="s">
         <v>13</v>
       </c>
       <c r="H145" s="2" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="I145" s="2" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="J145" s="2" t="s">
         <v>16</v>
@@ -8106,30 +8275,28 @@
         <v>146</v>
       </c>
       <c r="B147" s="2" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="C147" s="2" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="D147" s="2" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="E147" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F147" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Fix landed in commit 6f9671f on develop ("Make AI-engine / usage-limit build failures human-readable (Bugs S.No 146)") · github.com/RAGUWING369/AI-First-SDLC-App/commit/6f9671f. NOTE the old reference said daemon.py:271, which has ROTTED (that line is now a bare `except`); the real code is: backend/drivers/claude_driver.py (captures the engine's stderr tail) and backend/orchestration/build_activities.py → classify_build_failure() (turns a raw usage/rate-limit error into a plain-language reason). Prove it: pytest backend/tests/test_build_activities.py -k classify. This row is still marked Open — the code fix has landed but is awaiting the team's live test.</t>
-        </is>
+      <c r="F147" s="2" t="s">
+        <v>712</v>
       </c>
       <c r="G147" s="2" t="s">
         <v>13</v>
       </c>
       <c r="H147" s="2" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="I147" s="2" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="J147" s="2" t="s">
         <v>141</v>
@@ -8140,7 +8307,7 @@
         <v>147</v>
       </c>
       <c r="B148" s="2" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="D148" s="2" t="s">
         <v>571</v>
@@ -8148,28 +8315,20 @@
       <c r="E148" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F148" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Evidence — reproduce on any build with blocking findings: the remediation child work items on the Work Items board show a bare title and an EMPTY description. Root of the evidence trail, verifiable by reading the code: backend/orchestration/review_provider.py → parse_findings() read only rem/severity/title/file/line and silently dropped the agent's `problem`/`fix`/`category`, and build_activities.py → run_code_review_core() created the WorkItem with no description at all — so the reviewer's words could not reach the board. The agent's own contract already emits those fields: see the verdict JSON example in agents/08_code_review/agent.md.</t>
-        </is>
+      <c r="F148" s="2" t="s">
+        <v>716</v>
       </c>
       <c r="G148" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="H148" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">BOTH sides, and the PLATFORM was the hard blocker. (1) Platform: the remediation child WorkItem was created with title=finding.title and NO description at all (build_activities). Worse, the Finding dataclass had no description field and parse_findings (review_provider) SILENTLY DROPPED the agent's problem/fix/category — so even a perfectly humanized review could never reach the board; the reviewer's words were discarded before they got there. Agent 07's remediation manifest had the same hole: it was asked to fix each finding from its one-line title. (2) Agent: 08_code_review/agent.md asked for 'a concise title' with no readability directive, and its JSON example — which is what the agent actually imitates — showed terse fragments ('unbounded result set').</t>
-        </is>
-      </c>
-      <c r="I148" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Mirrors the proven S.No 118 pattern. PLATFORM: Finding now carries description/problem/fix/category and parse_findings maps them through; the WorkItem gets a real humanized brief composed by _remediation_description — a plain-language severity lead, 'What's wrong', 'What to do', and a 'Where' line keeping the technical nuance (file:line, review dimension, severity, REM id). A title-only finding says so honestly instead of implying a fuller brief. _render_remediation_section now folds the same detail into agent 07's manifest. AGENT: added a 'Writing standard' to 08_code_review/agent.md mirroring 06's proven one and scoped to the verdict findings fields (title = a board item's title, problem = what is wrong AND why it matters, fix = what to actually do, self-contained, no 'see above'); made the contract explicit that title/problem/fix are read by people on the Work Items board and are required on every blocking finding; REWROTE the JSON example into properly humanized findings. Audience is a developer, so the bar is 06's: plain language that keeps the technical nuance. Tests: parse_findings carries the fields + tolerates a detail-less finding; the composed description; the child WI end-to-end; the 07 brief. — REVIEW THE FIX: landed in commit 2a8bc23 on develop ("Fix artifact naming, build publish, remediation briefs, WI search, integrations (S.No 151/152/147/150/156)") · github.com/RAGUWING369/AI-First-SDLC-App/commit/2a8bc23. Walk it: backend/orchestration/review_provider.py → parse_findings() (now carries problem/fix/category); backend/orchestration/build_activities.py → Finding, _remediation_description() (builds the brief), _render_remediation_section() (gives agent 07 the same detail); agents/08_code_review/agent.md → 'Writing standard' + the rewritten verdict JSON example. Prove it: pytest backend/tests/test_build_activities.py -k remediation and pytest backend/tests/test_build_agents_migration.py -k parse_findings</t>
-        </is>
-      </c>
-      <c r="J148" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Fixed</t>
-        </is>
+      <c r="H148" s="2" t="s">
+        <v>717</v>
+      </c>
+      <c r="I148" s="2" t="s">
+        <v>718</v>
+      </c>
+      <c r="J148" s="2" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="149" spans="1:10" ht="259.5">
@@ -8177,10 +8336,10 @@
         <v>148</v>
       </c>
       <c r="B149" s="2" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D149" s="2" t="s">
-        <v>716</v>
+        <v>720</v>
       </c>
       <c r="E149" s="2" t="s">
         <v>22</v>
@@ -8197,13 +8356,13 @@
         <v>149</v>
       </c>
       <c r="B150" s="2" t="s">
-        <v>717</v>
+        <v>721</v>
       </c>
       <c r="D150" s="2" t="s">
-        <v>718</v>
+        <v>722</v>
       </c>
       <c r="E150" s="2" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
       <c r="G150" s="2" t="s">
         <v>23</v>
@@ -8217,7 +8376,7 @@
         <v>150</v>
       </c>
       <c r="B151" s="2" t="s">
-        <v>720</v>
+        <v>724</v>
       </c>
       <c r="D151" s="2" t="s">
         <v>130</v>
@@ -8231,20 +8390,14 @@
       <c r="G151" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="H151" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PhasesAndRuns rendered a plain native &lt;Select&gt; listing every work item in the project (~54), so finding one meant scrolling and eyeballing the list. The UI kit had only Input and Select — no Combobox/Autocomplete existed, so a searchable picker had to be built, not just wired up.</t>
-        </is>
-      </c>
-      <c r="I151" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Built a small reusable Combobox in the UI kit (team's choice over a filter box or a native &lt;datalist&gt;): type to filter the list in the dropdown itself, arrow keys move, Enter picks, Esc closes/reverts, click-outside closes, and it uses the standard combobox ARIA roles so screen readers announce it. Reuses the .input frame + .select chevron so it looks identical to the other controls, and says 'No work items match' rather than showing an empty box. Swapped into the Phases &amp; Runs work-item picker; available for any other long list. Tests (Combobox.test.tsx): filters as you type + click to pick, keyboard operable, empty-state, and shows the current selection when closed. — REVIEW THE FIX: landed in commit 2a8bc23 on develop ("Fix artifact naming, build publish, remediation briefs, WI search, integrations (S.No 151/152/147/150/156)") · github.com/RAGUWING369/AI-First-SDLC-App/commit/2a8bc23. Walk it: frontend/src/components/ui/index.tsx → Combobox (new reusable component); frontend/src/features/lifecycle/PhasesAndRuns.tsx (the picker now uses it); frontend/src/styles/components.css (.combobox*). Prove it: cd frontend &amp;&amp; npx vitest run src/components/ui/Combobox.test.tsx</t>
-        </is>
-      </c>
-      <c r="J151" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Fixed</t>
-        </is>
+      <c r="H151" s="2" t="s">
+        <v>725</v>
+      </c>
+      <c r="I151" s="2" t="s">
+        <v>726</v>
+      </c>
+      <c r="J151" s="2" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="152" spans="1:10" ht="162">
@@ -8252,7 +8405,7 @@
         <v>151</v>
       </c>
       <c r="B152" s="2" t="s">
-        <v>721</v>
+        <v>727</v>
       </c>
       <c r="D152" s="2" t="s">
         <v>93</v>
@@ -8266,20 +8419,14 @@
       <c r="G152" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="H152" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">work_item_key is a BRANCH SLUG, not a display name (build_types: 'branch name + run prompt'). trigger.py builds it as caller-supplied -&gt; the Jira id (TASK-001) -&gt; a fallback of 'WI-&lt;first 8 chars of the uuid&gt;'. Three places used it as a title: the Code Review artifact, the Code artifact, and the GitHub PR title (so it leaked to the system of record too). Rows that looked fine were agent-authored: open_build_pr / run_code_review are register-don't-recreate and never overwrite the agent's title — so bad names were always the platform's own fallback. The frontend was NOT at fault (artifactLabel already prefers the title).</t>
-        </is>
-      </c>
-      <c r="I152" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Added work_item_title to BuildInput, populated in trigger.py from work_item.title, and a display_name() helper that prefers the title and falls back to the key only when there is no title. The Code artifact, the Code Review artifact and the PR title now read the task title; work_item_key still names the branch, and the PR body carries it for traceability. Passed on the input rather than read from the DB inside the activity, so activities stay deterministic for Temporal replay. Tests: display_name prefers the title / falls back on blank+whitespace; artifacts + PR title carry the task title while the key stays in the body. — REVIEW THE FIX: landed in commit 2a8bc23 on develop ("Fix artifact naming, build publish, remediation briefs, WI search, integrations (S.No 151/152/147/150/156)") · github.com/RAGUWING369/AI-First-SDLC-App/commit/2a8bc23. Walk it: backend/orchestration/build_types.py → BuildInput.work_item_title + display_name(); backend/orchestration/trigger.py (populates it from work_item.title); backend/orchestration/build_activities.py → open_build_pr_core() (PR title + Code artifact) and run_code_review_core() (Code Review artifact). Prove it: pytest backend/tests/test_build_activities.py -k "display_name or task_title"</t>
-        </is>
-      </c>
-      <c r="J152" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Fixed</t>
-        </is>
+      <c r="H152" s="2" t="s">
+        <v>728</v>
+      </c>
+      <c r="I152" s="2" t="s">
+        <v>729</v>
+      </c>
+      <c r="J152" s="2" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="153" spans="1:10" ht="162">
@@ -8287,7 +8434,7 @@
         <v>152</v>
       </c>
       <c r="B153" s="2" t="s">
-        <v>722</v>
+        <v>730</v>
       </c>
       <c r="D153" s="2" t="s">
         <v>93</v>
@@ -8301,20 +8448,14 @@
       <c r="G153" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="H153" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The BUILD path had no publish step at all. The planning path has publish_artifacts_core, which publishes EVERY artifact of the run; the build path published exactly one — merge_build_pr_core grabbed only the single type='code' row. Grepping Status.PUBLISHED across orchestration returned only those two hits, so nothing else COULD publish them: the Assumptions and Code Review artifacts stayed Draft forever even though their gate was approved. Not intentional — 'internal' is those artifacts' SoR, not a lifecycle status, and the planning path deliberately publishes internal-SoR artifacts. A gap, not a decision.</t>
-        </is>
-      </c>
-      <c r="I153" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Added publish_build_artifacts_core mirroring the planning path's publish_artifacts_core and called it from BuildWorkflow after merge_build_pr: it publishes every artifact of the run, skips already-published ones, and takes an immutable S3 audit snapshot of any body-bearing artifact. It changes ONLY `status` — each artifact already carries its correct SoR from registration (code -&gt; git, review -&gt; internal), so this is structurally incapable of clobbering the code pointer's sor=git. Run.status=COMPLETED and the artifacts.published event moved out of merge into publish, so a run can no longer report 'completed' while its artifacts are still draft; merge now performs only the gated SoR write. Idempotent for Temporal retries/replays. Tests: publishes all three artifact types (not just code), sor=git + the PR pointer survive, snapshot written, idempotent, and the merge/publish split; the phase-2 acceptance replay test was extended through the new step. — REVIEW THE FIX: landed in commit 2a8bc23 on develop ("Fix artifact naming, build publish, remediation briefs, WI search, integrations (S.No 151/152/147/150/156)") · github.com/RAGUWING369/AI-First-SDLC-App/commit/2a8bc23. Walk it: backend/orchestration/build_activities.py → publish_build_artifacts_core() (new; mirrors the planning path's publish_artifacts_core in backend/orchestration/activities.py — compare them side-by-side) and merge_build_pr_core() (now does only the gated write); backend/orchestration/build_workflow.py (calls publish_build_artifacts after the merge). Prove it: pytest backend/tests/test_build_activities.py -k publish_build</t>
-        </is>
-      </c>
-      <c r="J153" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Fixed</t>
-        </is>
+      <c r="H153" s="2" t="s">
+        <v>731</v>
+      </c>
+      <c r="I153" s="2" t="s">
+        <v>732</v>
+      </c>
+      <c r="J153" s="2" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="154" spans="1:10" ht="129">
@@ -8322,7 +8463,7 @@
         <v>153</v>
       </c>
       <c r="B154" s="2" t="s">
-        <v>723</v>
+        <v>733</v>
       </c>
       <c r="D154" s="2" t="s">
         <v>93</v>
@@ -8345,13 +8486,13 @@
         <v>154</v>
       </c>
       <c r="B155" s="2" t="s">
-        <v>724</v>
+        <v>734</v>
       </c>
       <c r="D155" s="2" t="s">
-        <v>718</v>
+        <v>722</v>
       </c>
       <c r="E155" s="2" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
       <c r="G155" s="2" t="s">
         <v>23</v>
@@ -8365,7 +8506,7 @@
         <v>155</v>
       </c>
       <c r="B156" s="2" t="s">
-        <v>725</v>
+        <v>735</v>
       </c>
       <c r="D156" s="2" t="s">
         <v>147</v>
@@ -8385,7 +8526,7 @@
         <v>156</v>
       </c>
       <c r="B157" s="2" t="s">
-        <v>726</v>
+        <v>736</v>
       </c>
       <c r="D157" s="2" t="s">
         <v>147</v>
@@ -8393,28 +8534,20 @@
       <c r="E157" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F157" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Evidence (1) rotation deadlock — Integrations → any configured capability → the secret field renders a disabled 'configured' box with no way to type a new value; the input was gated on secrets[field] being non-empty while the only control that could set it was that same input (frontend/src/features/setup/ConnectCapability.tsx). Evidence (2) DATA LOSS, reproduced by a test written BEFORE the fix — PATCH /api/integrations/{id}/ with {"binding": {...}, "secrets": {}} (exactly what the drawer sends when you edit a configured connection without retyping the token) returned 200 with configured=False and the stored token destroyed. Verbatim failure: `assert resp.data["configured"] is True` -&gt; `assert False is True`. Re-run it yourself: pytest backend/tests/test_integrations_admin.py -k empty_secrets_object. Evidence (3) not-a-live-probe — the old docstring on backend/apps/integrations/services.py → test_integration_connection() stated it proves the pair is 'constructible and a secret has been stored, not that the upstream API is currently reachable'.</t>
-        </is>
+      <c r="F157" s="2" t="s">
+        <v>737</v>
       </c>
       <c r="G157" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="H157" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TWO independent causes, plus a latent data-loss bug found while investigating. (1) ROTATION — a UI deadlock; the backend was always fine (update_integration happily re-encrypts a new secret). ConnectCapability rendered the editable secret input ONLY when secrets[field] was already non-empty — and the only control that could set it was that very input, so it could never appear. The help text 'Enter a new value only to rotate it' described something unreachable. (2) TEST-BEFORE-SAVE — test_integration_connection was NOT a live probe (its own docstring said it proves the capability+vendor pair is constructible and a secret is stored, not that the API is reachable), AND the endpoint was detail=True + get_object(), so it structurally REQUIRED a saved row: that is why saving first was forced. (3) DATA LOSS (latent, proven by a failing test before fixing): the drawer sends secrets:{} whenever an admin edits a configured connection without retyping the token (e.g. changing only the project key). {} is not None, so update_integration re-encrypted an empty dict and SILENTLY WIPED the stored credential — the test showed `configured` flipping to False.</t>
-        </is>
-      </c>
-      <c r="I157" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(1) Rotation: an explicit `rotating` state + a Replace button next to the Configured badge (and Cancel to keep the stored value), which breaks the deadlock; secretsComplete now requires a value only once a rotation is actually opened, so Save is never blocked by a cancelled one. (2) Data loss fixed on BOTH ends: the frontend omits the `secrets` key entirely when nothing was typed, and the server treats an empty object as 'no change' rather than 'erase' (there is deliberately no way to blank a secret via PATCH — disconnect to remove). Regression test added. (3) Test-before-save: extracted a pure probe_connection() that writes nothing to the DB, and added POST /api/integrations/test-credentials/ (detail=False) which probes a throwaway in-memory connection that is NEVER saved; test-connection still probes a saved row and records health. The frontend dropped its !savedId guard and tests as-typed credentials. (4) REAL live probes via a capability-seam ping() on Jira (/rest/api/3/myself), GitHub (/user), Confluence (/rest/api/user/current) and Figma (/v1/me) — cheap, read-only 'who am I' calls that touch no project data; vendor errors are translated into actionable messages (401/403 -&gt; credentials rejected, 404 -&gt; check the site URL, 429 -&gt; rate-limited, 5xx -&gt; vendor down). Xray keeps the wiring-only check and SAYS SO ('no live check for this vendor') rather than implying reachability. NOTE — BEHAVIOR CHANGE: Test connection now makes a real authenticated call, so credentials that used to pass the constructible-only check will now fail if they are wrong; that is the point of the fix. Two pre-existing #39 tests saved dummy creds and asserted ok=True; their intent was 'the catalog slug resolves to a registered, constructible connector', never reachability, so they now assert the failure is not a registry-miss/build error. — REVIEW THE FIX: landed in commit 2a8bc23 on develop ("Fix artifact naming, build publish, remediation briefs, WI search, integrations (S.No 151/152/147/150/156)") · github.com/RAGUWING369/AI-First-SDLC-App/commit/2a8bc23. Walk it: backend/apps/integrations/services.py → probe_connection() (new pure core, no DB writes), test_credentials() (unsaved in-memory probe), update_integration() (empty secrets = no change); backend/api/views.py → IntegrationViewSet.test_credentials_action (POST /api/integrations/test-credentials/); the ping() methods on integrations/atlassian/tasktracker.py, atlassian/docstore.py, github/codehost.py, figma/designsource.py; frontend/src/features/setup/ConnectCapability.tsx (rotating state + Replace). Prove it: pytest backend/tests/test_integrations_admin.py</t>
-        </is>
-      </c>
-      <c r="J157" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Fixed</t>
-        </is>
+      <c r="H157" s="2" t="s">
+        <v>738</v>
+      </c>
+      <c r="I157" s="2" t="s">
+        <v>739</v>
+      </c>
+      <c r="J157" s="2" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="158" spans="1:10" ht="226.5">
@@ -8422,222 +8555,132 @@
         <v>157</v>
       </c>
       <c r="B158" s="2" t="s">
-        <v>727</v>
+        <v>740</v>
       </c>
       <c r="D158" s="2" t="s">
-        <v>728</v>
+        <v>741</v>
       </c>
       <c r="E158" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F158" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Evidence — reproduce: trigger a build, make the merge fail for a non-conflict reason (e.g. a branch-protection rule on the base), and the run goes terminally FAILED; the only way forward is re-triggering, which re-runs the WHOLE build from step 1. Why it was unavoidable, verifiable in code: backend/orchestration/build_workflow.py called mark_build_failed and RETURNED, which closes the Temporal workflow — and a closed workflow can never be signalled, so there was nothing left to resume. Check the Temporal history of any failed build: it ends at that activity. Note run.inputs (backend/apps/runs/models.py) is never written — there was no checkpoint anywhere.</t>
-        </is>
+      <c r="F158" s="2" t="s">
+        <v>742</v>
       </c>
       <c r="G158" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="H158" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">On any error both workflows called mark_build_failed/fail_run and RETURNED — which CLOSES the Temporal history for good. A closed workflow can never be signalled, so there was nothing left to resume: the only way forward was trigger_build/trigger_phase creating a brand-new Run + workflow from step 1, re-doing the expensive build. No checkpoint existed anywhere (run.inputs is never written). Note Temporal ALREADY retries transient activity errors (3 attempts) — that was never the gap; the gap was the terminally-closed workflow.</t>
-        </is>
-      </c>
-      <c r="I158" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The workflow now PARKS instead of dying — the same pattern already proven three times here (ENH-2's merge-gate loop S.No 141, the S.No 89 non-terminal STALLED park, and the abandon_run signal). New idempotent activities park_build/park_run (STALLED + a classified reason + the step to resume from) and resume_build/resume_run_state (back to RUNNING, markers cleared), plus a _park() helper in both workflows that waits (human-paced, no timeout) for `resume_run` or `abandon_run`. Wired to: BuildWorkflow's PR/review/gate-setup errors and NON-conflict merge errors, and AgentRunWorkflow's verify_writes. dispatch_build sits OUTSIDE the retry loop, so the build itself is NEVER redone; every retried step is idempotent (open_build_pr register-don't-recreate, open_merge_gate get_or_create). A merge error resumes under the SAME approval — clicking Resume IS the human action. ENH-2's conflict loop is preserved untouched, and abandon reuses today's exact terminal path, so the worst case is today's behavior. EmptyBuild stays terminal (is_empty_build): the agent produced no changes, so resuming would fail identically forever. New POST /api/runs/{id}/resume/ + resume_stalled_run (modelled on take-over/; fires only for a run parked at a resumable error, never an S.No 89 companion-offline park). RunConsole shows the reason + 'Resume from where it stopped' / 'Take over instead'. No workflow.patched needed: the changes are on exception paths, and a workflow that had taken one would already have completed. Tests: park/resume idempotency + marker clearing, is_empty_build, resume refusing a companion-offline park, and three live-Temporal saga tests (merge-error -&gt; park -&gt; resume -&gt; merge with no rebuild; abandon -&gt; terminal; empty-build -&gt; never parked). — REVIEW THE FIX: landed in commit d12d9c7 on develop ("Resume an interrupted phase instead of restarting it (Bugs S.No 157)") · github.com/RAGUWING369/AI-First-SDLC-App/commit/d12d9c7. Walk it: backend/orchestration/build_workflow.py → BuildWorkflow._park() + the resume_run/abandon_run signals; backend/orchestration/build_activities.py → park_build_core()/resume_build_core(); backend/orchestration/workflows.py → AgentRunWorkflow._park(); backend/orchestration/activities.py → park_run_core()/resume_run_state_core(); backend/orchestration/takeover.py → resume_stalled_run(); backend/api/views.py → RunViewSet.resume (POST /api/runs/{id}/resume/); build_types.py → is_empty_build(); frontend/src/features/lifecycle/RunConsole.tsx (Resume button). Prove it: pytest backend/tests/test_build_activities.py -k "park or resume or empty_build" and pytest backend/tests/test_phase_dispatch.py -k "park or resume". Live saga tests (need Temporal on localhost:7233, run ONE at a time — the file OOMs if run whole): pytest backend/tests/test_build_workflow.py::test_build_workflow_merge_error_parks_then_resumes_without_rebuilding</t>
-        </is>
-      </c>
-      <c r="J158" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Fixed</t>
-        </is>
+      <c r="H158" s="2" t="s">
+        <v>743</v>
+      </c>
+      <c r="I158" s="2" t="s">
+        <v>744</v>
+      </c>
+      <c r="J158" s="2" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="159" spans="1:10">
       <c r="A159" s="2">
         <v>158</v>
       </c>
-      <c r="B159" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">A phase run can fail with no reason shown at all — the run console says it failed but the failure line is empty</t>
-        </is>
-      </c>
-      <c r="C159" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Found while investigating S.No 157. When the write-completeness check (verify_writes) rejects a phase, the run shows as failed but the console shows NO reason — the user is told only that something went wrong, with nothing to act on. Every other failure path records a readable reason; this one recorded nothing.</t>
-        </is>
-      </c>
-      <c r="D159" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Phases &amp; Runs</t>
-        </is>
-      </c>
-      <c r="E159" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bug</t>
-        </is>
-      </c>
-      <c r="F159" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Evidence — reproduce: run a phase whose expected artifact is not registered, so the write-completeness check rejects it. The run console shows the run FAILED with an empty failure line — no reason at all. Verifiable in code: backend/orchestration/workflows.py ran verify_writes with RetryPolicy(maximum_attempts=1) and nothing caught its error, so the workflow crashed before fail_run — and fail_run is the only thing that writes run.outputs.error, which is exactly the field frontend/src/features/lifecycle/RunConsole.tsx reads for that line. Not a display bug: the reason was never recorded. Found while investigating S.No 157.</t>
-        </is>
-      </c>
-      <c r="G159" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P2</t>
-        </is>
-      </c>
-      <c r="H159" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">verify_writes runs with RetryPolicy(maximum_attempts=1) and NOTHING caught its error, so the exception propagated and CRASHED AgentRunWorkflow before fail_run could run. fail_run is the only thing that writes run.outputs.error — and RunConsole reads exactly that field for its failure line — so the run was left FAILED with an empty reason. Not a display bug: the reason was never recorded anywhere.</t>
-        </is>
-      </c>
-      <c r="I159" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Fixed by the same change as S.No 157: verify_writes is now wrapped, and its failure PARKS the run via park_run, which always records the classified reason on run.outputs.error. So the console now shows the real reason, and the user can Resume to re-check once the missing artifact is registered instead of re-running the whole phase. Test: park_run_core records the reason and stays non-terminal. — REVIEW THE FIX: landed in commit d12d9c7 on develop ("Resume an interrupted phase instead of restarting it (Bugs S.No 157)") · github.com/RAGUWING369/AI-First-SDLC-App/commit/d12d9c7 (same change as S.No 157). Walk it: backend/orchestration/workflows.py (verify_writes is now wrapped in try/except and parks instead of crashing) → backend/orchestration/activities.py → park_run_core() (always records the classified reason on run.outputs.error). Prove it: pytest backend/tests/test_phase_dispatch.py -k park_run_core</t>
-        </is>
-      </c>
-      <c r="J159" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Fixed</t>
-        </is>
-      </c>
-    </row>
-    <row r="160" spans="1:10">
+      <c r="B159" s="2" t="s">
+        <v>745</v>
+      </c>
+      <c r="C159" s="2" t="s">
+        <v>746</v>
+      </c>
+      <c r="D159" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="E159" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F159" s="2" t="s">
+        <v>747</v>
+      </c>
+      <c r="G159" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="H159" s="2" t="s">
+        <v>748</v>
+      </c>
+      <c r="I159" s="2" t="s">
+        <v>749</v>
+      </c>
+      <c r="J159" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="160" spans="1:10" ht="52.5" customHeight="1">
       <c r="A160" s="2">
         <v>159</v>
       </c>
-      <c r="B160" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Test connection reports OK without checking the repo address it was given - a mistyped repo still shows a green tick, and nothing validates it until the build phase fails</t>
-        </is>
-      </c>
-      <c r="C160" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Found live on 2026-07-17 while setting up tenant SpendLog-2 (Edvensoft-2) for the fresh single-repo end-to-end retest. The Code Host repo was saved as 'RAGUWING369/ SpendLog-2-single-repo-refresh-test' - a stray SPACE after the slash. Test connection reported success and health was written 'healthy', because the probe only asks GitHub 'who am I' (GET /user) and, by its own docstring, 'touches no repository'. The repo address - the one field the whole build depends on - is never resolved. The typo is harmless through ideation / requirements / PRD / architecture / UX / task breakdown (none of them touch the repo), and would only surface at the build phase, AFTER a full planning run, when GitHubCodeHost._repo() passes the string straight into the request path (GET /repos/RAGUWING369/ SpendLog-2-single-repo-refresh-test/branches/main) with no strip/normalisation - a 404 on a malformed URL. Same class of defect as S.No 156, one level up: 156 upgraded the probe from 'is the connector constructible' to 'is the token real' precisely because the old check 'reported OK for a mistyped token, which is exactly what a connection test exists to catch'. A mistyped REPO now reports OK for the same reason. Not GitHub-specific: the same gap applies to any connector with a configured target (Jira project key, Confluence space, Figma file, Xray).</t>
-        </is>
-      </c>
-      <c r="D160" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Integrations / Code Host / Connection test</t>
-        </is>
-      </c>
-      <c r="E160" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Enhancement</t>
-        </is>
-      </c>
-      <c r="F160" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Evidence - reproduce: in Integrations &gt; Code Host, save a repo with a typo (e.g. a space after the slash: 'OWNER/ repo-name'), then click Test connection.
-Observed: Test connection PASSES ('Signed in to GitHub as RAGUWING369.') and IntegrationConnection.health is written 'healthy', while scopes['repo'] still holds the invalid address. No warning anywhere. Live record on tenant 7828e953-987e-43b2-8d5f-c8a45bfa8c6a at 11:17-11:59 held scopes={'repo': 'RAGUWING369/ SpendLog-2-single-repo-refresh-test'} with health reported OK.
-Proof the probe cannot catch it - GitHubCodeHost.ping() in backend/integrations/github/codehost.py issues only GET /user and its docstring states it 'touches no repository'. probe_connection() in backend/apps/integrations/services.py calls exactly that ping() and returns {ok: True} on success.
-Proof the address is never normalised - GitHubCodeHost._repo() returns the configured string unchanged (no .strip()); callers such as get_branch() / open_pull_request() interpolate it directly into '/repos/{repo}/...'.
-Proof a real check is cheap and would have caught it - with the space removed, the same connector resolves the repo for real:
-  ch.ping()             -&gt; 'Signed in to GitHub as RAGUWING369.'
-  ch.get_branch(name='main') -&gt; BranchRef(sha=e252eaedb3, url=https://github.com/RAGUWING369/SpendLog-2-single-repo-refresh-test/tree/main)
-The identical call against the space version raises a 404. One extra read-only call is the whole difference.</t>
-        </is>
-      </c>
-      <c r="G160" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P3</t>
-        </is>
-      </c>
-      <c r="H160" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">probe_connection() validates CREDENTIALS only; it has no notion of the connection's configured TARGET. ping() is deliberately scoped to a cheap 'who am I' that touches no repository, and nothing else in the setup path resolves scopes['repo']. The first code that touches the repo address is the build phase, so a setup typo stays invisible until then. Compounding it, GitHubCodeHost._repo() does not strip or validate the string, so whitespace survives into the URL.</t>
-        </is>
-      </c>
-      <c r="I160" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">OPEN - not fixed, logged for completeness at the team's request (2026-07-17); typo corrected by hand on SpendLog-2 so the retest could proceed. Proposed: extend probe_connection() so that where a connection carries a configured target, the probe resolves THAT too, not just /user - for codehost, a read-only get_branch(default_base) or GET /repos/{repo}; the connector already exposes everything needed. Report it as its own line ('Signed in as X; repo Y found') so the admin sees both facts. Keep it capability-generic (Jira project key, Confluence space, Figma file), not a GitHub special case, and reuse _probe_failure_detail() - its existing 404 wording ('Authenticated, but that address isn't right - check for typos') is already almost exactly the message this needs. Cheap hardening worth doing at the same time: strip the repo string on save in create_integration()/update_integration() and in GitHubCodeHost._repo(), and reject an address that is not OWNER/NAME shaped. Related: S.No 156 (same principle, one level down).</t>
-        </is>
-      </c>
-      <c r="J160" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Open</t>
-        </is>
+      <c r="B160" s="2" t="s">
+        <v>750</v>
+      </c>
+      <c r="C160" s="2" t="s">
+        <v>751</v>
+      </c>
+      <c r="D160" s="2" t="s">
+        <v>752</v>
+      </c>
+      <c r="E160" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F160" s="2" t="s">
+        <v>753</v>
+      </c>
+      <c r="G160" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H160" s="2" t="s">
+        <v>754</v>
+      </c>
+      <c r="I160" s="2" t="s">
+        <v>755</v>
+      </c>
+      <c r="J160" s="2" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="161" spans="1:10">
       <c r="A161" s="2">
         <v>160</v>
       </c>
-      <c r="B161" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The platform silently DISCARDS the agent's entire phase document and reports its cost as zero: every artifact the platform files itself is 0 bytes, and the gate opens on a blank page</t>
-        </is>
-      </c>
-      <c r="C161" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Found live on 2026-07-17 on tenant SpendLog-2 (Edvensoft-2), run 2894a1e0 - the first ideation of the fresh single-repo retest. The companion ran the 01_ideation agent for ~6 minutes and reported a 34,474-character document costing $0.397562. The platform stored a 0-BYTE draft, content_hash = sha256 of the empty string, and run.cost_usd = 0.0. verify_writes then PASSED (it only checks that an artifact of the expected TYPE exists, never that it has content) and the gate opened on a blank document, asking a human to approve nothing. Temporal shows a clean history with no failure anywhere: the run looks perfect from every angle the platform reports on.
-SCOPE - this bites ONLY the platform's own fallback registration, which is why it hid for so long. When the agent registers its artifacts itself (register_artifact + stage_artifact_body over MCP), that path stages the body and the artifact is fine. Across the three live tenants: SpendLog-1 56 artifacts / 1 empty; Edvensoft 170 / 2 empty; SpendLog-2 1 / 1 empty. The empties are exactly the phase-typed artifacts the platform created itself - e.g. Edvensoft 'testing/testing' empty at 08:26 on 2026-07-17 while its sibling test_case / test_report artifacts, which the agent registered, have real bodies. On run 2894a1e0 the agent registered NOTHING, so the broken fallback carried the whole phase and the loss was total.
-AGGRAVATING - the phase.empty_result event blames the ENGINE for the platform's own bug: 'companion reported ok but the engine returned no final text', when the engine had in fact returned 34,474 characters. That message sent this investigation down the wrong path for a considerable time.</t>
-        </is>
-      </c>
-      <c r="D161" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Orchestration / Phase result registration / Artifacts</t>
-        </is>
-      </c>
-      <c r="E161" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bug</t>
-        </is>
-      </c>
-      <c r="F161" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Evidence - reproduce: run any planning phase on the companion in which the agent does not register the phase artifact itself. The staged draft is 0 bytes and the run's cost is 0.0, while the companion's report holds the real body and cost.
-Observed live (run 2894a1e0, tenant 7828e953-987e-43b2-8d5f-c8a45bfa8c6a):
-  run.outputs['report'] = {'status':'ok', 'body': &lt;34474 chars&gt;, 'cost_usd': 0.397562, 'message': ''}
-  run.outputs['cost_usd'] = 0.0                    &lt;- should be 0.397562
-  run.cost_usd            = 0.0000                 &lt;- should be 0.3976
-  artifact e619681e: content_hash = sha256:e3b0c44298fc1c149afbf4c8996fb92427ae41e4649b934ca495991b7852b855
-                     (that is the sha256 of the EMPTY string), title = '', status = draft
-  S3 drafts/&lt;tenant&gt;/&lt;project&gt;/2894a1e0-.../ideation.md -&gt; get() returns b'', length 0
-The COST is the decisive proof: 0.397562 arrived and 0.0 was stored. Only a defaulted read explains both fields going wrong at once, from one line.
-Ledger events for the run, in order: run.triggered 12:09:24 / phase.dispatched 12:09:28 / phase.reported 12:15:32 {'status':'ok'} / run.executed 12:15:36 / phase.empty_result 12:15:36 'companion reported ok but the engine returned no final text; the staged phase draft is empty' (FALSE - see Description) / gate.opened 12:15:38.
-Temporal history (agent-run-2894a1e0-6b6f-4772-9b0a-cc7ad8d4376f on 13.203.56.29:7233): #5 compose_manifest, #11 dispatch_phase, #18 SIGNAL phase_reported, #23 register_phase_result, #29 verify_writes, #35 open_gate. No failures.
-Code location - register_phase_result_core() in backend/orchestration/activities.py read the report with getattr(report,'body',''), getattr(report,'cost_usd',0.0) and getattr(report,'message',''), while register_phase_result_activity(inp: AgentRunInput, report) left `report` UNANNOTATED. It was the ONLY unannotated activity parameter in backend/orchestration (whole package scanned).
-Why the tests never caught it - every existing test in backend/tests/test_phase_dispatch.py passes a real PhaseReport dataclass straight into the core, a shape production never sends; the dict only appears once the argument crosses Temporal. Proof the new regression test reproduces it: on the pre-fix code it fails with  assert b'' == b'# PRD\nreal body'.</t>
-        </is>
-      </c>
-      <c r="G161" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P1</t>
-        </is>
-      </c>
-      <c r="H161" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Temporal's data converter converts an activity argument to the type its parameter is ANNOTATED with, and hands an UNANNOTATED parameter back as the raw decoded JSON - a plain dict. register_phase_result_activity annotated `inp: AgentRunInput` (which is exactly why inp always worked) but left `report` bare, so the PhaseReport arrived as a dict. register_phase_result_core then read it with getattr, which looks up an ATTRIBUTE - a dict has none - so getattr returned its DEFAULT for every field: body '' and cost_usd 0.0. Nothing raised. The defaults are indistinguishable from an engine that genuinely produced nothing, which is precisely what the phase.empty_result message then asserted.
-verify_writes could not save it either: verify_write_completeness_core asserts only that an artifact of the expected TYPE exists, never that its body is non-empty - so the platform's own 0-byte row satisfied the last check before the gate.</t>
-        </is>
-      </c>
-      <c r="I161" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">IN PROGRESS (2026-07-17) - fixed locally, NOT committed, pending team test. Three parts, all in backend/orchestration/activities.py:
-1. ROOT FIX - annotate the activity: register_phase_result_activity(inp: AgentRunInput, report: PhaseReport). Temporal now converts the payload to a PhaseReport, matching the `inp` parameter that always worked. A test asserts the annotation stays put, so it cannot be silently dropped again.
-2. DEFENCE - new _as_phase_report() coerces dict / PhaseReport / duck-typed object to a PhaseReport, and the core reads report.body / report.cost_usd / report.message directly - no getattr on a possible dict anywhere in the path. The cores are also called directly by tests and by the takeover path, so both shapes must keep working.
-3. HONESTY - the phase.empty_result message no longer reads the report via getattr, so it can no longer blame the engine for the platform's own defaulted read.
-Tests (backend/tests/test_phase_dispatch.py): test_register_phase_result_core_reads_a_dict_report sends the exact wire shape Temporal delivers and asserts the body is staged, the hash is not the empty-file hash, and the cost survives (run.cost_usd is a 4dp Decimal column, so the stored value is the rounded 0.3976). test_register_phase_result_activity_annotates_its_report_param guards the root fix. Both fail on the pre-fix code and pass after.
-Verified: test_phase_dispatch 26 passed / 3 skipped; test_orchestration_activities + test_acceptance_phase45 + test_acceptance_phase47 = 14 passed / 1 failed, that 1 being the PRE-EXISTING test_offline_companion_parks_for_takeover, which fails identically without this change (logged as S.No 161).
-NOT fixed here, deliberately: verify_writes still passes an empty artifact (it checks type presence, not content). Logged separately so the last line of defence is fixed on its own merits rather than as a side effect. Related: S.No 59 (the other half of this seam - pointer-only artifacts never staged), S.No 158 (verify_writes crash).</t>
-        </is>
-      </c>
-      <c r="J161" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">In Progress</t>
-        </is>
-      </c>
-    </row>
-    <row r="162" spans="1:1">
+      <c r="B161" s="2" t="s">
+        <v>756</v>
+      </c>
+      <c r="C161" s="2" t="s">
+        <v>757</v>
+      </c>
+      <c r="D161" s="2" t="s">
+        <v>758</v>
+      </c>
+      <c r="E161" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F161" s="2" t="s">
+        <v>759</v>
+      </c>
+      <c r="G161" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H161" s="2" t="s">
+        <v>760</v>
+      </c>
+      <c r="I161" s="2" t="s">
+        <v>761</v>
+      </c>
+      <c r="J161" s="2" t="s">
+        <v>762</v>
+      </c>
+    </row>
+    <row r="162" spans="1:10">
       <c r="A162" s="2">
         <v>161</v>
       </c>
     </row>
-    <row r="163" spans="1:1">
+    <row r="163" spans="1:10">
       <c r="A163" s="2">
         <v>162</v>
       </c>
@@ -8646,153 +8689,135 @@
       <c r="A164" s="2">
         <v>163</v>
       </c>
-      <c r="B164" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Clarification gate surfaced only Tier-1 (must-ask) questions - Tier-2 suggestions and Tier-3 inferences never reached the user</t>
-        </is>
-      </c>
-      <c r="C164" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The SDLC app promises a human is always in the loop and the platform never silently assumes. But agents classified each context gap into three tiers and only surfaced Tier 1 through the clarifications gate. Tier 2 (the agent's own suggestions) was written inline inside the deliverable, and Tier 3 (industry-standard inferences) was logged silently as assumptions the user never saw. So the user could not confirm or override the agent's Tier-2/3 choices, and the 'no silent assumptions' assurance was only partly true.</t>
-        </is>
-      </c>
-      <c r="D164" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Clarifications / Context Gap Scan</t>
-        </is>
-      </c>
-      <c r="E164" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Enhancement</t>
-        </is>
-      </c>
-      <c r="F164" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Observed live across Ideation, Requirements and PRD runs on tenant Edvensoft-2: every phase logged Tier-3 items as assumptions and opened 0 clarifications, so the user never saw the agent's inferences. Verified in code: ask_human was the only human-question touchpoint and the shared rules told agents to front-load only Tier 1 and Tier 2. Retested after the fix on a live UX-design run - a single gate now shows Tier 1/2/3 sections.</t>
-        </is>
-      </c>
-      <c r="G164" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P2</t>
-        </is>
-      </c>
-      <c r="H164" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The behaviour lived in the shared agent rules (backend/manifest/rules/prompt_rules.py): agents were told to 'front-load ALL Tier-1 and Tier-2 questions' and to record every Tier-3 inference silently as an assumption. Only Tier 1 was required/blocking; nothing surfaced Tier 2 or Tier 3 through the clarifications gate. The tier definitions were also thin (one line each), so classification was inconsistent.</t>
-        </is>
-      </c>
-      <c r="I164" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Reworked the shared rules so the agent front-loads ALL three tiers into ONE clarifications gate before starting work, each question tagged with its tier. Tier 1 stays required; Tier 2/3 are optional and carry the agent's proposed answer as a pre-filled 'suggestion' the user can accept, edit or override, with an 'Accept all' one-click. Any untouched Tier-2/3 item falls back to the suggestion, and the confirmed Tier-3 values are still recorded as assumptions for provenance. Also strengthened the tier definitions (a four-question test plus concrete examples per tier). The web gate groups questions under Tier 1/2/3 headers. No DB migration (questions are stored as JSON). Landed on develop in commit 0c19292; backend + frontend tests, type-checks and lint all pass; user-tested on a live UX-design run.</t>
-        </is>
-      </c>
-      <c r="J164" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Fixed</t>
-        </is>
+      <c r="B164" s="2" t="s">
+        <v>763</v>
+      </c>
+      <c r="C164" s="2" t="s">
+        <v>764</v>
+      </c>
+      <c r="D164" s="2" t="s">
+        <v>765</v>
+      </c>
+      <c r="E164" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F164" s="2" t="s">
+        <v>766</v>
+      </c>
+      <c r="G164" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="H164" s="2" t="s">
+        <v>767</v>
+      </c>
+      <c r="I164" s="2" t="s">
+        <v>768</v>
+      </c>
+      <c r="J164" s="2" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="165" spans="1:10">
       <c r="A165" s="2">
         <v>164</v>
       </c>
-      <c r="B165" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Platform does not verify the agent's tier classification - a mislabelled Tier-1 gap can still slip through as a Tier-3 guess</t>
-        </is>
-      </c>
-      <c r="C165" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Even with all three tiers now surfaced in the gate, the platform trusts the agent's own Tier 1/2/3 labelling. If the agent wrongly files a business-critical gap (for example pricing, compliance or a third-party integration) as a Tier-3 inference, it is shown pre-filled and quietly accepted rather than hard-asked. So the 'never assume' assurance still depends on the agent classifying correctly and the human reviewer noticing at the gate.</t>
-        </is>
-      </c>
-      <c r="D165" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Clarifications / Context Gap Scan</t>
-        </is>
-      </c>
-      <c r="E165" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Enhancement</t>
-        </is>
-      </c>
-      <c r="F165" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Design gap, not a live failure. ask_human and create_clarification carry no tier logic (runner/companion/state_mcp.py, backend/apps/clarifications/services.py); the tier reasoning lives only in the agent prompt (backend/manifest/rules/prompt_rules.py). No validator checks a question or assumption against the hard-coded Tier-1 'never infer' category list.</t>
-        </is>
-      </c>
-      <c r="G165" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P3</t>
-        </is>
-      </c>
-      <c r="H165" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">By design, tier classification is the agent's own reasoning; there is no control-plane check. The platform records and delivers whatever tiers the agent labels, and only a human reviewer reading the gate or the Assumptions Log can catch a misclassification.</t>
-        </is>
-      </c>
-      <c r="I165" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Proposed (future): a platform-side validator that scans each phase's questions and assumptions for the Tier-1 'never infer' categories and auto-promotes any match to a required Tier-1 question before the gate can close - turning tier classification from 'trust the agent' into 'the platform double-checks the high-risk categories'. Not yet implemented.</t>
-        </is>
-      </c>
-      <c r="J165" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="166" spans="1:1">
+      <c r="B165" s="2" t="s">
+        <v>769</v>
+      </c>
+      <c r="C165" s="2" t="s">
+        <v>770</v>
+      </c>
+      <c r="D165" s="2" t="s">
+        <v>765</v>
+      </c>
+      <c r="E165" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F165" s="2" t="s">
+        <v>771</v>
+      </c>
+      <c r="G165" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H165" s="2" t="s">
+        <v>772</v>
+      </c>
+      <c r="I165" s="2" t="s">
+        <v>773</v>
+      </c>
+      <c r="J165" s="2" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="166" spans="1:10" ht="409.6">
       <c r="A166" s="2">
         <v>165</v>
       </c>
-    </row>
-    <row r="167" spans="1:1">
+      <c r="B166" s="2" t="s">
+        <v>774</v>
+      </c>
+      <c r="D166" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="E166" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F166" s="2" t="e" vm="17">
+        <v>#VALUE!</v>
+      </c>
+      <c r="G166" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="J166" s="2" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="167" spans="1:10">
       <c r="A167" s="2">
         <v>166</v>
       </c>
     </row>
-    <row r="168" spans="1:1">
+    <row r="168" spans="1:10">
       <c r="A168" s="2">
         <v>167</v>
       </c>
     </row>
-    <row r="169" spans="1:1">
+    <row r="169" spans="1:10">
       <c r="A169" s="2">
         <v>168</v>
       </c>
     </row>
-    <row r="170" spans="1:1">
+    <row r="170" spans="1:10">
       <c r="A170" s="2">
         <v>169</v>
       </c>
     </row>
-    <row r="171" spans="1:1">
+    <row r="171" spans="1:10">
       <c r="A171" s="2">
         <v>170</v>
       </c>
     </row>
-    <row r="172" spans="1:1">
+    <row r="172" spans="1:10">
       <c r="A172" s="2">
         <v>171</v>
       </c>
     </row>
-    <row r="173" spans="1:1">
+    <row r="173" spans="1:10">
       <c r="A173" s="2">
         <v>172</v>
       </c>
     </row>
-    <row r="174" spans="1:1">
+    <row r="174" spans="1:10">
       <c r="A174" s="2">
         <v>173</v>
       </c>
     </row>
-    <row r="175" spans="1:1">
+    <row r="175" spans="1:10">
       <c r="A175" s="2">
         <v>174</v>
       </c>
     </row>
-    <row r="176" spans="1:1">
+    <row r="176" spans="1:10">
       <c r="A176" s="2">
         <v>175</v>
       </c>

--- a/docs/Bugs.xlsx
+++ b/docs/Bugs.xlsx
@@ -8768,18 +8768,120 @@
       <c r="G166" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="J166" s="2" t="s">
-        <v>141</v>
+      <c r="H166" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not a content bug - the artifact's diagrams and matrix were valid markdown. In the shared Markdown renderer (frontend/src/components/ui/Markdown.tsx) the rendered Mermaid diagram was placed in a div carrying the class 'diagram-frame', whose CSS rule '.diagram-frame svg { width:40px; height:40px }' - intended only for the empty-state placeholder icon - shrank every real diagram to a 40x40 px smudge. Confirmed by fetching both tenants' System Architecture artifacts from S3: test@edvensoft.com had 0 Mermaid diagrams (so it never hit the bug and looked fine), while test2@edvensoft.com had 3 valid 'graph TD' diagrams that got shrunk. Separately, GFM tables (the NFR-to-Architecture Traceability Matrix) rendered as a plain width:100% table with no scroll container, so a wide matrix over-extended its pane instead of scrolling. Both are shared-renderer defects, so they affect any artifact with diagrams or wide tables in any phase - which is why the same issue was expected to recur in later phases.</t>
+        </is>
+      </c>
+      <c r="I166" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Surgical fix in the shared Markdown renderer (frontend only - no backend, no DB, no agent change). (1) Diagrams: the rendered container no longer reuses the 'diagram-frame' placeholder class - it uses its own '.md-body__mermaid' class that owns its sizing (svg max-width:100%, height:auto), so diagrams render full size instead of 40x40. (2) Tables: every table is wrapped in a '.md-body__table-wrap' scroll container (overflow-x:auto, max-width:100%), so wide tables scroll inside their pane instead of spilling. Because the fix lives in the shared renderer it covers every phase/artifact and will not recur. Verified live in the running app: the demo diagram rendered at 582x299 px (not 40x40) with no 'diagram-frame' leak, and at mobile width a wide table scrolled inside its wrapper with the page NOT overflowing horizontally. Unit tests (Markdown.test.tsx), typecheck and lint all pass. Files: Markdown.tsx, components.css. To see it: restart the frontend container and hard-refresh the browser - no agent re-run needed, the stored artifact body is unchanged.</t>
+        </is>
+      </c>
+      <c r="J166" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fixed</t>
+        </is>
       </c>
     </row>
     <row r="167" spans="1:10">
       <c r="A167" s="2">
         <v>166</v>
       </c>
+      <c r="B167" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Work-item search dropdown (Combobox) is clipped for a small list - some items are unreachable because the list only scrolls when it is very long</t>
+        </is>
+      </c>
+      <c r="C167" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">On the Phases &amp; Runs page, the 'Search work items' dropdown shows only the first few items and the rest are cut off with no way to scroll to them when there is a small/limited number of work items. A scrollbar only appears when the list is very long. Observed with 6 work items: WI-6/WI-5/WI-4 show and the remaining ones are clipped and unreachable.</t>
+        </is>
+      </c>
+      <c r="D167" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Phases &amp; Runs / Combobox</t>
+        </is>
+      </c>
+      <c r="E167" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bug</t>
+        </is>
+      </c>
+      <c r="F167" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Repro: Phases &amp; Runs &gt; 'Search work items' with ~6 work items - the dropdown is cut off at the panel edge and cannot be scrolled to reach the hidden items. With many work items an internal scrollbar appears and all items are reachable.</t>
+        </is>
+      </c>
+      <c r="G167" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P3</t>
+        </is>
+      </c>
+      <c r="H167" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The shared Combobox dropdown (.combobox__list, frontend/src/components/ui) is absolutely positioned with max-height:260px and overflow-y:auto, and it sits inside a Panel whose CSS '.panel { overflow: hidden }' (used for rounded corners) clips the dropdown at the panel edge. When the list is shorter than 260px it gets NO internal scrollbar, so items past the panel edge are clipped and unreachable; only when the list exceeds 260px does the internal scrollbar appear - which is why 'scroll works' only with many items.</t>
+        </is>
+      </c>
+      <c r="I167" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Two options - team to decide, then fix. Option A (surgical, low-risk, recommended for this screen): stop the Trigger-a-phase Panel from clipping the floating dropdown - add a modifier class (e.g. .panel--menu { overflow: visible }) applied to that one panel; touches PhasesAndRuns.tsx + components.css; fixes this screen only. Option B (general): render the Combobox dropdown in a portal to document.body so it can never be clipped by any container - fixes every Combobox everywhere but is a larger change to the shared component (position calc, reposition on scroll/resize, test updates). Recommend A now; upgrade to B if the same clipping shows up on other screens.</t>
+        </is>
+      </c>
+      <c r="J167" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
     </row>
     <row r="168" spans="1:10">
       <c r="A168" s="2">
         <v>167</v>
+      </c>
+      <c r="B168" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Work-item (Epic / User Story / Task) descriptions from Task Breakdown are shown as raw markdown - the content is good but not rendered (bold, code, tables and lists appear as literal ** ` | characters)</t>
+        </is>
+      </c>
+      <c r="C168" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">In the work-item detail pages, the Description that the Task Breakdown agent writes is good but is displayed as plain text: markdown like **bold**, `code`, pipe tables and bullet lists appear as literal characters instead of being rendered, so it is not user-friendly. Observed on TASK-006, TASK-015 and US-009 (Story). General rule the team wants: wherever the app shows content that is meant to be markdown, it must render in a user-friendly way.</t>
+        </is>
+      </c>
+      <c r="D168" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Work Items / Content rendering</t>
+        </is>
+      </c>
+      <c r="E168" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bug</t>
+        </is>
+      </c>
+      <c r="F168" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Evidence (screenshots shared with the team): TASK-006 and TASK-015 Description panels and the US-009 'Description &amp; context' panel show literal '**Type:**', '**What to build:**', backtick-quoted code and pipe-tables as plain text instead of rendered markdown.</t>
+        </is>
+      </c>
+      <c r="G168" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P1</t>
+        </is>
+      </c>
+      <c r="H168" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The work-item detail views render the description as PLAIN TEXT in a &lt;p&gt; tag instead of through the shared Markdown renderer: WorkItemTask.tsx (line 134), WorkItemEpic.tsx (line 97) and WorkItemDefect.tsx all do '&lt;p className="t-body"&gt;{workItem.data.description}&lt;/p&gt;'. The Markdown component (frontend/src/components/ui/Markdown.tsx - GFM via react-markdown + remark-gfm, already used for artifact previews and hardened in S.No 165) is never applied to work-item descriptions, so the agent's markdown shows raw.</t>
+        </is>
+      </c>
+      <c r="I168" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FIXED. Routed work-item descriptions through the shared Markdown renderer (frontend/src/components/ui/Markdown.tsx) instead of a plain &lt;p&gt;. Added an optional className prop to Markdown (default 'doc-preview prose md-body') so it renders inside an existing Panel without a nested card; WorkItemTask.tsx and WorkItemEpic.tsx now render the description with &lt;Markdown className='prose md-body'&gt;, keeping the 'No description yet.' fallback. Bold, inline code, lists and tables now render correctly. Reuses the same hardened renderer as artifact previews (S.No 165), so it is consistent and not a temporary patch. Scope: Task and User Story/Epic detail (the reported surfaces); WorkItemDefect shows its description inside status Banners (different UX, not Task-Breakdown output) and Board cards show short snippets, both left as-is. Verified live: markdown renders in-panel with no nested card, no raw ** or backticks, no console errors; typecheck, lint and 20 frontend tests pass. User-verified on real work items.</t>
+        </is>
+      </c>
+      <c r="J168" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fixed</t>
+        </is>
       </c>
     </row>
     <row r="169" spans="1:10">

--- a/docs/Bugs.xlsx
+++ b/docs/Bugs.xlsx
@@ -8918,6 +8918,51 @@
       <c r="A170" s="2" t="n">
         <v>169</v>
       </c>
+      <c r="B170" s="2" t="inlineStr">
+        <is>
+          <t>Takeover timeout marks a companion run terminally 'failed' even when the companion later comes back and reports the phase succeeded with artifacts registered — the late success does not reconcile the run, and the UI shows a false 'engine exited, no artifact' message.</t>
+        </is>
+      </c>
+      <c r="C170" s="2" t="inlineStr">
+        <is>
+          <t>Found 2026-07-13 on the SpendLog Architecture run. When a companion (local Claude Code) goes offline after a phase is dispatched, the orchestrator's takeover reconciler fires phase.takeover (reason 'companion offline / no report before timeout') and sets the run to a terminal 'failed' state. If the companion later comes back, completes the work, registers artifacts, and posts phase.reported status=ok, that late success does NOT reconcile the run out of 'failed'. Result: the run shows failed with the canned UI message 'The engine exited before reporting. No artifact was registered.' — which is factually wrong (artifacts were registered, report status was ok). Event sequence proving the race: dispatched 19:49:55Z -&gt; ~7.5h gap (laptop asleep) -&gt; phase.reclaimed 03:25:12Z -&gt; phase.takeover 03:27:37Z (run set failed) -&gt; 11 artifacts registered 03:55:04-03:55:40Z -&gt; phase.reported ok 03:56:57Z.</t>
+        </is>
+      </c>
+      <c r="D170" s="2" t="inlineStr">
+        <is>
+          <t>Orchestration / Takeover + phase-report reconciliation</t>
+        </is>
+      </c>
+      <c r="E170" s="2" t="inlineStr">
+        <is>
+          <t>Bug</t>
+        </is>
+      </c>
+      <c r="F170" s="2" t="inlineStr">
+        <is>
+          <t>Found 2026-07-13, SpendLog Architecture run 8738d4ba-72ee-460f-b41f-86556fca5658 (tenant 212395b8-f118-4eef-93eb-ba2c45468226). Code: takeover path in the orchestrator + phase-report handler (backend/api/runner_views.py phases/&lt;id&gt;/report/).</t>
+        </is>
+      </c>
+      <c r="G170" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="H170" s="2" t="inlineStr">
+        <is>
+          <t>'failed' is a terminal state and swallows a later successful report. Takeover finalizes the run to failed while the companion is merely offline (e.g. laptop asleep), and nothing re-opens it when the companion returns and reports ok with artifacts — takeover wins a race it is about to lose.</t>
+        </is>
+      </c>
+      <c r="I170" s="2" t="inlineStr">
+        <is>
+          <t>OPEN — not yet fixed. Proposed: a successful late phase.reported (status=ok with registered artifacts) should reconcile the run to succeeded (the artifacts are the proof), OR takeover should not finalize while the companion is still making progress / a reclaim should re-open the run. Related operational trigger: companion-offline from laptop sleep stalls dispatched phases.</t>
+        </is>
+      </c>
+      <c r="J170" s="2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" s="2" t="n">

--- a/docs/Bugs.xlsx
+++ b/docs/Bugs.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30305"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30318"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="175" documentId="11_14FDEAE3397E350B81F2A24CBED9C52169691D91" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{77C94B95-75A2-4B7D-95F4-DEC09B2B7B6F}"/>
+  <xr:revisionPtr revIDLastSave="207" documentId="11_14FDEAE3397E350B81F2A24CBED9C52169691D91" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7A04FBDF-F9BB-4AA7-B306-D4BE47860DD0}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
   <metadataTypes count="1">
     <metadataType name="XLRICHVALUE" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1"/>
   </metadataTypes>
-  <futureMetadata name="XLRICHVALUE" count="17">
+  <futureMetadata name="XLRICHVALUE" count="21">
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
@@ -158,8 +158,36 @@
         </ext>
       </extLst>
     </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="17"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="18"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="19"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="20"/>
+        </ext>
+      </extLst>
+    </bk>
   </futureMetadata>
-  <valueMetadata count="17">
+  <valueMetadata count="21">
     <bk>
       <rc t="1" v="0"/>
     </bk>
@@ -211,12 +239,24 @@
     <bk>
       <rc t="1" v="16"/>
     </bk>
+    <bk>
+      <rc t="1" v="17"/>
+    </bk>
+    <bk>
+      <rc t="1" v="18"/>
+    </bk>
+    <bk>
+      <rc t="1" v="19"/>
+    </bk>
+    <bk>
+      <rc t="1" v="20"/>
+    </bk>
   </valueMetadata>
 </metadata>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1314" uniqueCount="775">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1393" uniqueCount="821">
   <si>
     <t>S.No</t>
   </si>
@@ -2326,10 +2366,10 @@
     <t>Companion / Dependency management</t>
   </si>
   <si>
-    <t>The companion depends on claude-agent-sdk, which in turn requires a newer anyio (the anyio.open_process 'user' keyword arrives in anyio 4.5.0; claude-agent-sdk 0.1.72 needs it). The repo's pins were stale (an old claude-agent-sdk pin and no floor on anyio), so a fresh environment installed anyio 4.4.0 and the agent crashed with "anyio.open_process() got an unexpected keyword argument 'user'". This session it was worked around by manually upgrading anyio on the host (pip install -U 'anyio&gt;=4.5' -&gt; 4.14.2), but that fix lives only on this machine - the repo still pins the broken combination, so the next developer or a rebuilt container will hit the same crash.</t>
-  </si>
-  <si>
-    <t>OPEN - not fixed this session (env-patched only). Recommended fix: pin the correct, mutually compatible versions in the repo lockfile/requirements - bump claude-agent-sdk to the version actually in use and add an explicit anyio&gt;=4.5 floor - then rebuild the companion/worker images from the lockfile so a clean install reproduces the working environment. Acceptance: a from-scratch install (no manual pip upgrades) runs a build without the open_process 'user' error.</t>
+    <t>Two compounding causes. (1) The companion ran in the GLOBAL Python with no venv, while the client app it builds (medslot / SDLC-expenselog) pins anyio==4.4.0 + httpx==0.27.0 in its own backend/requirements.txt. Any medslot build/preview `pip install -r requirements.txt` ran in that shared global env and downgraded anyio to 4.4.0, breaking claude-agent-sdk's engine launch (anyio.open_process(..., user=...) needs anyio&gt;=4.5) mid-build. (2) The repo's engine pins were also stale, so a clean install reproduced the broken combination. The earlier note treated this as pins-only; in practice the operative cause was the global-env pollution from the app being built.</t>
+  </si>
+  <si>
+    <t>Fixed 2026-07-20/21. (a) Pinned the engine dep set in the repo (commit 28531e1): claude-agent-sdk==0.1.72, mcp==1.27.0, anyio==4.14.2. (b) Dedicated companion venv OUTSIDE all projects: C:\Users\Msi\sdlc-companion-venv; launch by the venv's absolute python path WITHOUT activating, so build-subprocess pip installs still hit the global env and can never reach the companion's anyio. (c) Startup guard (commit 8c34c24): serve/run call _assert_engine_env() and exit(2) with an actionable message if anyio can't launch the engine. Validated live: WI-38/39/60/41/42/44/45 retriggers all cleared the engine-launch step with no anyio error.</t>
   </si>
   <si>
     <t>Build branches are merged without first being updated against their base, causing merge conflicts at the gate</t>
@@ -2672,6 +2712,42 @@
     <t>In Progress</t>
   </si>
   <si>
+    <t>When a build's remediation loop hit its cycle cap it hard-failed the WorkItem with no diagnostics and no way forward — the user could not complete the WorkItem.</t>
+  </si>
+  <si>
+    <t>The 07&lt;-&gt;08 remediation loop was capped at max_remediation_cycles. On exhaustion the workflow raised a hard failure and stopped. The run console showed only blocking-finding COUNTS across cycles (e.g. 2 -&gt; 1 -&gt; 3 -&gt; 3) with no visibility into what the findings actually were, and there was no automated retry — a human had to step in, defeating the automation promise. If remediation kept exhausting, the WorkItem was simply stuck.</t>
+  </si>
+  <si>
+    <t>Orchestration / Build saga / Remediation</t>
+  </si>
+  <si>
+    <t>commit 29e934b; backend/orchestration/build_workflow.py, build_activities.py (handle_remediation_exhausted), trigger.py, build_types.py</t>
+  </si>
+  <si>
+    <t>On remediation exhaustion the workflow had a single terminal branch (hard fail). It neither captured the real blocking-finding text nor attempted a fresh build attempt, so an exhausted WorkItem had nowhere to go.</t>
+  </si>
+  <si>
+    <t>commit 29e934b. run_code_review now persists the actual blocking-finding detail (rem/severity/title/file/line) into run.outputs['review_cycles'], not just counts. New handle_remediation_exhausted activity: if attempt &lt; max_auto_attempts (default 2) it marks the current run failed with a clear 'auto-retrying' message, logs build.remediation_exhausted_retry, and re-triggers the build with attempt+1 and a seeded prior_attempt_context digest of what blocked the prior attempt — fully automated, no human. Only after all auto-attempts are exhausted does it park for a human. Tests in backend/tests/test_build_activities.py. Validated live 2026-07-21: WI-60 fired build.remediation_exhausted_retry {attempt:1,next_attempt:2} and auto-started attempt 2.</t>
+  </si>
+  <si>
+    <t>A build's remediation could start from an empty tree or push a non-fast-forward when a different companion continued a WorkItem than the one that started it — remediation work was lost or the push was rejected.</t>
+  </si>
+  <si>
+    <t>Each companion provisioned its worktree from its own LOCAL branch state. When companion B continued a WorkItem that companion A had started and pushed, B based the worktree on a stale or absent local ref, producing either an empty build or a non-fast-forward push that failed during the remediation cycle. Subsumes the older stale-local-branch empty-build issue (#145).</t>
+  </si>
+  <si>
+    <t>Companion / Worktree provisioning</t>
+  </si>
+  <si>
+    <t>commits 9863c16, d008643; runner/companion/worktree.py (provision_worktree)</t>
+  </si>
+  <si>
+    <t>provision_worktree based the worktree on a possibly-stale local remote-tracking ref. git fetch does not prune, so a stale origin/&lt;branch&gt; ref (left after the remote branch was deleted) could resurrect a dead branch at an old commit; and a genuinely continued branch was never re-fetched from the true remote tip.</t>
+  </si>
+  <si>
+    <t>commits 9863c16 + d008643. provision_worktree now authoritatively checks `git ls-remote --heads &lt;remote&gt; &lt;branch&gt;`. If the branch exists on the remote it fetches and bases the worktree on &lt;remote&gt;/&lt;branch&gt; (git worktree add -B branch &lt;remote-tip&gt;), so ANY companion continues from the true shared work-in-progress; it falls back to `base` only for a genuinely new/offline branch. Tests in backend/tests/test_companion_runner.py (validated on the host with real git; the container has no git binary). Validated live: WI-39's remediation cycle pushed successfully after previously failing.</t>
+  </si>
+  <si>
     <t>Clarification gate surfaced only Tier-1 (must-ask) questions - Tier-2 suggestions and Tier-3 inferences never reached the user</t>
   </si>
   <si>
@@ -2708,6 +2784,117 @@
     <t>The team has observed that in the Architecture phase of System Architecure artifact: The container and component diagrams are not rendered properly and also NFR-to-Architecture Traceability Matrix Table is over entended not fitted in the designated window. 
 Note: The above issue is observed for tenant - test2@edvensoft.com but the same issues are not present for the tenant - test@edvensoft.com. You must go through both the tenant Architecture Phase - System architecture artifact to confirm and come up with the best fix.
 Important Note: The same issues might be come up in later phases or will be observed (definitive chance) - so we need a surgical fix not temporary.</t>
+  </si>
+  <si>
+    <t>Not a content bug - the artifact's diagrams and matrix were valid markdown. In the shared Markdown renderer (frontend/src/components/ui/Markdown.tsx) the rendered Mermaid diagram was placed in a div carrying the class 'diagram-frame', whose CSS rule '.diagram-frame svg { width:40px; height:40px }' - intended only for the empty-state placeholder icon - shrank every real diagram to a 40x40 px smudge. Confirmed by fetching both tenants' System Architecture artifacts from S3: test@edvensoft.com had 0 Mermaid diagrams (so it never hit the bug and looked fine), while test2@edvensoft.com had 3 valid 'graph TD' diagrams that got shrunk. Separately, GFM tables (the NFR-to-Architecture Traceability Matrix) rendered as a plain width:100% table with no scroll container, so a wide matrix over-extended its pane instead of scrolling. Both are shared-renderer defects, so they affect any artifact with diagrams or wide tables in any phase - which is why the same issue was expected to recur in later phases.</t>
+  </si>
+  <si>
+    <t>Surgical fix in the shared Markdown renderer (frontend only - no backend, no DB, no agent change). (1) Diagrams: the rendered container no longer reuses the 'diagram-frame' placeholder class - it uses its own '.md-body__mermaid' class that owns its sizing (svg max-width:100%, height:auto), so diagrams render full size instead of 40x40. (2) Tables: every table is wrapped in a '.md-body__table-wrap' scroll container (overflow-x:auto, max-width:100%), so wide tables scroll inside their pane instead of spilling. Because the fix lives in the shared renderer it covers every phase/artifact and will not recur. Verified live in the running app: the demo diagram rendered at 582x299 px (not 40x40) with no 'diagram-frame' leak, and at mobile width a wide table scrolled inside its wrapper with the page NOT overflowing horizontally. Unit tests (Markdown.test.tsx), typecheck and lint all pass. Files: Markdown.tsx, components.css. To see it: restart the frontend container and hard-refresh the browser - no agent re-run needed, the stored artifact body is unchanged.</t>
+  </si>
+  <si>
+    <t>Work-item search dropdown (Combobox) is clipped for a small list - some items are unreachable because the list only scrolls when it is very long</t>
+  </si>
+  <si>
+    <t>On the Phases &amp; Runs page, the 'Search work items' dropdown shows only the first few items and the rest are cut off with no way to scroll to them when there is a small/limited number of work items. A scrollbar only appears when the list is very long. Observed with 6 work items: WI-6/WI-5/WI-4 show and the remaining ones are clipped and unreachable.</t>
+  </si>
+  <si>
+    <t>Phases &amp; Runs / Combobox</t>
+  </si>
+  <si>
+    <t>Repro: Phases &amp; Runs &gt; 'Search work items' with ~6 work items - the dropdown is cut off at the panel edge and cannot be scrolled to reach the hidden items. With many work items an internal scrollbar appears and all items are reachable.</t>
+  </si>
+  <si>
+    <t>The shared Combobox dropdown (.combobox__list, frontend/src/components/ui) is absolutely positioned with max-height:260px and overflow-y:auto, and it sits inside a Panel whose CSS '.panel { overflow: hidden }' (used for rounded corners) clips the dropdown at the panel edge. When the list is shorter than 260px it gets NO internal scrollbar, so items past the panel edge are clipped and unreachable; only when the list exceeds 260px does the internal scrollbar appear - which is why 'scroll works' only with many items.</t>
+  </si>
+  <si>
+    <t>Two options - team to decide, then fix. Option A (surgical, low-risk, recommended for this screen): stop the Trigger-a-phase Panel from clipping the floating dropdown - add a modifier class (e.g. .panel--menu { overflow: visible }) applied to that one panel; touches PhasesAndRuns.tsx + components.css; fixes this screen only. Option B (general): render the Combobox dropdown in a portal to document.body so it can never be clipped by any container - fixes every Combobox everywhere but is a larger change to the shared component (position calc, reposition on scroll/resize, test updates). Recommend A now; upgrade to B if the same clipping shows up on other screens.</t>
+  </si>
+  <si>
+    <t>Work-item (Epic / User Story / Task) descriptions from Task Breakdown are shown as raw markdown - the content is good but not rendered (bold, code, tables and lists appear as literal ** ` | characters)</t>
+  </si>
+  <si>
+    <t>In the work-item detail pages, the Description that the Task Breakdown agent writes is good but is displayed as plain text: markdown like **bold**, `code`, pipe tables and bullet lists appear as literal characters instead of being rendered, so it is not user-friendly. Observed on TASK-006, TASK-015 and US-009 (Story). General rule the team wants: wherever the app shows content that is meant to be markdown, it must render in a user-friendly way.</t>
+  </si>
+  <si>
+    <t>Work Items / Content rendering</t>
+  </si>
+  <si>
+    <t>Evidence (screenshots shared with the team): TASK-006 and TASK-015 Description panels and the US-009 'Description &amp; context' panel show literal '**Type:**', '**What to build:**', backtick-quoted code and pipe-tables as plain text instead of rendered markdown.</t>
+  </si>
+  <si>
+    <t>The work-item detail views render the description as PLAIN TEXT in a &lt;p&gt; tag instead of through the shared Markdown renderer: WorkItemTask.tsx (line 134), WorkItemEpic.tsx (line 97) and WorkItemDefect.tsx all do '&lt;p className="t-body"&gt;{workItem.data.description}&lt;/p&gt;'. The Markdown component (frontend/src/components/ui/Markdown.tsx - GFM via react-markdown + remark-gfm, already used for artifact previews and hardened in S.No 165) is never applied to work-item descriptions, so the agent's markdown shows raw.</t>
+  </si>
+  <si>
+    <t>FIXED. Routed work-item descriptions through the shared Markdown renderer (frontend/src/components/ui/Markdown.tsx) instead of a plain &lt;p&gt;. Added an optional className prop to Markdown (default 'doc-preview prose md-body') so it renders inside an existing Panel without a nested card; WorkItemTask.tsx and WorkItemEpic.tsx now render the description with &lt;Markdown className='prose md-body'&gt;, keeping the 'No description yet.' fallback. Bold, inline code, lists and tables now render correctly. Reuses the same hardened renderer as artifact previews (S.No 165), so it is consistent and not a temporary patch. Scope: Task and User Story/Epic detail (the reported surfaces); WorkItemDefect shows its description inside status Banners (different UX, not Task-Breakdown output) and Board cards show short snippets, both left as-is. Verified live: markdown renders in-panel with no nested card, no raw ** or backticks, no console errors; typecheck, lint and 20 frontend tests pass. User-verified on real work items.</t>
+  </si>
+  <si>
+    <t>A WorkItem could show state=done while its run was still awaiting_gate / in review, with no workitem.transitioned event — the build agent marked its own item done, bypassing the merge gate.</t>
+  </si>
+  <si>
+    <t>Seen repeatedly (WI-40, WI-44, WI-41, WI-60). The WorkItem showed done while its run was still in the review/remediation loop or awaiting the merge gate, with no workitem.transitioned event (the only legitimate done path always logs one) and no merge. It resolved 'correctly' later when the gate was approved, but the premature/orphaned done was misleading and — more seriously — meant work was marked complete without an approved gate (a control-plane gate bypass, non-negotiables #2/#5).</t>
+  </si>
+  <si>
+    <t>Orchestration / Gates / Companion agent capability + GitHub webhook reconciliation</t>
+  </si>
+  <si>
+    <t>commits 83a2036 (primary) + 05058d0 (secondary); agents/07_implementation/agent.md, backend/api/runner_views.py, backend/integrations/webhooks.py</t>
+  </si>
+  <si>
+    <t>Two paths let a WorkItem reach done without an approved gate or a transition event. PRIMARY: the 07 implementation agent was instructed (agent.md step R2/7) to transition the item 'toward done' with the transition_work_item MCP tool once it judged acceptance met, and the companion allow-listed that tool. So the engine marked its own task done when it finished coding — before code review and the merge gate — and the agent-facing tool path (tools.transition_work_item) logs no workitem.transitioned event. SECONDARY: the merged-PR webhook (_reconcile_pull_request) set the item done on any merged-PR event, even while a merge_gate was still PENDING, and logged only webhook.pr_merged, never workitem.transitioned.</t>
+  </si>
+  <si>
+    <t>PRIMARY (commit 83a2036): (1) agents/07_implementation/agent.md no longer tells the agent to transition the item to done — it only logs completion; the platform closes each remediation item when the review re-run no longer sees the finding, and marks the item done only after the merge gate. (2) The agent/companion state endpoint (RunnerStateView, the single HTTP entry for every platform-state call) now rejects a transition_work_item call whose to_state is 'done' with 403; the orchestrator calls the tool in-process, not through this view, so its legitimate post-approval transition is unaffected. SECONDARY (commit 05058d0): the merged-PR webhook now defers to the saga while a merge_gate is PENDING (records webhook.pr_merged + publishes the code pointer but does not transition), and when it does legitimately transition a genuine out-of-band merge it emits the canonical workitem.transitioned event. Tests in backend/tests/test_runner_state_api.py and test_webhook_reconcile.py. Non-build phases and the agent's own -&gt; in_progress transition are unaffected.</t>
+  </si>
+  <si>
+    <t>Takeover timeout marks a companion run terminally 'failed' even when the companion later comes back and reports the phase succeeded with artifacts registered — the late success does not reconcile the run, and the UI shows a false 'engine exited, no artifact' message.</t>
+  </si>
+  <si>
+    <t>Found 2026-07-13 on the SpendLog Architecture run. When a companion (local Claude Code) goes offline after a phase is dispatched, the orchestrator's takeover reconciler fires phase.takeover (reason 'companion offline / no report before timeout') and sets the run to a terminal 'failed' state. If the companion later comes back, completes the work, registers artifacts, and posts phase.reported status=ok, that late success does NOT reconcile the run out of 'failed'. Result: the run shows failed with the canned UI message 'The engine exited before reporting. No artifact was registered.' — which is factually wrong (artifacts were registered, report status was ok). Event sequence proving the race: dispatched 19:49:55Z -&gt; ~7.5h gap (laptop asleep) -&gt; phase.reclaimed 03:25:12Z -&gt; phase.takeover 03:27:37Z (run set failed) -&gt; 11 artifacts registered 03:55:04-03:55:40Z -&gt; phase.reported ok 03:56:57Z.</t>
+  </si>
+  <si>
+    <t>Orchestration / Takeover + phase-report reconciliation</t>
+  </si>
+  <si>
+    <t>Found 2026-07-13, SpendLog Architecture run 8738d4ba-72ee-460f-b41f-86556fca5658 (tenant 212395b8-f118-4eef-93eb-ba2c45468226). Code: takeover path in the orchestrator + phase-report handler (backend/api/runner_views.py phases/&lt;id&gt;/report/).</t>
+  </si>
+  <si>
+    <t>'failed' is a terminal state and swallows a later successful report. Takeover finalizes the run to failed while the companion is merely offline (e.g. laptop asleep), and nothing re-opens it when the companion returns and reports ok with artifacts — takeover wins a race it is about to lose.</t>
+  </si>
+  <si>
+    <t>OPEN — not yet fixed. Proposed: a successful late phase.reported (status=ok with registered artifacts) should reconcile the run to succeeded (the artifacts are the proof), OR takeover should not finalize while the companion is still making progress / a reclaim should re-open the run. Related operational trigger: companion-offline from laptop sleep stalls dispatched phases.</t>
+  </si>
+  <si>
+    <t>In Repository page - The optional Preview URL box is not alliged with the rest of the boxes (UX design) and the message comment below the box which says – “A running app for 09b to explore while writing tests” where the user wouldn’t know what is 09b and the message is not understandable for the user.</t>
+  </si>
+  <si>
+    <t>Repositories</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Workspace Dashboard &amp; Phases and Runs pages: 
+In Workspace Dashboard a separate box is present for the companion and it says “Connected --” and in Phases &amp; Runs page it display a light green box which shows “Companion ready --” The team believes the top navigation bar already shows the companion status and do not need a separate companion status messages in the workspace dashboard and phases &amp; runs page.  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Workspace Dashboard - Phases &amp; Runs </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Run Concole page:
+When a user triggers a phase and navigates to the run console page to see the live progress - The page is displaying - Phases &amp; Runs: Id, Workflow Agent-run-Id and Engine: Claude. Now the team wants to understand what those IDs represent and is there a better way to humasize them because for a user they do not make any sense and he would not understand them.  
+Let say, the user created a “Work item 10” and he went to the phases and runs page and invoked the work item 10. Now he went to the run console page but, there he cannot know which work item is running. How does the user confirm that the right work item is running? This is a subtle part of the above issue – also needs fixing while fixing the above issue. 
+Team developer note: Sometimes ids are required for debugging. We have to understand what Ids are currently showing. Make them Human readable if required. </t>
+  </si>
+  <si>
+    <t>Run Console</t>
+  </si>
+  <si>
+    <t>Phases &amp; Runs Page:
+When the companion is offline – in the Trigger a Phase card – only Ideation, Requirements and PRD phases are shown as placeholders but should have shown all the phases. When the companion is online the page shows all the phases and they are clikable which is right response. 
+When the companion is offline: In the Runs card below the trigger a phase card: To the right-hand side, the most recent task is displayed which is not necessary and should be removed (no need any display) 
+When the companion is online: In the Runs card below, the trigger a phase card: To the right-hand side, the most recent task/phase is displayed which is the right response because the companion is online and ready to work.  
+Note: First, tell the team what the message is displayed dynamically there and will decide on removing or keeping it.</t>
+  </si>
+  <si>
+    <t>Clarifications Page:
+In the clarifications page: The default page states, "nothing is billed while it waits” message below the clarification header and “(billing $0) “text in the box below when no clarifications to present. The team decided to remove those two texts, and the rest of the message should be clealy aligned.</t>
   </si>
 </sst>
 </file>
@@ -3551,7 +3738,7 @@
 </file>
 
 <file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
-<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="17">
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="21">
   <rv s="0">
     <v>0</v>
     <v>5</v>
@@ -3620,6 +3807,22 @@
     <v>16</v>
     <v>5</v>
   </rv>
+  <rv s="0">
+    <v>17</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>18</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>19</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>20</v>
+    <v>5</v>
+  </rv>
 </rvData>
 </file>
 
@@ -3651,6 +3854,10 @@
   <rel r:id="rId15"/>
   <rel r:id="rId16"/>
   <rel r:id="rId17"/>
+  <rel r:id="rId18"/>
+  <rel r:id="rId19"/>
+  <rel r:id="rId20"/>
+  <rel r:id="rId21"/>
 </richValueRels>
 </file>
 
@@ -3955,7 +4162,7 @@
   <sheetFormatPr defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="25.85546875" style="2" customWidth="1"/>
+    <col min="2" max="2" width="33" style="2" customWidth="1"/>
     <col min="3" max="3" width="40" style="2" customWidth="1"/>
     <col min="4" max="4" width="16.140625" style="2" customWidth="1"/>
     <col min="5" max="5" width="14" style="2" bestFit="1" customWidth="1"/>
@@ -7967,20 +8174,14 @@
       <c r="G136" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="H136" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Two compounding causes. (1) The companion ran in the GLOBAL Python with no venv, while the client app it builds (medslot / SDLC-expenselog) pins anyio==4.4.0 + httpx==0.27.0 in its own backend/requirements.txt. Any medslot build/preview `pip install -r requirements.txt` ran in that shared global env and downgraded anyio to 4.4.0, breaking claude-agent-sdk's engine launch (anyio.open_process(..., user=...) needs anyio&gt;=4.5) mid-build. (2) The repo's engine pins were also stale, so a clean install reproduced the broken combination. The earlier note treated this as pins-only; in practice the operative cause was the global-env pollution from the app being built.</t>
-        </is>
-      </c>
-      <c r="I136" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Fixed 2026-07-20/21. (a) Pinned the engine dep set in the repo (commit 28531e1): claude-agent-sdk==0.1.72, mcp==1.27.0, anyio==4.14.2. (b) Dedicated companion venv OUTSIDE all projects: C:\Users\Msi\sdlc-companion-venv; launch by the venv's absolute python path WITHOUT activating, so build-subprocess pip installs still hit the global env and can never reach the companion's anyio. (c) Startup guard (commit 8c34c24): serve/run call _assert_engine_env() and exit(2) with an actionable message if anyio can't launch the engine. Validated live: WI-38/39/60/41/42/44/45 retriggers all cleared the engine-launch step with no anyio error.</t>
-        </is>
-      </c>
-      <c r="J136" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Fixed</t>
-        </is>
+      <c r="H136" s="2" t="s">
+        <v>661</v>
+      </c>
+      <c r="I136" s="2" t="s">
+        <v>662</v>
+      </c>
+      <c r="J136" s="2" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="137" spans="1:10" ht="409.6" customHeight="1">
@@ -8585,7 +8786,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="159" spans="1:10">
+    <row r="159" spans="1:10" ht="409.6">
       <c r="A159" s="2">
         <v>158</v>
       </c>
@@ -8649,7 +8850,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="161" spans="1:10">
+    <row r="161" spans="1:10" ht="409.6">
       <c r="A161" s="2">
         <v>160</v>
       </c>
@@ -8681,165 +8882,129 @@
         <v>762</v>
       </c>
     </row>
-    <row r="162" spans="1:10">
+    <row r="162" spans="1:10" ht="409.6">
       <c r="A162" s="2">
         <v>161</v>
       </c>
-      <c r="B162" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">When a build's remediation loop hit its cycle cap it hard-failed the WorkItem with no diagnostics and no way forward — the user could not complete the WorkItem.</t>
-        </is>
-      </c>
-      <c r="C162" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The 07&lt;-&gt;08 remediation loop was capped at max_remediation_cycles. On exhaustion the workflow raised a hard failure and stopped. The run console showed only blocking-finding COUNTS across cycles (e.g. 2 -&gt; 1 -&gt; 3 -&gt; 3) with no visibility into what the findings actually were, and there was no automated retry — a human had to step in, defeating the automation promise. If remediation kept exhausting, the WorkItem was simply stuck.</t>
-        </is>
-      </c>
-      <c r="D162" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Orchestration / Build saga / Remediation</t>
-        </is>
-      </c>
-      <c r="E162" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bug</t>
-        </is>
-      </c>
-      <c r="F162" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">commit 29e934b; backend/orchestration/build_workflow.py, build_activities.py (handle_remediation_exhausted), trigger.py, build_types.py</t>
-        </is>
-      </c>
-      <c r="G162" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P1</t>
-        </is>
-      </c>
-      <c r="H162" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">On remediation exhaustion the workflow had a single terminal branch (hard fail). It neither captured the real blocking-finding text nor attempted a fresh build attempt, so an exhausted WorkItem had nowhere to go.</t>
-        </is>
-      </c>
-      <c r="I162" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">commit 29e934b. run_code_review now persists the actual blocking-finding detail (rem/severity/title/file/line) into run.outputs['review_cycles'], not just counts. New handle_remediation_exhausted activity: if attempt &lt; max_auto_attempts (default 2) it marks the current run failed with a clear 'auto-retrying' message, logs build.remediation_exhausted_retry, and re-triggers the build with attempt+1 and a seeded prior_attempt_context digest of what blocked the prior attempt — fully automated, no human. Only after all auto-attempts are exhausted does it park for a human. Tests in backend/tests/test_build_activities.py. Validated live 2026-07-21: WI-60 fired build.remediation_exhausted_retry {attempt:1,next_attempt:2} and auto-started attempt 2.</t>
-        </is>
-      </c>
-      <c r="J162" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Fixed</t>
-        </is>
-      </c>
-    </row>
-    <row r="163" spans="1:10">
+      <c r="B162" s="2" t="s">
+        <v>763</v>
+      </c>
+      <c r="C162" s="2" t="s">
+        <v>764</v>
+      </c>
+      <c r="D162" s="2" t="s">
+        <v>765</v>
+      </c>
+      <c r="E162" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F162" s="2" t="s">
+        <v>766</v>
+      </c>
+      <c r="G162" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H162" s="2" t="s">
+        <v>767</v>
+      </c>
+      <c r="I162" s="2" t="s">
+        <v>768</v>
+      </c>
+      <c r="J162" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="163" spans="1:10" ht="388.5">
       <c r="A163" s="2">
         <v>162</v>
       </c>
-      <c r="B163" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">A build's remediation could start from an empty tree or push a non-fast-forward when a different companion continued a WorkItem than the one that started it — remediation work was lost or the push was rejected.</t>
-        </is>
-      </c>
-      <c r="C163" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Each companion provisioned its worktree from its own LOCAL branch state. When companion B continued a WorkItem that companion A had started and pushed, B based the worktree on a stale or absent local ref, producing either an empty build or a non-fast-forward push that failed during the remediation cycle. Subsumes the older stale-local-branch empty-build issue (#145).</t>
-        </is>
-      </c>
-      <c r="D163" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Companion / Worktree provisioning</t>
-        </is>
-      </c>
-      <c r="E163" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bug</t>
-        </is>
-      </c>
-      <c r="F163" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">commits 9863c16, d008643; runner/companion/worktree.py (provision_worktree)</t>
-        </is>
-      </c>
-      <c r="G163" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P1</t>
-        </is>
-      </c>
-      <c r="H163" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">provision_worktree based the worktree on a possibly-stale local remote-tracking ref. git fetch does not prune, so a stale origin/&lt;branch&gt; ref (left after the remote branch was deleted) could resurrect a dead branch at an old commit; and a genuinely continued branch was never re-fetched from the true remote tip.</t>
-        </is>
-      </c>
-      <c r="I163" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">commits 9863c16 + d008643. provision_worktree now authoritatively checks `git ls-remote --heads &lt;remote&gt; &lt;branch&gt;`. If the branch exists on the remote it fetches and bases the worktree on &lt;remote&gt;/&lt;branch&gt; (git worktree add -B branch &lt;remote-tip&gt;), so ANY companion continues from the true shared work-in-progress; it falls back to `base` only for a genuinely new/offline branch. Tests in backend/tests/test_companion_runner.py (validated on the host with real git; the container has no git binary). Validated live: WI-39's remediation cycle pushed successfully after previously failing.</t>
-        </is>
-      </c>
-      <c r="J163" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Fixed</t>
-        </is>
-      </c>
-    </row>
-    <row r="164" spans="1:10">
+      <c r="B163" s="2" t="s">
+        <v>769</v>
+      </c>
+      <c r="C163" s="2" t="s">
+        <v>770</v>
+      </c>
+      <c r="D163" s="2" t="s">
+        <v>771</v>
+      </c>
+      <c r="E163" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F163" s="2" t="s">
+        <v>772</v>
+      </c>
+      <c r="G163" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H163" s="2" t="s">
+        <v>773</v>
+      </c>
+      <c r="I163" s="2" t="s">
+        <v>774</v>
+      </c>
+      <c r="J163" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="164" spans="1:10" ht="409.6">
       <c r="A164" s="2">
         <v>163</v>
       </c>
       <c r="B164" s="2" t="s">
-        <v>763</v>
+        <v>775</v>
       </c>
       <c r="C164" s="2" t="s">
-        <v>764</v>
+        <v>776</v>
       </c>
       <c r="D164" s="2" t="s">
-        <v>765</v>
+        <v>777</v>
       </c>
       <c r="E164" s="2" t="s">
         <v>22</v>
       </c>
       <c r="F164" s="2" t="s">
-        <v>766</v>
+        <v>778</v>
       </c>
       <c r="G164" s="2" t="s">
         <v>36</v>
       </c>
       <c r="H164" s="2" t="s">
-        <v>767</v>
+        <v>779</v>
       </c>
       <c r="I164" s="2" t="s">
-        <v>768</v>
+        <v>780</v>
       </c>
       <c r="J164" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="165" spans="1:10">
+    <row r="165" spans="1:10" ht="226.5">
       <c r="A165" s="2">
         <v>164</v>
       </c>
       <c r="B165" s="2" t="s">
-        <v>769</v>
+        <v>781</v>
       </c>
       <c r="C165" s="2" t="s">
-        <v>770</v>
+        <v>782</v>
       </c>
       <c r="D165" s="2" t="s">
-        <v>765</v>
+        <v>777</v>
       </c>
       <c r="E165" s="2" t="s">
         <v>22</v>
       </c>
       <c r="F165" s="2" t="s">
-        <v>771</v>
+        <v>783</v>
       </c>
       <c r="G165" s="2" t="s">
         <v>23</v>
       </c>
       <c r="H165" s="2" t="s">
-        <v>772</v>
+        <v>784</v>
       </c>
       <c r="I165" s="2" t="s">
-        <v>773</v>
+        <v>785</v>
       </c>
       <c r="J165" s="2" t="s">
         <v>141</v>
@@ -8850,7 +9015,7 @@
         <v>165</v>
       </c>
       <c r="B166" s="2" t="s">
-        <v>774</v>
+        <v>786</v>
       </c>
       <c r="D166" s="2" t="s">
         <v>93</v>
@@ -8864,245 +9029,248 @@
       <c r="G166" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="H166" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Not a content bug - the artifact's diagrams and matrix were valid markdown. In the shared Markdown renderer (frontend/src/components/ui/Markdown.tsx) the rendered Mermaid diagram was placed in a div carrying the class 'diagram-frame', whose CSS rule '.diagram-frame svg { width:40px; height:40px }' - intended only for the empty-state placeholder icon - shrank every real diagram to a 40x40 px smudge. Confirmed by fetching both tenants' System Architecture artifacts from S3: test@edvensoft.com had 0 Mermaid diagrams (so it never hit the bug and looked fine), while test2@edvensoft.com had 3 valid 'graph TD' diagrams that got shrunk. Separately, GFM tables (the NFR-to-Architecture Traceability Matrix) rendered as a plain width:100% table with no scroll container, so a wide matrix over-extended its pane instead of scrolling. Both are shared-renderer defects, so they affect any artifact with diagrams or wide tables in any phase - which is why the same issue was expected to recur in later phases.</t>
-        </is>
-      </c>
-      <c r="I166" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Surgical fix in the shared Markdown renderer (frontend only - no backend, no DB, no agent change). (1) Diagrams: the rendered container no longer reuses the 'diagram-frame' placeholder class - it uses its own '.md-body__mermaid' class that owns its sizing (svg max-width:100%, height:auto), so diagrams render full size instead of 40x40. (2) Tables: every table is wrapped in a '.md-body__table-wrap' scroll container (overflow-x:auto, max-width:100%), so wide tables scroll inside their pane instead of spilling. Because the fix lives in the shared renderer it covers every phase/artifact and will not recur. Verified live in the running app: the demo diagram rendered at 582x299 px (not 40x40) with no 'diagram-frame' leak, and at mobile width a wide table scrolled inside its wrapper with the page NOT overflowing horizontally. Unit tests (Markdown.test.tsx), typecheck and lint all pass. Files: Markdown.tsx, components.css. To see it: restart the frontend container and hard-refresh the browser - no agent re-run needed, the stored artifact body is unchanged.</t>
-        </is>
-      </c>
-      <c r="J166" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Fixed</t>
-        </is>
-      </c>
-    </row>
-    <row r="167" spans="1:10">
+      <c r="H166" s="2" t="s">
+        <v>787</v>
+      </c>
+      <c r="I166" s="2" t="s">
+        <v>788</v>
+      </c>
+      <c r="J166" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="167" spans="1:10" ht="409.6">
       <c r="A167" s="2">
         <v>166</v>
       </c>
-      <c r="B167" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Work-item search dropdown (Combobox) is clipped for a small list - some items are unreachable because the list only scrolls when it is very long</t>
-        </is>
-      </c>
-      <c r="C167" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">On the Phases &amp; Runs page, the 'Search work items' dropdown shows only the first few items and the rest are cut off with no way to scroll to them when there is a small/limited number of work items. A scrollbar only appears when the list is very long. Observed with 6 work items: WI-6/WI-5/WI-4 show and the remaining ones are clipped and unreachable.</t>
-        </is>
-      </c>
-      <c r="D167" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Phases &amp; Runs / Combobox</t>
-        </is>
-      </c>
-      <c r="E167" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bug</t>
-        </is>
-      </c>
-      <c r="F167" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Repro: Phases &amp; Runs &gt; 'Search work items' with ~6 work items - the dropdown is cut off at the panel edge and cannot be scrolled to reach the hidden items. With many work items an internal scrollbar appears and all items are reachable.</t>
-        </is>
-      </c>
-      <c r="G167" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P3</t>
-        </is>
-      </c>
-      <c r="H167" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The shared Combobox dropdown (.combobox__list, frontend/src/components/ui) is absolutely positioned with max-height:260px and overflow-y:auto, and it sits inside a Panel whose CSS '.panel { overflow: hidden }' (used for rounded corners) clips the dropdown at the panel edge. When the list is shorter than 260px it gets NO internal scrollbar, so items past the panel edge are clipped and unreachable; only when the list exceeds 260px does the internal scrollbar appear - which is why 'scroll works' only with many items.</t>
-        </is>
-      </c>
-      <c r="I167" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Two options - team to decide, then fix. Option A (surgical, low-risk, recommended for this screen): stop the Trigger-a-phase Panel from clipping the floating dropdown - add a modifier class (e.g. .panel--menu { overflow: visible }) applied to that one panel; touches PhasesAndRuns.tsx + components.css; fixes this screen only. Option B (general): render the Combobox dropdown in a portal to document.body so it can never be clipped by any container - fixes every Combobox everywhere but is a larger change to the shared component (position calc, reposition on scroll/resize, test updates). Recommend A now; upgrade to B if the same clipping shows up on other screens.</t>
-        </is>
-      </c>
-      <c r="J167" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="168" spans="1:10">
+      <c r="B167" s="2" t="s">
+        <v>789</v>
+      </c>
+      <c r="C167" s="2" t="s">
+        <v>790</v>
+      </c>
+      <c r="D167" s="2" t="s">
+        <v>791</v>
+      </c>
+      <c r="E167" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F167" s="2" t="s">
+        <v>792</v>
+      </c>
+      <c r="G167" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H167" s="2" t="s">
+        <v>793</v>
+      </c>
+      <c r="I167" s="2" t="s">
+        <v>794</v>
+      </c>
+      <c r="J167" s="2" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="168" spans="1:10" ht="409.6">
       <c r="A168" s="2">
         <v>167</v>
       </c>
-      <c r="B168" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Work-item (Epic / User Story / Task) descriptions from Task Breakdown are shown as raw markdown - the content is good but not rendered (bold, code, tables and lists appear as literal ** ` | characters)</t>
-        </is>
-      </c>
-      <c r="C168" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">In the work-item detail pages, the Description that the Task Breakdown agent writes is good but is displayed as plain text: markdown like **bold**, `code`, pipe tables and bullet lists appear as literal characters instead of being rendered, so it is not user-friendly. Observed on TASK-006, TASK-015 and US-009 (Story). General rule the team wants: wherever the app shows content that is meant to be markdown, it must render in a user-friendly way.</t>
-        </is>
-      </c>
-      <c r="D168" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Work Items / Content rendering</t>
-        </is>
-      </c>
-      <c r="E168" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bug</t>
-        </is>
-      </c>
-      <c r="F168" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Evidence (screenshots shared with the team): TASK-006 and TASK-015 Description panels and the US-009 'Description &amp; context' panel show literal '**Type:**', '**What to build:**', backtick-quoted code and pipe-tables as plain text instead of rendered markdown.</t>
-        </is>
-      </c>
-      <c r="G168" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P1</t>
-        </is>
-      </c>
-      <c r="H168" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The work-item detail views render the description as PLAIN TEXT in a &lt;p&gt; tag instead of through the shared Markdown renderer: WorkItemTask.tsx (line 134), WorkItemEpic.tsx (line 97) and WorkItemDefect.tsx all do '&lt;p className="t-body"&gt;{workItem.data.description}&lt;/p&gt;'. The Markdown component (frontend/src/components/ui/Markdown.tsx - GFM via react-markdown + remark-gfm, already used for artifact previews and hardened in S.No 165) is never applied to work-item descriptions, so the agent's markdown shows raw.</t>
-        </is>
-      </c>
-      <c r="I168" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">FIXED. Routed work-item descriptions through the shared Markdown renderer (frontend/src/components/ui/Markdown.tsx) instead of a plain &lt;p&gt;. Added an optional className prop to Markdown (default 'doc-preview prose md-body') so it renders inside an existing Panel without a nested card; WorkItemTask.tsx and WorkItemEpic.tsx now render the description with &lt;Markdown className='prose md-body'&gt;, keeping the 'No description yet.' fallback. Bold, inline code, lists and tables now render correctly. Reuses the same hardened renderer as artifact previews (S.No 165), so it is consistent and not a temporary patch. Scope: Task and User Story/Epic detail (the reported surfaces); WorkItemDefect shows its description inside status Banners (different UX, not Task-Breakdown output) and Board cards show short snippets, both left as-is. Verified live: markdown renders in-panel with no nested card, no raw ** or backticks, no console errors; typecheck, lint and 20 frontend tests pass. User-verified on real work items.</t>
-        </is>
-      </c>
-      <c r="J168" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Fixed</t>
-        </is>
-      </c>
-    </row>
-    <row r="169" spans="1:10">
+      <c r="B168" s="2" t="s">
+        <v>795</v>
+      </c>
+      <c r="C168" s="2" t="s">
+        <v>796</v>
+      </c>
+      <c r="D168" s="2" t="s">
+        <v>797</v>
+      </c>
+      <c r="E168" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F168" s="2" t="s">
+        <v>798</v>
+      </c>
+      <c r="G168" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H168" s="2" t="s">
+        <v>799</v>
+      </c>
+      <c r="I168" s="2" t="s">
+        <v>800</v>
+      </c>
+      <c r="J168" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="169" spans="1:10" ht="409.6">
       <c r="A169" s="2">
         <v>168</v>
       </c>
-      <c r="B169" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">A WorkItem could show state=done while its run was still awaiting_gate / in review, with no workitem.transitioned event — the build agent marked its own item done, bypassing the merge gate.</t>
-        </is>
-      </c>
-      <c r="C169" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Seen repeatedly (WI-40, WI-44, WI-41, WI-60). The WorkItem showed done while its run was still in the review/remediation loop or awaiting the merge gate, with no workitem.transitioned event (the only legitimate done path always logs one) and no merge. It resolved 'correctly' later when the gate was approved, but the premature/orphaned done was misleading and — more seriously — meant work was marked complete without an approved gate (a control-plane gate bypass, non-negotiables #2/#5).</t>
-        </is>
-      </c>
-      <c r="D169" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Orchestration / Gates / Companion agent capability + GitHub webhook reconciliation</t>
-        </is>
-      </c>
-      <c r="E169" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bug</t>
-        </is>
-      </c>
-      <c r="F169" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">commits 83a2036 (primary) + 05058d0 (secondary); agents/07_implementation/agent.md, backend/api/runner_views.py, backend/integrations/webhooks.py</t>
-        </is>
-      </c>
-      <c r="G169" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P1</t>
-        </is>
-      </c>
-      <c r="H169" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Two paths let a WorkItem reach done without an approved gate or a transition event. PRIMARY: the 07 implementation agent was instructed (agent.md step R2/7) to transition the item 'toward done' with the transition_work_item MCP tool once it judged acceptance met, and the companion allow-listed that tool. So the engine marked its own task done when it finished coding — before code review and the merge gate — and the agent-facing tool path (tools.transition_work_item) logs no workitem.transitioned event. SECONDARY: the merged-PR webhook (_reconcile_pull_request) set the item done on any merged-PR event, even while a merge_gate was still PENDING, and logged only webhook.pr_merged, never workitem.transitioned.</t>
-        </is>
-      </c>
-      <c r="I169" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PRIMARY (commit 83a2036): (1) agents/07_implementation/agent.md no longer tells the agent to transition the item to done — it only logs completion; the platform closes each remediation item when the review re-run no longer sees the finding, and marks the item done only after the merge gate. (2) The agent/companion state endpoint (RunnerStateView, the single HTTP entry for every platform-state call) now rejects a transition_work_item call whose to_state is 'done' with 403; the orchestrator calls the tool in-process, not through this view, so its legitimate post-approval transition is unaffected. SECONDARY (commit 05058d0): the merged-PR webhook now defers to the saga while a merge_gate is PENDING (records webhook.pr_merged + publishes the code pointer but does not transition), and when it does legitimately transition a genuine out-of-band merge it emits the canonical workitem.transitioned event. Tests in backend/tests/test_runner_state_api.py and test_webhook_reconcile.py. Non-build phases and the agent's own -&gt; in_progress transition are unaffected.</t>
-        </is>
-      </c>
-      <c r="J169" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Fixed</t>
-        </is>
-      </c>
-    </row>
-    <row r="170" spans="1:10">
+      <c r="B169" s="2" t="s">
+        <v>801</v>
+      </c>
+      <c r="C169" s="2" t="s">
+        <v>802</v>
+      </c>
+      <c r="D169" s="2" t="s">
+        <v>803</v>
+      </c>
+      <c r="E169" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F169" s="2" t="s">
+        <v>804</v>
+      </c>
+      <c r="G169" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H169" s="2" t="s">
+        <v>805</v>
+      </c>
+      <c r="I169" s="2" t="s">
+        <v>806</v>
+      </c>
+      <c r="J169" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="170" spans="1:10" ht="388.5">
       <c r="A170" s="2">
         <v>169</v>
       </c>
-      <c r="B170" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Takeover timeout marks a companion run terminally 'failed' even when the companion later comes back and reports the phase succeeded with artifacts registered — the late success does not reconcile the run, and the UI shows a false 'engine exited, no artifact' message.</t>
-        </is>
-      </c>
-      <c r="C170" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Found 2026-07-13 on the SpendLog Architecture run. When a companion (local Claude Code) goes offline after a phase is dispatched, the orchestrator's takeover reconciler fires phase.takeover (reason 'companion offline / no report before timeout') and sets the run to a terminal 'failed' state. If the companion later comes back, completes the work, registers artifacts, and posts phase.reported status=ok, that late success does NOT reconcile the run out of 'failed'. Result: the run shows failed with the canned UI message 'The engine exited before reporting. No artifact was registered.' — which is factually wrong (artifacts were registered, report status was ok). Event sequence proving the race: dispatched 19:49:55Z -&gt; ~7.5h gap (laptop asleep) -&gt; phase.reclaimed 03:25:12Z -&gt; phase.takeover 03:27:37Z (run set failed) -&gt; 11 artifacts registered 03:55:04-03:55:40Z -&gt; phase.reported ok 03:56:57Z.</t>
-        </is>
-      </c>
-      <c r="D170" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Orchestration / Takeover + phase-report reconciliation</t>
-        </is>
-      </c>
-      <c r="E170" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bug</t>
-        </is>
-      </c>
-      <c r="F170" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Found 2026-07-13, SpendLog Architecture run 8738d4ba-72ee-460f-b41f-86556fca5658 (tenant 212395b8-f118-4eef-93eb-ba2c45468226). Code: takeover path in the orchestrator + phase-report handler (backend/api/runner_views.py phases/&lt;id&gt;/report/).</t>
-        </is>
-      </c>
-      <c r="G170" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P2</t>
-        </is>
-      </c>
-      <c r="H170" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">'failed' is a terminal state and swallows a later successful report. Takeover finalizes the run to failed while the companion is merely offline (e.g. laptop asleep), and nothing re-opens it when the companion returns and reports ok with artifacts — takeover wins a race it is about to lose.</t>
-        </is>
-      </c>
-      <c r="I170" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">OPEN — not yet fixed. Proposed: a successful late phase.reported (status=ok with registered artifacts) should reconcile the run to succeeded (the artifacts are the proof), OR takeover should not finalize while the companion is still making progress / a reclaim should re-open the run. Related operational trigger: companion-offline from laptop sleep stalls dispatched phases.</t>
-        </is>
-      </c>
-      <c r="J170" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="171" spans="1:10">
+      <c r="B170" s="2" t="s">
+        <v>807</v>
+      </c>
+      <c r="C170" s="2" t="s">
+        <v>808</v>
+      </c>
+      <c r="D170" s="2" t="s">
+        <v>809</v>
+      </c>
+      <c r="E170" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F170" s="2" t="s">
+        <v>810</v>
+      </c>
+      <c r="G170" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="H170" s="2" t="s">
+        <v>811</v>
+      </c>
+      <c r="I170" s="2" t="s">
+        <v>812</v>
+      </c>
+      <c r="J170" s="2" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="171" spans="1:10" ht="210.75">
       <c r="A171" s="2">
         <v>170</v>
       </c>
-    </row>
-    <row r="172" spans="1:10">
+      <c r="B171" s="2" t="s">
+        <v>813</v>
+      </c>
+      <c r="D171" s="2" t="s">
+        <v>814</v>
+      </c>
+      <c r="E171" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F171" s="2" t="e" vm="18">
+        <v>#VALUE!</v>
+      </c>
+      <c r="G171" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="J171" s="2" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="172" spans="1:10" ht="243">
       <c r="A172" s="2">
         <v>171</v>
       </c>
-    </row>
-    <row r="173" spans="1:10">
+      <c r="B172" s="2" t="s">
+        <v>815</v>
+      </c>
+      <c r="D172" s="2" t="s">
+        <v>816</v>
+      </c>
+      <c r="E172" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F172" s="2" t="e" vm="19">
+        <v>#VALUE!</v>
+      </c>
+      <c r="G172" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="J172" s="2" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="173" spans="1:10" ht="409.6">
       <c r="A173" s="2">
         <v>172</v>
       </c>
-    </row>
-    <row r="174" spans="1:10">
+      <c r="B173" s="2" t="s">
+        <v>817</v>
+      </c>
+      <c r="D173" s="2" t="s">
+        <v>818</v>
+      </c>
+      <c r="E173" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F173" s="2" t="e" vm="20">
+        <v>#VALUE!</v>
+      </c>
+      <c r="G173" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="J173" s="2" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="174" spans="1:10" ht="409.6">
       <c r="A174" s="2">
         <v>173</v>
       </c>
-    </row>
-    <row r="175" spans="1:10">
+      <c r="B174" s="2" t="s">
+        <v>819</v>
+      </c>
+      <c r="D174" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="E174" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F174" s="2" t="e" vm="21">
+        <v>#VALUE!</v>
+      </c>
+      <c r="G174" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="J174" s="2" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="175" spans="1:10" ht="194.25">
       <c r="A175" s="2">
         <v>174</v>
+      </c>
+      <c r="B175" s="2" t="s">
+        <v>820</v>
+      </c>
+      <c r="D175" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="E175" s="2" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="176" spans="1:10">

--- a/docs/Bugs.xlsx
+++ b/docs/Bugs.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30318"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30305"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="207" documentId="11_14FDEAE3397E350B81F2A24CBED9C52169691D91" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7A04FBDF-F9BB-4AA7-B306-D4BE47860DD0}"/>
+  <xr:revisionPtr revIDLastSave="217" documentId="11_14FDEAE3397E350B81F2A24CBED9C52169691D91" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B39CCE5D-1D7C-4DAE-8871-EA9F0B2E43B3}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
   <metadataTypes count="1">
     <metadataType name="XLRICHVALUE" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1"/>
   </metadataTypes>
-  <futureMetadata name="XLRICHVALUE" count="21">
+  <futureMetadata name="XLRICHVALUE" count="23">
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
@@ -186,8 +186,22 @@
         </ext>
       </extLst>
     </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="21"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="22"/>
+        </ext>
+      </extLst>
+    </bk>
   </futureMetadata>
-  <valueMetadata count="21">
+  <valueMetadata count="23">
     <bk>
       <rc t="1" v="0"/>
     </bk>
@@ -251,12 +265,18 @@
     <bk>
       <rc t="1" v="20"/>
     </bk>
+    <bk>
+      <rc t="1" v="21"/>
+    </bk>
+    <bk>
+      <rc t="1" v="22"/>
+    </bk>
   </valueMetadata>
 </metadata>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1393" uniqueCount="821">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1400" uniqueCount="822">
   <si>
     <t>S.No</t>
   </si>
@@ -2895,6 +2915,11 @@
   <si>
     <t>Clarifications Page:
 In the clarifications page: The default page states, "nothing is billed while it waits” message below the clarification header and “(billing $0) “text in the box below when no clarifications to present. The team decided to remove those two texts, and the rest of the message should be clealy aligned.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Phases &amp; Runs page: 
+After the user has connected the companion and selects the work item and triggers a phase – A Runs card shows in the page where the card shows info about the tiggered run and a link to navigate the run console page. Now here the team has decided to revome the “COST(EST)” column which is not needed anymore and the message below the card is also to be revomed (not needed any more). Those details were added for the testing purposes and do not need any more. 
+Note: Also check whether the same behaviour happens in the UI, like for example: while a clarification gate has opend and does a recon over the complete SDLC app and tell the team whether the same scenario of issues appears anywhere? </t>
   </si>
 </sst>
 </file>
@@ -3738,7 +3763,7 @@
 </file>
 
 <file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
-<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="21">
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="23">
   <rv s="0">
     <v>0</v>
     <v>5</v>
@@ -3823,6 +3848,14 @@
     <v>20</v>
     <v>5</v>
   </rv>
+  <rv s="0">
+    <v>21</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>22</v>
+    <v>5</v>
+  </rv>
 </rvData>
 </file>
 
@@ -3858,6 +3891,8 @@
   <rel r:id="rId19"/>
   <rel r:id="rId20"/>
   <rel r:id="rId21"/>
+  <rel r:id="rId22"/>
+  <rel r:id="rId23"/>
 </richValueRels>
 </file>
 
@@ -9272,10 +9307,37 @@
       <c r="E175" s="2" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="176" spans="1:10">
+      <c r="F175" s="2" t="e" vm="22">
+        <v>#VALUE!</v>
+      </c>
+      <c r="G175" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="J175" s="2" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="176" spans="1:10" ht="409.6">
       <c r="A176" s="2">
         <v>175</v>
+      </c>
+      <c r="B176" s="2" t="s">
+        <v>821</v>
+      </c>
+      <c r="D176" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="E176" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F176" s="2" t="e" vm="23">
+        <v>#VALUE!</v>
+      </c>
+      <c r="G176" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="J176" s="2" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="177" spans="1:1">

--- a/docs/Bugs.xlsx
+++ b/docs/Bugs.xlsx
@@ -2545,7 +2545,7 @@
     <t>When the AI build agent fails to run - most commonly because the Anthropic usage/rate limit is reached, but also on any agent CLI non-zero exit - the companion's error handler (runner/companion/daemon.py ~line 271) captures only the engine driver's generic wrapper string and reports it verbatim: 'Command failed with exit code 1 (exit code: 1) / Error output: Check stderr output for details'. The platform's classify_build_failure (backend/orchestration/build_activities.py) does not recognise this signature, so the raw string passes straight through to the build.failed reason and the run console. The user sees an opaque error with no indication that the real cause was a usage limit and no guidance on what to do. This bit WI-32: the usage limit was hit during the cycle-2 remediation build and the console showed only 'Command failed with exit code 1'. Same defect class as S.No 139 (classified reasons) but for the engine/usage-limit failure path, which was not covered.</t>
   </si>
   <si>
-    <t>OPEN - Fix A planned this session (this row's owner). Two parts: (1) Companion (daemon.py): capture the agent process's stderr tail and put the actual cause in the report message instead of the placeholder 'Check stderr output for details'. (2) Platform (classify_build_failure): recognise engine / usage-limit / rate-limit signatures ('exit code 1', 'usage limit', 'rate limit', '429', 'overloaded', 'quota', 'Failed to start Claude Code') and map them to a plain-language reason, e.g. 'The AI engine hit its usage limit - the build stopped; retry when the limit resets.' NOTE: true resume-from-checkpoint on a transient failure (so a re-run continues from the last cycle instead of rebuilding) is tracked separately as S.No 147 and is owned by the other developer. Acceptance: a usage-limit failure shows a clear, non-technical reason naming the usage limit, not a raw exit-code string.</t>
+    <t xml:space="preserve">FIXED &amp; TESTED (2026-07-21): code landed @6f9671f. classify_build_failure() in build_activities.py maps usage/rate-limit/exit-code-1 signatures to a plain reason, and the companion now reports the engine's stderr tail instead of the placeholder. Team verified live. --- Original fix note: OPEN - Fix A planned this session (this row's owner). Two parts: (1) Companion (daemon.py): capture the agent process's stderr tail and put the actual cause in the report message instead of the placeholder 'Check stderr output for details'. (2) Platform (classify_build_failure): recognise engine / usage-limit / rate-limit signatures ('exit code 1', 'usage limit', 'rate limit', '429', 'overloaded', 'quota', 'Failed to start Claude Code') and map them to a plain-language reason, e.g. 'The AI engine hit its usage limit - the build stopped; retry when the limit resets.' NOTE: true resume-from-checkpoint on a transient failure (so a re-run continues from the last cycle instead of rebuilding) is tracked separately as S.No 147 and is owned by the other developer. Acceptance: a usage-limit failure shows a clear, non-technical reason naming the usage limit, not a raw exit-code string.</t>
   </si>
   <si>
     <t>When the implementation of a Work Item is completed and give it away for the review agent - The review agent is doing its job and creating Remediation Work Items (if blocking or critical issues are present): The created Remediation Work Item Tasks are too technical and not humasined and high level</t>
@@ -2720,7 +2720,7 @@
 verify_writes could not save it either: verify_write_completeness_core asserts only that an artifact of the expected TYPE exists, never that its body is non-empty - so the platform's own 0-byte row satisfied the last check before the gate.</t>
   </si>
   <si>
-    <t>IN PROGRESS (2026-07-17) - fixed locally, NOT committed, pending team test. Three parts, all in backend/orchestration/activities.py:
+    <t xml:space="preserve">FIXED &amp; TESTED (2026-07-21): committed @26065d0. register_phase_result_activity now annotates report: PhaseReport, so Temporal delivers a real PhaseReport (not a dict) and the body + cost persist; the empty_result message no longer misblames the engine. Team verified live. --- Original fix note: IN PROGRESS (2026-07-17) - fixed locally, NOT committed, pending team test. Three parts, all in backend/orchestration/activities.py:
 1. ROOT FIX - annotate the activity: register_phase_result_activity(inp: AgentRunInput, report: PhaseReport). Temporal now converts the payload to a PhaseReport, matching the `inp` parameter that always worked. A test asserts the annotation stays put, so it cannot be silently dropped again.
 2. DEFENCE - new _as_phase_report() coerces dict / PhaseReport / duck-typed object to a PhaseReport, and the core reads report.body / report.cost_usd / report.message directly - no getattr on a possible dict anywhere in the path. The cores are also called directly by tests and by the takeover path, so both shapes must keep working.
 3. HONESTY - the phase.empty_result message no longer reads the report via getattr, so it can no longer blame the engine for the platform's own defaulted read.
@@ -8541,7 +8541,7 @@
         <v>714</v>
       </c>
       <c r="J147" s="2" t="s">
-        <v>141</v>
+        <v>16</v>
       </c>
     </row>
     <row r="148" spans="1:10" ht="210.75">
@@ -8914,7 +8914,7 @@
         <v>761</v>
       </c>
       <c r="J161" s="2" t="s">
-        <v>762</v>
+        <v>16</v>
       </c>
     </row>
     <row r="162" spans="1:10" ht="409.6">
@@ -9221,8 +9221,18 @@
       <c r="G171" s="2" t="s">
         <v>13</v>
       </c>
+      <c r="H171" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">S.No 170. The add-repo form lays its fields in a single row that bottom-aligns them. Every field was a label + input EXCEPT "Preview URL", which alone carried a help line under its input; that extra line changed the field's height and pushed its input out of line with the others. The help text also said "09b", an internal phase code that means nothing to a user.</t>
+        </is>
+      </c>
+      <c r="I171" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FIXED &amp; TESTED (2026-07-21). Removed the inline help from the Preview URL field so all four inputs bottom-align again, and moved the guidance to a single full-width line below the row, reworded in plain language with no "09b": "Preview URL is optional - if your app is already running somewhere, paste its address so the testing phase can open it and write tests against the live app." File: frontend/src/features/setup/Repositories.tsx.</t>
+        </is>
+      </c>
       <c r="J171" s="2" t="s">
-        <v>141</v>
+        <v>16</v>
       </c>
     </row>
     <row r="172" spans="1:10" ht="243">
@@ -9244,8 +9254,18 @@
       <c r="G172" s="2" t="s">
         <v>13</v>
       </c>
+      <c r="H172" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">S.No 171. The companion connection status was shown in THREE places at once - the top navigation-bar pill, a "Connected --" box on the Workspace Dashboard, and a green "Companion ready --" box on Phases &amp; Runs - all reading the same underlying runner status. The two page-level boxes were redundant.</t>
+        </is>
+      </c>
+      <c r="I172" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FIXED &amp; TESTED (2026-07-21). Removed the Dashboard "Companion" card and the Phases &amp; Runs "Companion ready" box (and the now-unused useRunners hook/vars they needed), leaving the top-bar pill as the single companion-status indicator. Files: frontend/src/features/observability/Dashboard.tsx, frontend/src/features/lifecycle/PhasesAndRuns.tsx.</t>
+        </is>
+      </c>
       <c r="J172" s="2" t="s">
-        <v>141</v>
+        <v>16</v>
       </c>
     </row>
     <row r="173" spans="1:10" ht="409.6">
@@ -9267,8 +9287,18 @@
       <c r="G173" s="2" t="s">
         <v>13</v>
       </c>
+      <c r="H173" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">S.No 172. The Run Console header and panel showed RAW ids (the run UUID, the Temporal workflow id, the engine) with no labels, and never showed which work item the run belonged to - so a user could not confirm the right work item was running. The work item WAS already fetched by the console, but only its title (with a UUID-slice fallback) was used, never its human key like "WI-42".</t>
+        </is>
+      </c>
+      <c r="I173" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FIXED &amp; TESTED (2026-07-21). Led the header with the work item's key + title so the user can confirm the right item; added a labelled meta row (Work item / Run ID / Engine / Workflow) with the long ids shortened and the full value on hover; shortened the panel title. Raw ids are kept (now labelled) for debugging, per the team's note. File: frontend/src/features/lifecycle/RunConsole.tsx.</t>
+        </is>
+      </c>
       <c r="J173" s="2" t="s">
-        <v>141</v>
+        <v>16</v>
       </c>
     </row>
     <row r="174" spans="1:10" ht="409.6">
@@ -9290,8 +9320,18 @@
       <c r="G174" s="2" t="s">
         <v>13</v>
       </c>
+      <c r="H174" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">S.No 173. When the companion was OFFLINE the Trigger-a-Phase card hardcoded only three phases as disabled placeholders instead of the full catalog, and the Runs card kept showing a label on the right even offline. Recon answer for the team: that right-side label is the CURRENTLY SELECTED work item's title (falling back to a UUID slice), not a "most recent run".</t>
+        </is>
+      </c>
+      <c r="I174" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FIXED &amp; TESTED (2026-07-21). The offline Trigger card now shows the FULL phase list, greyed and non-interactive, so the user sees every phase that exists; they become clickable once the companion is online. The Runs-card right-side work-item label is now hidden when offline and shown only when online (team decision). File: frontend/src/features/lifecycle/PhasesAndRuns.tsx.</t>
+        </is>
+      </c>
       <c r="J174" s="2" t="s">
-        <v>141</v>
+        <v>16</v>
       </c>
     </row>
     <row r="175" spans="1:10" ht="194.25">
@@ -9313,8 +9353,18 @@
       <c r="G175" s="2" t="s">
         <v>13</v>
       </c>
+      <c r="H175" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">S.No 174. The Clarifications page carried testing-era billing wording - a header clause "...and nothing is billed while it waits", an empty-state hint "(billing $0)", and a "Paused - no usage billed while waiting" chip - which the team decided to drop.</t>
+        </is>
+      </c>
+      <c r="I175" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FIXED &amp; TESTED (2026-07-21). Removed the header billing clause and the "(billing $0)" hint and re-aligned the message; reworded the pause chip to "Paused - waiting for your answer" with no cost/billing mention (team asked for a billing-free wording). File: frontend/src/features/lifecycle/Clarifications.tsx.</t>
+        </is>
+      </c>
       <c r="J175" s="2" t="s">
-        <v>141</v>
+        <v>16</v>
       </c>
     </row>
     <row r="176" spans="1:10" ht="409.6">
@@ -9336,8 +9386,18 @@
       <c r="G176" s="2" t="s">
         <v>13</v>
       </c>
+      <c r="H176" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">S.No 175. A "Cost (est.)" column/row and "no usage billed while waiting" text were added across many screens for testing reference and are no longer wanted. The requested recon found the same display on SEVEN screens, not just the Phases &amp; Runs Runs card.</t>
+        </is>
+      </c>
+      <c r="I176" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FIXED &amp; TESTED (2026-07-21). Removed the cost column/row and its note EVERYWHERE - Phases &amp; Runs Runs card, Run Console, Work Item (Task and Epic) panels, Phase Console table, Run Transcript table - and reworded every "no usage billed while waiting" pause banner to "Paused - waiting for your answer"; also removed a "$0 while waiting" note on the Dashboard. 7 files. NOTE: the /dev/components design-system showcase table still has a demo COST column - left intentionally (it is the raw component gallery, not an app screen); flagged to the team.</t>
+        </is>
+      </c>
       <c r="J176" s="2" t="s">
-        <v>141</v>
+        <v>16</v>
       </c>
     </row>
     <row r="177" spans="1:1">

--- a/docs/Bugs.xlsx
+++ b/docs/Bugs.xlsx
@@ -9400,29 +9400,229 @@
         <v>16</v>
       </c>
     </row>
-    <row r="177" spans="1:1">
+    <row r="177" spans="1:10">
       <c r="A177" s="2">
         <v>176</v>
       </c>
-    </row>
-    <row r="178" spans="1:1">
+      <c r="B177" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Security phase (10) runs with NO source code to scan. The Security Agent's whole job (SAST, dependency/CVE scan, SBOM, OWASP-in-code) needs the actual repository checked out, but the phase runs as a PLANNING phase that is never given the code - so it silently degrades to reviewing documents only. A user could get a clean-looking security report where no scanner ever ran against the code.</t>
+        </is>
+      </c>
+      <c r="D177" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Security phase / Orchestration</t>
+        </is>
+      </c>
+      <c r="E177" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bug</t>
+        </is>
+      </c>
+      <c r="F177" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Recon 2026-07-21. Verified: backend/apps/registry/catalog.py:72 registers 10_security with rides_build=False, so it routes trigger_phase -&gt; AgentRunWorkflow; dispatch_phase_core (backend/orchestration/activities.py) ships kind=plan with only manifest+agent_body and NO repo. Only the BUILD path provisions a git worktree. So SAST/SCA/SBOM/OWASP-in-code have nothing to scan. agents/10_security/agent.md:30 explicitly requires the companion worktree containing the full source code.</t>
+        </is>
+      </c>
+      <c r="G177" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P1</t>
+        </is>
+      </c>
+      <c r="H177" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10_security is a planning phase (no rides_build) and the planning dispatch never checks out the work item's repo. The agent's SAST/SCA/SBOM steps require the real source in a companion worktree, which only the build path provides.</t>
+        </is>
+      </c>
+      <c r="I177" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PLANNED (Fix A2, team-approved 2026-07-21): give repo-scoped PLANNING phases a READ-ONLY git worktree without putting them on the build/PR/merge path. New catalog flag reads_code=True on 10_security; trigger_phase resolves the work item's repo (reusing trigger_build's resolver, per-repo); dispatch carries repo/base; companion provisions a read-only worktree (branch sdlc-scan/&lt;run_id&gt;, torn down after, never committed/pushed); driver runs the planning agent with cwd in the worktree, Read/Grep/Glob allowed but Write/Edit blocked. Stays on AgentRunWorkflow so the security_engineer gate is unchanged. Also fixes 09_testing's identical latent gap via the same flag.</t>
+        </is>
+      </c>
+      <c r="J177" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="178" spans="1:10">
       <c r="A178" s="2">
         <v>177</v>
       </c>
-    </row>
-    <row r="179" spans="1:1">
+      <c r="B178" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Security findings never become trackable work. The Security Agent is supposed to open a defect work item for every Critical/High finding (the defect loopback), but the platform code that does this is never actually called in production - so findings just sit in the report and nothing lands on the board.</t>
+        </is>
+      </c>
+      <c r="D178" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Security phase / Quality</t>
+        </is>
+      </c>
+      <c r="E178" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bug</t>
+        </is>
+      </c>
+      <c r="F178" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Recon 2026-07-21. Verified: backend/apps/quality/services.py:334 record_security_findings() implements the Critical/High security_finding -&gt; defect child WorkItem loopback and is exercised by tests, but a repo-wide grep of backend shows NO production caller. The only non-test reference is a comment in backend/apps/gates/testgate.py:57. So in prod the loopback is dead code.</t>
+        </is>
+      </c>
+      <c r="G178" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P1</t>
+        </is>
+      </c>
+      <c r="H178" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">record_security_findings() exists and is tested but is invoked only from tests - no workflow/activity/MCP/gate path calls it. Critical/High security_finding artifacts therefore never spawn defect WorkItems.</t>
+        </is>
+      </c>
+      <c r="I178" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PLANNED (Fix B - auto-defects, team-approved 2026-07-21): wire record_security_findings() into the security run's completion so Critical/High security_finding artifacts auto-open defect child WorkItems (visible on the board), matching the tested call signature. NOTE per team decision the GATE stays advisory - the no_open_security_defects gate BLOCK is deliberately NOT added here (tracked separately as S.No 178).</t>
+        </is>
+      </c>
+      <c r="J178" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="179" spans="1:10">
       <c r="A179" s="2">
         <v>178</v>
       </c>
-    </row>
-    <row r="180" spans="1:1">
+      <c r="B179" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The security gate can be approved with open Critical findings. The agent's contract says the gate must not be grantable while any Critical/High finding is open, but no such rule exists in the platform - the security gate is a plain human approval.</t>
+        </is>
+      </c>
+      <c r="D179" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Security phase / Gates</t>
+        </is>
+      </c>
+      <c r="E179" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bug</t>
+        </is>
+      </c>
+      <c r="F179" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Recon 2026-07-21. Verified: backend/apps/gates/conditions.py returns conditions only for ux_design (WCAG) and testing; conditions_for_phase(security) -&gt; []. There is no conditions_for_security_phase and no no_open_security_defects derived condition. A comment in testgate.py:57 references the intent but nothing enforces it. Gate role is security_engineer (correct) but unconditioned.</t>
+        </is>
+      </c>
+      <c r="G179" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P2</t>
+        </is>
+      </c>
+      <c r="H179" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No security gate condition is wired; the gate is an unconditioned human approval, so a reviewer can approve with open Critical/High findings - contradicting agents/10_security/agent.md:329,430.</t>
+        </is>
+      </c>
+      <c r="I179" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OPEN - DEFERRED by team decision 2026-07-21: for now the security gate stays ADVISORY (human approval) and findings are tracked manually / via the auto-spawned defects (S.No 177). Adding a hard no_open_security_defects gate block is deferred to a later hardening pass; logged here so it is not lost.</t>
+        </is>
+      </c>
+      <c r="J179" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="180" spans="1:10">
       <c r="A180" s="2">
         <v>179</v>
       </c>
-    </row>
-    <row r="181" spans="1:1">
+      <c r="B180" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A blank security review passes the platform's completeness check. verify_writes only confirms that a generic artifact of type security exists - it never checks for the real security deliverables (security_review / security_finding / sbom), so an empty or missing review still passes and the gate opens on nothing.</t>
+        </is>
+      </c>
+      <c r="D180" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Security phase / Artifacts</t>
+        </is>
+      </c>
+      <c r="E180" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bug</t>
+        </is>
+      </c>
+      <c r="F180" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Recon 2026-07-21. Verified: AgentRunWorkflow calls verify_writes with [inp.phase] = [security]; the platform auto-registers one security-typed blob from the run's final text, so verify_write_completeness_core finds type security present and PASSES. The agent's real deliverables are types security_review/security_finding/threat_model/sbom - verify_writes knows nothing about them.</t>
+        </is>
+      </c>
+      <c r="G180" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P2</t>
+        </is>
+      </c>
+      <c r="H180" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">verify_writes checks only that a generic security-typed artifact exists, not the real security artifact types, so an empty review passes the last check before the gate.</t>
+        </is>
+      </c>
+      <c r="I180" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PLANNED (Fix C, team-approved 2026-07-21): require the real security artifact type (security_review at minimum) in the security phase's expected-artifact set so an empty/blank review fails loudly instead of passing on a 0-byte generic blob.</t>
+        </is>
+      </c>
+      <c r="J180" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="181" spans="1:10">
       <c r="A181" s="2">
         <v>180</v>
+      </c>
+      <c r="B181" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The Security agent body omits the two-step needed to persist a large artifact. It tells the model to register artifact bodies directly, but register_artifact only takes a hash + s3 key - the body must first be staged via stage_artifact_body. Every sibling agent spells this out; the security agent does not, so a literal run could stall or mis-call register_artifact.</t>
+        </is>
+      </c>
+      <c r="D181" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Security phase / Agent</t>
+        </is>
+      </c>
+      <c r="E181" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Enhancement</t>
+        </is>
+      </c>
+      <c r="F181" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Recon 2026-07-21. Verified: agents/10_security/agent.md:329,140-144 tells the model to register_artifact bodies directly, but register_artifact (mcp_platform_state/tools.py:314) takes content_hash + s3_key, not an inline body. The body must first be staged via stage_artifact_body (tools.py:558). agents/09_testing/agent.md:243-244 spells out the two-step; the security agent omits it.</t>
+        </is>
+      </c>
+      <c r="G181" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P3</t>
+        </is>
+      </c>
+      <c r="H181" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10_security/agent.md never mentions stage_artifact_body; it instructs a direct register_artifact of the body, which the tool contract does not support. Low severity but a real inconsistency vs sibling agents.</t>
+        </is>
+      </c>
+      <c r="I181" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PLANNED (Fix D, team-approved 2026-07-21): add the stage_artifact_body -&gt; register_artifact two-step to agents/10_security/agent.md, matching the pattern agents/09_testing/agent.md already documents.</t>
+        </is>
+      </c>
+      <c r="J181" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
       </c>
     </row>
     <row r="182" spans="1:1">

--- a/docs/Bugs.xlsx
+++ b/docs/Bugs.xlsx
@@ -9625,24 +9625,184 @@
         </is>
       </c>
     </row>
-    <row r="182" spans="1:1">
+    <row r="182" spans="1:10">
       <c r="A182" s="2">
         <v>181</v>
       </c>
-    </row>
-    <row r="183" spans="1:1">
+      <c r="B182" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Build phase: a companion-reported failure of the INITIAL build (before or at the first report) is terminal - the user cannot resume, only re-run from scratch. When the build agent's first report is status!=ok (e.g. the Claude session/usage limit is hit during the build itself, or the engine errors before reporting), the build workflow runs mark_build_failed and ends. The Run console then offers only 'Retry run' (a brand-new run), never 'Resume from where it stopped'. Every OTHER build error (open PR, merge, remediation) parks and is resumable - only this first-report failure is a dead end. S.No 162 branch-continuity helps only if a branch was already pushed; if the limit hits before any push, the whole build restarts. Blocks a user mid-build with no way to carry on.</t>
+        </is>
+      </c>
+      <c r="D182" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Build phase / Implementation</t>
+        </is>
+      </c>
+      <c r="E182" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bug</t>
+        </is>
+      </c>
+      <c r="F182" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Recon 2026-07-22. Verified: backend/orchestration/build_workflow.py:130-135 (report.status!=ok -&gt; mark_build_failed -&gt; return build_failed, terminal); the resumable _park branches are all inside the PR/review/merge block (:205,:264,:311), AFTER the first ok report; dispatch_build (:111-114) sits outside it; frontend RunConsole.tsx:236-249 shows 'Retry run' for status=failed and 'Resume' only for status=stalled.</t>
+        </is>
+      </c>
+      <c r="G182" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P2</t>
+        </is>
+      </c>
+      <c r="H182" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The initial-build report failure is routed to mark_build_failed (terminal) instead of the S.No 157 park path. dispatch_build is outside the resumable while-loop, so an engine/usage failure during it has no park branch; the Temporal workflow closes and a closed workflow can never be signalled to resume - so the only recovery is a fresh trigger.</t>
+        </is>
+      </c>
+      <c r="I182" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PLANNED (team to fix 2026-07-22): classify the initial-build report failure (reuse classify_build_failure) - when it is a usage/session/rate-limit or a transient engine failure, PARK the build as resumable (park_build, resume_from='dispatch_build') instead of mark_build_failed, so the workflow stays alive and 'Resume from where it stopped' re-dispatches; keep genuinely terminal failures on mark_build_failed. Combine with S.No 162 branch continuity so a resume continues the already-pushed branch.</t>
+        </is>
+      </c>
+      <c r="J182" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="183" spans="1:10">
       <c r="A183" s="2">
         <v>182</v>
       </c>
-    </row>
-    <row r="184" spans="1:1">
+      <c r="B183" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Planning &amp; Scan phases (ideation..deployment, and the Security scan): a mid-run engine failure fails the whole run terminally with NO resume - the user must re-run from scratch. When the companion reports the phase status!=ok (e.g. the Claude session/usage limit is hit mid-run, or the agent/engine errors), AgentRunWorkflow runs fail_run and ends. The Run console offers only 'Retry run', which starts a brand-new run from zero - there is no 'Resume from where it stopped'. Partial work already produced (e.g. security findings already registered) is not continued. This is exactly what hit the Security run on 2026-07-21 (failed on the session limit; a rerun must redo the entire scan). Remediation-exhaust does NOT apply here (planning/scan have no remediation loop). The only resumable park on this path is the narrow verify_writes case (a run that reported OK but is missing its artifact) - not a mid-run failure.</t>
+        </is>
+      </c>
+      <c r="D183" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Planning &amp; Scan phases / Runs</t>
+        </is>
+      </c>
+      <c r="E183" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bug</t>
+        </is>
+      </c>
+      <c r="F183" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Recon 2026-07-22. Verified: backend/orchestration/workflows.py:122-127 (report.status!=ok -&gt; fail_run -&gt; return phase_failed, terminal); the only _park on this workflow is the verify_writes check at :147-159 (post-report, artifact-missing); no remediation loop exists on this workflow; frontend RunConsole.tsx:236-249 gives 'Retry run' (fresh) for status=failed.</t>
+        </is>
+      </c>
+      <c r="G183" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P1</t>
+        </is>
+      </c>
+      <c r="H183" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A companion-reported phase failure is routed to fail_run (terminal) rather than the S.No 157 park path, which is wired ONLY around the verify_writes write-completeness check. So a mid-run engine/usage failure has no resumable branch - the workflow closes and cannot be signalled, forcing a fresh trigger. Planning/scan also produce no branch, so there is no S.No 162-style continuity to fall back on.</t>
+        </is>
+      </c>
+      <c r="I183" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PLANNED (team to fix 2026-07-22, TWO-part surgical fix - both parts required to be bulletproof; part 2 is logged separately as S.No 183): (1) On a companion-reported failure, classify it (reuse classify_phase_failure): if it is a usage/session/rate-limit or a transient engine failure, PARK the run resumable (park_run, resume_from='dispatch_phase') instead of fail_run, keeping the Temporal workflow alive so 'Resume from where it stopped' re-dispatches the remaining work; keep genuinely terminal failures on fail_run. (2) Depends on finding/artifact-level idempotency (S.No 183) so the resume/rerun continues rather than duplicating.</t>
+        </is>
+      </c>
+      <c r="J183" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="184" spans="1:10">
       <c r="A184" s="2">
         <v>183</v>
       </c>
-    </row>
-    <row r="185" spans="1:1">
+      <c r="B184" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Planning &amp; Scan phases: no artifact/finding-level idempotency, so a re-run (or a future resume) DUPLICATES what a failed run already produced. Idempotency today is keyed by run_id only (execute_agent_core skips duplicates only within the SAME run); a fresh Retry gets a NEW run_id, so nothing dedups against the failed run's already-registered artifacts. Concretely, the Security scan that failed on 2026-07-21 had already registered findings SEC-001..004; a fresh rerun re-scans and can register the same findings again as new artifacts (and, once the defect loopback of S.No 177 is wired, could open duplicate defect work items). This makes any 'continue after a failure' unsafe and must be fixed for the S.No 182 resume to be bulletproof.</t>
+        </is>
+      </c>
+      <c r="D184" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Planning &amp; Scan phases / Artifacts</t>
+        </is>
+      </c>
+      <c r="E184" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bug</t>
+        </is>
+      </c>
+      <c r="F184" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Recon 2026-07-22. Verified: backend/orchestration/activities.py execute_agent_core is idempotent by run_id only; a re-trigger creates a new Run/run_id (frontend RunConsole.tsx:141-148 handleRetry -&gt; trigger by agent_key); security findings carry a stable external_ref finding_id (SEC-00x) but nothing dedups artifacts across runs of the same work_item+phase.</t>
+        </is>
+      </c>
+      <c r="G184" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P2</t>
+        </is>
+      </c>
+      <c r="H184" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Artifact registration has no natural key beyond run_id, so across a failed run and its fresh retry there is no dedup on (work_item, phase, expected type / finding_id); partial output from the failed run is neither reused nor suppressed - it is duplicated.</t>
+        </is>
+      </c>
+      <c r="I184" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PLANNED (team to fix 2026-07-22): add finding/artifact-level idempotency keyed on a stable natural key - for findings the external_ref finding_id (SEC-00x); for phase artifacts (work_item, phase, type). On register, upsert by that key within the work_item+phase scope instead of always inserting, so a resumed or re-triggered run continues (updates/skips existing) rather than duplicating. Pairs with S.No 182.</t>
+        </is>
+      </c>
+      <c r="J184" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="185" spans="1:10">
       <c r="A185" s="2">
         <v>184</v>
+      </c>
+      <c r="B185" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Clarifications page: the answer dropdown's option list overflows OUTSIDE the clarification card and looks broken. The Tier-1 'choice' answer control is a native select; when the agent's options are long sentences (seen live in a build-phase clarification - TASK-033, run dd5080df - e.g. 'Create a new backlog task for expenses CRUD router (GET/POST/PATCH/DELETE /api/v1/expenses) and merge TASK-033 as-is...'), the browser-drawn option popup extends past the card's left/right edges and the long option text does not wrap, so option text spills outside the window. Cosmetic but unpolished and can push text off-screen.</t>
+        </is>
+      </c>
+      <c r="D185" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Clarifications / UI</t>
+        </is>
+      </c>
+      <c r="E185" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI issue</t>
+        </is>
+      </c>
+      <c r="F185" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Recon 2026-07-22. Verified: frontend/src/features/lifecycle/Clarifications.tsx:190-203 renders a native &lt;Select&gt; (design-system wrapper over &lt;select&gt;) with one &lt;option&gt; per agent-provided q.options; native &lt;select&gt; option popups are browser/OS-drawn (not in the DOM flow) so they are not clipped to the card, and native &lt;option&gt; text cannot be made to wrap - long option strings render on one line and overflow horizontally.</t>
+        </is>
+      </c>
+      <c r="G185" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P3</t>
+        </is>
+      </c>
+      <c r="H185" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The choice answer uses a native HTML select. A native select's option dropdown is rendered by the browser outside the page layout, so it is not constrained/clipped to the clarification card, and native &lt;option&gt; elements cannot be styled to wrap - long option labels render single-line and spill past the card bounds.</t>
+        </is>
+      </c>
+      <c r="I185" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PLANNED (team to fix 2026-07-22): replace the native select for clarification choices with a custom, card-constrained dropdown/listbox (popup width bounded to the field, long options wrap or truncate-with-tooltip), OR render long-option questions as a radio-button list (each option on its own wrapping line) instead of a dropdown. Preserve the isOtherOption free-text reveal behaviour (Clarifications.tsx:77).</t>
+        </is>
+      </c>
+      <c r="J185" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
       </c>
     </row>
     <row r="186" spans="1:1">

--- a/docs/Bugs.xlsx
+++ b/docs/Bugs.xlsx
@@ -9436,12 +9436,12 @@
       </c>
       <c r="I177" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">PLANNED (Fix A2, team-approved 2026-07-21): give repo-scoped PLANNING phases a READ-ONLY git worktree without putting them on the build/PR/merge path. New catalog flag reads_code=True on 10_security; trigger_phase resolves the work item's repo (reusing trigger_build's resolver, per-repo); dispatch carries repo/base; companion provisions a read-only worktree (branch sdlc-scan/&lt;run_id&gt;, torn down after, never committed/pushed); driver runs the planning agent with cwd in the worktree, Read/Grep/Glob allowed but Write/Edit blocked. Stays on AgentRunWorkflow so the security_engineer gate is unchanged. Also fixes 09_testing's identical latent gap via the same flag.</t>
+          <t xml:space="preserve">IMPLEMENTED (Fix A2, committed 2026-07-21; validated live by security run 371031a0 on 2026-07-22 - real code scanned in a read-only worktree): give repo-scoped PLANNING phases a READ-ONLY git worktree without putting them on the build/PR/merge path. New catalog flag reads_code=True on 10_security; trigger_phase resolves the work item's repo (reusing trigger_build's resolver, per-repo); dispatch carries repo/base; companion provisions a read-only worktree (branch sdlc-scan/&lt;run_id&gt;, torn down after, never committed/pushed); driver runs the planning agent with cwd in the worktree, Read/Grep/Glob allowed but Write/Edit blocked. Stays on AgentRunWorkflow so the security_engineer gate is unchanged. Also fixes 09_testing's identical latent gap via the same flag.</t>
         </is>
       </c>
       <c r="J177" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Open</t>
+          <t xml:space="preserve">Fixed</t>
         </is>
       </c>
     </row>
@@ -9481,12 +9481,12 @@
       </c>
       <c r="I178" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">PLANNED (Fix B - auto-defects, team-approved 2026-07-21): wire record_security_findings() into the security run's completion so Critical/High security_finding artifacts auto-open defect child WorkItems (visible on the board), matching the tested call signature. NOTE per team decision the GATE stays advisory - the no_open_security_defects gate BLOCK is deliberately NOT added here (tracked separately as S.No 178).</t>
+          <t xml:space="preserve">IMPLEMENTED (Fix B auto-defects, committed 2026-07-21; unit-tested; team accepted as Fixed 2026-07-22 without a live Critical/High run - medium/low findings intentionally do NOT open work items): wire record_security_findings() into the security run's completion so Critical/High security_finding artifacts auto-open defect child WorkItems (visible on the board), matching the tested call signature. NOTE per team decision the GATE stays advisory - the no_open_security_defects gate BLOCK is deliberately NOT added here (tracked separately as S.No 178).</t>
         </is>
       </c>
       <c r="J178" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Open</t>
+          <t xml:space="preserve">Fixed</t>
         </is>
       </c>
     </row>
@@ -9571,12 +9571,12 @@
       </c>
       <c r="I180" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">PLANNED (Fix C, team-approved 2026-07-21): require the real security artifact type (security_review at minimum) in the security phase's expected-artifact set so an empty/blank review fails loudly instead of passing on a 0-byte generic blob.</t>
+          <t xml:space="preserve">IMPLEMENTED (Fix C, committed 2026-07-21; validated live by run 371031a0 on 2026-07-22 - security_review required and passed the completeness check): require the real security artifact type (security_review at minimum) in the security phase's expected-artifact set so an empty/blank review fails loudly instead of passing on a 0-byte generic blob.</t>
         </is>
       </c>
       <c r="J180" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Open</t>
+          <t xml:space="preserve">Fixed</t>
         </is>
       </c>
     </row>
@@ -9616,12 +9616,12 @@
       </c>
       <c r="I181" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">PLANNED (Fix D, team-approved 2026-07-21): add the stage_artifact_body -&gt; register_artifact two-step to agents/10_security/agent.md, matching the pattern agents/09_testing/agent.md already documents.</t>
+          <t xml:space="preserve">IMPLEMENTED (Fix D, committed 2026-07-21; validated live by run 371031a0 on 2026-07-22 - 14 artifacts incl. large bodies staged and registered): add the stage_artifact_body -&gt; register_artifact two-step to agents/10_security/agent.md, matching the pattern agents/09_testing/agent.md already documents.</t>
         </is>
       </c>
       <c r="J181" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Open</t>
+          <t xml:space="preserve">Fixed</t>
         </is>
       </c>
     </row>
@@ -9805,29 +9805,229 @@
         </is>
       </c>
     </row>
-    <row r="186" spans="1:1">
+    <row r="186" spans="1:10">
       <c r="A186" s="2">
         <v>185</v>
       </c>
-    </row>
-    <row r="187" spans="1:1">
+      <c r="B186" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Security phase runs entirely as a MANUAL LLM review - no real SAST/SCA/SBOM scanner actually executes. On the live EPIC-004 run (371031a0) the security_review artifact itself states: Bandit 'blocked by sandbox restrictions -&gt; full manual pass performed'; cyclonedx-bom 'unavailable in sandbox -&gt; manual generation' (the SBOM metadata tool literally reads 'Manual CycloneDX Generation'); pip-audit/npm-audit are referenced as CI-integrated but were NOT run in the scan - the python-jose CVEs came from 'manual cross-reference with NVD/OSV'. So despite Bash being enabled in the scan, it produced NO tool-verified findings. A manual/LLM pass is not equivalent to running Bandit/Semgrep/pip-audit/Trivy/syft and cannot be trusted as a real scan.</t>
+        </is>
+      </c>
+      <c r="D186" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Security phase / Companion environment</t>
+        </is>
+      </c>
+      <c r="E186" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bug</t>
+        </is>
+      </c>
+      <c r="F186" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Recon 2026-07-22 on the successful live run 371031a0 (tenant 212395b8, EPIC-004/WI-22d8bd13). Verified from the run's security_review artifact body (Step 0 Tool Selection table + 'Pass 1 - Automated SAST (Manual Equivalent)': 'Bandit tool installation was blocked by sandbox restrictions') and the sbom artifact metadata.tools = 'Manual CycloneDX Generation'. Bash allow is live (claude_driver _SCAN_DISALLOWED_TOOLS permits Bash) but the scanners are not present/installable on the companion host.</t>
+        </is>
+      </c>
+      <c r="G186" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P1</t>
+        </is>
+      </c>
+      <c r="H186" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The companion host lacks the scanner toolchain and/or network to install it; even with Bash allowed, 'pip install bandit' (and cyclonedx-bom, etc.) is blocked by the sandbox/environment, so the agent falls back to manual analysis for SAST, SCA and SBOM. Nothing provisions or verifies the scanners before the scan runs.</t>
+        </is>
+      </c>
+      <c r="I186" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PLANNED (team to fix): provision the scanner toolchain for the scan - pre-install and make invokable on the companion host (or in a dedicated scan container/image) bandit, semgrep, pip-audit, cyclonedx-bom/syft, and a working 'npm audit', with the network their vuln DBs need. Have the scan RECORD each scanner's real invocation + exit status so 'tool ran' is verifiable from evidence, not agent prose; fall back to manual only when a tool is genuinely unavailable and label it as such (see S.No 186).</t>
+        </is>
+      </c>
+      <c r="J186" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="187" spans="1:10">
       <c r="A187" s="2">
         <v>186</v>
       </c>
-    </row>
-    <row r="188" spans="1:1">
+      <c r="B187" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Security review report OVERSTATES which tools actually ran. The 'Tool Selection' table lists Bandit/pip-audit/cyclonedx-bom as selected, and the verification checklist ticks pip-audit and npm-audit as [x] done, when in reality every one of those steps was performed MANUALLY (see S.No 185). A reader is misled into thinking the scan was tool-verified when it was an LLM manual pass. Security reports must be honest about manual-vs-tool or they give false assurance.</t>
+        </is>
+      </c>
+      <c r="D187" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Security phase / Agent (10_security)</t>
+        </is>
+      </c>
+      <c r="E187" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bug</t>
+        </is>
+      </c>
+      <c r="F187" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Recon 2026-07-22 on run 371031a0 security_review artifact: the Step 0 Tool Selection table presents tools as selected/used and the checklist marks '[x] pip-audit --requirement requirements.txt --fail-on-severity high' and '[x] npm audit --audit-level=high', though the body elsewhere says these were manual / CI-assumed and the CVEs were found by manual NVD/OSV cross-reference.</t>
+        </is>
+      </c>
+      <c r="G187" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P2</t>
+        </is>
+      </c>
+      <c r="H187" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">agents/10_security/agent.md lets the model present intended/CI tooling as if it executed in this scan; nothing constrains the report to distinguish 'tool actually run here' from 'manual equivalent' or 'assumed to run in CI'. Combined with S.No 185 (no tools present) this yields a report claiming tool coverage it does not have.</t>
+        </is>
+      </c>
+      <c r="I187" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PLANNED (team to fix): update agents/10_security/agent.md to require honest labelling - each SAST/SCA/SBOM step must be marked MANUAL vs TOOL-RUN, never tick a tool checkbox for a manual/assumed step, and CI-only checks must be labelled 'CI gate (not run in this scan)'. Best paired with S.No 185's exit-code recording so the report reflects what verifiably ran.</t>
+        </is>
+      </c>
+      <c r="J187" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="188" spans="1:10">
       <c r="A188" s="2">
         <v>187</v>
       </c>
-    </row>
-    <row r="189" spans="1:1">
+      <c r="B188" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Artifact preview: any NON-MARKDOWN artifact body renders as an unreadable wall of text - platform-wide, not just security. The security SBOM body is valid CycloneDX 1.5 JSON, but the Artifact preview shows it as a run-on blob of dictionaries. Every other artifact happens to be markdown so only JSON bodies expose it, but ANY phase that produces a JSON (or other non-markdown) body will render broken. Must be fixed generally, for all phases.</t>
+        </is>
+      </c>
+      <c r="D188" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Artifacts / Preview (all phases)</t>
+        </is>
+      </c>
+      <c r="E188" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bug</t>
+        </is>
+      </c>
+      <c r="F188" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Recon 2026-07-22 on run 371031a0 sbom artifact (body starts with '{' = CycloneDX JSON). Verified: backend/integrations/preview.py:139-142 _read_internal returns _INTERNAL_CONTENT_TYPE ('text/markdown', line 28) for EVERY internal S3 body regardless of format; frontend ArtifactPreviewScreen.tsx:119-121 renders content_type text/markdown via &lt;Markdown&gt;, so JSON is fed to the markdown renderer. The _FORMAT_CONTENT_TYPE map (preview.py:56) is only applied to the inline external_ref.body path (line 150), never the S3-body path.</t>
+        </is>
+      </c>
+      <c r="G188" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P2</t>
+        </is>
+      </c>
+      <c r="H188" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">content_type is not derived from the artifact body - the S3-body read path hardcodes text/markdown, so a JSON (or any non-markdown) body is handed to the markdown renderer and collapses into unreadable text. There is no format detection and no content_type stored on the artifact row.</t>
+        </is>
+      </c>
+      <c r="I188" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PLANNED (team to fix, general/SOTA): make _read_internal format-aware - detect JSON (parse-check, or a stored/registered format hint) and return application/json; render JSON in the preview pretty-printed (indented) in a code block, and fall other non-markdown formats through the existing &lt;pre&gt; path rather than &lt;Markdown&gt;. Fixes the SBOM and any future non-markdown artifact across ALL phases.</t>
+        </is>
+      </c>
+      <c r="J188" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="189" spans="1:10">
       <c r="A189" s="2">
         <v>188</v>
       </c>
-    </row>
-    <row r="190" spans="1:1">
+      <c r="B189" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Enhancement: let the user choose the security-scan target via a popup on the Security trigger. Today Security scans exactly one repo (the work item's pinned/default repo); a new/unpinned item on a multi-repo project errors out ('assign its repo... before running'), and there is no way to scan selected repos or the whole project. Team-decided flow: clicking the Security phase trigger opens a clean popup to select - (1) a specific/dedicated repo, (2) the default repo, or (3) the whole project / all repos (multi-repo); on selection the phase starts automatically. Works for a new item or one with a repo already assigned; non-disruptive to existing UI.</t>
+        </is>
+      </c>
+      <c r="D189" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Security phase / Trigger UX</t>
+        </is>
+      </c>
+      <c r="E189" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Enhancement</t>
+        </is>
+      </c>
+      <c r="F189" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Recon 2026-07-22. Verified: backend/orchestration/trigger.py:126-159 _resolve_work_item_repo resolves ONE repo (pinned -&gt; override -&gt; single default; multi-repo unpinned RAISES TriggerError) and the scan copies that whole repo into a worktree; there is no all-repos/selectable-repo path and no trigger-time repo picker.</t>
+        </is>
+      </c>
+      <c r="G189" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P3</t>
+        </is>
+      </c>
+      <c r="H189" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The scan target is resolved implicitly from the work item's single repo with no user choice; multi-repo unpinned is a hard error with no inline resolution, and whole-project coverage requires manually running Security on one work item per repo.</t>
+        </is>
+      </c>
+      <c r="I189" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PLANNED (team-decided flow): add a small, clean modal on the Security phase trigger offering (1) a specific repo, (2) the default repo, (3) the whole project/all repos; on select, resolve the repo(s) and trigger automatically - for 'whole project' fan out one scan per repo. This also removes the unpinned-multi-repo dead-end (user picks the repo in the popup instead of hitting the error). Keep existing Gates/Runs UI unchanged; only the trigger gains the modal.</t>
+        </is>
+      </c>
+      <c r="J189" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="190" spans="1:10">
       <c r="A190" s="2">
         <v>189</v>
+      </c>
+      <c r="B190" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gates page: when multiple phases run in parallel, multiple gates open but the user can only act on the TOP-MOST gate - the decision panel is bound to the first pending gate, so a user who wants to review/approve the 3rd gate first cannot. The pending-approvals rows are not selectable and do not drive the decision panel. Team-selected design = Option A: make each pending row selectable so clicking any gate loads THAT gate into the existing right-side decision panel (selected row highlighted), letting the user review and approve/reject any pending gate in any order. Smallest change to today's layout.</t>
+        </is>
+      </c>
+      <c r="D190" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gates / Approvals UI</t>
+        </is>
+      </c>
+      <c r="E190" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bug</t>
+        </is>
+      </c>
+      <c r="F190" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Recon 2026-07-22 (screenshot: 2 pending gates - WI-59 Merge/Tech Lead + WI-70 Phase/QA Lead - decision panel locked to the top gate). Verified: frontend Gates.tsx renders the pending list plus a single decision panel bound to the top/selected gate; the pending rows carry only a Preview link, with no row-select wiring to re-point the panel at a chosen gate.</t>
+        </is>
+      </c>
+      <c r="G190" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P2</t>
+        </is>
+      </c>
+      <c r="H190" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The decision panel is tied to a single (top/first) pending approval; the pending-approvals table rows have no selection handler to re-point the panel at a chosen gate, so out-of-order review/approval is impossible when several gates are pending at once.</t>
+        </is>
+      </c>
+      <c r="I190" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PLANNED (team-selected Option A): make each pending-approvals row selectable - clicking a row loads that gate into the existing decision panel (highlight the selected row, keep the panel layout as-is). No new drawer/cards. Preserves the current UI while allowing any pending gate to be reviewed and approved/rejected in any order.</t>
+        </is>
+      </c>
+      <c r="J190" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
       </c>
     </row>
     <row r="191" spans="1:1">

--- a/docs/Bugs.xlsx
+++ b/docs/Bugs.xlsx
@@ -10030,14 +10030,94 @@
         </is>
       </c>
     </row>
-    <row r="191" spans="1:1">
+    <row r="191" spans="1:10">
       <c r="A191" s="2">
         <v>190</v>
       </c>
-    </row>
-    <row r="192" spans="1:1">
+      <c r="B191" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Manifest context provisioning loses information platform-wide: get_context returns only the 50 NEWEST artifacts by recency and the Manifest Composer then caps them to the top 20, with NO type/dependency awareness. On a mature project (any phase past mid-lifecycle - e.g. CI/CD Phase 11), the oldest-but-required upstream artifacts (e.g. the Phase 4 architecture/adr) get evicted from the composed AGENTS.md, so an agent may NOT receive the exact inputs its own body declares it needs. Affects ALL agents, not just CI/CD - a definite, silent loss of information.</t>
+        </is>
+      </c>
+      <c r="D191" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Manifest Composer / get_context (all phases)</t>
+        </is>
+      </c>
+      <c r="E191" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bug</t>
+        </is>
+      </c>
+      <c r="F191" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Recon 2026-07-22 (CI/CD Phase 11 pre-test recon). Verified: mcp_platform_state/tools.py:195-262 get_context orders artifacts by -created_at and slices [:50]; the `phase` arg drives ONLY knowledge-search (tools.py:238), never artifact selection. backend/manifest/composer.py:44 max_artifacts=20 + composer.py:189-208 _render_artifacts truncate to the newest 20. agents/11_cicd/agent.md:18 expects the Phase 4 architecture/adr + Phase 10 security + Phase 9 test_report in # Relevant Artifacts, which recency+cap can silently drop.</t>
+        </is>
+      </c>
+      <c r="G191" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P2</t>
+        </is>
+      </c>
+      <c r="H191" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Artifact selection for the manifest is blind recency with a hard count cap and no per-agent dependency model - there is no declaration of which artifact TYPES an agent requires and no guarantee those reach it; newer artifacts crowd out older required ones.</t>
+        </is>
+      </c>
+      <c r="I191" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PLANNED (team-approved 2026-07-22, unified push+pull design): declare each agent's required artifact types ONCE in the catalog (AgentDefinition.needs_artifacts - single source of truth like rides_build); get_context builds a GUARANTEED required tier (latest version per declared type, repo-scoped) that is always injected and never evicted, PLUS a small capped situational-recency tail (team approved keeping the tail for safety). Thread agent_key into get_context; composer renders required-first; missing required types surfaced as named gaps. General across ALL phases. Paired with S.No 191 (accurate on-demand pull by type).</t>
+        </is>
+      </c>
+      <c r="J191" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="192" spans="1:10">
       <c r="A192" s="2">
         <v>191</v>
+      </c>
+      <c r="B192" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Agents cannot accurately pull a specific artifact BY TYPE mid-run: the list_artifacts platform-state tool filters only by phase/status, not by artifact type, so when a needed artifact is absent from the manifest the agent has no precise way to fetch 'the architecture artifact' - it must scan pointers by recency and guess. This is the on-demand half of the context fix; without it the guaranteed-push tier (S.No 190) has no reliable fallback.</t>
+        </is>
+      </c>
+      <c r="D192" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Platform-State MCP / list_artifacts (all agents)</t>
+        </is>
+      </c>
+      <c r="E192" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bug</t>
+        </is>
+      </c>
+      <c r="F192" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Recon 2026-07-22. Verified: mcp_platform_state/tools.py:602-613 list_artifacts(project_id, phase, status) has NO `type` filter; the companion wrapper runner/companion/state_mcp.py:51-55 likewise. get_artifact_body(id) exists (tools.py:579) but needs an id the agent can only obtain by listing. Artifacts ARE typed (backend/apps/registry/models.py:60).</t>
+        </is>
+      </c>
+      <c r="G192" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P3</t>
+        </is>
+      </c>
+      <c r="H192" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">list_artifacts predates the dependency-driven context model; type was never a filter, so 'fetch the artifact of type X' is not expressible - the agent cannot accurately recover a required input that fell outside the manifest.</t>
+        </is>
+      </c>
+      <c r="I192" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PLANNED (team-approved 2026-07-22): add a `type` filter to list_artifacts (tools.py) and expose it through the companion state_mcp wrapper; add a Manifest Composer instruction line telling agents to fetch any artifact not pre-injected via list_artifacts(type=...) then get_artifact_body(id). Completes the push+pull design with S.No 190.</t>
+        </is>
+      </c>
+      <c r="J192" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
       </c>
     </row>
     <row r="193" spans="1:1">

--- a/docs/Bugs.xlsx
+++ b/docs/Bugs.xlsx
@@ -10120,14 +10120,94 @@
         </is>
       </c>
     </row>
-    <row r="193" spans="1:1">
+    <row r="193" spans="1:10">
       <c r="A193" s="2">
         <v>192</v>
       </c>
-    </row>
-    <row r="194" spans="1:1">
+      <c r="B193" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Invitation &amp; password-reset emails are NOT actually delivered to users - the invitee only sees the accept/reset link in the dev console (server terminal log), never in an inbox. EMAIL_BACKEND defaults to Django's console backend and there is no SendGrid (or any SMTP/API) delivery wired for production. Today an admin must copy the invitation link out of the server log and share it manually (Slack/chat). Enhancement: turn on real transactional email delivery so invited users receive their invitation (and password resets) by email.</t>
+        </is>
+      </c>
+      <c r="D193" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Auth / Tenant invitations + password reset (email delivery)</t>
+        </is>
+      </c>
+      <c r="E193" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Enhancement</t>
+        </is>
+      </c>
+      <c r="F193" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Verified 2026-07-23. The email SEND code is already complete and wired: backend/apps/tenancy/emails.py (send_invitation_email / send_password_reset_email over Django send_mail), called on invitation create (backend/api/views.py:702) and on password reset. Links are built from FRONTEND_BASE_URL. The only stub is the delivery backend: backend/config/settings.py:169 EMAIL_BACKEND defaults to django.core.mail.backends.console.EmailBackend (prints to log instead of sending).</t>
+        </is>
+      </c>
+      <c r="G193" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P3</t>
+        </is>
+      </c>
+      <c r="H193" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Intentional dev stub, not a defect. EMAIL_BACKEND is a deliberate pluggable seam set to the console backend for local dev (links print to the log). No production mail backend/credentials were configured and no SendGrid integration exists yet, so nothing is transmitted over the wire.</t>
+        </is>
+      </c>
+      <c r="I193" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PLANNED - config only, no code change needed. Recommended: use Django's built-in SMTP backend against SendGrid's SMTP relay. Set EMAIL_BACKEND=django.core.mail.backends.smtp.EmailBackend, EMAIL_HOST=smtp.sendgrid.net, EMAIL_PORT=587, EMAIL_USE_TLS=True, EMAIL_HOST_USER=apikey (literal), EMAIL_HOST_PASSWORD=&lt;SENDGRID_API_KEY&gt;, DEFAULT_FROM_EMAIL=&lt;verified sender e.g. no-reply@edvensoft.com&gt;, and a correct FRONTEND_BASE_URL. Team side (in SendGrid, not our code): (1) verify a sender or domain via DNS auth, (2) generate an API key. Effort: a few hours, mostly the SendGrid sender verification; no new Python package required. Optional polish: add an EMAIL_* block to .env.example + a short docs note so it is a drop-in when creds arrive. The same seam also switches on password-reset emails.</t>
+        </is>
+      </c>
+      <c r="J193" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="194" spans="1:10">
       <c r="A194" s="2">
         <v>193</v>
+      </c>
+      <c r="B194" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Triggering the CI/CD phase (11_cicd) runs the agent to completion and registers its artifacts, but the build then FAILS at the very last step: the companion's pre-push secret scan blocks the branch push, so no PR is ever opened. Live: SpendLog WI-146 run cab0535c failed with '[high_entropy_secret] docker-compose.yml:64 - dev-***rs (55 chars)'. The CICD agent's Step 3 tells it to generate a local docker-compose.yml with database + cache services but gives NO secret-handling guidance, so the agent hardcodes a real generated dev password/token literal into the compose file. The pre-push guardrail correctly flags it and blocks the push (a TRUE positive), killing the build after all agent work is done.</t>
+        </is>
+      </c>
+      <c r="D194" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CI/CD phase (11_cicd) - generated docker-compose.yml</t>
+        </is>
+      </c>
+      <c r="E194" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bug</t>
+        </is>
+      </c>
+      <c r="F194" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Verified 2026-07-23. Confirmed AGENT-SIDE: docker-compose.yml exists nowhere on the SpendLog repo default branch (TARUN51/medslot-single-repo main has only backend/Dockerfile + backend/.env.example + frontend/.env.example), and the run's branch feature/WI-79a3804c never reached GitHub (push was blocked) - so the file was freshly generated by 11_cicd this run. Scanner working as intended: runner/companion/guardrails.py:59-75 flags a secret/password/token key assigned a &gt;=20-char, high-entropy (Shannon&gt;=3.5), non-placeholder value; ${VAR}/placeholder values are skipped. agents/11_cicd/agent.md Step 3 (compose) had no no-hardcode rule, unlike Step 2 (Dockerfile: 'no secrets in the Dockerfile'). Platform passes the finding through unchanged (backend/orchestration/build_activities.py:427); run is terminal so the console shows 'Retry run'. Note S.No 130 (commit 52533c4) only made the finding readable - it did not cause or change the block.</t>
+        </is>
+      </c>
+      <c r="G194" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P2</t>
+        </is>
+      </c>
+      <c r="H194" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The 11_cicd agent body's Step 3 instructs generating a local docker-compose.yml with database + cache services (which need credentials) but - unlike the Dockerfile and Jenkinsfile steps - never says how to handle those secret values. The agent therefore hardcodes a concrete dev credential literal, which the companion's pre-push secret scan (PG14) correctly blocks. NOT a scanner defect - the scanner did its job; the agent violated the 'never hardcode secrets' principle its own quality gate already states.</t>
+        </is>
+      </c>
+      <c r="I194" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FIXED 2026-07-23 (agent-body fix; team to re-test). agents/11_cicd/agent.md Step 3 now explicitly forbids hardcoding any secret in the compose file (even a dev DB/cache password) and requires env-var references (e.g. POSTGRES_PASSWORD: ${POSTGRES_PASSWORD} or env_file) plus a committed .env.example with placeholders only; the git-ignored real .env holds values. The Quality Gate line was also extended to cover local compose credentials, noting a hardcoded high-entropy value trips the pre-push scan. Scanner intentionally NOT weakened (that would let real secrets through). Immediate unblock: replace the literal on docker-compose.yml:64 with an env reference and re-trigger; a fresh run with the fixed agent body should no longer hardcode. VALIDATED LIVE 2026-07-23: a fresh end-to-end CICD run on SpendLog succeeded - agent wrote code, opened the PR, ran the code-review remediation loop, and merged with NO secret-scan block. Fix confirmed working.</t>
+        </is>
+      </c>
+      <c r="J194" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fixed</t>
+        </is>
       </c>
     </row>
     <row r="195" spans="1:1">

--- a/docs/Bugs.xlsx
+++ b/docs/Bugs.xlsx
@@ -10210,19 +10210,139 @@
         </is>
       </c>
     </row>
-    <row r="195" spans="1:1">
+    <row r="195" spans="1:10">
       <c r="A195" s="2">
         <v>194</v>
       </c>
-    </row>
-    <row r="196" spans="1:1">
+      <c r="B195" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Deployment phase (12): the agent body PROMISED the platform executes the deployment. Its Completion said the platform 'on approval executes the gated production deployment... then runs the smoke tests and the monitoring window... aborting and rolling back automatically' (agent.md:140, also lines 9 and 81). But the platform does NO such thing: on deployment-gate approval the workflow runs only publish_artifacts + transition_work_item-&gt;done (workflows.py:169-178). No deploy, no smoke tests, no monitoring, no rollback exists (the GitHub integration has no pipeline-trigger/deploy API). So the agent narrated a deployment to the user that never happened - a false statement, and dangerous in front of a customer.</t>
+        </is>
+      </c>
+      <c r="D195" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Deployment phase (12_deployment) - agent body vs platform</t>
+        </is>
+      </c>
+      <c r="E195" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bug</t>
+        </is>
+      </c>
+      <c r="F195" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Recon 2026-07-23 (Phase 12 pre-test). Verified: catalog 12_deployment is NOT rides_build/reads_code -&gt; planning path (trigger.py). On approval AgentRunWorkflow runs publish_artifacts + transition_work_item only (backend/orchestration/workflows.py:169-178); no deploy/workflow_dispatch/kubectl/ssh anywhere; backend/integrations/github/codehost.py has only PR/branch/merge ops, no pipeline/deploy API. Team decision 2026-07-23: Option A (governed release package + human-run pipeline); real platform execution = Option B, logged separately (S.No 196).</t>
+        </is>
+      </c>
+      <c r="G195" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P2</t>
+        </is>
+      </c>
+      <c r="H195" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The agent body described the intended end-state (platform-executed, gated deployment) but that platform-side execution was never built. The agent therefore claims a capability the product does not have, and - running in a planning context with no environment - risks reporting fabricated smoke-test/monitoring/deploy results.</t>
+        </is>
+      </c>
+      <c r="I195" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FIXED 2026-07-23 (Option A, team-approved). Reworded agents/12_deployment/agent.md to state the truth: the DevOps deployment-gate approval AUTHORIZES the release; the DevOps engineer then runs the documented deployment/smoke tests/monitoring via the phase-11 CD pipeline; the platform records the approval + publishes the deliverables and does NOT execute the deploy. Edited the intro, Step 5, and the Completion section, and added a Process guardrail forbidding the agent from reporting deploy/smoke/monitoring results as if it ran them. Agent-body migration string tests pass (21 passed).</t>
+        </is>
+      </c>
+      <c r="J195" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fixed</t>
+        </is>
+      </c>
+    </row>
+    <row r="196" spans="1:10">
       <c r="A196" s="2">
         <v>195</v>
       </c>
-    </row>
-    <row r="197" spans="1:1">
+      <c r="B196" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Deployment gate had NO readiness enforcement. The Deployment agent's whole philosophy is 'never deploy without a completed readiness checklist', but the deployment gate carried EMPTY conditions - a DevOps approver could approve the release with nothing checked. The readiness verdict the agent produces was only narrative, not a control-plane condition, so the platform never enforced it.</t>
+        </is>
+      </c>
+      <c r="D196" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Deployment gate (12) / gate conditions</t>
+        </is>
+      </c>
+      <c r="E196" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bug</t>
+        </is>
+      </c>
+      <c r="F196" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Recon 2026-07-23. Verified: conditions_for_phase (backend/apps/gates/conditions.py) composed only WCAG (ux_design) + blocking-test (testing); deployment was in neither set, so its Approval.conditions were []. The enforcement mechanism already existed - decide_gate (apps/gates/services.py:135-150) blocks approval on any unmet required condition - deployment just had no conditions attached.</t>
+        </is>
+      </c>
+      <c r="G196" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P2</t>
+        </is>
+      </c>
+      <c r="H196" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No per-phase readiness conditions were defined for the deployment gate; the agent's Step 1 readiness checklist lived only in the prompt with no control-plane counterpart, so it was unenforceable.</t>
+        </is>
+      </c>
+      <c r="I196" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FIXED 2026-07-23. Added backend/apps/gates/readiness.py (a reviewer-attested checklist mirroring the agent's Step 1: code quality, testing+UAT, security, migrations, rollback, on-call/comms, deliverables) and composed it into conditions_for_phase for phase 'deployment'. Enforcement + UI are automatic: decide_gate blocks approval until all required items are ticked, and the Gates page renders gate criteria via useGateCriteria. Added tests/test_readiness_gate.py - pure composition test passes; DB-backed enforcement tests run in CI. Some items could later become platform-DERIVED (e.g. open security/test defects) - noted as a future refinement.</t>
+        </is>
+      </c>
+      <c r="J196" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fixed</t>
+        </is>
+      </c>
+    </row>
+    <row r="197" spans="1:10">
       <c r="A197" s="2">
         <v>196</v>
+      </c>
+      <c r="B197" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ENHANCEMENT (Option B): make production deployment a platform-EXECUTED action. Today (Option A) the deployment phase produces the release package + readiness gate, and a human runs the actual deploy via the phase-11 CD pipeline. Enhancement: on deployment-gate approval, have the platform ITSELF execute the gated deployment using the documented strategy (blue/green or canary), then run the post-deploy smoke tests and the 30-minute monitoring window, and auto-rollback on any trigger - realising end to end what the deployment agent's runbook describes.</t>
+        </is>
+      </c>
+      <c r="D197" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Deployment phase (12) - platform-executed deployment</t>
+        </is>
+      </c>
+      <c r="E197" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Enhancement</t>
+        </is>
+      </c>
+      <c r="F197" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Logged 2026-07-23 per team decision (Q1: Option A now, Option B as enhancement). No environment exists yet for SpendLog/medslot; the team will create a test env later. Scope: a post-approval execution branch in AgentRunWorkflow (or a dedicated deployment workflow) + activities to dispatch the CD pipeline (e.g. GitHub Actions workflow_dispatch - not currently in integrations/github/codehost.py), run smoke tests, poll monitoring metrics, and trigger rollback.</t>
+        </is>
+      </c>
+      <c r="G197" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P3</t>
+        </is>
+      </c>
+      <c r="H197" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Deployment execution was intentionally deferred: the agent describes it, but the platform-side deploy/smoke/monitor/rollback was never built (Option A is what ships). This is the build to close that gap.</t>
+        </is>
+      </c>
+      <c r="I197" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PLANNED (enhancement, no target date). Large build: post-approval execution path + CD-pipeline dispatch connector (workflow_dispatch/deploy API) + smoke-test + monitoring-window + auto-rollback activities. Requires a real target environment. Pairs with S.No 194 (which reworded the agent to Option A); implementing this would move the agent's Completion wording back toward platform-executes.</t>
+        </is>
+      </c>
+      <c r="J197" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
       </c>
     </row>
     <row r="198" spans="1:1">

--- a/docs/Bugs.xlsx
+++ b/docs/Bugs.xlsx
@@ -10345,9 +10345,49 @@
         </is>
       </c>
     </row>
-    <row r="198" spans="1:1">
+    <row r="198" spans="1:10">
       <c r="A198" s="2">
         <v>197</v>
+      </c>
+      <c r="B198" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Greenfield flow does NOT populate the Knowledge Index, so its retrieval is dead for greenfield projects. The Knowledge Index (apps/knowledge) chunks artifact bodies into KnowledgeChunk rows and retrieve() ranks them with a hybrid of BM25 keyword + optional vector cosine (fused via Reciprocal Rank Fusion). But index_artifact is only called during brownfield onboarding - never on greenfield artifact registration/publish. So for a greenfield project retrieve() returns nothing, get_context's _retrieve_knowledge yields [], and agents rely solely on the required+situational artifact tiers. Separately, semantic search is globally OFF (EMBEDDING_PROVIDER=null) so even where chunks exist, only the keyword baseline runs and the pgvector column is empty.</t>
+        </is>
+      </c>
+      <c r="D198" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Knowledge Index / greenfield context retrieval</t>
+        </is>
+      </c>
+      <c r="E198" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Enhancement</t>
+        </is>
+      </c>
+      <c r="F198" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Verified 2026-07-23. index_artifact is called ONLY from backend/integrations/onboarding.py:400 (brownfield); no call on greenfield register/publish. Live backend env: EMBEDDING_PROVIDER=null (BM25-only; pgvector column unused). retrieve() (backend/apps/knowledge/index.py:106) already fuses BM25 + vector cosine via RRF and falls back to keyword if embeddings fail/are off. Providers built + ready: Voyage voyage-code-3 (dim 1024), Gemini gemini-embedding-001 (dim 1536); current column dim = 1536.</t>
+        </is>
+      </c>
+      <c r="G198" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P3</t>
+        </is>
+      </c>
+      <c r="H198" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">index_artifact was wired only into brownfield onboarding; greenfield artifact registration/publish never indexes. The embedding provider defaults to null (zero-cost baseline), so vectors are off platform-wide. Neither is a defect in the retrieval engine (which already does hybrid search) - it is unwired population + a disabled provider.</t>
+        </is>
+      </c>
+      <c r="I198" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PLANNED (enhancement + team decision on hybrid). (1) Populate greenfield: call index_artifact on artifact PUBLISH (gated), same path brownfield uses - publish-only (not every draft) to bound embedding cost. (2) Enable semantic search via a provider: Gemini gemini-embedding-001 (dim 1536) matches the current column so NO re-migration; Voyage voyage-code-3 (dim 1024, code-optimized) would need a column re-migration + re-embed. (3) KEEP the hybrid (team idea, already implemented): retrieve() fuses BM25 + vector via RRF so keyword covers exact identifiers, vectors cover meaning/synonyms, and it degrades gracefully to keyword-only if embeddings are off/fail. Pros of vector: semantic match, better on mature projects, fits agents' NL queries. Cons: per-chunk API cost+latency, external dependency/keys, dimension lock-in at migration, weaker on exact tokens, extra privacy egress. Net: enable greenfield population + turn on Gemini, keep both methods fused.</t>
+        </is>
+      </c>
+      <c r="J198" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
       </c>
     </row>
     <row r="199" spans="1:1">

--- a/docs/Bugs.xlsx
+++ b/docs/Bugs.xlsx
@@ -6369,11 +6369,15 @@
       <c r="G77" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="H77" s="2" t="s">
-        <v>318</v>
-      </c>
-      <c r="I77" s="2" t="s">
-        <v>319</v>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The edit UI was never built - only the WorkItemPatchSerializer (title/description/type/repo) was scaffolded on the backend; no frontend form calls it (the patch hook is wired only to the repo field on the Repo-Assignment card). state, estimate and depends_on are not editable (state is read-only, there is no estimate field, depends_on is excluded from the patch serializer).</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OPEN - surgical fix (recon 2026-07-24): FRONTEND-ONLY for the common case - add a small edit form/modal in WorkItemTask.tsx / WorkItemEpic.tsx that calls the existing usePatchWorkItem with {title, description, type}; no backend change needed (the PATCH endpoint is already live and tested). To also edit dependencies, add depends_on to WorkItemPatchSerializer.fields with same-project + no-cycle validation (mirror the repo check in perform_update). Estimate is out of scope until a WorkItem.estimate field is modelled (see S.No 75).</t>
+        </is>
       </c>
       <c r="J77" s="2" t="s">
         <v>141</v>
@@ -7265,11 +7269,15 @@
       <c r="G105" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="H105" s="2" t="s">
-        <v>493</v>
-      </c>
-      <c r="I105" s="2" t="s">
-        <v>494</v>
+      <c r="H105" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Two sources of truth for topology. Source A (backend, authoritative): repos.py _topology_for derives repo_topology from repo COUNT (&gt;=3 multi, ==2 split, else single) and _recompute_topology re-writes it on every add/remove repository. Source B (frontend): CreateProject.tsx offers only Single/Multi (2 of the model's 3 values) and posts repo_topology, which perform_create honours - but the first repo add/remove then recomputes and silently overrides the user's pick. Confirmed no backend feature branches on topology=='multi' (drift/api-contract do NOT read it); it is informational (manifest/context only).</t>
+        </is>
+      </c>
+      <c r="I105" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OPEN - surgical fix (recon 2026-07-24), Option (b), lowest risk: keep the count-derived value as the single source of truth (backend + tests unchanged - many tests assert derived values) and stop the create form presenting a choice it does not honour - drop the topology segmented control from CreateProject.tsx (or relabel it a non-authoritative hint) and widen the 2-value type in types.ts / hooks.ts. Topology then simply follows the repos actually registered. Option (a) - honour the explicit choice and stop auto-deriving - is higher risk (rewrites the derived-value tests, needs the missing 'Split' option added) and is not recommended since nothing branches on the value.</t>
+        </is>
       </c>
       <c r="J105" s="2" t="s">
         <v>141</v>
@@ -7678,6 +7686,16 @@
       <c r="G118" s="2" t="s">
         <v>23</v>
       </c>
+      <c r="H118" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The board bucket is computed in WorkItemsBoard.tsx byPhase from item.current_phase, which the backend derives (WorkItemViewSet._card_fields) as the latest Run's agent-spec key. Freshly fanned-out Task Breakdown items are state='proposed' with NO run yet, so current_phase='' - and byPhase falls phase-less items back to columns[0]. In the default board columns[0] is 01_ideation (Ideation column); when filtered to Tasks the columns switch to BUILD_COLUMNS whose first entry is 'implementation' (Implementation column). Both reported symptoms are the same defect: not-yet-run items blindly land in the first column.</t>
+        </is>
+      </c>
+      <c r="I118" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OPEN - surgical fix (recon 2026-07-24), FRONTEND-ONLY (WorkItemsBoard.tsx): add an explicit 'Backlog / Not started' column to PHASE_COLUMNS and BUILD_COLUMNS and, in byPhase, route items with an empty current_phase (or state=='proposed') to it instead of defaulting to columns[0]. No backend change. Update phases.test.ts / lifecycle.test.tsx if they assert on the column set/counts. Optional backend alternative: have _card_fields set current_phase to the producing phase for un-run items - larger semantic change, not needed.</t>
+        </is>
+      </c>
       <c r="J118" s="2" t="s">
         <v>141</v>
       </c>
@@ -7727,6 +7745,16 @@
       <c r="G120" s="2" t="s">
         <v>23</v>
       </c>
+      <c r="H120" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WorkItemDetail.tsx routes epic AND story to WorkItemEpic; only the leaf WorkItemTask renders the navigable 'Related work items' child-link panel (maps lifecycle.children to /work-items/{id} links). WorkItemEpic shows children only as a raw count ('Children: N'), never as links - so an epic shows a number not clickable stories, and a story (also routed to WorkItemEpic) shows a number not clickable tasks. The lifecycle endpoint already returns the DIRECT children at each level, so the epic-&gt;story-&gt;task data is present; the parent view just doesn't render it as navigation.</t>
+        </is>
+      </c>
+      <c r="I120" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OPEN - surgical fix (recon 2026-07-24), FRONTEND-ONLY, additive: add a 'Related work items' child-link panel to WorkItemEpic.tsx (mirror the one in WorkItemTask.tsx) that renders lifecycle.children as /work-items/{id} links. Each level then lists its own direct children, giving epic-&gt;story-&gt;task drill navigation. Low risk (additive UI); check WorkItemEpicGallery / lifecycle.test.tsx expectations. Optional: fix the child rows' mislabelled phase (views.py emits c.feature_stream as 'phase' - same class as the row-50 feature-stream/phase fix).</t>
+        </is>
+      </c>
       <c r="J120" s="2" t="s">
         <v>141</v>
       </c>
@@ -8369,11 +8397,15 @@
       <c r="G141" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="H141" s="2" t="s">
-        <v>687</v>
-      </c>
-      <c r="I141" s="2" t="s">
-        <v>688</v>
+      <c r="H141" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WorkItem.state is read-only on the API (excluded from WorkItemPatchSerializer, read_only on the read serializer) and is mutated ONLY by the orchestrator (successful build+merge / gate / reject / takeover). No human-facing transition endpoint exists; the frontend offers only Retry / Trigger phase / manual takeover (sets takeover_flag, not state). The MCP transition_work_item allows any-&gt;any but is unexposed to users, and there is no terminal state other than 'done' to mark a redundant/abandoned item.</t>
+        </is>
+      </c>
+      <c r="I141" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OPEN - surgical fix (recon 2026-07-24): add a GATED, AUDITED human-transition endpoint on WorkItemViewSet (@action 'transition') - role-checked (reuse resolve_actor + the gate-role pattern), accepting only an ALLOWLISTED set of human transitions (NOT the MCP any-&gt;any), and writing a ledger Event. Surface 'Mark done / Close as redundant / Skip' on the Work Items board + task page. Add a terminal CANCELLED (optionally CLOSED) value to WorkItem.State via a small migration so human-closed stays distinct from build-completed 'done'; audit every state-mapping site (frontend statusLabel, board columns, lifecycle rail run_status_to_node_state) when adding the value. The migration is the only non-trivial part; the orchestrator keeps its own unrestricted transition path. Related S.No 76.</t>
+        </is>
       </c>
       <c r="J141" s="2" t="s">
         <v>141</v>
@@ -8719,6 +8751,16 @@
       <c r="G154" s="2" t="s">
         <v>23</v>
       </c>
+      <c r="H154" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Artifacts are pointer-only by design (#1/#3): the Artifact row stores s3_key/content_hash/version/status, bodies live in S3 as run/phase-scoped drafts written by the agent-only MCP tool stage_artifact_body. The REST ArtifactViewSet is ReadOnly - its only body route is 'preview' (explicitly 'never an editor'), and update_artifact (MCP-only) mutates pointers/metadata, never a body. So there is no human path to edit a generated draft body.</t>
+        </is>
+      </c>
+      <c r="I154" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OPEN - surgical fix (recon 2026-07-24): add a DRAFT-ONLY edit path that respects the no-auto-publish non-negotiable (#5) - a new @action (e.g. 'edit') on ArtifactViewSet (allowed on a ReadOnly viewset) or a small service that: rejects unless status=='draft' AND sor=='internal', re-stages the edited body to S3 via the existing stage_artifact_body mechanics, updates s3_key + content_hash and bumps version, and writes an Event. Frontend: swap the read-only Markdown block in ArtifactPreviewScreen.tsx for an editable textarea + Save when status=='draft'. Scope the first cut to single-body markdown/text; multi-state wireframe HTML is a later pass. Medium size; the ONLY risk is letting an edit touch a staged/approved/published body - restrict strictly to draft+internal and it never bypasses a gate.</t>
+        </is>
+      </c>
       <c r="J154" s="2" t="s">
         <v>141</v>
       </c>
@@ -8759,6 +8801,16 @@
       <c r="G156" s="2" t="s">
         <v>23</v>
       </c>
+      <c r="H156" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IntegrationConnection is TenantScopedModel with NO project FK (unlike SourceDocument/DriftRecord in the same app, which are project-scoped), so a connection is shared across the whole tenant. The single resolution choke point is registry.get_connection(tenant_id, capability); the per-capability builders read creds via Config.from_connection(conn) and don't care about tenant-vs-project. RLS is tenant-based; adding a project filter needs NO RLS change (isolation stays at the tenant boundary). The cost is that ~16 resolution call sites (build_activities, review_provider, reconcile, publish, onboarding, design, preview, quality, views, repos) mostly carry only tenant_id, plus ~20 tests monkeypatch get_capability(tid,cap).</t>
+        </is>
+      </c>
+      <c r="I156" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OPEN - surgical INCREMENTAL path (recon 2026-07-24) - the naive per-project rewrite is deep, so do it in safe steps: (1) add a NULLABLE project FK to IntegrationConnection (existing rows become tenant-wide defaults; plain column+index migration, no RLS change); (2) make get_connection/get_capability take an OPTIONAL project_id kwarg and resolve project-first with tenant fallback: filter(tenant, capability, project_id).first() or filter(tenant, capability, project__isnull=True).first() - every existing caller keeps compiling and behaves exactly as today; (3) relax create_integration uniqueness from (tenant,capability) to (tenant,project,capability) and add project to the serializers/API/frontend; (4) thread project_id into the resolution call sites and their input structs one at a time. Regression risk is LOW while project_id stays an optional fallback kwarg (HIGH only if signatures change eagerly). Projects override selectively while tenant-wide connections keep working.</t>
+        </is>
+      </c>
       <c r="J156" s="2" t="s">
         <v>141</v>
       </c>
@@ -9195,11 +9247,15 @@
       <c r="H170" s="2" t="s">
         <v>811</v>
       </c>
-      <c r="I170" s="2" t="s">
-        <v>812</v>
-      </c>
-      <c r="J170" s="2" t="s">
-        <v>141</v>
+      <c r="I170" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FIXED - resolved by the S.No 89 work (non-terminal STALLED park). mark_phase_takeover_core now marks the run STALLED (not terminal FAILED) and register_phase_result_core clears takeover_flag on a late successful report, so a companion that went offline (e.g. laptop asleep) then returned and reported ok un-parks the run and flows on through register-&gt;verify-&gt;gate-&gt;publish; the false 'engine exited, no artifact' terminal-fail can no longer occur. Verified in backend/orchestration/activities.py (mark_phase_takeover_core + register_phase_result_core, both cite Bugs S.No 89).</t>
+        </is>
+      </c>
+      <c r="J170" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fixed</t>
+        </is>
       </c>
     </row>
     <row r="171" spans="1:10" ht="210.75">
@@ -10066,12 +10122,12 @@
       </c>
       <c r="I191" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">PLANNED (team-approved 2026-07-22, unified push+pull design): declare each agent's required artifact types ONCE in the catalog (AgentDefinition.needs_artifacts - single source of truth like rides_build); get_context builds a GUARANTEED required tier (latest version per declared type, repo-scoped) that is always injected and never evicted, PLUS a small capped situational-recency tail (team approved keeping the tail for safety). Thread agent_key into get_context; composer renders required-first; missing required types surfaced as named gaps. General across ALL phases. Paired with S.No 191 (accurate on-demand pull by type).</t>
+          <t xml:space="preserve">FIXED - implemented in code (commits c00a26c / ef37bf9, 2026-07-22). Each agent now DECLARES its required upstream artifact types once in the catalog (AgentDefinition.needs_artifacts) with a needs_artifacts_for() resolver; get_context / the Manifest Composer build a GUARANTEED required tier (latest version per declared type) that is always injected and never evicted by the recency tail, so a late-lifecycle phase always receives the specific upstream inputs its body names. Verified in backend/apps/registry/catalog.py + backend/manifest/composer.py + mcp_platform_state. Paired with S.No 191.</t>
         </is>
       </c>
       <c r="J191" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Open</t>
+          <t xml:space="preserve">Fixed</t>
         </is>
       </c>
     </row>
@@ -10111,12 +10167,12 @@
       </c>
       <c r="I192" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">PLANNED (team-approved 2026-07-22): add a `type` filter to list_artifacts (tools.py) and expose it through the companion state_mcp wrapper; add a Manifest Composer instruction line telling agents to fetch any artifact not pre-injected via list_artifacts(type=...) then get_artifact_body(id). Completes the push+pull design with S.No 190.</t>
+          <t xml:space="preserve">FIXED - implemented in code (2026-07-22). list_artifacts now takes a `type` filter (mcp_platform_state/tools.py, exposed through server.py and the companion state_mcp wrapper) so an agent can pull a specific upstream artifact by type on demand - list_artifacts(type='architecture') then get_artifact_body(id) - and the Manifest Composer instructs agents to use it for any input not pre-injected. Completes the push+pull design with S.No 190. Verified: tools.py list_artifacts type-filter cites Bugs S.No 191.</t>
         </is>
       </c>
       <c r="J192" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Open</t>
+          <t xml:space="preserve">Fixed</t>
         </is>
       </c>
     </row>

--- a/docs/Bugs.xlsx
+++ b/docs/Bugs.xlsx
@@ -10446,9 +10446,49 @@
         </is>
       </c>
     </row>
-    <row r="199" spans="1:1">
+    <row r="199" spans="1:10">
       <c r="A199" s="2">
         <v>198</v>
+      </c>
+      <c r="B199" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Connect-machine token generation fails silently when the workspace has no project, and the UI shows a fake placeholder token instead of the real error. A new member (e.g. a QA tester) creates a workspace but has not created a project yet, opens "Connect your machine" and clicks "Generate enrollment token". The screen appears to produce a token and shows the companion serve command, but the token displayed is a hardcoded placeholder "rnr_3f9a…b2" (note the literal ellipsis) — not a real token — so the companion cannot authenticate. Reported by a QA member who ran: python -m runner.companion serve --api-url http://localhost:8000 --tenant ce135c3e-... --token rnr_3f9a…b2. A genuine token is a ~43-character secrets.token_urlsafe(32) string with no rnr_ prefix and no ellipsis, so what he copied was never a real (or partial) token — generation had actually failed and the failure was masked as a valid-looking token.</t>
+        </is>
+      </c>
+      <c r="D199" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Connect Machine / companion enrollment (S-06)</t>
+        </is>
+      </c>
+      <c r="E199" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bug</t>
+        </is>
+      </c>
+      <c r="F199" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Reported 2026-07-24 by a QA member on a newly-created workspace that had no project yet. Verified in code (no screenshot): the string "rnr_3f9a…b2" is a hardcoded mock placeholder, not a truncated real token.</t>
+        </is>
+      </c>
+      <c r="G199" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P2</t>
+        </is>
+      </c>
+      <c r="H199" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Two layers. (1) The enroll endpoint requires a valid project: RunnerEnrollmentView.post (backend/api/runner_views.py:165-170) returns HTTP 400 ("project_id required" / "not found in tenant") when project_id is missing/invalid. (2) The Connect-machine screen picks the project from currentUser.memberships[0].project_id (frontend/src/features/identity/ConnectMachine.tsx:64); a brand-new workspace with no project has no membership, so project_id is empty and the POST 400s. The onGenerate catch block (ConnectMachine.tsx:68-70) swallows that error and calls setToken("rnr_3f9a…b2") — the same hardcoded placeholder used as the null fallback at line 61 — so a failed generation is rendered as a real-looking, copyable token instead of the backend's actual message. Net: there was no project to enroll the companion against, but the UI hid that behind a mock token. Same "fake mock data hides a real failure" pattern already fixed once on the invite-accept page (commit b77bdff).</t>
+        </is>
+      </c>
+      <c r="I199" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PLANNED (not yet fixed). Immediate workaround: the member must create a project (and be a member of it) before generating the token — then the button returns a real ~43-char token and the serve command authenticates. Proper fix (frontend, ConnectMachine.tsx): on token-generate failure, surface the backend's real error message and do NOT fall back to a hardcoded token; guard the flow when the user has no project yet (show a clear "create a project first" prompt) instead of posting an empty project_id; and ensure the placeholder mock value can never be presented as a copyable token.</t>
+        </is>
+      </c>
+      <c r="J199" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
       </c>
     </row>
     <row r="200" spans="1:1">

--- a/docs/Bugs.xlsx
+++ b/docs/Bugs.xlsx
@@ -7719,8 +7719,11 @@
       <c r="G119" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="I119" s="2" t="s">
-        <v>573</v>
+      <c r="I119" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FIXED (2026-07-15). agents/06_task_breakdown/agent.md: added a 'Writing standard' requiring every Epic/Story/Task Description + Acceptance Criterion to be plain-language-with-technical-nuance, detailed and self-contained enough that a developer can implement by reading it ALONE (behaviour, inputs/outputs, states, edge cases), with concrete hand-verifiable acceptance criteria and no bare placeholders; modelled the standard in all three template placeholders. Improvement flows to the Work Items board + artifact previews automatically. Test: test_agents_migration.test_task_breakdown_descriptions_and_ac_are_humanized. Per team decision the blast radius today was 06 only; the SAME defect in 02/09/00c/04/03/10 is logged as S.No 121-126 (register-condition per audience: technical-humanized for testing/security, plain+nuance for the rest) and NOT fixed this session.
+FOLLOW-UP COMPLETION (2026-07-24, verified live by the team). The 2026-07-15 fix set the INSTRUCTION but left the technical exemplars in place, and the model imitates exemplars more than rules — so Epics read well (they already had good plain-language examples) but Tasks still came out too technical. Completed the fix at the EXAMPLE level: agents/06_task_breakdown/agent.md now carries worked Story AND Task exemplars that OPEN with a one-sentence plain-language statement of intent (what it delivers and why) BEFORE the technical detail, with concrete given/when/then acceptance criteria; added an explicit 'lead with plain-language intent' requirement for both Stories and Tasks; and rewrote the terse counter-examples (the endpoint-string title, the venv/env-file acceptance criteria) so nothing pulls the output back to terse. Platform side: backend/manifest/composer.py raised the Current Work Item token budget 300-&gt;650 so long task descriptions reach the implementation agent untruncated (avg 1,263 / max 1,835 chars already exceeded the old ~1,200-char cap). Strengthened the test to assert the intent-lead + the worked exemplars. Committed f27455d (pushed to develop). Team re-ran Task Breakdown on tenant 7828e953 and confirmed a great improvement vs the old artifacts. Scope decision this session was Tasks + Stories; siblings S.No 121-126 (agents 02/09/00c/04/03/10) remain separately Open.</t>
+        </is>
       </c>
       <c r="J119" s="2" t="s">
         <v>16</v>

--- a/docs/Bugs.xlsx
+++ b/docs/Bugs.xlsx
@@ -10494,39 +10494,319 @@
         </is>
       </c>
     </row>
-    <row r="200" spans="1:1">
+    <row r="200" spans="1:10">
       <c r="A200" s="2">
         <v>199</v>
       </c>
-    </row>
-    <row r="201" spans="1:1">
+      <c r="B200" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">09b test-automation run parks with a Postgres DataError ("unsupported Unicode escape sequence ... \u0000 cannot be converted to text") after the PR and artifacts have already been created, even when the generated test itself passed. Reproduced twice on the same test case (WI-95 / TC-001): runs 1299c7de and e583a454 both parked identically with the same corrupted bytes, though neither companion report itself contained a NUL.</t>
+        </is>
+      </c>
+      <c r="D200" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">09b Test Automation / code review manifest</t>
+        </is>
+      </c>
+      <c r="E200" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bug</t>
+        </is>
+      </c>
+      <c r="F200" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Reproduced 2026-07-22, tenant 212395b8-f118-4eef-93eb-ba2c45468226, WI-95 (TC-001), repo TARUN51/medslot-single-repo, PR #31. Confirmed via list_pr_files + get_file that tests/automated/playwright-report/data/*.webm and *.png contained NUL bytes.</t>
+        </is>
+      </c>
+      <c r="G200" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P1</t>
+        </is>
+      </c>
+      <c r="H200" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AgentReviewProvider._render_pr_section (backend/orchestration/review_provider.py:225-245) inlines the content of every PR-changed file into the review manifest, which dispatch_review_task then stores in the JSON run.inputs column. A 09b build commits Playwright report artifacts (screenshots/videos) into the PR; those binaries contain NUL, which Postgres text/jsonb cannot store, so the save fails with DataError and the workflow parks the run as "pr/gate setup failed" - after the PR/test_report/code artifacts already registered successfully. See S.No 201 for the fix that stops new binaries from being committed in the first place.</t>
+        </is>
+      </c>
+      <c r="I200" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fixed. _render_pr_section now skips any file whose content contains a NUL byte (a binary marker) and inlines a "(binary file - omitted from review)" placeholder instead (review_provider.py:246-252). dispatch_review_task also scrubs NUL from the whole payload before saving, as defense-in-depth, via a shared build_types.scrub_nul helper; companion build reports are scrubbed the same way in build_report.py. Tests: test_render_pr_section_omits_binary_files, test_dispatch_review_task_scrubs_nul (test_review_dispatch.py), test_report_scrubs_nul_bytes_before_persisting (test_build_report_api.py).</t>
+        </is>
+      </c>
+      <c r="J200" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fixed</t>
+        </is>
+      </c>
+    </row>
+    <row r="201" spans="1:10">
       <c r="A201" s="2">
         <v>200</v>
       </c>
-    </row>
-    <row r="202" spans="1:1">
+      <c r="B201" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A 09b remediation build (auto-fixing a code-review finding) fails immediately with "no preview target for this repo - set the repo's Preview URL...", even though the repo's Preview URL was already set and the initial build had just run successfully against it.</t>
+        </is>
+      </c>
+      <c r="D201" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">09b Test Automation / remediation loop</t>
+        </is>
+      </c>
+      <c r="E201" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bug</t>
+        </is>
+      </c>
+      <c r="F201" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Reproduced 2026-07-22 on WI-95/TC-001 after the 08 review opened REM-W2/REM-W3; the run went straight to status=failed right after the build.remediation_dispatched event.</t>
+        </is>
+      </c>
+      <c r="G201" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P1</t>
+        </is>
+      </c>
+      <c r="H201" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dispatch_build_core (backend/orchestration/build_activities.py:62-81) ships payload['preview_url']/['preview_start'] for the test_automation phase, but dispatch_remediation_core (build_activities.py:781-826), which re-dispatches 09b to fix review findings, built its payload without that block - so the companion's remediation build had no preview target and its fail-loud guard tripped instantly. See S.No 199 for the review-manifest bug found on the same run.</t>
+        </is>
+      </c>
+      <c r="I201" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fixed. dispatch_remediation_core now ships the same preview_url/preview_start (resolved via apps.projects.preview_config), phase-gated identically to the initial dispatch (build_activities.py:816-822). Test: test_dispatch_remediation_ships_preview_for_test_automation (test_review_dispatch.py).</t>
+        </is>
+      </c>
+      <c r="J201" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fixed</t>
+        </is>
+      </c>
+    </row>
+    <row r="202" spans="1:10">
       <c r="A202" s="2">
         <v>201</v>
       </c>
-    </row>
-    <row r="203" spans="1:1">
+      <c r="B202" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The 09b test-automation agent commits its own generated run output (Playwright HTML report, test-results, MCP exploration snapshots) into the PR alongside the authored test script. These directories are bulky (one PR carried a 533KB report index.html plus screenshots and a video) and can contain binary files - the root cause of the review-manifest NUL crash at S.No 199. The 08 code review itself independently flagged this as a finding (REM-W1: "Generated Playwright artifacts... committed").</t>
+        </is>
+      </c>
+      <c r="D202" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">09b Test Automation / generated worktree output</t>
+        </is>
+      </c>
+      <c r="E202" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Enhancement</t>
+        </is>
+      </c>
+      <c r="F202" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Observed 2026-07-22, PR #31 (medslot-single-repo): tests/automated/playwright-report/, tests/automated/test-results/, and .playwright-mcp/ were all committed by the build.</t>
+        </is>
+      </c>
+      <c r="G202" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P2</t>
+        </is>
+      </c>
+      <c r="H202" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The 09b agent body had no instruction to ignore generated run/report output, so every file the dry run (Step 6) or Playwright MCP (Step 4) wrote into the worktree was committed by the platform, which commits everything present in the worktree.</t>
+        </is>
+      </c>
+      <c r="I202" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fixed. Added a required ".gitignore" step to agents/09b_test_automation/agent.md Step 3 (Scaffolding Detection, line 123 on): the agent creates/extends a worktree-root .gitignore excluding .playwright-mcp/, playwright-report/, test-results/, blob-report/, and framework build/cache directories, while still committing the authored test scripts, page objects, and config. Note: does not retroactively untrack files a prior run already committed on the same branch - see S.No 205.</t>
+        </is>
+      </c>
+      <c r="J202" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fixed</t>
+        </is>
+      </c>
+    </row>
+    <row r="203" spans="1:10">
       <c r="A203" s="2">
         <v>202</v>
       </c>
-    </row>
-    <row r="204" spans="1:1">
+      <c r="B203" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The "Test cases" coverage screen (per-story test-case list with automation status + Generate script) has no link anywhere in the UI - it is only reachable by typing its URL (/work-items/:id/test-cases) directly.</t>
+        </is>
+      </c>
+      <c r="D203" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Test cases (P3-09b coverage screen)</t>
+        </is>
+      </c>
+      <c r="E203" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Enhancement</t>
+        </is>
+      </c>
+      <c r="F203" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Observed 2026-07-22 while trying to generate a script for TC-001 on WI-70: the epic/story detail page had no way to navigate to its test cases.</t>
+        </is>
+      </c>
+      <c r="G203" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P2</t>
+        </is>
+      </c>
+      <c r="H203" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The coverage screen (frontend/src/features/lifecycle/TestCases.tsx) and its route were built, but the intended entry point (a tabbed story/epic detail) was deferred as a later enhancement, and no interim link was added in the meantime.</t>
+        </is>
+      </c>
+      <c r="I203" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fixed. Added a "Test cases" button to the work-item detail header (frontend/src/features/lifecycle/WorkItemEpic.tsx:88-92), linking to /work-items/:id/test-cases. The tabbed story/epic detail remains a separately deferred enhancement.</t>
+        </is>
+      </c>
+      <c r="J203" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fixed</t>
+        </is>
+      </c>
+    </row>
+    <row r="204" spans="1:10">
       <c r="A204" s="2">
         <v>203</v>
       </c>
-    </row>
-    <row r="205" spans="1:1">
+      <c r="B204" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The companion always runs the 09b Playwright MCP (and the generated test suite) headless, so a developer watching a run locally has no way to see the agent explore the app or the test execute, even while attended at the keyboard.</t>
+        </is>
+      </c>
+      <c r="D204" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Companion runner / 09b Live Application Exploration</t>
+        </is>
+      </c>
+      <c r="E204" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Enhancement</t>
+        </is>
+      </c>
+      <c r="F204" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Requested 2026-07-22, to observe a local 09b run end-to-end (locator discovery + test execution) for QA/demo purposes.</t>
+        </is>
+      </c>
+      <c r="G204" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P3</t>
+        </is>
+      </c>
+      <c r="H204" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">build_mcp_servers always passed --headless to the Playwright MCP (runner/companion/runner.py), and the agent's generated Playwright config had no signal telling it to run visibly instead.</t>
+        </is>
+      </c>
+      <c r="I204" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fixed. Added SDLC_COMPANION_HEADED, read by _headed_enabled() (runner/companion/runner.py:112-117): drops --headless from the Playwright MCP, and manifest_with_preview injects an instruction so the agent generates "headless: !process.env.SDLC_COMPANION_HEADED" in playwright.config.ts, so the same config still runs headless in CI. Added "serve --headed" as a first-class flag (runner/companion/__main__.py:110-115) that sets the env var in-process, so no separate shell export is needed. Default remains headless.</t>
+        </is>
+      </c>
+      <c r="J204" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fixed</t>
+        </is>
+      </c>
+    </row>
+    <row r="205" spans="1:10">
       <c r="A205" s="2">
         <v>204</v>
       </c>
-    </row>
-    <row r="206" spans="1:1">
+      <c r="B205" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">In Phases &amp; Runs, every catalog phase (Ideation .. Deployment) is shown as triggerable for ANY work-item type, including a test_case WI - a user can trigger "Ideation" or "Task Breakdown" on a test case, which is meaningless for that type and only 09b_test_automation should apply.</t>
+        </is>
+      </c>
+      <c r="D205" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Phases &amp; Runs / phase catalog</t>
+        </is>
+      </c>
+      <c r="E205" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Enhancement</t>
+        </is>
+      </c>
+      <c r="F205" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Observed 2026-07-22 while triggering 09b Test Automation on a test_case work item (WI-95): all ~16 phases appeared as trigger options, not just Test Automation.</t>
+        </is>
+      </c>
+      <c r="G205" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P3</t>
+        </is>
+      </c>
+      <c r="H205" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">There is no per-WI-type phase gating in the trigger UI or backend catalog - the phase picker (frontend/src/features/lifecycle/PhasesAndRuns.tsx) renders every catalog entry regardless of the selected work item's type.</t>
+        </is>
+      </c>
+      <c r="I205" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not fixed - deferred. Would need the phase catalog (or the picker) to filter by work_item.type, e.g. only 09b_test_automation (and perhaps re-running 09_testing) for type=test_case.</t>
+        </is>
+      </c>
+      <c r="J205" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="206" spans="1:10">
       <c r="A206" s="2">
         <v>205</v>
+      </c>
+      <c r="B206" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A .gitignore added by the 09b agent (S.No 201) only stops NEW files from being committed going forward - it does not untrack files a prior run on the SAME branch already committed (e.g. Playwright report binaries from an earlier attempt). Resuming or remediating on an existing branch/PR can therefore keep re-triggering the code review's binary-artifact finding (REM-W1, S.No 199) even after the .gitignore fix ships.</t>
+        </is>
+      </c>
+      <c r="D206" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">09b Test Automation / worktree branch reuse</t>
+        </is>
+      </c>
+      <c r="E206" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Enhancement</t>
+        </is>
+      </c>
+      <c r="F206" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Observed 2026-07-22: re-running 09b on the same branch/PR (#31) after adding the .gitignore rule still showed the previously-committed playwright-report binaries until the branch was closed and recreated from scratch.</t>
+        </is>
+      </c>
+      <c r="G206" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P3</t>
+        </is>
+      </c>
+      <c r="H206" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Git's .gitignore only governs untracked files from that point forward; files already added to the index/history stay tracked. The platform reuses the existing branch/worktree for a resumed or re-triggered build (register-don't-recreate), so old committed binaries persist across runs.</t>
+        </is>
+      </c>
+      <c r="I206" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not fixed - workaround documented: close the PR, delete the remote branch, and let 09b start a fresh branch so the new .gitignore takes effect from the first commit. A platform-side fix (e.g. "git rm --cached" the newly-ignored paths on resume) is not implemented.</t>
+        </is>
+      </c>
+      <c r="J206" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
       </c>
     </row>
     <row r="207" spans="1:1">

--- a/docs/Bugs.xlsx
+++ b/docs/Bugs.xlsx
@@ -10809,29 +10809,229 @@
         </is>
       </c>
     </row>
-    <row r="207" spans="1:1">
+    <row r="207" spans="1:10">
       <c r="A207" s="2">
         <v>206</v>
       </c>
-    </row>
-    <row r="208" spans="1:1">
+      <c r="B207" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A build (or phase) Run dispatched with inputs.dispatch.enrollment_id=null matched no companion in the claim query, so it sat running+pending forever, invisible in the UI, and blocked new triggers on the same WorkItem.</t>
+        </is>
+      </c>
+      <c r="D207" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Runner dispatch / claim (RunnerWorkClaimView)</t>
+        </is>
+      </c>
+      <c r="E207" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bug</t>
+        </is>
+      </c>
+      <c r="F207" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Surfaced 2026-07-21, tenant 212395b8-f118-4eef-93eb-ba2c45468226. Two paths hit it: the S.No 161 remediation auto-retry called trigger_build without triggered_by, and a user triggering before their companion enrolled. Validated live: run 812577a3 self-healed after the fix.</t>
+        </is>
+      </c>
+      <c r="G207" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P1</t>
+        </is>
+      </c>
+      <c r="H207" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RunnerWorkClaimView's claim query only matched Run.inputs.dispatch.enrollment_id == runner.id - a dispatch created with enrollment_id=null (no companion known yet) matched nothing, so no companion could ever claim it.</t>
+        </is>
+      </c>
+      <c r="I207" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fixed. backend/api/runner_views.py: the claim query now also broadcast-matches any pending/claimed dispatch with enrollment_id null/empty for the same tenant+project, and binds enrollment_id to the claiming companion. backend/orchestration/build_activities.py: handle_remediation_exhausted_core now forwards triggered_by into the retry's trigger_build call so retries route to the original companion instead of null. Tests added in test_phase_dispatch.py, test_build_activities.py.</t>
+        </is>
+      </c>
+      <c r="J207" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fixed</t>
+        </is>
+      </c>
+    </row>
+    <row r="208" spans="1:10">
       <c r="A208" s="2">
         <v>207</v>
       </c>
-    </row>
-    <row r="209" spans="1:1">
+      <c r="B208" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Clicking Retry run on a build whose feature branch a prior attempt had already pushed failed with "Empty build: the agent produced no changes to commit", even though real work already existed on the branch.</t>
+        </is>
+      </c>
+      <c r="D208" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Companion build retry / worktree (runner/companion)</t>
+        </is>
+      </c>
+      <c r="E208" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bug</t>
+        </is>
+      </c>
+      <c r="F208" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Surfaced 2026-07-21 on WI-45's retry after a companion redeploy. Validated live on WI-f717ea04 (merged) after the fix; also validated with a standalone host git script reproducing the exact retry scenario.</t>
+        </is>
+      </c>
+      <c r="G208" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P1</t>
+        </is>
+      </c>
+      <c r="H208" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">S.No 162's branch-continuity provisions the retry worktree from the branch's remote tip, not local/base. If the agent makes no new local commit on retry (the real work is already on the pushed branch), run_build left head_sha empty, and the empty-build guard failed the run even though the branch has real commits ahead of base.</t>
+        </is>
+      </c>
+      <c r="I208" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fixed. runner/companion/worktree.py adds commits_ahead_of_base(). runner/companion/runner.py's run_build now reports the existing branch tip as head_sha when there's no new local commit but the branch is already ahead of base, so the saga opens/continues the PR against the existing work instead of false-failing. Tests added in test_companion_runner.py.</t>
+        </is>
+      </c>
+      <c r="J208" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fixed</t>
+        </is>
+      </c>
+    </row>
+    <row r="209" spans="1:10">
       <c r="A209" s="2">
         <v>208</v>
       </c>
-    </row>
-    <row r="210" spans="1:1">
+      <c r="B209" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Follow-up to S.No 161: when remediation exhausts an attempt and the platform auto-starts a fresh run, the user got no proactive signal - the failed run's console showed 'auto-retrying' text but no link to the new run, so a WorkItem appeared to show a failed run AND a separate pending gate with nothing connecting them.</t>
+        </is>
+      </c>
+      <c r="D209" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Run console / lifecycle (RunConsole.tsx)</t>
+        </is>
+      </c>
+      <c r="E209" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Enhancement</t>
+        </is>
+      </c>
+      <c r="F209" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Confirmed this confused a user reviewing WI-43's gate. Backend already stored retry_run_id on the failed run's outputs (build_activities.py); zero frontend references to it before this fix.</t>
+        </is>
+      </c>
+      <c r="G209" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P2</t>
+        </is>
+      </c>
+      <c r="H209" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The notification bell only counts pending gates + clarifications (AppShell.tsx bellCount), and the failed-run view never rendered the stored outputs.retry_run_id, so the two runs for the same WorkItem appeared unrelated.</t>
+        </is>
+      </c>
+      <c r="I209" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fixed. frontend/src/features/lifecycle/RunConsole.tsx: the failed view now reads outputs.retry_run_id, shows an info banner ("The platform started a fresh attempt...") with a live status link to the retry run, and swaps the primary action to "Go to the retry run -&gt;" when one exists. Shipped as PR #7, merged to develop (aafd1f9).</t>
+        </is>
+      </c>
+      <c r="J209" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fixed</t>
+        </is>
+      </c>
+    </row>
+    <row r="210" spans="1:10">
       <c r="A210" s="2">
         <v>209</v>
       </c>
-    </row>
-    <row r="211" spans="1:1">
+      <c r="B210" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">When a companion dies/hangs mid-build (e.g. crashes during a remediation cycle), the claimed run just sits running with no user-facing signal until the orchestrator's takeover reconciler eventually fires and fails it - the user has no way to know earlier that their companion needs restarting.</t>
+        </is>
+      </c>
+      <c r="D210" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Runner heartbeat / takeover reconciler</t>
+        </is>
+      </c>
+      <c r="E210" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Enhancement</t>
+        </is>
+      </c>
+      <c r="F210" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Observed 2026-07-22 on WI-59 (run 925e7fde): companion 4a34ecf2's last heartbeat was 06:50:55 UTC; the run sat claimed/running with zero new events until "Build takeover - runner offline / no report before timeout" finally fired and failed it, well over an hour later. Retriggering after restarting the companion completed the build successfully.</t>
+        </is>
+      </c>
+      <c r="G210" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P3</t>
+        </is>
+      </c>
+      <c r="H210" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The takeover timeout is the only mechanism that reconciles a dead companion's claim; there is no earlier heartbeat-staleness check that surfaces a warning to the user while the run is still nominally in-flight.</t>
+        </is>
+      </c>
+      <c r="I210" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not fixed. Suggested: surface a "companion appears offline" warning on the run console (and/or the companion status pill) once RunnerEnrollment.last_seen exceeds the ONLINE_THRESHOLD for a run that is still claimed/running, instead of waiting for the full takeover window.</t>
+        </is>
+      </c>
+      <c r="J210" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="211" spans="1:10">
       <c r="A211" s="2">
         <v>210</v>
+      </c>
+      <c r="B211" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Two independently-dispatched work items (TASK-021 ExpenseRepository CRUD and TASK-033 DashboardService) each implemented get_monthly_total/get_category_breakdown/get_recent on the same repository class, with different return contracts (plain tuples vs a CategoryTotal dataclass) - since neither WI's planning had visibility into the other's in-flight interface, it only surfaced as an add/add merge conflict when both branches reached main.</t>
+        </is>
+      </c>
+      <c r="D211" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Work-item decomposition / planning - parallel WI interface overlap</t>
+        </is>
+      </c>
+      <c r="E211" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Enhancement</t>
+        </is>
+      </c>
+      <c r="F211" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Surfaced 2026-07-22 resolving WI-59's merge gate conflict against main (already carrying WI-35's merged CRUD repository). Resolved by keeping main's superset repository and adapting DashboardService/tests to the CategoryTotal contract; validated with the full backend suite (412 passed).</t>
+        </is>
+      </c>
+      <c r="G211" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P2</t>
+        </is>
+      </c>
+      <c r="H211" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Planning dispatches WIs against the same file/class independently when their scopes overlap (both needed the same three read methods), with no shared interface contract or ownership check between them before they diverge in the codebase - the S.No 137 recon closed a similar-looking report as a false alarm, but this is a real, reproduced instance of the same class of problem.</t>
+        </is>
+      </c>
+      <c r="I211" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not fixed generally (this instance resolved manually). Suggested: when planning dispatches multiple WIs that touch the same file/module, either serialize them or require an explicit shared interface note so the return contract is agreed before either branch is built.</t>
+        </is>
+      </c>
+      <c r="J211" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
       </c>
     </row>
     <row r="212" spans="1:1">

--- a/docs/Bugs.xlsx
+++ b/docs/Bugs.xlsx
@@ -4193,7 +4193,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J216"/>
+  <dimension ref="A1:J226"/>
   <sheetFormatPr defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="2" bestFit="1" customWidth="1"/>
@@ -11034,33 +11034,533 @@
         </is>
       </c>
     </row>
-    <row r="212" spans="1:1">
+    <row r="212" spans="1:10">
       <c r="A212" s="2">
         <v>211</v>
       </c>
-    </row>
-    <row r="213" spans="1:1">
+      <c r="B212" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No uniqueness check on project name — duplicates are created silently</t>
+        </is>
+      </c>
+      <c r="D212" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Project Setup</t>
+        </is>
+      </c>
+      <c r="E212" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bug</t>
+        </is>
+      </c>
+      <c r="G212" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P2</t>
+        </is>
+      </c>
+      <c r="H212" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Project.name has no unique constraint and the create endpoint is stock DRF, so creating a second project with an existing name succeeds. The workspace ends up with two identically-named projects and the top-bar selector cannot tell them apart. Found by the pre-execution QA audit of the greenfield test pack (docs/qa/AUDIT_FINDINGS.md).</t>
+        </is>
+      </c>
+      <c r="J212" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="213" spans="1:10">
       <c r="A213" s="2">
         <v>212</v>
       </c>
-    </row>
-    <row r="214" spans="1:1">
+      <c r="B213" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">'Set default' on Repositories does nothing — the backend endpoint exists but nothing calls it</t>
+        </is>
+      </c>
+      <c r="D213" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Repositories</t>
+        </is>
+      </c>
+      <c r="E213" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bug</t>
+        </is>
+      </c>
+      <c r="G213" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P3</t>
+        </is>
+      </c>
+      <c r="H213" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">POST .../set-default is implemented and permission-gated on the backend, but the frontend click handler is an empty stub. The control looks live and silently does nothing. Found by the pre-execution QA audit of the greenfield test pack (docs/qa/AUDIT_FINDINGS.md).</t>
+        </is>
+      </c>
+      <c r="J213" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="214" spans="1:10">
       <c r="A214" s="2">
         <v>213</v>
       </c>
-    </row>
-    <row r="215" spans="1:1">
+      <c r="B214" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lifecycle rail ignores the tier it computes — a task shows plan phases</t>
+        </is>
+      </c>
+      <c r="D214" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Work Items</t>
+        </is>
+      </c>
+      <c r="E214" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bug</t>
+        </is>
+      </c>
+      <c r="G214" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P2</t>
+        </is>
+      </c>
+      <c r="H214" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The lifecycle endpoint computes the work item's tier and then never uses it, emitting one node per registered spec regardless. A build-tier task renders the plan-tier phase rail, and the 'No phases run yet.' empty state can never appear. Found by the pre-execution QA audit of the greenfield test pack (docs/qa/AUDIT_FINDINGS.md).</t>
+        </is>
+      </c>
+      <c r="J214" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="215" spans="1:10">
       <c r="A215" s="2">
         <v>214</v>
       </c>
-    </row>
-    <row r="216" spans="1:1">
+      <c r="B215" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Project create, profile edit, work-item write, phase trigger, run takeover and companion enroll are unauthenticated</t>
+        </is>
+      </c>
+      <c r="D215" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Platform / Permissions</t>
+        </is>
+      </c>
+      <c r="E215" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bug</t>
+        </is>
+      </c>
+      <c r="G215" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P1</t>
+        </is>
+      </c>
+      <c r="H215" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DRF's project-wide default permission is AllowAny, and these endpoints never override it. A plain engineer with no admin grant can create projects, rewrite the project profile that every agent reads, create and edit work items, trigger phase runs, take over a run, and enroll a companion machine. Found by the pre-execution QA audit of the greenfield test pack (docs/qa/AUDIT_FINDINGS.md).</t>
+        </is>
+      </c>
+      <c r="J215" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="216" spans="1:10">
       <c r="A216" s="2">
         <v>215</v>
       </c>
+      <c r="B216" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A newly created test case does not appear until the page is reloaded</t>
+        </is>
+      </c>
+      <c r="D216" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Test Cases</t>
+        </is>
+      </c>
+      <c r="E216" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bug</t>
+        </is>
+      </c>
+      <c r="G216" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P3</t>
+        </is>
+      </c>
+      <c r="H216" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The create mutation invalidates the ['work-items'] query key, but the test-case table reads ['test-cases']. Nothing invalidates the list the user is looking at. Found by the pre-execution QA audit of the greenfield test pack (docs/qa/AUDIT_FINDINGS.md).</t>
+        </is>
+      </c>
+      <c r="J216" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="217" spans="1:10">
+      <c r="A217" s="2">
+        <v>216</v>
+      </c>
+      <c r="B217" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">takeover_flag is set and released but never read as a guard</t>
+        </is>
+      </c>
+      <c r="D217" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Recovery &amp; Takeover</t>
+        </is>
+      </c>
+      <c r="E217" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bug</t>
+        </is>
+      </c>
+      <c r="G217" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P3</t>
+        </is>
+      </c>
+      <c r="H217" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The flag's only reader in the backend is the manifest renderer. Trigger admission is decided purely by run status, so the flag guards nothing — and the timeout park sets it itself before any human acts. Found by the pre-execution QA audit of the greenfield test pack (docs/qa/AUDIT_FINDINGS.md).</t>
+        </is>
+      </c>
+      <c r="J217" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="218" spans="1:10">
+      <c r="A218" s="2">
+        <v>217</v>
+      </c>
+      <c r="B218" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">/recovery?run=&lt;id&gt; is inert — there is no way to take over a named run</t>
+        </is>
+      </c>
+      <c r="D218" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Recovery &amp; Takeover</t>
+        </is>
+      </c>
+      <c r="E218" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bug</t>
+        </is>
+      </c>
+      <c r="G218" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P2</t>
+        </is>
+      </c>
+      <c r="H218" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The recovery screen always targets the first stalled-or-failed run it finds in the project. When a ?run= parameter is supplied the target is forced undefined and the screen renders 'No parked runs', so the deep link is worse than useless. 'Take over instead' on the run console also navigates without a run parameter. Found by the pre-execution QA audit of the greenfield test pack (docs/qa/AUDIT_FINDINGS.md).</t>
+        </is>
+      </c>
+      <c r="J218" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="219" spans="1:10">
+      <c r="A219" s="2">
+        <v>218</v>
+      </c>
+      <c r="B219" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Five pieces of dead UI code that can never render</t>
+        </is>
+      </c>
+      <c r="D219" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Platform / UI</t>
+        </is>
+      </c>
+      <c r="E219" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bug</t>
+        </is>
+      </c>
+      <c r="G219" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P3</t>
+        </is>
+      </c>
+      <c r="H219" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The 'Pending gate' artifact badge and its traceability legend colour (pending_gate is not an artifact status); the 'running' work-item badge (not a WorkItem state); the roles gap banner (its condition requires no admin fallback, and a tenant admin always exists); the 'A description is required' validation (gallery-only); the 'Preview unavailable' state for internal artifacts (they 404 to 'Artifact not found' first); and the 'Platform only' system-of-record label (sor is never blank). Found by the pre-execution QA audit of the greenfield test pack (docs/qa/AUDIT_FINDINGS.md).</t>
+        </is>
+      </c>
+      <c r="J219" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="220" spans="1:10">
+      <c r="A220" s="2">
+        <v>219</v>
+      </c>
+      <c r="B220" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Silent failure paths — several actions fail with no message at all</t>
+        </is>
+      </c>
+      <c r="D220" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Platform / UI</t>
+        </is>
+      </c>
+      <c r="E220" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bug</t>
+        </is>
+      </c>
+      <c r="G220" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P2</t>
+        </is>
+      </c>
+      <c r="H220" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Invite resend and revoke have no error handler and the screen has no error surface; a repository 403 is swallowed; GenerateCell trigger errors are dropped; and a short password on accept-invite and on reset, plus a blank signup name, all 400 with the form left untouched. The user cannot tell a failure from a no-op. Found by the pre-execution QA audit of the greenfield test pack (docs/qa/AUDIT_FINDINGS.md).</t>
+        </is>
+      </c>
+      <c r="J220" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="221" spans="1:10">
+      <c r="A221" s="2">
+        <v>220</v>
+      </c>
+      <c r="B221" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A failed request renders as an empty or zero state instead of an error</t>
+        </is>
+      </c>
+      <c r="D221" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Platform / UI</t>
+        </is>
+      </c>
+      <c r="E221" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bug</t>
+        </is>
+      </c>
+      <c r="G221" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P1</t>
+        </is>
+      </c>
+      <c r="H221" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The dashboard, artifacts registry, traceability graph, repositories list and the admin user list all render their empty state when the request fails. A completely broken backend looks like a calm, brand-new workspace — which also means several test cases would pass against it. Found by the pre-execution QA audit of the greenfield test pack (docs/qa/AUDIT_FINDINGS.md).</t>
+        </is>
+      </c>
+      <c r="J221" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="222" spans="1:10">
+      <c r="A222" s="2">
+        <v>221</v>
+      </c>
+      <c r="B222" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">/onboarding sits in the greenfield sidebar and hardcodes brownfield copy</t>
+        </is>
+      </c>
+      <c r="D222" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Onboarding</t>
+        </is>
+      </c>
+      <c r="E222" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bug</t>
+        </is>
+      </c>
+      <c r="G222" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P2</t>
+        </is>
+      </c>
+      <c r="H222" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The onboarding route is rendered in the sidebar for every project regardless of track, and the screen states the project is brownfield with no track check. A greenfield user is one click from a wizard that describes a project they do not have. Found by the pre-execution QA audit of the greenfield test pack (docs/qa/AUDIT_FINDINGS.md).</t>
+        </is>
+      </c>
+      <c r="J222" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="223" spans="1:10">
+      <c r="A223" s="2">
+        <v>222</v>
+      </c>
+      <c r="B223" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Dashboard gates badge is not 'gates needing you' — it is unfiltered and capped at 20</t>
+        </is>
+      </c>
+      <c r="D223" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Dashboard</t>
+        </is>
+      </c>
+      <c r="E223" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bug</t>
+        </is>
+      </c>
+      <c r="G223" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P3</t>
+        </is>
+      </c>
+      <c r="H223" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The count is every pending gate on the project, with no user or role filter, and the underlying query is capped at 20. It reads as a personal to-do count and is neither. Found by the pre-execution QA audit of the greenfield test pack (docs/qa/AUDIT_FINDINGS.md).</t>
+        </is>
+      </c>
+      <c r="J223" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="224" spans="1:10">
+      <c r="A224" s="2">
+        <v>223</v>
+      </c>
+      <c r="B224" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Companion enrollment ignores the project multi-select</t>
+        </is>
+      </c>
+      <c r="D224" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Companion</t>
+        </is>
+      </c>
+      <c r="E224" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bug</t>
+        </is>
+      </c>
+      <c r="G224" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P2</t>
+        </is>
+      </c>
+      <c r="H224" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The 'Projects' multi-select on the enrollment screen is never passed to the enroll call; the token always binds to the first membership. In a multi-project workspace the machine is enrolled against the wrong project with no indication. Found by the pre-execution QA audit of the greenfield test pack (docs/qa/AUDIT_FINDINGS.md).</t>
+        </is>
+      </c>
+      <c r="J224" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="225" spans="1:10">
+      <c r="A225" s="2">
+        <v>224</v>
+      </c>
+      <c r="B225" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">'Published this week' counts artifacts by creation date, not publish date</t>
+        </is>
+      </c>
+      <c r="D225" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Dashboard</t>
+        </is>
+      </c>
+      <c r="E225" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bug</t>
+        </is>
+      </c>
+      <c r="G225" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P3</t>
+        </is>
+      </c>
+      <c r="H225" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Both the 'Published this week' figure and the 'Recent publishes' list filter on created_at. An artifact created eight days ago and published today never appears, and one created today but never published does. Found by the pre-execution QA audit of the greenfield test pack (docs/qa/AUDIT_FINDINGS.md).</t>
+        </is>
+      </c>
+      <c r="J225" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="226" spans="1:10">
+      <c r="A226" s="2">
+        <v>225</v>
+      </c>
+      <c r="B226" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">/admin/&lt;anything&gt; renders a developer placeholder</t>
+        </is>
+      </c>
+      <c r="D226" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Platform / UI</t>
+        </is>
+      </c>
+      <c r="E226" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bug</t>
+        </is>
+      </c>
+      <c r="G226" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P3</t>
+        </is>
+      </c>
+      <c r="H226" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">An unmatched admin route falls through to a placeholder reading 'Foundation route mounted. Feature screens land in T2-T5.' It is behind the admin guard, but any workspace admin with a stale bookmark or a typo reaches it in production. Found by the pre-execution QA audit of the greenfield test pack (docs/qa/AUDIT_FINDINGS.md).</t>
+        </is>
+      </c>
+      <c r="J226" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J216" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:J226" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/docs/Bugs.xlsx
+++ b/docs/Bugs.xlsx
@@ -4193,7 +4193,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J226"/>
+  <dimension ref="A1:J231"/>
   <sheetFormatPr defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="2" bestFit="1" customWidth="1"/>
@@ -11559,8 +11559,233 @@
         </is>
       </c>
     </row>
+    <row r="227" spans="1:10">
+      <c r="A227" s="2">
+        <v>226</v>
+      </c>
+      <c r="B227" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ideation registers ONE artifact containing the Context Gap Scan instead of opening the clarifications gate (intermittent)</t>
+        </is>
+      </c>
+      <c r="C227" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Greenfield: create a project, add a work item, trigger Ideation. Expected the clarifications gate with the agent's tiered questions. Instead the run went straight to a review gate with a single 'Ideation' artifact whose body WAS the gap scan — the questions themselves, ending 'I will not produce or register any artifact until you answer them'. Intermittent: the same code produced a correct gate on other runs, which is why it was chased as a prompt/model problem for days. Reported independently by two developers. Reproduced live on 2026-07-30 (run f390734e, then again as 457f65e1).</t>
+        </is>
+      </c>
+      <c r="D227" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Runs / Clarifications</t>
+        </is>
+      </c>
+      <c r="E227" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bug</t>
+        </is>
+      </c>
+      <c r="G227" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P1</t>
+        </is>
+      </c>
+      <c r="H227" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The Claude Code CLI (2.1.208) DEFERS tools out of the agent's initial context to save tokens, and 'ToolSearch' is the only mechanism that loads a deferred tool back (the SDK models this as deferredBuiltinTools). 'ToolSearch' was on the platform's planning and scan DENYLISTS — added 2026-07-09 in commit 98200ae, when it was merely another built-in to sandbox away, long before the CLI used it this way. Granting all 13 platform-state tools in allowed_tools therefore guaranteed nothing: whatever the CLI deferred was permanently invisible to the agent. Proof from run 457f65e1 — the agent's own first paragraph: 'The platform-state tools (ask_human, register_artifact, add_trace_edge, log_event) referenced in my operating instructions are not present in my available tool context', while THE SAME RUN successfully called list_artifacts and get_artifact. Read tools present, write tools and ask_human absent — so the agent produced 39,417 chars of finished deliverables as prose because it had nowhere to put them. Intermittent because what the CLI defers depends on context pressure, which varies run to run. NOT a model adherence problem, NOT a crashed MCP server, NOT the environment — all three were investigated and ruled out with evidence.</t>
+        </is>
+      </c>
+      <c r="I227" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Removed 'ToolSearch' from _PLANNING_DISALLOWED_TOOLS and _SCAN_DISALLOWED_TOOLS (backend/drivers/claude_driver.py) AND added it to the three allowlists — PLAN_ALLOWED_TOOLS (runner/companion/daemon.py), BUILD_ALLOWED_TOOLS (runner/companion/runner.py) and PLATFORM_TOOLS (backend/orchestration/activities.py); a denylist removal alone is not enough while an allowlist is in force. The sandbox is NOT widened: ToolSearch returns schemas only, for tools already granted, and execution stays gated by the same allowlist plus denylist. VERIFIED live end-to-end after the fix: ask_human called at 30s (4 tiered questions, Tier 1 required / Tier 2 with suggestion), then 7x register_artifact, 7x stage_artifact_body, 1x add_trace_edge, producing the full healthy 7-artifact ideation (ideation, feasibility_report, stakeholder_map, success_metrics, market_sizing, competitive_analysis, assumption) and the phase completed. Full write-up: docs/INCIDENT_2026-07-30_clarifications_gate.md.</t>
+        </is>
+      </c>
+      <c r="J227" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fixed</t>
+        </is>
+      </c>
+    </row>
+    <row r="228" spans="1:10">
+      <c r="A228" s="2">
+        <v>227</v>
+      </c>
+      <c r="B228" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A run whose agent registered nothing still produced an approvable artifact and opened a review gate</t>
+        </is>
+      </c>
+      <c r="C228" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The safety-net defect behind S.No 226. When the agent's tools were unreachable, the platform still filed its final message as the phase deliverable and opened a normal review gate on it — so a completely failed run looked like a successful one. This is why the underlying bug survived for weeks: nothing ever failed visibly, and a reviewer would have approved a document containing the agent's questions.</t>
+        </is>
+      </c>
+      <c r="D228" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Runs / Gates</t>
+        </is>
+      </c>
+      <c r="E228" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bug</t>
+        </is>
+      </c>
+      <c r="G228" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P1</t>
+        </is>
+      </c>
+      <c r="H228" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">register_phase_result_core (backend/orchestration/activities.py) unconditionally staged the engine's final text, registered it as a phase-typed artifact and let the run proceed to its gate; nothing examined what the text was. The existing guard, verify_write_completeness_core, checks that the expected artifact type exists and is non-empty — but for ideation it looks for type 'ideation', which is EXACTLY the artifact the platform had just created from the agent's questions, and non-empty because the gap scan was 3,441 real characters. The platform was manufacturing the evidence its own check looked for.</t>
+        </is>
+      </c>
+      <c r="I228" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The platform's own artifact is now stamped external_ref={'source': 'phase_report'} at both sinks (companion register_phase_result_core and direct execute_phase), and verify_write_completeness_core requires at least ONE artifact the AGENT registered. If the only record is the platform's copy of the final message the run FAILS with a message naming what to check, and NO gate opens. Evidence for the bar: across 47 successful runs spanning 13 phases the minimum artifact count was 2 (the platform's plus at least one agent-registered) and never 1; the failed run had exactly 1. Replayed against every historical successful run: 49 pass, 0 regress. PROVEN IN PRODUCTION — it caught the real intermittent bug on its first encounter (run 457f65e1 parked with a clear reason instead of filing a false artifact), which is how the root cause in S.No 226 was finally found.</t>
+        </is>
+      </c>
+      <c r="J228" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fixed</t>
+        </is>
+      </c>
+    </row>
+    <row r="229" spans="1:10">
+      <c r="A229" s="2">
+        <v>228</v>
+      </c>
+      <c r="B229" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Agent briefing (manifest) was silently truncated mid-sentence, losing project constraints and operating rules</t>
+        </is>
+      </c>
+      <c r="C229" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Every run is given a briefing document in seven sections, each capped. Two sections were over their cap on a normal greenfield project, so real content was cut — including the end of the user's own project constraints and the tail of the agent's operating rules. Nothing logged it and nothing showed it, so the only symptom was an agent that appeared to have forgotten something.</t>
+        </is>
+      </c>
+      <c r="D229" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Runs / Agents</t>
+        </is>
+      </c>
+      <c r="E229" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bug</t>
+        </is>
+      </c>
+      <c r="G229" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P2</t>
+        </is>
+      </c>
+      <c r="H229" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">backend/manifest/composer.py caps each section in tokens and cuts by CHARACTER count. Measured on a live ideation run: 'rules' needed 1,706 tokens against a 1,500 cap (780 chars lost) and 'project' needed 906 against 800 (378 chars lost). The Project section stopped mid-sentence inside the user's constraints at 'Authentication: Email + password only. No OTP, no'; the Rules section lost Rule 9, the assumptions protocol and the review-gate rule, because truncation removes the END and the last-written rules live there. The whole manifest was 3,594 tokens — under 2% of the model's 200k window — so a document with no size problem was being cut. The caps were early guesses applied equally to sections that grow without bound (artifact lists, event history) and sections we AUTHOR (rules, project profile), which is the category error.</t>
+        </is>
+      </c>
+      <c r="I229" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Caps raised where the content is authored and left alone where it grows without bound: rules 1500 -&gt; 3000, project 800 -&gt; 2000, important_context 1500 -&gt; 2000; relevant_artifacts / recent_events / retrieved_knowledge unchanged. Truncation now cuts at a LINE boundary instead of mid-character. compose_manifest_core emits a 'manifest.truncated' ledger event naming the cut sections, so it can never be silent again and the team has real data to tune the caps. Verified on the live project: all seven sections now fit (3,633 tokens, nothing cut, user constraints intact end-to-end). FUTURE ENHANCEMENT: these are fixed constants sized against a 200k window — when model selection is exposed to users they should scale from the selected model's context window instead (noted in docs/INCIDENT_2026-07-30_clarifications_gate.md).</t>
+        </is>
+      </c>
+      <c r="J229" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fixed</t>
+        </is>
+      </c>
+    </row>
+    <row r="230" spans="1:10">
+      <c r="A230" s="2">
+        <v>229</v>
+      </c>
+      <c r="B230" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MCP server config was sent as inline command-line JSON with a seven-variable environment</t>
+        </is>
+      </c>
+      <c r="C230" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hardening found while investigating S.No 226. The companion launches the platform-state MCP server — the process that provides EVERY tool an agent has — as a subprocess, and passed its whole configuration on the command line. Not confirmed as a cause of any observed failure, but two real risks, one of them a repeat of an already-fixed class of bug (Bugs row 64, Windows 'command line too long' misreported as 'Claude Code not found').</t>
+        </is>
+      </c>
+      <c r="D230" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Companion / Runs</t>
+        </is>
+      </c>
+      <c r="E230" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bug</t>
+        </is>
+      </c>
+      <c r="G230" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P2</t>
+        </is>
+      </c>
+      <c r="H230" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(1) The subprocess was given exactly seven environment variables. If that env ever REPLACES rather than extends the child's environment, Python cannot start on Windows: without SYSTEMROOT, Winsock fails to initialise and the interpreter dies during 'import asyncio' with OSError [WinError 10106], before any of our code runs — so the process that would have logged the failure is the one that died. Reproduced directly on a developer machine: 7 vars -&gt; exit 1; plus SYSTEMROOT -&gt; serves normally. (2) The config travelled as inline --mcp-config JSON on the command line. Windows caps a command line at ~32,767 chars (the ceiling behind Bugs row 64), and command lines are readable by any user from a process listing — so an inlined config publishes the runner token.</t>
+        </is>
+      </c>
+      <c r="I230" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The environment is now inherited from the machine and then overlaid with the seven runner values, and the entire config is written to a temp FILE whose path goes on the command line — the same shape the team already adopted for the agent body (--system-prompt-file). The file is deleted on every exit path because it carries the runner token. Applied to BOTH the planning path (daemon.state_mcp_servers) and the build path (runner.build_mcp_servers), which launch the identical server and carried the identical risk. Verified: command line 59 chars (the path) versus 6,708 inline; 88 env vars in the file with SYSTEMROOT and PATH present and the runner values correctly overlaid; file removed after the run; 31 companion daemon tests pass.</t>
+        </is>
+      </c>
+      <c r="J230" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fixed</t>
+        </is>
+      </c>
+    </row>
+    <row r="231" spans="1:10">
+      <c r="A231" s="2">
+        <v>230</v>
+      </c>
+      <c r="B231" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Clarification events from deleted runs on other work items leak into a fresh work item's manifest</t>
+        </is>
+      </c>
+      <c r="C231" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Observed while diagnosing S.No 226. A brand-new work item's agent reported: 'Two prior clarification.asked events appear in the run history but no answers were carried into this manifest.' Those events belonged to earlier runs on DIFFERENT work items that had since been deleted. At best this is noise in the briefing; at worst an agent reasons from another work item's clarifications, or believes questions were already asked and answered when they were not.</t>
+        </is>
+      </c>
+      <c r="D231" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Runs / Agents</t>
+        </is>
+      </c>
+      <c r="E231" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bug</t>
+        </is>
+      </c>
+      <c r="G231" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P3</t>
+        </is>
+      </c>
+      <c r="H231" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not yet diagnosed. The '# Recent Events' section of the manifest is populated from the ledger scoped to the project rather than to the work item, so clarification events raised against any work item in the project reach every run's briefing — and deleting the run does not remove its ledger events. Needs confirmation against mcp_platform_state.tools.get_context before a fix is proposed.</t>
+        </is>
+      </c>
+      <c r="I231" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">None — logged for triage. Suggested direction: scope clarification-related events in the manifest to the CURRENT work item, or carry the answers alongside the events so an agent never sees a question without its answer. See section 5 of docs/INCIDENT_2026-07-30_clarifications_gate.md.</t>
+        </is>
+      </c>
+      <c r="J231" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J226" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:J231" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/docs/Bugs.xlsx
+++ b/docs/Bugs.xlsx
@@ -1,9 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30305"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="217" documentId="11_14FDEAE3397E350B81F2A24CBED9C52169691D91" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B39CCE5D-1D7C-4DAE-8871-EA9F0B2E43B3}"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Msi\projects\SDLC-App\AI-First-SDLC-App\docs\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3B88536-8D4C-48DA-B36C-AF342305AE8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -11,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$J$216</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$J$231</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -276,7 +281,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1400" uniqueCount="822">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1830" uniqueCount="1078">
   <si>
     <t>S.No</t>
   </si>
@@ -1351,12 +1356,6 @@
     <t>backend/api/serializers.py WorkItemPatchSerializer (exists, title/description/type); no frontend edit UI</t>
   </si>
   <si>
-    <t>The edit UI was never built; only the PATCH serializer was scaffolded.</t>
-  </si>
-  <si>
-    <t>Deferred (later-phase optimization, per team decision). Add an edit UI over the existing PATCH endpoint; consider making dependencies and estimate editable too.</t>
-  </si>
-  <si>
     <t>Re-running Task Breakdown duplicates the whole backlog (create_work_item has no idempotency)</t>
   </si>
   <si>
@@ -1874,12 +1873,6 @@
   </si>
   <si>
     <t>frontend CreateProject (Single/Multi toggle); backend/apps/projects/repos.py _topology_for (recompute on add/remove); projects_project.repo_topology; Repositories page Topology chip + 'Multi-repo drives API-contract &amp; drift checks' copy</t>
-  </si>
-  <si>
-    <t>Two sources of truth for topology: the create-form choice and the count-derived value. Adding repos recomputes and can override the explicit pick; the create UI exposes 2 options while the model has 3.</t>
-  </si>
-  <si>
-    <t>Open - P3, later. Pick one source of truth: (a) honor the user's explicit choice and stop auto-deriving, or (b) always derive from count and clarify the labels so a 2-repo project still reads as multi to the user. Confirm whether API-contract/drift checks intentionally require 3+ repos ('multi') vs 2 ('split').</t>
   </si>
   <si>
     <t>A backend/worker restart drops the local companion and it does NOT auto-reconnect - the companion stops heartbeating/polling, and a run dispatched right after is left unclaimed until the companion is manually restarted</t>
@@ -2120,9 +2113,6 @@
 </t>
   </si>
   <si>
-    <t>FIXED (2026-07-15). agents/06_task_breakdown/agent.md: added a 'Writing standard' requiring every Epic/Story/Task Description + Acceptance Criterion to be plain-language-with-technical-nuance, detailed and self-contained enough that a developer can implement by reading it ALONE (behaviour, inputs/outputs, states, edge cases), with concrete hand-verifiable acceptance criteria and no bare placeholders; modelled the standard in all three template placeholders. Improvement flows to the Work Items board + artifact previews automatically. Test: test_agents_migration.test_task_breakdown_descriptions_and_ac_are_humanized. Per team decision the blast radius today was 06 only; the SAME defect in 02/09/00c/04/03/10 is logged as S.No 121-126 (register-condition per audience: technical-humanized for testing/security, plain+nuance for the rest) and NOT fixed this session.</t>
-  </si>
-  <si>
     <t>In the work items board when clicked on either epic or user story it shows children(3 or 4), instead when clicked on the childern it should show those tasks</t>
   </si>
   <si>
@@ -2464,12 +2454,6 @@
     <t>backend/apps/workitems/models.py (State: proposed/accepted/in_progress/in_review/blocked/done, no transition validation); backend/api/serializers.py WorkItemPatchSerializer (state NOT writable) + read_only state; backend/api/views.py WorkItemViewSet (trigger/build/take-over/lifecycle - no transition/mark-done action); mcp_platform_state/tools.py transition_work_item (any-&gt;any, internal only); frontend RunConsole.tsx (Retry only) / WorkItemTask.tsx (done is display-only) / OfflineTakeover.tsx</t>
   </si>
   <si>
-    <t>WorkItem.state is read-only on the API (excluded from WorkItemPatchSerializer; read_only on the read serializer) and mutated ONLY internally by the orchestrator (successful build+merge / gate / reject / takeover). No human-facing transition/mark-done/close/skip action or endpoint exists; the frontend offers only Retry / Trigger phase / manual takeover (sets takeover_flag, not state). transition_work_item allows any-&gt;any but is unexposed to users.</t>
-  </si>
-  <si>
-    <t>OPEN - proposed: add a GATED human action + API endpoint to move a WorkItem to a terminal state outside the happy path (e.g. 'Mark done', 'Close as redundant / won't-do', or 'Skip'), surfaced on the Work Items board + task page, with an audit Event. Decide whether to reuse 'done' or add a distinct terminal state (e.g. 'closed'/'cancelled') to distinguish completed-by-build from human-closed; guard with role/permission. Related S.No 76 (no task-edit UI; state not editable).</t>
-  </si>
-  <si>
     <t>Merge gate can't recover from a conflict without redoing the whole build. TWO related enhancements (logged together): (ENH-2, IMPLEMENT NOW) Merge-only retry / re-openable merge gate - when a merge hits a conflict, PAUSE at the merge step and let the user retry the merge after fixing the conflict, WITHOUT re-running the whole build. (ENH-1, FUTURE / only if needed) Reconcile the Run status on an EXTERNAL merge - when a user merges the PR by hand in GitHub, also flip the Run from failed to done (today the webhook updates the WorkItem + artifact but leaves the Run 'failed').</t>
   </si>
   <si>
@@ -2545,7 +2529,7 @@
     <t>When the AI build agent fails to run - most commonly because the Anthropic usage/rate limit is reached, but also on any agent CLI non-zero exit - the companion's error handler (runner/companion/daemon.py ~line 271) captures only the engine driver's generic wrapper string and reports it verbatim: 'Command failed with exit code 1 (exit code: 1) / Error output: Check stderr output for details'. The platform's classify_build_failure (backend/orchestration/build_activities.py) does not recognise this signature, so the raw string passes straight through to the build.failed reason and the run console. The user sees an opaque error with no indication that the real cause was a usage limit and no guidance on what to do. This bit WI-32: the usage limit was hit during the cycle-2 remediation build and the console showed only 'Command failed with exit code 1'. Same defect class as S.No 139 (classified reasons) but for the engine/usage-limit failure path, which was not covered.</t>
   </si>
   <si>
-    <t xml:space="preserve">FIXED &amp; TESTED (2026-07-21): code landed @6f9671f. classify_build_failure() in build_activities.py maps usage/rate-limit/exit-code-1 signatures to a plain reason, and the companion now reports the engine's stderr tail instead of the placeholder. Team verified live. --- Original fix note: OPEN - Fix A planned this session (this row's owner). Two parts: (1) Companion (daemon.py): capture the agent process's stderr tail and put the actual cause in the report message instead of the placeholder 'Check stderr output for details'. (2) Platform (classify_build_failure): recognise engine / usage-limit / rate-limit signatures ('exit code 1', 'usage limit', 'rate limit', '429', 'overloaded', 'quota', 'Failed to start Claude Code') and map them to a plain-language reason, e.g. 'The AI engine hit its usage limit - the build stopped; retry when the limit resets.' NOTE: true resume-from-checkpoint on a transient failure (so a re-run continues from the last cycle instead of rebuilding) is tracked separately as S.No 147 and is owned by the other developer. Acceptance: a usage-limit failure shows a clear, non-technical reason naming the usage limit, not a raw exit-code string.</t>
+    <t>FIXED &amp; TESTED (2026-07-21): code landed @6f9671f. classify_build_failure() in build_activities.py maps usage/rate-limit/exit-code-1 signatures to a plain reason, and the companion now reports the engine's stderr tail instead of the placeholder. Team verified live. --- Original fix note: OPEN - Fix A planned this session (this row's owner). Two parts: (1) Companion (daemon.py): capture the agent process's stderr tail and put the actual cause in the report message instead of the placeholder 'Check stderr output for details'. (2) Platform (classify_build_failure): recognise engine / usage-limit / rate-limit signatures ('exit code 1', 'usage limit', 'rate limit', '429', 'overloaded', 'quota', 'Failed to start Claude Code') and map them to a plain-language reason, e.g. 'The AI engine hit its usage limit - the build stopped; retry when the limit resets.' NOTE: true resume-from-checkpoint on a transient failure (so a re-run continues from the last cycle instead of rebuilding) is tracked separately as S.No 147 and is owned by the other developer. Acceptance: a usage-limit failure shows a clear, non-technical reason naming the usage limit, not a raw exit-code string.</t>
   </si>
   <si>
     <t>When the implementation of a Work Item is completed and give it away for the review agent - The review agent is doing its job and creating Remediation Work Items (if blocking or critical issues are present): The created Remediation Work Item Tasks are too technical and not humasined and high level</t>
@@ -2720,7 +2704,7 @@
 verify_writes could not save it either: verify_write_completeness_core asserts only that an artifact of the expected TYPE exists, never that its body is non-empty - so the platform's own 0-byte row satisfied the last check before the gate.</t>
   </si>
   <si>
-    <t xml:space="preserve">FIXED &amp; TESTED (2026-07-21): committed @26065d0. register_phase_result_activity now annotates report: PhaseReport, so Temporal delivers a real PhaseReport (not a dict) and the body + cost persist; the empty_result message no longer misblames the engine. Team verified live. --- Original fix note: IN PROGRESS (2026-07-17) - fixed locally, NOT committed, pending team test. Three parts, all in backend/orchestration/activities.py:
+    <t>FIXED &amp; TESTED (2026-07-21): committed @26065d0. register_phase_result_activity now annotates report: PhaseReport, so Temporal delivers a real PhaseReport (not a dict) and the body + cost persist; the empty_result message no longer misblames the engine. Team verified live. --- Original fix note: IN PROGRESS (2026-07-17) - fixed locally, NOT committed, pending team test. Three parts, all in backend/orchestration/activities.py:
 1. ROOT FIX - annotate the activity: register_phase_result_activity(inp: AgentRunInput, report: PhaseReport). Temporal now converts the payload to a PhaseReport, matching the `inp` parameter that always worked. A test asserts the annotation stays put, so it cannot be silently dropped again.
 2. DEFENCE - new _as_phase_report() coerces dict / PhaseReport / duck-typed object to a PhaseReport, and the core reads report.body / report.cost_usd / report.message directly - no getattr on a possible dict anywhere in the path. The cores are also called directly by tests and by the takeover path, so both shapes must keep working.
 3. HONESTY - the phase.empty_result message no longer reads the report via getattr, so it can no longer blame the engine for the platform's own defaulted read.
@@ -2729,9 +2713,6 @@
 NOT fixed here, deliberately: verify_writes still passes an empty artifact (it checks type presence, not content). Logged separately so the last line of defence is fixed on its own merits rather than as a side effect. Related: S.No 59 (the other half of this seam - pointer-only artifacts never staged), S.No 158 (verify_writes crash).</t>
   </si>
   <si>
-    <t>In Progress</t>
-  </si>
-  <si>
     <t>When a build's remediation loop hit its cycle cap it hard-failed the WorkItem with no diagnostics and no way forward — the user could not complete the WorkItem.</t>
   </si>
   <si>
@@ -2879,9 +2860,6 @@
   </si>
   <si>
     <t>'failed' is a terminal state and swallows a later successful report. Takeover finalizes the run to failed while the companion is merely offline (e.g. laptop asleep), and nothing re-opens it when the companion returns and reports ok with artifacts — takeover wins a race it is about to lose.</t>
-  </si>
-  <si>
-    <t>OPEN — not yet fixed. Proposed: a successful late phase.reported (status=ok with registered artifacts) should reconcile the run to succeeded (the artifacts are the proof), OR takeover should not finalize while the companion is still making progress / a reclaim should re-open the run. Related operational trigger: companion-offline from laptop sleep stalls dispatched phases.</t>
   </si>
   <si>
     <t>In Repository page - The optional Preview URL box is not alliged with the rest of the boxes (UX design) and the message comment below the box which says – “A running app for 09b to explore while writing tests” where the user wouldn’t know what is 09b and the message is not understandable for the user.</t>
@@ -2921,12 +2899,808 @@
 After the user has connected the companion and selects the work item and triggers a phase – A Runs card shows in the page where the card shows info about the tiggered run and a link to navigate the run console page. Now here the team has decided to revome the “COST(EST)” column which is not needed anymore and the message below the card is also to be revomed (not needed any more). Those details were added for the testing purposes and do not need any more. 
 Note: Also check whether the same behaviour happens in the UI, like for example: while a clarification gate has opend and does a recon over the complete SDLC app and tell the team whether the same scenario of issues appears anywhere? </t>
   </si>
+  <si>
+    <t>The edit UI was never built - only the WorkItemPatchSerializer (title/description/type/repo) was scaffolded on the backend; no frontend form calls it (the patch hook is wired only to the repo field on the Repo-Assignment card). state, estimate and depends_on are not editable (state is read-only, there is no estimate field, depends_on is excluded from the patch serializer).</t>
+  </si>
+  <si>
+    <t>OPEN - surgical fix (recon 2026-07-24): FRONTEND-ONLY for the common case - add a small edit form/modal in WorkItemTask.tsx / WorkItemEpic.tsx that calls the existing usePatchWorkItem with {title, description, type}; no backend change needed (the PATCH endpoint is already live and tested). To also edit dependencies, add depends_on to WorkItemPatchSerializer.fields with same-project + no-cycle validation (mirror the repo check in perform_update). Estimate is out of scope until a WorkItem.estimate field is modelled (see S.No 75).</t>
+  </si>
+  <si>
+    <t>Two sources of truth for topology. Source A (backend, authoritative): repos.py _topology_for derives repo_topology from repo COUNT (&gt;=3 multi, ==2 split, else single) and _recompute_topology re-writes it on every add/remove repository. Source B (frontend): CreateProject.tsx offers only Single/Multi (2 of the model's 3 values) and posts repo_topology, which perform_create honours - but the first repo add/remove then recomputes and silently overrides the user's pick. Confirmed no backend feature branches on topology=='multi' (drift/api-contract do NOT read it); it is informational (manifest/context only).</t>
+  </si>
+  <si>
+    <t>OPEN - surgical fix (recon 2026-07-24), Option (b), lowest risk: keep the count-derived value as the single source of truth (backend + tests unchanged - many tests assert derived values) and stop the create form presenting a choice it does not honour - drop the topology segmented control from CreateProject.tsx (or relabel it a non-authoritative hint) and widen the 2-value type in types.ts / hooks.ts. Topology then simply follows the repos actually registered. Option (a) - honour the explicit choice and stop auto-deriving - is higher risk (rewrites the derived-value tests, needs the missing 'Split' option added) and is not recommended since nothing branches on the value.</t>
+  </si>
+  <si>
+    <t>The board bucket is computed in WorkItemsBoard.tsx byPhase from item.current_phase, which the backend derives (WorkItemViewSet._card_fields) as the latest Run's agent-spec key. Freshly fanned-out Task Breakdown items are state='proposed' with NO run yet, so current_phase='' - and byPhase falls phase-less items back to columns[0]. In the default board columns[0] is 01_ideation (Ideation column); when filtered to Tasks the columns switch to BUILD_COLUMNS whose first entry is 'implementation' (Implementation column). Both reported symptoms are the same defect: not-yet-run items blindly land in the first column.</t>
+  </si>
+  <si>
+    <t>OPEN - surgical fix (recon 2026-07-24), FRONTEND-ONLY (WorkItemsBoard.tsx): add an explicit 'Backlog / Not started' column to PHASE_COLUMNS and BUILD_COLUMNS and, in byPhase, route items with an empty current_phase (or state=='proposed') to it instead of defaulting to columns[0]. No backend change. Update phases.test.ts / lifecycle.test.tsx if they assert on the column set/counts. Optional backend alternative: have _card_fields set current_phase to the producing phase for un-run items - larger semantic change, not needed.</t>
+  </si>
+  <si>
+    <t>FIXED (2026-07-15). agents/06_task_breakdown/agent.md: added a 'Writing standard' requiring every Epic/Story/Task Description + Acceptance Criterion to be plain-language-with-technical-nuance, detailed and self-contained enough that a developer can implement by reading it ALONE (behaviour, inputs/outputs, states, edge cases), with concrete hand-verifiable acceptance criteria and no bare placeholders; modelled the standard in all three template placeholders. Improvement flows to the Work Items board + artifact previews automatically. Test: test_agents_migration.test_task_breakdown_descriptions_and_ac_are_humanized. Per team decision the blast radius today was 06 only; the SAME defect in 02/09/00c/04/03/10 is logged as S.No 121-126 (register-condition per audience: technical-humanized for testing/security, plain+nuance for the rest) and NOT fixed this session.
+FOLLOW-UP COMPLETION (2026-07-24, verified live by the team). The 2026-07-15 fix set the INSTRUCTION but left the technical exemplars in place, and the model imitates exemplars more than rules — so Epics read well (they already had good plain-language examples) but Tasks still came out too technical. Completed the fix at the EXAMPLE level: agents/06_task_breakdown/agent.md now carries worked Story AND Task exemplars that OPEN with a one-sentence plain-language statement of intent (what it delivers and why) BEFORE the technical detail, with concrete given/when/then acceptance criteria; added an explicit 'lead with plain-language intent' requirement for both Stories and Tasks; and rewrote the terse counter-examples (the endpoint-string title, the venv/env-file acceptance criteria) so nothing pulls the output back to terse. Platform side: backend/manifest/composer.py raised the Current Work Item token budget 300-&gt;650 so long task descriptions reach the implementation agent untruncated (avg 1,263 / max 1,835 chars already exceeded the old ~1,200-char cap). Strengthened the test to assert the intent-lead + the worked exemplars. Committed f27455d (pushed to develop). Team re-ran Task Breakdown on tenant 7828e953 and confirmed a great improvement vs the old artifacts. Scope decision this session was Tasks + Stories; siblings S.No 121-126 (agents 02/09/00c/04/03/10) remain separately Open.</t>
+  </si>
+  <si>
+    <t>WorkItemDetail.tsx routes epic AND story to WorkItemEpic; only the leaf WorkItemTask renders the navigable 'Related work items' child-link panel (maps lifecycle.children to /work-items/{id} links). WorkItemEpic shows children only as a raw count ('Children: N'), never as links - so an epic shows a number not clickable stories, and a story (also routed to WorkItemEpic) shows a number not clickable tasks. The lifecycle endpoint already returns the DIRECT children at each level, so the epic-&gt;story-&gt;task data is present; the parent view just doesn't render it as navigation.</t>
+  </si>
+  <si>
+    <t>OPEN - surgical fix (recon 2026-07-24), FRONTEND-ONLY, additive: add a 'Related work items' child-link panel to WorkItemEpic.tsx (mirror the one in WorkItemTask.tsx) that renders lifecycle.children as /work-items/{id} links. Each level then lists its own direct children, giving epic-&gt;story-&gt;task drill navigation. Low risk (additive UI); check WorkItemEpicGallery / lifecycle.test.tsx expectations. Optional: fix the child rows' mislabelled phase (views.py emits c.feature_stream as 'phase' - same class as the row-50 feature-stream/phase fix).</t>
+  </si>
+  <si>
+    <t>WorkItem.state is read-only on the API (excluded from WorkItemPatchSerializer, read_only on the read serializer) and is mutated ONLY by the orchestrator (successful build+merge / gate / reject / takeover). No human-facing transition endpoint exists; the frontend offers only Retry / Trigger phase / manual takeover (sets takeover_flag, not state). The MCP transition_work_item allows any-&gt;any but is unexposed to users, and there is no terminal state other than 'done' to mark a redundant/abandoned item.</t>
+  </si>
+  <si>
+    <t>OPEN - surgical fix (recon 2026-07-24): add a GATED, AUDITED human-transition endpoint on WorkItemViewSet (@action 'transition') - role-checked (reuse resolve_actor + the gate-role pattern), accepting only an ALLOWLISTED set of human transitions (NOT the MCP any-&gt;any), and writing a ledger Event. Surface 'Mark done / Close as redundant / Skip' on the Work Items board + task page. Add a terminal CANCELLED (optionally CLOSED) value to WorkItem.State via a small migration so human-closed stays distinct from build-completed 'done'; audit every state-mapping site (frontend statusLabel, board columns, lifecycle rail run_status_to_node_state) when adding the value. The migration is the only non-trivial part; the orchestrator keeps its own unrestricted transition path. Related S.No 76.</t>
+  </si>
+  <si>
+    <t>Artifacts are pointer-only by design (#1/#3): the Artifact row stores s3_key/content_hash/version/status, bodies live in S3 as run/phase-scoped drafts written by the agent-only MCP tool stage_artifact_body. The REST ArtifactViewSet is ReadOnly - its only body route is 'preview' (explicitly 'never an editor'), and update_artifact (MCP-only) mutates pointers/metadata, never a body. So there is no human path to edit a generated draft body.</t>
+  </si>
+  <si>
+    <t>OPEN - surgical fix (recon 2026-07-24): add a DRAFT-ONLY edit path that respects the no-auto-publish non-negotiable (#5) - a new @action (e.g. 'edit') on ArtifactViewSet (allowed on a ReadOnly viewset) or a small service that: rejects unless status=='draft' AND sor=='internal', re-stages the edited body to S3 via the existing stage_artifact_body mechanics, updates s3_key + content_hash and bumps version, and writes an Event. Frontend: swap the read-only Markdown block in ArtifactPreviewScreen.tsx for an editable textarea + Save when status=='draft'. Scope the first cut to single-body markdown/text; multi-state wireframe HTML is a later pass. Medium size; the ONLY risk is letting an edit touch a staged/approved/published body - restrict strictly to draft+internal and it never bypasses a gate.</t>
+  </si>
+  <si>
+    <t>IntegrationConnection is TenantScopedModel with NO project FK (unlike SourceDocument/DriftRecord in the same app, which are project-scoped), so a connection is shared across the whole tenant. The single resolution choke point is registry.get_connection(tenant_id, capability); the per-capability builders read creds via Config.from_connection(conn) and don't care about tenant-vs-project. RLS is tenant-based; adding a project filter needs NO RLS change (isolation stays at the tenant boundary). The cost is that ~16 resolution call sites (build_activities, review_provider, reconcile, publish, onboarding, design, preview, quality, views, repos) mostly carry only tenant_id, plus ~20 tests monkeypatch get_capability(tid,cap).</t>
+  </si>
+  <si>
+    <t>OPEN - surgical INCREMENTAL path (recon 2026-07-24) - the naive per-project rewrite is deep, so do it in safe steps: (1) add a NULLABLE project FK to IntegrationConnection (existing rows become tenant-wide defaults; plain column+index migration, no RLS change); (2) make get_connection/get_capability take an OPTIONAL project_id kwarg and resolve project-first with tenant fallback: filter(tenant, capability, project_id).first() or filter(tenant, capability, project__isnull=True).first() - every existing caller keeps compiling and behaves exactly as today; (3) relax create_integration uniqueness from (tenant,capability) to (tenant,project,capability) and add project to the serializers/API/frontend; (4) thread project_id into the resolution call sites and their input structs one at a time. Regression risk is LOW while project_id stays an optional fallback kwarg (HIGH only if signatures change eagerly). Projects override selectively while tenant-wide connections keep working.</t>
+  </si>
+  <si>
+    <t>FIXED - resolved by the S.No 89 work (non-terminal STALLED park). mark_phase_takeover_core now marks the run STALLED (not terminal FAILED) and register_phase_result_core clears takeover_flag on a late successful report, so a companion that went offline (e.g. laptop asleep) then returned and reported ok un-parks the run and flows on through register-&gt;verify-&gt;gate-&gt;publish; the false 'engine exited, no artifact' terminal-fail can no longer occur. Verified in backend/orchestration/activities.py (mark_phase_takeover_core + register_phase_result_core, both cite Bugs S.No 89).</t>
+  </si>
+  <si>
+    <t>S.No 170. The add-repo form lays its fields in a single row that bottom-aligns them. Every field was a label + input EXCEPT "Preview URL", which alone carried a help line under its input; that extra line changed the field's height and pushed its input out of line with the others. The help text also said "09b", an internal phase code that means nothing to a user.</t>
+  </si>
+  <si>
+    <t>FIXED &amp; TESTED (2026-07-21). Removed the inline help from the Preview URL field so all four inputs bottom-align again, and moved the guidance to a single full-width line below the row, reworded in plain language with no "09b": "Preview URL is optional - if your app is already running somewhere, paste its address so the testing phase can open it and write tests against the live app." File: frontend/src/features/setup/Repositories.tsx.</t>
+  </si>
+  <si>
+    <t>S.No 171. The companion connection status was shown in THREE places at once - the top navigation-bar pill, a "Connected --" box on the Workspace Dashboard, and a green "Companion ready --" box on Phases &amp; Runs - all reading the same underlying runner status. The two page-level boxes were redundant.</t>
+  </si>
+  <si>
+    <t>FIXED &amp; TESTED (2026-07-21). Removed the Dashboard "Companion" card and the Phases &amp; Runs "Companion ready" box (and the now-unused useRunners hook/vars they needed), leaving the top-bar pill as the single companion-status indicator. Files: frontend/src/features/observability/Dashboard.tsx, frontend/src/features/lifecycle/PhasesAndRuns.tsx.</t>
+  </si>
+  <si>
+    <t>S.No 172. The Run Console header and panel showed RAW ids (the run UUID, the Temporal workflow id, the engine) with no labels, and never showed which work item the run belonged to - so a user could not confirm the right work item was running. The work item WAS already fetched by the console, but only its title (with a UUID-slice fallback) was used, never its human key like "WI-42".</t>
+  </si>
+  <si>
+    <t>FIXED &amp; TESTED (2026-07-21). Led the header with the work item's key + title so the user can confirm the right item; added a labelled meta row (Work item / Run ID / Engine / Workflow) with the long ids shortened and the full value on hover; shortened the panel title. Raw ids are kept (now labelled) for debugging, per the team's note. File: frontend/src/features/lifecycle/RunConsole.tsx.</t>
+  </si>
+  <si>
+    <t>S.No 173. When the companion was OFFLINE the Trigger-a-Phase card hardcoded only three phases as disabled placeholders instead of the full catalog, and the Runs card kept showing a label on the right even offline. Recon answer for the team: that right-side label is the CURRENTLY SELECTED work item's title (falling back to a UUID slice), not a "most recent run".</t>
+  </si>
+  <si>
+    <t>FIXED &amp; TESTED (2026-07-21). The offline Trigger card now shows the FULL phase list, greyed and non-interactive, so the user sees every phase that exists; they become clickable once the companion is online. The Runs-card right-side work-item label is now hidden when offline and shown only when online (team decision). File: frontend/src/features/lifecycle/PhasesAndRuns.tsx.</t>
+  </si>
+  <si>
+    <t>S.No 174. The Clarifications page carried testing-era billing wording - a header clause "...and nothing is billed while it waits", an empty-state hint "(billing $0)", and a "Paused - no usage billed while waiting" chip - which the team decided to drop.</t>
+  </si>
+  <si>
+    <t>FIXED &amp; TESTED (2026-07-21). Removed the header billing clause and the "(billing $0)" hint and re-aligned the message; reworded the pause chip to "Paused - waiting for your answer" with no cost/billing mention (team asked for a billing-free wording). File: frontend/src/features/lifecycle/Clarifications.tsx.</t>
+  </si>
+  <si>
+    <t>S.No 175. A "Cost (est.)" column/row and "no usage billed while waiting" text were added across many screens for testing reference and are no longer wanted. The requested recon found the same display on SEVEN screens, not just the Phases &amp; Runs Runs card.</t>
+  </si>
+  <si>
+    <t>FIXED &amp; TESTED (2026-07-21). Removed the cost column/row and its note EVERYWHERE - Phases &amp; Runs Runs card, Run Console, Work Item (Task and Epic) panels, Phase Console table, Run Transcript table - and reworded every "no usage billed while waiting" pause banner to "Paused - waiting for your answer"; also removed a "$0 while waiting" note on the Dashboard. 7 files. NOTE: the /dev/components design-system showcase table still has a demo COST column - left intentionally (it is the raw component gallery, not an app screen); flagged to the team.</t>
+  </si>
+  <si>
+    <t>Security phase (10) runs with NO source code to scan. The Security Agent's whole job (SAST, dependency/CVE scan, SBOM, OWASP-in-code) needs the actual repository checked out, but the phase runs as a PLANNING phase that is never given the code - so it silently degrades to reviewing documents only. A user could get a clean-looking security report where no scanner ever ran against the code.</t>
+  </si>
+  <si>
+    <t>Security phase / Orchestration</t>
+  </si>
+  <si>
+    <t>Recon 2026-07-21. Verified: backend/apps/registry/catalog.py:72 registers 10_security with rides_build=False, so it routes trigger_phase -&gt; AgentRunWorkflow; dispatch_phase_core (backend/orchestration/activities.py) ships kind=plan with only manifest+agent_body and NO repo. Only the BUILD path provisions a git worktree. So SAST/SCA/SBOM/OWASP-in-code have nothing to scan. agents/10_security/agent.md:30 explicitly requires the companion worktree containing the full source code.</t>
+  </si>
+  <si>
+    <t>10_security is a planning phase (no rides_build) and the planning dispatch never checks out the work item's repo. The agent's SAST/SCA/SBOM steps require the real source in a companion worktree, which only the build path provides.</t>
+  </si>
+  <si>
+    <t>IMPLEMENTED (Fix A2, committed 2026-07-21; validated live by security run 371031a0 on 2026-07-22 - real code scanned in a read-only worktree): give repo-scoped PLANNING phases a READ-ONLY git worktree without putting them on the build/PR/merge path. New catalog flag reads_code=True on 10_security; trigger_phase resolves the work item's repo (reusing trigger_build's resolver, per-repo); dispatch carries repo/base; companion provisions a read-only worktree (branch sdlc-scan/&lt;run_id&gt;, torn down after, never committed/pushed); driver runs the planning agent with cwd in the worktree, Read/Grep/Glob allowed but Write/Edit blocked. Stays on AgentRunWorkflow so the security_engineer gate is unchanged. Also fixes 09_testing's identical latent gap via the same flag.</t>
+  </si>
+  <si>
+    <t>Security findings never become trackable work. The Security Agent is supposed to open a defect work item for every Critical/High finding (the defect loopback), but the platform code that does this is never actually called in production - so findings just sit in the report and nothing lands on the board.</t>
+  </si>
+  <si>
+    <t>Security phase / Quality</t>
+  </si>
+  <si>
+    <t>Recon 2026-07-21. Verified: backend/apps/quality/services.py:334 record_security_findings() implements the Critical/High security_finding -&gt; defect child WorkItem loopback and is exercised by tests, but a repo-wide grep of backend shows NO production caller. The only non-test reference is a comment in backend/apps/gates/testgate.py:57. So in prod the loopback is dead code.</t>
+  </si>
+  <si>
+    <t>record_security_findings() exists and is tested but is invoked only from tests - no workflow/activity/MCP/gate path calls it. Critical/High security_finding artifacts therefore never spawn defect WorkItems.</t>
+  </si>
+  <si>
+    <t>IMPLEMENTED (Fix B auto-defects, committed 2026-07-21; unit-tested; team accepted as Fixed 2026-07-22 without a live Critical/High run - medium/low findings intentionally do NOT open work items): wire record_security_findings() into the security run's completion so Critical/High security_finding artifacts auto-open defect child WorkItems (visible on the board), matching the tested call signature. NOTE per team decision the GATE stays advisory - the no_open_security_defects gate BLOCK is deliberately NOT added here (tracked separately as S.No 178).</t>
+  </si>
+  <si>
+    <t>The security gate can be approved with open Critical findings. The agent's contract says the gate must not be grantable while any Critical/High finding is open, but no such rule exists in the platform - the security gate is a plain human approval.</t>
+  </si>
+  <si>
+    <t>Security phase / Gates</t>
+  </si>
+  <si>
+    <t>Recon 2026-07-21. Verified: backend/apps/gates/conditions.py returns conditions only for ux_design (WCAG) and testing; conditions_for_phase(security) -&gt; []. There is no conditions_for_security_phase and no no_open_security_defects derived condition. A comment in testgate.py:57 references the intent but nothing enforces it. Gate role is security_engineer (correct) but unconditioned.</t>
+  </si>
+  <si>
+    <t>No security gate condition is wired; the gate is an unconditioned human approval, so a reviewer can approve with open Critical/High findings - contradicting agents/10_security/agent.md:329,430.</t>
+  </si>
+  <si>
+    <t>OPEN - DEFERRED by team decision 2026-07-21: for now the security gate stays ADVISORY (human approval) and findings are tracked manually / via the auto-spawned defects (S.No 177). Adding a hard no_open_security_defects gate block is deferred to a later hardening pass; logged here so it is not lost.</t>
+  </si>
+  <si>
+    <t>A blank security review passes the platform's completeness check. verify_writes only confirms that a generic artifact of type security exists - it never checks for the real security deliverables (security_review / security_finding / sbom), so an empty or missing review still passes and the gate opens on nothing.</t>
+  </si>
+  <si>
+    <t>Security phase / Artifacts</t>
+  </si>
+  <si>
+    <t>Recon 2026-07-21. Verified: AgentRunWorkflow calls verify_writes with [inp.phase] = [security]; the platform auto-registers one security-typed blob from the run's final text, so verify_write_completeness_core finds type security present and PASSES. The agent's real deliverables are types security_review/security_finding/threat_model/sbom - verify_writes knows nothing about them.</t>
+  </si>
+  <si>
+    <t>verify_writes checks only that a generic security-typed artifact exists, not the real security artifact types, so an empty review passes the last check before the gate.</t>
+  </si>
+  <si>
+    <t>IMPLEMENTED (Fix C, committed 2026-07-21; validated live by run 371031a0 on 2026-07-22 - security_review required and passed the completeness check): require the real security artifact type (security_review at minimum) in the security phase's expected-artifact set so an empty/blank review fails loudly instead of passing on a 0-byte generic blob.</t>
+  </si>
+  <si>
+    <t>The Security agent body omits the two-step needed to persist a large artifact. It tells the model to register artifact bodies directly, but register_artifact only takes a hash + s3 key - the body must first be staged via stage_artifact_body. Every sibling agent spells this out; the security agent does not, so a literal run could stall or mis-call register_artifact.</t>
+  </si>
+  <si>
+    <t>Security phase / Agent</t>
+  </si>
+  <si>
+    <t>Recon 2026-07-21. Verified: agents/10_security/agent.md:329,140-144 tells the model to register_artifact bodies directly, but register_artifact (mcp_platform_state/tools.py:314) takes content_hash + s3_key, not an inline body. The body must first be staged via stage_artifact_body (tools.py:558). agents/09_testing/agent.md:243-244 spells out the two-step; the security agent omits it.</t>
+  </si>
+  <si>
+    <t>10_security/agent.md never mentions stage_artifact_body; it instructs a direct register_artifact of the body, which the tool contract does not support. Low severity but a real inconsistency vs sibling agents.</t>
+  </si>
+  <si>
+    <t>IMPLEMENTED (Fix D, committed 2026-07-21; validated live by run 371031a0 on 2026-07-22 - 14 artifacts incl. large bodies staged and registered): add the stage_artifact_body -&gt; register_artifact two-step to agents/10_security/agent.md, matching the pattern agents/09_testing/agent.md already documents.</t>
+  </si>
+  <si>
+    <t>Build phase: a companion-reported failure of the INITIAL build (before or at the first report) is terminal - the user cannot resume, only re-run from scratch. When the build agent's first report is status!=ok (e.g. the Claude session/usage limit is hit during the build itself, or the engine errors before reporting), the build workflow runs mark_build_failed and ends. The Run console then offers only 'Retry run' (a brand-new run), never 'Resume from where it stopped'. Every OTHER build error (open PR, merge, remediation) parks and is resumable - only this first-report failure is a dead end. S.No 162 branch-continuity helps only if a branch was already pushed; if the limit hits before any push, the whole build restarts. Blocks a user mid-build with no way to carry on.</t>
+  </si>
+  <si>
+    <t>Build phase / Implementation</t>
+  </si>
+  <si>
+    <t>Recon 2026-07-22. Verified: backend/orchestration/build_workflow.py:130-135 (report.status!=ok -&gt; mark_build_failed -&gt; return build_failed, terminal); the resumable _park branches are all inside the PR/review/merge block (:205,:264,:311), AFTER the first ok report; dispatch_build (:111-114) sits outside it; frontend RunConsole.tsx:236-249 shows 'Retry run' for status=failed and 'Resume' only for status=stalled.</t>
+  </si>
+  <si>
+    <t>The initial-build report failure is routed to mark_build_failed (terminal) instead of the S.No 157 park path. dispatch_build is outside the resumable while-loop, so an engine/usage failure during it has no park branch; the Temporal workflow closes and a closed workflow can never be signalled to resume - so the only recovery is a fresh trigger.</t>
+  </si>
+  <si>
+    <t>PLANNED (team to fix 2026-07-22): classify the initial-build report failure (reuse classify_build_failure) - when it is a usage/session/rate-limit or a transient engine failure, PARK the build as resumable (park_build, resume_from='dispatch_build') instead of mark_build_failed, so the workflow stays alive and 'Resume from where it stopped' re-dispatches; keep genuinely terminal failures on mark_build_failed. Combine with S.No 162 branch continuity so a resume continues the already-pushed branch.</t>
+  </si>
+  <si>
+    <t>Planning &amp; Scan phases (ideation..deployment, and the Security scan): a mid-run engine failure fails the whole run terminally with NO resume - the user must re-run from scratch. When the companion reports the phase status!=ok (e.g. the Claude session/usage limit is hit mid-run, or the agent/engine errors), AgentRunWorkflow runs fail_run and ends. The Run console offers only 'Retry run', which starts a brand-new run from zero - there is no 'Resume from where it stopped'. Partial work already produced (e.g. security findings already registered) is not continued. This is exactly what hit the Security run on 2026-07-21 (failed on the session limit; a rerun must redo the entire scan). Remediation-exhaust does NOT apply here (planning/scan have no remediation loop). The only resumable park on this path is the narrow verify_writes case (a run that reported OK but is missing its artifact) - not a mid-run failure.</t>
+  </si>
+  <si>
+    <t>Planning &amp; Scan phases / Runs</t>
+  </si>
+  <si>
+    <t>Recon 2026-07-22. Verified: backend/orchestration/workflows.py:122-127 (report.status!=ok -&gt; fail_run -&gt; return phase_failed, terminal); the only _park on this workflow is the verify_writes check at :147-159 (post-report, artifact-missing); no remediation loop exists on this workflow; frontend RunConsole.tsx:236-249 gives 'Retry run' (fresh) for status=failed.</t>
+  </si>
+  <si>
+    <t>A companion-reported phase failure is routed to fail_run (terminal) rather than the S.No 157 park path, which is wired ONLY around the verify_writes write-completeness check. So a mid-run engine/usage failure has no resumable branch - the workflow closes and cannot be signalled, forcing a fresh trigger. Planning/scan also produce no branch, so there is no S.No 162-style continuity to fall back on.</t>
+  </si>
+  <si>
+    <t>PLANNED (team to fix 2026-07-22, TWO-part surgical fix - both parts required to be bulletproof; part 2 is logged separately as S.No 183): (1) On a companion-reported failure, classify it (reuse classify_phase_failure): if it is a usage/session/rate-limit or a transient engine failure, PARK the run resumable (park_run, resume_from='dispatch_phase') instead of fail_run, keeping the Temporal workflow alive so 'Resume from where it stopped' re-dispatches the remaining work; keep genuinely terminal failures on fail_run. (2) Depends on finding/artifact-level idempotency (S.No 183) so the resume/rerun continues rather than duplicating.</t>
+  </si>
+  <si>
+    <t>Planning &amp; Scan phases: no artifact/finding-level idempotency, so a re-run (or a future resume) DUPLICATES what a failed run already produced. Idempotency today is keyed by run_id only (execute_agent_core skips duplicates only within the SAME run); a fresh Retry gets a NEW run_id, so nothing dedups against the failed run's already-registered artifacts. Concretely, the Security scan that failed on 2026-07-21 had already registered findings SEC-001..004; a fresh rerun re-scans and can register the same findings again as new artifacts (and, once the defect loopback of S.No 177 is wired, could open duplicate defect work items). This makes any 'continue after a failure' unsafe and must be fixed for the S.No 182 resume to be bulletproof.</t>
+  </si>
+  <si>
+    <t>Planning &amp; Scan phases / Artifacts</t>
+  </si>
+  <si>
+    <t>Recon 2026-07-22. Verified: backend/orchestration/activities.py execute_agent_core is idempotent by run_id only; a re-trigger creates a new Run/run_id (frontend RunConsole.tsx:141-148 handleRetry -&gt; trigger by agent_key); security findings carry a stable external_ref finding_id (SEC-00x) but nothing dedups artifacts across runs of the same work_item+phase.</t>
+  </si>
+  <si>
+    <t>Artifact registration has no natural key beyond run_id, so across a failed run and its fresh retry there is no dedup on (work_item, phase, expected type / finding_id); partial output from the failed run is neither reused nor suppressed - it is duplicated.</t>
+  </si>
+  <si>
+    <t>PLANNED (team to fix 2026-07-22): add finding/artifact-level idempotency keyed on a stable natural key - for findings the external_ref finding_id (SEC-00x); for phase artifacts (work_item, phase, type). On register, upsert by that key within the work_item+phase scope instead of always inserting, so a resumed or re-triggered run continues (updates/skips existing) rather than duplicating. Pairs with S.No 182.</t>
+  </si>
+  <si>
+    <t>Clarifications page: the answer dropdown's option list overflows OUTSIDE the clarification card and looks broken. The Tier-1 'choice' answer control is a native select; when the agent's options are long sentences (seen live in a build-phase clarification - TASK-033, run dd5080df - e.g. 'Create a new backlog task for expenses CRUD router (GET/POST/PATCH/DELETE /api/v1/expenses) and merge TASK-033 as-is...'), the browser-drawn option popup extends past the card's left/right edges and the long option text does not wrap, so option text spills outside the window. Cosmetic but unpolished and can push text off-screen.</t>
+  </si>
+  <si>
+    <t>Clarifications / UI</t>
+  </si>
+  <si>
+    <t>UI issue</t>
+  </si>
+  <si>
+    <t>Recon 2026-07-22. Verified: frontend/src/features/lifecycle/Clarifications.tsx:190-203 renders a native &lt;Select&gt; (design-system wrapper over &lt;select&gt;) with one &lt;option&gt; per agent-provided q.options; native &lt;select&gt; option popups are browser/OS-drawn (not in the DOM flow) so they are not clipped to the card, and native &lt;option&gt; text cannot be made to wrap - long option strings render on one line and overflow horizontally.</t>
+  </si>
+  <si>
+    <t>The choice answer uses a native HTML select. A native select's option dropdown is rendered by the browser outside the page layout, so it is not constrained/clipped to the clarification card, and native &lt;option&gt; elements cannot be styled to wrap - long option labels render single-line and spill past the card bounds.</t>
+  </si>
+  <si>
+    <t>PLANNED (team to fix 2026-07-22): replace the native select for clarification choices with a custom, card-constrained dropdown/listbox (popup width bounded to the field, long options wrap or truncate-with-tooltip), OR render long-option questions as a radio-button list (each option on its own wrapping line) instead of a dropdown. Preserve the isOtherOption free-text reveal behaviour (Clarifications.tsx:77).</t>
+  </si>
+  <si>
+    <t>Security phase runs entirely as a MANUAL LLM review - no real SAST/SCA/SBOM scanner actually executes. On the live EPIC-004 run (371031a0) the security_review artifact itself states: Bandit 'blocked by sandbox restrictions -&gt; full manual pass performed'; cyclonedx-bom 'unavailable in sandbox -&gt; manual generation' (the SBOM metadata tool literally reads 'Manual CycloneDX Generation'); pip-audit/npm-audit are referenced as CI-integrated but were NOT run in the scan - the python-jose CVEs came from 'manual cross-reference with NVD/OSV'. So despite Bash being enabled in the scan, it produced NO tool-verified findings. A manual/LLM pass is not equivalent to running Bandit/Semgrep/pip-audit/Trivy/syft and cannot be trusted as a real scan.</t>
+  </si>
+  <si>
+    <t>Security phase / Companion environment</t>
+  </si>
+  <si>
+    <t>Recon 2026-07-22 on the successful live run 371031a0 (tenant 212395b8, EPIC-004/WI-22d8bd13). Verified from the run's security_review artifact body (Step 0 Tool Selection table + 'Pass 1 - Automated SAST (Manual Equivalent)': 'Bandit tool installation was blocked by sandbox restrictions') and the sbom artifact metadata.tools = 'Manual CycloneDX Generation'. Bash allow is live (claude_driver _SCAN_DISALLOWED_TOOLS permits Bash) but the scanners are not present/installable on the companion host.</t>
+  </si>
+  <si>
+    <t>The companion host lacks the scanner toolchain and/or network to install it; even with Bash allowed, 'pip install bandit' (and cyclonedx-bom, etc.) is blocked by the sandbox/environment, so the agent falls back to manual analysis for SAST, SCA and SBOM. Nothing provisions or verifies the scanners before the scan runs.</t>
+  </si>
+  <si>
+    <t>PLANNED (team to fix): provision the scanner toolchain for the scan - pre-install and make invokable on the companion host (or in a dedicated scan container/image) bandit, semgrep, pip-audit, cyclonedx-bom/syft, and a working 'npm audit', with the network their vuln DBs need. Have the scan RECORD each scanner's real invocation + exit status so 'tool ran' is verifiable from evidence, not agent prose; fall back to manual only when a tool is genuinely unavailable and label it as such (see S.No 186).</t>
+  </si>
+  <si>
+    <t>Security review report OVERSTATES which tools actually ran. The 'Tool Selection' table lists Bandit/pip-audit/cyclonedx-bom as selected, and the verification checklist ticks pip-audit and npm-audit as [x] done, when in reality every one of those steps was performed MANUALLY (see S.No 185). A reader is misled into thinking the scan was tool-verified when it was an LLM manual pass. Security reports must be honest about manual-vs-tool or they give false assurance.</t>
+  </si>
+  <si>
+    <t>Security phase / Agent (10_security)</t>
+  </si>
+  <si>
+    <t>Recon 2026-07-22 on run 371031a0 security_review artifact: the Step 0 Tool Selection table presents tools as selected/used and the checklist marks '[x] pip-audit --requirement requirements.txt --fail-on-severity high' and '[x] npm audit --audit-level=high', though the body elsewhere says these were manual / CI-assumed and the CVEs were found by manual NVD/OSV cross-reference.</t>
+  </si>
+  <si>
+    <t>agents/10_security/agent.md lets the model present intended/CI tooling as if it executed in this scan; nothing constrains the report to distinguish 'tool actually run here' from 'manual equivalent' or 'assumed to run in CI'. Combined with S.No 185 (no tools present) this yields a report claiming tool coverage it does not have.</t>
+  </si>
+  <si>
+    <t>PLANNED (team to fix): update agents/10_security/agent.md to require honest labelling - each SAST/SCA/SBOM step must be marked MANUAL vs TOOL-RUN, never tick a tool checkbox for a manual/assumed step, and CI-only checks must be labelled 'CI gate (not run in this scan)'. Best paired with S.No 185's exit-code recording so the report reflects what verifiably ran.</t>
+  </si>
+  <si>
+    <t>Artifact preview: any NON-MARKDOWN artifact body renders as an unreadable wall of text - platform-wide, not just security. The security SBOM body is valid CycloneDX 1.5 JSON, but the Artifact preview shows it as a run-on blob of dictionaries. Every other artifact happens to be markdown so only JSON bodies expose it, but ANY phase that produces a JSON (or other non-markdown) body will render broken. Must be fixed generally, for all phases.</t>
+  </si>
+  <si>
+    <t>Artifacts / Preview (all phases)</t>
+  </si>
+  <si>
+    <t>Recon 2026-07-22 on run 371031a0 sbom artifact (body starts with '{' = CycloneDX JSON). Verified: backend/integrations/preview.py:139-142 _read_internal returns _INTERNAL_CONTENT_TYPE ('text/markdown', line 28) for EVERY internal S3 body regardless of format; frontend ArtifactPreviewScreen.tsx:119-121 renders content_type text/markdown via &lt;Markdown&gt;, so JSON is fed to the markdown renderer. The _FORMAT_CONTENT_TYPE map (preview.py:56) is only applied to the inline external_ref.body path (line 150), never the S3-body path.</t>
+  </si>
+  <si>
+    <t>content_type is not derived from the artifact body - the S3-body read path hardcodes text/markdown, so a JSON (or any non-markdown) body is handed to the markdown renderer and collapses into unreadable text. There is no format detection and no content_type stored on the artifact row.</t>
+  </si>
+  <si>
+    <t>PLANNED (team to fix, general/SOTA): make _read_internal format-aware - detect JSON (parse-check, or a stored/registered format hint) and return application/json; render JSON in the preview pretty-printed (indented) in a code block, and fall other non-markdown formats through the existing &lt;pre&gt; path rather than &lt;Markdown&gt;. Fixes the SBOM and any future non-markdown artifact across ALL phases.</t>
+  </si>
+  <si>
+    <t>Enhancement: let the user choose the security-scan target via a popup on the Security trigger. Today Security scans exactly one repo (the work item's pinned/default repo); a new/unpinned item on a multi-repo project errors out ('assign its repo... before running'), and there is no way to scan selected repos or the whole project. Team-decided flow: clicking the Security phase trigger opens a clean popup to select - (1) a specific/dedicated repo, (2) the default repo, or (3) the whole project / all repos (multi-repo); on selection the phase starts automatically. Works for a new item or one with a repo already assigned; non-disruptive to existing UI.</t>
+  </si>
+  <si>
+    <t>Security phase / Trigger UX</t>
+  </si>
+  <si>
+    <t>Recon 2026-07-22. Verified: backend/orchestration/trigger.py:126-159 _resolve_work_item_repo resolves ONE repo (pinned -&gt; override -&gt; single default; multi-repo unpinned RAISES TriggerError) and the scan copies that whole repo into a worktree; there is no all-repos/selectable-repo path and no trigger-time repo picker.</t>
+  </si>
+  <si>
+    <t>The scan target is resolved implicitly from the work item's single repo with no user choice; multi-repo unpinned is a hard error with no inline resolution, and whole-project coverage requires manually running Security on one work item per repo.</t>
+  </si>
+  <si>
+    <t>PLANNED (team-decided flow): add a small, clean modal on the Security phase trigger offering (1) a specific repo, (2) the default repo, (3) the whole project/all repos; on select, resolve the repo(s) and trigger automatically - for 'whole project' fan out one scan per repo. This also removes the unpinned-multi-repo dead-end (user picks the repo in the popup instead of hitting the error). Keep existing Gates/Runs UI unchanged; only the trigger gains the modal.</t>
+  </si>
+  <si>
+    <t>Gates page: when multiple phases run in parallel, multiple gates open but the user can only act on the TOP-MOST gate - the decision panel is bound to the first pending gate, so a user who wants to review/approve the 3rd gate first cannot. The pending-approvals rows are not selectable and do not drive the decision panel. Team-selected design = Option A: make each pending row selectable so clicking any gate loads THAT gate into the existing right-side decision panel (selected row highlighted), letting the user review and approve/reject any pending gate in any order. Smallest change to today's layout.</t>
+  </si>
+  <si>
+    <t>Gates / Approvals UI</t>
+  </si>
+  <si>
+    <t>Recon 2026-07-22 (screenshot: 2 pending gates - WI-59 Merge/Tech Lead + WI-70 Phase/QA Lead - decision panel locked to the top gate). Verified: frontend Gates.tsx renders the pending list plus a single decision panel bound to the top/selected gate; the pending rows carry only a Preview link, with no row-select wiring to re-point the panel at a chosen gate.</t>
+  </si>
+  <si>
+    <t>The decision panel is tied to a single (top/first) pending approval; the pending-approvals table rows have no selection handler to re-point the panel at a chosen gate, so out-of-order review/approval is impossible when several gates are pending at once.</t>
+  </si>
+  <si>
+    <t>PLANNED (team-selected Option A): make each pending-approvals row selectable - clicking a row loads that gate into the existing decision panel (highlight the selected row, keep the panel layout as-is). No new drawer/cards. Preserves the current UI while allowing any pending gate to be reviewed and approved/rejected in any order.</t>
+  </si>
+  <si>
+    <t>Manifest context provisioning loses information platform-wide: get_context returns only the 50 NEWEST artifacts by recency and the Manifest Composer then caps them to the top 20, with NO type/dependency awareness. On a mature project (any phase past mid-lifecycle - e.g. CI/CD Phase 11), the oldest-but-required upstream artifacts (e.g. the Phase 4 architecture/adr) get evicted from the composed AGENTS.md, so an agent may NOT receive the exact inputs its own body declares it needs. Affects ALL agents, not just CI/CD - a definite, silent loss of information.</t>
+  </si>
+  <si>
+    <t>Manifest Composer / get_context (all phases)</t>
+  </si>
+  <si>
+    <t>Recon 2026-07-22 (CI/CD Phase 11 pre-test recon). Verified: mcp_platform_state/tools.py:195-262 get_context orders artifacts by -created_at and slices [:50]; the `phase` arg drives ONLY knowledge-search (tools.py:238), never artifact selection. backend/manifest/composer.py:44 max_artifacts=20 + composer.py:189-208 _render_artifacts truncate to the newest 20. agents/11_cicd/agent.md:18 expects the Phase 4 architecture/adr + Phase 10 security + Phase 9 test_report in # Relevant Artifacts, which recency+cap can silently drop.</t>
+  </si>
+  <si>
+    <t>Artifact selection for the manifest is blind recency with a hard count cap and no per-agent dependency model - there is no declaration of which artifact TYPES an agent requires and no guarantee those reach it; newer artifacts crowd out older required ones.</t>
+  </si>
+  <si>
+    <t>FIXED - implemented in code (commits c00a26c / ef37bf9, 2026-07-22). Each agent now DECLARES its required upstream artifact types once in the catalog (AgentDefinition.needs_artifacts) with a needs_artifacts_for() resolver; get_context / the Manifest Composer build a GUARANTEED required tier (latest version per declared type) that is always injected and never evicted by the recency tail, so a late-lifecycle phase always receives the specific upstream inputs its body names. Verified in backend/apps/registry/catalog.py + backend/manifest/composer.py + mcp_platform_state. Paired with S.No 191.</t>
+  </si>
+  <si>
+    <t>Agents cannot accurately pull a specific artifact BY TYPE mid-run: the list_artifacts platform-state tool filters only by phase/status, not by artifact type, so when a needed artifact is absent from the manifest the agent has no precise way to fetch 'the architecture artifact' - it must scan pointers by recency and guess. This is the on-demand half of the context fix; without it the guaranteed-push tier (S.No 190) has no reliable fallback.</t>
+  </si>
+  <si>
+    <t>Platform-State MCP / list_artifacts (all agents)</t>
+  </si>
+  <si>
+    <t>Recon 2026-07-22. Verified: mcp_platform_state/tools.py:602-613 list_artifacts(project_id, phase, status) has NO `type` filter; the companion wrapper runner/companion/state_mcp.py:51-55 likewise. get_artifact_body(id) exists (tools.py:579) but needs an id the agent can only obtain by listing. Artifacts ARE typed (backend/apps/registry/models.py:60).</t>
+  </si>
+  <si>
+    <t>list_artifacts predates the dependency-driven context model; type was never a filter, so 'fetch the artifact of type X' is not expressible - the agent cannot accurately recover a required input that fell outside the manifest.</t>
+  </si>
+  <si>
+    <t>FIXED - implemented in code (2026-07-22). list_artifacts now takes a `type` filter (mcp_platform_state/tools.py, exposed through server.py and the companion state_mcp wrapper) so an agent can pull a specific upstream artifact by type on demand - list_artifacts(type='architecture') then get_artifact_body(id) - and the Manifest Composer instructs agents to use it for any input not pre-injected. Completes the push+pull design with S.No 190. Verified: tools.py list_artifacts type-filter cites Bugs S.No 191.</t>
+  </si>
+  <si>
+    <t>Invitation &amp; password-reset emails are NOT actually delivered to users - the invitee only sees the accept/reset link in the dev console (server terminal log), never in an inbox. EMAIL_BACKEND defaults to Django's console backend and there is no SendGrid (or any SMTP/API) delivery wired for production. Today an admin must copy the invitation link out of the server log and share it manually (Slack/chat). Enhancement: turn on real transactional email delivery so invited users receive their invitation (and password resets) by email.</t>
+  </si>
+  <si>
+    <t>Auth / Tenant invitations + password reset (email delivery)</t>
+  </si>
+  <si>
+    <t>Verified 2026-07-23. The email SEND code is already complete and wired: backend/apps/tenancy/emails.py (send_invitation_email / send_password_reset_email over Django send_mail), called on invitation create (backend/api/views.py:702) and on password reset. Links are built from FRONTEND_BASE_URL. The only stub is the delivery backend: backend/config/settings.py:169 EMAIL_BACKEND defaults to django.core.mail.backends.console.EmailBackend (prints to log instead of sending).</t>
+  </si>
+  <si>
+    <t>Intentional dev stub, not a defect. EMAIL_BACKEND is a deliberate pluggable seam set to the console backend for local dev (links print to the log). No production mail backend/credentials were configured and no SendGrid integration exists yet, so nothing is transmitted over the wire.</t>
+  </si>
+  <si>
+    <t>PLANNED - config only, no code change needed. Recommended: use Django's built-in SMTP backend against SendGrid's SMTP relay. Set EMAIL_BACKEND=django.core.mail.backends.smtp.EmailBackend, EMAIL_HOST=smtp.sendgrid.net, EMAIL_PORT=587, EMAIL_USE_TLS=True, EMAIL_HOST_USER=apikey (literal), EMAIL_HOST_PASSWORD=&lt;SENDGRID_API_KEY&gt;, DEFAULT_FROM_EMAIL=&lt;verified sender e.g. no-reply@edvensoft.com&gt;, and a correct FRONTEND_BASE_URL. Team side (in SendGrid, not our code): (1) verify a sender or domain via DNS auth, (2) generate an API key. Effort: a few hours, mostly the SendGrid sender verification; no new Python package required. Optional polish: add an EMAIL_* block to .env.example + a short docs note so it is a drop-in when creds arrive. The same seam also switches on password-reset emails.</t>
+  </si>
+  <si>
+    <t>Triggering the CI/CD phase (11_cicd) runs the agent to completion and registers its artifacts, but the build then FAILS at the very last step: the companion's pre-push secret scan blocks the branch push, so no PR is ever opened. Live: SpendLog WI-146 run cab0535c failed with '[high_entropy_secret] docker-compose.yml:64 - dev-***rs (55 chars)'. The CICD agent's Step 3 tells it to generate a local docker-compose.yml with database + cache services but gives NO secret-handling guidance, so the agent hardcodes a real generated dev password/token literal into the compose file. The pre-push guardrail correctly flags it and blocks the push (a TRUE positive), killing the build after all agent work is done.</t>
+  </si>
+  <si>
+    <t>CI/CD phase (11_cicd) - generated docker-compose.yml</t>
+  </si>
+  <si>
+    <t>Verified 2026-07-23. Confirmed AGENT-SIDE: docker-compose.yml exists nowhere on the SpendLog repo default branch (TARUN51/medslot-single-repo main has only backend/Dockerfile + backend/.env.example + frontend/.env.example), and the run's branch feature/WI-79a3804c never reached GitHub (push was blocked) - so the file was freshly generated by 11_cicd this run. Scanner working as intended: runner/companion/guardrails.py:59-75 flags a secret/password/token key assigned a &gt;=20-char, high-entropy (Shannon&gt;=3.5), non-placeholder value; ${VAR}/placeholder values are skipped. agents/11_cicd/agent.md Step 3 (compose) had no no-hardcode rule, unlike Step 2 (Dockerfile: 'no secrets in the Dockerfile'). Platform passes the finding through unchanged (backend/orchestration/build_activities.py:427); run is terminal so the console shows 'Retry run'. Note S.No 130 (commit 52533c4) only made the finding readable - it did not cause or change the block.</t>
+  </si>
+  <si>
+    <t>The 11_cicd agent body's Step 3 instructs generating a local docker-compose.yml with database + cache services (which need credentials) but - unlike the Dockerfile and Jenkinsfile steps - never says how to handle those secret values. The agent therefore hardcodes a concrete dev credential literal, which the companion's pre-push secret scan (PG14) correctly blocks. NOT a scanner defect - the scanner did its job; the agent violated the 'never hardcode secrets' principle its own quality gate already states.</t>
+  </si>
+  <si>
+    <t>FIXED 2026-07-23 (agent-body fix; team to re-test). agents/11_cicd/agent.md Step 3 now explicitly forbids hardcoding any secret in the compose file (even a dev DB/cache password) and requires env-var references (e.g. POSTGRES_PASSWORD: ${POSTGRES_PASSWORD} or env_file) plus a committed .env.example with placeholders only; the git-ignored real .env holds values. The Quality Gate line was also extended to cover local compose credentials, noting a hardcoded high-entropy value trips the pre-push scan. Scanner intentionally NOT weakened (that would let real secrets through). Immediate unblock: replace the literal on docker-compose.yml:64 with an env reference and re-trigger; a fresh run with the fixed agent body should no longer hardcode. VALIDATED LIVE 2026-07-23: a fresh end-to-end CICD run on SpendLog succeeded - agent wrote code, opened the PR, ran the code-review remediation loop, and merged with NO secret-scan block. Fix confirmed working.</t>
+  </si>
+  <si>
+    <t>Deployment phase (12): the agent body PROMISED the platform executes the deployment. Its Completion said the platform 'on approval executes the gated production deployment... then runs the smoke tests and the monitoring window... aborting and rolling back automatically' (agent.md:140, also lines 9 and 81). But the platform does NO such thing: on deployment-gate approval the workflow runs only publish_artifacts + transition_work_item-&gt;done (workflows.py:169-178). No deploy, no smoke tests, no monitoring, no rollback exists (the GitHub integration has no pipeline-trigger/deploy API). So the agent narrated a deployment to the user that never happened - a false statement, and dangerous in front of a customer.</t>
+  </si>
+  <si>
+    <t>Deployment phase (12_deployment) - agent body vs platform</t>
+  </si>
+  <si>
+    <t>Recon 2026-07-23 (Phase 12 pre-test). Verified: catalog 12_deployment is NOT rides_build/reads_code -&gt; planning path (trigger.py). On approval AgentRunWorkflow runs publish_artifacts + transition_work_item only (backend/orchestration/workflows.py:169-178); no deploy/workflow_dispatch/kubectl/ssh anywhere; backend/integrations/github/codehost.py has only PR/branch/merge ops, no pipeline/deploy API. Team decision 2026-07-23: Option A (governed release package + human-run pipeline); real platform execution = Option B, logged separately (S.No 196).</t>
+  </si>
+  <si>
+    <t>The agent body described the intended end-state (platform-executed, gated deployment) but that platform-side execution was never built. The agent therefore claims a capability the product does not have, and - running in a planning context with no environment - risks reporting fabricated smoke-test/monitoring/deploy results.</t>
+  </si>
+  <si>
+    <t>FIXED 2026-07-23 (Option A, team-approved). Reworded agents/12_deployment/agent.md to state the truth: the DevOps deployment-gate approval AUTHORIZES the release; the DevOps engineer then runs the documented deployment/smoke tests/monitoring via the phase-11 CD pipeline; the platform records the approval + publishes the deliverables and does NOT execute the deploy. Edited the intro, Step 5, and the Completion section, and added a Process guardrail forbidding the agent from reporting deploy/smoke/monitoring results as if it ran them. Agent-body migration string tests pass (21 passed).</t>
+  </si>
+  <si>
+    <t>Deployment gate had NO readiness enforcement. The Deployment agent's whole philosophy is 'never deploy without a completed readiness checklist', but the deployment gate carried EMPTY conditions - a DevOps approver could approve the release with nothing checked. The readiness verdict the agent produces was only narrative, not a control-plane condition, so the platform never enforced it.</t>
+  </si>
+  <si>
+    <t>Deployment gate (12) / gate conditions</t>
+  </si>
+  <si>
+    <t>Recon 2026-07-23. Verified: conditions_for_phase (backend/apps/gates/conditions.py) composed only WCAG (ux_design) + blocking-test (testing); deployment was in neither set, so its Approval.conditions were []. The enforcement mechanism already existed - decide_gate (apps/gates/services.py:135-150) blocks approval on any unmet required condition - deployment just had no conditions attached.</t>
+  </si>
+  <si>
+    <t>No per-phase readiness conditions were defined for the deployment gate; the agent's Step 1 readiness checklist lived only in the prompt with no control-plane counterpart, so it was unenforceable.</t>
+  </si>
+  <si>
+    <t>FIXED 2026-07-23. Added backend/apps/gates/readiness.py (a reviewer-attested checklist mirroring the agent's Step 1: code quality, testing+UAT, security, migrations, rollback, on-call/comms, deliverables) and composed it into conditions_for_phase for phase 'deployment'. Enforcement + UI are automatic: decide_gate blocks approval until all required items are ticked, and the Gates page renders gate criteria via useGateCriteria. Added tests/test_readiness_gate.py - pure composition test passes; DB-backed enforcement tests run in CI. Some items could later become platform-DERIVED (e.g. open security/test defects) - noted as a future refinement.</t>
+  </si>
+  <si>
+    <t>ENHANCEMENT (Option B): make production deployment a platform-EXECUTED action. Today (Option A) the deployment phase produces the release package + readiness gate, and a human runs the actual deploy via the phase-11 CD pipeline. Enhancement: on deployment-gate approval, have the platform ITSELF execute the gated deployment using the documented strategy (blue/green or canary), then run the post-deploy smoke tests and the 30-minute monitoring window, and auto-rollback on any trigger - realising end to end what the deployment agent's runbook describes.</t>
+  </si>
+  <si>
+    <t>Deployment phase (12) - platform-executed deployment</t>
+  </si>
+  <si>
+    <t>Logged 2026-07-23 per team decision (Q1: Option A now, Option B as enhancement). No environment exists yet for SpendLog/medslot; the team will create a test env later. Scope: a post-approval execution branch in AgentRunWorkflow (or a dedicated deployment workflow) + activities to dispatch the CD pipeline (e.g. GitHub Actions workflow_dispatch - not currently in integrations/github/codehost.py), run smoke tests, poll monitoring metrics, and trigger rollback.</t>
+  </si>
+  <si>
+    <t>Deployment execution was intentionally deferred: the agent describes it, but the platform-side deploy/smoke/monitor/rollback was never built (Option A is what ships). This is the build to close that gap.</t>
+  </si>
+  <si>
+    <t>PLANNED (enhancement, no target date). Large build: post-approval execution path + CD-pipeline dispatch connector (workflow_dispatch/deploy API) + smoke-test + monitoring-window + auto-rollback activities. Requires a real target environment. Pairs with S.No 194 (which reworded the agent to Option A); implementing this would move the agent's Completion wording back toward platform-executes.</t>
+  </si>
+  <si>
+    <t>Greenfield flow does NOT populate the Knowledge Index, so its retrieval is dead for greenfield projects. The Knowledge Index (apps/knowledge) chunks artifact bodies into KnowledgeChunk rows and retrieve() ranks them with a hybrid of BM25 keyword + optional vector cosine (fused via Reciprocal Rank Fusion). But index_artifact is only called during brownfield onboarding - never on greenfield artifact registration/publish. So for a greenfield project retrieve() returns nothing, get_context's _retrieve_knowledge yields [], and agents rely solely on the required+situational artifact tiers. Separately, semantic search is globally OFF (EMBEDDING_PROVIDER=null) so even where chunks exist, only the keyword baseline runs and the pgvector column is empty.</t>
+  </si>
+  <si>
+    <t>Knowledge Index / greenfield context retrieval</t>
+  </si>
+  <si>
+    <t>Verified 2026-07-23. index_artifact is called ONLY from backend/integrations/onboarding.py:400 (brownfield); no call on greenfield register/publish. Live backend env: EMBEDDING_PROVIDER=null (BM25-only; pgvector column unused). retrieve() (backend/apps/knowledge/index.py:106) already fuses BM25 + vector cosine via RRF and falls back to keyword if embeddings fail/are off. Providers built + ready: Voyage voyage-code-3 (dim 1024), Gemini gemini-embedding-001 (dim 1536); current column dim = 1536.</t>
+  </si>
+  <si>
+    <t>index_artifact was wired only into brownfield onboarding; greenfield artifact registration/publish never indexes. The embedding provider defaults to null (zero-cost baseline), so vectors are off platform-wide. Neither is a defect in the retrieval engine (which already does hybrid search) - it is unwired population + a disabled provider.</t>
+  </si>
+  <si>
+    <t>PLANNED (enhancement + team decision on hybrid). (1) Populate greenfield: call index_artifact on artifact PUBLISH (gated), same path brownfield uses - publish-only (not every draft) to bound embedding cost. (2) Enable semantic search via a provider: Gemini gemini-embedding-001 (dim 1536) matches the current column so NO re-migration; Voyage voyage-code-3 (dim 1024, code-optimized) would need a column re-migration + re-embed. (3) KEEP the hybrid (team idea, already implemented): retrieve() fuses BM25 + vector via RRF so keyword covers exact identifiers, vectors cover meaning/synonyms, and it degrades gracefully to keyword-only if embeddings are off/fail. Pros of vector: semantic match, better on mature projects, fits agents' NL queries. Cons: per-chunk API cost+latency, external dependency/keys, dimension lock-in at migration, weaker on exact tokens, extra privacy egress. Net: enable greenfield population + turn on Gemini, keep both methods fused.</t>
+  </si>
+  <si>
+    <t>Connect-machine token generation fails silently when the workspace has no project, and the UI shows a fake placeholder token instead of the real error. A new member (e.g. a QA tester) creates a workspace but has not created a project yet, opens "Connect your machine" and clicks "Generate enrollment token". The screen appears to produce a token and shows the companion serve command, but the token displayed is a hardcoded placeholder "rnr_3f9a…b2" (note the literal ellipsis) — not a real token — so the companion cannot authenticate. Reported by a QA member who ran: python -m runner.companion serve --api-url http://localhost:8000 --tenant ce135c3e-... --token rnr_3f9a…b2. A genuine token is a ~43-character secrets.token_urlsafe(32) string with no rnr_ prefix and no ellipsis, so what he copied was never a real (or partial) token — generation had actually failed and the failure was masked as a valid-looking token.</t>
+  </si>
+  <si>
+    <t>Connect Machine / companion enrollment (S-06)</t>
+  </si>
+  <si>
+    <t>Reported 2026-07-24 by a QA member on a newly-created workspace that had no project yet. Verified in code (no screenshot): the string "rnr_3f9a…b2" is a hardcoded mock placeholder, not a truncated real token.</t>
+  </si>
+  <si>
+    <t>Two layers. (1) The enroll endpoint requires a valid project: RunnerEnrollmentView.post (backend/api/runner_views.py:165-170) returns HTTP 400 ("project_id required" / "not found in tenant") when project_id is missing/invalid. (2) The Connect-machine screen picks the project from currentUser.memberships[0].project_id (frontend/src/features/identity/ConnectMachine.tsx:64); a brand-new workspace with no project has no membership, so project_id is empty and the POST 400s. The onGenerate catch block (ConnectMachine.tsx:68-70) swallows that error and calls setToken("rnr_3f9a…b2") — the same hardcoded placeholder used as the null fallback at line 61 — so a failed generation is rendered as a real-looking, copyable token instead of the backend's actual message. Net: there was no project to enroll the companion against, but the UI hid that behind a mock token. Same "fake mock data hides a real failure" pattern already fixed once on the invite-accept page (commit b77bdff).</t>
+  </si>
+  <si>
+    <t>PLANNED (not yet fixed). Immediate workaround: the member must create a project (and be a member of it) before generating the token — then the button returns a real ~43-char token and the serve command authenticates. Proper fix (frontend, ConnectMachine.tsx): on token-generate failure, surface the backend's real error message and do NOT fall back to a hardcoded token; guard the flow when the user has no project yet (show a clear "create a project first" prompt) instead of posting an empty project_id; and ensure the placeholder mock value can never be presented as a copyable token.</t>
+  </si>
+  <si>
+    <t>09b test-automation run parks with a Postgres DataError ("unsupported Unicode escape sequence ... \u0000 cannot be converted to text") after the PR and artifacts have already been created, even when the generated test itself passed. Reproduced twice on the same test case (WI-95 / TC-001): runs 1299c7de and e583a454 both parked identically with the same corrupted bytes, though neither companion report itself contained a NUL.</t>
+  </si>
+  <si>
+    <t>09b Test Automation / code review manifest</t>
+  </si>
+  <si>
+    <t>Reproduced 2026-07-22, tenant 212395b8-f118-4eef-93eb-ba2c45468226, WI-95 (TC-001), repo TARUN51/medslot-single-repo, PR #31. Confirmed via list_pr_files + get_file that tests/automated/playwright-report/data/*.webm and *.png contained NUL bytes.</t>
+  </si>
+  <si>
+    <t>AgentReviewProvider._render_pr_section (backend/orchestration/review_provider.py:225-245) inlines the content of every PR-changed file into the review manifest, which dispatch_review_task then stores in the JSON run.inputs column. A 09b build commits Playwright report artifacts (screenshots/videos) into the PR; those binaries contain NUL, which Postgres text/jsonb cannot store, so the save fails with DataError and the workflow parks the run as "pr/gate setup failed" - after the PR/test_report/code artifacts already registered successfully. See S.No 201 for the fix that stops new binaries from being committed in the first place.</t>
+  </si>
+  <si>
+    <t>Fixed. _render_pr_section now skips any file whose content contains a NUL byte (a binary marker) and inlines a "(binary file - omitted from review)" placeholder instead (review_provider.py:246-252). dispatch_review_task also scrubs NUL from the whole payload before saving, as defense-in-depth, via a shared build_types.scrub_nul helper; companion build reports are scrubbed the same way in build_report.py. Tests: test_render_pr_section_omits_binary_files, test_dispatch_review_task_scrubs_nul (test_review_dispatch.py), test_report_scrubs_nul_bytes_before_persisting (test_build_report_api.py).</t>
+  </si>
+  <si>
+    <t>A 09b remediation build (auto-fixing a code-review finding) fails immediately with "no preview target for this repo - set the repo's Preview URL...", even though the repo's Preview URL was already set and the initial build had just run successfully against it.</t>
+  </si>
+  <si>
+    <t>09b Test Automation / remediation loop</t>
+  </si>
+  <si>
+    <t>Reproduced 2026-07-22 on WI-95/TC-001 after the 08 review opened REM-W2/REM-W3; the run went straight to status=failed right after the build.remediation_dispatched event.</t>
+  </si>
+  <si>
+    <t>dispatch_build_core (backend/orchestration/build_activities.py:62-81) ships payload['preview_url']/['preview_start'] for the test_automation phase, but dispatch_remediation_core (build_activities.py:781-826), which re-dispatches 09b to fix review findings, built its payload without that block - so the companion's remediation build had no preview target and its fail-loud guard tripped instantly. See S.No 199 for the review-manifest bug found on the same run.</t>
+  </si>
+  <si>
+    <t>Fixed. dispatch_remediation_core now ships the same preview_url/preview_start (resolved via apps.projects.preview_config), phase-gated identically to the initial dispatch (build_activities.py:816-822). Test: test_dispatch_remediation_ships_preview_for_test_automation (test_review_dispatch.py).</t>
+  </si>
+  <si>
+    <t>The 09b test-automation agent commits its own generated run output (Playwright HTML report, test-results, MCP exploration snapshots) into the PR alongside the authored test script. These directories are bulky (one PR carried a 533KB report index.html plus screenshots and a video) and can contain binary files - the root cause of the review-manifest NUL crash at S.No 199. The 08 code review itself independently flagged this as a finding (REM-W1: "Generated Playwright artifacts... committed").</t>
+  </si>
+  <si>
+    <t>09b Test Automation / generated worktree output</t>
+  </si>
+  <si>
+    <t>Observed 2026-07-22, PR #31 (medslot-single-repo): tests/automated/playwright-report/, tests/automated/test-results/, and .playwright-mcp/ were all committed by the build.</t>
+  </si>
+  <si>
+    <t>The 09b agent body had no instruction to ignore generated run/report output, so every file the dry run (Step 6) or Playwright MCP (Step 4) wrote into the worktree was committed by the platform, which commits everything present in the worktree.</t>
+  </si>
+  <si>
+    <t>Fixed. Added a required ".gitignore" step to agents/09b_test_automation/agent.md Step 3 (Scaffolding Detection, line 123 on): the agent creates/extends a worktree-root .gitignore excluding .playwright-mcp/, playwright-report/, test-results/, blob-report/, and framework build/cache directories, while still committing the authored test scripts, page objects, and config. Note: does not retroactively untrack files a prior run already committed on the same branch - see S.No 205.</t>
+  </si>
+  <si>
+    <t>The "Test cases" coverage screen (per-story test-case list with automation status + Generate script) has no link anywhere in the UI - it is only reachable by typing its URL (/work-items/:id/test-cases) directly.</t>
+  </si>
+  <si>
+    <t>Test cases (P3-09b coverage screen)</t>
+  </si>
+  <si>
+    <t>Observed 2026-07-22 while trying to generate a script for TC-001 on WI-70: the epic/story detail page had no way to navigate to its test cases.</t>
+  </si>
+  <si>
+    <t>The coverage screen (frontend/src/features/lifecycle/TestCases.tsx) and its route were built, but the intended entry point (a tabbed story/epic detail) was deferred as a later enhancement, and no interim link was added in the meantime.</t>
+  </si>
+  <si>
+    <t>Fixed. Added a "Test cases" button to the work-item detail header (frontend/src/features/lifecycle/WorkItemEpic.tsx:88-92), linking to /work-items/:id/test-cases. The tabbed story/epic detail remains a separately deferred enhancement.</t>
+  </si>
+  <si>
+    <t>The companion always runs the 09b Playwright MCP (and the generated test suite) headless, so a developer watching a run locally has no way to see the agent explore the app or the test execute, even while attended at the keyboard.</t>
+  </si>
+  <si>
+    <t>Companion runner / 09b Live Application Exploration</t>
+  </si>
+  <si>
+    <t>Requested 2026-07-22, to observe a local 09b run end-to-end (locator discovery + test execution) for QA/demo purposes.</t>
+  </si>
+  <si>
+    <t>build_mcp_servers always passed --headless to the Playwright MCP (runner/companion/runner.py), and the agent's generated Playwright config had no signal telling it to run visibly instead.</t>
+  </si>
+  <si>
+    <t>Fixed. Added SDLC_COMPANION_HEADED, read by _headed_enabled() (runner/companion/runner.py:112-117): drops --headless from the Playwright MCP, and manifest_with_preview injects an instruction so the agent generates "headless: !process.env.SDLC_COMPANION_HEADED" in playwright.config.ts, so the same config still runs headless in CI. Added "serve --headed" as a first-class flag (runner/companion/__main__.py:110-115) that sets the env var in-process, so no separate shell export is needed. Default remains headless.</t>
+  </si>
+  <si>
+    <t>In Phases &amp; Runs, every catalog phase (Ideation .. Deployment) is shown as triggerable for ANY work-item type, including a test_case WI - a user can trigger "Ideation" or "Task Breakdown" on a test case, which is meaningless for that type and only 09b_test_automation should apply.</t>
+  </si>
+  <si>
+    <t>Phases &amp; Runs / phase catalog</t>
+  </si>
+  <si>
+    <t>Observed 2026-07-22 while triggering 09b Test Automation on a test_case work item (WI-95): all ~16 phases appeared as trigger options, not just Test Automation.</t>
+  </si>
+  <si>
+    <t>There is no per-WI-type phase gating in the trigger UI or backend catalog - the phase picker (frontend/src/features/lifecycle/PhasesAndRuns.tsx) renders every catalog entry regardless of the selected work item's type.</t>
+  </si>
+  <si>
+    <t>Not fixed - deferred. Would need the phase catalog (or the picker) to filter by work_item.type, e.g. only 09b_test_automation (and perhaps re-running 09_testing) for type=test_case.</t>
+  </si>
+  <si>
+    <t>A .gitignore added by the 09b agent (S.No 201) only stops NEW files from being committed going forward - it does not untrack files a prior run on the SAME branch already committed (e.g. Playwright report binaries from an earlier attempt). Resuming or remediating on an existing branch/PR can therefore keep re-triggering the code review's binary-artifact finding (REM-W1, S.No 199) even after the .gitignore fix ships.</t>
+  </si>
+  <si>
+    <t>09b Test Automation / worktree branch reuse</t>
+  </si>
+  <si>
+    <t>Observed 2026-07-22: re-running 09b on the same branch/PR (#31) after adding the .gitignore rule still showed the previously-committed playwright-report binaries until the branch was closed and recreated from scratch.</t>
+  </si>
+  <si>
+    <t>Git's .gitignore only governs untracked files from that point forward; files already added to the index/history stay tracked. The platform reuses the existing branch/worktree for a resumed or re-triggered build (register-don't-recreate), so old committed binaries persist across runs.</t>
+  </si>
+  <si>
+    <t>Not fixed - workaround documented: close the PR, delete the remote branch, and let 09b start a fresh branch so the new .gitignore takes effect from the first commit. A platform-side fix (e.g. "git rm --cached" the newly-ignored paths on resume) is not implemented.</t>
+  </si>
+  <si>
+    <t>A build (or phase) Run dispatched with inputs.dispatch.enrollment_id=null matched no companion in the claim query, so it sat running+pending forever, invisible in the UI, and blocked new triggers on the same WorkItem.</t>
+  </si>
+  <si>
+    <t>Runner dispatch / claim (RunnerWorkClaimView)</t>
+  </si>
+  <si>
+    <t>Surfaced 2026-07-21, tenant 212395b8-f118-4eef-93eb-ba2c45468226. Two paths hit it: the S.No 161 remediation auto-retry called trigger_build without triggered_by, and a user triggering before their companion enrolled. Validated live: run 812577a3 self-healed after the fix.</t>
+  </si>
+  <si>
+    <t>RunnerWorkClaimView's claim query only matched Run.inputs.dispatch.enrollment_id == runner.id - a dispatch created with enrollment_id=null (no companion known yet) matched nothing, so no companion could ever claim it.</t>
+  </si>
+  <si>
+    <t>Fixed. backend/api/runner_views.py: the claim query now also broadcast-matches any pending/claimed dispatch with enrollment_id null/empty for the same tenant+project, and binds enrollment_id to the claiming companion. backend/orchestration/build_activities.py: handle_remediation_exhausted_core now forwards triggered_by into the retry's trigger_build call so retries route to the original companion instead of null. Tests added in test_phase_dispatch.py, test_build_activities.py.</t>
+  </si>
+  <si>
+    <t>Clicking Retry run on a build whose feature branch a prior attempt had already pushed failed with "Empty build: the agent produced no changes to commit", even though real work already existed on the branch.</t>
+  </si>
+  <si>
+    <t>Companion build retry / worktree (runner/companion)</t>
+  </si>
+  <si>
+    <t>Surfaced 2026-07-21 on WI-45's retry after a companion redeploy. Validated live on WI-f717ea04 (merged) after the fix; also validated with a standalone host git script reproducing the exact retry scenario.</t>
+  </si>
+  <si>
+    <t>S.No 162's branch-continuity provisions the retry worktree from the branch's remote tip, not local/base. If the agent makes no new local commit on retry (the real work is already on the pushed branch), run_build left head_sha empty, and the empty-build guard failed the run even though the branch has real commits ahead of base.</t>
+  </si>
+  <si>
+    <t>Fixed. runner/companion/worktree.py adds commits_ahead_of_base(). runner/companion/runner.py's run_build now reports the existing branch tip as head_sha when there's no new local commit but the branch is already ahead of base, so the saga opens/continues the PR against the existing work instead of false-failing. Tests added in test_companion_runner.py.</t>
+  </si>
+  <si>
+    <t>Follow-up to S.No 161: when remediation exhausts an attempt and the platform auto-starts a fresh run, the user got no proactive signal - the failed run's console showed 'auto-retrying' text but no link to the new run, so a WorkItem appeared to show a failed run AND a separate pending gate with nothing connecting them.</t>
+  </si>
+  <si>
+    <t>Run console / lifecycle (RunConsole.tsx)</t>
+  </si>
+  <si>
+    <t>Confirmed this confused a user reviewing WI-43's gate. Backend already stored retry_run_id on the failed run's outputs (build_activities.py); zero frontend references to it before this fix.</t>
+  </si>
+  <si>
+    <t>The notification bell only counts pending gates + clarifications (AppShell.tsx bellCount), and the failed-run view never rendered the stored outputs.retry_run_id, so the two runs for the same WorkItem appeared unrelated.</t>
+  </si>
+  <si>
+    <t>Fixed. frontend/src/features/lifecycle/RunConsole.tsx: the failed view now reads outputs.retry_run_id, shows an info banner ("The platform started a fresh attempt...") with a live status link to the retry run, and swaps the primary action to "Go to the retry run -&gt;" when one exists. Shipped as PR #7, merged to develop (aafd1f9).</t>
+  </si>
+  <si>
+    <t>When a companion dies/hangs mid-build (e.g. crashes during a remediation cycle), the claimed run just sits running with no user-facing signal until the orchestrator's takeover reconciler eventually fires and fails it - the user has no way to know earlier that their companion needs restarting.</t>
+  </si>
+  <si>
+    <t>Runner heartbeat / takeover reconciler</t>
+  </si>
+  <si>
+    <t>Observed 2026-07-22 on WI-59 (run 925e7fde): companion 4a34ecf2's last heartbeat was 06:50:55 UTC; the run sat claimed/running with zero new events until "Build takeover - runner offline / no report before timeout" finally fired and failed it, well over an hour later. Retriggering after restarting the companion completed the build successfully.</t>
+  </si>
+  <si>
+    <t>The takeover timeout is the only mechanism that reconciles a dead companion's claim; there is no earlier heartbeat-staleness check that surfaces a warning to the user while the run is still nominally in-flight.</t>
+  </si>
+  <si>
+    <t>Not fixed. Suggested: surface a "companion appears offline" warning on the run console (and/or the companion status pill) once RunnerEnrollment.last_seen exceeds the ONLINE_THRESHOLD for a run that is still claimed/running, instead of waiting for the full takeover window.</t>
+  </si>
+  <si>
+    <t>Two independently-dispatched work items (TASK-021 ExpenseRepository CRUD and TASK-033 DashboardService) each implemented get_monthly_total/get_category_breakdown/get_recent on the same repository class, with different return contracts (plain tuples vs a CategoryTotal dataclass) - since neither WI's planning had visibility into the other's in-flight interface, it only surfaced as an add/add merge conflict when both branches reached main.</t>
+  </si>
+  <si>
+    <t>Work-item decomposition / planning - parallel WI interface overlap</t>
+  </si>
+  <si>
+    <t>Surfaced 2026-07-22 resolving WI-59's merge gate conflict against main (already carrying WI-35's merged CRUD repository). Resolved by keeping main's superset repository and adapting DashboardService/tests to the CategoryTotal contract; validated with the full backend suite (412 passed).</t>
+  </si>
+  <si>
+    <t>Planning dispatches WIs against the same file/class independently when their scopes overlap (both needed the same three read methods), with no shared interface contract or ownership check between them before they diverge in the codebase - the S.No 137 recon closed a similar-looking report as a false alarm, but this is a real, reproduced instance of the same class of problem.</t>
+  </si>
+  <si>
+    <t>Not fixed generally (this instance resolved manually). Suggested: when planning dispatches multiple WIs that touch the same file/module, either serialize them or require an explicit shared interface note so the return contract is agreed before either branch is built.</t>
+  </si>
+  <si>
+    <t>No uniqueness check on project name — duplicates are created silently</t>
+  </si>
+  <si>
+    <t>Project Setup</t>
+  </si>
+  <si>
+    <t>Project.name has no unique constraint and the create endpoint is stock DRF, so creating a second project with an existing name succeeds. The workspace ends up with two identically-named projects and the top-bar selector cannot tell them apart. Found by the pre-execution QA audit of the greenfield test pack (docs/qa/AUDIT_FINDINGS.md).</t>
+  </si>
+  <si>
+    <t>'Set default' on Repositories does nothing — the backend endpoint exists but nothing calls it</t>
+  </si>
+  <si>
+    <t>POST .../set-default is implemented and permission-gated on the backend, but the frontend click handler is an empty stub. The control looks live and silently does nothing. Found by the pre-execution QA audit of the greenfield test pack (docs/qa/AUDIT_FINDINGS.md).</t>
+  </si>
+  <si>
+    <t>Lifecycle rail ignores the tier it computes — a task shows plan phases</t>
+  </si>
+  <si>
+    <t>The lifecycle endpoint computes the work item's tier and then never uses it, emitting one node per registered spec regardless. A build-tier task renders the plan-tier phase rail, and the 'No phases run yet.' empty state can never appear. Found by the pre-execution QA audit of the greenfield test pack (docs/qa/AUDIT_FINDINGS.md).</t>
+  </si>
+  <si>
+    <t>Project create, profile edit, work-item write, phase trigger, run takeover and companion enroll are unauthenticated</t>
+  </si>
+  <si>
+    <t>Platform / Permissions</t>
+  </si>
+  <si>
+    <t>DRF's project-wide default permission is AllowAny, and these endpoints never override it. A plain engineer with no admin grant can create projects, rewrite the project profile that every agent reads, create and edit work items, trigger phase runs, take over a run, and enroll a companion machine. Found by the pre-execution QA audit of the greenfield test pack (docs/qa/AUDIT_FINDINGS.md).</t>
+  </si>
+  <si>
+    <t>A newly created test case does not appear until the page is reloaded</t>
+  </si>
+  <si>
+    <t>Test Cases</t>
+  </si>
+  <si>
+    <t>The create mutation invalidates the ['work-items'] query key, but the test-case table reads ['test-cases']. Nothing invalidates the list the user is looking at. Found by the pre-execution QA audit of the greenfield test pack (docs/qa/AUDIT_FINDINGS.md).</t>
+  </si>
+  <si>
+    <t>takeover_flag is set and released but never read as a guard</t>
+  </si>
+  <si>
+    <t>Recovery &amp; Takeover</t>
+  </si>
+  <si>
+    <t>The flag's only reader in the backend is the manifest renderer. Trigger admission is decided purely by run status, so the flag guards nothing — and the timeout park sets it itself before any human acts. Found by the pre-execution QA audit of the greenfield test pack (docs/qa/AUDIT_FINDINGS.md).</t>
+  </si>
+  <si>
+    <t>/recovery?run=&lt;id&gt; is inert — there is no way to take over a named run</t>
+  </si>
+  <si>
+    <t>The recovery screen always targets the first stalled-or-failed run it finds in the project. When a ?run= parameter is supplied the target is forced undefined and the screen renders 'No parked runs', so the deep link is worse than useless. 'Take over instead' on the run console also navigates without a run parameter. Found by the pre-execution QA audit of the greenfield test pack (docs/qa/AUDIT_FINDINGS.md).</t>
+  </si>
+  <si>
+    <t>Five pieces of dead UI code that can never render</t>
+  </si>
+  <si>
+    <t>Platform / UI</t>
+  </si>
+  <si>
+    <t>The 'Pending gate' artifact badge and its traceability legend colour (pending_gate is not an artifact status); the 'running' work-item badge (not a WorkItem state); the roles gap banner (its condition requires no admin fallback, and a tenant admin always exists); the 'A description is required' validation (gallery-only); the 'Preview unavailable' state for internal artifacts (they 404 to 'Artifact not found' first); and the 'Platform only' system-of-record label (sor is never blank). Found by the pre-execution QA audit of the greenfield test pack (docs/qa/AUDIT_FINDINGS.md).</t>
+  </si>
+  <si>
+    <t>Silent failure paths — several actions fail with no message at all</t>
+  </si>
+  <si>
+    <t>Invite resend and revoke have no error handler and the screen has no error surface; a repository 403 is swallowed; GenerateCell trigger errors are dropped; and a short password on accept-invite and on reset, plus a blank signup name, all 400 with the form left untouched. The user cannot tell a failure from a no-op. Found by the pre-execution QA audit of the greenfield test pack (docs/qa/AUDIT_FINDINGS.md).</t>
+  </si>
+  <si>
+    <t>A failed request renders as an empty or zero state instead of an error</t>
+  </si>
+  <si>
+    <t>The dashboard, artifacts registry, traceability graph, repositories list and the admin user list all render their empty state when the request fails. A completely broken backend looks like a calm, brand-new workspace — which also means several test cases would pass against it. Found by the pre-execution QA audit of the greenfield test pack (docs/qa/AUDIT_FINDINGS.md).</t>
+  </si>
+  <si>
+    <t>/onboarding sits in the greenfield sidebar and hardcodes brownfield copy</t>
+  </si>
+  <si>
+    <t>Onboarding</t>
+  </si>
+  <si>
+    <t>The onboarding route is rendered in the sidebar for every project regardless of track, and the screen states the project is brownfield with no track check. A greenfield user is one click from a wizard that describes a project they do not have. Found by the pre-execution QA audit of the greenfield test pack (docs/qa/AUDIT_FINDINGS.md).</t>
+  </si>
+  <si>
+    <t>Dashboard gates badge is not 'gates needing you' — it is unfiltered and capped at 20</t>
+  </si>
+  <si>
+    <t>The count is every pending gate on the project, with no user or role filter, and the underlying query is capped at 20. It reads as a personal to-do count and is neither. Found by the pre-execution QA audit of the greenfield test pack (docs/qa/AUDIT_FINDINGS.md).</t>
+  </si>
+  <si>
+    <t>Companion enrollment ignores the project multi-select</t>
+  </si>
+  <si>
+    <t>Companion</t>
+  </si>
+  <si>
+    <t>The 'Projects' multi-select on the enrollment screen is never passed to the enroll call; the token always binds to the first membership. In a multi-project workspace the machine is enrolled against the wrong project with no indication. Found by the pre-execution QA audit of the greenfield test pack (docs/qa/AUDIT_FINDINGS.md).</t>
+  </si>
+  <si>
+    <t>'Published this week' counts artifacts by creation date, not publish date</t>
+  </si>
+  <si>
+    <t>Both the 'Published this week' figure and the 'Recent publishes' list filter on created_at. An artifact created eight days ago and published today never appears, and one created today but never published does. Found by the pre-execution QA audit of the greenfield test pack (docs/qa/AUDIT_FINDINGS.md).</t>
+  </si>
+  <si>
+    <t>/admin/&lt;anything&gt; renders a developer placeholder</t>
+  </si>
+  <si>
+    <t>An unmatched admin route falls through to a placeholder reading 'Foundation route mounted. Feature screens land in T2-T5.' It is behind the admin guard, but any workspace admin with a stale bookmark or a typo reaches it in production. Found by the pre-execution QA audit of the greenfield test pack (docs/qa/AUDIT_FINDINGS.md).</t>
+  </si>
+  <si>
+    <t>Ideation registers ONE artifact containing the Context Gap Scan instead of opening the clarifications gate (intermittent)</t>
+  </si>
+  <si>
+    <t>Greenfield: create a project, add a work item, trigger Ideation. Expected the clarifications gate with the agent's tiered questions. Instead the run went straight to a review gate with a single 'Ideation' artifact whose body WAS the gap scan — the questions themselves, ending 'I will not produce or register any artifact until you answer them'. Intermittent: the same code produced a correct gate on other runs, which is why it was chased as a prompt/model problem for days. Reported independently by two developers. Reproduced live on 2026-07-30 (run f390734e, then again as 457f65e1).</t>
+  </si>
+  <si>
+    <t>Runs / Clarifications</t>
+  </si>
+  <si>
+    <t>The Claude Code CLI (2.1.208) DEFERS tools out of the agent's initial context to save tokens, and 'ToolSearch' is the only mechanism that loads a deferred tool back (the SDK models this as deferredBuiltinTools). 'ToolSearch' was on the platform's planning and scan DENYLISTS — added 2026-07-09 in commit 98200ae, when it was merely another built-in to sandbox away, long before the CLI used it this way. Granting all 13 platform-state tools in allowed_tools therefore guaranteed nothing: whatever the CLI deferred was permanently invisible to the agent. Proof from run 457f65e1 — the agent's own first paragraph: 'The platform-state tools (ask_human, register_artifact, add_trace_edge, log_event) referenced in my operating instructions are not present in my available tool context', while THE SAME RUN successfully called list_artifacts and get_artifact. Read tools present, write tools and ask_human absent — so the agent produced 39,417 chars of finished deliverables as prose because it had nowhere to put them. Intermittent because what the CLI defers depends on context pressure, which varies run to run. NOT a model adherence problem, NOT a crashed MCP server, NOT the environment — all three were investigated and ruled out with evidence.</t>
+  </si>
+  <si>
+    <t>Removed 'ToolSearch' from _PLANNING_DISALLOWED_TOOLS and _SCAN_DISALLOWED_TOOLS (backend/drivers/claude_driver.py) AND added it to the three allowlists — PLAN_ALLOWED_TOOLS (runner/companion/daemon.py), BUILD_ALLOWED_TOOLS (runner/companion/runner.py) and PLATFORM_TOOLS (backend/orchestration/activities.py); a denylist removal alone is not enough while an allowlist is in force. The sandbox is NOT widened: ToolSearch returns schemas only, for tools already granted, and execution stays gated by the same allowlist plus denylist. VERIFIED live end-to-end after the fix: ask_human called at 30s (4 tiered questions, Tier 1 required / Tier 2 with suggestion), then 7x register_artifact, 7x stage_artifact_body, 1x add_trace_edge, producing the full healthy 7-artifact ideation (ideation, feasibility_report, stakeholder_map, success_metrics, market_sizing, competitive_analysis, assumption) and the phase completed. Full write-up: docs/INCIDENT_2026-07-30_clarifications_gate.md.</t>
+  </si>
+  <si>
+    <t>A run whose agent registered nothing still produced an approvable artifact and opened a review gate</t>
+  </si>
+  <si>
+    <t>The safety-net defect behind S.No 226. When the agent's tools were unreachable, the platform still filed its final message as the phase deliverable and opened a normal review gate on it — so a completely failed run looked like a successful one. This is why the underlying bug survived for weeks: nothing ever failed visibly, and a reviewer would have approved a document containing the agent's questions.</t>
+  </si>
+  <si>
+    <t>Runs / Gates</t>
+  </si>
+  <si>
+    <t>register_phase_result_core (backend/orchestration/activities.py) unconditionally staged the engine's final text, registered it as a phase-typed artifact and let the run proceed to its gate; nothing examined what the text was. The existing guard, verify_write_completeness_core, checks that the expected artifact type exists and is non-empty — but for ideation it looks for type 'ideation', which is EXACTLY the artifact the platform had just created from the agent's questions, and non-empty because the gap scan was 3,441 real characters. The platform was manufacturing the evidence its own check looked for.</t>
+  </si>
+  <si>
+    <t>The platform's own artifact is now stamped external_ref={'source': 'phase_report'} at both sinks (companion register_phase_result_core and direct execute_phase), and verify_write_completeness_core requires at least ONE artifact the AGENT registered. If the only record is the platform's copy of the final message the run FAILS with a message naming what to check, and NO gate opens. Evidence for the bar: across 47 successful runs spanning 13 phases the minimum artifact count was 2 (the platform's plus at least one agent-registered) and never 1; the failed run had exactly 1. Replayed against every historical successful run: 49 pass, 0 regress. PROVEN IN PRODUCTION — it caught the real intermittent bug on its first encounter (run 457f65e1 parked with a clear reason instead of filing a false artifact), which is how the root cause in S.No 226 was finally found.</t>
+  </si>
+  <si>
+    <t>Agent briefing (manifest) was silently truncated mid-sentence, losing project constraints and operating rules</t>
+  </si>
+  <si>
+    <t>Every run is given a briefing document in seven sections, each capped. Two sections were over their cap on a normal greenfield project, so real content was cut — including the end of the user's own project constraints and the tail of the agent's operating rules. Nothing logged it and nothing showed it, so the only symptom was an agent that appeared to have forgotten something.</t>
+  </si>
+  <si>
+    <t>Runs / Agents</t>
+  </si>
+  <si>
+    <t>backend/manifest/composer.py caps each section in tokens and cuts by CHARACTER count. Measured on a live ideation run: 'rules' needed 1,706 tokens against a 1,500 cap (780 chars lost) and 'project' needed 906 against 800 (378 chars lost). The Project section stopped mid-sentence inside the user's constraints at 'Authentication: Email + password only. No OTP, no'; the Rules section lost Rule 9, the assumptions protocol and the review-gate rule, because truncation removes the END and the last-written rules live there. The whole manifest was 3,594 tokens — under 2% of the model's 200k window — so a document with no size problem was being cut. The caps were early guesses applied equally to sections that grow without bound (artifact lists, event history) and sections we AUTHOR (rules, project profile), which is the category error.</t>
+  </si>
+  <si>
+    <t>Caps raised where the content is authored and left alone where it grows without bound: rules 1500 -&gt; 3000, project 800 -&gt; 2000, important_context 1500 -&gt; 2000; relevant_artifacts / recent_events / retrieved_knowledge unchanged. Truncation now cuts at a LINE boundary instead of mid-character. compose_manifest_core emits a 'manifest.truncated' ledger event naming the cut sections, so it can never be silent again and the team has real data to tune the caps. Verified on the live project: all seven sections now fit (3,633 tokens, nothing cut, user constraints intact end-to-end). FUTURE ENHANCEMENT: these are fixed constants sized against a 200k window — when model selection is exposed to users they should scale from the selected model's context window instead (noted in docs/INCIDENT_2026-07-30_clarifications_gate.md).</t>
+  </si>
+  <si>
+    <t>MCP server config was sent as inline command-line JSON with a seven-variable environment</t>
+  </si>
+  <si>
+    <t>Hardening found while investigating S.No 226. The companion launches the platform-state MCP server — the process that provides EVERY tool an agent has — as a subprocess, and passed its whole configuration on the command line. Not confirmed as a cause of any observed failure, but two real risks, one of them a repeat of an already-fixed class of bug (Bugs row 64, Windows 'command line too long' misreported as 'Claude Code not found').</t>
+  </si>
+  <si>
+    <t>Companion / Runs</t>
+  </si>
+  <si>
+    <t>(1) The subprocess was given exactly seven environment variables. If that env ever REPLACES rather than extends the child's environment, Python cannot start on Windows: without SYSTEMROOT, Winsock fails to initialise and the interpreter dies during 'import asyncio' with OSError [WinError 10106], before any of our code runs — so the process that would have logged the failure is the one that died. Reproduced directly on a developer machine: 7 vars -&gt; exit 1; plus SYSTEMROOT -&gt; serves normally. (2) The config travelled as inline --mcp-config JSON on the command line. Windows caps a command line at ~32,767 chars (the ceiling behind Bugs row 64), and command lines are readable by any user from a process listing — so an inlined config publishes the runner token.</t>
+  </si>
+  <si>
+    <t>The environment is now inherited from the machine and then overlaid with the seven runner values, and the entire config is written to a temp FILE whose path goes on the command line — the same shape the team already adopted for the agent body (--system-prompt-file). The file is deleted on every exit path because it carries the runner token. Applied to BOTH the planning path (daemon.state_mcp_servers) and the build path (runner.build_mcp_servers), which launch the identical server and carried the identical risk. Verified: command line 59 chars (the path) versus 6,708 inline; 88 env vars in the file with SYSTEMROOT and PATH present and the runner values correctly overlaid; file removed after the run; 31 companion daemon tests pass.</t>
+  </si>
+  <si>
+    <t>Clarification events from deleted runs on other work items leak into a fresh work item's manifest</t>
+  </si>
+  <si>
+    <t>Observed while diagnosing S.No 226. A brand-new work item's agent reported: 'Two prior clarification.asked events appear in the run history but no answers were carried into this manifest.' Those events belonged to earlier runs on DIFFERENT work items that had since been deleted. At best this is noise in the briefing; at worst an agent reasons from another work item's clarifications, or believes questions were already asked and answered when they were not.</t>
+  </si>
+  <si>
+    <t>Not yet diagnosed. The '# Recent Events' section of the manifest is populated from the ledger scoped to the project rather than to the work item, so clarification events raised against any work item in the project reach every run's briefing — and deleting the run does not remove its ledger events. Needs confirmation against mcp_platform_state.tools.get_context before a fix is proposed.</t>
+  </si>
+  <si>
+    <t>None — logged for triage. Suggested direction: scope clarification-related events in the manifest to the CURRENT work item, or carry the answers alongside the events so an agent never sees a question without its answer. See section 5 of docs/INCIDENT_2026-07-30_clarifications_gate.md.</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3023,8 +3797,8 @@
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>3521075</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>2296615</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3070,8 +3844,8 @@
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>3417795</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>1543921</xdr:rowOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>1508875</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3118,8 +3892,8 @@
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>3520518</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>1147740</xdr:rowOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>1147739</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3165,8 +3939,8 @@
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>3523034</xdr:colOff>
-      <xdr:row>21</xdr:row>
-      <xdr:rowOff>1727201</xdr:rowOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>1727200</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3212,8 +3986,8 @@
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>3471333</xdr:colOff>
-      <xdr:row>25</xdr:row>
-      <xdr:rowOff>1678549</xdr:rowOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>1679535</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3259,8 +4033,8 @@
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>3444875</xdr:colOff>
-      <xdr:row>24</xdr:row>
-      <xdr:rowOff>1727021</xdr:rowOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>1727020</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3306,7 +4080,7 @@
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>3520639</xdr:colOff>
-      <xdr:row>26</xdr:row>
+      <xdr:row>35</xdr:row>
       <xdr:rowOff>1796213</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -3353,7 +4127,7 @@
     <xdr:to>
       <xdr:col>6</xdr:col>
       <xdr:colOff>4026</xdr:colOff>
-      <xdr:row>27</xdr:row>
+      <xdr:row>35</xdr:row>
       <xdr:rowOff>1739347</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -3400,7 +4174,7 @@
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>3520303</xdr:colOff>
-      <xdr:row>28</xdr:row>
+      <xdr:row>35</xdr:row>
       <xdr:rowOff>1762444</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -3447,7 +4221,7 @@
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>3228411</xdr:colOff>
-      <xdr:row>30</xdr:row>
+      <xdr:row>35</xdr:row>
       <xdr:rowOff>1531714</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -3494,8 +4268,8 @@
     <xdr:to>
       <xdr:col>6</xdr:col>
       <xdr:colOff>3735</xdr:colOff>
-      <xdr:row>30</xdr:row>
-      <xdr:rowOff>3505976</xdr:rowOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>1762838</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3541,8 +4315,8 @@
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>3521043</xdr:colOff>
-      <xdr:row>27</xdr:row>
-      <xdr:rowOff>3635375</xdr:rowOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>1778000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3588,8 +4362,8 @@
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>2609453</xdr:colOff>
-      <xdr:row>32</xdr:row>
-      <xdr:rowOff>1415835</xdr:rowOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>1415834</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3635,8 +4409,8 @@
     <xdr:to>
       <xdr:col>6</xdr:col>
       <xdr:colOff>664</xdr:colOff>
-      <xdr:row>38</xdr:row>
-      <xdr:rowOff>1705429</xdr:rowOff>
+      <xdr:row>75</xdr:row>
+      <xdr:rowOff>1705428</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3682,7 +4456,7 @@
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>3520006</xdr:colOff>
-      <xdr:row>39</xdr:row>
+      <xdr:row>75</xdr:row>
       <xdr:rowOff>1770673</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -4193,22 +4967,23 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J231"/>
-  <sheetFormatPr defaultRowHeight="15.75"/>
+  <sheetPr filterMode="1"/>
+  <dimension ref="A1:J238"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="7.85546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.81640625" style="2" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="33" style="2" customWidth="1"/>
     <col min="3" max="3" width="40" style="2" customWidth="1"/>
-    <col min="4" max="4" width="16.140625" style="2" customWidth="1"/>
+    <col min="4" max="4" width="16.1796875" style="2" customWidth="1"/>
     <col min="5" max="5" width="14" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="52.85546875" style="2" customWidth="1"/>
-    <col min="7" max="7" width="10.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="52.81640625" style="2" customWidth="1"/>
+    <col min="7" max="7" width="10.453125" style="2" bestFit="1" customWidth="1"/>
     <col min="8" max="9" width="28" style="2" customWidth="1"/>
-    <col min="10" max="10" width="9.42578125" style="2" bestFit="1" customWidth="1"/>
-    <col min="11" max="16384" width="9.140625" style="2"/>
+    <col min="10" max="10" width="9.453125" style="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="16384" width="9.1796875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="16.5">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4240,7 +5015,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="29.1" customHeight="1">
+    <row r="2" spans="1:10" ht="29.15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -4266,7 +5041,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="182.45" customHeight="1">
+    <row r="3" spans="1:10" ht="182.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -4295,7 +5070,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="29.1" customHeight="1">
+    <row r="4" spans="1:10" ht="29.15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -4318,7 +5093,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="29.1" customHeight="1">
+    <row r="5" spans="1:10" ht="29.15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="2">
         <v>4</v>
       </c>
@@ -4347,7 +5122,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="123.6" customHeight="1">
+    <row r="6" spans="1:10" ht="123.65" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="2">
         <v>5</v>
       </c>
@@ -4373,7 +5148,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:10" ht="57.95" customHeight="1">
+    <row r="7" spans="1:10" ht="58" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="2">
         <v>6</v>
       </c>
@@ -4399,7 +5174,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="8" spans="1:10" ht="43.5" customHeight="1">
+    <row r="8" spans="1:10" ht="43.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="2">
         <v>7</v>
       </c>
@@ -4425,7 +5200,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="101.45" customHeight="1">
+    <row r="9" spans="1:10" ht="101.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="2">
         <v>8</v>
       </c>
@@ -4451,7 +5226,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="101.45" customHeight="1">
+    <row r="10" spans="1:10" ht="101.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="2">
         <v>9</v>
       </c>
@@ -4477,7 +5252,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="11" spans="1:10" ht="362.45" customHeight="1">
+    <row r="11" spans="1:10" ht="362.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="2">
         <v>10</v>
       </c>
@@ -4506,7 +5281,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="12" spans="1:10" ht="174" customHeight="1">
+    <row r="12" spans="1:10" ht="174" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="2">
         <v>11</v>
       </c>
@@ -4532,7 +5307,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="13" spans="1:10" ht="72.599999999999994" customHeight="1">
+    <row r="13" spans="1:10" ht="72.650000000000006" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="2">
         <v>12</v>
       </c>
@@ -4555,7 +5330,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="14" spans="1:10" ht="72.599999999999994" customHeight="1">
+    <row r="14" spans="1:10" ht="72.650000000000006" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="2">
         <v>13</v>
       </c>
@@ -4581,7 +5356,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="15" spans="1:10" ht="57.95" customHeight="1">
+    <row r="15" spans="1:10" ht="58" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="2">
         <v>14</v>
       </c>
@@ -4607,7 +5382,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="16" spans="1:10" ht="87" customHeight="1">
+    <row r="16" spans="1:10" ht="87" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="2">
         <v>15</v>
       </c>
@@ -4633,7 +5408,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="17" spans="1:10" ht="116.1" customHeight="1">
+    <row r="17" spans="1:10" ht="116.15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="2">
         <v>16</v>
       </c>
@@ -4659,7 +5434,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:10" ht="29.1" customHeight="1">
+    <row r="18" spans="1:10" ht="29.15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="2">
         <v>17</v>
       </c>
@@ -4685,7 +5460,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="19" spans="1:10" ht="188.45" customHeight="1">
+    <row r="19" spans="1:10" ht="188.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="2">
         <v>18</v>
       </c>
@@ -4712,7 +5487,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="20" spans="1:10" ht="144.94999999999999" customHeight="1">
+    <row r="20" spans="1:10" ht="145" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="2">
         <v>19</v>
       </c>
@@ -4738,7 +5513,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="21" spans="1:10" ht="188.45" customHeight="1">
+    <row r="21" spans="1:10" ht="188.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="2">
         <v>20</v>
       </c>
@@ -4764,7 +5539,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="22" spans="1:10" ht="409.5" customHeight="1">
+    <row r="22" spans="1:10" ht="409.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="2">
         <v>21</v>
       </c>
@@ -4790,7 +5565,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="23" spans="1:10" ht="409.5" customHeight="1">
+    <row r="23" spans="1:10" ht="409.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="2">
         <v>22</v>
       </c>
@@ -4816,7 +5591,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="24" spans="1:10" ht="57.95" customHeight="1">
+    <row r="24" spans="1:10" ht="58" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="2">
         <v>23</v>
       </c>
@@ -4842,7 +5617,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="25" spans="1:10" ht="144.94999999999999" customHeight="1">
+    <row r="25" spans="1:10" ht="145" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="2">
         <v>24</v>
       </c>
@@ -4868,7 +5643,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="26" spans="1:10" ht="275.45" customHeight="1">
+    <row r="26" spans="1:10" ht="275.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="2">
         <v>25</v>
       </c>
@@ -4894,7 +5669,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="27" spans="1:10" ht="246.6" customHeight="1">
+    <row r="27" spans="1:10" ht="246.65" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="2">
         <v>26</v>
       </c>
@@ -4920,7 +5695,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="28" spans="1:10" ht="333.6" customHeight="1">
+    <row r="28" spans="1:10" ht="333.65" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="2">
         <v>27</v>
       </c>
@@ -4946,7 +5721,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="29" spans="1:10" ht="318.95" customHeight="1">
+    <row r="29" spans="1:10" ht="319" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="2">
         <v>28</v>
       </c>
@@ -4972,7 +5747,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="30" spans="1:10" ht="203.1" customHeight="1">
+    <row r="30" spans="1:10" ht="203.15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="2">
         <v>29</v>
       </c>
@@ -4998,7 +5773,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="31" spans="1:10" ht="324.95" customHeight="1">
+    <row r="31" spans="1:10" ht="325" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="2">
         <v>30</v>
       </c>
@@ -5024,7 +5799,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="32" spans="1:10" ht="261" customHeight="1">
+    <row r="32" spans="1:10" ht="261" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="2">
         <v>31</v>
       </c>
@@ -5050,7 +5825,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="33" spans="1:10" ht="231.95" customHeight="1">
+    <row r="33" spans="1:10" ht="232" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="2">
         <v>32</v>
       </c>
@@ -5076,7 +5851,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="34" spans="1:10" ht="72.599999999999994" customHeight="1">
+    <row r="34" spans="1:10" ht="72.650000000000006" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="2">
         <v>33</v>
       </c>
@@ -5102,7 +5877,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="35" spans="1:10" ht="57.95" customHeight="1">
+    <row r="35" spans="1:10" ht="58" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="2">
         <v>34</v>
       </c>
@@ -5128,7 +5903,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="36" spans="1:10" ht="261" customHeight="1">
+    <row r="36" spans="1:10" ht="261" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="2">
         <v>35</v>
       </c>
@@ -5148,7 +5923,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="37" spans="1:10" ht="231.95" customHeight="1">
+    <row r="37" spans="1:10" ht="232" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="2">
         <v>36</v>
       </c>
@@ -5174,7 +5949,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="38" spans="1:10" ht="101.45" customHeight="1">
+    <row r="38" spans="1:10" ht="101.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="2">
         <v>37</v>
       </c>
@@ -5200,7 +5975,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="39" spans="1:10" ht="409.5" customHeight="1">
+    <row r="39" spans="1:10" ht="409.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39" s="2">
         <v>38</v>
       </c>
@@ -5226,7 +6001,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="40" spans="1:10" ht="275.45" customHeight="1">
+    <row r="40" spans="1:10" ht="275.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="2">
         <v>39</v>
       </c>
@@ -5252,7 +6027,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="41" spans="1:10" ht="81">
+    <row r="41" spans="1:10" ht="77.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A41" s="2">
         <v>40</v>
       </c>
@@ -5281,7 +6056,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="42" spans="1:10" ht="275.25">
+    <row r="42" spans="1:10" ht="263.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A42" s="2">
         <v>41</v>
       </c>
@@ -5313,7 +6088,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="43" spans="1:10" ht="129">
+    <row r="43" spans="1:10" ht="124" hidden="1" x14ac:dyDescent="0.35">
       <c r="A43" s="2">
         <v>42</v>
       </c>
@@ -5342,7 +6117,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="44" spans="1:10" ht="162">
+    <row r="44" spans="1:10" ht="155" hidden="1" x14ac:dyDescent="0.35">
       <c r="A44" s="2">
         <v>43</v>
       </c>
@@ -5371,7 +6146,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="45" spans="1:10" ht="81">
+    <row r="45" spans="1:10" ht="77.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A45" s="2">
         <v>44</v>
       </c>
@@ -5400,7 +6175,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="46" spans="1:10" ht="96.75">
+    <row r="46" spans="1:10" ht="93" hidden="1" x14ac:dyDescent="0.35">
       <c r="A46" s="2">
         <v>45</v>
       </c>
@@ -5429,7 +6204,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="47" spans="1:10" ht="113.25">
+    <row r="47" spans="1:10" ht="108.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A47" s="2">
         <v>46</v>
       </c>
@@ -5458,7 +6233,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="48" spans="1:10" ht="96.75">
+    <row r="48" spans="1:10" ht="77.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A48" s="2">
         <v>47</v>
       </c>
@@ -5487,7 +6262,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="49" spans="1:10" ht="113.25">
+    <row r="49" spans="1:10" ht="108.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A49" s="2">
         <v>48</v>
       </c>
@@ -5516,7 +6291,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="50" spans="1:10" ht="81">
+    <row r="50" spans="1:10" ht="310" hidden="1" x14ac:dyDescent="0.35">
       <c r="A50" s="2">
         <v>49</v>
       </c>
@@ -5548,7 +6323,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="51" spans="1:10" ht="64.5">
+    <row r="51" spans="1:10" ht="341" hidden="1" x14ac:dyDescent="0.35">
       <c r="A51" s="2">
         <v>50</v>
       </c>
@@ -5577,7 +6352,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="52" spans="1:10" ht="81">
+    <row r="52" spans="1:10" ht="186" hidden="1" x14ac:dyDescent="0.35">
       <c r="A52" s="2">
         <v>51</v>
       </c>
@@ -5609,7 +6384,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="53" spans="1:10" ht="96.75">
+    <row r="53" spans="1:10" ht="263.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A53" s="2">
         <v>52</v>
       </c>
@@ -5641,7 +6416,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="54" spans="1:10" ht="372">
+    <row r="54" spans="1:10" ht="356.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A54" s="2">
         <v>53</v>
       </c>
@@ -5670,7 +6445,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="55" spans="1:10" ht="372">
+    <row r="55" spans="1:10" ht="263.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A55" s="2">
         <v>54</v>
       </c>
@@ -5699,7 +6474,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="56" spans="1:10" ht="409.6">
+    <row r="56" spans="1:10" ht="403" hidden="1" x14ac:dyDescent="0.35">
       <c r="A56" s="2">
         <v>55</v>
       </c>
@@ -5728,7 +6503,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="57" spans="1:10" ht="291.75">
+    <row r="57" spans="1:10" ht="217" hidden="1" x14ac:dyDescent="0.35">
       <c r="A57" s="2">
         <v>56</v>
       </c>
@@ -5757,7 +6532,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="58" spans="1:10" ht="409.6">
+    <row r="58" spans="1:10" ht="409.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A58" s="2">
         <v>57</v>
       </c>
@@ -5786,7 +6561,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="59" spans="1:10" ht="356.25">
+    <row r="59" spans="1:10" ht="248" hidden="1" x14ac:dyDescent="0.35">
       <c r="A59" s="2">
         <v>58</v>
       </c>
@@ -5815,7 +6590,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="60" spans="1:10" ht="409.6">
+    <row r="60" spans="1:10" ht="409.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A60" s="2">
         <v>59</v>
       </c>
@@ -5844,7 +6619,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="61" spans="1:10" ht="409.6">
+    <row r="61" spans="1:10" ht="409.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A61" s="2">
         <v>60</v>
       </c>
@@ -5870,7 +6645,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="62" spans="1:10" ht="409.6">
+    <row r="62" spans="1:10" ht="409.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A62" s="2">
         <v>61</v>
       </c>
@@ -5899,7 +6674,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="63" spans="1:10" ht="409.6">
+    <row r="63" spans="1:10" ht="409.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A63" s="2">
         <v>62</v>
       </c>
@@ -5931,7 +6706,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="64" spans="1:10" ht="409.6">
+    <row r="64" spans="1:10" ht="409.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A64" s="2">
         <v>63</v>
       </c>
@@ -5963,7 +6738,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="65" spans="1:10" ht="409.6">
+    <row r="65" spans="1:10" ht="409.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A65" s="2">
         <v>64</v>
       </c>
@@ -5995,7 +6770,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="66" spans="1:10" ht="409.6">
+    <row r="66" spans="1:10" ht="409.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A66" s="2">
         <v>65</v>
       </c>
@@ -6027,7 +6802,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="67" spans="1:10" ht="409.6">
+    <row r="67" spans="1:10" ht="372" hidden="1" x14ac:dyDescent="0.35">
       <c r="A67" s="2">
         <v>66</v>
       </c>
@@ -6059,7 +6834,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="68" spans="1:10" ht="409.6">
+    <row r="68" spans="1:10" ht="409.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A68" s="2">
         <v>67</v>
       </c>
@@ -6091,7 +6866,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="69" spans="1:10">
+    <row r="69" spans="1:10" ht="409.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A69" s="2">
         <v>68</v>
       </c>
@@ -6123,7 +6898,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="70" spans="1:10">
+    <row r="70" spans="1:10" ht="409.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A70" s="2">
         <v>69</v>
       </c>
@@ -6155,7 +6930,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="71" spans="1:10">
+    <row r="71" spans="1:10" ht="409.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A71" s="2">
         <v>70</v>
       </c>
@@ -6187,7 +6962,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="72" spans="1:10" ht="409.6">
+    <row r="72" spans="1:10" ht="201.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A72" s="2">
         <v>71</v>
       </c>
@@ -6219,7 +6994,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="73" spans="1:10" ht="409.6">
+    <row r="73" spans="1:10" ht="294.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A73" s="2">
         <v>72</v>
       </c>
@@ -6251,7 +7026,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="74" spans="1:10" ht="409.6">
+    <row r="74" spans="1:10" ht="409.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A74" s="2">
         <v>73</v>
       </c>
@@ -6283,7 +7058,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="75" spans="1:10" ht="409.6">
+    <row r="75" spans="1:10" ht="263.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A75" s="2">
         <v>74</v>
       </c>
@@ -6315,7 +7090,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="76" spans="1:10" ht="409.6">
+    <row r="76" spans="1:10" ht="217" x14ac:dyDescent="0.35">
       <c r="A76" s="2">
         <v>75</v>
       </c>
@@ -6347,7 +7122,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="77" spans="1:10" ht="409.6">
+    <row r="77" spans="1:10" ht="341" x14ac:dyDescent="0.35">
       <c r="A77" s="2">
         <v>76</v>
       </c>
@@ -6369,189 +7144,185 @@
       <c r="G77" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="H77" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The edit UI was never built - only the WorkItemPatchSerializer (title/description/type/repo) was scaffolded on the backend; no frontend form calls it (the patch hook is wired only to the repo field on the Repo-Assignment card). state, estimate and depends_on are not editable (state is read-only, there is no estimate field, depends_on is excluded from the patch serializer).</t>
-        </is>
-      </c>
-      <c r="I77" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">OPEN - surgical fix (recon 2026-07-24): FRONTEND-ONLY for the common case - add a small edit form/modal in WorkItemTask.tsx / WorkItemEpic.tsx that calls the existing usePatchWorkItem with {title, description, type}; no backend change needed (the PATCH endpoint is already live and tested). To also edit dependencies, add depends_on to WorkItemPatchSerializer.fields with same-project + no-cycle validation (mirror the repo check in perform_update). Estimate is out of scope until a WorkItem.estimate field is modelled (see S.No 75).</t>
-        </is>
+      <c r="H77" s="2" t="s">
+        <v>813</v>
+      </c>
+      <c r="I77" s="2" t="s">
+        <v>814</v>
       </c>
       <c r="J77" s="2" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="78" spans="1:10" ht="409.6">
+    <row r="78" spans="1:10" ht="387.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A78" s="2">
         <v>77</v>
       </c>
       <c r="B78" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="C78" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="D78" s="2" t="s">
         <v>320</v>
       </c>
-      <c r="C78" s="2" t="s">
+      <c r="E78" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F78" s="2" t="s">
         <v>321</v>
-      </c>
-      <c r="D78" s="2" t="s">
-        <v>322</v>
-      </c>
-      <c r="E78" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F78" s="2" t="s">
-        <v>323</v>
       </c>
       <c r="G78" s="2" t="s">
         <v>36</v>
       </c>
       <c r="H78" s="2" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="I78" s="2" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="J78" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="79" spans="1:10" ht="409.6">
+    <row r="79" spans="1:10" ht="279" x14ac:dyDescent="0.35">
       <c r="A79" s="2">
         <v>78</v>
       </c>
       <c r="B79" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="C79" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="D79" s="2" t="s">
         <v>326</v>
-      </c>
-      <c r="C79" s="2" t="s">
-        <v>327</v>
-      </c>
-      <c r="D79" s="2" t="s">
-        <v>328</v>
       </c>
       <c r="E79" s="2" t="s">
         <v>22</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="G79" s="2" t="s">
         <v>36</v>
       </c>
       <c r="H79" s="2" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="I79" s="2" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="J79" s="2" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="80" spans="1:10" ht="409.6">
+    <row r="80" spans="1:10" ht="217" x14ac:dyDescent="0.35">
       <c r="A80" s="2">
         <v>79</v>
       </c>
       <c r="B80" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="C80" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="D80" s="2" t="s">
         <v>332</v>
-      </c>
-      <c r="C80" s="2" t="s">
-        <v>333</v>
-      </c>
-      <c r="D80" s="2" t="s">
-        <v>334</v>
       </c>
       <c r="E80" s="2" t="s">
         <v>22</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="G80" s="2" t="s">
         <v>36</v>
       </c>
       <c r="H80" s="2" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="I80" s="2" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="J80" s="2" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="81" spans="1:10" ht="409.6">
+    <row r="81" spans="1:10" ht="356.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A81" s="2">
         <v>80</v>
       </c>
       <c r="B81" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="C81" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="D81" s="2" t="s">
         <v>338</v>
       </c>
-      <c r="C81" s="2" t="s">
+      <c r="E81" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F81" s="2" t="s">
         <v>339</v>
-      </c>
-      <c r="D81" s="2" t="s">
-        <v>340</v>
-      </c>
-      <c r="E81" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F81" s="2" t="s">
-        <v>341</v>
       </c>
       <c r="G81" s="2" t="s">
         <v>13</v>
       </c>
       <c r="H81" s="2" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="I81" s="2" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="J81" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="82" spans="1:10" ht="409.6">
+    <row r="82" spans="1:10" ht="217" x14ac:dyDescent="0.35">
       <c r="A82" s="2">
         <v>81</v>
       </c>
       <c r="B82" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="C82" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="D82" s="2" t="s">
         <v>344</v>
       </c>
-      <c r="C82" s="2" t="s">
+      <c r="E82" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F82" s="2" t="s">
         <v>345</v>
-      </c>
-      <c r="D82" s="2" t="s">
-        <v>346</v>
-      </c>
-      <c r="E82" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F82" s="2" t="s">
-        <v>347</v>
       </c>
       <c r="G82" s="2" t="s">
         <v>23</v>
       </c>
       <c r="H82" s="2" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="I82" s="2" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="J82" s="2" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="83" spans="1:10" ht="409.6">
+    <row r="83" spans="1:10" ht="310" hidden="1" x14ac:dyDescent="0.35">
       <c r="A83" s="2">
         <v>82</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="D83" s="2" t="s">
         <v>287</v>
@@ -6560,1122 +7331,1118 @@
         <v>12</v>
       </c>
       <c r="F83" s="2" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="G83" s="2" t="s">
         <v>13</v>
       </c>
       <c r="H83" s="2" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="I83" s="2" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="J83" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="84" spans="1:10" ht="409.6">
+    <row r="84" spans="1:10" ht="409.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A84" s="2">
         <v>83</v>
       </c>
       <c r="B84" s="2" t="s">
+        <v>353</v>
+      </c>
+      <c r="C84" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="D84" s="2" t="s">
         <v>355</v>
       </c>
-      <c r="C84" s="2" t="s">
+      <c r="E84" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F84" s="2" t="s">
         <v>356</v>
-      </c>
-      <c r="D84" s="2" t="s">
-        <v>357</v>
-      </c>
-      <c r="E84" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F84" s="2" t="s">
-        <v>358</v>
       </c>
       <c r="G84" s="2" t="s">
         <v>13</v>
       </c>
       <c r="H84" s="2" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="I84" s="2" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="J84" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="85" spans="1:10" ht="409.6">
+    <row r="85" spans="1:10" ht="409.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A85" s="2">
         <v>84</v>
       </c>
       <c r="B85" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="C85" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="D85" s="2" t="s">
         <v>361</v>
       </c>
-      <c r="C85" s="2" t="s">
+      <c r="E85" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F85" s="2" t="s">
         <v>362</v>
-      </c>
-      <c r="D85" s="2" t="s">
-        <v>363</v>
-      </c>
-      <c r="E85" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F85" s="2" t="s">
-        <v>364</v>
       </c>
       <c r="G85" s="2" t="s">
         <v>36</v>
       </c>
       <c r="H85" s="2" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="I85" s="2" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="J85" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="86" spans="1:10" ht="409.6">
+    <row r="86" spans="1:10" ht="279" x14ac:dyDescent="0.35">
       <c r="A86" s="2">
         <v>85</v>
       </c>
       <c r="B86" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="C86" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="D86" s="2" t="s">
         <v>367</v>
       </c>
-      <c r="C86" s="2" t="s">
+      <c r="E86" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F86" s="2" t="s">
         <v>368</v>
-      </c>
-      <c r="D86" s="2" t="s">
-        <v>369</v>
-      </c>
-      <c r="E86" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F86" s="2" t="s">
-        <v>370</v>
       </c>
       <c r="G86" s="2" t="s">
         <v>23</v>
       </c>
       <c r="H86" s="2" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="I86" s="2" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="J86" s="2" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="87" spans="1:10" ht="409.6">
+    <row r="87" spans="1:10" ht="310" hidden="1" x14ac:dyDescent="0.35">
       <c r="A87" s="2">
         <v>86</v>
       </c>
       <c r="B87" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="C87" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="D87" s="2" t="s">
         <v>373</v>
       </c>
-      <c r="C87" s="2" t="s">
+      <c r="E87" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F87" s="2" t="s">
         <v>374</v>
-      </c>
-      <c r="D87" s="2" t="s">
-        <v>375</v>
-      </c>
-      <c r="E87" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F87" s="2" t="s">
-        <v>376</v>
       </c>
       <c r="G87" s="2" t="s">
         <v>13</v>
       </c>
       <c r="H87" s="2" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="I87" s="2" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="J87" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="88" spans="1:10" ht="409.6">
+    <row r="88" spans="1:10" ht="279" x14ac:dyDescent="0.35">
       <c r="A88" s="2">
         <v>87</v>
       </c>
       <c r="B88" s="2" t="s">
+        <v>377</v>
+      </c>
+      <c r="C88" s="2" t="s">
+        <v>378</v>
+      </c>
+      <c r="D88" s="2" t="s">
         <v>379</v>
       </c>
-      <c r="C88" s="2" t="s">
+      <c r="E88" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F88" s="2" t="s">
         <v>380</v>
-      </c>
-      <c r="D88" s="2" t="s">
-        <v>381</v>
-      </c>
-      <c r="E88" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F88" s="2" t="s">
-        <v>382</v>
       </c>
       <c r="G88" s="2" t="s">
         <v>36</v>
       </c>
       <c r="H88" s="2" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="I88" s="2" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="J88" s="2" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="89" spans="1:10" ht="409.6">
+    <row r="89" spans="1:10" ht="279" x14ac:dyDescent="0.35">
       <c r="A89" s="2">
         <v>88</v>
       </c>
       <c r="B89" s="2" t="s">
+        <v>383</v>
+      </c>
+      <c r="C89" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="D89" s="2" t="s">
         <v>385</v>
       </c>
-      <c r="C89" s="2" t="s">
+      <c r="E89" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F89" s="2" t="s">
         <v>386</v>
-      </c>
-      <c r="D89" s="2" t="s">
-        <v>387</v>
-      </c>
-      <c r="E89" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F89" s="2" t="s">
-        <v>388</v>
       </c>
       <c r="G89" s="2" t="s">
         <v>36</v>
       </c>
       <c r="H89" s="2" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="I89" s="2" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="J89" s="2" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="90" spans="1:10" ht="409.6">
+    <row r="90" spans="1:10" ht="409.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A90" s="2">
         <v>89</v>
       </c>
       <c r="B90" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="C90" s="2" t="s">
+        <v>390</v>
+      </c>
+      <c r="D90" s="2" t="s">
         <v>391</v>
       </c>
-      <c r="C90" s="2" t="s">
+      <c r="E90" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F90" s="2" t="s">
         <v>392</v>
-      </c>
-      <c r="D90" s="2" t="s">
-        <v>393</v>
-      </c>
-      <c r="E90" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F90" s="2" t="s">
-        <v>394</v>
       </c>
       <c r="G90" s="2" t="s">
         <v>13</v>
       </c>
       <c r="H90" s="2" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="I90" s="2" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="J90" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="91" spans="1:10" ht="409.6">
+    <row r="91" spans="1:10" ht="217" hidden="1" x14ac:dyDescent="0.35">
       <c r="A91" s="2">
         <v>90</v>
       </c>
       <c r="B91" s="2" t="s">
+        <v>395</v>
+      </c>
+      <c r="C91" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="D91" s="2" t="s">
         <v>397</v>
       </c>
-      <c r="C91" s="2" t="s">
+      <c r="E91" s="2" t="s">
         <v>398</v>
       </c>
-      <c r="D91" s="2" t="s">
+      <c r="F91" s="2" t="s">
         <v>399</v>
-      </c>
-      <c r="E91" s="2" t="s">
-        <v>400</v>
-      </c>
-      <c r="F91" s="2" t="s">
-        <v>401</v>
       </c>
       <c r="G91" s="2" t="s">
         <v>13</v>
       </c>
       <c r="H91" s="2" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="I91" s="2" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="J91" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="92" spans="1:10" ht="409.6">
+    <row r="92" spans="1:10" ht="124" hidden="1" x14ac:dyDescent="0.35">
       <c r="A92" s="2">
         <v>91</v>
       </c>
       <c r="B92" s="2" t="s">
+        <v>402</v>
+      </c>
+      <c r="C92" s="2" t="s">
+        <v>403</v>
+      </c>
+      <c r="D92" s="2" t="s">
         <v>404</v>
-      </c>
-      <c r="C92" s="2" t="s">
-        <v>405</v>
-      </c>
-      <c r="D92" s="2" t="s">
-        <v>406</v>
       </c>
       <c r="E92" s="2" t="s">
         <v>22</v>
       </c>
       <c r="F92" s="2" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="G92" s="2" t="s">
         <v>13</v>
       </c>
       <c r="H92" s="2" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="I92" s="2" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="J92" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="93" spans="1:10" ht="409.6">
+    <row r="93" spans="1:10" ht="139.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A93" s="2">
         <v>92</v>
       </c>
       <c r="B93" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="C93" s="2" t="s">
+        <v>409</v>
+      </c>
+      <c r="D93" s="2" t="s">
         <v>410</v>
-      </c>
-      <c r="C93" s="2" t="s">
-        <v>411</v>
-      </c>
-      <c r="D93" s="2" t="s">
-        <v>412</v>
       </c>
       <c r="E93" s="2" t="s">
         <v>22</v>
       </c>
       <c r="F93" s="2" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="G93" s="2" t="s">
         <v>13</v>
       </c>
       <c r="H93" s="2" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="I93" s="2" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="J93" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="94" spans="1:10" ht="409.6">
+    <row r="94" spans="1:10" ht="108.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A94" s="2">
         <v>93</v>
       </c>
       <c r="B94" s="2" t="s">
+        <v>414</v>
+      </c>
+      <c r="C94" s="2" t="s">
+        <v>415</v>
+      </c>
+      <c r="D94" s="2" t="s">
         <v>416</v>
-      </c>
-      <c r="C94" s="2" t="s">
-        <v>417</v>
-      </c>
-      <c r="D94" s="2" t="s">
-        <v>418</v>
       </c>
       <c r="E94" s="2" t="s">
         <v>22</v>
       </c>
       <c r="F94" s="2" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="G94" s="2" t="s">
         <v>13</v>
       </c>
       <c r="H94" s="2" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="I94" s="2" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="J94" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="95" spans="1:10" ht="409.6">
+    <row r="95" spans="1:10" ht="139.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A95" s="2">
         <v>94</v>
       </c>
       <c r="B95" s="2" t="s">
+        <v>420</v>
+      </c>
+      <c r="C95" s="2" t="s">
+        <v>421</v>
+      </c>
+      <c r="D95" s="2" t="s">
         <v>422</v>
       </c>
-      <c r="C95" s="2" t="s">
+      <c r="E95" s="2" t="s">
         <v>423</v>
       </c>
-      <c r="D95" s="2" t="s">
+      <c r="F95" s="2" t="s">
         <v>424</v>
-      </c>
-      <c r="E95" s="2" t="s">
-        <v>425</v>
-      </c>
-      <c r="F95" s="2" t="s">
-        <v>426</v>
       </c>
       <c r="G95" s="2" t="s">
         <v>13</v>
       </c>
       <c r="H95" s="2" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="I95" s="2" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="J95" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="96" spans="1:10" ht="409.6">
+    <row r="96" spans="1:10" ht="155" hidden="1" x14ac:dyDescent="0.35">
       <c r="A96" s="2">
         <v>95</v>
       </c>
       <c r="B96" s="2" t="s">
+        <v>427</v>
+      </c>
+      <c r="C96" s="2" t="s">
+        <v>428</v>
+      </c>
+      <c r="D96" s="2" t="s">
         <v>429</v>
       </c>
-      <c r="C96" s="2" t="s">
+      <c r="E96" s="2" t="s">
         <v>430</v>
       </c>
-      <c r="D96" s="2" t="s">
+      <c r="F96" s="2" t="s">
         <v>431</v>
-      </c>
-      <c r="E96" s="2" t="s">
-        <v>432</v>
-      </c>
-      <c r="F96" s="2" t="s">
-        <v>433</v>
       </c>
       <c r="G96" s="2" t="s">
         <v>13</v>
       </c>
       <c r="H96" s="2" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="I96" s="2" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="J96" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="97" spans="1:10" ht="409.6">
+    <row r="97" spans="1:10" ht="108.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A97" s="2">
         <v>96</v>
       </c>
       <c r="B97" s="2" t="s">
+        <v>434</v>
+      </c>
+      <c r="C97" s="2" t="s">
+        <v>435</v>
+      </c>
+      <c r="D97" s="2" t="s">
         <v>436</v>
       </c>
-      <c r="C97" s="2" t="s">
+      <c r="E97" s="2" t="s">
         <v>437</v>
       </c>
-      <c r="D97" s="2" t="s">
+      <c r="F97" s="2" t="s">
         <v>438</v>
-      </c>
-      <c r="E97" s="2" t="s">
-        <v>439</v>
-      </c>
-      <c r="F97" s="2" t="s">
-        <v>440</v>
       </c>
       <c r="G97" s="2" t="s">
         <v>13</v>
       </c>
       <c r="H97" s="2" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="I97" s="2" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="J97" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="98" spans="1:10" ht="409.6">
+    <row r="98" spans="1:10" ht="139.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A98" s="2">
         <v>97</v>
       </c>
       <c r="B98" s="2" t="s">
+        <v>441</v>
+      </c>
+      <c r="C98" s="2" t="s">
+        <v>442</v>
+      </c>
+      <c r="D98" s="2" t="s">
         <v>443</v>
       </c>
-      <c r="C98" s="2" t="s">
+      <c r="E98" s="2" t="s">
         <v>444</v>
       </c>
-      <c r="D98" s="2" t="s">
+      <c r="F98" s="2" t="s">
         <v>445</v>
-      </c>
-      <c r="E98" s="2" t="s">
-        <v>446</v>
-      </c>
-      <c r="F98" s="2" t="s">
-        <v>447</v>
       </c>
       <c r="G98" s="2" t="s">
         <v>13</v>
       </c>
       <c r="H98" s="2" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="I98" s="2" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="J98" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="99" spans="1:10" ht="409.6">
+    <row r="99" spans="1:10" ht="93" hidden="1" x14ac:dyDescent="0.35">
       <c r="A99" s="2">
         <v>98</v>
       </c>
       <c r="B99" s="2" t="s">
+        <v>448</v>
+      </c>
+      <c r="C99" s="2" t="s">
+        <v>449</v>
+      </c>
+      <c r="D99" s="2" t="s">
         <v>450</v>
       </c>
-      <c r="C99" s="2" t="s">
+      <c r="E99" s="2" t="s">
+        <v>444</v>
+      </c>
+      <c r="F99" s="2" t="s">
         <v>451</v>
-      </c>
-      <c r="D99" s="2" t="s">
-        <v>452</v>
-      </c>
-      <c r="E99" s="2" t="s">
-        <v>446</v>
-      </c>
-      <c r="F99" s="2" t="s">
-        <v>453</v>
       </c>
       <c r="G99" s="2" t="s">
         <v>13</v>
       </c>
       <c r="H99" s="2" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="I99" s="2" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="J99" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="100" spans="1:10" ht="409.6">
+    <row r="100" spans="1:10" ht="170.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A100" s="2">
         <v>99</v>
       </c>
       <c r="B100" s="2" t="s">
+        <v>454</v>
+      </c>
+      <c r="C100" s="2" t="s">
+        <v>455</v>
+      </c>
+      <c r="D100" s="2" t="s">
         <v>456</v>
       </c>
-      <c r="C100" s="2" t="s">
+      <c r="E100" s="2" t="s">
         <v>457</v>
       </c>
-      <c r="D100" s="2" t="s">
+      <c r="F100" s="2" t="s">
         <v>458</v>
-      </c>
-      <c r="E100" s="2" t="s">
-        <v>459</v>
-      </c>
-      <c r="F100" s="2" t="s">
-        <v>460</v>
       </c>
       <c r="G100" s="2" t="s">
         <v>36</v>
       </c>
       <c r="H100" s="2" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="I100" s="2" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="J100" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="101" spans="1:10" ht="409.6">
+    <row r="101" spans="1:10" ht="124" hidden="1" x14ac:dyDescent="0.35">
       <c r="A101" s="2">
         <v>100</v>
       </c>
       <c r="B101" s="2" t="s">
+        <v>461</v>
+      </c>
+      <c r="C101" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="D101" s="2" t="s">
         <v>463</v>
-      </c>
-      <c r="C101" s="2" t="s">
-        <v>464</v>
-      </c>
-      <c r="D101" s="2" t="s">
-        <v>465</v>
       </c>
       <c r="E101" s="2" t="s">
         <v>22</v>
       </c>
       <c r="F101" s="2" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="G101" s="2" t="s">
         <v>13</v>
       </c>
       <c r="H101" s="2" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="I101" s="2" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="J101" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="102" spans="1:10" ht="409.6">
+    <row r="102" spans="1:10" ht="124" hidden="1" x14ac:dyDescent="0.35">
       <c r="A102" s="2">
         <v>101</v>
       </c>
       <c r="B102" s="2" t="s">
+        <v>467</v>
+      </c>
+      <c r="C102" s="2" t="s">
+        <v>468</v>
+      </c>
+      <c r="D102" s="2" t="s">
+        <v>463</v>
+      </c>
+      <c r="E102" s="2" t="s">
+        <v>430</v>
+      </c>
+      <c r="F102" s="2" t="s">
         <v>469</v>
-      </c>
-      <c r="C102" s="2" t="s">
-        <v>470</v>
-      </c>
-      <c r="D102" s="2" t="s">
-        <v>465</v>
-      </c>
-      <c r="E102" s="2" t="s">
-        <v>432</v>
-      </c>
-      <c r="F102" s="2" t="s">
-        <v>471</v>
       </c>
       <c r="G102" s="2" t="s">
         <v>13</v>
       </c>
       <c r="H102" s="2" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="I102" s="2" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="J102" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="103" spans="1:10" ht="409.6">
+    <row r="103" spans="1:10" ht="170.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A103" s="2">
         <v>102</v>
       </c>
       <c r="B103" s="2" t="s">
+        <v>472</v>
+      </c>
+      <c r="C103" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="D103" s="2" t="s">
         <v>474</v>
       </c>
-      <c r="C103" s="2" t="s">
+      <c r="E103" s="2" t="s">
         <v>475</v>
       </c>
-      <c r="D103" s="2" t="s">
+      <c r="F103" s="2" t="s">
         <v>476</v>
-      </c>
-      <c r="E103" s="2" t="s">
-        <v>477</v>
-      </c>
-      <c r="F103" s="2" t="s">
-        <v>478</v>
       </c>
       <c r="G103" s="2" t="s">
         <v>36</v>
       </c>
       <c r="H103" s="2" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="I103" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="J103" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="104" spans="1:10" ht="409.6">
+    <row r="104" spans="1:10" ht="263.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A104" s="2">
         <v>103</v>
       </c>
       <c r="B104" s="2" t="s">
+        <v>479</v>
+      </c>
+      <c r="C104" s="2" t="s">
+        <v>480</v>
+      </c>
+      <c r="D104" s="2" t="s">
         <v>481</v>
       </c>
-      <c r="C104" s="2" t="s">
+      <c r="E104" s="2" t="s">
         <v>482</v>
       </c>
-      <c r="D104" s="2" t="s">
+      <c r="F104" s="2" t="s">
         <v>483</v>
-      </c>
-      <c r="E104" s="2" t="s">
-        <v>484</v>
-      </c>
-      <c r="F104" s="2" t="s">
-        <v>485</v>
       </c>
       <c r="G104" s="2" t="s">
         <v>36</v>
       </c>
       <c r="H104" s="2" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="I104" s="2" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="J104" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="105" spans="1:10" ht="409.6">
+    <row r="105" spans="1:10" ht="387.5" x14ac:dyDescent="0.35">
       <c r="A105" s="2">
         <v>104</v>
       </c>
       <c r="B105" s="2" t="s">
+        <v>486</v>
+      </c>
+      <c r="C105" s="2" t="s">
+        <v>487</v>
+      </c>
+      <c r="D105" s="2" t="s">
         <v>488</v>
       </c>
-      <c r="C105" s="2" t="s">
+      <c r="E105" s="2" t="s">
         <v>489</v>
       </c>
-      <c r="D105" s="2" t="s">
+      <c r="F105" s="2" t="s">
         <v>490</v>
-      </c>
-      <c r="E105" s="2" t="s">
-        <v>491</v>
-      </c>
-      <c r="F105" s="2" t="s">
-        <v>492</v>
       </c>
       <c r="G105" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="H105" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Two sources of truth for topology. Source A (backend, authoritative): repos.py _topology_for derives repo_topology from repo COUNT (&gt;=3 multi, ==2 split, else single) and _recompute_topology re-writes it on every add/remove repository. Source B (frontend): CreateProject.tsx offers only Single/Multi (2 of the model's 3 values) and posts repo_topology, which perform_create honours - but the first repo add/remove then recomputes and silently overrides the user's pick. Confirmed no backend feature branches on topology=='multi' (drift/api-contract do NOT read it); it is informational (manifest/context only).</t>
-        </is>
-      </c>
-      <c r="I105" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">OPEN - surgical fix (recon 2026-07-24), Option (b), lowest risk: keep the count-derived value as the single source of truth (backend + tests unchanged - many tests assert derived values) and stop the create form presenting a choice it does not honour - drop the topology segmented control from CreateProject.tsx (or relabel it a non-authoritative hint) and widen the 2-value type in types.ts / hooks.ts. Topology then simply follows the repos actually registered. Option (a) - honour the explicit choice and stop auto-deriving - is higher risk (rewrites the derived-value tests, needs the missing 'Split' option added) and is not recommended since nothing branches on the value.</t>
-        </is>
+      <c r="H105" s="2" t="s">
+        <v>815</v>
+      </c>
+      <c r="I105" s="2" t="s">
+        <v>816</v>
       </c>
       <c r="J105" s="2" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="106" spans="1:10" ht="409.6">
+    <row r="106" spans="1:10" ht="409.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A106" s="2">
         <v>105</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>495</v>
+        <v>491</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>496</v>
+        <v>492</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>497</v>
+        <v>493</v>
       </c>
       <c r="E106" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F106" s="2" t="s">
-        <v>498</v>
+        <v>494</v>
       </c>
       <c r="G106" s="2" t="s">
         <v>36</v>
       </c>
       <c r="H106" s="2" t="s">
-        <v>499</v>
+        <v>495</v>
       </c>
       <c r="I106" s="2" t="s">
-        <v>500</v>
+        <v>496</v>
       </c>
       <c r="J106" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="107" spans="1:10" ht="409.6">
+    <row r="107" spans="1:10" ht="294.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A107" s="2">
         <v>106</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>501</v>
+        <v>497</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>502</v>
+        <v>498</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>503</v>
+        <v>499</v>
       </c>
       <c r="E107" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F107" s="2" t="s">
-        <v>504</v>
+        <v>500</v>
       </c>
       <c r="G107" s="2" t="s">
         <v>13</v>
       </c>
       <c r="H107" s="2" t="s">
-        <v>505</v>
+        <v>501</v>
       </c>
       <c r="I107" s="2" t="s">
-        <v>506</v>
+        <v>502</v>
       </c>
       <c r="J107" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="108" spans="1:10" ht="409.6">
+    <row r="108" spans="1:10" ht="409.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A108" s="2">
         <v>107</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>507</v>
+        <v>503</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>508</v>
+        <v>504</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>509</v>
+        <v>505</v>
       </c>
       <c r="E108" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F108" s="2" t="s">
-        <v>510</v>
+        <v>506</v>
       </c>
       <c r="G108" s="2" t="s">
         <v>13</v>
       </c>
       <c r="H108" s="2" t="s">
-        <v>511</v>
+        <v>507</v>
       </c>
       <c r="I108" s="2" t="s">
-        <v>512</v>
+        <v>508</v>
       </c>
       <c r="J108" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="109" spans="1:10" ht="330">
+    <row r="109" spans="1:10" ht="310" hidden="1" x14ac:dyDescent="0.35">
       <c r="A109" s="2">
         <v>108</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>513</v>
+        <v>509</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>514</v>
+        <v>510</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>515</v>
+        <v>511</v>
       </c>
       <c r="E109" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F109" s="2" t="s">
-        <v>516</v>
+        <v>512</v>
       </c>
       <c r="G109" s="2" t="s">
         <v>36</v>
       </c>
       <c r="H109" s="2" t="s">
-        <v>517</v>
+        <v>513</v>
       </c>
       <c r="I109" s="2" t="s">
-        <v>518</v>
+        <v>514</v>
       </c>
       <c r="J109" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="110" spans="1:10" ht="380.1">
+    <row r="110" spans="1:10" ht="409.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A110" s="2">
         <v>109</v>
       </c>
       <c r="B110" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="C110" s="2" t="s">
+        <v>516</v>
+      </c>
+      <c r="D110" s="2" t="s">
+        <v>517</v>
+      </c>
+      <c r="E110" s="2" t="s">
+        <v>518</v>
+      </c>
+      <c r="F110" s="2" t="s">
         <v>519</v>
-      </c>
-      <c r="C110" s="2" t="s">
-        <v>520</v>
-      </c>
-      <c r="D110" s="2" t="s">
-        <v>521</v>
-      </c>
-      <c r="E110" s="2" t="s">
-        <v>522</v>
-      </c>
-      <c r="F110" s="2" t="s">
-        <v>523</v>
       </c>
       <c r="G110" s="2" t="s">
         <v>13</v>
       </c>
       <c r="H110" s="2" t="s">
-        <v>524</v>
+        <v>520</v>
       </c>
       <c r="I110" s="2" t="s">
-        <v>525</v>
+        <v>521</v>
       </c>
       <c r="J110" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="111" spans="1:10" ht="380.1">
+    <row r="111" spans="1:10" ht="409.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A111" s="2">
         <v>110</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>526</v>
+        <v>522</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>527</v>
+        <v>523</v>
       </c>
       <c r="D111" s="2" t="s">
-        <v>528</v>
+        <v>524</v>
       </c>
       <c r="E111" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F111" s="2" t="s">
-        <v>529</v>
+        <v>525</v>
       </c>
       <c r="G111" s="2" t="s">
         <v>13</v>
       </c>
       <c r="H111" s="2" t="s">
-        <v>530</v>
+        <v>526</v>
       </c>
       <c r="I111" s="2" t="s">
-        <v>531</v>
+        <v>527</v>
       </c>
       <c r="J111" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="112" spans="1:10" ht="380.1">
+    <row r="112" spans="1:10" ht="409.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A112" s="2">
         <v>111</v>
       </c>
       <c r="B112" s="2" t="s">
+        <v>528</v>
+      </c>
+      <c r="C112" s="2" t="s">
+        <v>529</v>
+      </c>
+      <c r="D112" s="2" t="s">
+        <v>530</v>
+      </c>
+      <c r="E112" s="2" t="s">
+        <v>531</v>
+      </c>
+      <c r="F112" s="2" t="s">
         <v>532</v>
-      </c>
-      <c r="C112" s="2" t="s">
-        <v>533</v>
-      </c>
-      <c r="D112" s="2" t="s">
-        <v>534</v>
-      </c>
-      <c r="E112" s="2" t="s">
-        <v>535</v>
-      </c>
-      <c r="F112" s="2" t="s">
-        <v>536</v>
       </c>
       <c r="G112" s="2" t="s">
         <v>13</v>
       </c>
       <c r="H112" s="2" t="s">
-        <v>537</v>
+        <v>533</v>
       </c>
       <c r="I112" s="2" t="s">
-        <v>538</v>
+        <v>534</v>
       </c>
       <c r="J112" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="113" spans="1:10" ht="380.1">
+    <row r="113" spans="1:10" ht="409.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A113" s="2">
         <v>112</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>539</v>
+        <v>535</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>540</v>
+        <v>536</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>541</v>
+        <v>537</v>
       </c>
       <c r="E113" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F113" s="2" t="s">
-        <v>542</v>
+        <v>538</v>
       </c>
       <c r="G113" s="2" t="s">
         <v>13</v>
       </c>
       <c r="H113" s="2" t="s">
-        <v>543</v>
+        <v>539</v>
       </c>
       <c r="I113" s="2" t="s">
-        <v>544</v>
+        <v>540</v>
       </c>
       <c r="J113" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="114" spans="1:10" ht="380.1">
+    <row r="114" spans="1:10" ht="248" hidden="1" x14ac:dyDescent="0.35">
       <c r="A114" s="2">
         <v>113</v>
       </c>
       <c r="B114" s="2" t="s">
+        <v>541</v>
+      </c>
+      <c r="C114" s="2" t="s">
+        <v>542</v>
+      </c>
+      <c r="D114" s="2" t="s">
+        <v>543</v>
+      </c>
+      <c r="E114" s="2" t="s">
+        <v>544</v>
+      </c>
+      <c r="F114" s="2" t="s">
         <v>545</v>
-      </c>
-      <c r="C114" s="2" t="s">
-        <v>546</v>
-      </c>
-      <c r="D114" s="2" t="s">
-        <v>547</v>
-      </c>
-      <c r="E114" s="2" t="s">
-        <v>548</v>
-      </c>
-      <c r="F114" s="2" t="s">
-        <v>549</v>
       </c>
       <c r="G114" s="2" t="s">
         <v>36</v>
       </c>
       <c r="H114" s="2" t="s">
-        <v>550</v>
+        <v>546</v>
       </c>
       <c r="I114" s="2" t="s">
-        <v>551</v>
+        <v>547</v>
       </c>
       <c r="J114" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="115" spans="1:10" ht="380.1">
+    <row r="115" spans="1:10" ht="409.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A115" s="2">
         <v>114</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>553</v>
+        <v>549</v>
       </c>
       <c r="D115" s="2" t="s">
-        <v>554</v>
+        <v>550</v>
       </c>
       <c r="E115" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F115" s="2" t="s">
-        <v>555</v>
+        <v>551</v>
       </c>
       <c r="G115" s="2" t="s">
         <v>13</v>
       </c>
       <c r="H115" s="2" t="s">
-        <v>556</v>
+        <v>552</v>
       </c>
       <c r="I115" s="2" t="s">
-        <v>557</v>
+        <v>553</v>
       </c>
       <c r="J115" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="116" spans="1:10" ht="380.1">
+    <row r="116" spans="1:10" ht="409.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A116" s="2">
         <v>115</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>558</v>
+        <v>554</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>559</v>
+        <v>555</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>560</v>
+        <v>556</v>
       </c>
       <c r="E116" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F116" s="2" t="s">
-        <v>561</v>
+        <v>557</v>
       </c>
       <c r="G116" s="2" t="s">
         <v>13</v>
       </c>
       <c r="H116" s="2" t="s">
-        <v>562</v>
+        <v>558</v>
       </c>
       <c r="I116" s="2" t="s">
-        <v>563</v>
+        <v>559</v>
       </c>
       <c r="J116" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="117" spans="1:10" ht="380.1">
+    <row r="117" spans="1:10" ht="409.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A117" s="2">
         <v>116</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>564</v>
+        <v>560</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>565</v>
+        <v>561</v>
       </c>
       <c r="D117" s="2" t="s">
-        <v>566</v>
+        <v>562</v>
       </c>
       <c r="E117" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F117" s="2" t="s">
-        <v>567</v>
+        <v>563</v>
       </c>
       <c r="G117" s="2" t="s">
         <v>13</v>
       </c>
       <c r="H117" s="2" t="s">
-        <v>568</v>
+        <v>564</v>
       </c>
       <c r="I117" s="2" t="s">
-        <v>569</v>
+        <v>565</v>
       </c>
       <c r="J117" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="118" spans="1:10" ht="194.25">
+    <row r="118" spans="1:10" ht="372" x14ac:dyDescent="0.35">
       <c r="A118" s="2">
         <v>117</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>570</v>
+        <v>566</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>571</v>
+        <v>567</v>
       </c>
       <c r="E118" s="2" t="s">
         <v>12</v>
@@ -7686,26 +8453,22 @@
       <c r="G118" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="H118" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The board bucket is computed in WorkItemsBoard.tsx byPhase from item.current_phase, which the backend derives (WorkItemViewSet._card_fields) as the latest Run's agent-spec key. Freshly fanned-out Task Breakdown items are state='proposed' with NO run yet, so current_phase='' - and byPhase falls phase-less items back to columns[0]. In the default board columns[0] is 01_ideation (Ideation column); when filtered to Tasks the columns switch to BUILD_COLUMNS whose first entry is 'implementation' (Implementation column). Both reported symptoms are the same defect: not-yet-run items blindly land in the first column.</t>
-        </is>
-      </c>
-      <c r="I118" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">OPEN - surgical fix (recon 2026-07-24), FRONTEND-ONLY (WorkItemsBoard.tsx): add an explicit 'Backlog / Not started' column to PHASE_COLUMNS and BUILD_COLUMNS and, in byPhase, route items with an empty current_phase (or state=='proposed') to it instead of defaulting to columns[0]. No backend change. Update phases.test.ts / lifecycle.test.tsx if they assert on the column set/counts. Optional backend alternative: have _card_fields set current_phase to the producing phase for un-run items - larger semantic change, not needed.</t>
-        </is>
+      <c r="H118" s="2" t="s">
+        <v>817</v>
+      </c>
+      <c r="I118" s="2" t="s">
+        <v>818</v>
       </c>
       <c r="J118" s="2" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="119" spans="1:10" ht="409.6">
+    <row r="119" spans="1:10" ht="409.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A119" s="2">
         <v>118</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>572</v>
+        <v>568</v>
       </c>
       <c r="D119" s="2" t="s">
         <v>93</v>
@@ -7719,25 +8482,22 @@
       <c r="G119" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="I119" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">FIXED (2026-07-15). agents/06_task_breakdown/agent.md: added a 'Writing standard' requiring every Epic/Story/Task Description + Acceptance Criterion to be plain-language-with-technical-nuance, detailed and self-contained enough that a developer can implement by reading it ALONE (behaviour, inputs/outputs, states, edge cases), with concrete hand-verifiable acceptance criteria and no bare placeholders; modelled the standard in all three template placeholders. Improvement flows to the Work Items board + artifact previews automatically. Test: test_agents_migration.test_task_breakdown_descriptions_and_ac_are_humanized. Per team decision the blast radius today was 06 only; the SAME defect in 02/09/00c/04/03/10 is logged as S.No 121-126 (register-condition per audience: technical-humanized for testing/security, plain+nuance for the rest) and NOT fixed this session.
-FOLLOW-UP COMPLETION (2026-07-24, verified live by the team). The 2026-07-15 fix set the INSTRUCTION but left the technical exemplars in place, and the model imitates exemplars more than rules — so Epics read well (they already had good plain-language examples) but Tasks still came out too technical. Completed the fix at the EXAMPLE level: agents/06_task_breakdown/agent.md now carries worked Story AND Task exemplars that OPEN with a one-sentence plain-language statement of intent (what it delivers and why) BEFORE the technical detail, with concrete given/when/then acceptance criteria; added an explicit 'lead with plain-language intent' requirement for both Stories and Tasks; and rewrote the terse counter-examples (the endpoint-string title, the venv/env-file acceptance criteria) so nothing pulls the output back to terse. Platform side: backend/manifest/composer.py raised the Current Work Item token budget 300-&gt;650 so long task descriptions reach the implementation agent untruncated (avg 1,263 / max 1,835 chars already exceeded the old ~1,200-char cap). Strengthened the test to assert the intent-lead + the worked exemplars. Committed f27455d (pushed to develop). Team re-ran Task Breakdown on tenant 7828e953 and confirmed a great improvement vs the old artifacts. Scope decision this session was Tasks + Stories; siblings S.No 121-126 (agents 02/09/00c/04/03/10) remain separately Open.</t>
-        </is>
+      <c r="I119" s="2" t="s">
+        <v>819</v>
       </c>
       <c r="J119" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="120" spans="1:10" ht="113.25">
+    <row r="120" spans="1:10" ht="356.5" x14ac:dyDescent="0.35">
       <c r="A120" s="2">
         <v>119</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>574</v>
+        <v>569</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>571</v>
+        <v>567</v>
       </c>
       <c r="E120" s="2" t="s">
         <v>22</v>
@@ -7748,26 +8508,22 @@
       <c r="G120" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="H120" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WorkItemDetail.tsx routes epic AND story to WorkItemEpic; only the leaf WorkItemTask renders the navigable 'Related work items' child-link panel (maps lifecycle.children to /work-items/{id} links). WorkItemEpic shows children only as a raw count ('Children: N'), never as links - so an epic shows a number not clickable stories, and a story (also routed to WorkItemEpic) shows a number not clickable tasks. The lifecycle endpoint already returns the DIRECT children at each level, so the epic-&gt;story-&gt;task data is present; the parent view just doesn't render it as navigation.</t>
-        </is>
-      </c>
-      <c r="I120" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">OPEN - surgical fix (recon 2026-07-24), FRONTEND-ONLY, additive: add a 'Related work items' child-link panel to WorkItemEpic.tsx (mirror the one in WorkItemTask.tsx) that renders lifecycle.children as /work-items/{id} links. Each level then lists its own direct children, giving epic-&gt;story-&gt;task drill navigation. Low risk (additive UI); check WorkItemEpicGallery / lifecycle.test.tsx expectations. Optional: fix the child rows' mislabelled phase (views.py emits c.feature_stream as 'phase' - same class as the row-50 feature-stream/phase fix).</t>
-        </is>
+      <c r="H120" s="2" t="s">
+        <v>820</v>
+      </c>
+      <c r="I120" s="2" t="s">
+        <v>821</v>
       </c>
       <c r="J120" s="2" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="121" spans="1:10" ht="409.6">
+    <row r="121" spans="1:10" ht="409.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A121" s="2">
         <v>120</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>575</v>
+        <v>570</v>
       </c>
       <c r="D121" s="2" t="s">
         <v>93</v>
@@ -7782,24 +8538,24 @@
         <v>13</v>
       </c>
       <c r="I121" s="2" t="s">
-        <v>576</v>
+        <v>571</v>
       </c>
       <c r="J121" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="122" spans="1:10" ht="380.1">
+    <row r="122" spans="1:10" ht="217" x14ac:dyDescent="0.35">
       <c r="A122" s="2" t="s">
-        <v>577</v>
+        <v>572</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>578</v>
+        <v>573</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>579</v>
+        <v>574</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>580</v>
+        <v>575</v>
       </c>
       <c r="E122" s="2" t="s">
         <v>12</v>
@@ -7808,27 +8564,27 @@
         <v>13</v>
       </c>
       <c r="H122" s="2" t="s">
-        <v>581</v>
+        <v>576</v>
       </c>
       <c r="I122" s="2" t="s">
-        <v>582</v>
+        <v>577</v>
       </c>
       <c r="J122" s="2" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="123" spans="1:10" ht="380.1">
+    <row r="123" spans="1:10" ht="217" x14ac:dyDescent="0.35">
       <c r="A123" s="2" t="s">
-        <v>583</v>
+        <v>578</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>584</v>
+        <v>579</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>585</v>
+        <v>580</v>
       </c>
       <c r="D123" s="2" t="s">
-        <v>586</v>
+        <v>581</v>
       </c>
       <c r="E123" s="2" t="s">
         <v>12</v>
@@ -7837,27 +8593,27 @@
         <v>13</v>
       </c>
       <c r="H123" s="2" t="s">
-        <v>587</v>
+        <v>582</v>
       </c>
       <c r="I123" s="2" t="s">
-        <v>588</v>
+        <v>583</v>
       </c>
       <c r="J123" s="2" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="124" spans="1:10" ht="380.1">
+    <row r="124" spans="1:10" ht="186" x14ac:dyDescent="0.35">
       <c r="A124" s="2" t="s">
-        <v>589</v>
+        <v>584</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>590</v>
+        <v>585</v>
       </c>
       <c r="C124" s="2" t="s">
-        <v>591</v>
+        <v>586</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>592</v>
+        <v>587</v>
       </c>
       <c r="E124" s="2" t="s">
         <v>12</v>
@@ -7866,27 +8622,27 @@
         <v>36</v>
       </c>
       <c r="H124" s="2" t="s">
-        <v>593</v>
+        <v>588</v>
       </c>
       <c r="I124" s="2" t="s">
-        <v>594</v>
+        <v>589</v>
       </c>
       <c r="J124" s="2" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="125" spans="1:10" ht="380.1">
+    <row r="125" spans="1:10" ht="217" x14ac:dyDescent="0.35">
       <c r="A125" s="2" t="s">
-        <v>595</v>
+        <v>590</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>596</v>
+        <v>591</v>
       </c>
       <c r="C125" s="2" t="s">
-        <v>591</v>
+        <v>586</v>
       </c>
       <c r="D125" s="2" t="s">
-        <v>597</v>
+        <v>592</v>
       </c>
       <c r="E125" s="2" t="s">
         <v>12</v>
@@ -7895,27 +8651,27 @@
         <v>36</v>
       </c>
       <c r="H125" s="2" t="s">
-        <v>598</v>
+        <v>593</v>
       </c>
       <c r="I125" s="2" t="s">
-        <v>599</v>
+        <v>594</v>
       </c>
       <c r="J125" s="2" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="126" spans="1:10" ht="380.1">
+    <row r="126" spans="1:10" ht="124" x14ac:dyDescent="0.35">
       <c r="A126" s="2" t="s">
-        <v>600</v>
+        <v>595</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>601</v>
+        <v>596</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>602</v>
+        <v>597</v>
       </c>
       <c r="D126" s="2" t="s">
-        <v>603</v>
+        <v>598</v>
       </c>
       <c r="E126" s="2" t="s">
         <v>12</v>
@@ -7924,27 +8680,27 @@
         <v>36</v>
       </c>
       <c r="H126" s="2" t="s">
-        <v>604</v>
+        <v>599</v>
       </c>
       <c r="I126" s="2" t="s">
-        <v>605</v>
+        <v>600</v>
       </c>
       <c r="J126" s="2" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="127" spans="1:10" ht="380.1">
+    <row r="127" spans="1:10" ht="186" x14ac:dyDescent="0.35">
       <c r="A127" s="2" t="s">
-        <v>606</v>
+        <v>601</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>607</v>
+        <v>602</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>608</v>
+        <v>603</v>
       </c>
       <c r="D127" s="2" t="s">
-        <v>609</v>
+        <v>604</v>
       </c>
       <c r="E127" s="2" t="s">
         <v>12</v>
@@ -7953,670 +8709,666 @@
         <v>36</v>
       </c>
       <c r="H127" s="2" t="s">
-        <v>610</v>
+        <v>605</v>
       </c>
       <c r="I127" s="2" t="s">
-        <v>611</v>
+        <v>606</v>
       </c>
       <c r="J127" s="2" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="128" spans="1:10" ht="409.6" customHeight="1">
+    <row r="128" spans="1:10" ht="409.6" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A128" s="2">
         <v>127</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>612</v>
+        <v>607</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>613</v>
+        <v>608</v>
       </c>
       <c r="D128" s="2" t="s">
-        <v>614</v>
+        <v>609</v>
       </c>
       <c r="E128" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F128" s="2" t="s">
-        <v>615</v>
+        <v>610</v>
       </c>
       <c r="G128" s="2" t="s">
         <v>13</v>
       </c>
       <c r="H128" s="2" t="s">
-        <v>616</v>
+        <v>611</v>
       </c>
       <c r="I128" s="2" t="s">
-        <v>617</v>
+        <v>612</v>
       </c>
       <c r="J128" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="129" spans="1:10" ht="409.6" customHeight="1">
+    <row r="129" spans="1:10" ht="409.6" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A129" s="2">
         <v>128</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>618</v>
+        <v>613</v>
       </c>
       <c r="C129" s="2" t="s">
-        <v>619</v>
+        <v>614</v>
       </c>
       <c r="D129" s="2" t="s">
-        <v>620</v>
+        <v>615</v>
       </c>
       <c r="E129" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F129" s="2" t="s">
-        <v>621</v>
+        <v>616</v>
       </c>
       <c r="G129" s="2" t="s">
         <v>13</v>
       </c>
       <c r="H129" s="2" t="s">
-        <v>622</v>
+        <v>617</v>
       </c>
       <c r="I129" s="2" t="s">
-        <v>623</v>
+        <v>618</v>
       </c>
       <c r="J129" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="130" spans="1:10" ht="409.6" customHeight="1">
+    <row r="130" spans="1:10" ht="409.6" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A130" s="2">
         <v>129</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>624</v>
+        <v>619</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>625</v>
+        <v>620</v>
       </c>
       <c r="D130" s="2" t="s">
-        <v>626</v>
+        <v>621</v>
       </c>
       <c r="E130" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F130" s="2" t="s">
-        <v>627</v>
+        <v>622</v>
       </c>
       <c r="G130" s="2" t="s">
         <v>13</v>
       </c>
       <c r="H130" s="2" t="s">
-        <v>628</v>
+        <v>623</v>
       </c>
       <c r="I130" s="2" t="s">
-        <v>629</v>
+        <v>624</v>
       </c>
       <c r="J130" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="131" spans="1:10" ht="409.6" customHeight="1">
+    <row r="131" spans="1:10" ht="409.6" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A131" s="2">
         <v>130</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>630</v>
+        <v>625</v>
       </c>
       <c r="C131" s="2" t="s">
-        <v>631</v>
+        <v>626</v>
       </c>
       <c r="D131" s="2" t="s">
-        <v>632</v>
+        <v>627</v>
       </c>
       <c r="E131" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F131" s="2" t="s">
-        <v>633</v>
+        <v>628</v>
       </c>
       <c r="G131" s="2" t="s">
         <v>36</v>
       </c>
       <c r="H131" s="2" t="s">
-        <v>634</v>
+        <v>629</v>
       </c>
       <c r="I131" s="2" t="s">
-        <v>635</v>
+        <v>630</v>
       </c>
       <c r="J131" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="132" spans="1:10" ht="409.6" customHeight="1">
+    <row r="132" spans="1:10" ht="409.6" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A132" s="2">
         <v>131</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>636</v>
+        <v>631</v>
       </c>
       <c r="C132" s="2" t="s">
-        <v>637</v>
+        <v>632</v>
       </c>
       <c r="D132" s="2" t="s">
-        <v>638</v>
+        <v>633</v>
       </c>
       <c r="E132" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F132" s="2" t="s">
-        <v>639</v>
+        <v>634</v>
       </c>
       <c r="G132" s="2" t="s">
         <v>36</v>
       </c>
       <c r="H132" s="2" t="s">
-        <v>640</v>
+        <v>635</v>
       </c>
       <c r="I132" s="2" t="s">
-        <v>641</v>
+        <v>636</v>
       </c>
       <c r="J132" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="133" spans="1:10" ht="409.6" customHeight="1">
+    <row r="133" spans="1:10" ht="409.6" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A133" s="2">
         <v>132</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>642</v>
+        <v>637</v>
       </c>
       <c r="C133" s="2" t="s">
-        <v>643</v>
+        <v>638</v>
       </c>
       <c r="D133" s="2" t="s">
-        <v>644</v>
+        <v>639</v>
       </c>
       <c r="E133" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F133" s="2" t="s">
-        <v>645</v>
+        <v>640</v>
       </c>
       <c r="G133" s="2" t="s">
         <v>23</v>
       </c>
       <c r="H133" s="2" t="s">
-        <v>646</v>
+        <v>641</v>
       </c>
       <c r="I133" s="2" t="s">
-        <v>647</v>
+        <v>642</v>
       </c>
       <c r="J133" s="2" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="134" spans="1:10" ht="409.6" customHeight="1">
+    <row r="134" spans="1:10" ht="409.6" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A134" s="2">
         <v>133</v>
       </c>
       <c r="B134" s="2" t="s">
-        <v>648</v>
+        <v>643</v>
       </c>
       <c r="C134" s="2" t="s">
-        <v>649</v>
+        <v>644</v>
       </c>
       <c r="D134" s="2" t="s">
-        <v>650</v>
+        <v>645</v>
       </c>
       <c r="E134" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F134" s="2" t="s">
-        <v>639</v>
+        <v>634</v>
       </c>
       <c r="G134" s="2" t="s">
         <v>13</v>
       </c>
       <c r="H134" s="2" t="s">
-        <v>651</v>
+        <v>646</v>
       </c>
       <c r="I134" s="2" t="s">
-        <v>652</v>
+        <v>647</v>
       </c>
       <c r="J134" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="135" spans="1:10" ht="409.6" customHeight="1">
+    <row r="135" spans="1:10" ht="409.6" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A135" s="2">
         <v>134</v>
       </c>
       <c r="B135" s="2" t="s">
-        <v>653</v>
+        <v>648</v>
       </c>
       <c r="C135" s="2" t="s">
-        <v>654</v>
+        <v>649</v>
       </c>
       <c r="D135" s="2" t="s">
-        <v>655</v>
+        <v>650</v>
       </c>
       <c r="E135" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F135" s="2" t="s">
-        <v>639</v>
+        <v>634</v>
       </c>
       <c r="G135" s="2" t="s">
         <v>13</v>
       </c>
       <c r="H135" s="2" t="s">
-        <v>656</v>
+        <v>651</v>
       </c>
       <c r="I135" s="2" t="s">
-        <v>657</v>
+        <v>652</v>
       </c>
       <c r="J135" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="136" spans="1:10" ht="409.6" customHeight="1">
+    <row r="136" spans="1:10" ht="409.6" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A136" s="2">
         <v>135</v>
       </c>
       <c r="B136" s="2" t="s">
-        <v>658</v>
+        <v>653</v>
       </c>
       <c r="C136" s="2" t="s">
-        <v>659</v>
+        <v>654</v>
       </c>
       <c r="D136" s="2" t="s">
-        <v>660</v>
+        <v>655</v>
       </c>
       <c r="E136" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F136" s="2" t="s">
-        <v>639</v>
+        <v>634</v>
       </c>
       <c r="G136" s="2" t="s">
         <v>36</v>
       </c>
       <c r="H136" s="2" t="s">
-        <v>661</v>
+        <v>656</v>
       </c>
       <c r="I136" s="2" t="s">
-        <v>662</v>
+        <v>657</v>
       </c>
       <c r="J136" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="137" spans="1:10" ht="409.6" customHeight="1">
+    <row r="137" spans="1:10" ht="409.6" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A137" s="2">
         <v>136</v>
       </c>
       <c r="B137" s="2" t="s">
-        <v>663</v>
+        <v>658</v>
       </c>
       <c r="C137" s="2" t="s">
-        <v>664</v>
+        <v>659</v>
       </c>
       <c r="D137" s="2" t="s">
-        <v>614</v>
+        <v>609</v>
       </c>
       <c r="E137" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F137" s="2" t="s">
-        <v>639</v>
+        <v>634</v>
       </c>
       <c r="G137" s="2" t="s">
         <v>13</v>
       </c>
       <c r="H137" s="2" t="s">
-        <v>665</v>
+        <v>660</v>
       </c>
       <c r="I137" s="2" t="s">
-        <v>666</v>
+        <v>661</v>
       </c>
       <c r="J137" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="138" spans="1:10" ht="409.6" customHeight="1">
+    <row r="138" spans="1:10" ht="409.6" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A138" s="2">
         <v>137</v>
       </c>
       <c r="B138" s="2" t="s">
-        <v>667</v>
+        <v>662</v>
       </c>
       <c r="C138" s="2" t="s">
-        <v>668</v>
+        <v>663</v>
       </c>
       <c r="D138" s="2" t="s">
-        <v>669</v>
+        <v>664</v>
       </c>
       <c r="E138" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F138" s="2" t="s">
-        <v>639</v>
+        <v>634</v>
       </c>
       <c r="G138" s="2" t="s">
         <v>36</v>
       </c>
       <c r="H138" s="2" t="s">
-        <v>670</v>
+        <v>665</v>
       </c>
       <c r="I138" s="2" t="s">
-        <v>671</v>
+        <v>666</v>
       </c>
       <c r="J138" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="139" spans="1:10" ht="409.6" customHeight="1">
+    <row r="139" spans="1:10" ht="409.6" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A139" s="2">
         <v>138</v>
       </c>
       <c r="B139" s="2" t="s">
-        <v>672</v>
+        <v>667</v>
       </c>
       <c r="C139" s="2" t="s">
-        <v>673</v>
+        <v>668</v>
       </c>
       <c r="D139" s="2" t="s">
-        <v>674</v>
+        <v>669</v>
       </c>
       <c r="E139" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F139" s="2" t="s">
-        <v>675</v>
+        <v>670</v>
       </c>
       <c r="G139" s="2" t="s">
         <v>36</v>
       </c>
       <c r="H139" s="2" t="s">
-        <v>676</v>
+        <v>671</v>
       </c>
       <c r="I139" s="2" t="s">
-        <v>677</v>
+        <v>672</v>
       </c>
       <c r="J139" s="2" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="140" spans="1:10" ht="409.6" customHeight="1">
+    <row r="140" spans="1:10" ht="409.6" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A140" s="2">
         <v>139</v>
       </c>
       <c r="B140" s="2" t="s">
-        <v>678</v>
+        <v>673</v>
       </c>
       <c r="C140" s="2" t="s">
-        <v>679</v>
+        <v>674</v>
       </c>
       <c r="D140" s="2" t="s">
-        <v>680</v>
+        <v>675</v>
       </c>
       <c r="E140" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F140" s="2" t="s">
-        <v>639</v>
+        <v>634</v>
       </c>
       <c r="G140" s="2" t="s">
         <v>13</v>
       </c>
       <c r="H140" s="2" t="s">
-        <v>681</v>
+        <v>676</v>
       </c>
       <c r="I140" s="2" t="s">
-        <v>682</v>
+        <v>677</v>
       </c>
       <c r="J140" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="141" spans="1:10">
+    <row r="141" spans="1:10" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A141" s="2">
         <v>140</v>
       </c>
       <c r="B141" s="2" t="s">
-        <v>683</v>
+        <v>678</v>
       </c>
       <c r="C141" s="2" t="s">
-        <v>684</v>
+        <v>679</v>
       </c>
       <c r="D141" s="2" t="s">
-        <v>685</v>
+        <v>680</v>
       </c>
       <c r="E141" s="2" t="s">
         <v>22</v>
       </c>
       <c r="F141" s="2" t="s">
-        <v>686</v>
+        <v>681</v>
       </c>
       <c r="G141" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="H141" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WorkItem.state is read-only on the API (excluded from WorkItemPatchSerializer, read_only on the read serializer) and is mutated ONLY by the orchestrator (successful build+merge / gate / reject / takeover). No human-facing transition endpoint exists; the frontend offers only Retry / Trigger phase / manual takeover (sets takeover_flag, not state). The MCP transition_work_item allows any-&gt;any but is unexposed to users, and there is no terminal state other than 'done' to mark a redundant/abandoned item.</t>
-        </is>
-      </c>
-      <c r="I141" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">OPEN - surgical fix (recon 2026-07-24): add a GATED, AUDITED human-transition endpoint on WorkItemViewSet (@action 'transition') - role-checked (reuse resolve_actor + the gate-role pattern), accepting only an ALLOWLISTED set of human transitions (NOT the MCP any-&gt;any), and writing a ledger Event. Surface 'Mark done / Close as redundant / Skip' on the Work Items board + task page. Add a terminal CANCELLED (optionally CLOSED) value to WorkItem.State via a small migration so human-closed stays distinct from build-completed 'done'; audit every state-mapping site (frontend statusLabel, board columns, lifecycle rail run_status_to_node_state) when adding the value. The migration is the only non-trivial part; the orchestrator keeps its own unrestricted transition path. Related S.No 76.</t>
-        </is>
+      <c r="H141" s="2" t="s">
+        <v>822</v>
+      </c>
+      <c r="I141" s="2" t="s">
+        <v>823</v>
       </c>
       <c r="J141" s="2" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="142" spans="1:10">
+    <row r="142" spans="1:10" ht="409.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A142" s="2">
         <v>141</v>
       </c>
       <c r="B142" s="2" t="s">
-        <v>689</v>
+        <v>682</v>
       </c>
       <c r="C142" s="2" t="s">
-        <v>690</v>
+        <v>683</v>
       </c>
       <c r="D142" s="2" t="s">
-        <v>691</v>
+        <v>684</v>
       </c>
       <c r="E142" s="2" t="s">
         <v>22</v>
       </c>
       <c r="F142" s="2" t="s">
-        <v>692</v>
+        <v>685</v>
       </c>
       <c r="G142" s="2" t="s">
         <v>36</v>
       </c>
       <c r="H142" s="2" t="s">
-        <v>693</v>
+        <v>686</v>
       </c>
       <c r="I142" s="2" t="s">
-        <v>694</v>
+        <v>687</v>
       </c>
       <c r="J142" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="143" spans="1:10">
+    <row r="143" spans="1:10" ht="409.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A143" s="2">
         <v>142</v>
       </c>
       <c r="B143" s="2" t="s">
-        <v>695</v>
+        <v>688</v>
       </c>
       <c r="C143" s="2" t="s">
-        <v>696</v>
+        <v>689</v>
       </c>
       <c r="D143" s="2" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="E143" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F143" s="2" t="s">
-        <v>639</v>
+        <v>634</v>
       </c>
       <c r="G143" s="2" t="s">
         <v>36</v>
       </c>
       <c r="H143" s="2" t="s">
-        <v>697</v>
+        <v>690</v>
       </c>
       <c r="I143" s="2" t="s">
-        <v>698</v>
+        <v>691</v>
       </c>
       <c r="J143" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="144" spans="1:10">
+    <row r="144" spans="1:10" ht="341" hidden="1" x14ac:dyDescent="0.35">
       <c r="A144" s="2">
         <v>143</v>
       </c>
       <c r="B144" s="2" t="s">
-        <v>699</v>
+        <v>692</v>
       </c>
       <c r="C144" s="2" t="s">
-        <v>700</v>
+        <v>693</v>
       </c>
       <c r="D144" s="2" t="s">
-        <v>701</v>
+        <v>694</v>
       </c>
       <c r="E144" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F144" s="2" t="s">
-        <v>639</v>
+        <v>634</v>
       </c>
       <c r="G144" s="2" t="s">
         <v>36</v>
       </c>
       <c r="H144" s="2" t="s">
-        <v>702</v>
+        <v>695</v>
       </c>
       <c r="I144" s="2" t="s">
-        <v>703</v>
+        <v>696</v>
       </c>
       <c r="J144" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="145" spans="1:10" ht="409.6" customHeight="1">
+    <row r="145" spans="1:10" ht="409.6" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A145" s="2">
         <v>144</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>704</v>
+        <v>697</v>
       </c>
       <c r="C145" s="2" t="s">
-        <v>705</v>
+        <v>698</v>
       </c>
       <c r="D145" s="2" t="s">
-        <v>632</v>
+        <v>627</v>
       </c>
       <c r="E145" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F145" s="2" t="s">
-        <v>706</v>
+        <v>699</v>
       </c>
       <c r="G145" s="2" t="s">
         <v>13</v>
       </c>
       <c r="H145" s="2" t="s">
-        <v>707</v>
+        <v>700</v>
       </c>
       <c r="I145" s="2" t="s">
-        <v>708</v>
+        <v>701</v>
       </c>
       <c r="J145" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="146" spans="1:10">
+    <row r="146" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A146" s="2">
         <v>145</v>
       </c>
     </row>
-    <row r="147" spans="1:10" ht="409.6" customHeight="1">
+    <row r="147" spans="1:10" ht="409.6" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A147" s="2">
         <v>146</v>
       </c>
       <c r="B147" s="2" t="s">
-        <v>709</v>
+        <v>702</v>
       </c>
       <c r="C147" s="2" t="s">
-        <v>710</v>
+        <v>703</v>
       </c>
       <c r="D147" s="2" t="s">
-        <v>711</v>
+        <v>704</v>
       </c>
       <c r="E147" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F147" s="2" t="s">
-        <v>712</v>
+        <v>705</v>
       </c>
       <c r="G147" s="2" t="s">
         <v>13</v>
       </c>
       <c r="H147" s="2" t="s">
-        <v>713</v>
+        <v>706</v>
       </c>
       <c r="I147" s="2" t="s">
-        <v>714</v>
+        <v>707</v>
       </c>
       <c r="J147" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="148" spans="1:10" ht="210.75">
+    <row r="148" spans="1:10" ht="409.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A148" s="2">
         <v>147</v>
       </c>
       <c r="B148" s="2" t="s">
-        <v>715</v>
+        <v>708</v>
       </c>
       <c r="D148" s="2" t="s">
-        <v>571</v>
+        <v>567</v>
       </c>
       <c r="E148" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F148" s="2" t="s">
-        <v>716</v>
+        <v>709</v>
       </c>
       <c r="G148" s="2" t="s">
         <v>36</v>
       </c>
       <c r="H148" s="2" t="s">
-        <v>717</v>
+        <v>710</v>
       </c>
       <c r="I148" s="2" t="s">
-        <v>718</v>
+        <v>711</v>
       </c>
       <c r="J148" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="149" spans="1:10" ht="259.5">
+    <row r="149" spans="1:10" ht="201.5" x14ac:dyDescent="0.35">
       <c r="A149" s="2">
         <v>148</v>
       </c>
       <c r="B149" s="2" t="s">
-        <v>719</v>
+        <v>712</v>
       </c>
       <c r="D149" s="2" t="s">
-        <v>720</v>
+        <v>713</v>
       </c>
       <c r="E149" s="2" t="s">
         <v>22</v>
@@ -8628,18 +9380,18 @@
         <v>141</v>
       </c>
     </row>
-    <row r="150" spans="1:10" ht="275.25">
+    <row r="150" spans="1:10" ht="186" x14ac:dyDescent="0.35">
       <c r="A150" s="2">
         <v>149</v>
       </c>
       <c r="B150" s="2" t="s">
-        <v>721</v>
+        <v>714</v>
       </c>
       <c r="D150" s="2" t="s">
-        <v>722</v>
+        <v>715</v>
       </c>
       <c r="E150" s="2" t="s">
-        <v>723</v>
+        <v>716</v>
       </c>
       <c r="G150" s="2" t="s">
         <v>23</v>
@@ -8648,12 +9400,12 @@
         <v>141</v>
       </c>
     </row>
-    <row r="151" spans="1:10" ht="226.5">
+    <row r="151" spans="1:10" ht="409.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A151" s="2">
         <v>150</v>
       </c>
       <c r="B151" s="2" t="s">
-        <v>724</v>
+        <v>717</v>
       </c>
       <c r="D151" s="2" t="s">
         <v>130</v>
@@ -8668,21 +9420,21 @@
         <v>36</v>
       </c>
       <c r="H151" s="2" t="s">
-        <v>725</v>
+        <v>718</v>
       </c>
       <c r="I151" s="2" t="s">
-        <v>726</v>
+        <v>719</v>
       </c>
       <c r="J151" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="152" spans="1:10" ht="162">
+    <row r="152" spans="1:10" ht="409.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A152" s="2">
         <v>151</v>
       </c>
       <c r="B152" s="2" t="s">
-        <v>727</v>
+        <v>720</v>
       </c>
       <c r="D152" s="2" t="s">
         <v>93</v>
@@ -8697,21 +9449,21 @@
         <v>13</v>
       </c>
       <c r="H152" s="2" t="s">
-        <v>728</v>
+        <v>721</v>
       </c>
       <c r="I152" s="2" t="s">
-        <v>729</v>
+        <v>722</v>
       </c>
       <c r="J152" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="153" spans="1:10" ht="162">
+    <row r="153" spans="1:10" ht="409.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A153" s="2">
         <v>152</v>
       </c>
       <c r="B153" s="2" t="s">
-        <v>730</v>
+        <v>723</v>
       </c>
       <c r="D153" s="2" t="s">
         <v>93</v>
@@ -8726,21 +9478,21 @@
         <v>13</v>
       </c>
       <c r="H153" s="2" t="s">
-        <v>731</v>
+        <v>724</v>
       </c>
       <c r="I153" s="2" t="s">
-        <v>732</v>
+        <v>725</v>
       </c>
       <c r="J153" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="154" spans="1:10" ht="129">
+    <row r="154" spans="1:10" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A154" s="2">
         <v>153</v>
       </c>
       <c r="B154" s="2" t="s">
-        <v>733</v>
+        <v>726</v>
       </c>
       <c r="D154" s="2" t="s">
         <v>93</v>
@@ -8754,32 +9506,28 @@
       <c r="G154" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="H154" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Artifacts are pointer-only by design (#1/#3): the Artifact row stores s3_key/content_hash/version/status, bodies live in S3 as run/phase-scoped drafts written by the agent-only MCP tool stage_artifact_body. The REST ArtifactViewSet is ReadOnly - its only body route is 'preview' (explicitly 'never an editor'), and update_artifact (MCP-only) mutates pointers/metadata, never a body. So there is no human path to edit a generated draft body.</t>
-        </is>
-      </c>
-      <c r="I154" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">OPEN - surgical fix (recon 2026-07-24): add a DRAFT-ONLY edit path that respects the no-auto-publish non-negotiable (#5) - a new @action (e.g. 'edit') on ArtifactViewSet (allowed on a ReadOnly viewset) or a small service that: rejects unless status=='draft' AND sor=='internal', re-stages the edited body to S3 via the existing stage_artifact_body mechanics, updates s3_key + content_hash and bumps version, and writes an Event. Frontend: swap the read-only Markdown block in ArtifactPreviewScreen.tsx for an editable textarea + Save when status=='draft'. Scope the first cut to single-body markdown/text; multi-state wireframe HTML is a later pass. Medium size; the ONLY risk is letting an edit touch a staged/approved/published body - restrict strictly to draft+internal and it never bypasses a gate.</t>
-        </is>
+      <c r="H154" s="2" t="s">
+        <v>824</v>
+      </c>
+      <c r="I154" s="2" t="s">
+        <v>825</v>
       </c>
       <c r="J154" s="2" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="155" spans="1:10" ht="210.75">
+    <row r="155" spans="1:10" ht="155" x14ac:dyDescent="0.35">
       <c r="A155" s="2">
         <v>154</v>
       </c>
       <c r="B155" s="2" t="s">
-        <v>734</v>
+        <v>727</v>
       </c>
       <c r="D155" s="2" t="s">
-        <v>722</v>
+        <v>715</v>
       </c>
       <c r="E155" s="2" t="s">
-        <v>723</v>
+        <v>716</v>
       </c>
       <c r="G155" s="2" t="s">
         <v>23</v>
@@ -8788,12 +9536,12 @@
         <v>141</v>
       </c>
     </row>
-    <row r="156" spans="1:10" ht="113.25">
+    <row r="156" spans="1:10" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A156" s="2">
         <v>155</v>
       </c>
       <c r="B156" s="2" t="s">
-        <v>735</v>
+        <v>728</v>
       </c>
       <c r="D156" s="2" t="s">
         <v>147</v>
@@ -8804,26 +9552,22 @@
       <c r="G156" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="H156" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">IntegrationConnection is TenantScopedModel with NO project FK (unlike SourceDocument/DriftRecord in the same app, which are project-scoped), so a connection is shared across the whole tenant. The single resolution choke point is registry.get_connection(tenant_id, capability); the per-capability builders read creds via Config.from_connection(conn) and don't care about tenant-vs-project. RLS is tenant-based; adding a project filter needs NO RLS change (isolation stays at the tenant boundary). The cost is that ~16 resolution call sites (build_activities, review_provider, reconcile, publish, onboarding, design, preview, quality, views, repos) mostly carry only tenant_id, plus ~20 tests monkeypatch get_capability(tid,cap).</t>
-        </is>
-      </c>
-      <c r="I156" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">OPEN - surgical INCREMENTAL path (recon 2026-07-24) - the naive per-project rewrite is deep, so do it in safe steps: (1) add a NULLABLE project FK to IntegrationConnection (existing rows become tenant-wide defaults; plain column+index migration, no RLS change); (2) make get_connection/get_capability take an OPTIONAL project_id kwarg and resolve project-first with tenant fallback: filter(tenant, capability, project_id).first() or filter(tenant, capability, project__isnull=True).first() - every existing caller keeps compiling and behaves exactly as today; (3) relax create_integration uniqueness from (tenant,capability) to (tenant,project,capability) and add project to the serializers/API/frontend; (4) thread project_id into the resolution call sites and their input structs one at a time. Regression risk is LOW while project_id stays an optional fallback kwarg (HIGH only if signatures change eagerly). Projects override selectively while tenant-wide connections keep working.</t>
-        </is>
+      <c r="H156" s="2" t="s">
+        <v>826</v>
+      </c>
+      <c r="I156" s="2" t="s">
+        <v>827</v>
       </c>
       <c r="J156" s="2" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="157" spans="1:10" ht="162">
+    <row r="157" spans="1:10" ht="409.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A157" s="2">
         <v>156</v>
       </c>
       <c r="B157" s="2" t="s">
-        <v>736</v>
+        <v>729</v>
       </c>
       <c r="D157" s="2" t="s">
         <v>147</v>
@@ -8832,59 +9576,59 @@
         <v>12</v>
       </c>
       <c r="F157" s="2" t="s">
-        <v>737</v>
+        <v>730</v>
       </c>
       <c r="G157" s="2" t="s">
         <v>36</v>
       </c>
       <c r="H157" s="2" t="s">
-        <v>738</v>
+        <v>731</v>
       </c>
       <c r="I157" s="2" t="s">
-        <v>739</v>
+        <v>732</v>
       </c>
       <c r="J157" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="158" spans="1:10" ht="226.5">
+    <row r="158" spans="1:10" ht="409.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A158" s="2">
         <v>157</v>
       </c>
       <c r="B158" s="2" t="s">
-        <v>740</v>
+        <v>733</v>
       </c>
       <c r="D158" s="2" t="s">
-        <v>741</v>
+        <v>734</v>
       </c>
       <c r="E158" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F158" s="2" t="s">
-        <v>742</v>
+        <v>735</v>
       </c>
       <c r="G158" s="2" t="s">
         <v>13</v>
       </c>
       <c r="H158" s="2" t="s">
-        <v>743</v>
+        <v>736</v>
       </c>
       <c r="I158" s="2" t="s">
-        <v>744</v>
+        <v>737</v>
       </c>
       <c r="J158" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="159" spans="1:10" ht="409.6">
+    <row r="159" spans="1:10" ht="409.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A159" s="2">
         <v>158</v>
       </c>
       <c r="B159" s="2" t="s">
-        <v>745</v>
+        <v>738</v>
       </c>
       <c r="C159" s="2" t="s">
-        <v>746</v>
+        <v>739</v>
       </c>
       <c r="D159" s="2" t="s">
         <v>130</v>
@@ -8893,219 +9637,219 @@
         <v>12</v>
       </c>
       <c r="F159" s="2" t="s">
-        <v>747</v>
+        <v>740</v>
       </c>
       <c r="G159" s="2" t="s">
         <v>36</v>
       </c>
       <c r="H159" s="2" t="s">
-        <v>748</v>
+        <v>741</v>
       </c>
       <c r="I159" s="2" t="s">
-        <v>749</v>
+        <v>742</v>
       </c>
       <c r="J159" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="160" spans="1:10" ht="52.5" customHeight="1">
+    <row r="160" spans="1:10" ht="52.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A160" s="2">
         <v>159</v>
       </c>
       <c r="B160" s="2" t="s">
-        <v>750</v>
+        <v>743</v>
       </c>
       <c r="C160" s="2" t="s">
-        <v>751</v>
+        <v>744</v>
       </c>
       <c r="D160" s="2" t="s">
-        <v>752</v>
+        <v>745</v>
       </c>
       <c r="E160" s="2" t="s">
         <v>22</v>
       </c>
       <c r="F160" s="2" t="s">
-        <v>753</v>
+        <v>746</v>
       </c>
       <c r="G160" s="2" t="s">
         <v>23</v>
       </c>
       <c r="H160" s="2" t="s">
-        <v>754</v>
+        <v>747</v>
       </c>
       <c r="I160" s="2" t="s">
-        <v>755</v>
+        <v>748</v>
       </c>
       <c r="J160" s="2" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="161" spans="1:10" ht="409.6">
+    <row r="161" spans="1:10" ht="409.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A161" s="2">
         <v>160</v>
       </c>
       <c r="B161" s="2" t="s">
-        <v>756</v>
+        <v>749</v>
       </c>
       <c r="C161" s="2" t="s">
-        <v>757</v>
+        <v>750</v>
       </c>
       <c r="D161" s="2" t="s">
-        <v>758</v>
+        <v>751</v>
       </c>
       <c r="E161" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F161" s="2" t="s">
-        <v>759</v>
+        <v>752</v>
       </c>
       <c r="G161" s="2" t="s">
         <v>13</v>
       </c>
       <c r="H161" s="2" t="s">
-        <v>760</v>
+        <v>753</v>
       </c>
       <c r="I161" s="2" t="s">
-        <v>761</v>
+        <v>754</v>
       </c>
       <c r="J161" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="162" spans="1:10" ht="409.6">
+    <row r="162" spans="1:10" ht="409.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A162" s="2">
         <v>161</v>
       </c>
       <c r="B162" s="2" t="s">
-        <v>763</v>
+        <v>755</v>
       </c>
       <c r="C162" s="2" t="s">
-        <v>764</v>
+        <v>756</v>
       </c>
       <c r="D162" s="2" t="s">
-        <v>765</v>
+        <v>757</v>
       </c>
       <c r="E162" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F162" s="2" t="s">
-        <v>766</v>
+        <v>758</v>
       </c>
       <c r="G162" s="2" t="s">
         <v>13</v>
       </c>
       <c r="H162" s="2" t="s">
-        <v>767</v>
+        <v>759</v>
       </c>
       <c r="I162" s="2" t="s">
-        <v>768</v>
+        <v>760</v>
       </c>
       <c r="J162" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="163" spans="1:10" ht="388.5">
+    <row r="163" spans="1:10" ht="356.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A163" s="2">
         <v>162</v>
       </c>
       <c r="B163" s="2" t="s">
-        <v>769</v>
+        <v>761</v>
       </c>
       <c r="C163" s="2" t="s">
-        <v>770</v>
+        <v>762</v>
       </c>
       <c r="D163" s="2" t="s">
-        <v>771</v>
+        <v>763</v>
       </c>
       <c r="E163" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F163" s="2" t="s">
-        <v>772</v>
+        <v>764</v>
       </c>
       <c r="G163" s="2" t="s">
         <v>13</v>
       </c>
       <c r="H163" s="2" t="s">
-        <v>773</v>
+        <v>765</v>
       </c>
       <c r="I163" s="2" t="s">
-        <v>774</v>
+        <v>766</v>
       </c>
       <c r="J163" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="164" spans="1:10" ht="409.6">
+    <row r="164" spans="1:10" ht="409.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A164" s="2">
         <v>163</v>
       </c>
       <c r="B164" s="2" t="s">
-        <v>775</v>
+        <v>767</v>
       </c>
       <c r="C164" s="2" t="s">
-        <v>776</v>
+        <v>768</v>
       </c>
       <c r="D164" s="2" t="s">
-        <v>777</v>
+        <v>769</v>
       </c>
       <c r="E164" s="2" t="s">
         <v>22</v>
       </c>
       <c r="F164" s="2" t="s">
-        <v>778</v>
+        <v>770</v>
       </c>
       <c r="G164" s="2" t="s">
         <v>36</v>
       </c>
       <c r="H164" s="2" t="s">
-        <v>779</v>
+        <v>771</v>
       </c>
       <c r="I164" s="2" t="s">
-        <v>780</v>
+        <v>772</v>
       </c>
       <c r="J164" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="165" spans="1:10" ht="226.5">
+    <row r="165" spans="1:10" ht="201.5" x14ac:dyDescent="0.35">
       <c r="A165" s="2">
         <v>164</v>
       </c>
       <c r="B165" s="2" t="s">
-        <v>781</v>
+        <v>773</v>
       </c>
       <c r="C165" s="2" t="s">
-        <v>782</v>
+        <v>774</v>
       </c>
       <c r="D165" s="2" t="s">
-        <v>777</v>
+        <v>769</v>
       </c>
       <c r="E165" s="2" t="s">
         <v>22</v>
       </c>
       <c r="F165" s="2" t="s">
-        <v>783</v>
+        <v>775</v>
       </c>
       <c r="G165" s="2" t="s">
         <v>23</v>
       </c>
       <c r="H165" s="2" t="s">
-        <v>784</v>
+        <v>776</v>
       </c>
       <c r="I165" s="2" t="s">
-        <v>785</v>
+        <v>777</v>
       </c>
       <c r="J165" s="2" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="166" spans="1:10" ht="409.6">
+    <row r="166" spans="1:10" ht="409.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A166" s="2">
         <v>165</v>
       </c>
       <c r="B166" s="2" t="s">
-        <v>786</v>
+        <v>778</v>
       </c>
       <c r="D166" s="2" t="s">
         <v>93</v>
@@ -9120,2672 +9864,2180 @@
         <v>13</v>
       </c>
       <c r="H166" s="2" t="s">
-        <v>787</v>
+        <v>779</v>
       </c>
       <c r="I166" s="2" t="s">
-        <v>788</v>
+        <v>780</v>
       </c>
       <c r="J166" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="167" spans="1:10" ht="409.6">
+    <row r="167" spans="1:10" ht="387.5" x14ac:dyDescent="0.35">
       <c r="A167" s="2">
         <v>166</v>
       </c>
       <c r="B167" s="2" t="s">
-        <v>789</v>
+        <v>781</v>
       </c>
       <c r="C167" s="2" t="s">
-        <v>790</v>
+        <v>782</v>
       </c>
       <c r="D167" s="2" t="s">
-        <v>791</v>
+        <v>783</v>
       </c>
       <c r="E167" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F167" s="2" t="s">
-        <v>792</v>
+        <v>784</v>
       </c>
       <c r="G167" s="2" t="s">
         <v>23</v>
       </c>
       <c r="H167" s="2" t="s">
-        <v>793</v>
+        <v>785</v>
       </c>
       <c r="I167" s="2" t="s">
-        <v>794</v>
+        <v>786</v>
       </c>
       <c r="J167" s="2" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="168" spans="1:10" ht="409.6">
+    <row r="168" spans="1:10" ht="409.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A168" s="2">
         <v>167</v>
       </c>
       <c r="B168" s="2" t="s">
-        <v>795</v>
+        <v>787</v>
       </c>
       <c r="C168" s="2" t="s">
-        <v>796</v>
+        <v>788</v>
       </c>
       <c r="D168" s="2" t="s">
-        <v>797</v>
+        <v>789</v>
       </c>
       <c r="E168" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F168" s="2" t="s">
-        <v>798</v>
+        <v>790</v>
       </c>
       <c r="G168" s="2" t="s">
         <v>13</v>
       </c>
       <c r="H168" s="2" t="s">
-        <v>799</v>
+        <v>791</v>
       </c>
       <c r="I168" s="2" t="s">
-        <v>800</v>
+        <v>792</v>
       </c>
       <c r="J168" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="169" spans="1:10" ht="409.6">
+    <row r="169" spans="1:10" ht="409.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A169" s="2">
         <v>168</v>
       </c>
       <c r="B169" s="2" t="s">
-        <v>801</v>
+        <v>793</v>
       </c>
       <c r="C169" s="2" t="s">
-        <v>802</v>
+        <v>794</v>
       </c>
       <c r="D169" s="2" t="s">
-        <v>803</v>
+        <v>795</v>
       </c>
       <c r="E169" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F169" s="2" t="s">
-        <v>804</v>
+        <v>796</v>
       </c>
       <c r="G169" s="2" t="s">
         <v>13</v>
       </c>
       <c r="H169" s="2" t="s">
-        <v>805</v>
+        <v>797</v>
       </c>
       <c r="I169" s="2" t="s">
-        <v>806</v>
+        <v>798</v>
       </c>
       <c r="J169" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="170" spans="1:10" ht="388.5">
+    <row r="170" spans="1:10" ht="356.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A170" s="2">
         <v>169</v>
       </c>
       <c r="B170" s="2" t="s">
-        <v>807</v>
+        <v>799</v>
       </c>
       <c r="C170" s="2" t="s">
-        <v>808</v>
+        <v>800</v>
       </c>
       <c r="D170" s="2" t="s">
-        <v>809</v>
+        <v>801</v>
       </c>
       <c r="E170" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F170" s="2" t="s">
-        <v>810</v>
+        <v>802</v>
       </c>
       <c r="G170" s="2" t="s">
         <v>36</v>
       </c>
       <c r="H170" s="2" t="s">
+        <v>803</v>
+      </c>
+      <c r="I170" s="2" t="s">
+        <v>828</v>
+      </c>
+      <c r="J170" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="171" spans="1:10" ht="263.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A171" s="2">
+        <v>170</v>
+      </c>
+      <c r="B171" s="2" t="s">
+        <v>804</v>
+      </c>
+      <c r="D171" s="2" t="s">
+        <v>805</v>
+      </c>
+      <c r="E171" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F171" s="2" t="e" vm="18">
+        <v>#VALUE!</v>
+      </c>
+      <c r="G171" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H171" s="2" t="s">
+        <v>829</v>
+      </c>
+      <c r="I171" s="2" t="s">
+        <v>830</v>
+      </c>
+      <c r="J171" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="172" spans="1:10" ht="232.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A172" s="2">
+        <v>171</v>
+      </c>
+      <c r="B172" s="2" t="s">
+        <v>806</v>
+      </c>
+      <c r="D172" s="2" t="s">
+        <v>807</v>
+      </c>
+      <c r="E172" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F172" s="2" t="e" vm="19">
+        <v>#VALUE!</v>
+      </c>
+      <c r="G172" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H172" s="2" t="s">
+        <v>831</v>
+      </c>
+      <c r="I172" s="2" t="s">
+        <v>832</v>
+      </c>
+      <c r="J172" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="173" spans="1:10" ht="409.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A173" s="2">
+        <v>172</v>
+      </c>
+      <c r="B173" s="2" t="s">
+        <v>808</v>
+      </c>
+      <c r="D173" s="2" t="s">
+        <v>809</v>
+      </c>
+      <c r="E173" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F173" s="2" t="e" vm="20">
+        <v>#VALUE!</v>
+      </c>
+      <c r="G173" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H173" s="2" t="s">
+        <v>833</v>
+      </c>
+      <c r="I173" s="2" t="s">
+        <v>834</v>
+      </c>
+      <c r="J173" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="174" spans="1:10" ht="409.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A174" s="2">
+        <v>173</v>
+      </c>
+      <c r="B174" s="2" t="s">
+        <v>810</v>
+      </c>
+      <c r="D174" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="E174" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F174" s="2" t="e" vm="21">
+        <v>#VALUE!</v>
+      </c>
+      <c r="G174" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H174" s="2" t="s">
+        <v>835</v>
+      </c>
+      <c r="I174" s="2" t="s">
+        <v>836</v>
+      </c>
+      <c r="J174" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="175" spans="1:10" ht="186" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A175" s="2">
+        <v>174</v>
+      </c>
+      <c r="B175" s="2" t="s">
         <v>811</v>
       </c>
-      <c r="I170" s="2" t="inlineStr">
+      <c r="D175" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="E175" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F175" s="2" t="e" vm="22">
+        <v>#VALUE!</v>
+      </c>
+      <c r="G175" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H175" s="2" t="s">
+        <v>837</v>
+      </c>
+      <c r="I175" s="2" t="s">
+        <v>838</v>
+      </c>
+      <c r="J175" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="176" spans="1:10" ht="403" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A176" s="2">
+        <v>175</v>
+      </c>
+      <c r="B176" s="2" t="s">
+        <v>812</v>
+      </c>
+      <c r="D176" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="E176" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F176" s="2" t="e" vm="23">
+        <v>#VALUE!</v>
+      </c>
+      <c r="G176" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H176" s="2" t="s">
+        <v>839</v>
+      </c>
+      <c r="I176" s="2" t="s">
+        <v>840</v>
+      </c>
+      <c r="J176" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="177" spans="1:10" ht="409.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A177" s="2">
+        <v>176</v>
+      </c>
+      <c r="B177" s="2" t="s">
+        <v>841</v>
+      </c>
+      <c r="D177" s="2" t="s">
+        <v>842</v>
+      </c>
+      <c r="E177" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F177" s="2" t="s">
+        <v>843</v>
+      </c>
+      <c r="G177" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H177" s="2" t="s">
+        <v>844</v>
+      </c>
+      <c r="I177" s="2" t="s">
+        <v>845</v>
+      </c>
+      <c r="J177" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="178" spans="1:10" ht="341" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A178" s="2">
+        <v>177</v>
+      </c>
+      <c r="B178" s="2" t="s">
+        <v>846</v>
+      </c>
+      <c r="D178" s="2" t="s">
+        <v>847</v>
+      </c>
+      <c r="E178" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F178" s="2" t="s">
+        <v>848</v>
+      </c>
+      <c r="G178" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H178" s="2" t="s">
+        <v>849</v>
+      </c>
+      <c r="I178" s="2" t="s">
+        <v>850</v>
+      </c>
+      <c r="J178" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="179" spans="1:10" ht="186" x14ac:dyDescent="0.35">
+      <c r="A179" s="2">
+        <v>178</v>
+      </c>
+      <c r="B179" s="2" t="s">
+        <v>851</v>
+      </c>
+      <c r="D179" s="2" t="s">
+        <v>852</v>
+      </c>
+      <c r="E179" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F179" s="2" t="s">
+        <v>853</v>
+      </c>
+      <c r="G179" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="H179" s="2" t="s">
+        <v>854</v>
+      </c>
+      <c r="I179" s="2" t="s">
+        <v>855</v>
+      </c>
+      <c r="J179" s="2" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="180" spans="1:10" ht="217" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A180" s="2">
+        <v>179</v>
+      </c>
+      <c r="B180" s="2" t="s">
+        <v>856</v>
+      </c>
+      <c r="D180" s="2" t="s">
+        <v>857</v>
+      </c>
+      <c r="E180" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F180" s="2" t="s">
+        <v>858</v>
+      </c>
+      <c r="G180" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="H180" s="2" t="s">
+        <v>859</v>
+      </c>
+      <c r="I180" s="2" t="s">
+        <v>860</v>
+      </c>
+      <c r="J180" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="181" spans="1:10" ht="186" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A181" s="2">
+        <v>180</v>
+      </c>
+      <c r="B181" s="2" t="s">
+        <v>861</v>
+      </c>
+      <c r="D181" s="2" t="s">
+        <v>862</v>
+      </c>
+      <c r="E181" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F181" s="2" t="s">
+        <v>863</v>
+      </c>
+      <c r="G181" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H181" s="2" t="s">
+        <v>864</v>
+      </c>
+      <c r="I181" s="2" t="s">
+        <v>865</v>
+      </c>
+      <c r="J181" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="182" spans="1:10" ht="356.5" x14ac:dyDescent="0.35">
+      <c r="A182" s="2">
+        <v>181</v>
+      </c>
+      <c r="B182" s="2" t="s">
+        <v>866</v>
+      </c>
+      <c r="D182" s="2" t="s">
+        <v>867</v>
+      </c>
+      <c r="E182" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F182" s="2" t="s">
+        <v>868</v>
+      </c>
+      <c r="G182" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="H182" s="2" t="s">
+        <v>869</v>
+      </c>
+      <c r="I182" s="2" t="s">
+        <v>870</v>
+      </c>
+      <c r="J182" s="2" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="183" spans="1:10" ht="409.5" x14ac:dyDescent="0.35">
+      <c r="A183" s="2">
+        <v>182</v>
+      </c>
+      <c r="B183" s="2" t="s">
+        <v>871</v>
+      </c>
+      <c r="D183" s="2" t="s">
+        <v>872</v>
+      </c>
+      <c r="E183" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F183" s="2" t="s">
+        <v>873</v>
+      </c>
+      <c r="G183" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H183" s="2" t="s">
+        <v>874</v>
+      </c>
+      <c r="I183" s="2" t="s">
+        <v>875</v>
+      </c>
+      <c r="J183" s="2" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="184" spans="1:10" ht="356.5" x14ac:dyDescent="0.35">
+      <c r="A184" s="2">
+        <v>183</v>
+      </c>
+      <c r="B184" s="2" t="s">
+        <v>876</v>
+      </c>
+      <c r="D184" s="2" t="s">
+        <v>877</v>
+      </c>
+      <c r="E184" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F184" s="2" t="s">
+        <v>878</v>
+      </c>
+      <c r="G184" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="H184" s="2" t="s">
+        <v>879</v>
+      </c>
+      <c r="I184" s="2" t="s">
+        <v>880</v>
+      </c>
+      <c r="J184" s="2" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="185" spans="1:10" ht="294.5" x14ac:dyDescent="0.35">
+      <c r="A185" s="2">
+        <v>184</v>
+      </c>
+      <c r="B185" s="2" t="s">
+        <v>881</v>
+      </c>
+      <c r="D185" s="2" t="s">
+        <v>882</v>
+      </c>
+      <c r="E185" s="2" t="s">
+        <v>883</v>
+      </c>
+      <c r="F185" s="2" t="s">
+        <v>884</v>
+      </c>
+      <c r="G185" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H185" s="2" t="s">
+        <v>885</v>
+      </c>
+      <c r="I185" s="2" t="s">
+        <v>886</v>
+      </c>
+      <c r="J185" s="2" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="186" spans="1:10" ht="372" x14ac:dyDescent="0.35">
+      <c r="A186" s="2">
+        <v>185</v>
+      </c>
+      <c r="B186" s="2" t="s">
+        <v>887</v>
+      </c>
+      <c r="D186" s="2" t="s">
+        <v>888</v>
+      </c>
+      <c r="E186" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F186" s="2" t="s">
+        <v>889</v>
+      </c>
+      <c r="G186" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H186" s="2" t="s">
+        <v>890</v>
+      </c>
+      <c r="I186" s="2" t="s">
+        <v>891</v>
+      </c>
+      <c r="J186" s="2" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="187" spans="1:10" ht="232.5" x14ac:dyDescent="0.35">
+      <c r="A187" s="2">
+        <v>186</v>
+      </c>
+      <c r="B187" s="2" t="s">
+        <v>892</v>
+      </c>
+      <c r="D187" s="2" t="s">
+        <v>893</v>
+      </c>
+      <c r="E187" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F187" s="2" t="s">
+        <v>894</v>
+      </c>
+      <c r="G187" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="H187" s="2" t="s">
+        <v>895</v>
+      </c>
+      <c r="I187" s="2" t="s">
+        <v>896</v>
+      </c>
+      <c r="J187" s="2" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="188" spans="1:10" ht="248" x14ac:dyDescent="0.35">
+      <c r="A188" s="2">
+        <v>187</v>
+      </c>
+      <c r="B188" s="2" t="s">
+        <v>897</v>
+      </c>
+      <c r="D188" s="2" t="s">
+        <v>898</v>
+      </c>
+      <c r="E188" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F188" s="2" t="s">
+        <v>899</v>
+      </c>
+      <c r="G188" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="H188" s="2" t="s">
+        <v>900</v>
+      </c>
+      <c r="I188" s="2" t="s">
+        <v>901</v>
+      </c>
+      <c r="J188" s="2" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="189" spans="1:10" ht="325.5" x14ac:dyDescent="0.35">
+      <c r="A189" s="2">
+        <v>188</v>
+      </c>
+      <c r="B189" s="2" t="s">
+        <v>902</v>
+      </c>
+      <c r="D189" s="2" t="s">
+        <v>903</v>
+      </c>
+      <c r="E189" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F189" s="2" t="s">
+        <v>904</v>
+      </c>
+      <c r="G189" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H189" s="2" t="s">
+        <v>905</v>
+      </c>
+      <c r="I189" s="2" t="s">
+        <v>906</v>
+      </c>
+      <c r="J189" s="2" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="190" spans="1:10" ht="294.5" x14ac:dyDescent="0.35">
+      <c r="A190" s="2">
+        <v>189</v>
+      </c>
+      <c r="B190" s="2" t="s">
+        <v>907</v>
+      </c>
+      <c r="D190" s="2" t="s">
+        <v>908</v>
+      </c>
+      <c r="E190" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F190" s="2" t="s">
+        <v>909</v>
+      </c>
+      <c r="G190" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="H190" s="2" t="s">
+        <v>910</v>
+      </c>
+      <c r="I190" s="2" t="s">
+        <v>911</v>
+      </c>
+      <c r="J190" s="2" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="191" spans="1:10" ht="372" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A191" s="2">
+        <v>190</v>
+      </c>
+      <c r="B191" s="2" t="s">
+        <v>912</v>
+      </c>
+      <c r="D191" s="2" t="s">
+        <v>913</v>
+      </c>
+      <c r="E191" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F191" s="2" t="s">
+        <v>914</v>
+      </c>
+      <c r="G191" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="H191" s="2" t="s">
+        <v>915</v>
+      </c>
+      <c r="I191" s="2" t="s">
+        <v>916</v>
+      </c>
+      <c r="J191" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="192" spans="1:10" ht="325.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A192" s="2">
+        <v>191</v>
+      </c>
+      <c r="B192" s="2" t="s">
+        <v>917</v>
+      </c>
+      <c r="D192" s="2" t="s">
+        <v>918</v>
+      </c>
+      <c r="E192" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F192" s="2" t="s">
+        <v>919</v>
+      </c>
+      <c r="G192" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H192" s="2" t="s">
+        <v>920</v>
+      </c>
+      <c r="I192" s="2" t="s">
+        <v>921</v>
+      </c>
+      <c r="J192" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="193" spans="1:10" ht="409.5" x14ac:dyDescent="0.35">
+      <c r="A193" s="2">
+        <v>192</v>
+      </c>
+      <c r="B193" s="2" t="s">
+        <v>922</v>
+      </c>
+      <c r="D193" s="2" t="s">
+        <v>923</v>
+      </c>
+      <c r="E193" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F193" s="2" t="s">
+        <v>924</v>
+      </c>
+      <c r="G193" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H193" s="2" t="s">
+        <v>925</v>
+      </c>
+      <c r="I193" s="2" t="s">
+        <v>926</v>
+      </c>
+      <c r="J193" s="2" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="194" spans="1:10" ht="409.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A194" s="2">
+        <v>193</v>
+      </c>
+      <c r="B194" s="2" t="s">
+        <v>927</v>
+      </c>
+      <c r="D194" s="2" t="s">
+        <v>928</v>
+      </c>
+      <c r="E194" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F194" s="2" t="s">
+        <v>929</v>
+      </c>
+      <c r="G194" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="H194" s="2" t="s">
+        <v>930</v>
+      </c>
+      <c r="I194" s="2" t="s">
+        <v>931</v>
+      </c>
+      <c r="J194" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="195" spans="1:10" ht="372" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A195" s="2">
+        <v>194</v>
+      </c>
+      <c r="B195" s="2" t="s">
+        <v>932</v>
+      </c>
+      <c r="D195" s="2" t="s">
+        <v>933</v>
+      </c>
+      <c r="E195" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F195" s="2" t="s">
+        <v>934</v>
+      </c>
+      <c r="G195" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="H195" s="2" t="s">
+        <v>935</v>
+      </c>
+      <c r="I195" s="2" t="s">
+        <v>936</v>
+      </c>
+      <c r="J195" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="196" spans="1:10" ht="403" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A196" s="2">
+        <v>195</v>
+      </c>
+      <c r="B196" s="2" t="s">
+        <v>937</v>
+      </c>
+      <c r="D196" s="2" t="s">
+        <v>938</v>
+      </c>
+      <c r="E196" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F196" s="2" t="s">
+        <v>939</v>
+      </c>
+      <c r="G196" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="H196" s="2" t="s">
+        <v>940</v>
+      </c>
+      <c r="I196" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="J196" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="197" spans="1:10" ht="294.5" x14ac:dyDescent="0.35">
+      <c r="A197" s="2">
+        <v>196</v>
+      </c>
+      <c r="B197" s="2" t="s">
+        <v>942</v>
+      </c>
+      <c r="D197" s="2" t="s">
+        <v>943</v>
+      </c>
+      <c r="E197" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F197" s="2" t="s">
+        <v>944</v>
+      </c>
+      <c r="G197" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H197" s="2" t="s">
+        <v>945</v>
+      </c>
+      <c r="I197" s="2" t="s">
+        <v>946</v>
+      </c>
+      <c r="J197" s="2" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="198" spans="1:10" ht="409.5" x14ac:dyDescent="0.35">
+      <c r="A198" s="2">
+        <v>197</v>
+      </c>
+      <c r="B198" s="2" t="s">
+        <v>947</v>
+      </c>
+      <c r="D198" s="2" t="s">
+        <v>948</v>
+      </c>
+      <c r="E198" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F198" s="2" t="s">
+        <v>949</v>
+      </c>
+      <c r="G198" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H198" s="2" t="s">
+        <v>950</v>
+      </c>
+      <c r="I198" s="2" t="s">
+        <v>951</v>
+      </c>
+      <c r="J198" s="2" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="199" spans="1:10" ht="409.5" x14ac:dyDescent="0.35">
+      <c r="A199" s="2">
+        <v>198</v>
+      </c>
+      <c r="B199" s="2" t="s">
+        <v>952</v>
+      </c>
+      <c r="D199" s="2" t="s">
+        <v>953</v>
+      </c>
+      <c r="E199" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F199" s="2" t="s">
+        <v>954</v>
+      </c>
+      <c r="G199" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="H199" s="2" t="s">
+        <v>955</v>
+      </c>
+      <c r="I199" s="2" t="s">
+        <v>956</v>
+      </c>
+      <c r="J199" s="2" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="200" spans="1:10" ht="372" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A200" s="2">
+        <v>199</v>
+      </c>
+      <c r="B200" s="2" t="s">
+        <v>957</v>
+      </c>
+      <c r="D200" s="2" t="s">
+        <v>958</v>
+      </c>
+      <c r="E200" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F200" s="2" t="s">
+        <v>959</v>
+      </c>
+      <c r="G200" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H200" s="2" t="s">
+        <v>960</v>
+      </c>
+      <c r="I200" s="2" t="s">
+        <v>961</v>
+      </c>
+      <c r="J200" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="201" spans="1:10" ht="279" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A201" s="2">
+        <v>200</v>
+      </c>
+      <c r="B201" s="2" t="s">
+        <v>962</v>
+      </c>
+      <c r="D201" s="2" t="s">
+        <v>963</v>
+      </c>
+      <c r="E201" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F201" s="2" t="s">
+        <v>964</v>
+      </c>
+      <c r="G201" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H201" s="2" t="s">
+        <v>965</v>
+      </c>
+      <c r="I201" s="2" t="s">
+        <v>966</v>
+      </c>
+      <c r="J201" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="202" spans="1:10" ht="294.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A202" s="2">
+        <v>201</v>
+      </c>
+      <c r="B202" s="2" t="s">
+        <v>967</v>
+      </c>
+      <c r="D202" s="2" t="s">
+        <v>968</v>
+      </c>
+      <c r="E202" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F202" s="2" t="s">
+        <v>969</v>
+      </c>
+      <c r="G202" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="H202" s="2" t="s">
+        <v>970</v>
+      </c>
+      <c r="I202" s="2" t="s">
+        <v>971</v>
+      </c>
+      <c r="J202" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="203" spans="1:10" ht="155" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A203" s="2">
+        <v>202</v>
+      </c>
+      <c r="B203" s="2" t="s">
+        <v>972</v>
+      </c>
+      <c r="D203" s="2" t="s">
+        <v>973</v>
+      </c>
+      <c r="E203" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F203" s="2" t="s">
+        <v>974</v>
+      </c>
+      <c r="G203" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="H203" s="2" t="s">
+        <v>975</v>
+      </c>
+      <c r="I203" s="2" t="s">
+        <v>976</v>
+      </c>
+      <c r="J203" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="204" spans="1:10" ht="325.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A204" s="2">
+        <v>203</v>
+      </c>
+      <c r="B204" s="2" t="s">
+        <v>977</v>
+      </c>
+      <c r="D204" s="2" t="s">
+        <v>978</v>
+      </c>
+      <c r="E204" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F204" s="2" t="s">
+        <v>979</v>
+      </c>
+      <c r="G204" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H204" s="2" t="s">
+        <v>980</v>
+      </c>
+      <c r="I204" s="2" t="s">
+        <v>981</v>
+      </c>
+      <c r="J204" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="205" spans="1:10" ht="139.5" x14ac:dyDescent="0.35">
+      <c r="A205" s="2">
+        <v>204</v>
+      </c>
+      <c r="B205" s="2" t="s">
+        <v>982</v>
+      </c>
+      <c r="D205" s="2" t="s">
+        <v>983</v>
+      </c>
+      <c r="E205" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F205" s="2" t="s">
+        <v>984</v>
+      </c>
+      <c r="G205" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H205" s="2" t="s">
+        <v>985</v>
+      </c>
+      <c r="I205" s="2" t="s">
+        <v>986</v>
+      </c>
+      <c r="J205" s="2" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="206" spans="1:10" ht="201.5" x14ac:dyDescent="0.35">
+      <c r="A206" s="2">
+        <v>205</v>
+      </c>
+      <c r="B206" s="2" t="s">
+        <v>987</v>
+      </c>
+      <c r="D206" s="2" t="s">
+        <v>988</v>
+      </c>
+      <c r="E206" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F206" s="2" t="s">
+        <v>989</v>
+      </c>
+      <c r="G206" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H206" s="2" t="s">
+        <v>990</v>
+      </c>
+      <c r="I206" s="2" t="s">
+        <v>991</v>
+      </c>
+      <c r="J206" s="2" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="207" spans="1:10" ht="325.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A207" s="2">
+        <v>206</v>
+      </c>
+      <c r="B207" s="2" t="s">
+        <v>992</v>
+      </c>
+      <c r="D207" s="2" t="s">
+        <v>993</v>
+      </c>
+      <c r="E207" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F207" s="2" t="s">
+        <v>994</v>
+      </c>
+      <c r="G207" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H207" s="2" t="s">
+        <v>995</v>
+      </c>
+      <c r="I207" s="2" t="s">
+        <v>996</v>
+      </c>
+      <c r="J207" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="208" spans="1:10" ht="248" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A208" s="2">
+        <v>207</v>
+      </c>
+      <c r="B208" s="2" t="s">
+        <v>997</v>
+      </c>
+      <c r="D208" s="2" t="s">
+        <v>998</v>
+      </c>
+      <c r="E208" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F208" s="2" t="s">
+        <v>999</v>
+      </c>
+      <c r="G208" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H208" s="2" t="s">
+        <v>1000</v>
+      </c>
+      <c r="I208" s="2" t="s">
+        <v>1001</v>
+      </c>
+      <c r="J208" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="209" spans="1:10" ht="201.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A209" s="2">
+        <v>208</v>
+      </c>
+      <c r="B209" s="2" t="s">
+        <v>1002</v>
+      </c>
+      <c r="D209" s="2" t="s">
+        <v>1003</v>
+      </c>
+      <c r="E209" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F209" s="2" t="s">
+        <v>1004</v>
+      </c>
+      <c r="G209" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="H209" s="2" t="s">
+        <v>1005</v>
+      </c>
+      <c r="I209" s="2" t="s">
+        <v>1006</v>
+      </c>
+      <c r="J209" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="210" spans="1:10" ht="186" x14ac:dyDescent="0.35">
+      <c r="A210" s="2">
+        <v>209</v>
+      </c>
+      <c r="B210" s="2" t="s">
+        <v>1007</v>
+      </c>
+      <c r="D210" s="2" t="s">
+        <v>1008</v>
+      </c>
+      <c r="E210" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F210" s="2" t="s">
+        <v>1009</v>
+      </c>
+      <c r="G210" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H210" s="2" t="s">
+        <v>1010</v>
+      </c>
+      <c r="I210" s="2" t="s">
+        <v>1011</v>
+      </c>
+      <c r="J210" s="2" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="211" spans="1:10" ht="232.5" x14ac:dyDescent="0.35">
+      <c r="A211" s="2">
+        <v>210</v>
+      </c>
+      <c r="B211" s="2" t="s">
+        <v>1012</v>
+      </c>
+      <c r="D211" s="2" t="s">
+        <v>1013</v>
+      </c>
+      <c r="E211" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F211" s="2" t="s">
+        <v>1014</v>
+      </c>
+      <c r="G211" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="H211" s="2" t="s">
+        <v>1015</v>
+      </c>
+      <c r="I211" s="2" t="s">
+        <v>1016</v>
+      </c>
+      <c r="J211" s="2" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="212" spans="1:10" ht="217" x14ac:dyDescent="0.35">
+      <c r="A212" s="2">
+        <v>211</v>
+      </c>
+      <c r="B212" s="2" t="s">
+        <v>1017</v>
+      </c>
+      <c r="D212" s="2" t="s">
+        <v>1018</v>
+      </c>
+      <c r="E212" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G212" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="H212" s="2" t="s">
+        <v>1019</v>
+      </c>
+      <c r="J212" s="2" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="213" spans="1:10" ht="170.5" x14ac:dyDescent="0.35">
+      <c r="A213" s="2">
+        <v>212</v>
+      </c>
+      <c r="B213" s="2" t="s">
+        <v>1020</v>
+      </c>
+      <c r="D213" s="2" t="s">
+        <v>805</v>
+      </c>
+      <c r="E213" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G213" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H213" s="2" t="s">
+        <v>1021</v>
+      </c>
+      <c r="J213" s="2" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="214" spans="1:10" ht="217" x14ac:dyDescent="0.35">
+      <c r="A214" s="2">
+        <v>213</v>
+      </c>
+      <c r="B214" s="2" t="s">
+        <v>1022</v>
+      </c>
+      <c r="D214" s="2" t="s">
+        <v>567</v>
+      </c>
+      <c r="E214" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G214" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="H214" s="2" t="s">
+        <v>1023</v>
+      </c>
+      <c r="J214" s="2" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="215" spans="1:10" ht="248" x14ac:dyDescent="0.35">
+      <c r="A215" s="2">
+        <v>214</v>
+      </c>
+      <c r="B215" s="2" t="s">
+        <v>1024</v>
+      </c>
+      <c r="D215" s="2" t="s">
+        <v>1025</v>
+      </c>
+      <c r="E215" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G215" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H215" s="2" t="s">
+        <v>1026</v>
+      </c>
+      <c r="J215" s="2" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="216" spans="1:10" ht="170.5" x14ac:dyDescent="0.35">
+      <c r="A216" s="2">
+        <v>215</v>
+      </c>
+      <c r="B216" s="2" t="s">
+        <v>1027</v>
+      </c>
+      <c r="D216" s="2" t="s">
+        <v>1028</v>
+      </c>
+      <c r="E216" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G216" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H216" s="2" t="s">
+        <v>1029</v>
+      </c>
+      <c r="J216" s="2" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="217" spans="1:10" ht="186" x14ac:dyDescent="0.35">
+      <c r="A217" s="2">
+        <v>216</v>
+      </c>
+      <c r="B217" s="2" t="s">
+        <v>1030</v>
+      </c>
+      <c r="D217" s="2" t="s">
+        <v>1031</v>
+      </c>
+      <c r="E217" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G217" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H217" s="2" t="s">
+        <v>1032</v>
+      </c>
+      <c r="J217" s="2" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="218" spans="1:10" ht="263.5" x14ac:dyDescent="0.35">
+      <c r="A218" s="2">
+        <v>217</v>
+      </c>
+      <c r="B218" s="2" t="s">
+        <v>1033</v>
+      </c>
+      <c r="D218" s="2" t="s">
+        <v>1031</v>
+      </c>
+      <c r="E218" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G218" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="H218" s="2" t="s">
+        <v>1034</v>
+      </c>
+      <c r="J218" s="2" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="219" spans="1:10" ht="341" x14ac:dyDescent="0.35">
+      <c r="A219" s="2">
+        <v>218</v>
+      </c>
+      <c r="B219" s="2" t="s">
+        <v>1035</v>
+      </c>
+      <c r="D219" s="2" t="s">
+        <v>1036</v>
+      </c>
+      <c r="E219" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G219" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H219" s="2" t="s">
+        <v>1037</v>
+      </c>
+      <c r="J219" s="2" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="220" spans="1:10" ht="263.5" x14ac:dyDescent="0.35">
+      <c r="A220" s="2">
+        <v>219</v>
+      </c>
+      <c r="B220" s="2" t="s">
+        <v>1038</v>
+      </c>
+      <c r="D220" s="2" t="s">
+        <v>1036</v>
+      </c>
+      <c r="E220" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G220" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="H220" s="2" t="s">
+        <v>1039</v>
+      </c>
+      <c r="J220" s="2" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="221" spans="1:10" ht="232.5" x14ac:dyDescent="0.35">
+      <c r="A221" s="2">
+        <v>220</v>
+      </c>
+      <c r="B221" s="2" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D221" s="2" t="s">
+        <v>1036</v>
+      </c>
+      <c r="E221" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G221" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H221" s="2" t="s">
+        <v>1041</v>
+      </c>
+      <c r="J221" s="2" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="222" spans="1:10" ht="201.5" x14ac:dyDescent="0.35">
+      <c r="A222" s="2">
+        <v>221</v>
+      </c>
+      <c r="B222" s="2" t="s">
+        <v>1042</v>
+      </c>
+      <c r="D222" s="2" t="s">
+        <v>1043</v>
+      </c>
+      <c r="E222" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G222" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="H222" s="2" t="s">
+        <v>1044</v>
+      </c>
+      <c r="J222" s="2" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="223" spans="1:10" ht="170.5" x14ac:dyDescent="0.35">
+      <c r="A223" s="2">
+        <v>222</v>
+      </c>
+      <c r="B223" s="2" t="s">
+        <v>1045</v>
+      </c>
+      <c r="D223" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E223" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G223" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H223" s="2" t="s">
+        <v>1046</v>
+      </c>
+      <c r="J223" s="2" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="224" spans="1:10" ht="201.5" x14ac:dyDescent="0.35">
+      <c r="A224" s="2">
+        <v>223</v>
+      </c>
+      <c r="B224" s="2" t="s">
+        <v>1047</v>
+      </c>
+      <c r="D224" s="2" t="s">
+        <v>1048</v>
+      </c>
+      <c r="E224" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G224" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="H224" s="2" t="s">
+        <v>1049</v>
+      </c>
+      <c r="J224" s="2" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="225" spans="1:10" ht="201.5" x14ac:dyDescent="0.35">
+      <c r="A225" s="2">
+        <v>224</v>
+      </c>
+      <c r="B225" s="2" t="s">
+        <v>1050</v>
+      </c>
+      <c r="D225" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E225" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G225" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H225" s="2" t="s">
+        <v>1051</v>
+      </c>
+      <c r="J225" s="2" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="226" spans="1:10" ht="201.5" x14ac:dyDescent="0.35">
+      <c r="A226" s="2">
+        <v>225</v>
+      </c>
+      <c r="B226" s="2" t="s">
+        <v>1052</v>
+      </c>
+      <c r="D226" s="2" t="s">
+        <v>1036</v>
+      </c>
+      <c r="E226" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G226" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H226" s="2" t="s">
+        <v>1053</v>
+      </c>
+      <c r="J226" s="2" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="227" spans="1:10" ht="409.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A227" s="2">
+        <v>226</v>
+      </c>
+      <c r="B227" s="2" t="s">
+        <v>1054</v>
+      </c>
+      <c r="C227" s="2" t="s">
+        <v>1055</v>
+      </c>
+      <c r="D227" s="2" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E227" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G227" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H227" s="2" t="s">
+        <v>1057</v>
+      </c>
+      <c r="I227" s="2" t="s">
+        <v>1058</v>
+      </c>
+      <c r="J227" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="228" spans="1:10" ht="409.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A228" s="2">
+        <v>227</v>
+      </c>
+      <c r="B228" s="2" t="s">
+        <v>1059</v>
+      </c>
+      <c r="C228" s="2" t="s">
+        <v>1060</v>
+      </c>
+      <c r="D228" s="2" t="s">
+        <v>1061</v>
+      </c>
+      <c r="E228" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G228" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H228" s="2" t="s">
+        <v>1062</v>
+      </c>
+      <c r="I228" s="2" t="s">
+        <v>1063</v>
+      </c>
+      <c r="J228" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="229" spans="1:10" ht="409.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A229" s="2">
+        <v>228</v>
+      </c>
+      <c r="B229" s="2" t="s">
+        <v>1064</v>
+      </c>
+      <c r="C229" s="2" t="s">
+        <v>1065</v>
+      </c>
+      <c r="D229" s="2" t="s">
+        <v>1066</v>
+      </c>
+      <c r="E229" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G229" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="H229" s="2" t="s">
+        <v>1067</v>
+      </c>
+      <c r="I229" s="2" t="s">
+        <v>1068</v>
+      </c>
+      <c r="J229" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="230" spans="1:10" ht="409.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A230" s="2">
+        <v>229</v>
+      </c>
+      <c r="B230" s="2" t="s">
+        <v>1069</v>
+      </c>
+      <c r="C230" s="2" t="s">
+        <v>1070</v>
+      </c>
+      <c r="D230" s="2" t="s">
+        <v>1071</v>
+      </c>
+      <c r="E230" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G230" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="H230" s="2" t="s">
+        <v>1072</v>
+      </c>
+      <c r="I230" s="2" t="s">
+        <v>1073</v>
+      </c>
+      <c r="J230" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="231" spans="1:10" ht="232.5" x14ac:dyDescent="0.35">
+      <c r="A231" s="2">
+        <v>230</v>
+      </c>
+      <c r="B231" s="2" t="s">
+        <v>1074</v>
+      </c>
+      <c r="C231" s="2" t="s">
+        <v>1075</v>
+      </c>
+      <c r="D231" s="2" t="s">
+        <v>1066</v>
+      </c>
+      <c r="E231" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G231" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H231" s="2" t="s">
+        <v>1076</v>
+      </c>
+      <c r="I231" s="2" t="s">
+        <v>1077</v>
+      </c>
+      <c r="J231" s="2" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="232" spans="1:10" ht="232.5" x14ac:dyDescent="0.35">
+      <c r="A232" s="2">
+        <v>231</v>
+      </c>
+      <c r="B232" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">FIXED - resolved by the S.No 89 work (non-terminal STALLED park). mark_phase_takeover_core now marks the run STALLED (not terminal FAILED) and register_phase_result_core clears takeover_flag on a late successful report, so a companion that went offline (e.g. laptop asleep) then returned and reported ok un-parks the run and flows on through register-&gt;verify-&gt;gate-&gt;publish; the false 'engine exited, no artifact' terminal-fail can no longer occur. Verified in backend/orchestration/activities.py (mark_phase_takeover_core + register_phase_result_core, both cite Bugs S.No 89).</t>
+          <t xml:space="preserve">A single transient error while waiting for a clarification answer kills the whole wait, so the agent carries on with no answers and the phase produces a status message instead of its deliverable</t>
         </is>
       </c>
-      <c r="J170" s="2" t="inlineStr">
+      <c r="C232" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Requirements phase on a fresh account. The agent completed its gap scan and called ask_human; the clarification was created and is still visible in the Clarifications screen. One poll then returned 500 and the wait loop raised, unblocking the agent with no answers. Obeying Rule 1 (no artifacts before the answers return) it registered nothing and closed with a status report, which the platform filed as the phase artifact. The run then parked on the write-completeness check.</t>
+        </is>
+      </c>
+      <c r="D232" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Clarifications / companion ask_human (runner/companion/clarify.py)</t>
+        </is>
+      </c>
+      <c r="E232" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bug</t>
+        </is>
+      </c>
+      <c r="F232" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Run fad927a2, requirements phase, account tarun105@gmail.com, reported 2026-08-03. The artifact body opened 'The platform's database is currently unavailable (PostgreSQL connection error on 13.203.56.29)' and listed the 8 Tier-2 questions. Trigger was the connection churn logged separately as S.No 235.</t>
+        </is>
+      </c>
+      <c r="G232" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P1</t>
+        </is>
+      </c>
+      <c r="H232" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ClarificationClient.poll treated ANY status &gt;= 400 as fatal, drawing no distinction between a 500 that would clear on the next tick and a 404 that never will. A second death path existed alongside it: _urllib_transport converts an HTTPError into a (status, payload) pair, but a refused or reset connection arrives as OSError and escaped straight through poll, never meeting the status check at all. Distinct from S.No 110 (code-review poll timeout too short) - this is error classification, not duration.</t>
+        </is>
+      </c>
+      <c r="I232" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fixed. runner/companion/clarify.py: new TransientClarificationError, subclassing ClarificationError so existing callers are unaffected. 500/502/503/504/408/425/429 and connection-level OSError are retried; 400/401/403/404/409 and cancelled stay terminal and fail fast. create() retries too, since a failed create means the clarification never exists. Any successful poll resets the window; the loop gives up only after 15 minutes of consecutive failure and logs each retry to stderr. Retry cadence matches poll_interval, so riding out an outage adds no load that was not already there. Safe because waiting is free - the model is idle on the open tool call. 19 tests added (24 in test_companion_clarify.py). Commit d86ca35.</t>
+        </is>
+      </c>
+      <c r="J232" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Fixed</t>
         </is>
       </c>
     </row>
-    <row r="171" spans="1:10" ht="210.75">
-      <c r="A171" s="2">
-        <v>170</v>
-      </c>
-      <c r="B171" s="2" t="s">
-        <v>813</v>
-      </c>
-      <c r="D171" s="2" t="s">
-        <v>814</v>
-      </c>
-      <c r="E171" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F171" s="2" t="e" vm="18">
-        <v>#VALUE!</v>
-      </c>
-      <c r="G171" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H171" s="2" t="inlineStr">
+    <row r="233" spans="1:10" ht="232.5" x14ac:dyDescent="0.35">
+      <c r="A233" s="2">
+        <v>232</v>
+      </c>
+      <c r="B233" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">S.No 170. The add-repo form lays its fields in a single row that bottom-aligns them. Every field was a label + input EXCEPT "Preview URL", which alone carried a help line under its input; that extra line changed the field's height and pushed its input out of line with the others. The help text also said "09b", an internal phase code that means nothing to a user.</t>
+          <t xml:space="preserve">A failed run's closing message still renders as an ordinary draft deliverable in Artifacts, so error text and clarification questions read as the phase document</t>
         </is>
       </c>
-      <c r="I171" s="2" t="inlineStr">
+      <c r="C233" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">FIXED &amp; TESTED (2026-07-21). Removed the inline help from the Preview URL field so all four inputs bottom-align again, and moved the guidance to a single full-width line below the row, reworded in plain language with no "09b": "Preview URL is optional - if your app is already running somewhere, paste its address so the testing phase can open it and write tests against the live app." File: frontend/src/features/setup/Repositories.tsx.</t>
+          <t xml:space="preserve">After the 2026-07-30 fix the review gate no longer opens on the platform's copy of the engine's final message, but the artifact still exists and is browsable. The Artifacts screen showed it as 'Requirements - SPENDLog v1 draft' with a 'Read-through from the system-of-record' banner and eight unanswered clarification questions in the body. Half the reported symptom was fixed; the visible half was not.</t>
         </is>
       </c>
-      <c r="J171" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="172" spans="1:10" ht="243">
-      <c r="A172" s="2">
-        <v>171</v>
-      </c>
-      <c r="B172" s="2" t="s">
-        <v>815</v>
-      </c>
-      <c r="D172" s="2" t="s">
-        <v>816</v>
-      </c>
-      <c r="E172" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F172" s="2" t="e" vm="19">
-        <v>#VALUE!</v>
-      </c>
-      <c r="G172" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H172" s="2" t="inlineStr">
+      <c r="D233" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">S.No 171. The companion connection status was shown in THREE places at once - the top navigation-bar pill, a "Connected --" box on the Workspace Dashboard, and a green "Companion ready --" box on Phases &amp; Runs - all reading the same underlying runner status. The two page-level boxes were redundant.</t>
+          <t xml:space="preserve">Artifacts registry + preview (frontend)</t>
         </is>
       </c>
-      <c r="I172" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">FIXED &amp; TESTED (2026-07-21). Removed the Dashboard "Companion" card and the Phases &amp; Runs "Companion ready" box (and the now-unused useRunners hook/vars they needed), leaving the top-bar pill as the single companion-status indicator. Files: frontend/src/features/observability/Dashboard.tsx, frontend/src/features/lifecycle/PhasesAndRuns.tsx.</t>
-        </is>
-      </c>
-      <c r="J172" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="173" spans="1:10" ht="409.6">
-      <c r="A173" s="2">
-        <v>172</v>
-      </c>
-      <c r="B173" s="2" t="s">
-        <v>817</v>
-      </c>
-      <c r="D173" s="2" t="s">
-        <v>818</v>
-      </c>
-      <c r="E173" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F173" s="2" t="e" vm="20">
-        <v>#VALUE!</v>
-      </c>
-      <c r="G173" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H173" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">S.No 172. The Run Console header and panel showed RAW ids (the run UUID, the Temporal workflow id, the engine) with no labels, and never showed which work item the run belonged to - so a user could not confirm the right work item was running. The work item WAS already fetched by the console, but only its title (with a UUID-slice fallback) was used, never its human key like "WI-42".</t>
-        </is>
-      </c>
-      <c r="I173" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">FIXED &amp; TESTED (2026-07-21). Led the header with the work item's key + title so the user can confirm the right item; added a labelled meta row (Work item / Run ID / Engine / Workflow) with the long ids shortened and the full value on hover; shortened the panel title. Raw ids are kept (now labelled) for debugging, per the team's note. File: frontend/src/features/lifecycle/RunConsole.tsx.</t>
-        </is>
-      </c>
-      <c r="J173" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="174" spans="1:10" ht="409.6">
-      <c r="A174" s="2">
-        <v>173</v>
-      </c>
-      <c r="B174" s="2" t="s">
-        <v>819</v>
-      </c>
-      <c r="D174" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="E174" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F174" s="2" t="e" vm="21">
-        <v>#VALUE!</v>
-      </c>
-      <c r="G174" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H174" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">S.No 173. When the companion was OFFLINE the Trigger-a-Phase card hardcoded only three phases as disabled placeholders instead of the full catalog, and the Runs card kept showing a label on the right even offline. Recon answer for the team: that right-side label is the CURRENTLY SELECTED work item's title (falling back to a UUID slice), not a "most recent run".</t>
-        </is>
-      </c>
-      <c r="I174" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">FIXED &amp; TESTED (2026-07-21). The offline Trigger card now shows the FULL phase list, greyed and non-interactive, so the user sees every phase that exists; they become clickable once the companion is online. The Runs-card right-side work-item label is now hidden when offline and shown only when online (team decision). File: frontend/src/features/lifecycle/PhasesAndRuns.tsx.</t>
-        </is>
-      </c>
-      <c r="J174" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="175" spans="1:10" ht="194.25">
-      <c r="A175" s="2">
-        <v>174</v>
-      </c>
-      <c r="B175" s="2" t="s">
-        <v>820</v>
-      </c>
-      <c r="D175" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="E175" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F175" s="2" t="e" vm="22">
-        <v>#VALUE!</v>
-      </c>
-      <c r="G175" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H175" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">S.No 174. The Clarifications page carried testing-era billing wording - a header clause "...and nothing is billed while it waits", an empty-state hint "(billing $0)", and a "Paused - no usage billed while waiting" chip - which the team decided to drop.</t>
-        </is>
-      </c>
-      <c r="I175" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">FIXED &amp; TESTED (2026-07-21). Removed the header billing clause and the "(billing $0)" hint and re-aligned the message; reworded the pause chip to "Paused - waiting for your answer" with no cost/billing mention (team asked for a billing-free wording). File: frontend/src/features/lifecycle/Clarifications.tsx.</t>
-        </is>
-      </c>
-      <c r="J175" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="176" spans="1:10" ht="409.6">
-      <c r="A176" s="2">
-        <v>175</v>
-      </c>
-      <c r="B176" s="2" t="s">
-        <v>821</v>
-      </c>
-      <c r="D176" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="E176" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F176" s="2" t="e" vm="23">
-        <v>#VALUE!</v>
-      </c>
-      <c r="G176" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H176" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">S.No 175. A "Cost (est.)" column/row and "no usage billed while waiting" text were added across many screens for testing reference and are no longer wanted. The requested recon found the same display on SEVEN screens, not just the Phases &amp; Runs Runs card.</t>
-        </is>
-      </c>
-      <c r="I176" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">FIXED &amp; TESTED (2026-07-21). Removed the cost column/row and its note EVERYWHERE - Phases &amp; Runs Runs card, Run Console, Work Item (Task and Epic) panels, Phase Console table, Run Transcript table - and reworded every "no usage billed while waiting" pause banner to "Paused - waiting for your answer"; also removed a "$0 while waiting" note on the Dashboard. 7 files. NOTE: the /dev/components design-system showcase table still has a demo COST column - left intentionally (it is the raw component gallery, not an app screen); flagged to the team.</t>
-        </is>
-      </c>
-      <c r="J176" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="177" spans="1:10">
-      <c r="A177" s="2">
-        <v>176</v>
-      </c>
-      <c r="B177" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Security phase (10) runs with NO source code to scan. The Security Agent's whole job (SAST, dependency/CVE scan, SBOM, OWASP-in-code) needs the actual repository checked out, but the phase runs as a PLANNING phase that is never given the code - so it silently degrades to reviewing documents only. A user could get a clean-looking security report where no scanner ever ran against the code.</t>
-        </is>
-      </c>
-      <c r="D177" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Security phase / Orchestration</t>
-        </is>
-      </c>
-      <c r="E177" s="2" t="inlineStr">
+      <c r="E233" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Bug</t>
         </is>
       </c>
-      <c r="F177" s="2" t="inlineStr">
+      <c r="F233" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Recon 2026-07-21. Verified: backend/apps/registry/catalog.py:72 registers 10_security with rides_build=False, so it routes trigger_phase -&gt; AgentRunWorkflow; dispatch_phase_core (backend/orchestration/activities.py) ships kind=plan with only manifest+agent_body and NO repo. Only the BUILD path provisions a git worktree. So SAST/SCA/SBOM/OWASP-in-code have nothing to scan. agents/10_security/agent.md:30 explicitly requires the companion worktree containing the full source code.</t>
+          <t xml:space="preserve">Same run as S.No 231. Follow-up to S.No 227, which stopped the gate but not the artifact. Confirmed by grep -r phase_report frontend/src returning nothing before the fix.</t>
         </is>
       </c>
-      <c r="G177" s="2" t="inlineStr">
+      <c r="G233" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P2</t>
+        </is>
+      </c>
+      <c r="H233" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">S.No 227 stamped the platform's own artifact with external_ref.source = 'phase_report' and made verify_write_completeness_core require at least one agent-registered artifact. Both are backend-only. The marker was never exposed by the preview endpoint and the frontend Artifact type had no external_ref field at all, so the UI had no way to tell the platform's copy of a closing message from a real deliverable.</t>
+        </is>
+      </c>
+      <c r="I233" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fixed. backend/integrations/preview.py returns 'source' in the preview payload. frontend/src/types.ts gains external_ref on Artifact, the shared PHASE_REPORT_ARTIFACT constant and an isPhaseReport() helper. ArtifactsRegistry shows 'Run output - not a deliverable' and a Run output badge instead of Draft; ArtifactPreviewScreen replaces the read-through banner with a warning naming what the row is and telling the reader to re-run the phase. A test asserts the marker string matches the backend's so the contract cannot drift. 6 frontend tests added. Commit b58e1f7.</t>
+        </is>
+      </c>
+      <c r="J233" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fixed</t>
+        </is>
+      </c>
+    </row>
+    <row r="234" spans="1:10" ht="232.5" x14ac:dyDescent="0.35">
+      <c r="A234" s="2">
+        <v>233</v>
+      </c>
+      <c r="B234" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The write-completeness failure message blames the agent's write tools even when the write tools worked and a different tool failed</t>
+        </is>
+      </c>
+      <c r="C234" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The run parked with a message ending 'no register_artifact at all points at the agent's write tools being absent from its context'. In this run the write tools were fine - ask_human was what broke - so the message sent the reader hunting the wrong subsystem while the real evidence (a pending clarification on the run) sat unmentioned.</t>
+        </is>
+      </c>
+      <c r="D234" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Orchestration / write-completeness (verify_write_completeness_core)</t>
+        </is>
+      </c>
+      <c r="E234" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bug</t>
+        </is>
+      </c>
+      <c r="F234" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Same run as S.No 231. The wording was correct for the run it was written for (S.No 226 - ToolSearch denylisted, granted tools deferred out of reach) and became misleading as soon as a second cause appeared.</t>
+        </is>
+      </c>
+      <c r="G234" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P2</t>
+        </is>
+      </c>
+      <c r="H234" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The message asserted a single remembered cause rather than deriving one from evidence, so it could only ever be right about the run it was authored for. The platform already holds a decisive and cheap signal it was not consulting: a PENDING Clarification on the run means the agent did reach its tools, asked, and never got an answer - at which point Rule 1 forbids it writing anything.</t>
+        </is>
+      </c>
+      <c r="I234" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fixed. backend/orchestration/activities.py: new _no_agent_artifact_reason() checks for a pending clarification on the run first. If one exists the message names it, states plainly that this is not a tooling failure, and points at the recovery that works (answer it, then re-run - answered clarifications replay into the new manifest). With no pending clarification the original tooling wording is unchanged. Only PENDING counts; an answered one means the agent got what it asked for. 3 tests added in test_rules_migration.py. Commit b58e1f7.</t>
+        </is>
+      </c>
+      <c r="J234" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fixed</t>
+        </is>
+      </c>
+    </row>
+    <row r="235" spans="1:10" ht="232.5" x14ac:dyDescent="0.35">
+      <c r="A235" s="2">
+        <v>234</v>
+      </c>
+      <c r="B235" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A clarification whose run has already ended still tells the user that answering will resume the run in the same session</t>
+        </is>
+      </c>
+      <c r="C235" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The Clarifications screen header reads 'Answering resumes the run in the same session' and the card reads 'Paused - waiting for your answer'. Once the run has ended the companion's poll loop and the engine session are both gone, so answering resumes nothing. The user is left waiting for something that cannot happen.</t>
+        </is>
+      </c>
+      <c r="D235" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Clarifications screen / clarification lifecycle</t>
+        </is>
+      </c>
+      <c r="E235" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bug</t>
+        </is>
+      </c>
+      <c r="F235" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Same run as S.No 231, whose clarification sat pending against a parked run. Adjacent to S.No 230 (stale clarification history) but a different problem.</t>
+        </is>
+      </c>
+      <c r="G235" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P2</t>
+        </is>
+      </c>
+      <c r="H235" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nothing reconciles a pending Clarification whose waiter has died, and the screen's copy assumed a live session unconditionally. Note the obvious fix is wrong: cancelling an orphaned clarification would make it UNANSWERABLE, because answer_clarification rejects any status other than PENDING - destroying the one recovery that works, since composer._render_clarifications replays answered clarifications into a re-dispatched run's manifest.</t>
+        </is>
+      </c>
+      <c r="I235" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fixed. The clarification deliberately stays PENDING and answerable; nothing is cancelled. ClarificationSerializer exposes run_status, frontend types gain isRunListening() (live only while the run is pending or running), and Clarifications.tsx shows 'This run has ended' plus an explanation that answering still helps because the answers replay on the next run. Only the promise changed. Commit b58e1f7.</t>
+        </is>
+      </c>
+      <c r="J235" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fixed</t>
+        </is>
+      </c>
+    </row>
+    <row r="236" spans="1:10" ht="232.5" x14ac:dyDescent="0.35">
+      <c r="A236" s="2">
+        <v>235</v>
+      </c>
+      <c r="B236" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Every API request opens a brand new database connection to a remote Postgres, so a single dropped handshake becomes a user-facing 500</t>
+        </is>
+      </c>
+      <c r="C236" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Intermittent OperationalError 500s across the app - 'server closed the connection unexpectedly' - most often on /api/runner/code-intel/ because that is the highest-frequency endpoint. Seen repeatedly across accounts and sessions. This is the trigger behind S.No 231.</t>
+        </is>
+      </c>
+      <c r="D236" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Database connection handling (settings.py / tenancy middleware)</t>
+        </is>
+      </c>
+      <c r="E236" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bug</t>
+        </is>
+      </c>
+      <c r="F236" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Measured 2026-08-03: 50 sequential connects to 13.203.56.29 averaged 320ms (p50 320, max 341), 0 failures at the time of measurement, so the fault is intermittent rather than reproducible on demand.</t>
+        </is>
+      </c>
+      <c r="G236" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">P1</t>
         </is>
       </c>
-      <c r="H177" s="2" t="inlineStr">
+      <c r="H236" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10_security is a planning phase (no rides_build) and the planning dispatch never checks out the work item's repo. The agent's SAST/SCA/SBOM steps require the real source in a companion worktree, which only the build path provides.</t>
+          <t xml:space="preserve">CONN_MAX_AGE is 0 and CONN_HEALTH_CHECKS is False, so Django discards and reopens a connection for every request. Each costs ~320ms of TCP+TLS+auth over the public internet. The companion polls two endpoints every 5s, about 24 new connections per minute per companion. TenantContextMiddleware calls set_current_tenant() as the first DB touch of every tenant-scoped request and nothing retries, so one failed handshake is an unhandled 500. Ruled out by measurement: not connection exhaustion (15 of 97 usable in use) and not a server crash (postmaster uptime 1d7h, no restart). Postgres also serves Temporal (9 backends) on the same host with shared_buffers at 128MB.</t>
         </is>
       </c>
-      <c r="I177" s="2" t="inlineStr">
+      <c r="I236" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">IMPLEMENTED (Fix A2, committed 2026-07-21; validated live by security run 371031a0 on 2026-07-22 - real code scanned in a read-only worktree): give repo-scoped PLANNING phases a READ-ONLY git worktree without putting them on the build/PR/merge path. New catalog flag reads_code=True on 10_security; trigger_phase resolves the work item's repo (reusing trigger_build's resolver, per-repo); dispatch carries repo/base; companion provisions a read-only worktree (branch sdlc-scan/&lt;run_id&gt;, torn down after, never committed/pushed); driver runs the planning agent with cwd in the worktree, Read/Grep/Glob allowed but Write/Edit blocked. Stays on AgentRunWorkflow so the security_engineer gate is unchanged. Also fixes 09_testing's identical latent gap via the same flag.</t>
+          <t xml:space="preserve">Not fixed. Plan: set CONN_MAX_AGE (60-600) plus CONN_HEALTH_CHECKS, and retry the connect. CONN_MAX_AGE must NOT ship without an explicit cross-tenant isolation test: set_config(..., false) is session-scoped, so a reused connection carries app.tenant_id across requests. The finally: clear_current_tenant() in TenantContextMiddleware should cover it, but 'should' is not good enough for a tenant-isolation boundary. Note no application change can make a public-internet link reliable - retry is the mitigation; a private network or a pooler beside the database is the cure. The 5s idle poll interval was deliberately left alone: raising it adds the same latency to every phase pickup for far less benefit.</t>
         </is>
       </c>
-      <c r="J177" s="2" t="inlineStr">
+      <c r="J236" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fixed</t>
+          <t xml:space="preserve">Open</t>
         </is>
       </c>
     </row>
-    <row r="178" spans="1:10">
-      <c r="A178" s="2">
-        <v>177</v>
-      </c>
-      <c r="B178" s="2" t="inlineStr">
+    <row r="237" spans="1:10" ht="232.5" x14ac:dyDescent="0.35">
+      <c r="A237" s="2">
+        <v>236</v>
+      </c>
+      <c r="B237" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Security findings never become trackable work. The Security Agent is supposed to open a defect work item for every Critical/High finding (the defect loopback), but the platform code that does this is never actually called in production - so findings just sit in the report and nothing lands on the board.</t>
+          <t xml:space="preserve">Deleting issues in Jira leaves the platform holding pointers to issues that no longer exist, with no detection and no repair path</t>
         </is>
       </c>
-      <c r="D178" s="2" t="inlineStr">
+      <c r="C237" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Security phase / Quality</t>
+          <t xml:space="preserve">After a successful backlog export the user deleted all the issues in Jira and re-exported. The dialog reported '0 work items reconciled (0 created, 1 failed)' with the Jira error 'Please select valid parent issue'. The platform's state was untouched by the deletion, so 81 items still carried keys for issues that were gone.</t>
         </is>
       </c>
-      <c r="E178" s="2" t="inlineStr">
+      <c r="D237" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Jira reconciliation / external_ref lifecycle</t>
+        </is>
+      </c>
+      <c r="E237" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Bug</t>
         </is>
       </c>
-      <c r="F178" s="2" t="inlineStr">
+      <c r="F237" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Recon 2026-07-21. Verified: backend/apps/quality/services.py:334 record_security_findings() implements the Critical/High security_finding -&gt; defect child WorkItem loopback and is exercised by tests, but a repo-wide grep of backend shows NO production caller. The only non-test reference is a comment in backend/apps/gates/testgate.py:57. So in prod the loopback is dead code.</t>
+          <t xml:space="preserve">Tenant 212395b8, project SpendLog, reported 2026-08-03. The one attempted item was WI-152, whose parent epic WI-147 still held external_ref.id ST-317 for a deleted issue. Distinct from S.No 142, which was Jira's type hierarchy rejecting a Task under a Story - this is a pointer to an issue that no longer exists.</t>
         </is>
       </c>
-      <c r="G178" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P1</t>
-        </is>
-      </c>
-      <c r="H178" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">record_security_findings() exists and is tested but is invoked only from tests - no workflow/activity/MCP/gate path calls it. Critical/High security_finding artifacts therefore never spawn defect WorkItems.</t>
-        </is>
-      </c>
-      <c r="I178" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">IMPLEMENTED (Fix B auto-defects, committed 2026-07-21; unit-tested; team accepted as Fixed 2026-07-22 without a live Critical/High run - medium/low findings intentionally do NOT open work items): wire record_security_findings() into the security run's completion so Critical/High security_finding artifacts auto-open defect child WorkItems (visible on the board), matching the tested call signature. NOTE per team decision the GATE stays advisory - the no_open_security_defects gate BLOCK is deliberately NOT added here (tracked separately as S.No 178).</t>
-        </is>
-      </c>
-      <c r="J178" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Fixed</t>
-        </is>
-      </c>
-    </row>
-    <row r="179" spans="1:10">
-      <c r="A179" s="2">
-        <v>178</v>
-      </c>
-      <c r="B179" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The security gate can be approved with open Critical findings. The agent's contract says the gate must not be grantable while any Critical/High finding is open, but no such rule exists in the platform - the security gate is a plain human approval.</t>
-        </is>
-      </c>
-      <c r="D179" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Security phase / Gates</t>
-        </is>
-      </c>
-      <c r="E179" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bug</t>
-        </is>
-      </c>
-      <c r="F179" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Recon 2026-07-21. Verified: backend/apps/gates/conditions.py returns conditions only for ux_design (WCAG) and testing; conditions_for_phase(security) -&gt; []. There is no conditions_for_security_phase and no no_open_security_defects derived condition. A comment in testgate.py:57 references the intent but nothing enforces it. Gate role is security_engineer (correct) but unconditioned.</t>
-        </is>
-      </c>
-      <c r="G179" s="2" t="inlineStr">
+      <c r="G237" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">P2</t>
         </is>
       </c>
-      <c r="H179" s="2" t="inlineStr">
+      <c r="H237" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">No security gate condition is wired; the gate is an unconditioned human approval, so a reviewer can approve with open Critical/High findings - contradicting agents/10_security/agent.md:329,430.</t>
+          <t xml:space="preserve">reconcile treats external_ref as durable truth and never checks the pointer still resolves in the system of record, so an external deletion creates a silent split-brain. external_ref is read-only on the API ('set by reconciliation, not by clients'), so there is no repair, force or re-publish path - recovering required direct database surgery to clear the stale pointers and rewind the states.</t>
         </is>
       </c>
-      <c r="I179" s="2" t="inlineStr">
+      <c r="I237" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">OPEN - DEFERRED by team decision 2026-07-21: for now the security gate stays ADVISORY (human approval) and findings are tracked manually / via the auto-spawned defects (S.No 177). Adding a hard no_open_security_defects gate block is deferred to a later hardening pass; logged here so it is not lost.</t>
+          <t xml:space="preserve">Not fixed. Worked around by script: snapshot the affected items, clear the SoR keys, reset state to proposed, re-export, then restore the original states (reconcile forces ACCEPTED on success, which would otherwise erase 'done' on completed work). Suggested fix: validate the pointer on re-export and treat a 404 as 'not reconciled' so register-don't-recreate can recreate it, or expose an explicit repair action.</t>
         </is>
       </c>
-      <c r="J179" s="2" t="inlineStr">
+      <c r="J237" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Open</t>
         </is>
       </c>
     </row>
-    <row r="180" spans="1:10">
-      <c r="A180" s="2">
-        <v>179</v>
-      </c>
-      <c r="B180" s="2" t="inlineStr">
+    <row r="238" spans="1:10" ht="232.5" x14ac:dyDescent="0.35">
+      <c r="A238" s="2">
+        <v>237</v>
+      </c>
+      <c r="B238" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">A blank security review passes the platform's completeness check. verify_writes only confirms that a generic artifact of type security exists - it never checks for the real security deliverables (security_review / security_finding / sbom), so an empty or missing review still passes and the gate opens on nothing.</t>
+          <t xml:space="preserve">Only proposed work items can ever be exported to the task tracker, so anything past planning can never reach Jira</t>
         </is>
       </c>
-      <c r="D180" s="2" t="inlineStr">
+      <c r="C238" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Security phase / Artifacts</t>
+          <t xml:space="preserve">Of 109 task-breakdown epics, stories and tasks in SpendLog, only 39 had ever reached Jira. The other 70 were never eligible: once a work item moves into implementation it leaves the proposed state and drops out of the export candidate set permanently. Independent of any Jira-side deletion.</t>
         </is>
       </c>
-      <c r="E180" s="2" t="inlineStr">
+      <c r="D238" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bug</t>
+          <t xml:space="preserve">Jira reconciliation (reconcile_backlog)</t>
         </is>
       </c>
-      <c r="F180" s="2" t="inlineStr">
+      <c r="E238" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Recon 2026-07-21. Verified: AgentRunWorkflow calls verify_writes with [inp.phase] = [security]; the platform auto-registers one security-typed blob from the run's final text, so verify_write_completeness_core finds type security present and PASSES. The agent's real deliverables are types security_review/security_finding/threat_model/sbom - verify_writes knows nothing about them.</t>
+          <t xml:space="preserve">Enhancement</t>
         </is>
       </c>
-      <c r="G180" s="2" t="inlineStr">
+      <c r="F238" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tenant 212395b8, project SpendLog, reported 2026-08-03. Measured: 68 done, 1 in_review, 1 in_progress and 1 proposed against 81 accepted. Surfaced alongside S.No 236 while restoring the backlog.</t>
+        </is>
+      </c>
+      <c r="G238" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">P2</t>
         </is>
       </c>
-      <c r="H180" s="2" t="inlineStr">
+      <c r="H238" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">verify_writes checks only that a generic security-typed artifact exists, not the real security artifact types, so an empty review passes the last check before the gate.</t>
+          <t xml:space="preserve">reconcile_backlog filters candidates on state=PROPOSED only. That is correct as an idempotency guard for a first export but means the export can never be re-run over a project's real backlog, and there is no way to push an implementation-phase item to the tracker at all.</t>
         </is>
       </c>
-      <c r="I180" s="2" t="inlineStr">
+      <c r="I238" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">IMPLEMENTED (Fix C, committed 2026-07-21; validated live by run 371031a0 on 2026-07-22 - security_review required and passed the completeness check): require the real security artifact type (security_review at minimum) in the security phase's expected-artifact set so an empty/blank review fails loudly instead of passing on a 0-byte generic blob.</t>
+          <t xml:space="preserve">Not fixed. Restoring the full 57-item backlog needed a snapshot/rewind/restore script because a naive rewind would have flipped 21 completed items from done to accepted and lost that history. Suggested: select candidates on 'has no SoR id' rather than on state, so an item's lifecycle stage stops deciding whether it can be tracked.</t>
         </is>
       </c>
-      <c r="J180" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Fixed</t>
-        </is>
-      </c>
-    </row>
-    <row r="181" spans="1:10">
-      <c r="A181" s="2">
-        <v>180</v>
-      </c>
-      <c r="B181" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The Security agent body omits the two-step needed to persist a large artifact. It tells the model to register artifact bodies directly, but register_artifact only takes a hash + s3 key - the body must first be staged via stage_artifact_body. Every sibling agent spells this out; the security agent does not, so a literal run could stall or mis-call register_artifact.</t>
-        </is>
-      </c>
-      <c r="D181" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Security phase / Agent</t>
-        </is>
-      </c>
-      <c r="E181" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Enhancement</t>
-        </is>
-      </c>
-      <c r="F181" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Recon 2026-07-21. Verified: agents/10_security/agent.md:329,140-144 tells the model to register_artifact bodies directly, but register_artifact (mcp_platform_state/tools.py:314) takes content_hash + s3_key, not an inline body. The body must first be staged via stage_artifact_body (tools.py:558). agents/09_testing/agent.md:243-244 spells out the two-step; the security agent omits it.</t>
-        </is>
-      </c>
-      <c r="G181" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P3</t>
-        </is>
-      </c>
-      <c r="H181" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10_security/agent.md never mentions stage_artifact_body; it instructs a direct register_artifact of the body, which the tool contract does not support. Low severity but a real inconsistency vs sibling agents.</t>
-        </is>
-      </c>
-      <c r="I181" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">IMPLEMENTED (Fix D, committed 2026-07-21; validated live by run 371031a0 on 2026-07-22 - 14 artifacts incl. large bodies staged and registered): add the stage_artifact_body -&gt; register_artifact two-step to agents/10_security/agent.md, matching the pattern agents/09_testing/agent.md already documents.</t>
-        </is>
-      </c>
-      <c r="J181" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Fixed</t>
-        </is>
-      </c>
-    </row>
-    <row r="182" spans="1:10">
-      <c r="A182" s="2">
-        <v>181</v>
-      </c>
-      <c r="B182" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Build phase: a companion-reported failure of the INITIAL build (before or at the first report) is terminal - the user cannot resume, only re-run from scratch. When the build agent's first report is status!=ok (e.g. the Claude session/usage limit is hit during the build itself, or the engine errors before reporting), the build workflow runs mark_build_failed and ends. The Run console then offers only 'Retry run' (a brand-new run), never 'Resume from where it stopped'. Every OTHER build error (open PR, merge, remediation) parks and is resumable - only this first-report failure is a dead end. S.No 162 branch-continuity helps only if a branch was already pushed; if the limit hits before any push, the whole build restarts. Blocks a user mid-build with no way to carry on.</t>
-        </is>
-      </c>
-      <c r="D182" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Build phase / Implementation</t>
-        </is>
-      </c>
-      <c r="E182" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bug</t>
-        </is>
-      </c>
-      <c r="F182" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Recon 2026-07-22. Verified: backend/orchestration/build_workflow.py:130-135 (report.status!=ok -&gt; mark_build_failed -&gt; return build_failed, terminal); the resumable _park branches are all inside the PR/review/merge block (:205,:264,:311), AFTER the first ok report; dispatch_build (:111-114) sits outside it; frontend RunConsole.tsx:236-249 shows 'Retry run' for status=failed and 'Resume' only for status=stalled.</t>
-        </is>
-      </c>
-      <c r="G182" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P2</t>
-        </is>
-      </c>
-      <c r="H182" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The initial-build report failure is routed to mark_build_failed (terminal) instead of the S.No 157 park path. dispatch_build is outside the resumable while-loop, so an engine/usage failure during it has no park branch; the Temporal workflow closes and a closed workflow can never be signalled to resume - so the only recovery is a fresh trigger.</t>
-        </is>
-      </c>
-      <c r="I182" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PLANNED (team to fix 2026-07-22): classify the initial-build report failure (reuse classify_build_failure) - when it is a usage/session/rate-limit or a transient engine failure, PARK the build as resumable (park_build, resume_from='dispatch_build') instead of mark_build_failed, so the workflow stays alive and 'Resume from where it stopped' re-dispatches; keep genuinely terminal failures on mark_build_failed. Combine with S.No 162 branch continuity so a resume continues the already-pushed branch.</t>
-        </is>
-      </c>
-      <c r="J182" s="2" t="inlineStr">
+      <c r="J238" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Open</t>
         </is>
       </c>
     </row>
-    <row r="183" spans="1:10">
-      <c r="A183" s="2">
-        <v>182</v>
-      </c>
-      <c r="B183" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Planning &amp; Scan phases (ideation..deployment, and the Security scan): a mid-run engine failure fails the whole run terminally with NO resume - the user must re-run from scratch. When the companion reports the phase status!=ok (e.g. the Claude session/usage limit is hit mid-run, or the agent/engine errors), AgentRunWorkflow runs fail_run and ends. The Run console offers only 'Retry run', which starts a brand-new run from zero - there is no 'Resume from where it stopped'. Partial work already produced (e.g. security findings already registered) is not continued. This is exactly what hit the Security run on 2026-07-21 (failed on the session limit; a rerun must redo the entire scan). Remediation-exhaust does NOT apply here (planning/scan have no remediation loop). The only resumable park on this path is the narrow verify_writes case (a run that reported OK but is missing its artifact) - not a mid-run failure.</t>
-        </is>
-      </c>
-      <c r="D183" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Planning &amp; Scan phases / Runs</t>
-        </is>
-      </c>
-      <c r="E183" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bug</t>
-        </is>
-      </c>
-      <c r="F183" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Recon 2026-07-22. Verified: backend/orchestration/workflows.py:122-127 (report.status!=ok -&gt; fail_run -&gt; return phase_failed, terminal); the only _park on this workflow is the verify_writes check at :147-159 (post-report, artifact-missing); no remediation loop exists on this workflow; frontend RunConsole.tsx:236-249 gives 'Retry run' (fresh) for status=failed.</t>
-        </is>
-      </c>
-      <c r="G183" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P1</t>
-        </is>
-      </c>
-      <c r="H183" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">A companion-reported phase failure is routed to fail_run (terminal) rather than the S.No 157 park path, which is wired ONLY around the verify_writes write-completeness check. So a mid-run engine/usage failure has no resumable branch - the workflow closes and cannot be signalled, forcing a fresh trigger. Planning/scan also produce no branch, so there is no S.No 162-style continuity to fall back on.</t>
-        </is>
-      </c>
-      <c r="I183" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PLANNED (team to fix 2026-07-22, TWO-part surgical fix - both parts required to be bulletproof; part 2 is logged separately as S.No 183): (1) On a companion-reported failure, classify it (reuse classify_phase_failure): if it is a usage/session/rate-limit or a transient engine failure, PARK the run resumable (park_run, resume_from='dispatch_phase') instead of fail_run, keeping the Temporal workflow alive so 'Resume from where it stopped' re-dispatches the remaining work; keep genuinely terminal failures on fail_run. (2) Depends on finding/artifact-level idempotency (S.No 183) so the resume/rerun continues rather than duplicating.</t>
-        </is>
-      </c>
-      <c r="J183" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="184" spans="1:10">
-      <c r="A184" s="2">
-        <v>183</v>
-      </c>
-      <c r="B184" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Planning &amp; Scan phases: no artifact/finding-level idempotency, so a re-run (or a future resume) DUPLICATES what a failed run already produced. Idempotency today is keyed by run_id only (execute_agent_core skips duplicates only within the SAME run); a fresh Retry gets a NEW run_id, so nothing dedups against the failed run's already-registered artifacts. Concretely, the Security scan that failed on 2026-07-21 had already registered findings SEC-001..004; a fresh rerun re-scans and can register the same findings again as new artifacts (and, once the defect loopback of S.No 177 is wired, could open duplicate defect work items). This makes any 'continue after a failure' unsafe and must be fixed for the S.No 182 resume to be bulletproof.</t>
-        </is>
-      </c>
-      <c r="D184" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Planning &amp; Scan phases / Artifacts</t>
-        </is>
-      </c>
-      <c r="E184" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bug</t>
-        </is>
-      </c>
-      <c r="F184" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Recon 2026-07-22. Verified: backend/orchestration/activities.py execute_agent_core is idempotent by run_id only; a re-trigger creates a new Run/run_id (frontend RunConsole.tsx:141-148 handleRetry -&gt; trigger by agent_key); security findings carry a stable external_ref finding_id (SEC-00x) but nothing dedups artifacts across runs of the same work_item+phase.</t>
-        </is>
-      </c>
-      <c r="G184" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P2</t>
-        </is>
-      </c>
-      <c r="H184" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Artifact registration has no natural key beyond run_id, so across a failed run and its fresh retry there is no dedup on (work_item, phase, expected type / finding_id); partial output from the failed run is neither reused nor suppressed - it is duplicated.</t>
-        </is>
-      </c>
-      <c r="I184" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PLANNED (team to fix 2026-07-22): add finding/artifact-level idempotency keyed on a stable natural key - for findings the external_ref finding_id (SEC-00x); for phase artifacts (work_item, phase, type). On register, upsert by that key within the work_item+phase scope instead of always inserting, so a resumed or re-triggered run continues (updates/skips existing) rather than duplicating. Pairs with S.No 182.</t>
-        </is>
-      </c>
-      <c r="J184" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="185" spans="1:10">
-      <c r="A185" s="2">
-        <v>184</v>
-      </c>
-      <c r="B185" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Clarifications page: the answer dropdown's option list overflows OUTSIDE the clarification card and looks broken. The Tier-1 'choice' answer control is a native select; when the agent's options are long sentences (seen live in a build-phase clarification - TASK-033, run dd5080df - e.g. 'Create a new backlog task for expenses CRUD router (GET/POST/PATCH/DELETE /api/v1/expenses) and merge TASK-033 as-is...'), the browser-drawn option popup extends past the card's left/right edges and the long option text does not wrap, so option text spills outside the window. Cosmetic but unpolished and can push text off-screen.</t>
-        </is>
-      </c>
-      <c r="D185" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Clarifications / UI</t>
-        </is>
-      </c>
-      <c r="E185" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">UI issue</t>
-        </is>
-      </c>
-      <c r="F185" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Recon 2026-07-22. Verified: frontend/src/features/lifecycle/Clarifications.tsx:190-203 renders a native &lt;Select&gt; (design-system wrapper over &lt;select&gt;) with one &lt;option&gt; per agent-provided q.options; native &lt;select&gt; option popups are browser/OS-drawn (not in the DOM flow) so they are not clipped to the card, and native &lt;option&gt; text cannot be made to wrap - long option strings render on one line and overflow horizontally.</t>
-        </is>
-      </c>
-      <c r="G185" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P3</t>
-        </is>
-      </c>
-      <c r="H185" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The choice answer uses a native HTML select. A native select's option dropdown is rendered by the browser outside the page layout, so it is not constrained/clipped to the clarification card, and native &lt;option&gt; elements cannot be styled to wrap - long option labels render single-line and spill past the card bounds.</t>
-        </is>
-      </c>
-      <c r="I185" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PLANNED (team to fix 2026-07-22): replace the native select for clarification choices with a custom, card-constrained dropdown/listbox (popup width bounded to the field, long options wrap or truncate-with-tooltip), OR render long-option questions as a radio-button list (each option on its own wrapping line) instead of a dropdown. Preserve the isOtherOption free-text reveal behaviour (Clarifications.tsx:77).</t>
-        </is>
-      </c>
-      <c r="J185" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="186" spans="1:10">
-      <c r="A186" s="2">
-        <v>185</v>
-      </c>
-      <c r="B186" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Security phase runs entirely as a MANUAL LLM review - no real SAST/SCA/SBOM scanner actually executes. On the live EPIC-004 run (371031a0) the security_review artifact itself states: Bandit 'blocked by sandbox restrictions -&gt; full manual pass performed'; cyclonedx-bom 'unavailable in sandbox -&gt; manual generation' (the SBOM metadata tool literally reads 'Manual CycloneDX Generation'); pip-audit/npm-audit are referenced as CI-integrated but were NOT run in the scan - the python-jose CVEs came from 'manual cross-reference with NVD/OSV'. So despite Bash being enabled in the scan, it produced NO tool-verified findings. A manual/LLM pass is not equivalent to running Bandit/Semgrep/pip-audit/Trivy/syft and cannot be trusted as a real scan.</t>
-        </is>
-      </c>
-      <c r="D186" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Security phase / Companion environment</t>
-        </is>
-      </c>
-      <c r="E186" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bug</t>
-        </is>
-      </c>
-      <c r="F186" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Recon 2026-07-22 on the successful live run 371031a0 (tenant 212395b8, EPIC-004/WI-22d8bd13). Verified from the run's security_review artifact body (Step 0 Tool Selection table + 'Pass 1 - Automated SAST (Manual Equivalent)': 'Bandit tool installation was blocked by sandbox restrictions') and the sbom artifact metadata.tools = 'Manual CycloneDX Generation'. Bash allow is live (claude_driver _SCAN_DISALLOWED_TOOLS permits Bash) but the scanners are not present/installable on the companion host.</t>
-        </is>
-      </c>
-      <c r="G186" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P1</t>
-        </is>
-      </c>
-      <c r="H186" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The companion host lacks the scanner toolchain and/or network to install it; even with Bash allowed, 'pip install bandit' (and cyclonedx-bom, etc.) is blocked by the sandbox/environment, so the agent falls back to manual analysis for SAST, SCA and SBOM. Nothing provisions or verifies the scanners before the scan runs.</t>
-        </is>
-      </c>
-      <c r="I186" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PLANNED (team to fix): provision the scanner toolchain for the scan - pre-install and make invokable on the companion host (or in a dedicated scan container/image) bandit, semgrep, pip-audit, cyclonedx-bom/syft, and a working 'npm audit', with the network their vuln DBs need. Have the scan RECORD each scanner's real invocation + exit status so 'tool ran' is verifiable from evidence, not agent prose; fall back to manual only when a tool is genuinely unavailable and label it as such (see S.No 186).</t>
-        </is>
-      </c>
-      <c r="J186" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="187" spans="1:10">
-      <c r="A187" s="2">
-        <v>186</v>
-      </c>
-      <c r="B187" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Security review report OVERSTATES which tools actually ran. The 'Tool Selection' table lists Bandit/pip-audit/cyclonedx-bom as selected, and the verification checklist ticks pip-audit and npm-audit as [x] done, when in reality every one of those steps was performed MANUALLY (see S.No 185). A reader is misled into thinking the scan was tool-verified when it was an LLM manual pass. Security reports must be honest about manual-vs-tool or they give false assurance.</t>
-        </is>
-      </c>
-      <c r="D187" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Security phase / Agent (10_security)</t>
-        </is>
-      </c>
-      <c r="E187" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bug</t>
-        </is>
-      </c>
-      <c r="F187" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Recon 2026-07-22 on run 371031a0 security_review artifact: the Step 0 Tool Selection table presents tools as selected/used and the checklist marks '[x] pip-audit --requirement requirements.txt --fail-on-severity high' and '[x] npm audit --audit-level=high', though the body elsewhere says these were manual / CI-assumed and the CVEs were found by manual NVD/OSV cross-reference.</t>
-        </is>
-      </c>
-      <c r="G187" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P2</t>
-        </is>
-      </c>
-      <c r="H187" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">agents/10_security/agent.md lets the model present intended/CI tooling as if it executed in this scan; nothing constrains the report to distinguish 'tool actually run here' from 'manual equivalent' or 'assumed to run in CI'. Combined with S.No 185 (no tools present) this yields a report claiming tool coverage it does not have.</t>
-        </is>
-      </c>
-      <c r="I187" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PLANNED (team to fix): update agents/10_security/agent.md to require honest labelling - each SAST/SCA/SBOM step must be marked MANUAL vs TOOL-RUN, never tick a tool checkbox for a manual/assumed step, and CI-only checks must be labelled 'CI gate (not run in this scan)'. Best paired with S.No 185's exit-code recording so the report reflects what verifiably ran.</t>
-        </is>
-      </c>
-      <c r="J187" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="188" spans="1:10">
-      <c r="A188" s="2">
-        <v>187</v>
-      </c>
-      <c r="B188" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Artifact preview: any NON-MARKDOWN artifact body renders as an unreadable wall of text - platform-wide, not just security. The security SBOM body is valid CycloneDX 1.5 JSON, but the Artifact preview shows it as a run-on blob of dictionaries. Every other artifact happens to be markdown so only JSON bodies expose it, but ANY phase that produces a JSON (or other non-markdown) body will render broken. Must be fixed generally, for all phases.</t>
-        </is>
-      </c>
-      <c r="D188" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Artifacts / Preview (all phases)</t>
-        </is>
-      </c>
-      <c r="E188" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bug</t>
-        </is>
-      </c>
-      <c r="F188" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Recon 2026-07-22 on run 371031a0 sbom artifact (body starts with '{' = CycloneDX JSON). Verified: backend/integrations/preview.py:139-142 _read_internal returns _INTERNAL_CONTENT_TYPE ('text/markdown', line 28) for EVERY internal S3 body regardless of format; frontend ArtifactPreviewScreen.tsx:119-121 renders content_type text/markdown via &lt;Markdown&gt;, so JSON is fed to the markdown renderer. The _FORMAT_CONTENT_TYPE map (preview.py:56) is only applied to the inline external_ref.body path (line 150), never the S3-body path.</t>
-        </is>
-      </c>
-      <c r="G188" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P2</t>
-        </is>
-      </c>
-      <c r="H188" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">content_type is not derived from the artifact body - the S3-body read path hardcodes text/markdown, so a JSON (or any non-markdown) body is handed to the markdown renderer and collapses into unreadable text. There is no format detection and no content_type stored on the artifact row.</t>
-        </is>
-      </c>
-      <c r="I188" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PLANNED (team to fix, general/SOTA): make _read_internal format-aware - detect JSON (parse-check, or a stored/registered format hint) and return application/json; render JSON in the preview pretty-printed (indented) in a code block, and fall other non-markdown formats through the existing &lt;pre&gt; path rather than &lt;Markdown&gt;. Fixes the SBOM and any future non-markdown artifact across ALL phases.</t>
-        </is>
-      </c>
-      <c r="J188" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="189" spans="1:10">
-      <c r="A189" s="2">
-        <v>188</v>
-      </c>
-      <c r="B189" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Enhancement: let the user choose the security-scan target via a popup on the Security trigger. Today Security scans exactly one repo (the work item's pinned/default repo); a new/unpinned item on a multi-repo project errors out ('assign its repo... before running'), and there is no way to scan selected repos or the whole project. Team-decided flow: clicking the Security phase trigger opens a clean popup to select - (1) a specific/dedicated repo, (2) the default repo, or (3) the whole project / all repos (multi-repo); on selection the phase starts automatically. Works for a new item or one with a repo already assigned; non-disruptive to existing UI.</t>
-        </is>
-      </c>
-      <c r="D189" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Security phase / Trigger UX</t>
-        </is>
-      </c>
-      <c r="E189" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Enhancement</t>
-        </is>
-      </c>
-      <c r="F189" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Recon 2026-07-22. Verified: backend/orchestration/trigger.py:126-159 _resolve_work_item_repo resolves ONE repo (pinned -&gt; override -&gt; single default; multi-repo unpinned RAISES TriggerError) and the scan copies that whole repo into a worktree; there is no all-repos/selectable-repo path and no trigger-time repo picker.</t>
-        </is>
-      </c>
-      <c r="G189" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P3</t>
-        </is>
-      </c>
-      <c r="H189" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The scan target is resolved implicitly from the work item's single repo with no user choice; multi-repo unpinned is a hard error with no inline resolution, and whole-project coverage requires manually running Security on one work item per repo.</t>
-        </is>
-      </c>
-      <c r="I189" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PLANNED (team-decided flow): add a small, clean modal on the Security phase trigger offering (1) a specific repo, (2) the default repo, (3) the whole project/all repos; on select, resolve the repo(s) and trigger automatically - for 'whole project' fan out one scan per repo. This also removes the unpinned-multi-repo dead-end (user picks the repo in the popup instead of hitting the error). Keep existing Gates/Runs UI unchanged; only the trigger gains the modal.</t>
-        </is>
-      </c>
-      <c r="J189" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="190" spans="1:10">
-      <c r="A190" s="2">
-        <v>189</v>
-      </c>
-      <c r="B190" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gates page: when multiple phases run in parallel, multiple gates open but the user can only act on the TOP-MOST gate - the decision panel is bound to the first pending gate, so a user who wants to review/approve the 3rd gate first cannot. The pending-approvals rows are not selectable and do not drive the decision panel. Team-selected design = Option A: make each pending row selectable so clicking any gate loads THAT gate into the existing right-side decision panel (selected row highlighted), letting the user review and approve/reject any pending gate in any order. Smallest change to today's layout.</t>
-        </is>
-      </c>
-      <c r="D190" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gates / Approvals UI</t>
-        </is>
-      </c>
-      <c r="E190" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bug</t>
-        </is>
-      </c>
-      <c r="F190" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Recon 2026-07-22 (screenshot: 2 pending gates - WI-59 Merge/Tech Lead + WI-70 Phase/QA Lead - decision panel locked to the top gate). Verified: frontend Gates.tsx renders the pending list plus a single decision panel bound to the top/selected gate; the pending rows carry only a Preview link, with no row-select wiring to re-point the panel at a chosen gate.</t>
-        </is>
-      </c>
-      <c r="G190" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P2</t>
-        </is>
-      </c>
-      <c r="H190" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The decision panel is tied to a single (top/first) pending approval; the pending-approvals table rows have no selection handler to re-point the panel at a chosen gate, so out-of-order review/approval is impossible when several gates are pending at once.</t>
-        </is>
-      </c>
-      <c r="I190" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PLANNED (team-selected Option A): make each pending-approvals row selectable - clicking a row loads that gate into the existing decision panel (highlight the selected row, keep the panel layout as-is). No new drawer/cards. Preserves the current UI while allowing any pending gate to be reviewed and approved/rejected in any order.</t>
-        </is>
-      </c>
-      <c r="J190" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="191" spans="1:10">
-      <c r="A191" s="2">
-        <v>190</v>
-      </c>
-      <c r="B191" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Manifest context provisioning loses information platform-wide: get_context returns only the 50 NEWEST artifacts by recency and the Manifest Composer then caps them to the top 20, with NO type/dependency awareness. On a mature project (any phase past mid-lifecycle - e.g. CI/CD Phase 11), the oldest-but-required upstream artifacts (e.g. the Phase 4 architecture/adr) get evicted from the composed AGENTS.md, so an agent may NOT receive the exact inputs its own body declares it needs. Affects ALL agents, not just CI/CD - a definite, silent loss of information.</t>
-        </is>
-      </c>
-      <c r="D191" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Manifest Composer / get_context (all phases)</t>
-        </is>
-      </c>
-      <c r="E191" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bug</t>
-        </is>
-      </c>
-      <c r="F191" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Recon 2026-07-22 (CI/CD Phase 11 pre-test recon). Verified: mcp_platform_state/tools.py:195-262 get_context orders artifacts by -created_at and slices [:50]; the `phase` arg drives ONLY knowledge-search (tools.py:238), never artifact selection. backend/manifest/composer.py:44 max_artifacts=20 + composer.py:189-208 _render_artifacts truncate to the newest 20. agents/11_cicd/agent.md:18 expects the Phase 4 architecture/adr + Phase 10 security + Phase 9 test_report in # Relevant Artifacts, which recency+cap can silently drop.</t>
-        </is>
-      </c>
-      <c r="G191" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P2</t>
-        </is>
-      </c>
-      <c r="H191" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Artifact selection for the manifest is blind recency with a hard count cap and no per-agent dependency model - there is no declaration of which artifact TYPES an agent requires and no guarantee those reach it; newer artifacts crowd out older required ones.</t>
-        </is>
-      </c>
-      <c r="I191" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">FIXED - implemented in code (commits c00a26c / ef37bf9, 2026-07-22). Each agent now DECLARES its required upstream artifact types once in the catalog (AgentDefinition.needs_artifacts) with a needs_artifacts_for() resolver; get_context / the Manifest Composer build a GUARANTEED required tier (latest version per declared type) that is always injected and never evicted by the recency tail, so a late-lifecycle phase always receives the specific upstream inputs its body names. Verified in backend/apps/registry/catalog.py + backend/manifest/composer.py + mcp_platform_state. Paired with S.No 191.</t>
-        </is>
-      </c>
-      <c r="J191" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Fixed</t>
-        </is>
-      </c>
-    </row>
-    <row r="192" spans="1:10">
-      <c r="A192" s="2">
-        <v>191</v>
-      </c>
-      <c r="B192" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Agents cannot accurately pull a specific artifact BY TYPE mid-run: the list_artifacts platform-state tool filters only by phase/status, not by artifact type, so when a needed artifact is absent from the manifest the agent has no precise way to fetch 'the architecture artifact' - it must scan pointers by recency and guess. This is the on-demand half of the context fix; without it the guaranteed-push tier (S.No 190) has no reliable fallback.</t>
-        </is>
-      </c>
-      <c r="D192" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Platform-State MCP / list_artifacts (all agents)</t>
-        </is>
-      </c>
-      <c r="E192" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bug</t>
-        </is>
-      </c>
-      <c r="F192" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Recon 2026-07-22. Verified: mcp_platform_state/tools.py:602-613 list_artifacts(project_id, phase, status) has NO `type` filter; the companion wrapper runner/companion/state_mcp.py:51-55 likewise. get_artifact_body(id) exists (tools.py:579) but needs an id the agent can only obtain by listing. Artifacts ARE typed (backend/apps/registry/models.py:60).</t>
-        </is>
-      </c>
-      <c r="G192" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P3</t>
-        </is>
-      </c>
-      <c r="H192" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">list_artifacts predates the dependency-driven context model; type was never a filter, so 'fetch the artifact of type X' is not expressible - the agent cannot accurately recover a required input that fell outside the manifest.</t>
-        </is>
-      </c>
-      <c r="I192" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">FIXED - implemented in code (2026-07-22). list_artifacts now takes a `type` filter (mcp_platform_state/tools.py, exposed through server.py and the companion state_mcp wrapper) so an agent can pull a specific upstream artifact by type on demand - list_artifacts(type='architecture') then get_artifact_body(id) - and the Manifest Composer instructs agents to use it for any input not pre-injected. Completes the push+pull design with S.No 190. Verified: tools.py list_artifacts type-filter cites Bugs S.No 191.</t>
-        </is>
-      </c>
-      <c r="J192" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Fixed</t>
-        </is>
-      </c>
-    </row>
-    <row r="193" spans="1:10">
-      <c r="A193" s="2">
-        <v>192</v>
-      </c>
-      <c r="B193" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Invitation &amp; password-reset emails are NOT actually delivered to users - the invitee only sees the accept/reset link in the dev console (server terminal log), never in an inbox. EMAIL_BACKEND defaults to Django's console backend and there is no SendGrid (or any SMTP/API) delivery wired for production. Today an admin must copy the invitation link out of the server log and share it manually (Slack/chat). Enhancement: turn on real transactional email delivery so invited users receive their invitation (and password resets) by email.</t>
-        </is>
-      </c>
-      <c r="D193" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Auth / Tenant invitations + password reset (email delivery)</t>
-        </is>
-      </c>
-      <c r="E193" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Enhancement</t>
-        </is>
-      </c>
-      <c r="F193" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Verified 2026-07-23. The email SEND code is already complete and wired: backend/apps/tenancy/emails.py (send_invitation_email / send_password_reset_email over Django send_mail), called on invitation create (backend/api/views.py:702) and on password reset. Links are built from FRONTEND_BASE_URL. The only stub is the delivery backend: backend/config/settings.py:169 EMAIL_BACKEND defaults to django.core.mail.backends.console.EmailBackend (prints to log instead of sending).</t>
-        </is>
-      </c>
-      <c r="G193" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P3</t>
-        </is>
-      </c>
-      <c r="H193" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Intentional dev stub, not a defect. EMAIL_BACKEND is a deliberate pluggable seam set to the console backend for local dev (links print to the log). No production mail backend/credentials were configured and no SendGrid integration exists yet, so nothing is transmitted over the wire.</t>
-        </is>
-      </c>
-      <c r="I193" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PLANNED - config only, no code change needed. Recommended: use Django's built-in SMTP backend against SendGrid's SMTP relay. Set EMAIL_BACKEND=django.core.mail.backends.smtp.EmailBackend, EMAIL_HOST=smtp.sendgrid.net, EMAIL_PORT=587, EMAIL_USE_TLS=True, EMAIL_HOST_USER=apikey (literal), EMAIL_HOST_PASSWORD=&lt;SENDGRID_API_KEY&gt;, DEFAULT_FROM_EMAIL=&lt;verified sender e.g. no-reply@edvensoft.com&gt;, and a correct FRONTEND_BASE_URL. Team side (in SendGrid, not our code): (1) verify a sender or domain via DNS auth, (2) generate an API key. Effort: a few hours, mostly the SendGrid sender verification; no new Python package required. Optional polish: add an EMAIL_* block to .env.example + a short docs note so it is a drop-in when creds arrive. The same seam also switches on password-reset emails.</t>
-        </is>
-      </c>
-      <c r="J193" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="194" spans="1:10">
-      <c r="A194" s="2">
-        <v>193</v>
-      </c>
-      <c r="B194" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Triggering the CI/CD phase (11_cicd) runs the agent to completion and registers its artifacts, but the build then FAILS at the very last step: the companion's pre-push secret scan blocks the branch push, so no PR is ever opened. Live: SpendLog WI-146 run cab0535c failed with '[high_entropy_secret] docker-compose.yml:64 - dev-***rs (55 chars)'. The CICD agent's Step 3 tells it to generate a local docker-compose.yml with database + cache services but gives NO secret-handling guidance, so the agent hardcodes a real generated dev password/token literal into the compose file. The pre-push guardrail correctly flags it and blocks the push (a TRUE positive), killing the build after all agent work is done.</t>
-        </is>
-      </c>
-      <c r="D194" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CI/CD phase (11_cicd) - generated docker-compose.yml</t>
-        </is>
-      </c>
-      <c r="E194" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bug</t>
-        </is>
-      </c>
-      <c r="F194" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Verified 2026-07-23. Confirmed AGENT-SIDE: docker-compose.yml exists nowhere on the SpendLog repo default branch (TARUN51/medslot-single-repo main has only backend/Dockerfile + backend/.env.example + frontend/.env.example), and the run's branch feature/WI-79a3804c never reached GitHub (push was blocked) - so the file was freshly generated by 11_cicd this run. Scanner working as intended: runner/companion/guardrails.py:59-75 flags a secret/password/token key assigned a &gt;=20-char, high-entropy (Shannon&gt;=3.5), non-placeholder value; ${VAR}/placeholder values are skipped. agents/11_cicd/agent.md Step 3 (compose) had no no-hardcode rule, unlike Step 2 (Dockerfile: 'no secrets in the Dockerfile'). Platform passes the finding through unchanged (backend/orchestration/build_activities.py:427); run is terminal so the console shows 'Retry run'. Note S.No 130 (commit 52533c4) only made the finding readable - it did not cause or change the block.</t>
-        </is>
-      </c>
-      <c r="G194" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P2</t>
-        </is>
-      </c>
-      <c r="H194" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The 11_cicd agent body's Step 3 instructs generating a local docker-compose.yml with database + cache services (which need credentials) but - unlike the Dockerfile and Jenkinsfile steps - never says how to handle those secret values. The agent therefore hardcodes a concrete dev credential literal, which the companion's pre-push secret scan (PG14) correctly blocks. NOT a scanner defect - the scanner did its job; the agent violated the 'never hardcode secrets' principle its own quality gate already states.</t>
-        </is>
-      </c>
-      <c r="I194" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">FIXED 2026-07-23 (agent-body fix; team to re-test). agents/11_cicd/agent.md Step 3 now explicitly forbids hardcoding any secret in the compose file (even a dev DB/cache password) and requires env-var references (e.g. POSTGRES_PASSWORD: ${POSTGRES_PASSWORD} or env_file) plus a committed .env.example with placeholders only; the git-ignored real .env holds values. The Quality Gate line was also extended to cover local compose credentials, noting a hardcoded high-entropy value trips the pre-push scan. Scanner intentionally NOT weakened (that would let real secrets through). Immediate unblock: replace the literal on docker-compose.yml:64 with an env reference and re-trigger; a fresh run with the fixed agent body should no longer hardcode. VALIDATED LIVE 2026-07-23: a fresh end-to-end CICD run on SpendLog succeeded - agent wrote code, opened the PR, ran the code-review remediation loop, and merged with NO secret-scan block. Fix confirmed working.</t>
-        </is>
-      </c>
-      <c r="J194" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Fixed</t>
-        </is>
-      </c>
-    </row>
-    <row r="195" spans="1:10">
-      <c r="A195" s="2">
-        <v>194</v>
-      </c>
-      <c r="B195" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Deployment phase (12): the agent body PROMISED the platform executes the deployment. Its Completion said the platform 'on approval executes the gated production deployment... then runs the smoke tests and the monitoring window... aborting and rolling back automatically' (agent.md:140, also lines 9 and 81). But the platform does NO such thing: on deployment-gate approval the workflow runs only publish_artifacts + transition_work_item-&gt;done (workflows.py:169-178). No deploy, no smoke tests, no monitoring, no rollback exists (the GitHub integration has no pipeline-trigger/deploy API). So the agent narrated a deployment to the user that never happened - a false statement, and dangerous in front of a customer.</t>
-        </is>
-      </c>
-      <c r="D195" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Deployment phase (12_deployment) - agent body vs platform</t>
-        </is>
-      </c>
-      <c r="E195" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bug</t>
-        </is>
-      </c>
-      <c r="F195" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Recon 2026-07-23 (Phase 12 pre-test). Verified: catalog 12_deployment is NOT rides_build/reads_code -&gt; planning path (trigger.py). On approval AgentRunWorkflow runs publish_artifacts + transition_work_item only (backend/orchestration/workflows.py:169-178); no deploy/workflow_dispatch/kubectl/ssh anywhere; backend/integrations/github/codehost.py has only PR/branch/merge ops, no pipeline/deploy API. Team decision 2026-07-23: Option A (governed release package + human-run pipeline); real platform execution = Option B, logged separately (S.No 196).</t>
-        </is>
-      </c>
-      <c r="G195" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P2</t>
-        </is>
-      </c>
-      <c r="H195" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The agent body described the intended end-state (platform-executed, gated deployment) but that platform-side execution was never built. The agent therefore claims a capability the product does not have, and - running in a planning context with no environment - risks reporting fabricated smoke-test/monitoring/deploy results.</t>
-        </is>
-      </c>
-      <c r="I195" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">FIXED 2026-07-23 (Option A, team-approved). Reworded agents/12_deployment/agent.md to state the truth: the DevOps deployment-gate approval AUTHORIZES the release; the DevOps engineer then runs the documented deployment/smoke tests/monitoring via the phase-11 CD pipeline; the platform records the approval + publishes the deliverables and does NOT execute the deploy. Edited the intro, Step 5, and the Completion section, and added a Process guardrail forbidding the agent from reporting deploy/smoke/monitoring results as if it ran them. Agent-body migration string tests pass (21 passed).</t>
-        </is>
-      </c>
-      <c r="J195" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Fixed</t>
-        </is>
-      </c>
-    </row>
-    <row r="196" spans="1:10">
-      <c r="A196" s="2">
-        <v>195</v>
-      </c>
-      <c r="B196" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Deployment gate had NO readiness enforcement. The Deployment agent's whole philosophy is 'never deploy without a completed readiness checklist', but the deployment gate carried EMPTY conditions - a DevOps approver could approve the release with nothing checked. The readiness verdict the agent produces was only narrative, not a control-plane condition, so the platform never enforced it.</t>
-        </is>
-      </c>
-      <c r="D196" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Deployment gate (12) / gate conditions</t>
-        </is>
-      </c>
-      <c r="E196" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bug</t>
-        </is>
-      </c>
-      <c r="F196" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Recon 2026-07-23. Verified: conditions_for_phase (backend/apps/gates/conditions.py) composed only WCAG (ux_design) + blocking-test (testing); deployment was in neither set, so its Approval.conditions were []. The enforcement mechanism already existed - decide_gate (apps/gates/services.py:135-150) blocks approval on any unmet required condition - deployment just had no conditions attached.</t>
-        </is>
-      </c>
-      <c r="G196" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P2</t>
-        </is>
-      </c>
-      <c r="H196" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">No per-phase readiness conditions were defined for the deployment gate; the agent's Step 1 readiness checklist lived only in the prompt with no control-plane counterpart, so it was unenforceable.</t>
-        </is>
-      </c>
-      <c r="I196" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">FIXED 2026-07-23. Added backend/apps/gates/readiness.py (a reviewer-attested checklist mirroring the agent's Step 1: code quality, testing+UAT, security, migrations, rollback, on-call/comms, deliverables) and composed it into conditions_for_phase for phase 'deployment'. Enforcement + UI are automatic: decide_gate blocks approval until all required items are ticked, and the Gates page renders gate criteria via useGateCriteria. Added tests/test_readiness_gate.py - pure composition test passes; DB-backed enforcement tests run in CI. Some items could later become platform-DERIVED (e.g. open security/test defects) - noted as a future refinement.</t>
-        </is>
-      </c>
-      <c r="J196" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Fixed</t>
-        </is>
-      </c>
-    </row>
-    <row r="197" spans="1:10">
-      <c r="A197" s="2">
-        <v>196</v>
-      </c>
-      <c r="B197" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ENHANCEMENT (Option B): make production deployment a platform-EXECUTED action. Today (Option A) the deployment phase produces the release package + readiness gate, and a human runs the actual deploy via the phase-11 CD pipeline. Enhancement: on deployment-gate approval, have the platform ITSELF execute the gated deployment using the documented strategy (blue/green or canary), then run the post-deploy smoke tests and the 30-minute monitoring window, and auto-rollback on any trigger - realising end to end what the deployment agent's runbook describes.</t>
-        </is>
-      </c>
-      <c r="D197" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Deployment phase (12) - platform-executed deployment</t>
-        </is>
-      </c>
-      <c r="E197" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Enhancement</t>
-        </is>
-      </c>
-      <c r="F197" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Logged 2026-07-23 per team decision (Q1: Option A now, Option B as enhancement). No environment exists yet for SpendLog/medslot; the team will create a test env later. Scope: a post-approval execution branch in AgentRunWorkflow (or a dedicated deployment workflow) + activities to dispatch the CD pipeline (e.g. GitHub Actions workflow_dispatch - not currently in integrations/github/codehost.py), run smoke tests, poll monitoring metrics, and trigger rollback.</t>
-        </is>
-      </c>
-      <c r="G197" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P3</t>
-        </is>
-      </c>
-      <c r="H197" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Deployment execution was intentionally deferred: the agent describes it, but the platform-side deploy/smoke/monitor/rollback was never built (Option A is what ships). This is the build to close that gap.</t>
-        </is>
-      </c>
-      <c r="I197" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PLANNED (enhancement, no target date). Large build: post-approval execution path + CD-pipeline dispatch connector (workflow_dispatch/deploy API) + smoke-test + monitoring-window + auto-rollback activities. Requires a real target environment. Pairs with S.No 194 (which reworded the agent to Option A); implementing this would move the agent's Completion wording back toward platform-executes.</t>
-        </is>
-      </c>
-      <c r="J197" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="198" spans="1:10">
-      <c r="A198" s="2">
-        <v>197</v>
-      </c>
-      <c r="B198" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Greenfield flow does NOT populate the Knowledge Index, so its retrieval is dead for greenfield projects. The Knowledge Index (apps/knowledge) chunks artifact bodies into KnowledgeChunk rows and retrieve() ranks them with a hybrid of BM25 keyword + optional vector cosine (fused via Reciprocal Rank Fusion). But index_artifact is only called during brownfield onboarding - never on greenfield artifact registration/publish. So for a greenfield project retrieve() returns nothing, get_context's _retrieve_knowledge yields [], and agents rely solely on the required+situational artifact tiers. Separately, semantic search is globally OFF (EMBEDDING_PROVIDER=null) so even where chunks exist, only the keyword baseline runs and the pgvector column is empty.</t>
-        </is>
-      </c>
-      <c r="D198" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Knowledge Index / greenfield context retrieval</t>
-        </is>
-      </c>
-      <c r="E198" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Enhancement</t>
-        </is>
-      </c>
-      <c r="F198" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Verified 2026-07-23. index_artifact is called ONLY from backend/integrations/onboarding.py:400 (brownfield); no call on greenfield register/publish. Live backend env: EMBEDDING_PROVIDER=null (BM25-only; pgvector column unused). retrieve() (backend/apps/knowledge/index.py:106) already fuses BM25 + vector cosine via RRF and falls back to keyword if embeddings fail/are off. Providers built + ready: Voyage voyage-code-3 (dim 1024), Gemini gemini-embedding-001 (dim 1536); current column dim = 1536.</t>
-        </is>
-      </c>
-      <c r="G198" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P3</t>
-        </is>
-      </c>
-      <c r="H198" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">index_artifact was wired only into brownfield onboarding; greenfield artifact registration/publish never indexes. The embedding provider defaults to null (zero-cost baseline), so vectors are off platform-wide. Neither is a defect in the retrieval engine (which already does hybrid search) - it is unwired population + a disabled provider.</t>
-        </is>
-      </c>
-      <c r="I198" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PLANNED (enhancement + team decision on hybrid). (1) Populate greenfield: call index_artifact on artifact PUBLISH (gated), same path brownfield uses - publish-only (not every draft) to bound embedding cost. (2) Enable semantic search via a provider: Gemini gemini-embedding-001 (dim 1536) matches the current column so NO re-migration; Voyage voyage-code-3 (dim 1024, code-optimized) would need a column re-migration + re-embed. (3) KEEP the hybrid (team idea, already implemented): retrieve() fuses BM25 + vector via RRF so keyword covers exact identifiers, vectors cover meaning/synonyms, and it degrades gracefully to keyword-only if embeddings are off/fail. Pros of vector: semantic match, better on mature projects, fits agents' NL queries. Cons: per-chunk API cost+latency, external dependency/keys, dimension lock-in at migration, weaker on exact tokens, extra privacy egress. Net: enable greenfield population + turn on Gemini, keep both methods fused.</t>
-        </is>
-      </c>
-      <c r="J198" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="199" spans="1:10">
-      <c r="A199" s="2">
-        <v>198</v>
-      </c>
-      <c r="B199" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Connect-machine token generation fails silently when the workspace has no project, and the UI shows a fake placeholder token instead of the real error. A new member (e.g. a QA tester) creates a workspace but has not created a project yet, opens "Connect your machine" and clicks "Generate enrollment token". The screen appears to produce a token and shows the companion serve command, but the token displayed is a hardcoded placeholder "rnr_3f9a…b2" (note the literal ellipsis) — not a real token — so the companion cannot authenticate. Reported by a QA member who ran: python -m runner.companion serve --api-url http://localhost:8000 --tenant ce135c3e-... --token rnr_3f9a…b2. A genuine token is a ~43-character secrets.token_urlsafe(32) string with no rnr_ prefix and no ellipsis, so what he copied was never a real (or partial) token — generation had actually failed and the failure was masked as a valid-looking token.</t>
-        </is>
-      </c>
-      <c r="D199" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Connect Machine / companion enrollment (S-06)</t>
-        </is>
-      </c>
-      <c r="E199" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bug</t>
-        </is>
-      </c>
-      <c r="F199" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Reported 2026-07-24 by a QA member on a newly-created workspace that had no project yet. Verified in code (no screenshot): the string "rnr_3f9a…b2" is a hardcoded mock placeholder, not a truncated real token.</t>
-        </is>
-      </c>
-      <c r="G199" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P2</t>
-        </is>
-      </c>
-      <c r="H199" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Two layers. (1) The enroll endpoint requires a valid project: RunnerEnrollmentView.post (backend/api/runner_views.py:165-170) returns HTTP 400 ("project_id required" / "not found in tenant") when project_id is missing/invalid. (2) The Connect-machine screen picks the project from currentUser.memberships[0].project_id (frontend/src/features/identity/ConnectMachine.tsx:64); a brand-new workspace with no project has no membership, so project_id is empty and the POST 400s. The onGenerate catch block (ConnectMachine.tsx:68-70) swallows that error and calls setToken("rnr_3f9a…b2") — the same hardcoded placeholder used as the null fallback at line 61 — so a failed generation is rendered as a real-looking, copyable token instead of the backend's actual message. Net: there was no project to enroll the companion against, but the UI hid that behind a mock token. Same "fake mock data hides a real failure" pattern already fixed once on the invite-accept page (commit b77bdff).</t>
-        </is>
-      </c>
-      <c r="I199" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PLANNED (not yet fixed). Immediate workaround: the member must create a project (and be a member of it) before generating the token — then the button returns a real ~43-char token and the serve command authenticates. Proper fix (frontend, ConnectMachine.tsx): on token-generate failure, surface the backend's real error message and do NOT fall back to a hardcoded token; guard the flow when the user has no project yet (show a clear "create a project first" prompt) instead of posting an empty project_id; and ensure the placeholder mock value can never be presented as a copyable token.</t>
-        </is>
-      </c>
-      <c r="J199" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="200" spans="1:10">
-      <c r="A200" s="2">
-        <v>199</v>
-      </c>
-      <c r="B200" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">09b test-automation run parks with a Postgres DataError ("unsupported Unicode escape sequence ... \u0000 cannot be converted to text") after the PR and artifacts have already been created, even when the generated test itself passed. Reproduced twice on the same test case (WI-95 / TC-001): runs 1299c7de and e583a454 both parked identically with the same corrupted bytes, though neither companion report itself contained a NUL.</t>
-        </is>
-      </c>
-      <c r="D200" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">09b Test Automation / code review manifest</t>
-        </is>
-      </c>
-      <c r="E200" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bug</t>
-        </is>
-      </c>
-      <c r="F200" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Reproduced 2026-07-22, tenant 212395b8-f118-4eef-93eb-ba2c45468226, WI-95 (TC-001), repo TARUN51/medslot-single-repo, PR #31. Confirmed via list_pr_files + get_file that tests/automated/playwright-report/data/*.webm and *.png contained NUL bytes.</t>
-        </is>
-      </c>
-      <c r="G200" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P1</t>
-        </is>
-      </c>
-      <c r="H200" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">AgentReviewProvider._render_pr_section (backend/orchestration/review_provider.py:225-245) inlines the content of every PR-changed file into the review manifest, which dispatch_review_task then stores in the JSON run.inputs column. A 09b build commits Playwright report artifacts (screenshots/videos) into the PR; those binaries contain NUL, which Postgres text/jsonb cannot store, so the save fails with DataError and the workflow parks the run as "pr/gate setup failed" - after the PR/test_report/code artifacts already registered successfully. See S.No 201 for the fix that stops new binaries from being committed in the first place.</t>
-        </is>
-      </c>
-      <c r="I200" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Fixed. _render_pr_section now skips any file whose content contains a NUL byte (a binary marker) and inlines a "(binary file - omitted from review)" placeholder instead (review_provider.py:246-252). dispatch_review_task also scrubs NUL from the whole payload before saving, as defense-in-depth, via a shared build_types.scrub_nul helper; companion build reports are scrubbed the same way in build_report.py. Tests: test_render_pr_section_omits_binary_files, test_dispatch_review_task_scrubs_nul (test_review_dispatch.py), test_report_scrubs_nul_bytes_before_persisting (test_build_report_api.py).</t>
-        </is>
-      </c>
-      <c r="J200" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Fixed</t>
-        </is>
-      </c>
-    </row>
-    <row r="201" spans="1:10">
-      <c r="A201" s="2">
-        <v>200</v>
-      </c>
-      <c r="B201" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">A 09b remediation build (auto-fixing a code-review finding) fails immediately with "no preview target for this repo - set the repo's Preview URL...", even though the repo's Preview URL was already set and the initial build had just run successfully against it.</t>
-        </is>
-      </c>
-      <c r="D201" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">09b Test Automation / remediation loop</t>
-        </is>
-      </c>
-      <c r="E201" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bug</t>
-        </is>
-      </c>
-      <c r="F201" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Reproduced 2026-07-22 on WI-95/TC-001 after the 08 review opened REM-W2/REM-W3; the run went straight to status=failed right after the build.remediation_dispatched event.</t>
-        </is>
-      </c>
-      <c r="G201" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P1</t>
-        </is>
-      </c>
-      <c r="H201" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">dispatch_build_core (backend/orchestration/build_activities.py:62-81) ships payload['preview_url']/['preview_start'] for the test_automation phase, but dispatch_remediation_core (build_activities.py:781-826), which re-dispatches 09b to fix review findings, built its payload without that block - so the companion's remediation build had no preview target and its fail-loud guard tripped instantly. See S.No 199 for the review-manifest bug found on the same run.</t>
-        </is>
-      </c>
-      <c r="I201" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Fixed. dispatch_remediation_core now ships the same preview_url/preview_start (resolved via apps.projects.preview_config), phase-gated identically to the initial dispatch (build_activities.py:816-822). Test: test_dispatch_remediation_ships_preview_for_test_automation (test_review_dispatch.py).</t>
-        </is>
-      </c>
-      <c r="J201" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Fixed</t>
-        </is>
-      </c>
-    </row>
-    <row r="202" spans="1:10">
-      <c r="A202" s="2">
-        <v>201</v>
-      </c>
-      <c r="B202" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The 09b test-automation agent commits its own generated run output (Playwright HTML report, test-results, MCP exploration snapshots) into the PR alongside the authored test script. These directories are bulky (one PR carried a 533KB report index.html plus screenshots and a video) and can contain binary files - the root cause of the review-manifest NUL crash at S.No 199. The 08 code review itself independently flagged this as a finding (REM-W1: "Generated Playwright artifacts... committed").</t>
-        </is>
-      </c>
-      <c r="D202" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">09b Test Automation / generated worktree output</t>
-        </is>
-      </c>
-      <c r="E202" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Enhancement</t>
-        </is>
-      </c>
-      <c r="F202" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Observed 2026-07-22, PR #31 (medslot-single-repo): tests/automated/playwright-report/, tests/automated/test-results/, and .playwright-mcp/ were all committed by the build.</t>
-        </is>
-      </c>
-      <c r="G202" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P2</t>
-        </is>
-      </c>
-      <c r="H202" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The 09b agent body had no instruction to ignore generated run/report output, so every file the dry run (Step 6) or Playwright MCP (Step 4) wrote into the worktree was committed by the platform, which commits everything present in the worktree.</t>
-        </is>
-      </c>
-      <c r="I202" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Fixed. Added a required ".gitignore" step to agents/09b_test_automation/agent.md Step 3 (Scaffolding Detection, line 123 on): the agent creates/extends a worktree-root .gitignore excluding .playwright-mcp/, playwright-report/, test-results/, blob-report/, and framework build/cache directories, while still committing the authored test scripts, page objects, and config. Note: does not retroactively untrack files a prior run already committed on the same branch - see S.No 205.</t>
-        </is>
-      </c>
-      <c r="J202" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Fixed</t>
-        </is>
-      </c>
-    </row>
-    <row r="203" spans="1:10">
-      <c r="A203" s="2">
-        <v>202</v>
-      </c>
-      <c r="B203" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The "Test cases" coverage screen (per-story test-case list with automation status + Generate script) has no link anywhere in the UI - it is only reachable by typing its URL (/work-items/:id/test-cases) directly.</t>
-        </is>
-      </c>
-      <c r="D203" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Test cases (P3-09b coverage screen)</t>
-        </is>
-      </c>
-      <c r="E203" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Enhancement</t>
-        </is>
-      </c>
-      <c r="F203" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Observed 2026-07-22 while trying to generate a script for TC-001 on WI-70: the epic/story detail page had no way to navigate to its test cases.</t>
-        </is>
-      </c>
-      <c r="G203" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P2</t>
-        </is>
-      </c>
-      <c r="H203" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The coverage screen (frontend/src/features/lifecycle/TestCases.tsx) and its route were built, but the intended entry point (a tabbed story/epic detail) was deferred as a later enhancement, and no interim link was added in the meantime.</t>
-        </is>
-      </c>
-      <c r="I203" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Fixed. Added a "Test cases" button to the work-item detail header (frontend/src/features/lifecycle/WorkItemEpic.tsx:88-92), linking to /work-items/:id/test-cases. The tabbed story/epic detail remains a separately deferred enhancement.</t>
-        </is>
-      </c>
-      <c r="J203" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Fixed</t>
-        </is>
-      </c>
-    </row>
-    <row r="204" spans="1:10">
-      <c r="A204" s="2">
-        <v>203</v>
-      </c>
-      <c r="B204" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The companion always runs the 09b Playwright MCP (and the generated test suite) headless, so a developer watching a run locally has no way to see the agent explore the app or the test execute, even while attended at the keyboard.</t>
-        </is>
-      </c>
-      <c r="D204" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Companion runner / 09b Live Application Exploration</t>
-        </is>
-      </c>
-      <c r="E204" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Enhancement</t>
-        </is>
-      </c>
-      <c r="F204" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Requested 2026-07-22, to observe a local 09b run end-to-end (locator discovery + test execution) for QA/demo purposes.</t>
-        </is>
-      </c>
-      <c r="G204" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P3</t>
-        </is>
-      </c>
-      <c r="H204" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">build_mcp_servers always passed --headless to the Playwright MCP (runner/companion/runner.py), and the agent's generated Playwright config had no signal telling it to run visibly instead.</t>
-        </is>
-      </c>
-      <c r="I204" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Fixed. Added SDLC_COMPANION_HEADED, read by _headed_enabled() (runner/companion/runner.py:112-117): drops --headless from the Playwright MCP, and manifest_with_preview injects an instruction so the agent generates "headless: !process.env.SDLC_COMPANION_HEADED" in playwright.config.ts, so the same config still runs headless in CI. Added "serve --headed" as a first-class flag (runner/companion/__main__.py:110-115) that sets the env var in-process, so no separate shell export is needed. Default remains headless.</t>
-        </is>
-      </c>
-      <c r="J204" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Fixed</t>
-        </is>
-      </c>
-    </row>
-    <row r="205" spans="1:10">
-      <c r="A205" s="2">
-        <v>204</v>
-      </c>
-      <c r="B205" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">In Phases &amp; Runs, every catalog phase (Ideation .. Deployment) is shown as triggerable for ANY work-item type, including a test_case WI - a user can trigger "Ideation" or "Task Breakdown" on a test case, which is meaningless for that type and only 09b_test_automation should apply.</t>
-        </is>
-      </c>
-      <c r="D205" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Phases &amp; Runs / phase catalog</t>
-        </is>
-      </c>
-      <c r="E205" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Enhancement</t>
-        </is>
-      </c>
-      <c r="F205" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Observed 2026-07-22 while triggering 09b Test Automation on a test_case work item (WI-95): all ~16 phases appeared as trigger options, not just Test Automation.</t>
-        </is>
-      </c>
-      <c r="G205" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P3</t>
-        </is>
-      </c>
-      <c r="H205" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">There is no per-WI-type phase gating in the trigger UI or backend catalog - the phase picker (frontend/src/features/lifecycle/PhasesAndRuns.tsx) renders every catalog entry regardless of the selected work item's type.</t>
-        </is>
-      </c>
-      <c r="I205" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Not fixed - deferred. Would need the phase catalog (or the picker) to filter by work_item.type, e.g. only 09b_test_automation (and perhaps re-running 09_testing) for type=test_case.</t>
-        </is>
-      </c>
-      <c r="J205" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="206" spans="1:10">
-      <c r="A206" s="2">
-        <v>205</v>
-      </c>
-      <c r="B206" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">A .gitignore added by the 09b agent (S.No 201) only stops NEW files from being committed going forward - it does not untrack files a prior run on the SAME branch already committed (e.g. Playwright report binaries from an earlier attempt). Resuming or remediating on an existing branch/PR can therefore keep re-triggering the code review's binary-artifact finding (REM-W1, S.No 199) even after the .gitignore fix ships.</t>
-        </is>
-      </c>
-      <c r="D206" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">09b Test Automation / worktree branch reuse</t>
-        </is>
-      </c>
-      <c r="E206" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Enhancement</t>
-        </is>
-      </c>
-      <c r="F206" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Observed 2026-07-22: re-running 09b on the same branch/PR (#31) after adding the .gitignore rule still showed the previously-committed playwright-report binaries until the branch was closed and recreated from scratch.</t>
-        </is>
-      </c>
-      <c r="G206" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P3</t>
-        </is>
-      </c>
-      <c r="H206" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Git's .gitignore only governs untracked files from that point forward; files already added to the index/history stay tracked. The platform reuses the existing branch/worktree for a resumed or re-triggered build (register-don't-recreate), so old committed binaries persist across runs.</t>
-        </is>
-      </c>
-      <c r="I206" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Not fixed - workaround documented: close the PR, delete the remote branch, and let 09b start a fresh branch so the new .gitignore takes effect from the first commit. A platform-side fix (e.g. "git rm --cached" the newly-ignored paths on resume) is not implemented.</t>
-        </is>
-      </c>
-      <c r="J206" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="207" spans="1:10">
-      <c r="A207" s="2">
-        <v>206</v>
-      </c>
-      <c r="B207" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">A build (or phase) Run dispatched with inputs.dispatch.enrollment_id=null matched no companion in the claim query, so it sat running+pending forever, invisible in the UI, and blocked new triggers on the same WorkItem.</t>
-        </is>
-      </c>
-      <c r="D207" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Runner dispatch / claim (RunnerWorkClaimView)</t>
-        </is>
-      </c>
-      <c r="E207" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bug</t>
-        </is>
-      </c>
-      <c r="F207" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Surfaced 2026-07-21, tenant 212395b8-f118-4eef-93eb-ba2c45468226. Two paths hit it: the S.No 161 remediation auto-retry called trigger_build without triggered_by, and a user triggering before their companion enrolled. Validated live: run 812577a3 self-healed after the fix.</t>
-        </is>
-      </c>
-      <c r="G207" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P1</t>
-        </is>
-      </c>
-      <c r="H207" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">RunnerWorkClaimView's claim query only matched Run.inputs.dispatch.enrollment_id == runner.id - a dispatch created with enrollment_id=null (no companion known yet) matched nothing, so no companion could ever claim it.</t>
-        </is>
-      </c>
-      <c r="I207" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Fixed. backend/api/runner_views.py: the claim query now also broadcast-matches any pending/claimed dispatch with enrollment_id null/empty for the same tenant+project, and binds enrollment_id to the claiming companion. backend/orchestration/build_activities.py: handle_remediation_exhausted_core now forwards triggered_by into the retry's trigger_build call so retries route to the original companion instead of null. Tests added in test_phase_dispatch.py, test_build_activities.py.</t>
-        </is>
-      </c>
-      <c r="J207" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Fixed</t>
-        </is>
-      </c>
-    </row>
-    <row r="208" spans="1:10">
-      <c r="A208" s="2">
-        <v>207</v>
-      </c>
-      <c r="B208" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Clicking Retry run on a build whose feature branch a prior attempt had already pushed failed with "Empty build: the agent produced no changes to commit", even though real work already existed on the branch.</t>
-        </is>
-      </c>
-      <c r="D208" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Companion build retry / worktree (runner/companion)</t>
-        </is>
-      </c>
-      <c r="E208" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bug</t>
-        </is>
-      </c>
-      <c r="F208" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Surfaced 2026-07-21 on WI-45's retry after a companion redeploy. Validated live on WI-f717ea04 (merged) after the fix; also validated with a standalone host git script reproducing the exact retry scenario.</t>
-        </is>
-      </c>
-      <c r="G208" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P1</t>
-        </is>
-      </c>
-      <c r="H208" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">S.No 162's branch-continuity provisions the retry worktree from the branch's remote tip, not local/base. If the agent makes no new local commit on retry (the real work is already on the pushed branch), run_build left head_sha empty, and the empty-build guard failed the run even though the branch has real commits ahead of base.</t>
-        </is>
-      </c>
-      <c r="I208" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Fixed. runner/companion/worktree.py adds commits_ahead_of_base(). runner/companion/runner.py's run_build now reports the existing branch tip as head_sha when there's no new local commit but the branch is already ahead of base, so the saga opens/continues the PR against the existing work instead of false-failing. Tests added in test_companion_runner.py.</t>
-        </is>
-      </c>
-      <c r="J208" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Fixed</t>
-        </is>
-      </c>
-    </row>
-    <row r="209" spans="1:10">
-      <c r="A209" s="2">
-        <v>208</v>
-      </c>
-      <c r="B209" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Follow-up to S.No 161: when remediation exhausts an attempt and the platform auto-starts a fresh run, the user got no proactive signal - the failed run's console showed 'auto-retrying' text but no link to the new run, so a WorkItem appeared to show a failed run AND a separate pending gate with nothing connecting them.</t>
-        </is>
-      </c>
-      <c r="D209" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Run console / lifecycle (RunConsole.tsx)</t>
-        </is>
-      </c>
-      <c r="E209" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Enhancement</t>
-        </is>
-      </c>
-      <c r="F209" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Confirmed this confused a user reviewing WI-43's gate. Backend already stored retry_run_id on the failed run's outputs (build_activities.py); zero frontend references to it before this fix.</t>
-        </is>
-      </c>
-      <c r="G209" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P2</t>
-        </is>
-      </c>
-      <c r="H209" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The notification bell only counts pending gates + clarifications (AppShell.tsx bellCount), and the failed-run view never rendered the stored outputs.retry_run_id, so the two runs for the same WorkItem appeared unrelated.</t>
-        </is>
-      </c>
-      <c r="I209" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Fixed. frontend/src/features/lifecycle/RunConsole.tsx: the failed view now reads outputs.retry_run_id, shows an info banner ("The platform started a fresh attempt...") with a live status link to the retry run, and swaps the primary action to "Go to the retry run -&gt;" when one exists. Shipped as PR #7, merged to develop (aafd1f9).</t>
-        </is>
-      </c>
-      <c r="J209" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Fixed</t>
-        </is>
-      </c>
-    </row>
-    <row r="210" spans="1:10">
-      <c r="A210" s="2">
-        <v>209</v>
-      </c>
-      <c r="B210" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">When a companion dies/hangs mid-build (e.g. crashes during a remediation cycle), the claimed run just sits running with no user-facing signal until the orchestrator's takeover reconciler eventually fires and fails it - the user has no way to know earlier that their companion needs restarting.</t>
-        </is>
-      </c>
-      <c r="D210" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Runner heartbeat / takeover reconciler</t>
-        </is>
-      </c>
-      <c r="E210" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Enhancement</t>
-        </is>
-      </c>
-      <c r="F210" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Observed 2026-07-22 on WI-59 (run 925e7fde): companion 4a34ecf2's last heartbeat was 06:50:55 UTC; the run sat claimed/running with zero new events until "Build takeover - runner offline / no report before timeout" finally fired and failed it, well over an hour later. Retriggering after restarting the companion completed the build successfully.</t>
-        </is>
-      </c>
-      <c r="G210" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P3</t>
-        </is>
-      </c>
-      <c r="H210" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The takeover timeout is the only mechanism that reconciles a dead companion's claim; there is no earlier heartbeat-staleness check that surfaces a warning to the user while the run is still nominally in-flight.</t>
-        </is>
-      </c>
-      <c r="I210" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Not fixed. Suggested: surface a "companion appears offline" warning on the run console (and/or the companion status pill) once RunnerEnrollment.last_seen exceeds the ONLINE_THRESHOLD for a run that is still claimed/running, instead of waiting for the full takeover window.</t>
-        </is>
-      </c>
-      <c r="J210" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="211" spans="1:10">
-      <c r="A211" s="2">
-        <v>210</v>
-      </c>
-      <c r="B211" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Two independently-dispatched work items (TASK-021 ExpenseRepository CRUD and TASK-033 DashboardService) each implemented get_monthly_total/get_category_breakdown/get_recent on the same repository class, with different return contracts (plain tuples vs a CategoryTotal dataclass) - since neither WI's planning had visibility into the other's in-flight interface, it only surfaced as an add/add merge conflict when both branches reached main.</t>
-        </is>
-      </c>
-      <c r="D211" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Work-item decomposition / planning - parallel WI interface overlap</t>
-        </is>
-      </c>
-      <c r="E211" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Enhancement</t>
-        </is>
-      </c>
-      <c r="F211" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Surfaced 2026-07-22 resolving WI-59's merge gate conflict against main (already carrying WI-35's merged CRUD repository). Resolved by keeping main's superset repository and adapting DashboardService/tests to the CategoryTotal contract; validated with the full backend suite (412 passed).</t>
-        </is>
-      </c>
-      <c r="G211" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P2</t>
-        </is>
-      </c>
-      <c r="H211" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Planning dispatches WIs against the same file/class independently when their scopes overlap (both needed the same three read methods), with no shared interface contract or ownership check between them before they diverge in the codebase - the S.No 137 recon closed a similar-looking report as a false alarm, but this is a real, reproduced instance of the same class of problem.</t>
-        </is>
-      </c>
-      <c r="I211" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Not fixed generally (this instance resolved manually). Suggested: when planning dispatches multiple WIs that touch the same file/module, either serialize them or require an explicit shared interface note so the return contract is agreed before either branch is built.</t>
-        </is>
-      </c>
-      <c r="J211" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="212" spans="1:10">
-      <c r="A212" s="2">
-        <v>211</v>
-      </c>
-      <c r="B212" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">No uniqueness check on project name — duplicates are created silently</t>
-        </is>
-      </c>
-      <c r="D212" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Project Setup</t>
-        </is>
-      </c>
-      <c r="E212" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bug</t>
-        </is>
-      </c>
-      <c r="G212" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P2</t>
-        </is>
-      </c>
-      <c r="H212" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Project.name has no unique constraint and the create endpoint is stock DRF, so creating a second project with an existing name succeeds. The workspace ends up with two identically-named projects and the top-bar selector cannot tell them apart. Found by the pre-execution QA audit of the greenfield test pack (docs/qa/AUDIT_FINDINGS.md).</t>
-        </is>
-      </c>
-      <c r="J212" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="213" spans="1:10">
-      <c r="A213" s="2">
-        <v>212</v>
-      </c>
-      <c r="B213" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">'Set default' on Repositories does nothing — the backend endpoint exists but nothing calls it</t>
-        </is>
-      </c>
-      <c r="D213" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Repositories</t>
-        </is>
-      </c>
-      <c r="E213" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bug</t>
-        </is>
-      </c>
-      <c r="G213" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P3</t>
-        </is>
-      </c>
-      <c r="H213" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">POST .../set-default is implemented and permission-gated on the backend, but the frontend click handler is an empty stub. The control looks live and silently does nothing. Found by the pre-execution QA audit of the greenfield test pack (docs/qa/AUDIT_FINDINGS.md).</t>
-        </is>
-      </c>
-      <c r="J213" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="214" spans="1:10">
-      <c r="A214" s="2">
-        <v>213</v>
-      </c>
-      <c r="B214" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Lifecycle rail ignores the tier it computes — a task shows plan phases</t>
-        </is>
-      </c>
-      <c r="D214" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Work Items</t>
-        </is>
-      </c>
-      <c r="E214" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bug</t>
-        </is>
-      </c>
-      <c r="G214" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P2</t>
-        </is>
-      </c>
-      <c r="H214" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The lifecycle endpoint computes the work item's tier and then never uses it, emitting one node per registered spec regardless. A build-tier task renders the plan-tier phase rail, and the 'No phases run yet.' empty state can never appear. Found by the pre-execution QA audit of the greenfield test pack (docs/qa/AUDIT_FINDINGS.md).</t>
-        </is>
-      </c>
-      <c r="J214" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="215" spans="1:10">
-      <c r="A215" s="2">
-        <v>214</v>
-      </c>
-      <c r="B215" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Project create, profile edit, work-item write, phase trigger, run takeover and companion enroll are unauthenticated</t>
-        </is>
-      </c>
-      <c r="D215" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Platform / Permissions</t>
-        </is>
-      </c>
-      <c r="E215" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bug</t>
-        </is>
-      </c>
-      <c r="G215" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P1</t>
-        </is>
-      </c>
-      <c r="H215" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">DRF's project-wide default permission is AllowAny, and these endpoints never override it. A plain engineer with no admin grant can create projects, rewrite the project profile that every agent reads, create and edit work items, trigger phase runs, take over a run, and enroll a companion machine. Found by the pre-execution QA audit of the greenfield test pack (docs/qa/AUDIT_FINDINGS.md).</t>
-        </is>
-      </c>
-      <c r="J215" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="216" spans="1:10">
-      <c r="A216" s="2">
-        <v>215</v>
-      </c>
-      <c r="B216" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">A newly created test case does not appear until the page is reloaded</t>
-        </is>
-      </c>
-      <c r="D216" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Test Cases</t>
-        </is>
-      </c>
-      <c r="E216" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bug</t>
-        </is>
-      </c>
-      <c r="G216" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P3</t>
-        </is>
-      </c>
-      <c r="H216" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The create mutation invalidates the ['work-items'] query key, but the test-case table reads ['test-cases']. Nothing invalidates the list the user is looking at. Found by the pre-execution QA audit of the greenfield test pack (docs/qa/AUDIT_FINDINGS.md).</t>
-        </is>
-      </c>
-      <c r="J216" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="217" spans="1:10">
-      <c r="A217" s="2">
-        <v>216</v>
-      </c>
-      <c r="B217" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">takeover_flag is set and released but never read as a guard</t>
-        </is>
-      </c>
-      <c r="D217" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Recovery &amp; Takeover</t>
-        </is>
-      </c>
-      <c r="E217" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bug</t>
-        </is>
-      </c>
-      <c r="G217" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P3</t>
-        </is>
-      </c>
-      <c r="H217" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The flag's only reader in the backend is the manifest renderer. Trigger admission is decided purely by run status, so the flag guards nothing — and the timeout park sets it itself before any human acts. Found by the pre-execution QA audit of the greenfield test pack (docs/qa/AUDIT_FINDINGS.md).</t>
-        </is>
-      </c>
-      <c r="J217" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="218" spans="1:10">
-      <c r="A218" s="2">
-        <v>217</v>
-      </c>
-      <c r="B218" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">/recovery?run=&lt;id&gt; is inert — there is no way to take over a named run</t>
-        </is>
-      </c>
-      <c r="D218" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Recovery &amp; Takeover</t>
-        </is>
-      </c>
-      <c r="E218" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bug</t>
-        </is>
-      </c>
-      <c r="G218" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P2</t>
-        </is>
-      </c>
-      <c r="H218" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The recovery screen always targets the first stalled-or-failed run it finds in the project. When a ?run= parameter is supplied the target is forced undefined and the screen renders 'No parked runs', so the deep link is worse than useless. 'Take over instead' on the run console also navigates without a run parameter. Found by the pre-execution QA audit of the greenfield test pack (docs/qa/AUDIT_FINDINGS.md).</t>
-        </is>
-      </c>
-      <c r="J218" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="219" spans="1:10">
-      <c r="A219" s="2">
-        <v>218</v>
-      </c>
-      <c r="B219" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Five pieces of dead UI code that can never render</t>
-        </is>
-      </c>
-      <c r="D219" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Platform / UI</t>
-        </is>
-      </c>
-      <c r="E219" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bug</t>
-        </is>
-      </c>
-      <c r="G219" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P3</t>
-        </is>
-      </c>
-      <c r="H219" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The 'Pending gate' artifact badge and its traceability legend colour (pending_gate is not an artifact status); the 'running' work-item badge (not a WorkItem state); the roles gap banner (its condition requires no admin fallback, and a tenant admin always exists); the 'A description is required' validation (gallery-only); the 'Preview unavailable' state for internal artifacts (they 404 to 'Artifact not found' first); and the 'Platform only' system-of-record label (sor is never blank). Found by the pre-execution QA audit of the greenfield test pack (docs/qa/AUDIT_FINDINGS.md).</t>
-        </is>
-      </c>
-      <c r="J219" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="220" spans="1:10">
-      <c r="A220" s="2">
-        <v>219</v>
-      </c>
-      <c r="B220" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Silent failure paths — several actions fail with no message at all</t>
-        </is>
-      </c>
-      <c r="D220" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Platform / UI</t>
-        </is>
-      </c>
-      <c r="E220" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bug</t>
-        </is>
-      </c>
-      <c r="G220" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P2</t>
-        </is>
-      </c>
-      <c r="H220" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Invite resend and revoke have no error handler and the screen has no error surface; a repository 403 is swallowed; GenerateCell trigger errors are dropped; and a short password on accept-invite and on reset, plus a blank signup name, all 400 with the form left untouched. The user cannot tell a failure from a no-op. Found by the pre-execution QA audit of the greenfield test pack (docs/qa/AUDIT_FINDINGS.md).</t>
-        </is>
-      </c>
-      <c r="J220" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="221" spans="1:10">
-      <c r="A221" s="2">
-        <v>220</v>
-      </c>
-      <c r="B221" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">A failed request renders as an empty or zero state instead of an error</t>
-        </is>
-      </c>
-      <c r="D221" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Platform / UI</t>
-        </is>
-      </c>
-      <c r="E221" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bug</t>
-        </is>
-      </c>
-      <c r="G221" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P1</t>
-        </is>
-      </c>
-      <c r="H221" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The dashboard, artifacts registry, traceability graph, repositories list and the admin user list all render their empty state when the request fails. A completely broken backend looks like a calm, brand-new workspace — which also means several test cases would pass against it. Found by the pre-execution QA audit of the greenfield test pack (docs/qa/AUDIT_FINDINGS.md).</t>
-        </is>
-      </c>
-      <c r="J221" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="222" spans="1:10">
-      <c r="A222" s="2">
-        <v>221</v>
-      </c>
-      <c r="B222" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">/onboarding sits in the greenfield sidebar and hardcodes brownfield copy</t>
-        </is>
-      </c>
-      <c r="D222" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Onboarding</t>
-        </is>
-      </c>
-      <c r="E222" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bug</t>
-        </is>
-      </c>
-      <c r="G222" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P2</t>
-        </is>
-      </c>
-      <c r="H222" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The onboarding route is rendered in the sidebar for every project regardless of track, and the screen states the project is brownfield with no track check. A greenfield user is one click from a wizard that describes a project they do not have. Found by the pre-execution QA audit of the greenfield test pack (docs/qa/AUDIT_FINDINGS.md).</t>
-        </is>
-      </c>
-      <c r="J222" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="223" spans="1:10">
-      <c r="A223" s="2">
-        <v>222</v>
-      </c>
-      <c r="B223" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Dashboard gates badge is not 'gates needing you' — it is unfiltered and capped at 20</t>
-        </is>
-      </c>
-      <c r="D223" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Dashboard</t>
-        </is>
-      </c>
-      <c r="E223" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bug</t>
-        </is>
-      </c>
-      <c r="G223" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P3</t>
-        </is>
-      </c>
-      <c r="H223" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The count is every pending gate on the project, with no user or role filter, and the underlying query is capped at 20. It reads as a personal to-do count and is neither. Found by the pre-execution QA audit of the greenfield test pack (docs/qa/AUDIT_FINDINGS.md).</t>
-        </is>
-      </c>
-      <c r="J223" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="224" spans="1:10">
-      <c r="A224" s="2">
-        <v>223</v>
-      </c>
-      <c r="B224" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Companion enrollment ignores the project multi-select</t>
-        </is>
-      </c>
-      <c r="D224" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Companion</t>
-        </is>
-      </c>
-      <c r="E224" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bug</t>
-        </is>
-      </c>
-      <c r="G224" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P2</t>
-        </is>
-      </c>
-      <c r="H224" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The 'Projects' multi-select on the enrollment screen is never passed to the enroll call; the token always binds to the first membership. In a multi-project workspace the machine is enrolled against the wrong project with no indication. Found by the pre-execution QA audit of the greenfield test pack (docs/qa/AUDIT_FINDINGS.md).</t>
-        </is>
-      </c>
-      <c r="J224" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="225" spans="1:10">
-      <c r="A225" s="2">
-        <v>224</v>
-      </c>
-      <c r="B225" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">'Published this week' counts artifacts by creation date, not publish date</t>
-        </is>
-      </c>
-      <c r="D225" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Dashboard</t>
-        </is>
-      </c>
-      <c r="E225" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bug</t>
-        </is>
-      </c>
-      <c r="G225" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P3</t>
-        </is>
-      </c>
-      <c r="H225" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Both the 'Published this week' figure and the 'Recent publishes' list filter on created_at. An artifact created eight days ago and published today never appears, and one created today but never published does. Found by the pre-execution QA audit of the greenfield test pack (docs/qa/AUDIT_FINDINGS.md).</t>
-        </is>
-      </c>
-      <c r="J225" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="226" spans="1:10">
-      <c r="A226" s="2">
-        <v>225</v>
-      </c>
-      <c r="B226" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">/admin/&lt;anything&gt; renders a developer placeholder</t>
-        </is>
-      </c>
-      <c r="D226" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Platform / UI</t>
-        </is>
-      </c>
-      <c r="E226" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bug</t>
-        </is>
-      </c>
-      <c r="G226" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P3</t>
-        </is>
-      </c>
-      <c r="H226" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">An unmatched admin route falls through to a placeholder reading 'Foundation route mounted. Feature screens land in T2-T5.' It is behind the admin guard, but any workspace admin with a stale bookmark or a typo reaches it in production. Found by the pre-execution QA audit of the greenfield test pack (docs/qa/AUDIT_FINDINGS.md).</t>
-        </is>
-      </c>
-      <c r="J226" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="227" spans="1:10">
-      <c r="A227" s="2">
-        <v>226</v>
-      </c>
-      <c r="B227" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Ideation registers ONE artifact containing the Context Gap Scan instead of opening the clarifications gate (intermittent)</t>
-        </is>
-      </c>
-      <c r="C227" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Greenfield: create a project, add a work item, trigger Ideation. Expected the clarifications gate with the agent's tiered questions. Instead the run went straight to a review gate with a single 'Ideation' artifact whose body WAS the gap scan — the questions themselves, ending 'I will not produce or register any artifact until you answer them'. Intermittent: the same code produced a correct gate on other runs, which is why it was chased as a prompt/model problem for days. Reported independently by two developers. Reproduced live on 2026-07-30 (run f390734e, then again as 457f65e1).</t>
-        </is>
-      </c>
-      <c r="D227" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Runs / Clarifications</t>
-        </is>
-      </c>
-      <c r="E227" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bug</t>
-        </is>
-      </c>
-      <c r="G227" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P1</t>
-        </is>
-      </c>
-      <c r="H227" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The Claude Code CLI (2.1.208) DEFERS tools out of the agent's initial context to save tokens, and 'ToolSearch' is the only mechanism that loads a deferred tool back (the SDK models this as deferredBuiltinTools). 'ToolSearch' was on the platform's planning and scan DENYLISTS — added 2026-07-09 in commit 98200ae, when it was merely another built-in to sandbox away, long before the CLI used it this way. Granting all 13 platform-state tools in allowed_tools therefore guaranteed nothing: whatever the CLI deferred was permanently invisible to the agent. Proof from run 457f65e1 — the agent's own first paragraph: 'The platform-state tools (ask_human, register_artifact, add_trace_edge, log_event) referenced in my operating instructions are not present in my available tool context', while THE SAME RUN successfully called list_artifacts and get_artifact. Read tools present, write tools and ask_human absent — so the agent produced 39,417 chars of finished deliverables as prose because it had nowhere to put them. Intermittent because what the CLI defers depends on context pressure, which varies run to run. NOT a model adherence problem, NOT a crashed MCP server, NOT the environment — all three were investigated and ruled out with evidence.</t>
-        </is>
-      </c>
-      <c r="I227" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Removed 'ToolSearch' from _PLANNING_DISALLOWED_TOOLS and _SCAN_DISALLOWED_TOOLS (backend/drivers/claude_driver.py) AND added it to the three allowlists — PLAN_ALLOWED_TOOLS (runner/companion/daemon.py), BUILD_ALLOWED_TOOLS (runner/companion/runner.py) and PLATFORM_TOOLS (backend/orchestration/activities.py); a denylist removal alone is not enough while an allowlist is in force. The sandbox is NOT widened: ToolSearch returns schemas only, for tools already granted, and execution stays gated by the same allowlist plus denylist. VERIFIED live end-to-end after the fix: ask_human called at 30s (4 tiered questions, Tier 1 required / Tier 2 with suggestion), then 7x register_artifact, 7x stage_artifact_body, 1x add_trace_edge, producing the full healthy 7-artifact ideation (ideation, feasibility_report, stakeholder_map, success_metrics, market_sizing, competitive_analysis, assumption) and the phase completed. Full write-up: docs/INCIDENT_2026-07-30_clarifications_gate.md.</t>
-        </is>
-      </c>
-      <c r="J227" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Fixed</t>
-        </is>
-      </c>
-    </row>
-    <row r="228" spans="1:10">
-      <c r="A228" s="2">
-        <v>227</v>
-      </c>
-      <c r="B228" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">A run whose agent registered nothing still produced an approvable artifact and opened a review gate</t>
-        </is>
-      </c>
-      <c r="C228" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The safety-net defect behind S.No 226. When the agent's tools were unreachable, the platform still filed its final message as the phase deliverable and opened a normal review gate on it — so a completely failed run looked like a successful one. This is why the underlying bug survived for weeks: nothing ever failed visibly, and a reviewer would have approved a document containing the agent's questions.</t>
-        </is>
-      </c>
-      <c r="D228" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Runs / Gates</t>
-        </is>
-      </c>
-      <c r="E228" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bug</t>
-        </is>
-      </c>
-      <c r="G228" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P1</t>
-        </is>
-      </c>
-      <c r="H228" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">register_phase_result_core (backend/orchestration/activities.py) unconditionally staged the engine's final text, registered it as a phase-typed artifact and let the run proceed to its gate; nothing examined what the text was. The existing guard, verify_write_completeness_core, checks that the expected artifact type exists and is non-empty — but for ideation it looks for type 'ideation', which is EXACTLY the artifact the platform had just created from the agent's questions, and non-empty because the gap scan was 3,441 real characters. The platform was manufacturing the evidence its own check looked for.</t>
-        </is>
-      </c>
-      <c r="I228" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The platform's own artifact is now stamped external_ref={'source': 'phase_report'} at both sinks (companion register_phase_result_core and direct execute_phase), and verify_write_completeness_core requires at least ONE artifact the AGENT registered. If the only record is the platform's copy of the final message the run FAILS with a message naming what to check, and NO gate opens. Evidence for the bar: across 47 successful runs spanning 13 phases the minimum artifact count was 2 (the platform's plus at least one agent-registered) and never 1; the failed run had exactly 1. Replayed against every historical successful run: 49 pass, 0 regress. PROVEN IN PRODUCTION — it caught the real intermittent bug on its first encounter (run 457f65e1 parked with a clear reason instead of filing a false artifact), which is how the root cause in S.No 226 was finally found.</t>
-        </is>
-      </c>
-      <c r="J228" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Fixed</t>
-        </is>
-      </c>
-    </row>
-    <row r="229" spans="1:10">
-      <c r="A229" s="2">
-        <v>228</v>
-      </c>
-      <c r="B229" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Agent briefing (manifest) was silently truncated mid-sentence, losing project constraints and operating rules</t>
-        </is>
-      </c>
-      <c r="C229" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Every run is given a briefing document in seven sections, each capped. Two sections were over their cap on a normal greenfield project, so real content was cut — including the end of the user's own project constraints and the tail of the agent's operating rules. Nothing logged it and nothing showed it, so the only symptom was an agent that appeared to have forgotten something.</t>
-        </is>
-      </c>
-      <c r="D229" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Runs / Agents</t>
-        </is>
-      </c>
-      <c r="E229" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bug</t>
-        </is>
-      </c>
-      <c r="G229" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P2</t>
-        </is>
-      </c>
-      <c r="H229" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">backend/manifest/composer.py caps each section in tokens and cuts by CHARACTER count. Measured on a live ideation run: 'rules' needed 1,706 tokens against a 1,500 cap (780 chars lost) and 'project' needed 906 against 800 (378 chars lost). The Project section stopped mid-sentence inside the user's constraints at 'Authentication: Email + password only. No OTP, no'; the Rules section lost Rule 9, the assumptions protocol and the review-gate rule, because truncation removes the END and the last-written rules live there. The whole manifest was 3,594 tokens — under 2% of the model's 200k window — so a document with no size problem was being cut. The caps were early guesses applied equally to sections that grow without bound (artifact lists, event history) and sections we AUTHOR (rules, project profile), which is the category error.</t>
-        </is>
-      </c>
-      <c r="I229" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Caps raised where the content is authored and left alone where it grows without bound: rules 1500 -&gt; 3000, project 800 -&gt; 2000, important_context 1500 -&gt; 2000; relevant_artifacts / recent_events / retrieved_knowledge unchanged. Truncation now cuts at a LINE boundary instead of mid-character. compose_manifest_core emits a 'manifest.truncated' ledger event naming the cut sections, so it can never be silent again and the team has real data to tune the caps. Verified on the live project: all seven sections now fit (3,633 tokens, nothing cut, user constraints intact end-to-end). FUTURE ENHANCEMENT: these are fixed constants sized against a 200k window — when model selection is exposed to users they should scale from the selected model's context window instead (noted in docs/INCIDENT_2026-07-30_clarifications_gate.md).</t>
-        </is>
-      </c>
-      <c r="J229" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Fixed</t>
-        </is>
-      </c>
-    </row>
-    <row r="230" spans="1:10">
-      <c r="A230" s="2">
-        <v>229</v>
-      </c>
-      <c r="B230" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">MCP server config was sent as inline command-line JSON with a seven-variable environment</t>
-        </is>
-      </c>
-      <c r="C230" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Hardening found while investigating S.No 226. The companion launches the platform-state MCP server — the process that provides EVERY tool an agent has — as a subprocess, and passed its whole configuration on the command line. Not confirmed as a cause of any observed failure, but two real risks, one of them a repeat of an already-fixed class of bug (Bugs row 64, Windows 'command line too long' misreported as 'Claude Code not found').</t>
-        </is>
-      </c>
-      <c r="D230" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Companion / Runs</t>
-        </is>
-      </c>
-      <c r="E230" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bug</t>
-        </is>
-      </c>
-      <c r="G230" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P2</t>
-        </is>
-      </c>
-      <c r="H230" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(1) The subprocess was given exactly seven environment variables. If that env ever REPLACES rather than extends the child's environment, Python cannot start on Windows: without SYSTEMROOT, Winsock fails to initialise and the interpreter dies during 'import asyncio' with OSError [WinError 10106], before any of our code runs — so the process that would have logged the failure is the one that died. Reproduced directly on a developer machine: 7 vars -&gt; exit 1; plus SYSTEMROOT -&gt; serves normally. (2) The config travelled as inline --mcp-config JSON on the command line. Windows caps a command line at ~32,767 chars (the ceiling behind Bugs row 64), and command lines are readable by any user from a process listing — so an inlined config publishes the runner token.</t>
-        </is>
-      </c>
-      <c r="I230" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The environment is now inherited from the machine and then overlaid with the seven runner values, and the entire config is written to a temp FILE whose path goes on the command line — the same shape the team already adopted for the agent body (--system-prompt-file). The file is deleted on every exit path because it carries the runner token. Applied to BOTH the planning path (daemon.state_mcp_servers) and the build path (runner.build_mcp_servers), which launch the identical server and carried the identical risk. Verified: command line 59 chars (the path) versus 6,708 inline; 88 env vars in the file with SYSTEMROOT and PATH present and the runner values correctly overlaid; file removed after the run; 31 companion daemon tests pass.</t>
-        </is>
-      </c>
-      <c r="J230" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Fixed</t>
-        </is>
-      </c>
-    </row>
-    <row r="231" spans="1:10">
-      <c r="A231" s="2">
-        <v>230</v>
-      </c>
-      <c r="B231" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Clarification events from deleted runs on other work items leak into a fresh work item's manifest</t>
-        </is>
-      </c>
-      <c r="C231" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Observed while diagnosing S.No 226. A brand-new work item's agent reported: 'Two prior clarification.asked events appear in the run history but no answers were carried into this manifest.' Those events belonged to earlier runs on DIFFERENT work items that had since been deleted. At best this is noise in the briefing; at worst an agent reasons from another work item's clarifications, or believes questions were already asked and answered when they were not.</t>
-        </is>
-      </c>
-      <c r="D231" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Runs / Agents</t>
-        </is>
-      </c>
-      <c r="E231" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bug</t>
-        </is>
-      </c>
-      <c r="G231" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P3</t>
-        </is>
-      </c>
-      <c r="H231" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Not yet diagnosed. The '# Recent Events' section of the manifest is populated from the ledger scoped to the project rather than to the work item, so clarification events raised against any work item in the project reach every run's briefing — and deleting the run does not remove its ledger events. Needs confirmation against mcp_platform_state.tools.get_context before a fix is proposed.</t>
-        </is>
-      </c>
-      <c r="I231" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">None — logged for triage. Suggested direction: scope clarification-related events in the manifest to the CURRENT work item, or carry the answers alongside the events so an agent never sees a question without its answer. See section 5 of docs/INCIDENT_2026-07-30_clarifications_gate.md.</t>
-        </is>
-      </c>
-      <c r="J231" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Open</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:J231" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:J238" xr:uid="{00000000-0009-0000-0000-000000000000}">
+    <filterColumn colId="9">
+      <filters blank="1">
+        <filter val="Open"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/docs/Bugs.xlsx
+++ b/docs/Bugs.xlsx
@@ -4968,7 +4968,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr filterMode="1"/>
-  <dimension ref="A1:J238"/>
+  <dimension ref="A1:J239"/>
   <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="7.81640625" style="2" bestFit="1" customWidth="1"/>
@@ -11921,12 +11921,12 @@
       </c>
       <c r="I236" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not fixed. Plan: set CONN_MAX_AGE (60-600) plus CONN_HEALTH_CHECKS, and retry the connect. CONN_MAX_AGE must NOT ship without an explicit cross-tenant isolation test: set_config(..., false) is session-scoped, so a reused connection carries app.tenant_id across requests. The finally: clear_current_tenant() in TenantContextMiddleware should cover it, but 'should' is not good enough for a tenant-isolation boundary. Note no application change can make a public-internet link reliable - retry is the mitigation; a private network or a pooler beside the database is the cure. The 5s idle poll interval was deliberately left alone: raising it adds the same latency to every phase pickup for far less benefit.</t>
+          <t xml:space="preserve">Fixed. backend/config/settings.py sets CONN_MAX_AGE=60 and CONN_HEALTH_CHECKS=True, both env-overridable (DB_CONN_MAX_AGE / DB_CONN_HEALTH_CHECKS) so they can be switched off without a deploy. Health checks probe a reused connection at request start and replace a dead one transparently. apps/tenancy/middleware.py: _enter_tenant_scope retries the first DB touch once on a fresh connection (a real outage still surfaces), and _release_tenant_scope clears app.tenant_id and DISCARDS the connection if clearing fails, so one can never return to the pool still scoped to a tenant - the session-GUC hazard that connection reuse introduces. Proven by tests/test_persistent_connection_rls.py (10 tests): the database half drives the real RLS policies over one reused connection as the non-superuser app role, the middleware half drives set/release/discard/retry. Both halves mutation-tested - removing the discard fails 1, removing the retry fails 2, re-granting the app role SUPERUSER fails all 3 database tests. Live check against the remote DB: 4 consecutive requests shared one backend_pid, scope correct during each and '' after. Not fixable in code: no application change makes a public-internet link reliable - a private network or a pooler beside the database is the cure.</t>
         </is>
       </c>
       <c r="J236" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Open</t>
+          <t xml:space="preserve">Fixed</t>
         </is>
       </c>
     </row>
@@ -12030,8 +12030,58 @@
         </is>
       </c>
     </row>
+    <row r="239" spans="1:10" ht="232.5" x14ac:dyDescent="0.35">
+      <c r="A239" s="2">
+        <v>238</v>
+      </c>
+      <c r="B239" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Every RLS isolation test passes without testing anything, because the app role in the local database is a superuser</t>
+        </is>
+      </c>
+      <c r="C239" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">All seven test_rls_isolates_* tests fail when run against the compose database - the app role reads every tenant's rows. They had only ever been run against the remote database, so the vacuum went unnoticed. A green RLS test proves nothing unless the role under test is actually subject to RLS.</t>
+        </is>
+      </c>
+      <c r="D239" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Test environment / RLS test suite</t>
+        </is>
+      </c>
+      <c r="E239" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bug</t>
+        </is>
+      </c>
+      <c r="F239" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Found 2026-08-03 while building the tenant-isolation test required before enabling CONN_MAX_AGE (S.No 235). pg_roles showed sdlc_app with rolsuper=true in the compose database.</t>
+        </is>
+      </c>
+      <c r="G239" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P2</t>
+        </is>
+      </c>
+      <c r="H239" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The compose database's sdlc_app role was created as SUPERUSER, and PostgreSQL exempts superusers from row-level security entirely. The tests connect as that role precisely because the Django test connection is the privileged migration role and would bypass RLS - so the workaround was defeated by the role it switched to. Against the remote database the role is not superuser, which is why this was never seen.</t>
+        </is>
+      </c>
+      <c r="I239" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fixed in the environment: ALTER ROLE sdlc_app NOSUPERUSER on the compose database, after which all seven pass and the suite baseline moves from 33 failed/1093 passed to 26 failed/1113 passed. Documented in section 13 of docs/INCIDENT_2026-07-30_clarifications_gate.md. The new tests in test_persistent_connection_rls.py are mutation-checked against a re-granted SUPERUSER so this specific vacuum cannot return unnoticed. Still worth doing: assert the role is not superuser in a fixture, so any environment where RLS cannot bite fails loudly instead of reporting green.</t>
+        </is>
+      </c>
+      <c r="J239" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fixed</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J238" xr:uid="{00000000-0009-0000-0000-000000000000}">
+  <autoFilter ref="A1:J239" xr:uid="{00000000-0009-0000-0000-000000000000}">
     <filterColumn colId="9">
       <filters blank="1">
         <filter val="Open"/>

--- a/docs/Bugs.xlsx
+++ b/docs/Bugs.xlsx
@@ -4968,7 +4968,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr filterMode="1"/>
-  <dimension ref="A1:J239"/>
+  <dimension ref="A1:J240"/>
   <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="7.81640625" style="2" bestFit="1" customWidth="1"/>
@@ -12080,6 +12080,56 @@
         </is>
       </c>
     </row>
+    <row r="240" spans="1:10" ht="232.5" x14ac:dyDescent="0.35">
+      <c r="A240" s="2">
+        <v>239</v>
+      </c>
+      <c r="B240" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Secret scanner keeps blocking legitimate builds - fifth occurrence of the same class</t>
+        </is>
+      </c>
+      <c r="C240" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Five builds across two tenants were stopped by a high_entropy_secret finding that was not a credential. Latest: PeopleDesk TASK-013 (Auth module) blocked on packages/backend/src/auth/jwt.strategy.ts:73 with conf***ow (24 chars) - the value was configService.getOrThrow, the NestJS call that READS the secret from config. Earlier in the same class: 535 findings across one npm install (all dependency variable names), self.refresh_token_expiry_seconds, a change-me placeholder in .env.example, and mock JWTs in a test file.</t>
+        </is>
+      </c>
+      <c r="D240" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Companion / pre-push secret scan (guardrails.scan_text)</t>
+        </is>
+      </c>
+      <c r="E240" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bug</t>
+        </is>
+      </c>
+      <c r="F240" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tenant 9dd11483 (QA, PeopleDesk) run e4de562f 2026-08-16; tenant 212395b8 (dev) WI-32/WI-34/WI-38. Related rows: 144, 193. NOTE: the S.No 150 and 151 cited in commits 7b5fe6a and cbe56fe point at unrelated UI/artifact bugs - those two scanner occurrences were never logged here, and the 535-finding block was not logged either, so this class reads as 1 occurrence in the sheet when it is 5.</t>
+        </is>
+      </c>
+      <c r="G240" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P1</t>
+        </is>
+      </c>
+      <c r="H240" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">_ASSIGNMENT made the quotes OPTIONAL - ['"]?(value)['"]? - so any identifier, attribute chain or method call after a secret/token keyword was eligible to be scored for entropy. It was never changed since the scanner was written; all four previous fixes added a downstream exception (placeholders, template files, test files, dotted identifiers, bare identifiers) that was narrower than the class, so the class returned in a new shape each time. A hardcoded credential in code is ALWAYS a quoted string literal, so an unquoted RHS in source is an expression and can never be a leak.</t>
+        </is>
+      </c>
+      <c r="I240" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fixed. guardrails.py now scores string LITERALS only: _ASSIGNMENT_QUOTED runs everywhere; the unquoted _ASSIGNMENT_BARE runs only where an unquoted value can be a literal - config-shaped files, or a comment line in code (_scans_bare_values). Detection is unchanged on every true positive incl. the S.No 193 policy (a literal in a config file is a leak even when it is a dev/CI one). A false-positive/true-positive regression corpus in test_guardrails.py now pins every shape that has ever wrongly blocked. Also: agent 07 was never told the scanner exists (11_cicd was) - it now carries the same rule plus the .gitignore rule from 09b; a block now gets one bounded auto-retry seeded with the redacted findings instead of being a dead end; and the findings are persisted on the run (D6).</t>
+        </is>
+      </c>
+      <c r="J240" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fixed</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:J239" xr:uid="{00000000-0009-0000-0000-000000000000}">
     <filterColumn colId="9">

--- a/docs/Bugs.xlsx
+++ b/docs/Bugs.xlsx
@@ -4968,7 +4968,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr filterMode="1"/>
-  <dimension ref="A1:J240"/>
+  <dimension ref="A1:J241"/>
   <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="7.81640625" style="2" bestFit="1" customWidth="1"/>
@@ -9324,11 +9324,15 @@
       <c r="H147" s="2" t="s">
         <v>706</v>
       </c>
-      <c r="I147" s="2" t="s">
-        <v>707</v>
-      </c>
-      <c r="J147" s="2" t="s">
-        <v>16</v>
+      <c r="I147" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">REOPENED 2026-08-17 - the stderr capture never once fired. Across nine engine-exit failures on two tenants (four AFTER this fix landed), not one run carried an "Engine stderr" tail: every report.message was byte-identical to the placeholder this row says was fixed. Cause: the fix instrumented the wrong channel. Claude Code emits its diagnostics - including the usage-limit notice - on STDOUT as non-JSON lines, which the SDK drops at logger.debug ("Skipping non-JSON line from CLI stdout"); the companion configured no logging at all, so the root logger had no handlers and logging.lastResort is WARNING-level, and those records went nowhere. ProcessError.stderr is hardcoded to the placeholder by the SDK, so the stderr deque stayed empty and _with_stderr_tail was a no-op every time. Superseded by S.No 240. --- Original note: FIXED &amp; TESTED (2026-07-21): code landed @6f9671f. classify_build_failure() in build_activities.py maps usage/rate-limit/exit-code-1 signatures to a plain reason, and the companion now reports the engine's stderr tail instead of the placeholder. Team verified live. --- Original fix note: OPEN - Fix A planned this session (this row's owner). Two parts: (1) Companion (daemon.py): capture the agent process's stderr tail and put the actual cause in the report message instead of the placeholder 'Check stderr output for details'. (2) Platform (classify_build_failure): recognise engine / usage-limit / rate-limit signatures ('exit code 1', 'usage limit', 'rate limit', '429', 'overloaded', 'quota', 'Failed to start Claude Code') and map them to a plain-language reason, e.g. 'The AI engine hit its usage limit - the build stopped; retry when the limit resets.' NOTE: true resume-from-checkpoint on a transient failure (so a re-run continues from the last cycle instead of rebuilding) is tracked separately as S.No 147 and is owned by the other developer. Acceptance: a usage-limit failure shows a clear, non-technical reason naming the usage limit, not a raw exit-code string.</t>
+        </is>
+      </c>
+      <c r="J147" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Superseded by S.No 240</t>
+        </is>
       </c>
     </row>
     <row r="148" spans="1:10" ht="409.5" hidden="1" x14ac:dyDescent="0.35">
@@ -12125,6 +12129,56 @@
         </is>
       </c>
       <c r="J240" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fixed</t>
+        </is>
+      </c>
+    </row>
+    <row r="241" spans="1:10" ht="232.5" x14ac:dyDescent="0.35">
+      <c r="A241" s="2">
+        <v>240</v>
+      </c>
+      <c r="B241" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The AI engine exits and the platform records nothing about why - nine failures, one identical message</t>
+        </is>
+      </c>
+      <c r="C241" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nine builds across two tenants failed with a byte-identical reason and none could be root-caused. They lasted 0.2, 2.7, 7.3, 9.3, 12.5, 23.8 and 75.2 minutes from dispatch to failure, so they cannot all share one cause - at least two distinct bugs were wearing the same label. Latest: PeopleDesk TASK-014 (POST /api/auth/login), where the engine died 12.5 minutes into REMEDIATION and destroyed a run that already had a working PR and a completed code review.</t>
+        </is>
+      </c>
+      <c r="D241" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Build pipeline / Failure observability + Companion + engine driver</t>
+        </is>
+      </c>
+      <c r="E241" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bug</t>
+        </is>
+      </c>
+      <c r="F241" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tenant 9dd11483 (QA, PeopleDesk) run 5f4d4a2c 2026-08-17; also runs a34002c4, 031a6c94, 01fdf693, 82bfe859 (tenant 212395b8) and 018e077c, 36e916f5, 771365ff, 470b0443. Reopens and supersedes S.No 146.</t>
+        </is>
+      </c>
+      <c r="G241" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P1</t>
+        </is>
+      </c>
+      <c r="H241" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Three losses stack. (1) The cause travels on the CLI stdout as non-JSON lines; the SDK drops them at logger.debug and the companion configured NO logging anywhere, so with no root handler and lastResort at WARNING those records were discarded outright. (2) The SDK hardcodes ProcessError(stderr="Check stderr output for details"), so the real stderr is never in the exception and the S.No 146 deque stayed empty. (3) _consume_stream accumulated messages/text/cost/subtype in LOCAL variables, all discarded when the transport raised - TASK-014 lost 12.5 minutes of work with no record. On top of that classify_build_failure asserted "The most common cause is a usage/rate limit", a guess stated as a finding that steered the investigation, and pointed at a companion terminal that no longer existed by the time anyone read it. Separately, an engine exit was the only recoverable-looking failure with no recourse: mark_build_failed + return closes the Temporal history for good.</t>
+        </is>
+      </c>
+      <c r="I241" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fixed 2026-08-17. (1) claude_driver attaches a handler to the claude_agent_sdk logger at DEBUG for the duration of a run (installed/removed around it, so no global logging state leaks) - this captures the discarded stdout diagnostic AND query.py's "Fatal error in message reader". (2) _consume_stream now folds message count, artifacts registered, cost, result subtype and the tail of the agent's last output into the raised error, so a 12-second failure can never again read like a 12-minute one. (3) New runner/companion/enginelog.py writes a rotating companion-engine.log - there was NO log file before, which is why eight of nine were unrecoverable. (4) classify_build_failure/classify_phase_failure stop asserting a cause, show the engine's own output, decode the usage-limit reset epoch when present, and name the log file. (5) An engine exit now PARKS via the existing S.No 157 machinery at both dispatch sites, so the PR and review survive and Resume re-dispatches; empty build and secret block stay on their own paths (is_engine_exit). Pinned by an engine-failure corpus in test_build_activities.py.</t>
+        </is>
+      </c>
+      <c r="J241" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Fixed</t>
         </is>

--- a/docs/Bugs.xlsx
+++ b/docs/Bugs.xlsx
@@ -4968,7 +4968,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr filterMode="1"/>
-  <dimension ref="A1:J241"/>
+  <dimension ref="A1:J242"/>
   <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="7.81640625" style="2" bestFit="1" customWidth="1"/>
@@ -12184,6 +12184,56 @@
         </is>
       </c>
     </row>
+    <row r="242" spans="1:10" ht="232.5" x14ac:dyDescent="0.35">
+      <c r="A242" s="2">
+        <v>241</v>
+      </c>
+      <c r="B242" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Code review remediation loop can never finish - the build agent is briefed with a finding the reviewer is no longer raising</t>
+        </is>
+      </c>
+      <c r="C242" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TASK-029 (Apply Leave form) ran for 26 hours across two runs, 20 review cycles and 15 remediation rebuilds without ever clearing review. The QA member resumed it four times; each resume granted a fresh cycle budget and hit the same wall. The reviewer was blocking on one thing (the duration-preview endpoint accepts reversed date ranges) while the implementation agent was repeatedly asked to fix a different thing it had already fixed 15 cycles earlier (a COMPOFF_EXPIRED message in a frontend file). The loop could not converge by construction, not by chance.</t>
+        </is>
+      </c>
+      <c r="D242" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Build pipeline / code review remediation loop (run_code_review_core, dispatch_remediation_core, review manifest)</t>
+        </is>
+      </c>
+      <c r="E242" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bug</t>
+        </is>
+      </c>
+      <c r="F242" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tenant 9dd11483 (QA, PeopleDesk) WI-87 TASK-029, runs 4e62a433 (failed, 4 cycles) and b80802ac (stalled, 16 cycles), 2026-08-26 to 2026-08-27. Same signature on every other remediation-exhausted run in the tenant: WI-55, 57, 65, 67, 72, 86 - 8 of 8, against 0 of the 24 runs that converged normally in 2-3 cycles.</t>
+        </is>
+      </c>
+      <c r="G242" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P1</t>
+        </is>
+      </c>
+      <c r="H242" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A rem id (REM-W1, REM-C1) is a POSITION in one review's output, not an identity: the reviewer numbers its findings from 1 on every re-review, and the review manifest never carried the previous cycle's ids, so the agent had nothing to reuse even though agents/08_code_review/agent.md line 274 instructs it to. Three defects then compound. (1) REM-W1 silently comes to mean a different problem the moment the finding set changes shape. (2) run_code_review_core only ever wrote a remediation child WorkItem at creation - the reopen branch flipped state and nothing else, so title, description, file and line stayed frozen at cycle 1 forever, and dispatch_remediation_core briefs agent 07 from exactly those fields. (3) The children hang off the WorkItem, not the run, so the auto-retry run inherited the failed attempt's board and was mis-briefed on its very first cycle. Evidence on WI-87: the board was written 9 times, all inside the first 20 minutes; 14 of the 15 remediation builds ran after it stopped changing; and the file the reviewer was blocking on was last touched by the INITIAL build and by none of the 15 remediation builds. The one-line fix the reviewer wanted (previewWorkingDays never calls the validateDateRange that already sits directly above it) was never attempted.</t>
+        </is>
+      </c>
+      <c r="I242" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fixed 2026-08-27 on develop (commit e7e791e). (1) run_code_review_core now rewrites the child's title, description, severity, file and line from the CURRENT finding every cycle instead of only flipping state, and logs remediation.retargeted when the meaning under an id really changes, so the collision is visible instead of hidden behind a count. (2) The review manifest gained a 'Findings Already Open From Your Previous Review' section listing live rem ids with file:line, so the reviewer can honour the reuse-or-omit contract its own body states; absent on cycle 1 and degrades to nothing on any error, since a missing section must never fail a review. (3) handle_remediation_exhausted_core closes the open remediation board before starting a retry attempt - closed, never deleted, and prior_attempt_context already carries the substance forward to the new agent. 5 new tests in test_build_activities.py and test_review_dispatch.py, 4 of them verified failing against the unfixed source. No data repair needed: TASK-029 self-corrects on its next review cycle after the QA member pulls, restarts the worker and clicks Resume.</t>
+        </is>
+      </c>
+      <c r="J242" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fixed</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:J239" xr:uid="{00000000-0009-0000-0000-000000000000}">
     <filterColumn colId="9">

--- a/docs/Bugs.xlsx
+++ b/docs/Bugs.xlsx
@@ -4968,7 +4968,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr filterMode="1"/>
-  <dimension ref="A1:J242"/>
+  <dimension ref="A1:J243"/>
   <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="7.81640625" style="2" bestFit="1" customWidth="1"/>
@@ -12234,6 +12234,56 @@
         </is>
       </c>
     </row>
+    <row r="243" spans="1:10" ht="232.5" x14ac:dyDescent="0.35">
+      <c r="A243" s="2">
+        <v>242</v>
+      </c>
+      <c r="B243" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A worker handing over to a newer build can quit while a build is still running, stranding it with no error</t>
+        </is>
+      </c>
+      <c r="C243" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The worker hand-over is meant to let an outgoing worker finish what it holds before it leaves. It decides whether it is still holding something by asking whether a step is executing right now - but for nearly all of a build the worker is doing nothing, waiting for the developer's companion to write the code and report back. After five minutes of that wait it concludes it is finished and shuts down. The build is stamped with that worker's build id, so when the companion finally reports there is no worker that matches and the run stops dead showing 'Queued' with a healthy companion and a healthy worker. Same symptom as the unversioned-worker fence found the same day, different cause - which is exactly what makes it expensive to diagnose the second time.</t>
+        </is>
+      </c>
+      <c r="D243" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Temporal worker hand-over (orchestration/worker_election.drain_when_superseded)</t>
+        </is>
+      </c>
+      <c r="E243" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bug</t>
+        </is>
+      </c>
+      <c r="F243" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Found 2026-08-28 by reading the code while fixing the queued-build incident on tenant 9dd11483 (QA, PeopleDesk) TASK-030. NOT yet observed in the wild. Confirmed against the live server that the premise holds: workflow build-run-9da5a94d carries worker stamp build_id=20260828T073458Z-83c57f55a83d with use_versioning=True, so a versioned worker does tie the execution to its own build, while TASK-029 (served unversioned) carries no such tie. The hand-over code reached develop the same day in eda970d + 9347e13.</t>
+        </is>
+      </c>
+      <c r="G243" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P2</t>
+        </is>
+      </c>
+      <c r="H243" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">drain_when_superseded declares itself drained when TrackingExecutor reports in_flight == 0 and idle &gt;= WORKER_DRAIN_IDLE_SECONDS (default 300s). TrackingExecutor is the ACTIVITY executor, so it counts only activities that are executing. A build spends nearly all of its life inside workflow.wait_condition waiting for the companion's build report, with no activity in flight for 20-90 minutes, so a worker minding a perfectly live build reports itself idle within five minutes of that wait starting. Idleness is therefore the wrong signal: it measures 'am I busy this second', not 'is any build still tied to me'. Once the worker exits, the workflow task scheduled by the companion's report has no matching poller and the run stalls with no error anywhere - the same dead end as a fenced-out worker.</t>
+        </is>
+      </c>
+      <c r="I243" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not fixed. Stopgap with NO code change: set WORKER_DRAIN_IDLE_SECONDS longer than a build (e.g. 7200), so a superseded worker lingers long enough to see its builds through; WORKER_DRAIN_MAX_SECONDS (default 86400) still caps it. Proper fix: drain on whether any workflow is still assigned to this build rather than on activity idleness. Note get_worker_task_reachability cannot be used for that signal - it reports a non-default build as still NEW_WORKFLOWS reachable. Scope: only bites when a second worker running DIFFERENT code starts mid-build on a shared queue; a task queue per stack (as the brownfield stack already does with sdlc-brown) removes the race entirely, so this row is moot if the team splits the queues.</t>
+        </is>
+      </c>
+      <c r="J243" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:J239" xr:uid="{00000000-0009-0000-0000-000000000000}">
     <filterColumn colId="9">

--- a/docs/Bugs.xlsx
+++ b/docs/Bugs.xlsx
@@ -4968,7 +4968,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr filterMode="1"/>
-  <dimension ref="A1:J243"/>
+  <dimension ref="A1:J244"/>
   <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="7.81640625" style="2" bestFit="1" customWidth="1"/>
@@ -12284,6 +12284,56 @@
         </is>
       </c>
     </row>
+    <row r="244" spans="1:10" ht="232.5" x14ac:dyDescent="0.35">
+      <c r="A244" s="2">
+        <v>243</v>
+      </c>
+      <c r="B244" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">An explicit acceptance criterion was dropped by the build agent and passed by the review agent - the API has no CORS, so no browser can reach it</t>
+        </is>
+      </c>
+      <c r="C244" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TASK-006's description told the implementation agent, in one sentence carrying four requirements, to "Configure CORS to allow the FRONTEND_URL env var origin with credentials". The ValidationPipe with all three flags, Swagger at /api/docs and the health endpoint - the other three requirements in that same sentence - were all delivered. CORS was not. The review agent passed the PR, the merge gate was approved, and TASK-006 is marked done and merged as PR #11 on 2026-08-13. The miss stayed invisible for 18 days and 29 further tasks because nothing in the pipeline ever opens a browser. It surfaced only when a QA member tried to open the product for the first time: the SPA is on :5173, the API on :3000, and every request including the login POST dies at the browser preflight.</t>
+        </is>
+      </c>
+      <c r="D244" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Agent quality / implementation + code review acceptance-criteria coverage (PeopleDesk TASK-006)</t>
+        </is>
+      </c>
+      <c r="E244" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bug</t>
+        </is>
+      </c>
+      <c r="F244" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tenant 9dd11483 (QA, PeopleDesk) TASK-006 = WI-64, PR edvensoft/PeopleDesk#11 merged 2026-08-13. The same requirement is also stated in FOUND-003 = WI-56 (PR #3) and was missed there too. Verified 2026-09-01 by reading packages/backend/src/main.ts at origin/main via the platform's codehost capability: no enableCors call present. Surfaced as finding B1 of the QA readiness review dated 2026-08-31.</t>
+        </is>
+      </c>
+      <c r="G244" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P1</t>
+        </is>
+      </c>
+      <c r="H244" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Two gaps in sequence. (1) The build agent completed three of four requirements in a single run-on sentence and silently dropped the fourth; nothing checks a delivered PR back against the individual clauses of its acceptance criteria, so a partial delivery reads as a complete one. (2) The review agent inspects the diff for defects in what was written, not for what the work item asked for and is absent - a call that was never made has no line to flag. Neither the agent's tests nor CI could catch it: CORS is enforced by the browser, and every test in the pipeline calls the API in-process via supertest, where no preflight ever occurs. The requirement was stated twice (FOUND-003 and TASK-006) and missed both times, so this is a systematic gap, not a one-off slip.</t>
+        </is>
+      </c>
+      <c r="I244" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not fixed. The PRODUCT fix is routed through the platform itself as TASK-050 (WI-212) under WI-56/FOUND-003 in tenant 9dd11483 - one enableCors({ origin: FRONTEND_URL, credentials: true }) call in packages/backend/src/main.ts plus preflight e2e tests - deliberately built, reviewed and merged by the normal build loop rather than hand-patched, so the fix is itself a test of the pipeline. The PLATFORM finding is the open item: the code review agent is never given the work item's acceptance criteria to verify delivery against. Candidate fix - include the work item's acceptance criteria verbatim in the 08_code_review manifest and require an explicit per-criterion verdict before a review may report zero blocking findings.</t>
+        </is>
+      </c>
+      <c r="J244" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:J239" xr:uid="{00000000-0009-0000-0000-000000000000}">
     <filterColumn colId="9">

--- a/docs/Bugs.xlsx
+++ b/docs/Bugs.xlsx
@@ -4968,7 +4968,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr filterMode="1"/>
-  <dimension ref="A1:J244"/>
+  <dimension ref="A1:J245"/>
   <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="7.81640625" style="2" bestFit="1" customWidth="1"/>
@@ -12334,6 +12334,56 @@
         </is>
       </c>
     </row>
+    <row r="245" spans="1:10" ht="232.5" x14ac:dyDescent="0.35">
+      <c r="A245" s="2">
+        <v>244</v>
+      </c>
+      <c r="B245" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A worker restart on changed code silently orphans every build still running - the job stays addressed to a code version that no longer exists</t>
+        </is>
+      </c>
+      <c r="C245" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TASK-036 showed 'dispatched for review' for 31 hours with no error anywhere. The workflow reported Running, the worker reported healthy and was polling the same queue seconds before it was checked, the queue reported healthy, and the UI showed a normal state. Nothing was wrong with the agent, the review or the shared server: the review agent had in fact reported back four separate times. The job was simply addressed to a worker build that no longer existed, and no part of the platform notices that. Recovering it required terminating the workflow by hand, because a restart cannot help - each restart mints yet another version, no closer to the one the job is waiting for.</t>
+        </is>
+      </c>
+      <c r="D245" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Temporal worker build-ID versioning (orchestration/worker_election.elect)</t>
+        </is>
+      </c>
+      <c r="E245" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bug</t>
+        </is>
+      </c>
+      <c r="F245" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tenant 9dd11483 (QA, PeopleDesk) TASK-036 = WI-93, run 7ebe493a, workflow build-run-7ebe493a-c054-4e99-adfb-fefd312176d6, PR edvensoft/PeopleDesk#43. Build started 2026-09-01 10:02 UTC on build 20260901T075033Z-a2228a4ad85e; worker restarted 2026-09-02 07:53 UTC as 20260902T075326Z-5ceff9d45ff3; workflow task pending and unstarted from 2026-09-02 02:00:18 UTC until terminated 2026-09-03 09:18 UTC. Queue sdlc-planning then carried 6 registered version sets and 8 running workflows, ALL 8 stranded on retired builds (7 were pre-existing orphans up to 42 days old, never noticed). Same family as S.No 242 and the 2026-08-28 TASK-030 fence, different mechanism.</t>
+        </is>
+      </c>
+      <c r="G245" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P1</t>
+        </is>
+      </c>
+      <c r="H245" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">worker_election.elect registers each worker's badge with BuildIdOpAddNewDefault, which makes every badge a NEW INCOMPATIBLE version set rather than a successor of the previous one. The badge is derived from the newest source file mtime plus a code fingerprint, so any git pull or edit produces a new badge and therefore a new incompatible generation. Temporal deliberately pins a running workflow to the build it started on for its whole life, so that it cannot have code change underneath it. Those two behaviours are individually correct and jointly fatal: our version changes on every code change while a build lasts hours, so any restart during a build leaves that build addressed to a generation nobody serves - permanently, and with no error, no failed state and no alert. The versioning was added on 2026-08-26 to fence out a stale worker running old code; the cure now strands the work it was protecting.</t>
+        </is>
+      </c>
+      <c r="I245" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not fixed. Recovery for this instance (2026-09-03): terminated the one workflow by exact id, closed run 7ebe493a via mark_build_failed_core so the work item was no longer blocked by an active run, and re-triggered TASK-036 - the branch feature/WI-35b48096 and PR #43 were untouched, and the new run continues from the remote tip, so only the last review cycle repeats. Candidate fixes, in preference order: (1) one task queue per stack, which sdlc-brown already does and which removes the contest entirely; (2) register each new badge as COMPATIBLE with the previous one (BuildIdOpAddNewCompatible) so a newer worker may serve older in-flight workflows, accepting that this reintroduces some stale-worker risk; (3) at minimum, detect and surface the condition - compare each running workflow's stamped build against the live pollers and raise it in the UI, because today the only symptom is silence. NOTE a separate open sub-question on the same run: the run_code_review activity never once completed its 30-minute wait across three attempts while the companion reported four times, so the worker was not staying alive through the wait; cause not determined from server-side data and needs the worker/companion log from the QA member's machine.</t>
+        </is>
+      </c>
+      <c r="J245" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:J239" xr:uid="{00000000-0009-0000-0000-000000000000}">
     <filterColumn colId="9">

--- a/docs/Bugs.xlsx
+++ b/docs/Bugs.xlsx
@@ -5919,6 +5919,11 @@
       <c r="G36" s="2" t="s">
         <v>36</v>
       </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NOT FIXED - notes for this redesign (2026-09-03). Four findings belong to it, and they are all one question: how does a headless machine authenticate? (1) Disconnect revokes exactly one enrollment row, so a developer who generated three tokens still holds two working ones after clicking it. (2) The enrollment token is passed on the command line, so any process listing on that machine reveals it (multi_project_recon C1). (3) Enrollment tokens never expire (C4). (4) Found while closing S.No 214: POST /api/runners/ still accepts an anonymous caller, and was deliberately LEFT OPEN, because the documented CLI onboarding (runner/README.md Quick start step 1) sends only a tenant header and has no session to present. Closing that half on its own breaks onboarding while answering none of the credential model.</t>
+        </is>
+      </c>
       <c r="J36" s="2" t="s">
         <v>141</v>
       </c>
@@ -8566,11 +8571,15 @@
       <c r="H122" s="2" t="s">
         <v>576</v>
       </c>
-      <c r="I122" s="2" t="s">
-        <v>577</v>
-      </c>
-      <c r="J122" s="2" t="s">
-        <v>141</v>
+      <c r="I122" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fixed 2026-09-03. agents/02_requirements/agent.md now carries a Writing standard block plus worked examples: lead every user story, functional requirement and acceptance criterion with a one-sentence plain-language statement of intent, then keep the full SHALL and Given/When/Then precision. The standard adds a sentence; it removes no rigour. Ports the pattern that fixed S.No 118 for agent 06, exemplars included, because 06 proved the instruction alone did not change the output. Pinned by test_agents_migration.</t>
+        </is>
+      </c>
+      <c r="J122" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fixed</t>
+        </is>
       </c>
     </row>
     <row r="123" spans="1:10" ht="217" x14ac:dyDescent="0.35">
@@ -8595,11 +8604,15 @@
       <c r="H123" s="2" t="s">
         <v>582</v>
       </c>
-      <c r="I123" s="2" t="s">
-        <v>583</v>
-      </c>
-      <c r="J123" s="2" t="s">
-        <v>141</v>
+      <c r="I123" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fixed 2026-09-03. agents/09_testing/agent.md now carries a Clarity standard block plus worked examples covering UAT scenarios, defect reports and test-case Expected Results. Deliberately humanized-TECHNICAL rather than plain language: a QA reader has to interpret precise detail correctly, and flattening it into everyday words causes misreading. A test pins that this register stays distinct from agent 02's, so a later tidy-up cannot collapse the two into one voice.</t>
+        </is>
+      </c>
+      <c r="J123" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fixed</t>
+        </is>
       </c>
     </row>
     <row r="124" spans="1:10" ht="186" x14ac:dyDescent="0.35">
@@ -8624,11 +8637,15 @@
       <c r="H124" s="2" t="s">
         <v>588</v>
       </c>
-      <c r="I124" s="2" t="s">
-        <v>589</v>
-      </c>
-      <c r="J124" s="2" t="s">
-        <v>141</v>
+      <c r="I124" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fixed 2026-09-03. agents/00c_intelligent_context_extractor/agent.md now requires the Executive Summary, health dashboard and module docs to lead in plain language while keeping the technical nuance, to give every number its meaning rather than the bare figure, and never to present an unmeasured value as zero (say unavailable, and why). Worked example and counter-example included.</t>
+        </is>
+      </c>
+      <c r="J124" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fixed</t>
+        </is>
       </c>
     </row>
     <row r="125" spans="1:10" ht="217" x14ac:dyDescent="0.35">
@@ -8653,11 +8670,15 @@
       <c r="H125" s="2" t="s">
         <v>593</v>
       </c>
-      <c r="I125" s="2" t="s">
-        <v>594</v>
-      </c>
-      <c r="J125" s="2" t="s">
-        <v>141</v>
+      <c r="I125" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fixed 2026-09-03. agents/04_architecture/agent.md now applies the readable-by-a-non-technical-stakeholder bar it already set for the C4 context diagram to the ADR Context, Rationale and Consequences: name the constraint that forced the decision, name the rejected alternatives and why they lost, and state the cost accepted. An ADR whose consequences are all positive is incomplete, and whoever inherits it finds the cost the hard way.</t>
+        </is>
+      </c>
+      <c r="J125" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fixed</t>
+        </is>
       </c>
     </row>
     <row r="126" spans="1:10" ht="124" x14ac:dyDescent="0.35">
@@ -8682,11 +8703,15 @@
       <c r="H126" s="2" t="s">
         <v>599</v>
       </c>
-      <c r="I126" s="2" t="s">
-        <v>600</v>
-      </c>
-      <c r="J126" s="2" t="s">
-        <v>141</v>
+      <c r="I126" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fixed 2026-09-03. agents/03_prd/agent.md now has a writing standard scoped to the per-feature acceptance criteria, which were the part written for engineers; the rest of the PRD was already well humanized. Each criterion must state an observable outcome someone could verify by hand, at least one per feature must cover the unhappy path, and the template scaffolding must never ship as written. These criteria are copied downstream by agent 06 and verified by agent 08, so vagueness here propagates.</t>
+        </is>
+      </c>
+      <c r="J126" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fixed</t>
+        </is>
       </c>
     </row>
     <row r="127" spans="1:10" ht="186" x14ac:dyDescent="0.35">
@@ -8711,11 +8736,15 @@
       <c r="H127" s="2" t="s">
         <v>605</v>
       </c>
-      <c r="I127" s="2" t="s">
-        <v>606</v>
-      </c>
-      <c r="J127" s="2" t="s">
-        <v>141</v>
+      <c r="I127" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fixed 2026-09-03. agents/10_security/agent.md now uses two registers deliberately. Findings are humanized-TECHNICAL: keep the CWE/OWASP category AND say what an attacker actually gains and what they need in order to get it. The stakeholder executive summary is plain language, with no unexplained acronyms and no severity table standing in for a conclusion. Worked example and counter-example included.</t>
+        </is>
+      </c>
+      <c r="J127" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fixed</t>
+        </is>
       </c>
     </row>
     <row r="128" spans="1:10" ht="409.6" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
@@ -10375,11 +10404,15 @@
       <c r="H183" s="2" t="s">
         <v>874</v>
       </c>
-      <c r="I183" s="2" t="s">
-        <v>875</v>
-      </c>
-      <c r="J183" s="2" t="s">
-        <v>141</v>
+      <c r="I183" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fixed 2026-09-03. AgentRunWorkflow now PARKS and re-dispatches on an engine exit instead of calling fail_run and returning. That return closed the Temporal history for good, and a closed workflow can never be signalled, so Resume was impossible for ever afterwards and the console could only offer a fresh run from zero. Ports the loop BuildWorkflow already used for S.No 240; _park, the activities and is_engine_exit all already existed on the planning side, so it is three edits to one file. A genuine phase failure still ends the run terminally, which is right. Verified by replaying a real old-code workflow history against the new code (20 events, no non-determinism), so upgrading the worker does not strand runs that are already open.</t>
+        </is>
+      </c>
+      <c r="J183" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fixed</t>
+        </is>
       </c>
     </row>
     <row r="184" spans="1:10" ht="356.5" x14ac:dyDescent="0.35">
@@ -10462,11 +10495,15 @@
       <c r="H186" s="2" t="s">
         <v>890</v>
       </c>
-      <c r="I186" s="2" t="s">
-        <v>891</v>
-      </c>
-      <c r="J186" s="2" t="s">
-        <v>141</v>
+      <c r="I186" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fixed 2026-09-03 - one live security run still needed to confirm end to end. All three causes addressed. (A) Egress: ProjectProfile.scan.registries is merged into the companion's extra_allowed_hosts at dispatch via _phase_extras, which is the server-side declaration path the guardrails comment itself said did not exist. (B) Provisioning: bandit, pip-audit and cyclonedx-bom pinned in backend/requirements.txt so the companion has them after a normal install, rather than the agent being asked to pip install mid-run. (C) Honesty: see S.No 186. Requires migration projects.0012, which adds the scan column with a database default so a branch without the field can still insert.</t>
+        </is>
+      </c>
+      <c r="J186" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fixed</t>
+        </is>
       </c>
     </row>
     <row r="187" spans="1:10" ht="232.5" x14ac:dyDescent="0.35">
@@ -10491,11 +10528,15 @@
       <c r="H187" s="2" t="s">
         <v>895</v>
       </c>
-      <c r="I187" s="2" t="s">
-        <v>896</v>
-      </c>
-      <c r="J187" s="2" t="s">
-        <v>141</v>
+      <c r="I187" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fixed 2026-09-03. agents/10_security/agent.md must now open with a Scan Provenance table, before any finding, labelling every SAST / SCA / SBOM step as TOOL-RUN (with the command and its exit status), MANUAL (with the reason no tool ran) or CI-GATE (with where it is configured). Ticking a tool checkbox for a manual step is forbidden, and a tool expected for the language but unavailable must be raised as an info finding so the reviewer at the gate sees the coverage gap. Shipped AHEAD of S.No 185's provisioning work, because it turns a misleading report into an honest one immediately.</t>
+        </is>
+      </c>
+      <c r="J187" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fixed</t>
+        </is>
       </c>
     </row>
     <row r="188" spans="1:10" ht="248" x14ac:dyDescent="0.35">
@@ -11282,8 +11323,15 @@
       <c r="H215" s="2" t="s">
         <v>1026</v>
       </c>
-      <c r="J215" s="2" t="s">
-        <v>141</v>
+      <c r="I215" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fixed 2026-09-03, except the enrollment POST - see S.No 35. Two layers. (1) The remaining anonymous writes now require a session: project create, profile, export-policy, source-documents, traceability and onboard-atlassian; every WorkItemViewSet write; RunViewSet take-over and resume; and runner revoke. (2) Editing the project profile additionally requires tech_lead or admin, because it re-steers every agent that will ever run on the project. Trigger, build, take-over and resume require project MEMBERSHIP rather than a lead role - each role drives its own phase (a Product Owner triggers ideation, an Engineer triggers implementation), so a lead-only bar would lock most of the team out of ordinary work. Membership also closes a hole of its own: IsAuthenticatedMember only ever checked for a session, so a signed-in user could act on a project they were not a member of.</t>
+        </is>
+      </c>
+      <c r="J215" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fixed</t>
+        </is>
       </c>
     </row>
     <row r="216" spans="1:10" ht="170.5" x14ac:dyDescent="0.35">
@@ -11420,8 +11468,15 @@
       <c r="H221" s="2" t="s">
         <v>1041</v>
       </c>
-      <c r="J221" s="2" t="s">
-        <v>141</v>
+      <c r="I221" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fixed 2026-09-03. A new shared ErrorState primitive in components/ui is rendered BEFORE the empty check on all five screens that read a failed request as an empty list: Dashboard, Traceability, Artifacts registry, Admin users and Repositories. One shared primitive rather than five inline banners, because the finding is that five screens independently forgot the same case, and a single component is what makes the sixth screen inherit the behaviour. 15 tests, each asserting the error appears AND that the reassuring empty-state copy does not.</t>
+        </is>
+      </c>
+      <c r="J221" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fixed</t>
+        </is>
       </c>
     </row>
     <row r="222" spans="1:10" ht="201.5" x14ac:dyDescent="0.35">
@@ -12325,12 +12380,12 @@
       </c>
       <c r="I244" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not fixed. The PRODUCT fix is routed through the platform itself as TASK-050 (WI-212) under WI-56/FOUND-003 in tenant 9dd11483 - one enableCors({ origin: FRONTEND_URL, credentials: true }) call in packages/backend/src/main.ts plus preflight e2e tests - deliberately built, reviewed and merged by the normal build loop rather than hand-patched, so the fix is itself a test of the pipeline. The PLATFORM finding is the open item: the code review agent is never given the work item's acceptance criteria to verify delivery against. Candidate fix - include the work item's acceptance criteria verbatim in the 08_code_review manifest and require an explicit per-criterion verdict before a review may report zero blocking findings.</t>
+          <t xml:space="preserve">Fixed 2026-09-03. The root cause recorded on this row was wrong, and building to it would have fixed nothing: agent 08 IS given the acceptance criteria (the work item goes to the manifest composer) and has always carried the Step 4a cross-reference. The real gap was the OUTPUT contract - nothing required a per-criterion verdict, so an APPROVED verdict with an empty findings array looked identical whether the agent had checked four criteria or skimmed the diff. Two halves shipped: agent 08 must now emit an acceptance_criteria array (criterion text verbatim, met / not_met / not_verifiable, concrete evidence, and any not_met also raised as a blocking finding), and guard_acceptance_criteria fails the build CLOSED when an approving verdict does not satisfy it. It deliberately does not fire when no criteria can be parsed, or when the review already demands changes. This also needed truncation register T2, which was letting the criteria be cut from the manifest before any agent read them.</t>
         </is>
       </c>
       <c r="J244" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Open</t>
+          <t xml:space="preserve">Fixed</t>
         </is>
       </c>
     </row>

--- a/docs/Bugs.xlsx
+++ b/docs/Bugs.xlsx
@@ -281,7 +281,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1830" uniqueCount="1078">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1834" uniqueCount="1082">
   <si>
     <t>S.No</t>
   </si>
@@ -3694,6 +3694,18 @@
   </si>
   <si>
     <t>None — logged for triage. Suggested direction: scope clarification-related events in the manifest to the CURRENT work item, or carry the answers alongside the events so an agent never sees a question without its answer. See section 5 of docs/INCIDENT_2026-07-30_clarifications_gate.md.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FIXED (verified 2026-09-07). Already shipped: the build workflow's dispatch now sits inside a `while True:` loop (backend/orchestration/build_workflow.py line 118), and a first report that failed because the ENGINE went away is classified by is_engine_exit and PARKED as resumable with resume_from='dispatch_build' (line 158-163) instead of being routed to mark_build_failed. On Resume the loop re-dispatches the build; the Temporal workflow stays open, so the run can still be signalled. That is exactly the fix this row planned. A genuine build failure (the code did not build) still ends the run, which is correct - only the engine disappearing is resumable.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fixed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FIXED (verified 2026-09-07). Team-selected Option A is live: every pending-approval row carries a button that loads THAT gate into the existing right-side decision panel (frontend/src/features/lifecycle/Gates.tsx lines 220-224), and the selected row is highlighted (line 241). The panel layout is unchanged - no new drawer or cards. A `?gate=&lt;id&gt;` deep link opens the named gate (line 64), and a link naming a gate that is no longer pending selects NOTHING and says so rather than silently falling back to the first gate (line 75). Gates can now be reviewed and decided in any order.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FIXED (verified 2026-09-07). The recovery screen now fetches the run the link names instead of discarding the parameter (frontend/src/features/observability/OfflineTakeover.tsx lines 24-35), and BOTH loading branches are guarded (line 45), so a deep link no longer flashes 'No parked runs' while its request is still in flight. A run id that does not resolve now reports that plainly. The run console produces the `?run=&lt;id&gt;` URL, so the feature is reachable from both ends - fixing only one side would have left it unreachable.</t>
   </si>
 </sst>
 </file>
@@ -10376,10 +10388,10 @@
         <v>869</v>
       </c>
       <c r="I182" s="2" t="s">
-        <v>870</v>
+        <v>1078</v>
       </c>
       <c r="J182" s="2" t="s">
-        <v>141</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="183" spans="1:10" ht="409.5" x14ac:dyDescent="0.35">
@@ -10620,10 +10632,10 @@
         <v>910</v>
       </c>
       <c r="I190" s="2" t="s">
-        <v>911</v>
+        <v>1080</v>
       </c>
       <c r="J190" s="2" t="s">
-        <v>141</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="191" spans="1:10" ht="372" hidden="1" x14ac:dyDescent="0.35">
@@ -11399,8 +11411,11 @@
       <c r="H218" s="2" t="s">
         <v>1034</v>
       </c>
+      <c r="I218" s="2" t="s">
+        <v>1081</v>
+      </c>
       <c r="J218" s="2" t="s">
-        <v>141</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="219" spans="1:10" ht="341" x14ac:dyDescent="0.35">

--- a/docs/Bugs.xlsx
+++ b/docs/Bugs.xlsx
@@ -281,7 +281,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1834" uniqueCount="1082">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1851" uniqueCount="1099">
   <si>
     <t>S.No</t>
   </si>
@@ -3706,6 +3706,162 @@
   </si>
   <si>
     <t xml:space="preserve">FIXED (verified 2026-09-07). The recovery screen now fetches the run the link names instead of discarding the parameter (frontend/src/features/observability/OfflineTakeover.tsx lines 24-35), and BOTH loading branches are guarded (line 45), so a deep link no longer flashes 'No parked runs' while its request is still in flight. A run id that does not resolve now reports that plainly. The run console produces the `?run=&lt;id&gt;` URL, so the feature is reachable from both ends - fixing only one side would have left it unreachable.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOT FIXED - SPECIFIED. The team chose the full redesign and asked for it written up and parked, not built in this batch. The spec is docs/CONNECT_MACHINE_REDESIGN_SPEC.md (P2 batch, commits 96803a6 and bb7cae6). This row stays OPEN until it is built.
+WHAT THE SPEC ESTABLISHES, in short:
+CONNECTING A MACHINE READS LIKE ONE STEP AND IS NINE. Install Python; clone the platform's OWN source repository; install its dependencies; install and sign in to Claude Code; install git and clone a copy of each project repository; run an enrol command from inside that checkout with two long ids; copy the token out of the terminal; run a serve command with the token on the command line. The token everybody talks about is step 8 of 9. The spec lists all nine so the work cannot quietly shrink back to 'fix the token'.
+THE COMPLAINT IN THIS ROW IS STRUCTURAL, NOT COSMETIC. The companion is not a package - there is no packaging of any kind - and it runs from a clone of the platform because it reaches back into the platform's code at startup. That is literally why a user has to be in the backend repository. No amount of installer polish removes it.
+BUT THE COUPLING IS SMALL AND COUNTABLE: four modules, none of which needs the platform's web framework at runtime. Extraction is bounded work, not a rewrite. This is the finding that makes the whole plan affordable.
+TWO STEPS CAN NEVER BE AUTOMATED AWAY: signing in to Claude Code, which Anthropic owns, and agreeing to let software touch your code, which is a person's decision. 'Zero manual steps' is not reachable; 'two clicks and one sign-in' is. Stated plainly so the goal is not later restated as the former.
+FIVE LAYERS, each shipping alone: make it installable; a signed installer; pairing in the browser instead of a token; a setup assistant that turns each prerequisite into a button; and keeping it running. Layer one is about a third of the work and is also what lets the anonymous enrolment endpoint be closed, so it goes first whatever else happens.
+ALL FOUR FINDINGS ON THIS ROW ARE ONE QUESTION - how does a headless machine authenticate - and layer three answers it once. S.No 138 is folded in for the same reason.
+START CODE SIGNING BEFORE THE CODE: certificates cost money and have lead times, and unsigned installers are blocked by Windows and refused by macOS. It is the only item whose delay cannot be absorbed by working harder.
+COSTING: roughly 2.5-3 weeks for layers 1-3, 6-8 weeks for all five. A CORRECTION to an earlier estimate of 7-9 days, which assumed packaging that does not exist.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Open</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FIXED (P2 batch, commit dcfb579).
+WHAT WAS WRONG: the AI agent that writes code could also change the STATUS of the work item it was working on. It could mark its own task finished, or push it back to 'not started', or park it in a state that nothing in the platform ever moves an item out of.
+WHY THAT MATTERS: whether a piece of work is done is a decision for a person at a gate, not for the thing doing the work. An agent marking its own homework is how a task reaches 'done' with nobody having reviewed it.
+A CORRECTION TO THIS ROW: this was already HALF fixed before the batch started, by commit 83a2036, which stopped the agent setting 'done' specifically. The row did not say so. What was left open was every OTHER state, which was still reachable.
+THE FIX: the rule was inverted. Instead of a list of states the agent may NOT set (which has to be remembered and extended every time a state is added), there is now a list of the one state it MAY set - 'in progress', when it starts work, which is the single transition the agent's own instructions tell it to make. Everything else is refused with a message saying what it is allowed to do. A state added later is refused by default rather than quietly permitted until somebody remembers the list.
+That prediction was tested immediately: the 'cancelled' state added in S.No 140 was refused by this rule with no extra code, and there is a test asserting it.
+VERIFIED: a test per forbidden state (proposed, accepted, in review, blocked, done, cancelled) asserts a 403 AND that the item was not written anyway; the agent's legitimate move to 'in progress' still works; the platform's own transitions are untouched, because they do not go through the agent's entry point.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FIXED (P2 batch, commit 411d96a). New ADR: docs/decisions/0005-the-platform-observes-the-code-host-it-does-not-police-it.md
+WHAT WAS WRONG: when a developer merged a pull request on GitHub by hand, instead of letting the platform merge it after the gate was approved, the run sat waiting for an approval nobody would ever give. The work item never reached done, its artefacts stayed as drafts, and the preview environment was never torn down. The reviewer was looking at a panel asking them to approve a merge that had already happened, with nothing on screen saying so.
+A CORRECTION TO WHAT WAS REPORTED EARLIER: I said an approval would then hit GitHub's merge API, get a 405, and park in a retry loop. That is WRONG. The merge step already reads the pull request first and does nothing if it is already merged - its own docstring says it is idempotent. So the run completes correctly the moment ANY approval arrives. This made the fix much smaller and much safer than described.
+THE REAL BUG: nobody ever approves, and nothing tells anybody they should.
+THE FIX, and the team's choice of shape: the platform DETECTS the external merge and says so; a HUMAN still decides. Nothing in the platform ever approves a gate.
+ - The webhook now captures who merged it and when (GitHub sends both; both were being thrown away) and writes that onto the pending gate as a note.
+ - The Gates screen shows it: 'Already merged on GitHub - merged outside the platform by &lt;name&gt; on &lt;date&gt;', and the button becomes 'Acknowledge merge &amp; complete'. Same endpoint, same role check, same audit trail as any other approval.
+ - Because webhooks are not guaranteed delivery, a sweep runs when the Gates screen is read: it finds gates stuck past an hour, asks GitHub whether the PR was merged, and ANNOTATES only. It never decides.
+WHY HUMAN ACKNOWLEDGEMENT, RECORDED: the webhook secret is a single global setting and the workspace is named in the URL, so anyone able to sign a payload could aim one at any workspace. Because detection only annotates, the worst a forged delivery can do is add a false note that a person must still act on. That containment is the reason this shape is right, and it is why the ADR exists.
+STILL NEEDED FOR THIS TO WORK LIVE: a reachable webhook URL and GITHUB_WEBHOOK_SECRET set on the deployment. The sweep is also the only thing that will recover the run already stranded today - no webhook fires retroactively for it.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOT FIXED - FOLDED INTO S.No 35 by team decision, and specified there. Stays OPEN.
+WHY THEY ARE THE SAME BUG: enrolling a machine from the command line has no logged-in session, so WHO OWNS an enrolment is whatever identifier a human typed on the command line - or nobody, if they typed nothing. And once a token exists, it authenticates any machine holding it. Two developers sharing one enrolment record is the expected outcome of that design, not a mishap.
+That matters because dispatch routes work to a companion BY the developer on the enrolment. Sharing one record means runs, claims and attribution can be conflated, per-developer accounting is wrong, and debugging 'whose machine claimed what' becomes guesswork.
+WHY IT IS NOT FIXED SEPARATELY: giving each developer their own record does not help while the only way to create one is a command that cannot tell who is running it. Layer three of the Connect Machine spec makes the person who clicks Approve in the browser the owner, with no other path to an enrolment - which removes the possibility rather than patching the symptom.
+WHEN IT IS BUILT: the spec's migration section requires existing shared enrolments to be identified and reported BEFORE they are broken up. A run attributed to the wrong person is bad; a developer whose companion silently stops claiming work mid-sprint is worse.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FIXED (P2 batch, commits 41b9068 and 76de57b). NEEDS A MIGRATION RUN - see the end.
+WHAT WAS WRONG: there was no way to say 'this is not going to happen'. A duplicate, a defect nobody will fix, a task overtaken by a later decision - the only two options were to mark it done, or leave it open for ever.
+WHY THAT MATTERS: marking it done puts a lie into every report that counts finished work. Leaving it open for ever is how a board stops being read at all. Finished and abandoned are different facts and the platform could only record one of them.
+THE FIX: work items gained a second final state, 'cancelled', which only a person can set.
+ - A tech lead or admin can cancel from the task page, from the defect page ('Won't fix...'), from the run console beside Retry (where the decision usually gets made, watching a build fail again), and from a row menu in the Work Items list, for clearing several stale items without opening each one.
+ - The dialog ASKS WHY, as a short list of standing reasons rather than an empty box a busy person leaves blank. In six months that sentence is the only answer to 'why is this cancelled'. Marking something done by hand needs no reason - the work is the reason.
+ - Cancelled items come off the board by default, but the board SAYS how many it is hiding and one click brings them back. Nothing disappears silently. The dashboard count excludes them too, so the number and the board cannot disagree.
+TEAM DECISION - CANCELLING A DEFECT RELEASES THE GATE IT WAS BLOCKING: a defect nobody will ever fix must not hold a story shut for ever. On its own that would let 'we won't fix this' quietly become 'this passed', so the release and the disclosure ship together: every gate still waiting on that story gains a checklist line naming the defect, who cancelled it and why, and the reviewer must tick it before they can approve. The dialog warns about this BEFORE the decision, not after.
+MAKING IT STICK: six places moved a work item without asking what state it was already in - a merged pull request, a rejected gate, a failed build, the test and accessibility defect loops, and the remediation board. Every one of them would have quietly resurrected a cancelled item. They now leave it alone, and the skip is recorded rather than silent.
+FOUND WHILE FIXING THIS: the board's status badge fell through to 'Draft' for anything it did not recognise, so FOUR of the six states rendered as drafts - an item in review, blocked, or accepted, as well as a cancelled one. Now an exhaustive list, and the state is a proper type, so the next state added is a build error in every place that must handle it rather than a wrong label on screen. That change also found dead code: the board tested for a 'running' state that work items have never had.
+VERIFIED: 18 backend tests and 16 frontend tests; two of the guards were proved load-bearing by removing them and watching the tests fail. Also driven end to end in the browser - cancelled a task and a defect, watched the board hide them and the gate raise its acknowledgement and refuse approval until it was ticked.
+OUTSTANDING: migration workitems/0007 must be run by the team. It only changes a list of allowed values - no table is touched and the SQL it generates is empty - so it is safe to run at any time, including while an older release is still serving.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOT FIXED THIS BATCH - APPROVED AND SEQUENCED. The team approved option 3 and chose to do it AFTER one live security run, so the change is made against real observed output rather than an assumption about it. Stays OPEN.
+Nothing about this was rejected or dropped; it is waiting on evidence, not on a decision.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FIXED (P2 batch, commits 3bdb017 and 8a583b2).
+WHAT WAS WRONG: the security phase produces a software bill of materials - the list of every third-party package the product depends on, and its licence. It is written as JSON, because machines read it. The preview screen was told, by hardcoded assumption, that EVERY internal document is markdown, so the JSON was handed to the markdown renderer and collapsed into one unreadable run-on blob.
+WHY THAT MATTERS: the bill of materials is the artefact somebody opens to answer 'what are we shipping, and are we allowed to ship it'. It was unreadable to the person who needed it.
+TWO THINGS FOUND ON THE WAY: the platform already had a mechanism for an artefact to declare its format, and BOTH halves of it were dead - the list of known formats did not include JSON, and nothing anywhere ever set the format. Neither half had ever run.
+THE FIX:
+ - The platform now tells the truth about an artefact's format instead of assuming, and an agent can declare it outright rather than leaving the platform to guess.
+ - The bill of materials is RENDERED for people: headline figures (how many components, how many licences, which scanner produced it, when, which standard), then a components table, then any known vulnerabilities. A large one is SUMMARISED rather than cut off, with the count stated, so a reader is never silently shown a partial inventory.
+ - 'View raw' shows the stored file exactly as saved, and switches back.
+THE CONSTRAINT THAT SHAPED IT: three different things read that stored file - the preview screen, the publish step, and the agents themselves. Rendering it for all three would hand an agent a table where it asked for parseable data. The renderer is attached to the PREVIEW only, and a test asserts the other two still get byte-identical raw JSON.
+ALSO CLOSED A LATENT VERSION OF THE SAME BUG: the architecture agent was told to produce an 'OpenAPI-style specification' with nothing pinning the format. It happens to emit prose today; the instruction now says so explicitly, so it cannot silently become raw YAML and break identically.
+STILL AN OPEN PRODUCT QUESTION FOR THE TEAM: when a bill of materials is PUBLISHED to a system of record, should it push the raw file or the rendered table? Publish still pushes raw. Noted, not answered.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FIXED (P2 batch, commit 76b6475). Fixed together with S.No 223 - one screen, one change.
+WHAT WAS WRONG: the Connect Machine screen had a placeholder token written into the code as a stand-in for the real thing. It was used in two places: as the fallback when there was no token yet, AND in the error handler. So when generating a token FAILED, the screen set the placeholder - and because the screen decided 'we have a token, therefore it worked', a failure rendered as a SUCCESS.
+WHY THAT MATTERS: the user was shown a copyable token, told it was theirs, and it could never authenticate anything. They would take it to their machine and get an unexplained failure there instead, with nothing connecting the two.
+THE FIX: the placeholder is deleted outright - not replaced with a better placeholder. The success view is now reachable only by a genuine success. A failure shows the server's own message. The command shown before a token exists says &lt;your-token&gt; rather than pretending to be one.
+ALSO GUARDED: a brand-new workspace with no project yet was sending an empty project and getting a rejection it could not explain. The screen now says 'create a project first', with a link, and sends nothing.
+FOUND AGAINST REAL DATA, NOT IN A TEST: a person with three roles on one project appeared in the project picker three times, because the platform stores one row per role. The picker now lists each project once.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FIXED (P2 batch, commit 8355f94). NEEDS A MIGRATION RUN AND A PRE-CHECK - see the end.
+WHAT WAS WRONG: nothing stopped two projects in one workspace having the same name.
+WHY THAT MATTERS: every screen that names a project - the project switcher, the board header, an invitation - named two different things identically, and the wrong one could be worked on for days before anyone noticed.
+THE BEST PART: the screen that reports this was ALREADY BUILT. Create Project already says 'A project named X already exists in this workspace' - it just waits for the server to return a 409 conflict, and the server never returned one, or anything else. So the fix needed no frontend change at all; it lit up an existing message.
+THE FIX: the database now enforces one name per workspace, and the API returns the 409 the screen was waiting for. Blank and whitespace-only names are rejected too - those were being accepted.
+CASE-INSENSITIVE, deliberately: 'Billing Service' and 'billing service' are the same project to a person reading a list, and allowing both would leave exactly the confusion this fixes.
+A DECISION THE TEAM TOOK: an archived project KEEPS its name reserved. Un-archiving a project to find its name had been taken by something else would be the worse surprise.
+OUTSTANDING - PLEASE READ BEFORE RUNNING THE MIGRATION: migration projects/0013 will FAIL if two projects already share a name. Run the check as the postgres owner before migrating and rename any duplicates first. Note that running the check as the application user reports zero rows whether or not there are duplicates, because row-level security hides other tenants' rows from it - that is not a clean result, it is no result.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOT IN THIS BATCH - DROPPED BY TEAM DECISION, deliberately, so it is not re-litigated later. Stays OPEN.
+The Work Items dashboard redesign will own this. Fixing the lifecycle rail here would have meant building something the redesign then replaces - work done twice, and a screen that changes twice for the people using it.
+This row is not a lower priority than the rest of the batch; it has a different owner.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FIXED (P2 batch, commit 93f05d0).
+WHAT WAS WRONG: seven places did something on the user's behalf and, when the server refused, showed nothing at all. An invitation resend that quietly did nothing. A repository refusal caught and thrown away. A button that flipped back as if nothing had been asked. Three password forms that sat there in silence.
+WHY THAT MATTERS: a person cannot tell 'it failed' from 'I mis-clicked', so they try again, and again. The most common failure - 'you need the tech lead role for this' - is one they could act on immediately if anyone told them.
+THE ROOT CAUSE, in one line: the platform had a shared way to report a failed READ and no shared way to report a failed WRITE. So four screens each invented their own spelling and three more gave up.
+THE FIX: one shared way to show a failed write, used everywhere, which is what stops a fifth screen inventing a fifth. Deliberately with NO retry button - retrying a write is a re-submit, not a refetch, and offering one invites a duplicate.
+The password forms now put the server's complaint ON THE FIELD it names ('this password is too short') and fall back to a banner when the server names no field. Several screens were checking for one specific failure and dropping everything else; the default now always shows something.
+ONE EXTRA DEFECT FOUND AND FIXED HERE: the password reset form asked you to confirm your new password and then never compared the two. A mistyped confirmation silently accepted the FIRST value - you set a password you did not think you set, and the server cannot detect this because it is only ever sent one. Fixed in the same change.
+STILL TRUE AND WORTH KNOWING: 'Set default' on the Repositories screen does nothing. That is not this bug - there is no endpoint behind it yet.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FIXED (P2 batch, commit ae34363).
+WHAT WAS WRONG: a project in this platform is one of two kinds. Greenfield means you are building something new - there is no code yet. Brownfield means there is an existing codebase to bring in. Onboarding is the wizard for the second kind: it reads your repositories, indexes the code and reports the gaps.
+It was offered to everybody. And the page did not merely appear where it should not - it ASSERTED the wrong thing. It put a 'Brownfield' badge at the top and said 'Brownfield project. Let's assess what already exists' over whatever project you had open. On a project started from scratch that morning, that sentence is simply false.
+A CORRECTION TO WHAT I TOLD THE TEAM: I described the project kinds as greenfield / brownfield / multi. There are only TWO. 'Multi' is a different field, about how many repositories a project has. Nothing depended on the error, but the row should not carry it.
+THE BLOCKER, AND WHAT IT NEEDED: the screen could not check the project's kind because it did not have it. The signed-in user carries a list of their projects - id, name, and the role they hold - and nothing about the projects themselves. The kind now travels with it, the same way the role already does, at no extra cost.
+THE FIX (team chose 'hide it', over 'grey it out with a reason'):
+ - The sidebar does not offer Onboarding on a project started from scratch. A menu item you can never usefully click is clutter, and a permanently dead row in every new project's sidebar is worse than an absence.
+ - All three onboarding addresses explain themselves if reached directly, rather than running a wizard or asserting the wrong thing. Hiding a link is not closing a door - the address can still be typed, bookmarked, or carried over from another project.
+ - The server refuses too, and says why. The menu disappearing is not a guarantee.
+TEAM DECISION: uploading a specification document is arguably useful on a new project too, but it is hidden with the rest for now - it is only reachable from the hub anyway, and 'let a new project upload a spec' is worth designing properly rather than leaving as a side door.
+A DETAIL WORTH KEEPING: both the menu and the guard hide only on an explicit 'greenfield'. If the server is briefly older than the app during a deployment and says nothing, the item STAYS - a brownfield team must never be locked out of the screen that starts their lifecycle.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FIXED (P2 batch, commit 76b6475). Fixed together with S.No 198 - one screen, one change.
+WHAT WAS WRONG: the Connect Machine screen showed a 'Projects' picker that did nothing at all. It had no value, no handler and no state behind it - it was decoration. Whatever you selected, the token was always issued against the FIRST project in your list. It also carried a second piece of made-up data: a hardcoded project name in the list.
+WHY THAT MATTERS: a developer on several projects would connect their machine, believe it was enrolled for the project they picked, and find their phases dispatched somewhere else - with the screen having told them otherwise.
+THE FIX: the picker is real, it drives what is sent, and it defaults to the project you currently have open. The invented project name is gone.
+MADE SINGLE-SELECT, deliberately: the enrolment API binds one machine registration to one project. A multi-select was a promise the server cannot keep. Enrolling one machine for several projects at once is part of the Connect Machine redesign (S.No 35), not something to imply with a control that cannot deliver it.
+A BUG FOUND BY THE NEW TESTS: the first version of this fix read the project once, before the user's details had loaded, and then never again - so it stayed empty for ever. Caught before it shipped, and the fix now re-reads it as the page settles.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FIXED (P2 batch, commit 92c3d18).
+WHAT WAS WRONG: once a work item had been exported to Jira, the platform stored the Jira issue key and treated it as permanently true. If somebody deleted that issue in Jira, the platform went on holding a key that pointed at nothing - with no way to notice and no way to repair it.
+WHY THAT MATTERS: the work item silently stops being tracked anywhere. It is not re-created, because the platform believes it already exists.
+THE FIX: before trusting a stored key, the platform now asks the tracker whether that issue still exists. If it is genuinely gone, the pointer is cleared and the item is exported again.
+THE SAFETY RULE THAT MAKES THIS SAFE, and it is the most important line in the change: ONLY 'not found' and 'gone' count as gone. An expired token, a permissions error, rate limiting, or Jira being down leave the pointer completely untouched. Without that rule, one expired token would have wiped every pointer in the project in a single pass and re-created every issue as a duplicate. There is a test for each of those failure kinds.
+A CAVEAT RECORDED RATHER THAN FIXED: the platform matches an existing issue by its EXACT title, so two work items with identical titles would both adopt the same Jira issue. Worth knowing; not fixed here.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FIXED (P2 batch, commit 92c3d18). Fixed alongside S.No 236 - same file, same pass.
+WHAT WAS WRONG: when exporting a project's backlog to Jira, the platform only considered items in the very first state, 'proposed'. Anything that had moved on - into implementation, review, or done - could never be exported, ever.
+WHY THAT MATTERS: in the SpendLog project, 70 of 109 items were permanently ineligible. The backlog in Jira could never be a true picture of the work.
+THE FIX: candidates are now chosen on 'has no tracker id yet', which is the actual question, instead of on what stage the work has reached. An item's progress no longer decides whether it is allowed to be tracked.
+THE TEAM'S EXPLICIT RULE, AND THE TRAP IT AVOIDS: the export used to force every item it touched to 'accepted'. That was harmless while only brand-new items were eligible. With the above change it would have dragged completed work backwards and destroyed the history - exactly the trap that made the July recovery need a snapshot-and-rewind script. So an export now only promotes an item that has not started; anything further along keeps its state. There is a test that fails loudly if that guard is ever removed.
+ONE MORE THING FOUND AND CLOSED: the export was scoped to epics, stories and tasks. Defects and test cases are created directly in progress, so the change above would have made hundreds of them eligible and flooded Jira on the first run.
+AND A REFUSAL ADDED: if the project has no Jira project key configured, the platform now refuses to export rather than creating issues blindly with no way to find them again.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FIXED (P2 batch, commit 93f05d0).
+WHAT WAS WRONG: seven places did something on the user's behalf and, when the server refused, showed nothing at all. An invitation resend that quietly did nothing. A repository refusal caught and thrown away. A button that flipped back as if nothing had been asked. Three password forms that sat there in silence.
+WHY THAT MATTERS: a person cannot tell 'it failed' from 'I mis-clicked', so they try again, and again. The most common failure - 'you need the tech lead role for this' - is one they could act on immediately if anyone told them.
+THE ROOT CAUSE, in one line: the platform had a shared way to report a failed READ and no shared way to report a failed WRITE. So four screens each invented their own spelling and three more gave up.
+THE FIX: one shared way to show a failed write, used everywhere, which is what stops a fifth screen inventing a fifth. Deliberately with NO retry button - retrying a write is a re-submit, not a refetch, and offering one invites a duplicate.
+The password forms now put the server's complaint ON THE FIELD it names ('this password is too short') and fall back to a banner when the server names no field. Several screens were checking for one specific failure and dropping everything else; the default now always shows something.
+ONE EXTRA DEFECT FOUND AND FIXED HERE: the password reset form asked you to confirm your new password and then never compared the two. A mistyped confirmation silently accepted the FIRST value - you set a password you did not think you set, and the server cannot detect this because it is only ever sent one. Fixed in the same change.
+STILL TRUE AND WORTH KNOWING: 'Set default' on the Repositories screen does nothing. That is not this bug - there is no endpoint behind it yet.
+A FOLLOW-UP IN THE SAME ROW (commit 403060f), found by LOOKING at the screen rather than by a test: the message shown when 'Generate script' fails sat in an unbounded table cell and sprawled across to the table edge, reading as loose text rather than something attached to the button that had failed. The test asserted the message appears, and it did - only the screenshot showed it appearing badly. It is now capped and sits directly under its own button. A passing test says the thing is there; only looking says it is right.</t>
   </si>
 </sst>
 </file>
@@ -5931,13 +6087,11 @@
       <c r="G36" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="I36" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">NOT FIXED - notes for this redesign (2026-09-03). Four findings belong to it, and they are all one question: how does a headless machine authenticate? (1) Disconnect revokes exactly one enrollment row, so a developer who generated three tokens still holds two working ones after clicking it. (2) The enrollment token is passed on the command line, so any process listing on that machine reveals it (multi_project_recon C1). (3) Enrollment tokens never expire (C4). (4) Found while closing S.No 214: POST /api/runners/ still accepts an anonymous caller, and was deliberately LEFT OPEN, because the documented CLI onboarding (runner/README.md Quick start step 1) sends only a tenant header and has no session to present. Closing that half on its own breaks onboarding while answering none of the credential model.</t>
-        </is>
+      <c r="I36" s="2" t="s">
+        <v>1082</v>
       </c>
       <c r="J36" s="2" t="s">
-        <v>141</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="37" spans="1:10" ht="232" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
@@ -7517,10 +7671,10 @@
         <v>381</v>
       </c>
       <c r="I88" s="2" t="s">
-        <v>382</v>
+        <v>1084</v>
       </c>
       <c r="J88" s="2" t="s">
-        <v>141</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="89" spans="1:10" ht="279" x14ac:dyDescent="0.35">
@@ -7549,10 +7703,10 @@
         <v>387</v>
       </c>
       <c r="I89" s="2" t="s">
-        <v>388</v>
+        <v>1085</v>
       </c>
       <c r="J89" s="2" t="s">
-        <v>141</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="90" spans="1:10" ht="409.5" hidden="1" x14ac:dyDescent="0.35">
@@ -9137,10 +9291,10 @@
         <v>671</v>
       </c>
       <c r="I139" s="2" t="s">
-        <v>672</v>
+        <v>1086</v>
       </c>
       <c r="J139" s="2" t="s">
-        <v>141</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="140" spans="1:10" ht="409.6" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
@@ -9201,10 +9355,10 @@
         <v>822</v>
       </c>
       <c r="I141" s="2" t="s">
-        <v>823</v>
+        <v>1087</v>
       </c>
       <c r="J141" s="2" t="s">
-        <v>141</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="142" spans="1:10" ht="409.5" hidden="1" x14ac:dyDescent="0.35">
@@ -10301,10 +10455,10 @@
         <v>854</v>
       </c>
       <c r="I179" s="2" t="s">
-        <v>855</v>
+        <v>1088</v>
       </c>
       <c r="J179" s="2" t="s">
-        <v>141</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="180" spans="1:10" ht="217" hidden="1" x14ac:dyDescent="0.35">
@@ -10574,10 +10728,10 @@
         <v>900</v>
       </c>
       <c r="I188" s="2" t="s">
-        <v>901</v>
+        <v>1089</v>
       </c>
       <c r="J188" s="2" t="s">
-        <v>141</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="189" spans="1:10" ht="325.5" x14ac:dyDescent="0.35">
@@ -10893,10 +11047,10 @@
         <v>955</v>
       </c>
       <c r="I199" s="2" t="s">
-        <v>956</v>
+        <v>1090</v>
       </c>
       <c r="J199" s="2" t="s">
-        <v>141</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="200" spans="1:10" ht="372" hidden="1" x14ac:dyDescent="0.35">
@@ -11266,8 +11420,11 @@
       <c r="H212" s="2" t="s">
         <v>1019</v>
       </c>
+      <c r="I212" s="2" t="s">
+        <v>1091</v>
+      </c>
       <c r="J212" s="2" t="s">
-        <v>141</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="213" spans="1:10" ht="170.5" x14ac:dyDescent="0.35">
@@ -11312,8 +11469,11 @@
       <c r="H214" s="2" t="s">
         <v>1023</v>
       </c>
+      <c r="I214" s="2" t="s">
+        <v>1092</v>
+      </c>
       <c r="J214" s="2" t="s">
-        <v>141</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="215" spans="1:10" ht="248" x14ac:dyDescent="0.35">
@@ -11460,8 +11620,11 @@
       <c r="H220" s="2" t="s">
         <v>1039</v>
       </c>
+      <c r="I220" s="2" t="s">
+        <v>1098</v>
+      </c>
       <c r="J220" s="2" t="s">
-        <v>141</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="221" spans="1:10" ht="232.5" x14ac:dyDescent="0.35">
@@ -11513,8 +11676,11 @@
       <c r="H222" s="2" t="s">
         <v>1044</v>
       </c>
+      <c r="I222" s="2" t="s">
+        <v>1094</v>
+      </c>
       <c r="J222" s="2" t="s">
-        <v>141</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="223" spans="1:10" ht="170.5" x14ac:dyDescent="0.35">
@@ -11559,8 +11725,11 @@
       <c r="H224" s="2" t="s">
         <v>1049</v>
       </c>
+      <c r="I224" s="2" t="s">
+        <v>1095</v>
+      </c>
       <c r="J224" s="2" t="s">
-        <v>141</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="225" spans="1:10" ht="201.5" x14ac:dyDescent="0.35">
@@ -12043,15 +12212,11 @@
           <t xml:space="preserve">reconcile treats external_ref as durable truth and never checks the pointer still resolves in the system of record, so an external deletion creates a silent split-brain. external_ref is read-only on the API ('set by reconciliation, not by clients'), so there is no repair, force or re-publish path - recovering required direct database surgery to clear the stale pointers and rewind the states.</t>
         </is>
       </c>
-      <c r="I237" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Not fixed. Worked around by script: snapshot the affected items, clear the SoR keys, reset state to proposed, re-export, then restore the original states (reconcile forces ACCEPTED on success, which would otherwise erase 'done' on completed work). Suggested fix: validate the pointer on re-export and treat a 404 as 'not reconciled' so register-don't-recreate can recreate it, or expose an explicit repair action.</t>
-        </is>
-      </c>
-      <c r="J237" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Open</t>
-        </is>
+      <c r="I237" s="2" t="s">
+        <v>1096</v>
+      </c>
+      <c r="J237" s="2" t="s">
+        <v>1079</v>
       </c>
     </row>
     <row r="238" spans="1:10" ht="232.5" x14ac:dyDescent="0.35">
@@ -12093,15 +12258,11 @@
           <t xml:space="preserve">reconcile_backlog filters candidates on state=PROPOSED only. That is correct as an idempotency guard for a first export but means the export can never be re-run over a project's real backlog, and there is no way to push an implementation-phase item to the tracker at all.</t>
         </is>
       </c>
-      <c r="I238" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Not fixed. Restoring the full 57-item backlog needed a snapshot/rewind/restore script because a naive rewind would have flipped 21 completed items from done to accepted and lost that history. Suggested: select candidates on 'has no SoR id' rather than on state, so an item's lifecycle stage stops deciding whether it can be tracked.</t>
-        </is>
-      </c>
-      <c r="J238" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Open</t>
-        </is>
+      <c r="I238" s="2" t="s">
+        <v>1097</v>
+      </c>
+      <c r="J238" s="2" t="s">
+        <v>1079</v>
       </c>
     </row>
     <row r="239" spans="1:10" ht="232.5" x14ac:dyDescent="0.35">

--- a/docs/Bugs.xlsx
+++ b/docs/Bugs.xlsx
@@ -5159,7 +5159,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr filterMode="1"/>
-  <dimension ref="A1:J245"/>
+  <dimension ref="A1:J248"/>
   <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="7.81640625" style="2" bestFit="1" customWidth="1"/>
@@ -12590,6 +12590,180 @@
         </is>
       </c>
     </row>
+    <row r="246" spans="1:10" ht="232.5" x14ac:dyDescent="0.35">
+      <c r="A246" s="2">
+        <v>245</v>
+      </c>
+      <c r="B246" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The worker will not start at all once a queue has accumulated ten code versions - Temporal refuses the eleventh</t>
+        </is>
+      </c>
+      <c r="C246" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">On 2026-09-08 the team's stack would not start. The worker container exited immediately with a Temporal error reading 'update would exceed number of compatible version sets permitted in namespace dynamic config (11/10)'. Nothing was wrong with the code that had just been pulled, and nothing was wrong with the team's setup. The queue the worker serves had filled up.
+WHAT FILLS UP. Every time the worker starts, it registers a fingerprint of the code it is running so that only the newest code serves work (the fence added on 2026-08-26). Each fingerprint is registered as a brand-new, separate version group. Temporal allows a queue ten of those. The eleventh is refused, and the refusal is not caught, so it comes out as a crash with a stack trace.
+MEASURED THE SAME DAY on the shared server: queue sdlc-brown held 10 version groups (full - this is the one that would not start) and sdlc-planning held 7, three code changes away from the same wall. Build ids cannot be removed from a queue, so this cannot be cleaned up by waiting or by restarting.
+WHY IT LOOKS LIKE A DIFFERENT BUG. A worker that stands down because someone else has newer code exits SILENTLY after about three seconds. This one exits with a loud Python traceback. Same underlying cause as S.No 244, completely different symptom, which is why it was diagnosed as a separate problem.</t>
+        </is>
+      </c>
+      <c r="D246" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Temporal worker build-ID versioning (orchestration/worker_election._claim)</t>
+        </is>
+      </c>
+      <c r="E246" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bug</t>
+        </is>
+      </c>
+      <c r="F246" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Found 2026-09-08 while diagnosing why the team's worker container kept exiting. Measured live against 13.203.56.29: get_worker_build_id_compatibility reported 10 version sets on sdlc-brown (default 20260907T085207Z-4a30a56e8f43) and 7 on sdlc-planning (default 20260907T143603Z-7962c1135cae). Same family as S.No 242 and S.No 244; this is the third and last symptom of the same design.</t>
+        </is>
+      </c>
+      <c r="G246" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P1</t>
+        </is>
+      </c>
+      <c r="H246" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">worker_election._claim registers every badge with BuildIdOpAddNewDefault, which creates a NEW INCOMPATIBLE version set rather than adding the badge to the existing one. The badge changes on every code change, so the count of version sets on a queue grows by one per code change and never shrinks. Temporal's default cap is ten per queue (limit.versionCompatibleSetLimitPerQueue).
+The refusal arrives as gRPC FAILED_PRECONDITION. worker_election treats only PERMISSION_DENIED and UNIMPLEMENTED as 'versioning is off, carry on unversioned' (_VERSIONING_OFF), so FAILED_PRECONDITION propagates out of elect() and kills the process.
+NOTE the crash is the CORRECT behaviour and must not be 'fixed' by degrading to unversioned: a versioned build already owns the queue, and that fences unversioned workers out of newly started workflows, so the worker would come up looking healthy, poll happily and serve nothing. A per-person queue does not fix this either - it gives each person their own ten-change fuse, which is exactly what sdlc-brown, a dedicated per-stack queue, has just proved by filling up.</t>
+        </is>
+      </c>
+      <c r="I246" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not fixed. Two parts, and the first is needed even if the second lands.
+IMMEDIATE, for the queue that is already full: merge the existing version sets into one with Temporal's BuildIdOpMergeSets, keeping the live build as the merged default. No infrastructure change and no queue rename. Verified safe on sdlc-brown: all three of its running workflows carry use_versioning=False, so they sit in no version set and a merge cannot touch them. Merging cannot be undone.
+PERMANENT: register each new badge as COMPATIBLE with the current default (BuildIdOpAddNewCompatible with promote_set=True) instead of as a new default, so one set accumulates build ids rather than the queue accumulating sets. This is the same one-line change that fixes S.No 244 and closes S.No 242.
+REMAINING END, to be handled by the detector in S.No 246 rather than assumed away: build ids still accumulate inside the one set, against a separate and much higher per-queue cap. The detector must watch both counts and warn well before either is reached, so this can never again present as a dead stack. The deeper option, logged for later, is to derive the Temporal build id from the two WORKFLOW files only - they changed 21 times in the 203 code changes measured over two months - which requires moving the stale-worker fence somewhere other than the build id first.</t>
+        </is>
+      </c>
+      <c r="J246" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="247" spans="1:10" ht="232.5" x14ac:dyDescent="0.35">
+      <c r="A247" s="2">
+        <v>246</v>
+      </c>
+      <c r="B247" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nothing in the platform notices a run whose worker no longer exists - twelve dead jobs, up to 46 days old, none of them reported</t>
+        </is>
+      </c>
+      <c r="C247" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">This is the reason S.No 242 and S.No 244 were expensive rather than merely annoying. When a run's worker is gone, every surface still reports health. The workflow says Running. The worker says healthy and is polling. The queue says healthy. The screen shows the normal state - 'dispatched for review', or a Resume button, or a gate waiting for approval. No error is raised anywhere, no status turns red, and no reconciler picks it up.
+MEASURED 2026-09-08 on the shared server: 12 workflows that Temporal still called Running, and NOT ONE of them was being served. Two were genuine build orphans (pinned to the 2 Sep build after the queue moved to the 7 Sep build) - one of them started that same day. The other ten were older abandoned runs from before versioning existed, 12 to 46 days old. Nobody had noticed any of them.
+THE WORST CASE, live at the time of writing: TASK-038 (WI-95, run c639da98) is orphaned AND has a pending tech_lead merge gate. A reviewer can open the Gates screen, see a perfectly ordinary approval, click Approve - and nothing will happen, because the signal has no worker to land on. There is no way for that reviewer to find out. It will read as the platform being broken, not as a dead run.
+WHY THIS IS ITS OWN ROW. Orphaning is survivable; it is recoverable in minutes once you know. Not being told for 46 days is not survivable, and it is a different fix - detection, not versioning. Whatever variant of this appears next, this row is what makes it loud instead of silent.</t>
+        </is>
+      </c>
+      <c r="D247" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Run health / reconciliation (apps.runs.reconcile + the run and gate screens)</t>
+        </is>
+      </c>
+      <c r="E247" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bug</t>
+        </is>
+      </c>
+      <c r="F247" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Found 2026-09-08 by comparing every running workflow's most_recent_worker_version_stamp.build_id against the build id that currently owns its queue, on 13.203.56.29. sdlc-planning: 9 running, 9 not on the default build (oldest 46 days). sdlc-brown: 3 running, 3 not on the default build (oldest 35 days). QA tenant 9dd11483-4826-45b9-b011-52c4b5299c3a holds the two genuine orphans: TASK-038 = WI-95 run c639da98 (awaiting_gate, approval b69ae127) and TASK-039 = WI-96 run a6a01845 (stalled). Precedent for the diagnosis step is recorded on S.No 244.</t>
+        </is>
+      </c>
+      <c r="G247" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P1</t>
+        </is>
+      </c>
+      <c r="H247" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Temporal pins a running workflow to the build id it started on, for life, and offers no signal when no worker carries that build id any more - get_worker_task_reachability reports a retired build as still reachable for new workflows, so it cannot be used for this. The platform never asks the question either. Run status is written by the workflow itself, so a workflow that cannot be advanced also cannot update its own status: the last thing it wrote stays on screen for ever, and that last thing is always a healthy-looking state.
+There is no reconciler for this condition. apps.runs.reconcile recovers claims and stalled reports, which are cases where something CHANGES; an orphaned workflow changes nothing, which is precisely why nothing catches it.</t>
+        </is>
+      </c>
+      <c r="I247" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not fixed. Three parts, smallest first.
+1. DETECT. A reconciler pass that compares each non-terminal run's stamped build id against the build ids currently served on its queue, and marks the run when they do not match. Cheap, read-only, and it needs no new state.
+2. SAY SO. Surface it on the run console and - critically - on the gate panel, so a reviewer is told 'this run cannot be advanced' instead of being shown an Approve button that silently does nothing. Same treatment as the external-merge annotation from S.No 88: annotate, never decide.
+3. WATCH THE CEILINGS. The same pass counts version sets and build ids per queue and warns before either cap is reached, which is what stops S.No 245 ever presenting as a dead stack again.
+Recovery stays a human action - terminate and re-trigger, or merge the version sets when replay is safe. This row is about being told, not about deciding.</t>
+        </is>
+      </c>
+      <c r="J247" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="248" spans="1:10" ht="232.5" x14ac:dyDescent="0.35">
+      <c r="A248" s="2">
+        <v>247</v>
+      </c>
+      <c r="B248" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A worker that has been fenced out exits silently with no restart policy, so it presents as a crash loop with no explanation</t>
+        </is>
+      </c>
+      <c r="C248" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A QA member reported 'the worker keeps exiting'. It reads as a crash. It is the fence working exactly as designed, and saying so in a log line nobody was watching.
+WHAT ACTUALLY HAPPENS. If someone else on the same queue has newer code, the worker stands down - by design, so that old code never serves work. Standing down is a bare return in orchestration/worker.py, so the PROCESS ENDS, and the worker service in docker-compose.yml has no restart policy at all. So it is not a running worker that politely declines work; it is a stopped container. Restart it without pulling and it holds the same election, reaches the same answer, and exits again in about three seconds. Restart it again and the same.
+WHY IT COSTS DAYS. The person seeing this has no reason to connect 'my container will not stay up' with 'a colleague pulled newer code'. There is no error, no non-zero exit that says why, nothing on any screen, and the one log line that explains it scrolls past in a compose log they are not reading. Meanwhile their own in-flight builds are pinned to their now-retired build and are quietly dead (S.No 244), so the two symptoms arrive together and neither explains the other.
+This is not the versioning being wrong. It is the versioning being unexplainable to the person it happens to.</t>
+        </is>
+      </c>
+      <c r="D248" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Temporal worker startup / operator experience (orchestration.worker + docker-compose worker service)</t>
+        </is>
+      </c>
+      <c r="E248" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bug</t>
+        </is>
+      </c>
+      <c r="F248" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Found 2026-09-08 while reconciling two independent investigations of the same incident. Verified: worker.py line 60 returns on STAND_DOWN; docke